--- a/output/timesheet.xlsx
+++ b/output/timesheet.xlsx
@@ -16,8 +16,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="HH:MM"/>
+  </numFmts>
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,6 +32,9 @@
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="3">
@@ -57,11 +63,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -427,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -476,6 +485,2123 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Employee 32</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="4" t="n">
+        <v>0.2361111111111111</v>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151503.jpg</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>single punch only</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Employee 32</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>46264</v>
+      </c>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="4" t="n">
+        <v>0.2340277777777778</v>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151503.jpg</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>single punch only</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Employee 32</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>46263</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>0.7347222222222223</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>0.2270833333333333</v>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151503.jpg</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Employee 32</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>46261</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>0.7166666666666667</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>0.2361111111111111</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151503.jpg</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Employee 32</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>46260</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>0.7381944444444445</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>0.2256944444444444</v>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151513.jpg</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Employee 32</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>0.2375</v>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151513.jpg</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Employee 32</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>46258</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="E8" s="2" t="n"/>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151513.jpg</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>single punch only</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Employee 32</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>46257</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>0.7291666666666666</v>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>0.2506944444444444</v>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151513.jpg</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Employee 32</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>46256</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>0.7541666666666667</v>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>0.2388888888888889</v>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151518.jpg</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Employee 32</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>46254</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>0.7291666666666666</v>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>0.2222222222222222</v>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151518.jpg</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Employee 32</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>46253</v>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>0.7305555555555555</v>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>0.2215277777777778</v>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151518.jpg</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Employee 32</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>46252</v>
+      </c>
+      <c r="D13" s="2" t="n"/>
+      <c r="E13" s="4" t="n">
+        <v>0.2354166666666667</v>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151518.jpg</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>single punch only</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Employee 32</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>46251</v>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>0.7402777777777778</v>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>0.2472222222222222</v>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151526.jpg</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Employee 32</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>46250</v>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>0.7180555555555556</v>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>0.2298611111111111</v>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151526.jpg</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Employee 32</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>46249</v>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>0.7201388888888889</v>
+      </c>
+      <c r="E16" s="2" t="n"/>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151526.jpg</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>single punch only</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Employee 32</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>46247</v>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>0.7243055555555555</v>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>0.2479166666666667</v>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151526.jpg</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Employee 32</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>46246</v>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>0.7402777777777778</v>
+      </c>
+      <c r="E18" s="4" t="n">
+        <v>0.2361111111111111</v>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151530.jpg</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Employee 32</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>46245</v>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>0.7319444444444444</v>
+      </c>
+      <c r="E19" s="4" t="n">
+        <v>0.2215277777777778</v>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151530.jpg</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Employee 32</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>46244</v>
+      </c>
+      <c r="D20" s="4" t="n">
+        <v>0.7597222222222222</v>
+      </c>
+      <c r="E20" s="4" t="n">
+        <v>0.2409722222222222</v>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151530.jpg</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Employee 32</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>46243</v>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>0.2402777777777778</v>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151530.jpg</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Employee 32</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>46242</v>
+      </c>
+      <c r="D22" s="4" t="n">
+        <v>0.7243055555555555</v>
+      </c>
+      <c r="E22" s="4" t="n">
+        <v>0.2402777777777778</v>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151536.jpg</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Employee 32</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>46240</v>
+      </c>
+      <c r="D23" s="4" t="n">
+        <v>0.7576388888888889</v>
+      </c>
+      <c r="E23" s="4" t="n">
+        <v>0.2326388888888889</v>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151536.jpg</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Employee 32</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>46239</v>
+      </c>
+      <c r="D24" s="2" t="n"/>
+      <c r="E24" s="4" t="n">
+        <v>0.2229166666666667</v>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151536.jpg</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>single punch only</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Employee 32</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>46238</v>
+      </c>
+      <c r="D25" s="4" t="n">
+        <v>0.7458333333333333</v>
+      </c>
+      <c r="E25" s="2" t="n"/>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151536.jpg</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>single punch only</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Employee 32</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>46237</v>
+      </c>
+      <c r="D26" s="4" t="n">
+        <v>0.7444444444444445</v>
+      </c>
+      <c r="E26" s="4" t="n">
+        <v>0.3097222222222222</v>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151539.jpg</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Employee 32</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>46236</v>
+      </c>
+      <c r="D27" s="4" t="n">
+        <v>0.7534722222222222</v>
+      </c>
+      <c r="E27" s="4" t="n">
+        <v>0.2604166666666667</v>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151539.jpg</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Employee 32</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>46235</v>
+      </c>
+      <c r="D28" s="4" t="n">
+        <v>0.7430555555555556</v>
+      </c>
+      <c r="E28" s="4" t="n">
+        <v>0.2368055555555555</v>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151539.jpg</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Employee 34</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D29" s="2" t="n"/>
+      <c r="E29" s="4" t="n">
+        <v>0.2527777777777778</v>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151552.jpg</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>single punch only</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Employee 34</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>46264</v>
+      </c>
+      <c r="D30" s="4" t="n">
+        <v>0.7354166666666667</v>
+      </c>
+      <c r="E30" s="4" t="n">
+        <v>0.2659722222222222</v>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151552.jpg</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Employee 34</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>46263</v>
+      </c>
+      <c r="D31" s="4" t="n">
+        <v>0.7479166666666667</v>
+      </c>
+      <c r="E31" s="4" t="n">
+        <v>0.2541666666666667</v>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151552.jpg</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Employee 34</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>46262</v>
+      </c>
+      <c r="D32" s="4" t="n">
+        <v>0.7701388888888889</v>
+      </c>
+      <c r="E32" s="4" t="n">
+        <v>0.2805555555555556</v>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151552.jpg</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Employee 34</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>46261</v>
+      </c>
+      <c r="D33" s="4" t="n">
+        <v>0.8506944444444444</v>
+      </c>
+      <c r="E33" s="4" t="n">
+        <v>0.2555555555555555</v>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151558.jpg</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>extra punches: 17:07 17:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Employee 34</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>46260</v>
+      </c>
+      <c r="D34" s="4" t="n">
+        <v>0.8791666666666667</v>
+      </c>
+      <c r="E34" s="4" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151558.jpg</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>extra punch: 17:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Employee 34</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="D35" s="4" t="n">
+        <v>0.7298611111111111</v>
+      </c>
+      <c r="E35" s="4" t="n">
+        <v>0.2611111111111111</v>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151558.jpg</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Employee 34</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>46258</v>
+      </c>
+      <c r="D36" s="4" t="n">
+        <v>0.7270833333333333</v>
+      </c>
+      <c r="E36" s="4" t="n">
+        <v>0.2631944444444445</v>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151558.jpg</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Employee 34</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>46257</v>
+      </c>
+      <c r="D37" s="4" t="n">
+        <v>0.7263888888888889</v>
+      </c>
+      <c r="E37" s="4" t="n">
+        <v>0.24375</v>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151604.jpg</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Employee 34</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>46256</v>
+      </c>
+      <c r="D38" s="4" t="n">
+        <v>0.7513888888888889</v>
+      </c>
+      <c r="E38" s="4" t="n">
+        <v>0.2611111111111111</v>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151604.jpg</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Employee 34</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>46255</v>
+      </c>
+      <c r="D39" s="4" t="n">
+        <v>0.8354166666666667</v>
+      </c>
+      <c r="E39" s="4" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151604.jpg</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Employee 34</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>46254</v>
+      </c>
+      <c r="D40" s="4" t="n">
+        <v>0.7979166666666667</v>
+      </c>
+      <c r="E40" s="4" t="n">
+        <v>0.2625</v>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151604.jpg</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Employee 34</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>46253</v>
+      </c>
+      <c r="D41" s="4" t="n">
+        <v>0.7451388888888889</v>
+      </c>
+      <c r="E41" s="4" t="n">
+        <v>0.2777777777777778</v>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151608.jpg</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Employee 34</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>46252</v>
+      </c>
+      <c r="D42" s="4" t="n">
+        <v>0.7416666666666667</v>
+      </c>
+      <c r="E42" s="4" t="n">
+        <v>0.25625</v>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151608.jpg</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>Employee 34</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>46251</v>
+      </c>
+      <c r="D43" s="4" t="n">
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="E43" s="4" t="n">
+        <v>0.2333333333333333</v>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151608.jpg</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Employee 34</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>46250</v>
+      </c>
+      <c r="D44" s="4" t="n">
+        <v>0.7229166666666667</v>
+      </c>
+      <c r="E44" s="4" t="n">
+        <v>0.2708333333333333</v>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151608.jpg</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>Employee 34</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>46249</v>
+      </c>
+      <c r="D45" s="4" t="n">
+        <v>0.7277777777777777</v>
+      </c>
+      <c r="E45" s="4" t="n">
+        <v>0.1513888888888889</v>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151612.jpg</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Employee 34</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>46248</v>
+      </c>
+      <c r="D46" s="4" t="n">
+        <v>0.7076388888888889</v>
+      </c>
+      <c r="E46" s="4" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151612.jpg</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>Employee 34</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>46247</v>
+      </c>
+      <c r="D47" s="4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E47" s="4" t="n">
+        <v>0.1423611111111111</v>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151612.jpg</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Employee 34</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>46246</v>
+      </c>
+      <c r="D48" s="4" t="n">
+        <v>0.7409722222222223</v>
+      </c>
+      <c r="E48" s="4" t="n">
+        <v>0.1430555555555555</v>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151612.jpg</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>Employee 34</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>46245</v>
+      </c>
+      <c r="D49" s="4" t="n">
+        <v>0.7444444444444445</v>
+      </c>
+      <c r="E49" s="4" t="n">
+        <v>0.14375</v>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151619.jpg</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Employee 34</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>46244</v>
+      </c>
+      <c r="D50" s="4" t="n">
+        <v>0.7638888888888888</v>
+      </c>
+      <c r="E50" s="4" t="n">
+        <v>0.1354166666666667</v>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151619.jpg</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>Employee 34</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>46243</v>
+      </c>
+      <c r="D51" s="4" t="n">
+        <v>0.8381944444444445</v>
+      </c>
+      <c r="E51" s="4" t="n">
+        <v>0.1444444444444444</v>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151619.jpg</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>Employee 34</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>46242</v>
+      </c>
+      <c r="D52" s="4" t="n">
+        <v>0.8090277777777778</v>
+      </c>
+      <c r="E52" s="4" t="n">
+        <v>0.1388888888888889</v>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151619.jpg</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>extra punch: 03:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>Employee 34</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>46241</v>
+      </c>
+      <c r="D53" s="4" t="n">
+        <v>0.7298611111111111</v>
+      </c>
+      <c r="E53" s="4" t="n">
+        <v>0.1451388888888889</v>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151624.jpg</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>Employee 34</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>46240</v>
+      </c>
+      <c r="D54" s="4" t="n">
+        <v>0.7659722222222223</v>
+      </c>
+      <c r="E54" s="4" t="n">
+        <v>0.1444444444444444</v>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151624.jpg</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>Employee 34</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="n">
+        <v>46239</v>
+      </c>
+      <c r="D55" s="4" t="n">
+        <v>0.6881944444444444</v>
+      </c>
+      <c r="E55" s="4" t="n">
+        <v>0.1444444444444444</v>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151624.jpg</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>Employee 34</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>46238</v>
+      </c>
+      <c r="D56" s="4" t="n">
+        <v>0.7708333333333334</v>
+      </c>
+      <c r="E56" s="4" t="n">
+        <v>0.1451388888888889</v>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151624.jpg</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>Employee 34</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>46237</v>
+      </c>
+      <c r="D57" s="4" t="n">
+        <v>0.7472222222222222</v>
+      </c>
+      <c r="E57" s="4" t="n">
+        <v>0.1458333333333333</v>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151629.jpg</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>Employee 34</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>46236</v>
+      </c>
+      <c r="D58" s="4" t="n">
+        <v>0.7395833333333334</v>
+      </c>
+      <c r="E58" s="4" t="n">
+        <v>0.14375</v>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151629.jpg</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>Employee 34</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>46235</v>
+      </c>
+      <c r="D59" s="4" t="n">
+        <v>0.7576388888888889</v>
+      </c>
+      <c r="E59" s="4" t="n">
+        <v>0.14375</v>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151629.jpg</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>last day of month; final record</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>Employee 37</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>46256</v>
+      </c>
+      <c r="D60" s="4" t="n">
+        <v>0.7513888888888889</v>
+      </c>
+      <c r="E60" s="4" t="n">
+        <v>0.2805555555555556</v>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151706.jpg</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>Employee 37</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>46254</v>
+      </c>
+      <c r="D61" s="4" t="n">
+        <v>0.7256944444444444</v>
+      </c>
+      <c r="E61" s="4" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151706.jpg</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>Employee 37</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>46253</v>
+      </c>
+      <c r="D62" s="4" t="n">
+        <v>0.7298611111111111</v>
+      </c>
+      <c r="E62" s="4" t="n">
+        <v>0.2763888888888889</v>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151706.jpg</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>Employee 37</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="n">
+        <v>46252</v>
+      </c>
+      <c r="D63" s="4" t="n">
+        <v>0.7451388888888889</v>
+      </c>
+      <c r="E63" s="4" t="n">
+        <v>0.2826388888888889</v>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151706.jpg</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>Employee 37</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>46251</v>
+      </c>
+      <c r="D64" s="4" t="n">
+        <v>0.7333333333333333</v>
+      </c>
+      <c r="E64" s="4" t="n">
+        <v>0.2743055555555556</v>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151710.jpg</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>Employee 37</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="n">
+        <v>46250</v>
+      </c>
+      <c r="D65" s="4" t="n">
+        <v>0.7236111111111111</v>
+      </c>
+      <c r="E65" s="4" t="n">
+        <v>0.2902777777777778</v>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151710.jpg</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>Employee 37</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>46249</v>
+      </c>
+      <c r="D66" s="4" t="n">
+        <v>0.7388888888888889</v>
+      </c>
+      <c r="E66" s="4" t="n">
+        <v>0.2395833333333333</v>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151710.jpg</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>Employee 37</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>46247</v>
+      </c>
+      <c r="D67" s="4" t="n">
+        <v>0.7270833333333333</v>
+      </c>
+      <c r="E67" s="4" t="n">
+        <v>0.2465277777777778</v>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151710.jpg</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>Employee 37</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="n">
+        <v>46246</v>
+      </c>
+      <c r="D68" s="4" t="n">
+        <v>0.7493055555555556</v>
+      </c>
+      <c r="E68" s="4" t="n">
+        <v>0.2340277777777778</v>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151715.jpg</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>Employee 37</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="n">
+        <v>46245</v>
+      </c>
+      <c r="D69" s="4" t="n">
+        <v>0.7402777777777778</v>
+      </c>
+      <c r="E69" s="4" t="n">
+        <v>0.2381944444444444</v>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151715.jpg</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>Employee 37</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="n">
+        <v>46244</v>
+      </c>
+      <c r="D70" s="4" t="n">
+        <v>0.75625</v>
+      </c>
+      <c r="E70" s="2" t="n"/>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151715.jpg</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>single punch only</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>Employee 37</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="n">
+        <v>46243</v>
+      </c>
+      <c r="D71" s="4" t="n">
+        <v>0.75625</v>
+      </c>
+      <c r="E71" s="4" t="n">
+        <v>0.2381944444444444</v>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151715.jpg</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>Employee 37</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="n">
+        <v>46242</v>
+      </c>
+      <c r="D72" s="4" t="n">
+        <v>0.7326388888888888</v>
+      </c>
+      <c r="E72" s="4" t="n">
+        <v>0.2597222222222222</v>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151719.jpg</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>Employee 37</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="n">
+        <v>46240</v>
+      </c>
+      <c r="D73" s="4" t="n">
+        <v>0.7423611111111111</v>
+      </c>
+      <c r="E73" s="4" t="n">
+        <v>0.2701388888888889</v>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151719.jpg</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>Employee 37</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="n">
+        <v>46239</v>
+      </c>
+      <c r="D74" s="4" t="n">
+        <v>0.7763888888888889</v>
+      </c>
+      <c r="E74" s="4" t="n">
+        <v>0.25625</v>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151719.jpg</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>Employee 37</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="n">
+        <v>46238</v>
+      </c>
+      <c r="D75" s="4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E75" s="4" t="n">
+        <v>0.2527777777777778</v>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151719.jpg</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>Employee 37</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="n">
+        <v>46237</v>
+      </c>
+      <c r="D76" s="4" t="n">
+        <v>0.7479166666666667</v>
+      </c>
+      <c r="E76" s="4" t="n">
+        <v>0.2604166666666667</v>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151723.jpg</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>Employee 37</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="n">
+        <v>46236</v>
+      </c>
+      <c r="D77" s="4" t="n">
+        <v>0.7493055555555556</v>
+      </c>
+      <c r="E77" s="4" t="n">
+        <v>0.2645833333333333</v>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151723.jpg</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>Employee 37</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="n">
+        <v>46235</v>
+      </c>
+      <c r="D78" s="4" t="n">
+        <v>0.7444444444444445</v>
+      </c>
+      <c r="E78" s="4" t="n">
+        <v>0.2625</v>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151723.jpg</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>last day of month; final record</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/timesheet.xlsx
+++ b/output/timesheet.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G78"/>
+  <dimension ref="A1:G157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2602,6 +2602,2179 @@
         </is>
       </c>
     </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>Employee 38</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D79" s="2" t="n"/>
+      <c r="E79" s="4" t="n">
+        <v>0.2527777777777778</v>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151731.jpg</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>single punch only</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>Employee 38</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="n">
+        <v>46264</v>
+      </c>
+      <c r="D80" s="4" t="n">
+        <v>0.75625</v>
+      </c>
+      <c r="E80" s="4" t="n">
+        <v>0.2965277777777778</v>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151731.jpg</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>Employee 38</t>
+        </is>
+      </c>
+      <c r="C81" s="3" t="n">
+        <v>46263</v>
+      </c>
+      <c r="D81" s="4" t="n">
+        <v>0.7326388888888888</v>
+      </c>
+      <c r="E81" s="4" t="n">
+        <v>0.2965277777777778</v>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151731.jpg</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>Employee 38</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="n">
+        <v>46261</v>
+      </c>
+      <c r="D82" s="4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E82" s="4" t="n">
+        <v>0.2666666666666667</v>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151731.jpg</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>Employee 38</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="n">
+        <v>46260</v>
+      </c>
+      <c r="D83" s="4" t="n">
+        <v>0.7534722222222222</v>
+      </c>
+      <c r="E83" s="4" t="n">
+        <v>0.3243055555555556</v>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151737.jpg</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>extra punch: 17:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>Employee 38</t>
+        </is>
+      </c>
+      <c r="C84" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="D84" s="4" t="n">
+        <v>0.7548611111111111</v>
+      </c>
+      <c r="E84" s="4" t="n">
+        <v>0.2763888888888889</v>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151737.jpg</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>Employee 38</t>
+        </is>
+      </c>
+      <c r="C85" s="3" t="n">
+        <v>46258</v>
+      </c>
+      <c r="D85" s="4" t="n">
+        <v>0.7388888888888889</v>
+      </c>
+      <c r="E85" s="4" t="n">
+        <v>0.3263888888888889</v>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151737.jpg</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>Employee 38</t>
+        </is>
+      </c>
+      <c r="C86" s="3" t="n">
+        <v>46257</v>
+      </c>
+      <c r="D86" s="4" t="n">
+        <v>0.7493055555555556</v>
+      </c>
+      <c r="E86" s="4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151737.jpg</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>Employee 38</t>
+        </is>
+      </c>
+      <c r="C87" s="3" t="n">
+        <v>46256</v>
+      </c>
+      <c r="D87" s="4" t="n">
+        <v>0.7243055555555555</v>
+      </c>
+      <c r="E87" s="4" t="n">
+        <v>0.2069444444444444</v>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151742.jpg</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>Employee 38</t>
+        </is>
+      </c>
+      <c r="C88" s="3" t="n">
+        <v>46254</v>
+      </c>
+      <c r="D88" s="2" t="n"/>
+      <c r="E88" s="4" t="n">
+        <v>0.3576388888888889</v>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151742.jpg</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>single punch only</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>Employee 38</t>
+        </is>
+      </c>
+      <c r="C89" s="3" t="n">
+        <v>46253</v>
+      </c>
+      <c r="D89" s="4" t="n">
+        <v>0.7173611111111111</v>
+      </c>
+      <c r="E89" s="4" t="n">
+        <v>0.475</v>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151742.jpg</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>Employee 38</t>
+        </is>
+      </c>
+      <c r="C90" s="3" t="n">
+        <v>46252</v>
+      </c>
+      <c r="D90" s="4" t="n">
+        <v>0.7583333333333333</v>
+      </c>
+      <c r="E90" s="4" t="n">
+        <v>0.3083333333333333</v>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151742.jpg</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>Employee 38</t>
+        </is>
+      </c>
+      <c r="C91" s="3" t="n">
+        <v>46251</v>
+      </c>
+      <c r="D91" s="4" t="n">
+        <v>0.7680555555555556</v>
+      </c>
+      <c r="E91" s="4" t="n">
+        <v>0.3979166666666666</v>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151746.jpg</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>Employee 38</t>
+        </is>
+      </c>
+      <c r="C92" s="3" t="n">
+        <v>46250</v>
+      </c>
+      <c r="D92" s="4" t="n">
+        <v>0.7722222222222223</v>
+      </c>
+      <c r="E92" s="4" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151746.jpg</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>Employee 38</t>
+        </is>
+      </c>
+      <c r="C93" s="3" t="n">
+        <v>46249</v>
+      </c>
+      <c r="D93" s="4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E93" s="4" t="n">
+        <v>0.2354166666666667</v>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151746.jpg</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>Employee 38</t>
+        </is>
+      </c>
+      <c r="C94" s="3" t="n">
+        <v>46247</v>
+      </c>
+      <c r="D94" s="2" t="n"/>
+      <c r="E94" s="4" t="n">
+        <v>0.3347222222222222</v>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151746.jpg</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>single punch only</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>Employee 38</t>
+        </is>
+      </c>
+      <c r="C95" s="3" t="n">
+        <v>46246</v>
+      </c>
+      <c r="D95" s="2" t="n"/>
+      <c r="E95" s="4" t="n">
+        <v>0.2986111111111111</v>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151751.jpg</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>single punch only</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>Employee 38</t>
+        </is>
+      </c>
+      <c r="C96" s="3" t="n">
+        <v>46245</v>
+      </c>
+      <c r="D96" s="2" t="n"/>
+      <c r="E96" s="4" t="n">
+        <v>0.3118055555555556</v>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151751.jpg</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>single punch only</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>Employee 38</t>
+        </is>
+      </c>
+      <c r="C97" s="3" t="n">
+        <v>46244</v>
+      </c>
+      <c r="D97" s="4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E97" s="4" t="n">
+        <v>0.2263888888888889</v>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151751.jpg</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>Employee 38</t>
+        </is>
+      </c>
+      <c r="C98" s="3" t="n">
+        <v>46243</v>
+      </c>
+      <c r="D98" s="4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E98" s="4" t="n">
+        <v>0.2798611111111111</v>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151751.jpg</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>Employee 38</t>
+        </is>
+      </c>
+      <c r="C99" s="3" t="n">
+        <v>46242</v>
+      </c>
+      <c r="D99" s="4" t="n">
+        <v>0.7604166666666666</v>
+      </c>
+      <c r="E99" s="4" t="n">
+        <v>0.3055555555555556</v>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151757.jpg</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>Employee 38</t>
+        </is>
+      </c>
+      <c r="C100" s="3" t="n">
+        <v>46240</v>
+      </c>
+      <c r="D100" s="4" t="n">
+        <v>0.7590277777777777</v>
+      </c>
+      <c r="E100" s="4" t="n">
+        <v>0.30625</v>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151757.jpg</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>Employee 38</t>
+        </is>
+      </c>
+      <c r="C101" s="3" t="n">
+        <v>46239</v>
+      </c>
+      <c r="D101" s="4" t="n">
+        <v>0.7715277777777778</v>
+      </c>
+      <c r="E101" s="4" t="n">
+        <v>0.3222222222222222</v>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151757.jpg</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>Employee 38</t>
+        </is>
+      </c>
+      <c r="C102" s="3" t="n">
+        <v>46238</v>
+      </c>
+      <c r="D102" s="4" t="n">
+        <v>0.7166666666666667</v>
+      </c>
+      <c r="E102" s="4" t="n">
+        <v>0.2763888888888889</v>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151757.jpg</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>Employee 38</t>
+        </is>
+      </c>
+      <c r="C103" s="3" t="n">
+        <v>46237</v>
+      </c>
+      <c r="D103" s="4" t="n">
+        <v>0.7159722222222222</v>
+      </c>
+      <c r="E103" s="4" t="n">
+        <v>0.3034722222222222</v>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151759.jpg</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>Employee 38</t>
+        </is>
+      </c>
+      <c r="C104" s="3" t="n">
+        <v>46236</v>
+      </c>
+      <c r="D104" s="4" t="n">
+        <v>0.7430555555555556</v>
+      </c>
+      <c r="E104" s="4" t="n">
+        <v>0.2958333333333333</v>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151759.jpg</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>Employee 38</t>
+        </is>
+      </c>
+      <c r="C105" s="3" t="n">
+        <v>46235</v>
+      </c>
+      <c r="D105" s="4" t="n">
+        <v>0.7458333333333333</v>
+      </c>
+      <c r="E105" s="4" t="n">
+        <v>0.2381944444444444</v>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151759.jpg</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>last day of month; final record</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>Employee 39</t>
+        </is>
+      </c>
+      <c r="C106" s="3" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D106" s="2" t="n"/>
+      <c r="E106" s="4" t="n">
+        <v>0.2777777777777778</v>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151809.jpg</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>single punch only</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>Employee 39</t>
+        </is>
+      </c>
+      <c r="C107" s="3" t="n">
+        <v>46264</v>
+      </c>
+      <c r="D107" s="4" t="n">
+        <v>0.7541666666666667</v>
+      </c>
+      <c r="E107" s="4" t="n">
+        <v>0.2590277777777778</v>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151809.jpg</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>Employee 39</t>
+        </is>
+      </c>
+      <c r="C108" s="3" t="n">
+        <v>46263</v>
+      </c>
+      <c r="D108" s="4" t="n">
+        <v>0.7458333333333333</v>
+      </c>
+      <c r="E108" s="4" t="n">
+        <v>0.2569444444444444</v>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151809.jpg</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>extra punch: 17:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>Employee 39</t>
+        </is>
+      </c>
+      <c r="C109" s="3" t="n">
+        <v>46262</v>
+      </c>
+      <c r="D109" s="2" t="n"/>
+      <c r="E109" s="4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151809.jpg</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>single punch only</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>Employee 39</t>
+        </is>
+      </c>
+      <c r="C110" s="3" t="n">
+        <v>46261</v>
+      </c>
+      <c r="D110" s="4" t="n">
+        <v>0.7944444444444444</v>
+      </c>
+      <c r="E110" s="4" t="n">
+        <v>0.2493055555555556</v>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151819.jpg</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>Employee 39</t>
+        </is>
+      </c>
+      <c r="C111" s="3" t="n">
+        <v>46260</v>
+      </c>
+      <c r="D111" s="4" t="n">
+        <v>0.7555555555555555</v>
+      </c>
+      <c r="E111" s="4" t="n">
+        <v>0.2479166666666667</v>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151819.jpg</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>Employee 39</t>
+        </is>
+      </c>
+      <c r="C112" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="D112" s="4" t="n">
+        <v>0.7597222222222222</v>
+      </c>
+      <c r="E112" s="4" t="n">
+        <v>0.2375</v>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151819.jpg</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>Employee 39</t>
+        </is>
+      </c>
+      <c r="C113" s="3" t="n">
+        <v>46258</v>
+      </c>
+      <c r="D113" s="4" t="n">
+        <v>0.7506944444444444</v>
+      </c>
+      <c r="E113" s="4" t="n">
+        <v>0.2375</v>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151819.jpg</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>Employee 39</t>
+        </is>
+      </c>
+      <c r="C114" s="3" t="n">
+        <v>46257</v>
+      </c>
+      <c r="D114" s="4" t="n">
+        <v>0.7618055555555555</v>
+      </c>
+      <c r="E114" s="4" t="n">
+        <v>0.2479166666666667</v>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151826.jpg</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>Employee 39</t>
+        </is>
+      </c>
+      <c r="C115" s="3" t="n">
+        <v>46256</v>
+      </c>
+      <c r="D115" s="2" t="n"/>
+      <c r="E115" s="4" t="n">
+        <v>0.2875</v>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151826.jpg</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>single punch only</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>Employee 39</t>
+        </is>
+      </c>
+      <c r="C116" s="3" t="n">
+        <v>46254</v>
+      </c>
+      <c r="D116" s="4" t="n">
+        <v>0.7243055555555555</v>
+      </c>
+      <c r="E116" s="4" t="n">
+        <v>0.2472222222222222</v>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151826.jpg</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>Employee 39</t>
+        </is>
+      </c>
+      <c r="C117" s="3" t="n">
+        <v>46253</v>
+      </c>
+      <c r="D117" s="4" t="n">
+        <v>0.7416666666666667</v>
+      </c>
+      <c r="E117" s="4" t="n">
+        <v>0.2395833333333333</v>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151826.jpg</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>Employee 39</t>
+        </is>
+      </c>
+      <c r="C118" s="3" t="n">
+        <v>46252</v>
+      </c>
+      <c r="D118" s="4" t="n">
+        <v>0.7416666666666667</v>
+      </c>
+      <c r="E118" s="4" t="n">
+        <v>0.2916666666666667</v>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151831.jpg</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>Employee 39</t>
+        </is>
+      </c>
+      <c r="C119" s="3" t="n">
+        <v>46251</v>
+      </c>
+      <c r="D119" s="4" t="n">
+        <v>0.7326388888888888</v>
+      </c>
+      <c r="E119" s="4" t="n">
+        <v>0.3416666666666667</v>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151831.jpg</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>Employee 39</t>
+        </is>
+      </c>
+      <c r="C120" s="3" t="n">
+        <v>46250</v>
+      </c>
+      <c r="D120" s="4" t="n">
+        <v>0.7381944444444445</v>
+      </c>
+      <c r="E120" s="4" t="n">
+        <v>0.2409722222222222</v>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151831.jpg</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>Employee 39</t>
+        </is>
+      </c>
+      <c r="C121" s="3" t="n">
+        <v>46249</v>
+      </c>
+      <c r="D121" s="4" t="n">
+        <v>0.7611111111111111</v>
+      </c>
+      <c r="E121" s="4" t="n">
+        <v>0.2354166666666667</v>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151831.jpg</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>Employee 39</t>
+        </is>
+      </c>
+      <c r="C122" s="3" t="n">
+        <v>46247</v>
+      </c>
+      <c r="D122" s="2" t="n"/>
+      <c r="E122" s="4" t="n">
+        <v>0.4402777777777778</v>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151837.jpg</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>single punch only</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>Employee 39</t>
+        </is>
+      </c>
+      <c r="C123" s="3" t="n">
+        <v>46246</v>
+      </c>
+      <c r="D123" s="4" t="n">
+        <v>0.7423611111111111</v>
+      </c>
+      <c r="E123" s="4" t="n">
+        <v>0.2284722222222222</v>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151837.jpg</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>Employee 39</t>
+        </is>
+      </c>
+      <c r="C124" s="3" t="n">
+        <v>46245</v>
+      </c>
+      <c r="D124" s="4" t="n">
+        <v>0.7375</v>
+      </c>
+      <c r="E124" s="4" t="n">
+        <v>0.2375</v>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151837.jpg</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>Employee 39</t>
+        </is>
+      </c>
+      <c r="C125" s="3" t="n">
+        <v>46244</v>
+      </c>
+      <c r="D125" s="4" t="n">
+        <v>0.7611111111111111</v>
+      </c>
+      <c r="E125" s="4" t="n">
+        <v>0.2256944444444444</v>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151837.jpg</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>Employee 39</t>
+        </is>
+      </c>
+      <c r="C126" s="3" t="n">
+        <v>46243</v>
+      </c>
+      <c r="D126" s="4" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="E126" s="4" t="n">
+        <v>0.2395833333333333</v>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151844.jpg</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>Employee 39</t>
+        </is>
+      </c>
+      <c r="C127" s="3" t="n">
+        <v>46242</v>
+      </c>
+      <c r="D127" s="4" t="n">
+        <v>0.7618055555555555</v>
+      </c>
+      <c r="E127" s="4" t="n">
+        <v>0.2201388888888889</v>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151844.jpg</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>Employee 39</t>
+        </is>
+      </c>
+      <c r="C128" s="3" t="n">
+        <v>46240</v>
+      </c>
+      <c r="D128" s="4" t="n">
+        <v>0.7625</v>
+      </c>
+      <c r="E128" s="4" t="n">
+        <v>0.2409722222222222</v>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151844.jpg</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>Employee 39</t>
+        </is>
+      </c>
+      <c r="C129" s="3" t="n">
+        <v>46239</v>
+      </c>
+      <c r="D129" s="4" t="n">
+        <v>0.7722222222222223</v>
+      </c>
+      <c r="E129" s="4" t="n">
+        <v>0.4743055555555555</v>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151844.jpg</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>Employee 39</t>
+        </is>
+      </c>
+      <c r="C130" s="3" t="n">
+        <v>46238</v>
+      </c>
+      <c r="D130" s="4" t="n">
+        <v>0.7506944444444444</v>
+      </c>
+      <c r="E130" s="4" t="n">
+        <v>0.4965277777777778</v>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151849.jpg</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>Employee 39</t>
+        </is>
+      </c>
+      <c r="C131" s="3" t="n">
+        <v>46237</v>
+      </c>
+      <c r="D131" s="4" t="n">
+        <v>0.7472222222222222</v>
+      </c>
+      <c r="E131" s="4" t="n">
+        <v>0.2618055555555556</v>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151849.jpg</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>Employee 39</t>
+        </is>
+      </c>
+      <c r="C132" s="3" t="n">
+        <v>46236</v>
+      </c>
+      <c r="D132" s="4" t="n">
+        <v>0.7430555555555556</v>
+      </c>
+      <c r="E132" s="4" t="n">
+        <v>0.2972222222222222</v>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151849.jpg</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>Employee 39</t>
+        </is>
+      </c>
+      <c r="C133" s="3" t="n">
+        <v>46235</v>
+      </c>
+      <c r="D133" s="4" t="n">
+        <v>0.7319444444444444</v>
+      </c>
+      <c r="E133" s="4" t="n">
+        <v>0.2590277777777778</v>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151849.jpg</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>last day of month; final record</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>Employee 40</t>
+        </is>
+      </c>
+      <c r="C134" s="3" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D134" s="2" t="n"/>
+      <c r="E134" s="4" t="n">
+        <v>0.2416666666666667</v>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151859.jpg</t>
+        </is>
+      </c>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>single punch only</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>Employee 40</t>
+        </is>
+      </c>
+      <c r="C135" s="3" t="n">
+        <v>46264</v>
+      </c>
+      <c r="D135" s="4" t="n">
+        <v>0.7513888888888889</v>
+      </c>
+      <c r="E135" s="4" t="n">
+        <v>0.2423611111111111</v>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151859.jpg</t>
+        </is>
+      </c>
+      <c r="G135" s="2" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>Employee 40</t>
+        </is>
+      </c>
+      <c r="C136" s="3" t="n">
+        <v>46263</v>
+      </c>
+      <c r="D136" s="4" t="n">
+        <v>0.7548611111111111</v>
+      </c>
+      <c r="E136" s="4" t="n">
+        <v>0.2444444444444444</v>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151859.jpg</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>Employee 40</t>
+        </is>
+      </c>
+      <c r="C137" s="3" t="n">
+        <v>46261</v>
+      </c>
+      <c r="D137" s="4" t="n">
+        <v>0.7513888888888889</v>
+      </c>
+      <c r="E137" s="4" t="n">
+        <v>0.2472222222222222</v>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151859.jpg</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>Employee 40</t>
+        </is>
+      </c>
+      <c r="C138" s="3" t="n">
+        <v>46260</v>
+      </c>
+      <c r="D138" s="4" t="n">
+        <v>0.7555555555555555</v>
+      </c>
+      <c r="E138" s="4" t="n">
+        <v>0.2465277777777778</v>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151906.jpg</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>Employee 40</t>
+        </is>
+      </c>
+      <c r="C139" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="D139" s="4" t="n">
+        <v>0.7506944444444444</v>
+      </c>
+      <c r="E139" s="4" t="n">
+        <v>0.2368055555555555</v>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151906.jpg</t>
+        </is>
+      </c>
+      <c r="G139" s="2" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>Employee 40</t>
+        </is>
+      </c>
+      <c r="C140" s="3" t="n">
+        <v>46258</v>
+      </c>
+      <c r="D140" s="4" t="n">
+        <v>0.7520833333333333</v>
+      </c>
+      <c r="E140" s="4" t="n">
+        <v>0.2347222222222222</v>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151906.jpg</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>Employee 40</t>
+        </is>
+      </c>
+      <c r="C141" s="3" t="n">
+        <v>46257</v>
+      </c>
+      <c r="D141" s="4" t="n">
+        <v>0.7527777777777778</v>
+      </c>
+      <c r="E141" s="4" t="n">
+        <v>0.2458333333333333</v>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151906.jpg</t>
+        </is>
+      </c>
+      <c r="G141" s="2" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>Employee 40</t>
+        </is>
+      </c>
+      <c r="C142" s="3" t="n">
+        <v>46256</v>
+      </c>
+      <c r="D142" s="4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E142" s="4" t="n">
+        <v>0.2402777777777778</v>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151910.jpg</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>Employee 40</t>
+        </is>
+      </c>
+      <c r="C143" s="3" t="n">
+        <v>46254</v>
+      </c>
+      <c r="D143" s="4" t="n">
+        <v>0.7520833333333333</v>
+      </c>
+      <c r="E143" s="4" t="n">
+        <v>0.2402777777777778</v>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151910.jpg</t>
+        </is>
+      </c>
+      <c r="G143" s="2" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>Employee 40</t>
+        </is>
+      </c>
+      <c r="C144" s="3" t="n">
+        <v>46253</v>
+      </c>
+      <c r="D144" s="4" t="n">
+        <v>0.7506944444444444</v>
+      </c>
+      <c r="E144" s="4" t="n">
+        <v>0.2423611111111111</v>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151910.jpg</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>Employee 40</t>
+        </is>
+      </c>
+      <c r="C145" s="3" t="n">
+        <v>46252</v>
+      </c>
+      <c r="D145" s="4" t="n">
+        <v>0.7527777777777778</v>
+      </c>
+      <c r="E145" s="4" t="n">
+        <v>0.2451388888888889</v>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151910.jpg</t>
+        </is>
+      </c>
+      <c r="G145" s="2" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>Employee 40</t>
+        </is>
+      </c>
+      <c r="C146" s="3" t="n">
+        <v>46251</v>
+      </c>
+      <c r="D146" s="4" t="n">
+        <v>0.7541666666666667</v>
+      </c>
+      <c r="E146" s="4" t="n">
+        <v>0.2395833333333333</v>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151915.jpg</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>Employee 40</t>
+        </is>
+      </c>
+      <c r="C147" s="3" t="n">
+        <v>46250</v>
+      </c>
+      <c r="D147" s="4" t="n">
+        <v>0.7520833333333333</v>
+      </c>
+      <c r="E147" s="4" t="n">
+        <v>0.2354166666666667</v>
+      </c>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151915.jpg</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>Employee 40</t>
+        </is>
+      </c>
+      <c r="C148" s="3" t="n">
+        <v>46249</v>
+      </c>
+      <c r="D148" s="4" t="n">
+        <v>0.7513888888888889</v>
+      </c>
+      <c r="E148" s="4" t="n">
+        <v>0.2381944444444444</v>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151915.jpg</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>Employee 40</t>
+        </is>
+      </c>
+      <c r="C149" s="3" t="n">
+        <v>46247</v>
+      </c>
+      <c r="D149" s="4" t="n">
+        <v>0.7576388888888889</v>
+      </c>
+      <c r="E149" s="4" t="n">
+        <v>0.2444444444444444</v>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151915.jpg</t>
+        </is>
+      </c>
+      <c r="G149" s="2" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>Employee 40</t>
+        </is>
+      </c>
+      <c r="C150" s="3" t="n">
+        <v>46246</v>
+      </c>
+      <c r="D150" s="2" t="n"/>
+      <c r="E150" s="2" t="n"/>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151915.jpg</t>
+        </is>
+      </c>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t>PLEASE VERIFY: check-in/out times not captured (gap between source photos)</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>Employee 40</t>
+        </is>
+      </c>
+      <c r="C151" s="3" t="n">
+        <v>46242</v>
+      </c>
+      <c r="D151" s="4" t="n">
+        <v>0.7548611111111111</v>
+      </c>
+      <c r="E151" s="4" t="n">
+        <v>0.2430555555555556</v>
+      </c>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151924.jpg</t>
+        </is>
+      </c>
+      <c r="G151" s="2" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>Employee 40</t>
+        </is>
+      </c>
+      <c r="C152" s="3" t="n">
+        <v>46240</v>
+      </c>
+      <c r="D152" s="4" t="n">
+        <v>0.7513888888888889</v>
+      </c>
+      <c r="E152" s="4" t="n">
+        <v>0.2402777777777778</v>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151924.jpg</t>
+        </is>
+      </c>
+      <c r="G152" s="2" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>Employee 40</t>
+        </is>
+      </c>
+      <c r="C153" s="3" t="n">
+        <v>46239</v>
+      </c>
+      <c r="D153" s="4" t="n">
+        <v>0.7611111111111111</v>
+      </c>
+      <c r="E153" s="4" t="n">
+        <v>0.2368055555555555</v>
+      </c>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151924.jpg</t>
+        </is>
+      </c>
+      <c r="G153" s="2" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>Employee 40</t>
+        </is>
+      </c>
+      <c r="C154" s="3" t="n">
+        <v>46238</v>
+      </c>
+      <c r="D154" s="4" t="n">
+        <v>0.7520833333333333</v>
+      </c>
+      <c r="E154" s="4" t="n">
+        <v>0.2451388888888889</v>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151924.jpg</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>Employee 40</t>
+        </is>
+      </c>
+      <c r="C155" s="3" t="n">
+        <v>46237</v>
+      </c>
+      <c r="D155" s="4" t="n">
+        <v>0.7527777777777778</v>
+      </c>
+      <c r="E155" s="4" t="n">
+        <v>0.24375</v>
+      </c>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151928.jpg</t>
+        </is>
+      </c>
+      <c r="G155" s="2" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>Employee 40</t>
+        </is>
+      </c>
+      <c r="C156" s="3" t="n">
+        <v>46236</v>
+      </c>
+      <c r="D156" s="4" t="n">
+        <v>0.7520833333333333</v>
+      </c>
+      <c r="E156" s="4" t="n">
+        <v>0.24375</v>
+      </c>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151928.jpg</t>
+        </is>
+      </c>
+      <c r="G156" s="2" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>Employee 40</t>
+        </is>
+      </c>
+      <c r="C157" s="3" t="n">
+        <v>46235</v>
+      </c>
+      <c r="D157" s="4" t="n">
+        <v>0.7506944444444444</v>
+      </c>
+      <c r="E157" s="4" t="n">
+        <v>0.2451388888888889</v>
+      </c>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151928.jpg</t>
+        </is>
+      </c>
+      <c r="G157" s="2" t="inlineStr">
+        <is>
+          <t>last day of month; final record</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/timesheet.xlsx
+++ b/output/timesheet.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G157"/>
+  <dimension ref="A1:G234"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4775,6 +4775,2157 @@
         </is>
       </c>
     </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>Employee 41</t>
+        </is>
+      </c>
+      <c r="C158" s="3" t="n">
+        <v>46264</v>
+      </c>
+      <c r="D158" s="4" t="n">
+        <v>0.7215277777777778</v>
+      </c>
+      <c r="E158" s="4" t="n">
+        <v>0.2958333333333333</v>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151937.jpg</t>
+        </is>
+      </c>
+      <c r="G158" s="2" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>Employee 41</t>
+        </is>
+      </c>
+      <c r="C159" s="3" t="n">
+        <v>46263</v>
+      </c>
+      <c r="D159" s="4" t="n">
+        <v>0.7104166666666667</v>
+      </c>
+      <c r="E159" s="4" t="n">
+        <v>0.2513888888888889</v>
+      </c>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151937.jpg</t>
+        </is>
+      </c>
+      <c r="G159" s="2" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>Employee 41</t>
+        </is>
+      </c>
+      <c r="C160" s="3" t="n">
+        <v>46261</v>
+      </c>
+      <c r="D160" s="4" t="n">
+        <v>0.7111111111111111</v>
+      </c>
+      <c r="E160" s="4" t="n">
+        <v>0.4881944444444444</v>
+      </c>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151937.jpg</t>
+        </is>
+      </c>
+      <c r="G160" s="2" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>Employee 41</t>
+        </is>
+      </c>
+      <c r="C161" s="3" t="n">
+        <v>46260</v>
+      </c>
+      <c r="D161" s="4" t="n">
+        <v>0.7152777777777778</v>
+      </c>
+      <c r="E161" s="4" t="n">
+        <v>0.2375</v>
+      </c>
+      <c r="F161" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151937.jpg</t>
+        </is>
+      </c>
+      <c r="G161" s="2" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>Employee 41</t>
+        </is>
+      </c>
+      <c r="C162" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="D162" s="4" t="n">
+        <v>0.7222222222222222</v>
+      </c>
+      <c r="E162" s="4" t="n">
+        <v>0.2854166666666667</v>
+      </c>
+      <c r="F162" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151944.jpg</t>
+        </is>
+      </c>
+      <c r="G162" s="2" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>Employee 41</t>
+        </is>
+      </c>
+      <c r="C163" s="3" t="n">
+        <v>46258</v>
+      </c>
+      <c r="D163" s="4" t="n">
+        <v>0.7055555555555556</v>
+      </c>
+      <c r="E163" s="4" t="n">
+        <v>0.2784722222222222</v>
+      </c>
+      <c r="F163" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151944.jpg</t>
+        </is>
+      </c>
+      <c r="G163" s="2" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>Employee 41</t>
+        </is>
+      </c>
+      <c r="C164" s="3" t="n">
+        <v>46257</v>
+      </c>
+      <c r="D164" s="4" t="n">
+        <v>0.7076388888888889</v>
+      </c>
+      <c r="E164" s="4" t="n">
+        <v>0.2444444444444444</v>
+      </c>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151944.jpg</t>
+        </is>
+      </c>
+      <c r="G164" s="2" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>Employee 41</t>
+        </is>
+      </c>
+      <c r="C165" s="3" t="n">
+        <v>46256</v>
+      </c>
+      <c r="D165" s="4" t="n">
+        <v>0.7083333333333334</v>
+      </c>
+      <c r="E165" s="4" t="n">
+        <v>0.2888888888888889</v>
+      </c>
+      <c r="F165" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151944.jpg</t>
+        </is>
+      </c>
+      <c r="G165" s="2" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>Employee 41</t>
+        </is>
+      </c>
+      <c r="C166" s="3" t="n">
+        <v>46254</v>
+      </c>
+      <c r="D166" s="4" t="n">
+        <v>0.70625</v>
+      </c>
+      <c r="E166" s="4" t="n">
+        <v>0.4298611111111111</v>
+      </c>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151952.jpg</t>
+        </is>
+      </c>
+      <c r="G166" s="2" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>Employee 41</t>
+        </is>
+      </c>
+      <c r="C167" s="3" t="n">
+        <v>46253</v>
+      </c>
+      <c r="D167" s="4" t="n">
+        <v>0.7305555555555555</v>
+      </c>
+      <c r="E167" s="4" t="n">
+        <v>0.2944444444444445</v>
+      </c>
+      <c r="F167" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151952.jpg</t>
+        </is>
+      </c>
+      <c r="G167" s="2" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>Employee 41</t>
+        </is>
+      </c>
+      <c r="C168" s="3" t="n">
+        <v>46252</v>
+      </c>
+      <c r="D168" s="4" t="n">
+        <v>0.7208333333333333</v>
+      </c>
+      <c r="E168" s="4" t="n">
+        <v>0.3659722222222222</v>
+      </c>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151952.jpg</t>
+        </is>
+      </c>
+      <c r="G168" s="2" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>Employee 41</t>
+        </is>
+      </c>
+      <c r="C169" s="3" t="n">
+        <v>46251</v>
+      </c>
+      <c r="D169" s="4" t="n">
+        <v>0.7069444444444445</v>
+      </c>
+      <c r="E169" s="4" t="n">
+        <v>0.3104166666666667</v>
+      </c>
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_151952.jpg</t>
+        </is>
+      </c>
+      <c r="G169" s="2" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>Employee 41</t>
+        </is>
+      </c>
+      <c r="C170" s="3" t="n">
+        <v>46250</v>
+      </c>
+      <c r="D170" s="4" t="n">
+        <v>0.7173611111111111</v>
+      </c>
+      <c r="E170" s="4" t="n">
+        <v>0.3416666666666667</v>
+      </c>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_152000.jpg</t>
+        </is>
+      </c>
+      <c r="G170" s="2" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>Employee 41</t>
+        </is>
+      </c>
+      <c r="C171" s="3" t="n">
+        <v>46249</v>
+      </c>
+      <c r="D171" s="4" t="n">
+        <v>0.7625</v>
+      </c>
+      <c r="E171" s="4" t="n">
+        <v>0.2680555555555555</v>
+      </c>
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_152000.jpg</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>Employee 41</t>
+        </is>
+      </c>
+      <c r="C172" s="3" t="n">
+        <v>46247</v>
+      </c>
+      <c r="D172" s="4" t="n">
+        <v>0.7583333333333333</v>
+      </c>
+      <c r="E172" s="4" t="n">
+        <v>0.3409722222222222</v>
+      </c>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_152000.jpg</t>
+        </is>
+      </c>
+      <c r="G172" s="2" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>Employee 41</t>
+        </is>
+      </c>
+      <c r="C173" s="3" t="n">
+        <v>46246</v>
+      </c>
+      <c r="D173" s="4" t="n">
+        <v>0.7222222222222222</v>
+      </c>
+      <c r="E173" s="4" t="n">
+        <v>0.2694444444444444</v>
+      </c>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_152000.jpg</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>Employee 41</t>
+        </is>
+      </c>
+      <c r="C174" s="3" t="n">
+        <v>46245</v>
+      </c>
+      <c r="D174" s="4" t="n">
+        <v>0.7618055555555555</v>
+      </c>
+      <c r="E174" s="4" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_152000.jpg</t>
+        </is>
+      </c>
+      <c r="G174" s="2" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>Employee 41</t>
+        </is>
+      </c>
+      <c r="C175" s="3" t="n">
+        <v>46244</v>
+      </c>
+      <c r="D175" s="4" t="n">
+        <v>0.75625</v>
+      </c>
+      <c r="E175" s="4" t="n">
+        <v>0.2298611111111111</v>
+      </c>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_152006.jpg</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>extra punch: 06:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>Employee 41</t>
+        </is>
+      </c>
+      <c r="C176" s="3" t="n">
+        <v>46243</v>
+      </c>
+      <c r="D176" s="4" t="n">
+        <v>0.7694444444444445</v>
+      </c>
+      <c r="E176" s="4" t="n">
+        <v>0.2451388888888889</v>
+      </c>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_152006.jpg</t>
+        </is>
+      </c>
+      <c r="G176" s="2" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>Employee 41</t>
+        </is>
+      </c>
+      <c r="C177" s="3" t="n">
+        <v>46242</v>
+      </c>
+      <c r="D177" s="4" t="n">
+        <v>0.6965277777777777</v>
+      </c>
+      <c r="E177" s="4" t="n">
+        <v>0.2388888888888889</v>
+      </c>
+      <c r="F177" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_152006.jpg</t>
+        </is>
+      </c>
+      <c r="G177" s="2" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>Employee 41</t>
+        </is>
+      </c>
+      <c r="C178" s="3" t="n">
+        <v>46240</v>
+      </c>
+      <c r="D178" s="2" t="n"/>
+      <c r="E178" s="4" t="n">
+        <v>0.2715277777777778</v>
+      </c>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_152012.jpg</t>
+        </is>
+      </c>
+      <c r="G178" s="2" t="inlineStr">
+        <is>
+          <t>single punch only</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>Employee 41</t>
+        </is>
+      </c>
+      <c r="C179" s="3" t="n">
+        <v>46239</v>
+      </c>
+      <c r="D179" s="4" t="n">
+        <v>0.7152777777777778</v>
+      </c>
+      <c r="E179" s="4" t="n">
+        <v>0.2756944444444445</v>
+      </c>
+      <c r="F179" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_152012.jpg</t>
+        </is>
+      </c>
+      <c r="G179" s="2" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>Employee 41</t>
+        </is>
+      </c>
+      <c r="C180" s="3" t="n">
+        <v>46238</v>
+      </c>
+      <c r="D180" s="4" t="n">
+        <v>0.7527777777777778</v>
+      </c>
+      <c r="E180" s="4" t="n">
+        <v>0.2729166666666666</v>
+      </c>
+      <c r="F180" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_152012.jpg</t>
+        </is>
+      </c>
+      <c r="G180" s="2" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>Employee 41</t>
+        </is>
+      </c>
+      <c r="C181" s="3" t="n">
+        <v>46237</v>
+      </c>
+      <c r="D181" s="4" t="n">
+        <v>0.7201388888888889</v>
+      </c>
+      <c r="E181" s="4" t="n">
+        <v>0.2451388888888889</v>
+      </c>
+      <c r="F181" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_152012.jpg</t>
+        </is>
+      </c>
+      <c r="G181" s="2" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>Employee 41</t>
+        </is>
+      </c>
+      <c r="C182" s="3" t="n">
+        <v>46236</v>
+      </c>
+      <c r="D182" s="4" t="n">
+        <v>0.7722222222222223</v>
+      </c>
+      <c r="E182" s="4" t="n">
+        <v>0.2722222222222222</v>
+      </c>
+      <c r="F182" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_152017.jpg</t>
+        </is>
+      </c>
+      <c r="G182" s="2" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>Employee 41</t>
+        </is>
+      </c>
+      <c r="C183" s="3" t="n">
+        <v>46235</v>
+      </c>
+      <c r="D183" s="4" t="n">
+        <v>0.7854166666666667</v>
+      </c>
+      <c r="E183" s="4" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="F183" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_152017.jpg</t>
+        </is>
+      </c>
+      <c r="G183" s="2" t="inlineStr">
+        <is>
+          <t>last day of month; final record</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>Employee 42</t>
+        </is>
+      </c>
+      <c r="C184" s="3" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D184" s="2" t="n"/>
+      <c r="E184" s="4" t="n">
+        <v>0.3888888888888889</v>
+      </c>
+      <c r="F184" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_152028.jpg</t>
+        </is>
+      </c>
+      <c r="G184" s="2" t="inlineStr">
+        <is>
+          <t>single punch only</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t>Employee 42</t>
+        </is>
+      </c>
+      <c r="C185" s="3" t="n">
+        <v>46264</v>
+      </c>
+      <c r="D185" s="4" t="n">
+        <v>0.7472222222222222</v>
+      </c>
+      <c r="E185" s="4" t="n">
+        <v>0.2798611111111111</v>
+      </c>
+      <c r="F185" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_152028.jpg</t>
+        </is>
+      </c>
+      <c r="G185" s="2" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t>Employee 42</t>
+        </is>
+      </c>
+      <c r="C186" s="3" t="n">
+        <v>46263</v>
+      </c>
+      <c r="D186" s="4" t="n">
+        <v>0.7291666666666666</v>
+      </c>
+      <c r="E186" s="2" t="n"/>
+      <c r="F186" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_152028.jpg</t>
+        </is>
+      </c>
+      <c r="G186" s="2" t="inlineStr">
+        <is>
+          <t>single punch only</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B187" s="2" t="inlineStr">
+        <is>
+          <t>Employee 42</t>
+        </is>
+      </c>
+      <c r="C187" s="3" t="n">
+        <v>46261</v>
+      </c>
+      <c r="D187" s="4" t="n">
+        <v>0.8645833333333334</v>
+      </c>
+      <c r="E187" s="4" t="n">
+        <v>0.2833333333333333</v>
+      </c>
+      <c r="F187" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_152028.jpg</t>
+        </is>
+      </c>
+      <c r="G187" s="2" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B188" s="2" t="inlineStr">
+        <is>
+          <t>Employee 42</t>
+        </is>
+      </c>
+      <c r="C188" s="3" t="n">
+        <v>46260</v>
+      </c>
+      <c r="D188" s="4" t="n">
+        <v>0.6986111111111111</v>
+      </c>
+      <c r="E188" s="2" t="n"/>
+      <c r="F188" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_152039.jpg</t>
+        </is>
+      </c>
+      <c r="G188" s="2" t="inlineStr">
+        <is>
+          <t>single punch only</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B189" s="2" t="inlineStr">
+        <is>
+          <t>Employee 42</t>
+        </is>
+      </c>
+      <c r="C189" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="D189" s="4" t="n">
+        <v>0.6895833333333333</v>
+      </c>
+      <c r="E189" s="4" t="n">
+        <v>0.2868055555555555</v>
+      </c>
+      <c r="F189" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_152039.jpg</t>
+        </is>
+      </c>
+      <c r="G189" s="2" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B190" s="2" t="inlineStr">
+        <is>
+          <t>Employee 42</t>
+        </is>
+      </c>
+      <c r="C190" s="3" t="n">
+        <v>46258</v>
+      </c>
+      <c r="D190" s="4" t="n">
+        <v>0.7506944444444444</v>
+      </c>
+      <c r="E190" s="2" t="n"/>
+      <c r="F190" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_152039.jpg</t>
+        </is>
+      </c>
+      <c r="G190" s="2" t="inlineStr">
+        <is>
+          <t>single punch only</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B191" s="2" t="inlineStr">
+        <is>
+          <t>Employee 42</t>
+        </is>
+      </c>
+      <c r="C191" s="3" t="n">
+        <v>46257</v>
+      </c>
+      <c r="D191" s="4" t="n">
+        <v>0.7569444444444444</v>
+      </c>
+      <c r="E191" s="4" t="n">
+        <v>0.2548611111111111</v>
+      </c>
+      <c r="F191" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_152039.jpg</t>
+        </is>
+      </c>
+      <c r="G191" s="2" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B192" s="2" t="inlineStr">
+        <is>
+          <t>Employee 42</t>
+        </is>
+      </c>
+      <c r="C192" s="3" t="n">
+        <v>46256</v>
+      </c>
+      <c r="D192" s="4" t="n">
+        <v>0.74375</v>
+      </c>
+      <c r="E192" s="2" t="n"/>
+      <c r="F192" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_152049.jpg</t>
+        </is>
+      </c>
+      <c r="G192" s="2" t="inlineStr">
+        <is>
+          <t>single punch only</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B193" s="2" t="inlineStr">
+        <is>
+          <t>Employee 42</t>
+        </is>
+      </c>
+      <c r="C193" s="3" t="n">
+        <v>46254</v>
+      </c>
+      <c r="D193" s="2" t="n"/>
+      <c r="E193" s="4" t="n">
+        <v>0.2868055555555555</v>
+      </c>
+      <c r="F193" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_152049.jpg</t>
+        </is>
+      </c>
+      <c r="G193" s="2" t="inlineStr">
+        <is>
+          <t>single punch only</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B194" s="2" t="inlineStr">
+        <is>
+          <t>Employee 42</t>
+        </is>
+      </c>
+      <c r="C194" s="3" t="n">
+        <v>46253</v>
+      </c>
+      <c r="D194" s="4" t="n">
+        <v>0.74375</v>
+      </c>
+      <c r="E194" s="4" t="n">
+        <v>0.3166666666666667</v>
+      </c>
+      <c r="F194" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_152049.jpg</t>
+        </is>
+      </c>
+      <c r="G194" s="2" t="inlineStr">
+        <is>
+          <t>extra punch: 08:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B195" s="2" t="inlineStr">
+        <is>
+          <t>Employee 42</t>
+        </is>
+      </c>
+      <c r="C195" s="3" t="n">
+        <v>46252</v>
+      </c>
+      <c r="D195" s="4" t="n">
+        <v>0.7645833333333333</v>
+      </c>
+      <c r="E195" s="4" t="n">
+        <v>0.28125</v>
+      </c>
+      <c r="F195" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_152049.jpg</t>
+        </is>
+      </c>
+      <c r="G195" s="2" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B196" s="2" t="inlineStr">
+        <is>
+          <t>Employee 42</t>
+        </is>
+      </c>
+      <c r="C196" s="3" t="n">
+        <v>46251</v>
+      </c>
+      <c r="D196" s="4" t="n">
+        <v>0.7326388888888888</v>
+      </c>
+      <c r="E196" s="4" t="n">
+        <v>0.2833333333333333</v>
+      </c>
+      <c r="F196" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_152053.jpg</t>
+        </is>
+      </c>
+      <c r="G196" s="2" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B197" s="2" t="inlineStr">
+        <is>
+          <t>Employee 42</t>
+        </is>
+      </c>
+      <c r="C197" s="3" t="n">
+        <v>46250</v>
+      </c>
+      <c r="D197" s="4" t="n">
+        <v>0.7104166666666667</v>
+      </c>
+      <c r="E197" s="4" t="n">
+        <v>0.3409722222222222</v>
+      </c>
+      <c r="F197" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_152053.jpg</t>
+        </is>
+      </c>
+      <c r="G197" s="2" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B198" s="2" t="inlineStr">
+        <is>
+          <t>Employee 42</t>
+        </is>
+      </c>
+      <c r="C198" s="3" t="n">
+        <v>46249</v>
+      </c>
+      <c r="D198" s="4" t="n">
+        <v>0.7270833333333333</v>
+      </c>
+      <c r="E198" s="4" t="n">
+        <v>0.2423611111111111</v>
+      </c>
+      <c r="F198" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_152053.jpg</t>
+        </is>
+      </c>
+      <c r="G198" s="2" t="inlineStr">
+        <is>
+          <t>extra punches: 17:27 07:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B199" s="2" t="inlineStr">
+        <is>
+          <t>Employee 42</t>
+        </is>
+      </c>
+      <c r="C199" s="3" t="n">
+        <v>46247</v>
+      </c>
+      <c r="D199" s="4" t="n">
+        <v>0.7236111111111111</v>
+      </c>
+      <c r="E199" s="4" t="n">
+        <v>0.3388888888888889</v>
+      </c>
+      <c r="F199" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_152053.jpg</t>
+        </is>
+      </c>
+      <c r="G199" s="2" t="inlineStr">
+        <is>
+          <t>extra punch: 17:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B200" s="2" t="inlineStr">
+        <is>
+          <t>Employee 42</t>
+        </is>
+      </c>
+      <c r="C200" s="3" t="n">
+        <v>46246</v>
+      </c>
+      <c r="D200" s="4" t="n">
+        <v>0.7222222222222222</v>
+      </c>
+      <c r="E200" s="4" t="n">
+        <v>0.2548611111111111</v>
+      </c>
+      <c r="F200" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_152058.jpg</t>
+        </is>
+      </c>
+      <c r="G200" s="2" t="inlineStr">
+        <is>
+          <t>extra punches: 07:44 06:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B201" s="2" t="inlineStr">
+        <is>
+          <t>Employee 42</t>
+        </is>
+      </c>
+      <c r="C201" s="3" t="n">
+        <v>46245</v>
+      </c>
+      <c r="D201" s="4" t="n">
+        <v>0.7465277777777778</v>
+      </c>
+      <c r="E201" s="4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F201" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_152058.jpg</t>
+        </is>
+      </c>
+      <c r="G201" s="2" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B202" s="2" t="inlineStr">
+        <is>
+          <t>Employee 42</t>
+        </is>
+      </c>
+      <c r="C202" s="3" t="n">
+        <v>46244</v>
+      </c>
+      <c r="D202" s="4" t="n">
+        <v>0.7479166666666667</v>
+      </c>
+      <c r="E202" s="4" t="n">
+        <v>0.2875</v>
+      </c>
+      <c r="F202" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_152058.jpg</t>
+        </is>
+      </c>
+      <c r="G202" s="2" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B203" s="2" t="inlineStr">
+        <is>
+          <t>Employee 42</t>
+        </is>
+      </c>
+      <c r="C203" s="3" t="n">
+        <v>46243</v>
+      </c>
+      <c r="D203" s="4" t="n">
+        <v>0.7555555555555555</v>
+      </c>
+      <c r="E203" s="4" t="n">
+        <v>0.2784722222222222</v>
+      </c>
+      <c r="F203" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_152058.jpg</t>
+        </is>
+      </c>
+      <c r="G203" s="2" t="inlineStr"/>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B204" s="2" t="inlineStr">
+        <is>
+          <t>Employee 42</t>
+        </is>
+      </c>
+      <c r="C204" s="3" t="n">
+        <v>46242</v>
+      </c>
+      <c r="D204" s="4" t="n">
+        <v>0.7284722222222222</v>
+      </c>
+      <c r="E204" s="4" t="n">
+        <v>0.2791666666666667</v>
+      </c>
+      <c r="F204" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_152106.jpg</t>
+        </is>
+      </c>
+      <c r="G204" s="2" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B205" s="2" t="inlineStr">
+        <is>
+          <t>Employee 42</t>
+        </is>
+      </c>
+      <c r="C205" s="3" t="n">
+        <v>46240</v>
+      </c>
+      <c r="D205" s="4" t="n">
+        <v>0.7277777777777777</v>
+      </c>
+      <c r="E205" s="4" t="n">
+        <v>0.3986111111111111</v>
+      </c>
+      <c r="F205" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_152106.jpg</t>
+        </is>
+      </c>
+      <c r="G205" s="2" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B206" s="2" t="inlineStr">
+        <is>
+          <t>Employee 42</t>
+        </is>
+      </c>
+      <c r="C206" s="3" t="n">
+        <v>46239</v>
+      </c>
+      <c r="D206" s="4" t="n">
+        <v>0.7715277777777778</v>
+      </c>
+      <c r="E206" s="2" t="n"/>
+      <c r="F206" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_152106.jpg</t>
+        </is>
+      </c>
+      <c r="G206" s="2" t="inlineStr">
+        <is>
+          <t>single punch only</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B207" s="2" t="inlineStr">
+        <is>
+          <t>Employee 42</t>
+        </is>
+      </c>
+      <c r="C207" s="3" t="n">
+        <v>46238</v>
+      </c>
+      <c r="D207" s="4" t="n">
+        <v>0.7263888888888889</v>
+      </c>
+      <c r="E207" s="4" t="n">
+        <v>0.3305555555555555</v>
+      </c>
+      <c r="F207" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_152106.jpg</t>
+        </is>
+      </c>
+      <c r="G207" s="2" t="inlineStr"/>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B208" s="2" t="inlineStr">
+        <is>
+          <t>Employee 42</t>
+        </is>
+      </c>
+      <c r="C208" s="3" t="n">
+        <v>46237</v>
+      </c>
+      <c r="D208" s="4" t="n">
+        <v>0.7111111111111111</v>
+      </c>
+      <c r="E208" s="4" t="n">
+        <v>0.3291666666666667</v>
+      </c>
+      <c r="F208" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_152113.jpg</t>
+        </is>
+      </c>
+      <c r="G208" s="2" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B209" s="2" t="inlineStr">
+        <is>
+          <t>Employee 42</t>
+        </is>
+      </c>
+      <c r="C209" s="3" t="n">
+        <v>46236</v>
+      </c>
+      <c r="D209" s="4" t="n">
+        <v>0.3583333333333333</v>
+      </c>
+      <c r="E209" s="2" t="n"/>
+      <c r="F209" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_152113.jpg</t>
+        </is>
+      </c>
+      <c r="G209" s="2" t="inlineStr">
+        <is>
+          <t>single punch only</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B210" s="2" t="inlineStr">
+        <is>
+          <t>Employee 42</t>
+        </is>
+      </c>
+      <c r="C210" s="3" t="n">
+        <v>46235</v>
+      </c>
+      <c r="D210" s="4" t="n">
+        <v>0.7347222222222223</v>
+      </c>
+      <c r="E210" s="4" t="n">
+        <v>0.3305555555555555</v>
+      </c>
+      <c r="F210" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_152113.jpg</t>
+        </is>
+      </c>
+      <c r="G210" s="2" t="inlineStr">
+        <is>
+          <t>last day of month; final record</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B211" s="2" t="inlineStr">
+        <is>
+          <t>Employee 44</t>
+        </is>
+      </c>
+      <c r="C211" s="3" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D211" s="2" t="n"/>
+      <c r="E211" s="4" t="n">
+        <v>0.2569444444444444</v>
+      </c>
+      <c r="F211" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_152124.jpg</t>
+        </is>
+      </c>
+      <c r="G211" s="2" t="inlineStr">
+        <is>
+          <t>single punch only</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B212" s="2" t="inlineStr">
+        <is>
+          <t>Employee 44</t>
+        </is>
+      </c>
+      <c r="C212" s="3" t="n">
+        <v>46264</v>
+      </c>
+      <c r="D212" s="4" t="n">
+        <v>0.7458333333333333</v>
+      </c>
+      <c r="E212" s="4" t="n">
+        <v>0.2555555555555555</v>
+      </c>
+      <c r="F212" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_152124.jpg</t>
+        </is>
+      </c>
+      <c r="G212" s="2" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B213" s="2" t="inlineStr">
+        <is>
+          <t>Employee 44</t>
+        </is>
+      </c>
+      <c r="C213" s="3" t="n">
+        <v>46263</v>
+      </c>
+      <c r="D213" s="4" t="n">
+        <v>0.7444444444444445</v>
+      </c>
+      <c r="E213" s="4" t="n">
+        <v>0.2201388888888889</v>
+      </c>
+      <c r="F213" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_152124.jpg</t>
+        </is>
+      </c>
+      <c r="G213" s="2" t="inlineStr"/>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B214" s="2" t="inlineStr">
+        <is>
+          <t>Employee 44</t>
+        </is>
+      </c>
+      <c r="C214" s="3" t="n">
+        <v>46261</v>
+      </c>
+      <c r="D214" s="4" t="n">
+        <v>0.7569444444444444</v>
+      </c>
+      <c r="E214" s="4" t="n">
+        <v>0.2722222222222222</v>
+      </c>
+      <c r="F214" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_152124.jpg</t>
+        </is>
+      </c>
+      <c r="G214" s="2" t="inlineStr"/>
+    </row>
+    <row r="215">
+      <c r="A215" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B215" s="2" t="inlineStr">
+        <is>
+          <t>Employee 44</t>
+        </is>
+      </c>
+      <c r="C215" s="3" t="n">
+        <v>46260</v>
+      </c>
+      <c r="D215" s="4" t="n">
+        <v>0.7541666666666667</v>
+      </c>
+      <c r="E215" s="4" t="n">
+        <v>0.2555555555555555</v>
+      </c>
+      <c r="F215" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_152137.jpg</t>
+        </is>
+      </c>
+      <c r="G215" s="2" t="inlineStr"/>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B216" s="2" t="inlineStr">
+        <is>
+          <t>Employee 44</t>
+        </is>
+      </c>
+      <c r="C216" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="D216" s="4" t="n">
+        <v>0.7541666666666667</v>
+      </c>
+      <c r="E216" s="4" t="n">
+        <v>0.3555555555555556</v>
+      </c>
+      <c r="F216" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_152137.jpg</t>
+        </is>
+      </c>
+      <c r="G216" s="2" t="inlineStr">
+        <is>
+          <t>extra punch: 06:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B217" s="2" t="inlineStr">
+        <is>
+          <t>Employee 44</t>
+        </is>
+      </c>
+      <c r="C217" s="3" t="n">
+        <v>46258</v>
+      </c>
+      <c r="D217" s="4" t="n">
+        <v>0.7513888888888889</v>
+      </c>
+      <c r="E217" s="4" t="n">
+        <v>0.2319444444444445</v>
+      </c>
+      <c r="F217" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_152137.jpg</t>
+        </is>
+      </c>
+      <c r="G217" s="2" t="inlineStr">
+        <is>
+          <t>extra punch: 18:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B218" s="2" t="inlineStr">
+        <is>
+          <t>Employee 44</t>
+        </is>
+      </c>
+      <c r="C218" s="3" t="n">
+        <v>46257</v>
+      </c>
+      <c r="D218" s="4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E218" s="4" t="n">
+        <v>0.2402777777777778</v>
+      </c>
+      <c r="F218" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_152137.jpg</t>
+        </is>
+      </c>
+      <c r="G218" s="2" t="inlineStr"/>
+    </row>
+    <row r="219">
+      <c r="A219" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B219" s="2" t="inlineStr">
+        <is>
+          <t>Employee 44</t>
+        </is>
+      </c>
+      <c r="C219" s="3" t="n">
+        <v>46256</v>
+      </c>
+      <c r="D219" s="4" t="n">
+        <v>0.74375</v>
+      </c>
+      <c r="E219" s="4" t="n">
+        <v>0.2402777777777778</v>
+      </c>
+      <c r="F219" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_152141.jpg</t>
+        </is>
+      </c>
+      <c r="G219" s="2" t="inlineStr">
+        <is>
+          <t>extra punches: 17:51 06:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B220" s="2" t="inlineStr">
+        <is>
+          <t>Employee 44</t>
+        </is>
+      </c>
+      <c r="C220" s="3" t="n">
+        <v>46254</v>
+      </c>
+      <c r="D220" s="4" t="n">
+        <v>0.7451388888888889</v>
+      </c>
+      <c r="E220" s="4" t="n">
+        <v>0.2583333333333334</v>
+      </c>
+      <c r="F220" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_152141.jpg</t>
+        </is>
+      </c>
+      <c r="G220" s="2" t="inlineStr"/>
+    </row>
+    <row r="221">
+      <c r="A221" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B221" s="2" t="inlineStr">
+        <is>
+          <t>Employee 44</t>
+        </is>
+      </c>
+      <c r="C221" s="3" t="n">
+        <v>46253</v>
+      </c>
+      <c r="D221" s="4" t="n">
+        <v>0.7423611111111111</v>
+      </c>
+      <c r="E221" s="4" t="n">
+        <v>0.2527777777777778</v>
+      </c>
+      <c r="F221" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_152141.jpg</t>
+        </is>
+      </c>
+      <c r="G221" s="2" t="inlineStr"/>
+    </row>
+    <row r="222">
+      <c r="A222" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B222" s="2" t="inlineStr">
+        <is>
+          <t>Employee 44</t>
+        </is>
+      </c>
+      <c r="C222" s="3" t="n">
+        <v>46252</v>
+      </c>
+      <c r="D222" s="4" t="n">
+        <v>0.7611111111111111</v>
+      </c>
+      <c r="E222" s="4" t="n">
+        <v>0.2395833333333333</v>
+      </c>
+      <c r="F222" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_152141.jpg</t>
+        </is>
+      </c>
+      <c r="G222" s="2" t="inlineStr"/>
+    </row>
+    <row r="223">
+      <c r="A223" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B223" s="2" t="inlineStr">
+        <is>
+          <t>Employee 44</t>
+        </is>
+      </c>
+      <c r="C223" s="3" t="n">
+        <v>46251</v>
+      </c>
+      <c r="D223" s="4" t="n">
+        <v>0.7555555555555555</v>
+      </c>
+      <c r="E223" s="4" t="n">
+        <v>0.2541666666666667</v>
+      </c>
+      <c r="F223" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_152158.jpg</t>
+        </is>
+      </c>
+      <c r="G223" s="2" t="inlineStr"/>
+    </row>
+    <row r="224">
+      <c r="A224" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B224" s="2" t="inlineStr">
+        <is>
+          <t>Employee 44</t>
+        </is>
+      </c>
+      <c r="C224" s="3" t="n">
+        <v>46250</v>
+      </c>
+      <c r="D224" s="4" t="n">
+        <v>0.7458333333333333</v>
+      </c>
+      <c r="E224" s="4" t="n">
+        <v>0.25625</v>
+      </c>
+      <c r="F224" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_152158.jpg</t>
+        </is>
+      </c>
+      <c r="G224" s="2" t="inlineStr"/>
+    </row>
+    <row r="225">
+      <c r="A225" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B225" s="2" t="inlineStr">
+        <is>
+          <t>Employee 44</t>
+        </is>
+      </c>
+      <c r="C225" s="3" t="n">
+        <v>46249</v>
+      </c>
+      <c r="D225" s="4" t="n">
+        <v>0.7506944444444444</v>
+      </c>
+      <c r="E225" s="4" t="n">
+        <v>0.2333333333333333</v>
+      </c>
+      <c r="F225" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_152158.jpg</t>
+        </is>
+      </c>
+      <c r="G225" s="2" t="inlineStr">
+        <is>
+          <t>extra punch: 06:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B226" s="2" t="inlineStr">
+        <is>
+          <t>Employee 44</t>
+        </is>
+      </c>
+      <c r="C226" s="3" t="n">
+        <v>46247</v>
+      </c>
+      <c r="D226" s="4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E226" s="4" t="n">
+        <v>0.25625</v>
+      </c>
+      <c r="F226" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_152158.jpg</t>
+        </is>
+      </c>
+      <c r="G226" s="2" t="inlineStr"/>
+    </row>
+    <row r="227">
+      <c r="A227" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B227" s="2" t="inlineStr">
+        <is>
+          <t>Employee 44</t>
+        </is>
+      </c>
+      <c r="C227" s="3" t="n">
+        <v>46246</v>
+      </c>
+      <c r="D227" s="4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E227" s="4" t="n">
+        <v>0.2618055555555556</v>
+      </c>
+      <c r="F227" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_152205.jpg</t>
+        </is>
+      </c>
+      <c r="G227" s="2" t="inlineStr"/>
+    </row>
+    <row r="228">
+      <c r="A228" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B228" s="2" t="inlineStr">
+        <is>
+          <t>Employee 44</t>
+        </is>
+      </c>
+      <c r="C228" s="3" t="n">
+        <v>46245</v>
+      </c>
+      <c r="D228" s="4" t="n">
+        <v>0.7465277777777778</v>
+      </c>
+      <c r="E228" s="4" t="n">
+        <v>0.2541666666666667</v>
+      </c>
+      <c r="F228" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_152205.jpg</t>
+        </is>
+      </c>
+      <c r="G228" s="2" t="inlineStr"/>
+    </row>
+    <row r="229">
+      <c r="A229" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B229" s="2" t="inlineStr">
+        <is>
+          <t>Employee 44</t>
+        </is>
+      </c>
+      <c r="C229" s="3" t="n">
+        <v>46244</v>
+      </c>
+      <c r="D229" s="4" t="n">
+        <v>0.7479166666666667</v>
+      </c>
+      <c r="E229" s="4" t="n">
+        <v>0.2534722222222222</v>
+      </c>
+      <c r="F229" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_152205.jpg</t>
+        </is>
+      </c>
+      <c r="G229" s="2" t="inlineStr"/>
+    </row>
+    <row r="230">
+      <c r="A230" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B230" s="2" t="inlineStr">
+        <is>
+          <t>Employee 44</t>
+        </is>
+      </c>
+      <c r="C230" s="3" t="n">
+        <v>46243</v>
+      </c>
+      <c r="D230" s="4" t="n">
+        <v>0.6729166666666667</v>
+      </c>
+      <c r="E230" s="4" t="n">
+        <v>0.2368055555555555</v>
+      </c>
+      <c r="F230" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_152205.jpg</t>
+        </is>
+      </c>
+      <c r="G230" s="2" t="inlineStr"/>
+    </row>
+    <row r="231">
+      <c r="A231" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B231" s="2" t="inlineStr">
+        <is>
+          <t>Employee 44</t>
+        </is>
+      </c>
+      <c r="C231" s="3" t="n">
+        <v>46242</v>
+      </c>
+      <c r="D231" s="4" t="n">
+        <v>0.7291666666666666</v>
+      </c>
+      <c r="E231" s="4" t="n">
+        <v>0.2479166666666667</v>
+      </c>
+      <c r="F231" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_152209.jpg</t>
+        </is>
+      </c>
+      <c r="G231" s="2" t="inlineStr">
+        <is>
+          <t>extra punch: 07:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B232" s="2" t="inlineStr">
+        <is>
+          <t>Employee 44</t>
+        </is>
+      </c>
+      <c r="C232" s="3" t="n">
+        <v>46240</v>
+      </c>
+      <c r="D232" s="4" t="n">
+        <v>0.75625</v>
+      </c>
+      <c r="E232" s="4" t="n">
+        <v>0.2277777777777778</v>
+      </c>
+      <c r="F232" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_152209.jpg</t>
+        </is>
+      </c>
+      <c r="G232" s="2" t="inlineStr"/>
+    </row>
+    <row r="233">
+      <c r="A233" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B233" s="2" t="inlineStr">
+        <is>
+          <t>Employee 44</t>
+        </is>
+      </c>
+      <c r="C233" s="3" t="n">
+        <v>46239</v>
+      </c>
+      <c r="D233" s="4" t="n">
+        <v>0.7611111111111111</v>
+      </c>
+      <c r="E233" s="4" t="n">
+        <v>0.2333333333333333</v>
+      </c>
+      <c r="F233" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_152209.jpg</t>
+        </is>
+      </c>
+      <c r="G233" s="2" t="inlineStr">
+        <is>
+          <t>extra punch: 18:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B234" s="2" t="inlineStr">
+        <is>
+          <t>Employee 44</t>
+        </is>
+      </c>
+      <c r="C234" s="3" t="n">
+        <v>46238</v>
+      </c>
+      <c r="D234" s="4" t="n">
+        <v>0.7604166666666666</v>
+      </c>
+      <c r="E234" s="4" t="n">
+        <v>0.2173611111111111</v>
+      </c>
+      <c r="F234" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_152209.jpg</t>
+        </is>
+      </c>
+      <c r="G234" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/timesheet.xlsx
+++ b/output/timesheet.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G234"/>
+  <dimension ref="A1:G288"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1242,7 +1242,9 @@
       <c r="C29" s="3" t="n">
         <v>46265</v>
       </c>
-      <c r="D29" s="2" t="n"/>
+      <c r="D29" s="4" t="n">
+        <v>0.7354166666666667</v>
+      </c>
       <c r="E29" s="4" t="n">
         <v>0.2527777777777778</v>
       </c>
@@ -1253,7 +1255,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>corrected from a clearer re-scan photo later in the album</t>
         </is>
       </c>
     </row>
@@ -2616,7 +2618,9 @@
       <c r="C79" s="3" t="n">
         <v>46265</v>
       </c>
-      <c r="D79" s="2" t="n"/>
+      <c r="D79" s="4" t="n">
+        <v>0.7604166666666666</v>
+      </c>
       <c r="E79" s="4" t="n">
         <v>0.2527777777777778</v>
       </c>
@@ -2627,7 +2631,7 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>corrected from a clearer re-scan photo later in the album</t>
         </is>
       </c>
     </row>
@@ -3363,7 +3367,9 @@
       <c r="C106" s="3" t="n">
         <v>46265</v>
       </c>
-      <c r="D106" s="2" t="n"/>
+      <c r="D106" s="4" t="n">
+        <v>0.7513888888888889</v>
+      </c>
       <c r="E106" s="4" t="n">
         <v>0.2777777777777778</v>
       </c>
@@ -3374,7 +3380,7 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>corrected from a clearer re-scan photo later in the album</t>
         </is>
       </c>
     </row>
@@ -4135,9 +4141,11 @@
       <c r="C134" s="3" t="n">
         <v>46265</v>
       </c>
-      <c r="D134" s="2" t="n"/>
+      <c r="D134" s="4" t="n">
+        <v>0.7520833333333333</v>
+      </c>
       <c r="E134" s="4" t="n">
-        <v>0.2416666666666667</v>
+        <v>0.2361111111111111</v>
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
@@ -4146,7 +4154,7 @@
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>corrected from a clearer re-scan photo later in the album</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5509,9 @@
       <c r="C184" s="3" t="n">
         <v>46265</v>
       </c>
-      <c r="D184" s="2" t="n"/>
+      <c r="D184" s="4" t="n">
+        <v>0.7215277777777778</v>
+      </c>
       <c r="E184" s="4" t="n">
         <v>0.3888888888888889</v>
       </c>
@@ -5512,7 +5522,7 @@
       </c>
       <c r="G184" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>corrected from a clearer re-scan photo later in the album</t>
         </is>
       </c>
     </row>
@@ -6266,7 +6276,9 @@
       <c r="C211" s="3" t="n">
         <v>46265</v>
       </c>
-      <c r="D211" s="2" t="n"/>
+      <c r="D211" s="4" t="n">
+        <v>0.7527777777777778</v>
+      </c>
       <c r="E211" s="4" t="n">
         <v>0.2569444444444444</v>
       </c>
@@ -6277,7 +6289,7 @@
       </c>
       <c r="G211" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>corrected from a clearer re-scan photo later in the album</t>
         </is>
       </c>
     </row>
@@ -6925,6 +6937,1490 @@
         </is>
       </c>
       <c r="G234" s="2" t="inlineStr"/>
+    </row>
+    <row r="235">
+      <c r="A235" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B235" s="2" t="inlineStr">
+        <is>
+          <t>Employee 44</t>
+        </is>
+      </c>
+      <c r="C235" s="3" t="n">
+        <v>46237</v>
+      </c>
+      <c r="D235" s="4" t="n">
+        <v>0.7402777777777778</v>
+      </c>
+      <c r="E235" s="4" t="n">
+        <v>0.2472222222222222</v>
+      </c>
+      <c r="F235" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_152214.jpg</t>
+        </is>
+      </c>
+      <c r="G235" s="2" t="inlineStr">
+        <is>
+          <t>extra punch: 17:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B236" s="2" t="inlineStr">
+        <is>
+          <t>Employee 44</t>
+        </is>
+      </c>
+      <c r="C236" s="3" t="n">
+        <v>46236</v>
+      </c>
+      <c r="D236" s="4" t="n">
+        <v>0.7381944444444445</v>
+      </c>
+      <c r="E236" s="4" t="n">
+        <v>0.2201388888888889</v>
+      </c>
+      <c r="F236" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_152214.jpg</t>
+        </is>
+      </c>
+      <c r="G236" s="2" t="inlineStr"/>
+    </row>
+    <row r="237">
+      <c r="A237" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B237" s="2" t="inlineStr">
+        <is>
+          <t>Employee 44</t>
+        </is>
+      </c>
+      <c r="C237" s="3" t="n">
+        <v>46235</v>
+      </c>
+      <c r="D237" s="4" t="n">
+        <v>0.7430555555555556</v>
+      </c>
+      <c r="E237" s="4" t="n">
+        <v>0.2569444444444444</v>
+      </c>
+      <c r="F237" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260831_152214.jpg</t>
+        </is>
+      </c>
+      <c r="G237" s="2" t="inlineStr">
+        <is>
+          <t>extra punch: 17:55; last day of month; final record</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B238" s="2" t="inlineStr">
+        <is>
+          <t>Employee 4</t>
+        </is>
+      </c>
+      <c r="C238" s="3" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D238" s="4" t="n">
+        <v>0.7527777777777778</v>
+      </c>
+      <c r="E238" s="4" t="n">
+        <v>0.2493055555555556</v>
+      </c>
+      <c r="F238" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260901_065955.jpg</t>
+        </is>
+      </c>
+      <c r="G238" s="2" t="inlineStr"/>
+    </row>
+    <row r="239">
+      <c r="A239" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B239" s="2" t="inlineStr">
+        <is>
+          <t>Employee 4</t>
+        </is>
+      </c>
+      <c r="C239" s="3" t="n">
+        <v>46264</v>
+      </c>
+      <c r="D239" s="4" t="n">
+        <v>0.7458333333333333</v>
+      </c>
+      <c r="E239" s="4" t="n">
+        <v>0.3006944444444444</v>
+      </c>
+      <c r="F239" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260901_065955.jpg</t>
+        </is>
+      </c>
+      <c r="G239" s="2" t="inlineStr"/>
+    </row>
+    <row r="240">
+      <c r="A240" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B240" s="2" t="inlineStr">
+        <is>
+          <t>Employee 4</t>
+        </is>
+      </c>
+      <c r="C240" s="3" t="n">
+        <v>46263</v>
+      </c>
+      <c r="D240" s="4" t="n">
+        <v>0.6736111111111112</v>
+      </c>
+      <c r="E240" s="4" t="n">
+        <v>0.30625</v>
+      </c>
+      <c r="F240" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260901_065955.jpg</t>
+        </is>
+      </c>
+      <c r="G240" s="2" t="inlineStr"/>
+    </row>
+    <row r="241">
+      <c r="A241" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B241" s="2" t="inlineStr">
+        <is>
+          <t>Employee 4</t>
+        </is>
+      </c>
+      <c r="C241" s="3" t="n">
+        <v>46261</v>
+      </c>
+      <c r="D241" s="4" t="n">
+        <v>0.6916666666666667</v>
+      </c>
+      <c r="E241" s="4" t="n">
+        <v>0.2791666666666667</v>
+      </c>
+      <c r="F241" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260901_065955.jpg</t>
+        </is>
+      </c>
+      <c r="G241" s="2" t="inlineStr"/>
+    </row>
+    <row r="242">
+      <c r="A242" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B242" s="2" t="inlineStr">
+        <is>
+          <t>Employee 4</t>
+        </is>
+      </c>
+      <c r="C242" s="3" t="n">
+        <v>46260</v>
+      </c>
+      <c r="D242" s="2" t="n"/>
+      <c r="E242" s="2" t="n"/>
+      <c r="F242" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260901_065955.jpg</t>
+        </is>
+      </c>
+      <c r="G242" s="2" t="inlineStr">
+        <is>
+          <t>PLEASE VERIFY: check-in/out times not captured (gap between source photos)</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B243" s="2" t="inlineStr">
+        <is>
+          <t>Employee 6</t>
+        </is>
+      </c>
+      <c r="C243" s="3" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D243" s="4" t="n">
+        <v>0.7375</v>
+      </c>
+      <c r="E243" s="4" t="n">
+        <v>0.2451388888888889</v>
+      </c>
+      <c r="F243" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260901_070012.jpg</t>
+        </is>
+      </c>
+      <c r="G243" s="2" t="inlineStr"/>
+    </row>
+    <row r="244">
+      <c r="A244" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B244" s="2" t="inlineStr">
+        <is>
+          <t>Employee 6</t>
+        </is>
+      </c>
+      <c r="C244" s="3" t="n">
+        <v>46264</v>
+      </c>
+      <c r="D244" s="4" t="n">
+        <v>0.6888888888888889</v>
+      </c>
+      <c r="E244" s="4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F244" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260901_070012.jpg</t>
+        </is>
+      </c>
+      <c r="G244" s="2" t="inlineStr"/>
+    </row>
+    <row r="245">
+      <c r="A245" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B245" s="2" t="inlineStr">
+        <is>
+          <t>Employee 6</t>
+        </is>
+      </c>
+      <c r="C245" s="3" t="n">
+        <v>46263</v>
+      </c>
+      <c r="D245" s="4" t="n">
+        <v>0.7083333333333334</v>
+      </c>
+      <c r="E245" s="4" t="n">
+        <v>0.2465277777777778</v>
+      </c>
+      <c r="F245" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260901_070012.jpg</t>
+        </is>
+      </c>
+      <c r="G245" s="2" t="inlineStr"/>
+    </row>
+    <row r="246">
+      <c r="A246" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B246" s="2" t="inlineStr">
+        <is>
+          <t>Employee 6</t>
+        </is>
+      </c>
+      <c r="C246" s="3" t="n">
+        <v>46261</v>
+      </c>
+      <c r="D246" s="4" t="n">
+        <v>0.6986111111111111</v>
+      </c>
+      <c r="E246" s="4" t="n">
+        <v>0.2569444444444444</v>
+      </c>
+      <c r="F246" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260901_070012.jpg</t>
+        </is>
+      </c>
+      <c r="G246" s="2" t="inlineStr"/>
+    </row>
+    <row r="247">
+      <c r="A247" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B247" s="2" t="inlineStr">
+        <is>
+          <t>Employee 6</t>
+        </is>
+      </c>
+      <c r="C247" s="3" t="n">
+        <v>46260</v>
+      </c>
+      <c r="D247" s="2" t="n"/>
+      <c r="E247" s="2" t="n"/>
+      <c r="F247" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260901_070012.jpg</t>
+        </is>
+      </c>
+      <c r="G247" s="2" t="inlineStr">
+        <is>
+          <t>PLEASE VERIFY: check-in/out times not captured (gap between source photos)</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B248" s="2" t="inlineStr">
+        <is>
+          <t>Employee 7</t>
+        </is>
+      </c>
+      <c r="C248" s="3" t="n">
+        <v>46263</v>
+      </c>
+      <c r="D248" s="2" t="n"/>
+      <c r="E248" s="4" t="n">
+        <v>0.2986111111111111</v>
+      </c>
+      <c r="F248" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260901_070022.jpg</t>
+        </is>
+      </c>
+      <c r="G248" s="2" t="inlineStr">
+        <is>
+          <t>single punch only</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B249" s="2" t="inlineStr">
+        <is>
+          <t>Employee 7</t>
+        </is>
+      </c>
+      <c r="C249" s="3" t="n">
+        <v>46261</v>
+      </c>
+      <c r="D249" s="4" t="n">
+        <v>0.8090277777777778</v>
+      </c>
+      <c r="E249" s="4" t="n">
+        <v>0.3375</v>
+      </c>
+      <c r="F249" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260901_070022.jpg</t>
+        </is>
+      </c>
+      <c r="G249" s="2" t="inlineStr"/>
+    </row>
+    <row r="250">
+      <c r="A250" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B250" s="2" t="inlineStr">
+        <is>
+          <t>Employee 7</t>
+        </is>
+      </c>
+      <c r="C250" s="3" t="n">
+        <v>46260</v>
+      </c>
+      <c r="D250" s="4" t="n">
+        <v>0.8083333333333333</v>
+      </c>
+      <c r="E250" s="4" t="n">
+        <v>0.3854166666666667</v>
+      </c>
+      <c r="F250" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260901_070022.jpg</t>
+        </is>
+      </c>
+      <c r="G250" s="2" t="inlineStr"/>
+    </row>
+    <row r="251">
+      <c r="A251" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B251" s="2" t="inlineStr">
+        <is>
+          <t>Employee 7</t>
+        </is>
+      </c>
+      <c r="C251" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="D251" s="4" t="n">
+        <v>0.7506944444444444</v>
+      </c>
+      <c r="E251" s="4" t="n">
+        <v>0.2673611111111111</v>
+      </c>
+      <c r="F251" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260901_070022.jpg</t>
+        </is>
+      </c>
+      <c r="G251" s="2" t="inlineStr"/>
+    </row>
+    <row r="252">
+      <c r="A252" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B252" s="2" t="inlineStr">
+        <is>
+          <t>Employee 9</t>
+        </is>
+      </c>
+      <c r="C252" s="3" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D252" s="4" t="n">
+        <v>0.7555555555555555</v>
+      </c>
+      <c r="E252" s="4" t="n">
+        <v>0.2472222222222222</v>
+      </c>
+      <c r="F252" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260901_070037.jpg</t>
+        </is>
+      </c>
+      <c r="G252" s="2" t="inlineStr"/>
+    </row>
+    <row r="253">
+      <c r="A253" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B253" s="2" t="inlineStr">
+        <is>
+          <t>Employee 9</t>
+        </is>
+      </c>
+      <c r="C253" s="3" t="n">
+        <v>46264</v>
+      </c>
+      <c r="D253" s="4" t="n">
+        <v>0.6805555555555556</v>
+      </c>
+      <c r="E253" s="4" t="n">
+        <v>0.30625</v>
+      </c>
+      <c r="F253" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260901_070037.jpg</t>
+        </is>
+      </c>
+      <c r="G253" s="2" t="inlineStr"/>
+    </row>
+    <row r="254">
+      <c r="A254" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B254" s="2" t="inlineStr">
+        <is>
+          <t>Employee 9</t>
+        </is>
+      </c>
+      <c r="C254" s="3" t="n">
+        <v>46263</v>
+      </c>
+      <c r="D254" s="4" t="n">
+        <v>0.7708333333333334</v>
+      </c>
+      <c r="E254" s="4" t="n">
+        <v>0.2993055555555555</v>
+      </c>
+      <c r="F254" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260901_070037.jpg</t>
+        </is>
+      </c>
+      <c r="G254" s="2" t="inlineStr"/>
+    </row>
+    <row r="255">
+      <c r="A255" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B255" s="2" t="inlineStr">
+        <is>
+          <t>Employee 9</t>
+        </is>
+      </c>
+      <c r="C255" s="3" t="n">
+        <v>46261</v>
+      </c>
+      <c r="D255" s="4" t="n">
+        <v>0.7861111111111111</v>
+      </c>
+      <c r="E255" s="4" t="n">
+        <v>0.2826388888888889</v>
+      </c>
+      <c r="F255" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260901_070037.jpg</t>
+        </is>
+      </c>
+      <c r="G255" s="2" t="inlineStr"/>
+    </row>
+    <row r="256">
+      <c r="A256" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B256" s="2" t="inlineStr">
+        <is>
+          <t>Employee 9</t>
+        </is>
+      </c>
+      <c r="C256" s="3" t="n">
+        <v>46260</v>
+      </c>
+      <c r="D256" s="2" t="n"/>
+      <c r="E256" s="2" t="n"/>
+      <c r="F256" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260901_070037.jpg</t>
+        </is>
+      </c>
+      <c r="G256" s="2" t="inlineStr">
+        <is>
+          <t>PLEASE VERIFY: check-in/out times not captured (gap between source photos)</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B257" s="2" t="inlineStr">
+        <is>
+          <t>Employee 10</t>
+        </is>
+      </c>
+      <c r="C257" s="3" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D257" s="4" t="n">
+        <v>0.7534722222222222</v>
+      </c>
+      <c r="E257" s="4" t="n">
+        <v>0.2805555555555556</v>
+      </c>
+      <c r="F257" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260901_070045.jpg</t>
+        </is>
+      </c>
+      <c r="G257" s="2" t="inlineStr"/>
+    </row>
+    <row r="258">
+      <c r="A258" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B258" s="2" t="inlineStr">
+        <is>
+          <t>Employee 10</t>
+        </is>
+      </c>
+      <c r="C258" s="3" t="n">
+        <v>46263</v>
+      </c>
+      <c r="D258" s="4" t="n">
+        <v>0.4041666666666667</v>
+      </c>
+      <c r="E258" s="2" t="n"/>
+      <c r="F258" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260901_070045.jpg</t>
+        </is>
+      </c>
+      <c r="G258" s="2" t="inlineStr">
+        <is>
+          <t>single punch only</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B259" s="2" t="inlineStr">
+        <is>
+          <t>Employee 10</t>
+        </is>
+      </c>
+      <c r="C259" s="3" t="n">
+        <v>46261</v>
+      </c>
+      <c r="D259" s="4" t="n">
+        <v>0.7395833333333334</v>
+      </c>
+      <c r="E259" s="2" t="n"/>
+      <c r="F259" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260901_070045.jpg</t>
+        </is>
+      </c>
+      <c r="G259" s="2" t="inlineStr">
+        <is>
+          <t>single punch only</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B260" s="2" t="inlineStr">
+        <is>
+          <t>Employee 10</t>
+        </is>
+      </c>
+      <c r="C260" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="D260" s="4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E260" s="2" t="n"/>
+      <c r="F260" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260901_070045.jpg</t>
+        </is>
+      </c>
+      <c r="G260" s="2" t="inlineStr">
+        <is>
+          <t>single punch only</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B261" s="2" t="inlineStr">
+        <is>
+          <t>Employee 10</t>
+        </is>
+      </c>
+      <c r="C261" s="3" t="n">
+        <v>46258</v>
+      </c>
+      <c r="D261" s="2" t="n"/>
+      <c r="E261" s="2" t="n"/>
+      <c r="F261" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260901_070045.jpg</t>
+        </is>
+      </c>
+      <c r="G261" s="2" t="inlineStr">
+        <is>
+          <t>PLEASE VERIFY: check-in/out time not captured (gap between source photos)</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B262" s="2" t="inlineStr">
+        <is>
+          <t>Employee 19</t>
+        </is>
+      </c>
+      <c r="C262" s="3" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D262" s="4" t="n">
+        <v>0.7680555555555556</v>
+      </c>
+      <c r="E262" s="4" t="n">
+        <v>0.3319444444444444</v>
+      </c>
+      <c r="F262" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260901_070157.jpg</t>
+        </is>
+      </c>
+      <c r="G262" s="2" t="inlineStr"/>
+    </row>
+    <row r="263">
+      <c r="A263" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B263" s="2" t="inlineStr">
+        <is>
+          <t>Employee 19</t>
+        </is>
+      </c>
+      <c r="C263" s="3" t="n">
+        <v>46264</v>
+      </c>
+      <c r="D263" s="4" t="n">
+        <v>0.7534722222222222</v>
+      </c>
+      <c r="E263" s="4" t="n">
+        <v>0.3534722222222222</v>
+      </c>
+      <c r="F263" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260901_070157.jpg</t>
+        </is>
+      </c>
+      <c r="G263" s="2" t="inlineStr"/>
+    </row>
+    <row r="264">
+      <c r="A264" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B264" s="2" t="inlineStr">
+        <is>
+          <t>Employee 19</t>
+        </is>
+      </c>
+      <c r="C264" s="3" t="n">
+        <v>46263</v>
+      </c>
+      <c r="D264" s="4" t="n">
+        <v>0.7569444444444444</v>
+      </c>
+      <c r="E264" s="4" t="n">
+        <v>0.3652777777777778</v>
+      </c>
+      <c r="F264" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260901_070157.jpg</t>
+        </is>
+      </c>
+      <c r="G264" s="2" t="inlineStr"/>
+    </row>
+    <row r="265">
+      <c r="A265" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B265" s="2" t="inlineStr">
+        <is>
+          <t>Employee 19</t>
+        </is>
+      </c>
+      <c r="C265" s="3" t="n">
+        <v>46261</v>
+      </c>
+      <c r="D265" s="4" t="n">
+        <v>0.7395833333333334</v>
+      </c>
+      <c r="E265" s="4" t="n">
+        <v>0.3652777777777778</v>
+      </c>
+      <c r="F265" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260901_070157.jpg</t>
+        </is>
+      </c>
+      <c r="G265" s="2" t="inlineStr"/>
+    </row>
+    <row r="266">
+      <c r="A266" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B266" s="2" t="inlineStr">
+        <is>
+          <t>Employee 19</t>
+        </is>
+      </c>
+      <c r="C266" s="3" t="n">
+        <v>46260</v>
+      </c>
+      <c r="D266" s="2" t="n"/>
+      <c r="E266" s="2" t="n"/>
+      <c r="F266" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260901_070157.jpg</t>
+        </is>
+      </c>
+      <c r="G266" s="2" t="inlineStr">
+        <is>
+          <t>PLEASE VERIFY: check-in/out times not captured (gap between source photos)</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B267" s="2" t="inlineStr">
+        <is>
+          <t>Employee 21</t>
+        </is>
+      </c>
+      <c r="C267" s="3" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D267" s="4" t="n">
+        <v>0.7555555555555555</v>
+      </c>
+      <c r="E267" s="4" t="n">
+        <v>0.2631944444444445</v>
+      </c>
+      <c r="F267" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260901_070210.jpg</t>
+        </is>
+      </c>
+      <c r="G267" s="2" t="inlineStr"/>
+    </row>
+    <row r="268">
+      <c r="A268" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B268" s="2" t="inlineStr">
+        <is>
+          <t>Employee 21</t>
+        </is>
+      </c>
+      <c r="C268" s="3" t="n">
+        <v>46264</v>
+      </c>
+      <c r="D268" s="4" t="n">
+        <v>0.7493055555555556</v>
+      </c>
+      <c r="E268" s="4" t="n">
+        <v>0.3194444444444444</v>
+      </c>
+      <c r="F268" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260901_070210.jpg</t>
+        </is>
+      </c>
+      <c r="G268" s="2" t="inlineStr"/>
+    </row>
+    <row r="269">
+      <c r="A269" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B269" s="2" t="inlineStr">
+        <is>
+          <t>Employee 21</t>
+        </is>
+      </c>
+      <c r="C269" s="3" t="n">
+        <v>46263</v>
+      </c>
+      <c r="D269" s="4" t="n">
+        <v>0.7513888888888889</v>
+      </c>
+      <c r="E269" s="4" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="F269" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260901_070210.jpg</t>
+        </is>
+      </c>
+      <c r="G269" s="2" t="inlineStr"/>
+    </row>
+    <row r="270">
+      <c r="A270" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B270" s="2" t="inlineStr">
+        <is>
+          <t>Employee 21</t>
+        </is>
+      </c>
+      <c r="C270" s="3" t="n">
+        <v>46261</v>
+      </c>
+      <c r="D270" s="4" t="n">
+        <v>0.7430555555555556</v>
+      </c>
+      <c r="E270" s="4" t="n">
+        <v>0.2909722222222222</v>
+      </c>
+      <c r="F270" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260901_070210.jpg</t>
+        </is>
+      </c>
+      <c r="G270" s="2" t="inlineStr"/>
+    </row>
+    <row r="271">
+      <c r="A271" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B271" s="2" t="inlineStr">
+        <is>
+          <t>Employee 21</t>
+        </is>
+      </c>
+      <c r="C271" s="3" t="n">
+        <v>46260</v>
+      </c>
+      <c r="D271" s="2" t="n"/>
+      <c r="E271" s="2" t="n"/>
+      <c r="F271" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260901_070210.jpg</t>
+        </is>
+      </c>
+      <c r="G271" s="2" t="inlineStr">
+        <is>
+          <t>PLEASE VERIFY: check-in/out times not captured (gap between source photos)</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B272" s="2" t="inlineStr">
+        <is>
+          <t>Employee 25</t>
+        </is>
+      </c>
+      <c r="C272" s="3" t="n">
+        <v>46264</v>
+      </c>
+      <c r="D272" s="4" t="n">
+        <v>0.7354166666666667</v>
+      </c>
+      <c r="E272" s="4" t="n">
+        <v>0.3208333333333334</v>
+      </c>
+      <c r="F272" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260901_070242.jpg</t>
+        </is>
+      </c>
+      <c r="G272" s="2" t="inlineStr"/>
+    </row>
+    <row r="273">
+      <c r="A273" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B273" s="2" t="inlineStr">
+        <is>
+          <t>Employee 25</t>
+        </is>
+      </c>
+      <c r="C273" s="3" t="n">
+        <v>46263</v>
+      </c>
+      <c r="D273" s="4" t="n">
+        <v>0.8895833333333333</v>
+      </c>
+      <c r="E273" s="4" t="n">
+        <v>0.3347222222222222</v>
+      </c>
+      <c r="F273" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260901_070242.jpg</t>
+        </is>
+      </c>
+      <c r="G273" s="2" t="inlineStr">
+        <is>
+          <t>extra punch: 08:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B274" s="2" t="inlineStr">
+        <is>
+          <t>Employee 25</t>
+        </is>
+      </c>
+      <c r="C274" s="3" t="n">
+        <v>46261</v>
+      </c>
+      <c r="D274" s="4" t="n">
+        <v>0.7493055555555556</v>
+      </c>
+      <c r="E274" s="4" t="n">
+        <v>0.2798611111111111</v>
+      </c>
+      <c r="F274" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260901_070242.jpg</t>
+        </is>
+      </c>
+      <c r="G274" s="2" t="inlineStr"/>
+    </row>
+    <row r="275">
+      <c r="A275" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B275" s="2" t="inlineStr">
+        <is>
+          <t>Employee 25</t>
+        </is>
+      </c>
+      <c r="C275" s="3" t="n">
+        <v>46260</v>
+      </c>
+      <c r="D275" s="4" t="n">
+        <v>0.8013888888888889</v>
+      </c>
+      <c r="E275" s="4" t="n">
+        <v>0.3055555555555556</v>
+      </c>
+      <c r="F275" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260901_070242.jpg</t>
+        </is>
+      </c>
+      <c r="G275" s="2" t="inlineStr"/>
+    </row>
+    <row r="276">
+      <c r="A276" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B276" s="2" t="inlineStr">
+        <is>
+          <t>Employee 27</t>
+        </is>
+      </c>
+      <c r="C276" s="3" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D276" s="4" t="n">
+        <v>0.9326388888888889</v>
+      </c>
+      <c r="E276" s="4" t="n">
+        <v>0.1479166666666667</v>
+      </c>
+      <c r="F276" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260901_070256.jpg</t>
+        </is>
+      </c>
+      <c r="G276" s="2" t="inlineStr">
+        <is>
+          <t>extra punch: 22:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B277" s="2" t="inlineStr">
+        <is>
+          <t>Employee 27</t>
+        </is>
+      </c>
+      <c r="C277" s="3" t="n">
+        <v>46264</v>
+      </c>
+      <c r="D277" s="4" t="n">
+        <v>0.75625</v>
+      </c>
+      <c r="E277" s="4" t="n">
+        <v>0.14375</v>
+      </c>
+      <c r="F277" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260901_070256.jpg</t>
+        </is>
+      </c>
+      <c r="G277" s="2" t="inlineStr"/>
+    </row>
+    <row r="278">
+      <c r="A278" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B278" s="2" t="inlineStr">
+        <is>
+          <t>Employee 27</t>
+        </is>
+      </c>
+      <c r="C278" s="3" t="n">
+        <v>46263</v>
+      </c>
+      <c r="D278" s="4" t="n">
+        <v>0.7479166666666667</v>
+      </c>
+      <c r="E278" s="4" t="n">
+        <v>0.1451388888888889</v>
+      </c>
+      <c r="F278" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260901_070256.jpg</t>
+        </is>
+      </c>
+      <c r="G278" s="2" t="inlineStr"/>
+    </row>
+    <row r="279">
+      <c r="A279" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B279" s="2" t="inlineStr">
+        <is>
+          <t>Employee 27</t>
+        </is>
+      </c>
+      <c r="C279" s="3" t="n">
+        <v>46262</v>
+      </c>
+      <c r="D279" s="4" t="n">
+        <v>0.7159722222222222</v>
+      </c>
+      <c r="E279" s="4" t="n">
+        <v>0.1493055555555556</v>
+      </c>
+      <c r="F279" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260901_070256.jpg</t>
+        </is>
+      </c>
+      <c r="G279" s="2" t="inlineStr"/>
+    </row>
+    <row r="280">
+      <c r="A280" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B280" s="2" t="inlineStr">
+        <is>
+          <t>Employee 28</t>
+        </is>
+      </c>
+      <c r="C280" s="3" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D280" s="4" t="n">
+        <v>0.4131944444444444</v>
+      </c>
+      <c r="E280" s="4" t="n">
+        <v>0.1868055555555556</v>
+      </c>
+      <c r="F280" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260901_070305.jpg</t>
+        </is>
+      </c>
+      <c r="G280" s="2" t="inlineStr"/>
+    </row>
+    <row r="281">
+      <c r="A281" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B281" s="2" t="inlineStr">
+        <is>
+          <t>Employee 28</t>
+        </is>
+      </c>
+      <c r="C281" s="3" t="n">
+        <v>46264</v>
+      </c>
+      <c r="D281" s="4" t="n">
+        <v>0.5097222222222222</v>
+      </c>
+      <c r="E281" s="4" t="n">
+        <v>0.1847222222222222</v>
+      </c>
+      <c r="F281" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260901_070305.jpg</t>
+        </is>
+      </c>
+      <c r="G281" s="2" t="inlineStr"/>
+    </row>
+    <row r="282">
+      <c r="A282" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B282" s="2" t="inlineStr">
+        <is>
+          <t>Employee 28</t>
+        </is>
+      </c>
+      <c r="C282" s="3" t="n">
+        <v>46263</v>
+      </c>
+      <c r="D282" s="4" t="n">
+        <v>0.4527777777777778</v>
+      </c>
+      <c r="E282" s="4" t="n">
+        <v>0.1847222222222222</v>
+      </c>
+      <c r="F282" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260901_070305.jpg</t>
+        </is>
+      </c>
+      <c r="G282" s="2" t="inlineStr"/>
+    </row>
+    <row r="283">
+      <c r="A283" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B283" s="2" t="inlineStr">
+        <is>
+          <t>Employee 28</t>
+        </is>
+      </c>
+      <c r="C283" s="3" t="n">
+        <v>46262</v>
+      </c>
+      <c r="D283" s="4" t="n">
+        <v>0.4055555555555556</v>
+      </c>
+      <c r="E283" s="4" t="n">
+        <v>0.1881944444444444</v>
+      </c>
+      <c r="F283" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260901_070305.jpg</t>
+        </is>
+      </c>
+      <c r="G283" s="2" t="inlineStr"/>
+    </row>
+    <row r="284">
+      <c r="A284" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B284" s="2" t="inlineStr">
+        <is>
+          <t>Employee 37</t>
+        </is>
+      </c>
+      <c r="C284" s="3" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D284" s="4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E284" s="4" t="n">
+        <v>0.2909722222222222</v>
+      </c>
+      <c r="F284" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260901_070423.jpg</t>
+        </is>
+      </c>
+      <c r="G284" s="2" t="inlineStr"/>
+    </row>
+    <row r="285">
+      <c r="A285" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B285" s="2" t="inlineStr">
+        <is>
+          <t>Employee 37</t>
+        </is>
+      </c>
+      <c r="C285" s="3" t="n">
+        <v>46264</v>
+      </c>
+      <c r="D285" s="4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E285" s="4" t="n">
+        <v>0.2888888888888889</v>
+      </c>
+      <c r="F285" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260901_070423.jpg</t>
+        </is>
+      </c>
+      <c r="G285" s="2" t="inlineStr"/>
+    </row>
+    <row r="286">
+      <c r="A286" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B286" s="2" t="inlineStr">
+        <is>
+          <t>Employee 37</t>
+        </is>
+      </c>
+      <c r="C286" s="3" t="n">
+        <v>46263</v>
+      </c>
+      <c r="D286" s="4" t="n">
+        <v>0.7472222222222222</v>
+      </c>
+      <c r="E286" s="4" t="n">
+        <v>0.2965277777777778</v>
+      </c>
+      <c r="F286" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260901_070423.jpg</t>
+        </is>
+      </c>
+      <c r="G286" s="2" t="inlineStr"/>
+    </row>
+    <row r="287">
+      <c r="A287" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B287" s="2" t="inlineStr">
+        <is>
+          <t>Employee 37</t>
+        </is>
+      </c>
+      <c r="C287" s="3" t="n">
+        <v>46261</v>
+      </c>
+      <c r="D287" s="4" t="n">
+        <v>0.6763888888888889</v>
+      </c>
+      <c r="E287" s="4" t="n">
+        <v>0.24375</v>
+      </c>
+      <c r="F287" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260901_070423.jpg</t>
+        </is>
+      </c>
+      <c r="G287" s="2" t="inlineStr"/>
+    </row>
+    <row r="288">
+      <c r="A288" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B288" s="2" t="inlineStr">
+        <is>
+          <t>Employee 41</t>
+        </is>
+      </c>
+      <c r="C288" s="3" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D288" s="4" t="n">
+        <v>0.7097222222222223</v>
+      </c>
+      <c r="E288" s="2" t="n"/>
+      <c r="F288" s="2" t="inlineStr">
+        <is>
+          <t>IMG_20260901_070506.jpg</t>
+        </is>
+      </c>
+      <c r="G288" s="2" t="inlineStr">
+        <is>
+          <t>single punch only</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/timesheet.xlsx
+++ b/output/timesheet.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E288"/>
+  <dimension ref="A1:E308"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1054,27 +1054,6 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="n">
-        <v>46265</v>
-      </c>
-      <c r="C29" s="4" t="n">
-        <v>0.2527777777777778</v>
-      </c>
-      <c r="D29" s="4" t="n">
-        <v>0.7354166666666667</v>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>corrected from a clearer re-scan photo later in the album</t>
-        </is>
-      </c>
-    </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
@@ -1082,17 +1061,17 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>0.2659722222222222</v>
+        <v>0.2527777777777778</v>
       </c>
       <c r="D30" s="4" t="n">
         <v>0.7354166666666667</v>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>corrected from a clearer re-scan photo later in the album</t>
         </is>
       </c>
     </row>
@@ -1103,13 +1082,13 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>0.2541666666666667</v>
+        <v>0.2659722222222222</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>0.7479166666666667</v>
+        <v>0.7354166666666667</v>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
@@ -1124,13 +1103,13 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0.2805555555555556</v>
+        <v>0.2541666666666667</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>0.7701388888888889</v>
+        <v>0.7479166666666667</v>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
@@ -1145,17 +1124,17 @@
         </is>
       </c>
       <c r="B33" s="3" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.2555555555555555</v>
+        <v>0.2805555555555556</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.8506944444444444</v>
+        <v>0.7701388888888889</v>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>extra punches: 17:07 17:02</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -1166,17 +1145,17 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.275</v>
+        <v>0.2555555555555555</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>0.8791666666666667</v>
+        <v>0.8506944444444444</v>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>extra punch: 17:56</t>
+          <t>extra punches: 17:07 17:02</t>
         </is>
       </c>
     </row>
@@ -1187,17 +1166,17 @@
         </is>
       </c>
       <c r="B35" s="3" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>0.2611111111111111</v>
+        <v>0.275</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>0.7298611111111111</v>
+        <v>0.8791666666666667</v>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>extra punch: 17:56</t>
         </is>
       </c>
     </row>
@@ -1208,13 +1187,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C36" s="4" t="n">
-        <v>0.2631944444444445</v>
+        <v>0.2611111111111111</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>0.7270833333333333</v>
+        <v>0.7298611111111111</v>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
@@ -1229,13 +1208,13 @@
         </is>
       </c>
       <c r="B37" s="3" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="C37" s="4" t="n">
-        <v>0.24375</v>
+        <v>0.2631944444444445</v>
       </c>
       <c r="D37" s="4" t="n">
-        <v>0.7263888888888889</v>
+        <v>0.7270833333333333</v>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
@@ -1250,13 +1229,13 @@
         </is>
       </c>
       <c r="B38" s="3" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="C38" s="4" t="n">
-        <v>0.2611111111111111</v>
+        <v>0.24375</v>
       </c>
       <c r="D38" s="4" t="n">
-        <v>0.7513888888888889</v>
+        <v>0.7263888888888889</v>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
@@ -1271,13 +1250,13 @@
         </is>
       </c>
       <c r="B39" s="3" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="C39" s="4" t="n">
-        <v>0.275</v>
+        <v>0.2611111111111111</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>0.8354166666666667</v>
+        <v>0.7513888888888889</v>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
@@ -1292,13 +1271,13 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C40" s="4" t="n">
-        <v>0.2625</v>
+        <v>0.275</v>
       </c>
       <c r="D40" s="4" t="n">
-        <v>0.7979166666666667</v>
+        <v>0.8354166666666667</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
@@ -1313,13 +1292,13 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C41" s="4" t="n">
-        <v>0.2777777777777778</v>
+        <v>0.2625</v>
       </c>
       <c r="D41" s="4" t="n">
-        <v>0.7451388888888889</v>
+        <v>0.7979166666666667</v>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
@@ -1334,13 +1313,13 @@
         </is>
       </c>
       <c r="B42" s="3" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="C42" s="4" t="n">
-        <v>0.25625</v>
+        <v>0.2777777777777778</v>
       </c>
       <c r="D42" s="4" t="n">
-        <v>0.7416666666666667</v>
+        <v>0.7451388888888889</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
@@ -1355,13 +1334,13 @@
         </is>
       </c>
       <c r="B43" s="3" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="C43" s="4" t="n">
-        <v>0.2333333333333333</v>
+        <v>0.25625</v>
       </c>
       <c r="D43" s="4" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.7416666666666667</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
@@ -1376,13 +1355,13 @@
         </is>
       </c>
       <c r="B44" s="3" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="C44" s="4" t="n">
-        <v>0.2708333333333333</v>
+        <v>0.2333333333333333</v>
       </c>
       <c r="D44" s="4" t="n">
-        <v>0.7229166666666667</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
@@ -1397,13 +1376,13 @@
         </is>
       </c>
       <c r="B45" s="3" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="C45" s="4" t="n">
-        <v>0.1513888888888889</v>
+        <v>0.2708333333333333</v>
       </c>
       <c r="D45" s="4" t="n">
-        <v>0.7277777777777777</v>
+        <v>0.7229166666666667</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
@@ -1418,13 +1397,13 @@
         </is>
       </c>
       <c r="B46" s="3" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="C46" s="4" t="n">
-        <v>0.15</v>
+        <v>0.1513888888888889</v>
       </c>
       <c r="D46" s="4" t="n">
-        <v>0.7076388888888889</v>
+        <v>0.7277777777777777</v>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
@@ -1439,13 +1418,13 @@
         </is>
       </c>
       <c r="B47" s="3" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="C47" s="4" t="n">
-        <v>0.1423611111111111</v>
+        <v>0.15</v>
       </c>
       <c r="D47" s="4" t="n">
-        <v>0.75</v>
+        <v>0.7076388888888889</v>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
@@ -1460,13 +1439,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="C48" s="4" t="n">
-        <v>0.1430555555555555</v>
+        <v>0.1423611111111111</v>
       </c>
       <c r="D48" s="4" t="n">
-        <v>0.7409722222222223</v>
+        <v>0.75</v>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
@@ -1481,13 +1460,13 @@
         </is>
       </c>
       <c r="B49" s="3" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="C49" s="4" t="n">
-        <v>0.14375</v>
+        <v>0.1430555555555555</v>
       </c>
       <c r="D49" s="4" t="n">
-        <v>0.7444444444444445</v>
+        <v>0.7409722222222223</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -1502,13 +1481,13 @@
         </is>
       </c>
       <c r="B50" s="3" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="C50" s="4" t="n">
-        <v>0.1354166666666667</v>
+        <v>0.14375</v>
       </c>
       <c r="D50" s="4" t="n">
-        <v>0.7638888888888888</v>
+        <v>0.7444444444444445</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -1523,13 +1502,13 @@
         </is>
       </c>
       <c r="B51" s="3" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="C51" s="4" t="n">
-        <v>0.1444444444444444</v>
+        <v>0.1354166666666667</v>
       </c>
       <c r="D51" s="4" t="n">
-        <v>0.8381944444444445</v>
+        <v>0.7638888888888888</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -1544,17 +1523,17 @@
         </is>
       </c>
       <c r="B52" s="3" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="C52" s="4" t="n">
-        <v>0.1388888888888889</v>
+        <v>0.1444444444444444</v>
       </c>
       <c r="D52" s="4" t="n">
-        <v>0.8090277777777778</v>
+        <v>0.8381944444444445</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>extra punch: 03:24</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -1565,17 +1544,17 @@
         </is>
       </c>
       <c r="B53" s="3" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="C53" s="4" t="n">
-        <v>0.1451388888888889</v>
+        <v>0.1388888888888889</v>
       </c>
       <c r="D53" s="4" t="n">
-        <v>0.7298611111111111</v>
+        <v>0.8090277777777778</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>extra punch: 03:24</t>
         </is>
       </c>
     </row>
@@ -1586,13 +1565,13 @@
         </is>
       </c>
       <c r="B54" s="3" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C54" s="4" t="n">
-        <v>0.1444444444444444</v>
+        <v>0.1451388888888889</v>
       </c>
       <c r="D54" s="4" t="n">
-        <v>0.7659722222222223</v>
+        <v>0.7298611111111111</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -1607,13 +1586,13 @@
         </is>
       </c>
       <c r="B55" s="3" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C55" s="4" t="n">
         <v>0.1444444444444444</v>
       </c>
       <c r="D55" s="4" t="n">
-        <v>0.6881944444444444</v>
+        <v>0.7659722222222223</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -1628,13 +1607,13 @@
         </is>
       </c>
       <c r="B56" s="3" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C56" s="4" t="n">
-        <v>0.1451388888888889</v>
+        <v>0.1444444444444444</v>
       </c>
       <c r="D56" s="4" t="n">
-        <v>0.7708333333333334</v>
+        <v>0.6881944444444444</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
@@ -1649,13 +1628,13 @@
         </is>
       </c>
       <c r="B57" s="3" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C57" s="4" t="n">
-        <v>0.1458333333333333</v>
+        <v>0.1451388888888889</v>
       </c>
       <c r="D57" s="4" t="n">
-        <v>0.7472222222222222</v>
+        <v>0.7708333333333334</v>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
@@ -1670,13 +1649,13 @@
         </is>
       </c>
       <c r="B58" s="3" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="C58" s="4" t="n">
-        <v>0.14375</v>
+        <v>0.1458333333333333</v>
       </c>
       <c r="D58" s="4" t="n">
-        <v>0.7395833333333334</v>
+        <v>0.7472222222222222</v>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
@@ -1691,59 +1670,38 @@
         </is>
       </c>
       <c r="B59" s="3" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="C59" s="4" t="n">
         <v>0.14375</v>
       </c>
       <c r="D59" s="4" t="n">
-        <v>0.7576388888888889</v>
+        <v>0.7395833333333334</v>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>last day of month; final record</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B60" s="3" t="n">
-        <v>46256</v>
+        <v>46235</v>
       </c>
       <c r="C60" s="4" t="n">
-        <v>0.2805555555555556</v>
+        <v>0.14375</v>
       </c>
       <c r="D60" s="4" t="n">
-        <v>0.7513888888888889</v>
+        <v>0.7576388888888889</v>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="B61" s="3" t="n">
-        <v>46254</v>
-      </c>
-      <c r="C61" s="4" t="n">
-        <v>0.275</v>
-      </c>
-      <c r="D61" s="4" t="n">
-        <v>0.7256944444444444</v>
-      </c>
-      <c r="E61" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>last day of month; final record</t>
         </is>
       </c>
     </row>
@@ -1754,13 +1712,13 @@
         </is>
       </c>
       <c r="B62" s="3" t="n">
-        <v>46253</v>
+        <v>46256</v>
       </c>
       <c r="C62" s="4" t="n">
-        <v>0.2763888888888889</v>
+        <v>0.2805555555555556</v>
       </c>
       <c r="D62" s="4" t="n">
-        <v>0.7298611111111111</v>
+        <v>0.7513888888888889</v>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
@@ -1775,13 +1733,13 @@
         </is>
       </c>
       <c r="B63" s="3" t="n">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="C63" s="4" t="n">
-        <v>0.2826388888888889</v>
+        <v>0.275</v>
       </c>
       <c r="D63" s="4" t="n">
-        <v>0.7451388888888889</v>
+        <v>0.7256944444444444</v>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
@@ -1796,13 +1754,13 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>46251</v>
+        <v>46253</v>
       </c>
       <c r="C64" s="4" t="n">
-        <v>0.2743055555555556</v>
+        <v>0.2763888888888889</v>
       </c>
       <c r="D64" s="4" t="n">
-        <v>0.7333333333333333</v>
+        <v>0.7298611111111111</v>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
@@ -1817,13 +1775,13 @@
         </is>
       </c>
       <c r="B65" s="3" t="n">
-        <v>46250</v>
+        <v>46252</v>
       </c>
       <c r="C65" s="4" t="n">
-        <v>0.2902777777777778</v>
+        <v>0.2826388888888889</v>
       </c>
       <c r="D65" s="4" t="n">
-        <v>0.7236111111111111</v>
+        <v>0.7451388888888889</v>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
@@ -1838,13 +1796,13 @@
         </is>
       </c>
       <c r="B66" s="3" t="n">
-        <v>46249</v>
+        <v>46251</v>
       </c>
       <c r="C66" s="4" t="n">
-        <v>0.2395833333333333</v>
+        <v>0.2743055555555556</v>
       </c>
       <c r="D66" s="4" t="n">
-        <v>0.7388888888888889</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
@@ -1859,13 +1817,13 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>46247</v>
+        <v>46250</v>
       </c>
       <c r="C67" s="4" t="n">
-        <v>0.2465277777777778</v>
+        <v>0.2902777777777778</v>
       </c>
       <c r="D67" s="4" t="n">
-        <v>0.7270833333333333</v>
+        <v>0.7236111111111111</v>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
@@ -1880,13 +1838,13 @@
         </is>
       </c>
       <c r="B68" s="3" t="n">
-        <v>46246</v>
+        <v>46249</v>
       </c>
       <c r="C68" s="4" t="n">
-        <v>0.2340277777777778</v>
+        <v>0.2395833333333333</v>
       </c>
       <c r="D68" s="4" t="n">
-        <v>0.7493055555555556</v>
+        <v>0.7388888888888889</v>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
@@ -1901,13 +1859,13 @@
         </is>
       </c>
       <c r="B69" s="3" t="n">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="C69" s="4" t="n">
-        <v>0.2381944444444444</v>
+        <v>0.2465277777777778</v>
       </c>
       <c r="D69" s="4" t="n">
-        <v>0.7402777777777778</v>
+        <v>0.7270833333333333</v>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
@@ -1922,19 +1880,17 @@
         </is>
       </c>
       <c r="B70" s="3" t="n">
-        <v>46244</v>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>46246</v>
+      </c>
+      <c r="C70" s="4" t="n">
+        <v>0.2340277777777778</v>
       </c>
       <c r="D70" s="4" t="n">
-        <v>0.75625</v>
+        <v>0.7493055555555556</v>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -1945,13 +1901,13 @@
         </is>
       </c>
       <c r="B71" s="3" t="n">
-        <v>46243</v>
+        <v>46245</v>
       </c>
       <c r="C71" s="4" t="n">
         <v>0.2381944444444444</v>
       </c>
       <c r="D71" s="4" t="n">
-        <v>0.75625</v>
+        <v>0.7402777777777778</v>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
@@ -1966,17 +1922,19 @@
         </is>
       </c>
       <c r="B72" s="3" t="n">
-        <v>46242</v>
-      </c>
-      <c r="C72" s="4" t="n">
-        <v>0.2597222222222222</v>
+        <v>46244</v>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D72" s="4" t="n">
-        <v>0.7326388888888888</v>
+        <v>0.75625</v>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
@@ -1987,13 +1945,13 @@
         </is>
       </c>
       <c r="B73" s="3" t="n">
-        <v>46240</v>
+        <v>46243</v>
       </c>
       <c r="C73" s="4" t="n">
-        <v>0.2701388888888889</v>
+        <v>0.2381944444444444</v>
       </c>
       <c r="D73" s="4" t="n">
-        <v>0.7423611111111111</v>
+        <v>0.75625</v>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
@@ -2008,13 +1966,13 @@
         </is>
       </c>
       <c r="B74" s="3" t="n">
-        <v>46239</v>
+        <v>46242</v>
       </c>
       <c r="C74" s="4" t="n">
-        <v>0.25625</v>
+        <v>0.2597222222222222</v>
       </c>
       <c r="D74" s="4" t="n">
-        <v>0.7763888888888889</v>
+        <v>0.7326388888888888</v>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
@@ -2029,13 +1987,13 @@
         </is>
       </c>
       <c r="B75" s="3" t="n">
-        <v>46238</v>
+        <v>46240</v>
       </c>
       <c r="C75" s="4" t="n">
-        <v>0.2527777777777778</v>
+        <v>0.2701388888888889</v>
       </c>
       <c r="D75" s="4" t="n">
-        <v>0.75</v>
+        <v>0.7423611111111111</v>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
@@ -2050,13 +2008,13 @@
         </is>
       </c>
       <c r="B76" s="3" t="n">
-        <v>46237</v>
+        <v>46239</v>
       </c>
       <c r="C76" s="4" t="n">
-        <v>0.2604166666666667</v>
+        <v>0.25625</v>
       </c>
       <c r="D76" s="4" t="n">
-        <v>0.7479166666666667</v>
+        <v>0.7763888888888889</v>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
@@ -2071,13 +2029,13 @@
         </is>
       </c>
       <c r="B77" s="3" t="n">
-        <v>46236</v>
+        <v>46238</v>
       </c>
       <c r="C77" s="4" t="n">
-        <v>0.2645833333333333</v>
+        <v>0.2527777777777778</v>
       </c>
       <c r="D77" s="4" t="n">
-        <v>0.7493055555555556</v>
+        <v>0.75</v>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
@@ -2092,80 +2050,59 @@
         </is>
       </c>
       <c r="B78" s="3" t="n">
-        <v>46235</v>
+        <v>46237</v>
       </c>
       <c r="C78" s="4" t="n">
-        <v>0.2625</v>
+        <v>0.2604166666666667</v>
       </c>
       <c r="D78" s="4" t="n">
-        <v>0.7444444444444445</v>
+        <v>0.7479166666666667</v>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>last day of month; final record</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B79" s="3" t="n">
-        <v>46265</v>
+        <v>46236</v>
       </c>
       <c r="C79" s="4" t="n">
-        <v>0.2527777777777778</v>
+        <v>0.2645833333333333</v>
       </c>
       <c r="D79" s="4" t="n">
-        <v>0.7604166666666666</v>
+        <v>0.7493055555555556</v>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>corrected from a clearer re-scan photo later in the album</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B80" s="3" t="n">
-        <v>46264</v>
+        <v>46235</v>
       </c>
       <c r="C80" s="4" t="n">
-        <v>0.2965277777777778</v>
+        <v>0.2625</v>
       </c>
       <c r="D80" s="4" t="n">
-        <v>0.75625</v>
+        <v>0.7444444444444445</v>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="B81" s="3" t="n">
-        <v>46263</v>
-      </c>
-      <c r="C81" s="4" t="n">
-        <v>0.2965277777777778</v>
-      </c>
-      <c r="D81" s="4" t="n">
-        <v>0.7326388888888888</v>
-      </c>
-      <c r="E81" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>last day of month; final record</t>
         </is>
       </c>
     </row>
@@ -2176,17 +2113,17 @@
         </is>
       </c>
       <c r="B82" s="3" t="n">
-        <v>46261</v>
+        <v>46265</v>
       </c>
       <c r="C82" s="4" t="n">
-        <v>0.2666666666666667</v>
+        <v>0.2527777777777778</v>
       </c>
       <c r="D82" s="4" t="n">
-        <v>0.75</v>
+        <v>0.7604166666666666</v>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>corrected from a clearer re-scan photo later in the album</t>
         </is>
       </c>
     </row>
@@ -2197,17 +2134,17 @@
         </is>
       </c>
       <c r="B83" s="3" t="n">
-        <v>46260</v>
+        <v>46264</v>
       </c>
       <c r="C83" s="4" t="n">
-        <v>0.3243055555555556</v>
+        <v>0.2965277777777778</v>
       </c>
       <c r="D83" s="4" t="n">
-        <v>0.7534722222222222</v>
+        <v>0.75625</v>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>extra punch: 17:56</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2218,13 +2155,13 @@
         </is>
       </c>
       <c r="B84" s="3" t="n">
-        <v>46259</v>
+        <v>46263</v>
       </c>
       <c r="C84" s="4" t="n">
-        <v>0.2763888888888889</v>
+        <v>0.2965277777777778</v>
       </c>
       <c r="D84" s="4" t="n">
-        <v>0.7548611111111111</v>
+        <v>0.7326388888888888</v>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
@@ -2239,13 +2176,13 @@
         </is>
       </c>
       <c r="B85" s="3" t="n">
-        <v>46258</v>
+        <v>46261</v>
       </c>
       <c r="C85" s="4" t="n">
-        <v>0.3263888888888889</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="D85" s="4" t="n">
-        <v>0.7388888888888889</v>
+        <v>0.75</v>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
@@ -2260,17 +2197,17 @@
         </is>
       </c>
       <c r="B86" s="3" t="n">
-        <v>46257</v>
+        <v>46260</v>
       </c>
       <c r="C86" s="4" t="n">
-        <v>0.25</v>
+        <v>0.3243055555555556</v>
       </c>
       <c r="D86" s="4" t="n">
-        <v>0.7493055555555556</v>
+        <v>0.7534722222222222</v>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>extra punch: 17:56</t>
         </is>
       </c>
     </row>
@@ -2281,13 +2218,13 @@
         </is>
       </c>
       <c r="B87" s="3" t="n">
-        <v>46256</v>
+        <v>46259</v>
       </c>
       <c r="C87" s="4" t="n">
-        <v>0.2069444444444444</v>
+        <v>0.2763888888888889</v>
       </c>
       <c r="D87" s="4" t="n">
-        <v>0.7243055555555555</v>
+        <v>0.7548611111111111</v>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
@@ -2302,19 +2239,17 @@
         </is>
       </c>
       <c r="B88" s="3" t="n">
-        <v>46254</v>
+        <v>46258</v>
       </c>
       <c r="C88" s="4" t="n">
-        <v>0.3576388888888889</v>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.3263888888888889</v>
+      </c>
+      <c r="D88" s="4" t="n">
+        <v>0.7388888888888889</v>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2325,13 +2260,13 @@
         </is>
       </c>
       <c r="B89" s="3" t="n">
-        <v>46253</v>
+        <v>46257</v>
       </c>
       <c r="C89" s="4" t="n">
-        <v>0.475</v>
+        <v>0.25</v>
       </c>
       <c r="D89" s="4" t="n">
-        <v>0.7173611111111111</v>
+        <v>0.7493055555555556</v>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
@@ -2346,13 +2281,13 @@
         </is>
       </c>
       <c r="B90" s="3" t="n">
-        <v>46252</v>
+        <v>46256</v>
       </c>
       <c r="C90" s="4" t="n">
-        <v>0.3083333333333333</v>
+        <v>0.2069444444444444</v>
       </c>
       <c r="D90" s="4" t="n">
-        <v>0.7583333333333333</v>
+        <v>0.7243055555555555</v>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
@@ -2367,17 +2302,19 @@
         </is>
       </c>
       <c r="B91" s="3" t="n">
-        <v>46251</v>
+        <v>46254</v>
       </c>
       <c r="C91" s="4" t="n">
-        <v>0.3979166666666666</v>
-      </c>
-      <c r="D91" s="4" t="n">
-        <v>0.7680555555555556</v>
+        <v>0.3576388888888889</v>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
@@ -2388,13 +2325,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>46250</v>
+        <v>46253</v>
       </c>
       <c r="C92" s="4" t="n">
-        <v>0.325</v>
+        <v>0.475</v>
       </c>
       <c r="D92" s="4" t="n">
-        <v>0.7722222222222223</v>
+        <v>0.7173611111111111</v>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
@@ -2409,13 +2346,13 @@
         </is>
       </c>
       <c r="B93" s="3" t="n">
-        <v>46249</v>
+        <v>46252</v>
       </c>
       <c r="C93" s="4" t="n">
-        <v>0.2354166666666667</v>
+        <v>0.3083333333333333</v>
       </c>
       <c r="D93" s="4" t="n">
-        <v>0.75</v>
+        <v>0.7583333333333333</v>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
@@ -2430,19 +2367,17 @@
         </is>
       </c>
       <c r="B94" s="3" t="n">
-        <v>46247</v>
+        <v>46251</v>
       </c>
       <c r="C94" s="4" t="n">
-        <v>0.3347222222222222</v>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.3979166666666666</v>
+      </c>
+      <c r="D94" s="4" t="n">
+        <v>0.7680555555555556</v>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2453,19 +2388,17 @@
         </is>
       </c>
       <c r="B95" s="3" t="n">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="C95" s="4" t="n">
-        <v>0.2986111111111111</v>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.325</v>
+      </c>
+      <c r="D95" s="4" t="n">
+        <v>0.7722222222222223</v>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2476,19 +2409,17 @@
         </is>
       </c>
       <c r="B96" s="3" t="n">
-        <v>46245</v>
+        <v>46249</v>
       </c>
       <c r="C96" s="4" t="n">
-        <v>0.3118055555555556</v>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.2354166666666667</v>
+      </c>
+      <c r="D96" s="4" t="n">
+        <v>0.75</v>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2499,17 +2430,19 @@
         </is>
       </c>
       <c r="B97" s="3" t="n">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="C97" s="4" t="n">
-        <v>0.2263888888888889</v>
-      </c>
-      <c r="D97" s="4" t="n">
-        <v>0.75</v>
+        <v>0.3347222222222222</v>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
@@ -2520,17 +2453,19 @@
         </is>
       </c>
       <c r="B98" s="3" t="n">
-        <v>46243</v>
+        <v>46246</v>
       </c>
       <c r="C98" s="4" t="n">
-        <v>0.2798611111111111</v>
-      </c>
-      <c r="D98" s="4" t="n">
-        <v>0.75</v>
+        <v>0.2986111111111111</v>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
@@ -2541,17 +2476,19 @@
         </is>
       </c>
       <c r="B99" s="3" t="n">
-        <v>46242</v>
+        <v>46245</v>
       </c>
       <c r="C99" s="4" t="n">
-        <v>0.3055555555555556</v>
-      </c>
-      <c r="D99" s="4" t="n">
-        <v>0.7604166666666666</v>
+        <v>0.3118055555555556</v>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
@@ -2562,13 +2499,13 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>46240</v>
+        <v>46244</v>
       </c>
       <c r="C100" s="4" t="n">
-        <v>0.30625</v>
+        <v>0.2263888888888889</v>
       </c>
       <c r="D100" s="4" t="n">
-        <v>0.7590277777777777</v>
+        <v>0.75</v>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
@@ -2583,13 +2520,13 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>46239</v>
+        <v>46243</v>
       </c>
       <c r="C101" s="4" t="n">
-        <v>0.3222222222222222</v>
+        <v>0.2798611111111111</v>
       </c>
       <c r="D101" s="4" t="n">
-        <v>0.7715277777777778</v>
+        <v>0.75</v>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
@@ -2604,13 +2541,13 @@
         </is>
       </c>
       <c r="B102" s="3" t="n">
-        <v>46238</v>
+        <v>46242</v>
       </c>
       <c r="C102" s="4" t="n">
-        <v>0.2763888888888889</v>
+        <v>0.3055555555555556</v>
       </c>
       <c r="D102" s="4" t="n">
-        <v>0.7166666666666667</v>
+        <v>0.7604166666666666</v>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
@@ -2625,13 +2562,13 @@
         </is>
       </c>
       <c r="B103" s="3" t="n">
-        <v>46237</v>
+        <v>46240</v>
       </c>
       <c r="C103" s="4" t="n">
-        <v>0.3034722222222222</v>
+        <v>0.30625</v>
       </c>
       <c r="D103" s="4" t="n">
-        <v>0.7159722222222222</v>
+        <v>0.7590277777777777</v>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
@@ -2646,13 +2583,13 @@
         </is>
       </c>
       <c r="B104" s="3" t="n">
-        <v>46236</v>
+        <v>46239</v>
       </c>
       <c r="C104" s="4" t="n">
-        <v>0.2958333333333333</v>
+        <v>0.3222222222222222</v>
       </c>
       <c r="D104" s="4" t="n">
-        <v>0.7430555555555556</v>
+        <v>0.7715277777777778</v>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
@@ -2667,55 +2604,55 @@
         </is>
       </c>
       <c r="B105" s="3" t="n">
-        <v>46235</v>
+        <v>46238</v>
       </c>
       <c r="C105" s="4" t="n">
-        <v>0.2381944444444444</v>
+        <v>0.2763888888888889</v>
       </c>
       <c r="D105" s="4" t="n">
-        <v>0.7458333333333333</v>
+        <v>0.7166666666666667</v>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>last day of month; final record</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>46265</v>
+        <v>46237</v>
       </c>
       <c r="C106" s="4" t="n">
-        <v>0.2777777777777778</v>
+        <v>0.3034722222222222</v>
       </c>
       <c r="D106" s="4" t="n">
-        <v>0.7513888888888889</v>
+        <v>0.7159722222222222</v>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>corrected from a clearer re-scan photo later in the album</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B107" s="3" t="n">
-        <v>46264</v>
+        <v>46236</v>
       </c>
       <c r="C107" s="4" t="n">
-        <v>0.2590277777777778</v>
+        <v>0.2958333333333333</v>
       </c>
       <c r="D107" s="4" t="n">
-        <v>0.7541666666666667</v>
+        <v>0.7430555555555556</v>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
@@ -2726,44 +2663,21 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B108" s="3" t="n">
-        <v>46263</v>
+        <v>46235</v>
       </c>
       <c r="C108" s="4" t="n">
-        <v>0.2569444444444444</v>
+        <v>0.2381944444444444</v>
       </c>
       <c r="D108" s="4" t="n">
         <v>0.7458333333333333</v>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>extra punch: 17:53</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="B109" s="3" t="n">
-        <v>46262</v>
-      </c>
-      <c r="C109" s="4" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E109" s="2" t="inlineStr">
-        <is>
-          <t>single punch only</t>
+          <t>last day of month; final record</t>
         </is>
       </c>
     </row>
@@ -2774,17 +2688,17 @@
         </is>
       </c>
       <c r="B110" s="3" t="n">
-        <v>46261</v>
+        <v>46265</v>
       </c>
       <c r="C110" s="4" t="n">
-        <v>0.2493055555555556</v>
+        <v>0.2777777777777778</v>
       </c>
       <c r="D110" s="4" t="n">
-        <v>0.7944444444444444</v>
+        <v>0.7513888888888889</v>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>corrected from a clearer re-scan photo later in the album</t>
         </is>
       </c>
     </row>
@@ -2795,13 +2709,13 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>46260</v>
+        <v>46264</v>
       </c>
       <c r="C111" s="4" t="n">
-        <v>0.2479166666666667</v>
+        <v>0.2590277777777778</v>
       </c>
       <c r="D111" s="4" t="n">
-        <v>0.7555555555555555</v>
+        <v>0.7541666666666667</v>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
@@ -2816,17 +2730,17 @@
         </is>
       </c>
       <c r="B112" s="3" t="n">
-        <v>46259</v>
+        <v>46263</v>
       </c>
       <c r="C112" s="4" t="n">
-        <v>0.2375</v>
+        <v>0.2569444444444444</v>
       </c>
       <c r="D112" s="4" t="n">
-        <v>0.7597222222222222</v>
+        <v>0.7458333333333333</v>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>extra punch: 17:53</t>
         </is>
       </c>
     </row>
@@ -2837,17 +2751,19 @@
         </is>
       </c>
       <c r="B113" s="3" t="n">
-        <v>46258</v>
+        <v>46262</v>
       </c>
       <c r="C113" s="4" t="n">
-        <v>0.2375</v>
-      </c>
-      <c r="D113" s="4" t="n">
-        <v>0.7506944444444444</v>
+        <v>0.25</v>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
@@ -2858,13 +2774,13 @@
         </is>
       </c>
       <c r="B114" s="3" t="n">
-        <v>46257</v>
+        <v>46261</v>
       </c>
       <c r="C114" s="4" t="n">
-        <v>0.2479166666666667</v>
+        <v>0.2493055555555556</v>
       </c>
       <c r="D114" s="4" t="n">
-        <v>0.7618055555555555</v>
+        <v>0.7944444444444444</v>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
@@ -2879,19 +2795,17 @@
         </is>
       </c>
       <c r="B115" s="3" t="n">
-        <v>46256</v>
+        <v>46260</v>
       </c>
       <c r="C115" s="4" t="n">
-        <v>0.2875</v>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.2479166666666667</v>
+      </c>
+      <c r="D115" s="4" t="n">
+        <v>0.7555555555555555</v>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2902,13 +2816,13 @@
         </is>
       </c>
       <c r="B116" s="3" t="n">
-        <v>46254</v>
+        <v>46259</v>
       </c>
       <c r="C116" s="4" t="n">
-        <v>0.2472222222222222</v>
+        <v>0.2375</v>
       </c>
       <c r="D116" s="4" t="n">
-        <v>0.7243055555555555</v>
+        <v>0.7597222222222222</v>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
@@ -2923,13 +2837,13 @@
         </is>
       </c>
       <c r="B117" s="3" t="n">
-        <v>46253</v>
+        <v>46258</v>
       </c>
       <c r="C117" s="4" t="n">
-        <v>0.2395833333333333</v>
+        <v>0.2375</v>
       </c>
       <c r="D117" s="4" t="n">
-        <v>0.7416666666666667</v>
+        <v>0.7506944444444444</v>
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
@@ -2944,13 +2858,13 @@
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>46252</v>
+        <v>46257</v>
       </c>
       <c r="C118" s="4" t="n">
-        <v>0.2916666666666667</v>
+        <v>0.2479166666666667</v>
       </c>
       <c r="D118" s="4" t="n">
-        <v>0.7416666666666667</v>
+        <v>0.7618055555555555</v>
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
@@ -2965,17 +2879,19 @@
         </is>
       </c>
       <c r="B119" s="3" t="n">
-        <v>46251</v>
+        <v>46256</v>
       </c>
       <c r="C119" s="4" t="n">
-        <v>0.3416666666666667</v>
-      </c>
-      <c r="D119" s="4" t="n">
-        <v>0.7326388888888888</v>
+        <v>0.2875</v>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
@@ -2986,13 +2902,13 @@
         </is>
       </c>
       <c r="B120" s="3" t="n">
-        <v>46250</v>
+        <v>46254</v>
       </c>
       <c r="C120" s="4" t="n">
-        <v>0.2409722222222222</v>
+        <v>0.2472222222222222</v>
       </c>
       <c r="D120" s="4" t="n">
-        <v>0.7381944444444445</v>
+        <v>0.7243055555555555</v>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
@@ -3007,13 +2923,13 @@
         </is>
       </c>
       <c r="B121" s="3" t="n">
-        <v>46249</v>
+        <v>46253</v>
       </c>
       <c r="C121" s="4" t="n">
-        <v>0.2354166666666667</v>
+        <v>0.2395833333333333</v>
       </c>
       <c r="D121" s="4" t="n">
-        <v>0.7611111111111111</v>
+        <v>0.7416666666666667</v>
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
@@ -3028,19 +2944,17 @@
         </is>
       </c>
       <c r="B122" s="3" t="n">
-        <v>46247</v>
+        <v>46252</v>
       </c>
       <c r="C122" s="4" t="n">
-        <v>0.4402777777777778</v>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.2916666666666667</v>
+      </c>
+      <c r="D122" s="4" t="n">
+        <v>0.7416666666666667</v>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3051,13 +2965,13 @@
         </is>
       </c>
       <c r="B123" s="3" t="n">
-        <v>46246</v>
+        <v>46251</v>
       </c>
       <c r="C123" s="4" t="n">
-        <v>0.2284722222222222</v>
+        <v>0.3416666666666667</v>
       </c>
       <c r="D123" s="4" t="n">
-        <v>0.7423611111111111</v>
+        <v>0.7326388888888888</v>
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
@@ -3072,13 +2986,13 @@
         </is>
       </c>
       <c r="B124" s="3" t="n">
-        <v>46245</v>
+        <v>46250</v>
       </c>
       <c r="C124" s="4" t="n">
-        <v>0.2375</v>
+        <v>0.2409722222222222</v>
       </c>
       <c r="D124" s="4" t="n">
-        <v>0.7375</v>
+        <v>0.7381944444444445</v>
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
@@ -3093,10 +3007,10 @@
         </is>
       </c>
       <c r="B125" s="3" t="n">
-        <v>46244</v>
+        <v>46249</v>
       </c>
       <c r="C125" s="4" t="n">
-        <v>0.2256944444444444</v>
+        <v>0.2354166666666667</v>
       </c>
       <c r="D125" s="4" t="n">
         <v>0.7611111111111111</v>
@@ -3114,17 +3028,19 @@
         </is>
       </c>
       <c r="B126" s="3" t="n">
-        <v>46243</v>
+        <v>46247</v>
       </c>
       <c r="C126" s="4" t="n">
-        <v>0.2395833333333333</v>
-      </c>
-      <c r="D126" s="4" t="n">
-        <v>0.725</v>
+        <v>0.4402777777777778</v>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
@@ -3135,13 +3051,13 @@
         </is>
       </c>
       <c r="B127" s="3" t="n">
-        <v>46242</v>
+        <v>46246</v>
       </c>
       <c r="C127" s="4" t="n">
-        <v>0.2201388888888889</v>
+        <v>0.2284722222222222</v>
       </c>
       <c r="D127" s="4" t="n">
-        <v>0.7618055555555555</v>
+        <v>0.7423611111111111</v>
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
@@ -3156,13 +3072,13 @@
         </is>
       </c>
       <c r="B128" s="3" t="n">
-        <v>46240</v>
+        <v>46245</v>
       </c>
       <c r="C128" s="4" t="n">
-        <v>0.2409722222222222</v>
+        <v>0.2375</v>
       </c>
       <c r="D128" s="4" t="n">
-        <v>0.7625</v>
+        <v>0.7375</v>
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
@@ -3177,13 +3093,13 @@
         </is>
       </c>
       <c r="B129" s="3" t="n">
-        <v>46239</v>
+        <v>46244</v>
       </c>
       <c r="C129" s="4" t="n">
-        <v>0.4743055555555555</v>
+        <v>0.2256944444444444</v>
       </c>
       <c r="D129" s="4" t="n">
-        <v>0.7722222222222223</v>
+        <v>0.7611111111111111</v>
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
@@ -3198,13 +3114,13 @@
         </is>
       </c>
       <c r="B130" s="3" t="n">
-        <v>46238</v>
+        <v>46243</v>
       </c>
       <c r="C130" s="4" t="n">
-        <v>0.4965277777777778</v>
+        <v>0.2395833333333333</v>
       </c>
       <c r="D130" s="4" t="n">
-        <v>0.7506944444444444</v>
+        <v>0.725</v>
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
@@ -3219,13 +3135,13 @@
         </is>
       </c>
       <c r="B131" s="3" t="n">
-        <v>46237</v>
+        <v>46242</v>
       </c>
       <c r="C131" s="4" t="n">
-        <v>0.2618055555555556</v>
+        <v>0.2201388888888889</v>
       </c>
       <c r="D131" s="4" t="n">
-        <v>0.7472222222222222</v>
+        <v>0.7618055555555555</v>
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
@@ -3240,13 +3156,13 @@
         </is>
       </c>
       <c r="B132" s="3" t="n">
-        <v>46236</v>
+        <v>46240</v>
       </c>
       <c r="C132" s="4" t="n">
-        <v>0.2972222222222222</v>
+        <v>0.2409722222222222</v>
       </c>
       <c r="D132" s="4" t="n">
-        <v>0.7430555555555556</v>
+        <v>0.7625</v>
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
@@ -3261,55 +3177,55 @@
         </is>
       </c>
       <c r="B133" s="3" t="n">
-        <v>46235</v>
+        <v>46239</v>
       </c>
       <c r="C133" s="4" t="n">
-        <v>0.2590277777777778</v>
+        <v>0.4743055555555555</v>
       </c>
       <c r="D133" s="4" t="n">
-        <v>0.7319444444444444</v>
+        <v>0.7722222222222223</v>
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>last day of month; final record</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>46265</v>
+        <v>46238</v>
       </c>
       <c r="C134" s="4" t="n">
-        <v>0.2361111111111111</v>
+        <v>0.4965277777777778</v>
       </c>
       <c r="D134" s="4" t="n">
-        <v>0.7520833333333333</v>
+        <v>0.7506944444444444</v>
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>corrected from a clearer re-scan photo later in the album</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>46264</v>
+        <v>46237</v>
       </c>
       <c r="C135" s="4" t="n">
-        <v>0.2423611111111111</v>
+        <v>0.2618055555555556</v>
       </c>
       <c r="D135" s="4" t="n">
-        <v>0.7513888888888889</v>
+        <v>0.7472222222222222</v>
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
@@ -3320,17 +3236,17 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B136" s="3" t="n">
-        <v>46263</v>
+        <v>46236</v>
       </c>
       <c r="C136" s="4" t="n">
-        <v>0.2444444444444444</v>
+        <v>0.2972222222222222</v>
       </c>
       <c r="D136" s="4" t="n">
-        <v>0.7548611111111111</v>
+        <v>0.7430555555555556</v>
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
@@ -3341,42 +3257,21 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B137" s="3" t="n">
-        <v>46261</v>
+        <v>46235</v>
       </c>
       <c r="C137" s="4" t="n">
-        <v>0.2472222222222222</v>
+        <v>0.2590277777777778</v>
       </c>
       <c r="D137" s="4" t="n">
-        <v>0.7513888888888889</v>
+        <v>0.7319444444444444</v>
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="B138" s="3" t="n">
-        <v>46260</v>
-      </c>
-      <c r="C138" s="4" t="n">
-        <v>0.2465277777777778</v>
-      </c>
-      <c r="D138" s="4" t="n">
-        <v>0.7555555555555555</v>
-      </c>
-      <c r="E138" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>last day of month; final record</t>
         </is>
       </c>
     </row>
@@ -3387,17 +3282,17 @@
         </is>
       </c>
       <c r="B139" s="3" t="n">
-        <v>46259</v>
+        <v>46265</v>
       </c>
       <c r="C139" s="4" t="n">
-        <v>0.2368055555555555</v>
+        <v>0.2361111111111111</v>
       </c>
       <c r="D139" s="4" t="n">
-        <v>0.7506944444444444</v>
+        <v>0.7520833333333333</v>
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>corrected from a clearer re-scan photo later in the album</t>
         </is>
       </c>
     </row>
@@ -3408,13 +3303,13 @@
         </is>
       </c>
       <c r="B140" s="3" t="n">
-        <v>46258</v>
+        <v>46264</v>
       </c>
       <c r="C140" s="4" t="n">
-        <v>0.2347222222222222</v>
+        <v>0.2423611111111111</v>
       </c>
       <c r="D140" s="4" t="n">
-        <v>0.7520833333333333</v>
+        <v>0.7513888888888889</v>
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
@@ -3429,13 +3324,13 @@
         </is>
       </c>
       <c r="B141" s="3" t="n">
-        <v>46257</v>
+        <v>46263</v>
       </c>
       <c r="C141" s="4" t="n">
-        <v>0.2458333333333333</v>
+        <v>0.2444444444444444</v>
       </c>
       <c r="D141" s="4" t="n">
-        <v>0.7527777777777778</v>
+        <v>0.7548611111111111</v>
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
@@ -3450,13 +3345,13 @@
         </is>
       </c>
       <c r="B142" s="3" t="n">
-        <v>46256</v>
+        <v>46261</v>
       </c>
       <c r="C142" s="4" t="n">
-        <v>0.2402777777777778</v>
+        <v>0.2472222222222222</v>
       </c>
       <c r="D142" s="4" t="n">
-        <v>0.75</v>
+        <v>0.7513888888888889</v>
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
@@ -3471,13 +3366,13 @@
         </is>
       </c>
       <c r="B143" s="3" t="n">
-        <v>46254</v>
+        <v>46260</v>
       </c>
       <c r="C143" s="4" t="n">
-        <v>0.2402777777777778</v>
+        <v>0.2465277777777778</v>
       </c>
       <c r="D143" s="4" t="n">
-        <v>0.7520833333333333</v>
+        <v>0.7555555555555555</v>
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
@@ -3492,10 +3387,10 @@
         </is>
       </c>
       <c r="B144" s="3" t="n">
-        <v>46253</v>
+        <v>46259</v>
       </c>
       <c r="C144" s="4" t="n">
-        <v>0.2423611111111111</v>
+        <v>0.2368055555555555</v>
       </c>
       <c r="D144" s="4" t="n">
         <v>0.7506944444444444</v>
@@ -3513,13 +3408,13 @@
         </is>
       </c>
       <c r="B145" s="3" t="n">
-        <v>46252</v>
+        <v>46258</v>
       </c>
       <c r="C145" s="4" t="n">
-        <v>0.2451388888888889</v>
+        <v>0.2347222222222222</v>
       </c>
       <c r="D145" s="4" t="n">
-        <v>0.7527777777777778</v>
+        <v>0.7520833333333333</v>
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
@@ -3534,13 +3429,13 @@
         </is>
       </c>
       <c r="B146" s="3" t="n">
-        <v>46251</v>
+        <v>46257</v>
       </c>
       <c r="C146" s="4" t="n">
-        <v>0.2395833333333333</v>
+        <v>0.2458333333333333</v>
       </c>
       <c r="D146" s="4" t="n">
-        <v>0.7541666666666667</v>
+        <v>0.7527777777777778</v>
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
@@ -3555,13 +3450,13 @@
         </is>
       </c>
       <c r="B147" s="3" t="n">
-        <v>46250</v>
+        <v>46256</v>
       </c>
       <c r="C147" s="4" t="n">
-        <v>0.2354166666666667</v>
+        <v>0.2402777777777778</v>
       </c>
       <c r="D147" s="4" t="n">
-        <v>0.7520833333333333</v>
+        <v>0.75</v>
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
@@ -3576,13 +3471,13 @@
         </is>
       </c>
       <c r="B148" s="3" t="n">
-        <v>46249</v>
+        <v>46254</v>
       </c>
       <c r="C148" s="4" t="n">
-        <v>0.2381944444444444</v>
+        <v>0.2402777777777778</v>
       </c>
       <c r="D148" s="4" t="n">
-        <v>0.7513888888888889</v>
+        <v>0.7520833333333333</v>
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
@@ -3597,13 +3492,13 @@
         </is>
       </c>
       <c r="B149" s="3" t="n">
-        <v>46247</v>
+        <v>46253</v>
       </c>
       <c r="C149" s="4" t="n">
-        <v>0.2444444444444444</v>
+        <v>0.2423611111111111</v>
       </c>
       <c r="D149" s="4" t="n">
-        <v>0.7576388888888889</v>
+        <v>0.7506944444444444</v>
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
@@ -3618,21 +3513,17 @@
         </is>
       </c>
       <c r="B150" s="3" t="n">
-        <v>46246</v>
-      </c>
-      <c r="C150" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D150" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>46252</v>
+      </c>
+      <c r="C150" s="4" t="n">
+        <v>0.2451388888888889</v>
+      </c>
+      <c r="D150" s="4" t="n">
+        <v>0.7527777777777778</v>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>PLEASE VERIFY: check-in/out times not captured (gap between source photos)</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3643,13 +3534,13 @@
         </is>
       </c>
       <c r="B151" s="3" t="n">
-        <v>46242</v>
+        <v>46251</v>
       </c>
       <c r="C151" s="4" t="n">
-        <v>0.2430555555555556</v>
+        <v>0.2395833333333333</v>
       </c>
       <c r="D151" s="4" t="n">
-        <v>0.7548611111111111</v>
+        <v>0.7541666666666667</v>
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
@@ -3664,13 +3555,13 @@
         </is>
       </c>
       <c r="B152" s="3" t="n">
-        <v>46240</v>
+        <v>46250</v>
       </c>
       <c r="C152" s="4" t="n">
-        <v>0.2402777777777778</v>
+        <v>0.2354166666666667</v>
       </c>
       <c r="D152" s="4" t="n">
-        <v>0.7513888888888889</v>
+        <v>0.7520833333333333</v>
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
@@ -3685,13 +3576,13 @@
         </is>
       </c>
       <c r="B153" s="3" t="n">
-        <v>46239</v>
+        <v>46249</v>
       </c>
       <c r="C153" s="4" t="n">
-        <v>0.2368055555555555</v>
+        <v>0.2381944444444444</v>
       </c>
       <c r="D153" s="4" t="n">
-        <v>0.7611111111111111</v>
+        <v>0.7513888888888889</v>
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
@@ -3706,13 +3597,13 @@
         </is>
       </c>
       <c r="B154" s="3" t="n">
-        <v>46238</v>
+        <v>46247</v>
       </c>
       <c r="C154" s="4" t="n">
-        <v>0.2451388888888889</v>
+        <v>0.2444444444444444</v>
       </c>
       <c r="D154" s="4" t="n">
-        <v>0.7520833333333333</v>
+        <v>0.7576388888888889</v>
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
@@ -3727,17 +3618,21 @@
         </is>
       </c>
       <c r="B155" s="3" t="n">
-        <v>46237</v>
-      </c>
-      <c r="C155" s="4" t="n">
-        <v>0.24375</v>
-      </c>
-      <c r="D155" s="4" t="n">
-        <v>0.7527777777777778</v>
+        <v>46246</v>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>PLEASE VERIFY: check-in/out times not captured (gap between source photos)</t>
         </is>
       </c>
     </row>
@@ -3748,13 +3643,13 @@
         </is>
       </c>
       <c r="B156" s="3" t="n">
-        <v>46236</v>
+        <v>46242</v>
       </c>
       <c r="C156" s="4" t="n">
-        <v>0.24375</v>
+        <v>0.2430555555555556</v>
       </c>
       <c r="D156" s="4" t="n">
-        <v>0.7520833333333333</v>
+        <v>0.7548611111111111</v>
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
@@ -3769,34 +3664,34 @@
         </is>
       </c>
       <c r="B157" s="3" t="n">
-        <v>46235</v>
+        <v>46240</v>
       </c>
       <c r="C157" s="4" t="n">
-        <v>0.2451388888888889</v>
+        <v>0.2402777777777778</v>
       </c>
       <c r="D157" s="4" t="n">
-        <v>0.7506944444444444</v>
+        <v>0.7513888888888889</v>
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>last day of month; final record</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B158" s="3" t="n">
-        <v>46264</v>
+        <v>46239</v>
       </c>
       <c r="C158" s="4" t="n">
-        <v>0.2958333333333333</v>
+        <v>0.2368055555555555</v>
       </c>
       <c r="D158" s="4" t="n">
-        <v>0.7215277777777778</v>
+        <v>0.7611111111111111</v>
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
@@ -3807,17 +3702,17 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B159" s="3" t="n">
-        <v>46263</v>
+        <v>46238</v>
       </c>
       <c r="C159" s="4" t="n">
-        <v>0.2513888888888889</v>
+        <v>0.2451388888888889</v>
       </c>
       <c r="D159" s="4" t="n">
-        <v>0.7104166666666667</v>
+        <v>0.7520833333333333</v>
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
@@ -3828,17 +3723,17 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B160" s="3" t="n">
-        <v>46261</v>
+        <v>46237</v>
       </c>
       <c r="C160" s="4" t="n">
-        <v>0.4881944444444444</v>
+        <v>0.24375</v>
       </c>
       <c r="D160" s="4" t="n">
-        <v>0.7111111111111111</v>
+        <v>0.7527777777777778</v>
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
@@ -3849,17 +3744,17 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B161" s="3" t="n">
-        <v>46260</v>
+        <v>46236</v>
       </c>
       <c r="C161" s="4" t="n">
-        <v>0.2375</v>
+        <v>0.24375</v>
       </c>
       <c r="D161" s="4" t="n">
-        <v>0.7152777777777778</v>
+        <v>0.7520833333333333</v>
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
@@ -3870,42 +3765,21 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B162" s="3" t="n">
-        <v>46259</v>
+        <v>46235</v>
       </c>
       <c r="C162" s="4" t="n">
-        <v>0.2854166666666667</v>
+        <v>0.2451388888888889</v>
       </c>
       <c r="D162" s="4" t="n">
-        <v>0.7222222222222222</v>
+        <v>0.7506944444444444</v>
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="B163" s="3" t="n">
-        <v>46258</v>
-      </c>
-      <c r="C163" s="4" t="n">
-        <v>0.2784722222222222</v>
-      </c>
-      <c r="D163" s="4" t="n">
-        <v>0.7055555555555556</v>
-      </c>
-      <c r="E163" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>last day of month; final record</t>
         </is>
       </c>
     </row>
@@ -3916,13 +3790,13 @@
         </is>
       </c>
       <c r="B164" s="3" t="n">
-        <v>46257</v>
+        <v>46264</v>
       </c>
       <c r="C164" s="4" t="n">
-        <v>0.2444444444444444</v>
+        <v>0.2958333333333333</v>
       </c>
       <c r="D164" s="4" t="n">
-        <v>0.7076388888888889</v>
+        <v>0.7215277777777778</v>
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
@@ -3937,13 +3811,13 @@
         </is>
       </c>
       <c r="B165" s="3" t="n">
-        <v>46256</v>
+        <v>46263</v>
       </c>
       <c r="C165" s="4" t="n">
-        <v>0.2888888888888889</v>
+        <v>0.2513888888888889</v>
       </c>
       <c r="D165" s="4" t="n">
-        <v>0.7083333333333334</v>
+        <v>0.7104166666666667</v>
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
@@ -3958,13 +3832,13 @@
         </is>
       </c>
       <c r="B166" s="3" t="n">
-        <v>46254</v>
+        <v>46261</v>
       </c>
       <c r="C166" s="4" t="n">
-        <v>0.4298611111111111</v>
+        <v>0.4881944444444444</v>
       </c>
       <c r="D166" s="4" t="n">
-        <v>0.70625</v>
+        <v>0.7111111111111111</v>
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
@@ -3979,13 +3853,13 @@
         </is>
       </c>
       <c r="B167" s="3" t="n">
-        <v>46253</v>
+        <v>46260</v>
       </c>
       <c r="C167" s="4" t="n">
-        <v>0.2944444444444445</v>
+        <v>0.2375</v>
       </c>
       <c r="D167" s="4" t="n">
-        <v>0.7305555555555555</v>
+        <v>0.7152777777777778</v>
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
@@ -4000,13 +3874,13 @@
         </is>
       </c>
       <c r="B168" s="3" t="n">
-        <v>46252</v>
+        <v>46259</v>
       </c>
       <c r="C168" s="4" t="n">
-        <v>0.3659722222222222</v>
+        <v>0.2854166666666667</v>
       </c>
       <c r="D168" s="4" t="n">
-        <v>0.7208333333333333</v>
+        <v>0.7222222222222222</v>
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
@@ -4021,13 +3895,13 @@
         </is>
       </c>
       <c r="B169" s="3" t="n">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="C169" s="4" t="n">
-        <v>0.3104166666666667</v>
+        <v>0.2784722222222222</v>
       </c>
       <c r="D169" s="4" t="n">
-        <v>0.7069444444444445</v>
+        <v>0.7055555555555556</v>
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
@@ -4042,13 +3916,13 @@
         </is>
       </c>
       <c r="B170" s="3" t="n">
-        <v>46250</v>
+        <v>46257</v>
       </c>
       <c r="C170" s="4" t="n">
-        <v>0.3416666666666667</v>
+        <v>0.2444444444444444</v>
       </c>
       <c r="D170" s="4" t="n">
-        <v>0.7173611111111111</v>
+        <v>0.7076388888888889</v>
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
@@ -4063,13 +3937,13 @@
         </is>
       </c>
       <c r="B171" s="3" t="n">
-        <v>46249</v>
+        <v>46256</v>
       </c>
       <c r="C171" s="4" t="n">
-        <v>0.2680555555555555</v>
+        <v>0.2888888888888889</v>
       </c>
       <c r="D171" s="4" t="n">
-        <v>0.7625</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="E171" s="2" t="inlineStr">
         <is>
@@ -4084,13 +3958,13 @@
         </is>
       </c>
       <c r="B172" s="3" t="n">
-        <v>46247</v>
+        <v>46254</v>
       </c>
       <c r="C172" s="4" t="n">
-        <v>0.3409722222222222</v>
+        <v>0.4298611111111111</v>
       </c>
       <c r="D172" s="4" t="n">
-        <v>0.7583333333333333</v>
+        <v>0.70625</v>
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
@@ -4105,13 +3979,13 @@
         </is>
       </c>
       <c r="B173" s="3" t="n">
-        <v>46246</v>
+        <v>46253</v>
       </c>
       <c r="C173" s="4" t="n">
-        <v>0.2694444444444444</v>
+        <v>0.2944444444444445</v>
       </c>
       <c r="D173" s="4" t="n">
-        <v>0.7222222222222222</v>
+        <v>0.7305555555555555</v>
       </c>
       <c r="E173" s="2" t="inlineStr">
         <is>
@@ -4126,13 +4000,13 @@
         </is>
       </c>
       <c r="B174" s="3" t="n">
-        <v>46245</v>
+        <v>46252</v>
       </c>
       <c r="C174" s="4" t="n">
-        <v>0.275</v>
+        <v>0.3659722222222222</v>
       </c>
       <c r="D174" s="4" t="n">
-        <v>0.7618055555555555</v>
+        <v>0.7208333333333333</v>
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
@@ -4147,17 +4021,17 @@
         </is>
       </c>
       <c r="B175" s="3" t="n">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="C175" s="4" t="n">
-        <v>0.2298611111111111</v>
+        <v>0.3104166666666667</v>
       </c>
       <c r="D175" s="4" t="n">
-        <v>0.75625</v>
+        <v>0.7069444444444445</v>
       </c>
       <c r="E175" s="2" t="inlineStr">
         <is>
-          <t>extra punch: 06:48</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -4168,13 +4042,13 @@
         </is>
       </c>
       <c r="B176" s="3" t="n">
-        <v>46243</v>
+        <v>46250</v>
       </c>
       <c r="C176" s="4" t="n">
-        <v>0.2451388888888889</v>
+        <v>0.3416666666666667</v>
       </c>
       <c r="D176" s="4" t="n">
-        <v>0.7694444444444445</v>
+        <v>0.7173611111111111</v>
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
@@ -4189,13 +4063,13 @@
         </is>
       </c>
       <c r="B177" s="3" t="n">
-        <v>46242</v>
+        <v>46249</v>
       </c>
       <c r="C177" s="4" t="n">
-        <v>0.2388888888888889</v>
+        <v>0.2680555555555555</v>
       </c>
       <c r="D177" s="4" t="n">
-        <v>0.6965277777777777</v>
+        <v>0.7625</v>
       </c>
       <c r="E177" s="2" t="inlineStr">
         <is>
@@ -4210,19 +4084,17 @@
         </is>
       </c>
       <c r="B178" s="3" t="n">
-        <v>46240</v>
+        <v>46247</v>
       </c>
       <c r="C178" s="4" t="n">
-        <v>0.2715277777777778</v>
-      </c>
-      <c r="D178" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.3409722222222222</v>
+      </c>
+      <c r="D178" s="4" t="n">
+        <v>0.7583333333333333</v>
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -4233,13 +4105,13 @@
         </is>
       </c>
       <c r="B179" s="3" t="n">
-        <v>46239</v>
+        <v>46246</v>
       </c>
       <c r="C179" s="4" t="n">
-        <v>0.2756944444444445</v>
+        <v>0.2694444444444444</v>
       </c>
       <c r="D179" s="4" t="n">
-        <v>0.7152777777777778</v>
+        <v>0.7222222222222222</v>
       </c>
       <c r="E179" s="2" t="inlineStr">
         <is>
@@ -4254,13 +4126,13 @@
         </is>
       </c>
       <c r="B180" s="3" t="n">
-        <v>46238</v>
+        <v>46245</v>
       </c>
       <c r="C180" s="4" t="n">
-        <v>0.2729166666666666</v>
+        <v>0.275</v>
       </c>
       <c r="D180" s="4" t="n">
-        <v>0.7527777777777778</v>
+        <v>0.7618055555555555</v>
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
@@ -4275,17 +4147,17 @@
         </is>
       </c>
       <c r="B181" s="3" t="n">
-        <v>46237</v>
+        <v>46244</v>
       </c>
       <c r="C181" s="4" t="n">
-        <v>0.2451388888888889</v>
+        <v>0.2298611111111111</v>
       </c>
       <c r="D181" s="4" t="n">
-        <v>0.7201388888888889</v>
+        <v>0.75625</v>
       </c>
       <c r="E181" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>extra punch: 06:48</t>
         </is>
       </c>
     </row>
@@ -4296,13 +4168,13 @@
         </is>
       </c>
       <c r="B182" s="3" t="n">
-        <v>46236</v>
+        <v>46243</v>
       </c>
       <c r="C182" s="4" t="n">
-        <v>0.2722222222222222</v>
+        <v>0.2451388888888889</v>
       </c>
       <c r="D182" s="4" t="n">
-        <v>0.7722222222222223</v>
+        <v>0.7694444444444445</v>
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
@@ -4317,55 +4189,57 @@
         </is>
       </c>
       <c r="B183" s="3" t="n">
-        <v>46235</v>
+        <v>46242</v>
       </c>
       <c r="C183" s="4" t="n">
-        <v>0.275</v>
+        <v>0.2388888888888889</v>
       </c>
       <c r="D183" s="4" t="n">
-        <v>0.7854166666666667</v>
+        <v>0.6965277777777777</v>
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
-          <t>last day of month; final record</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B184" s="3" t="n">
-        <v>46265</v>
+        <v>46240</v>
       </c>
       <c r="C184" s="4" t="n">
-        <v>0.3888888888888889</v>
-      </c>
-      <c r="D184" s="4" t="n">
-        <v>0.7215277777777778</v>
+        <v>0.2715277777777778</v>
+      </c>
+      <c r="D184" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>corrected from a clearer re-scan photo later in the album</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B185" s="3" t="n">
-        <v>46264</v>
+        <v>46239</v>
       </c>
       <c r="C185" s="4" t="n">
-        <v>0.2798611111111111</v>
+        <v>0.2756944444444445</v>
       </c>
       <c r="D185" s="4" t="n">
-        <v>0.7472222222222222</v>
+        <v>0.7152777777777778</v>
       </c>
       <c r="E185" s="2" t="inlineStr">
         <is>
@@ -4376,40 +4250,38 @@
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B186" s="3" t="n">
-        <v>46263</v>
-      </c>
-      <c r="C186" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>46238</v>
+      </c>
+      <c r="C186" s="4" t="n">
+        <v>0.2729166666666666</v>
       </c>
       <c r="D186" s="4" t="n">
-        <v>0.7291666666666666</v>
+        <v>0.7527777777777778</v>
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B187" s="3" t="n">
-        <v>46261</v>
+        <v>46237</v>
       </c>
       <c r="C187" s="4" t="n">
-        <v>0.2833333333333333</v>
+        <v>0.2451388888888889</v>
       </c>
       <c r="D187" s="4" t="n">
-        <v>0.8645833333333334</v>
+        <v>0.7201388888888889</v>
       </c>
       <c r="E187" s="2" t="inlineStr">
         <is>
@@ -4420,67 +4292,42 @@
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B188" s="3" t="n">
-        <v>46260</v>
-      </c>
-      <c r="C188" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>46236</v>
+      </c>
+      <c r="C188" s="4" t="n">
+        <v>0.2722222222222222</v>
       </c>
       <c r="D188" s="4" t="n">
-        <v>0.6986111111111111</v>
+        <v>0.7722222222222223</v>
       </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B189" s="3" t="n">
-        <v>46259</v>
+        <v>46235</v>
       </c>
       <c r="C189" s="4" t="n">
-        <v>0.2868055555555555</v>
+        <v>0.275</v>
       </c>
       <c r="D189" s="4" t="n">
-        <v>0.6895833333333333</v>
+        <v>0.7854166666666667</v>
       </c>
       <c r="E189" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="B190" s="3" t="n">
-        <v>46258</v>
-      </c>
-      <c r="C190" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D190" s="4" t="n">
-        <v>0.7506944444444444</v>
-      </c>
-      <c r="E190" s="2" t="inlineStr">
-        <is>
-          <t>single punch only</t>
+          <t>last day of month; final record</t>
         </is>
       </c>
     </row>
@@ -4491,17 +4338,17 @@
         </is>
       </c>
       <c r="B191" s="3" t="n">
-        <v>46257</v>
+        <v>46265</v>
       </c>
       <c r="C191" s="4" t="n">
-        <v>0.2548611111111111</v>
+        <v>0.3888888888888889</v>
       </c>
       <c r="D191" s="4" t="n">
-        <v>0.7569444444444444</v>
+        <v>0.7215277777777778</v>
       </c>
       <c r="E191" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>corrected from a clearer re-scan photo later in the album</t>
         </is>
       </c>
     </row>
@@ -4512,19 +4359,17 @@
         </is>
       </c>
       <c r="B192" s="3" t="n">
-        <v>46256</v>
-      </c>
-      <c r="C192" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>46264</v>
+      </c>
+      <c r="C192" s="4" t="n">
+        <v>0.2798611111111111</v>
       </c>
       <c r="D192" s="4" t="n">
-        <v>0.74375</v>
+        <v>0.7472222222222222</v>
       </c>
       <c r="E192" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -4535,15 +4380,15 @@
         </is>
       </c>
       <c r="B193" s="3" t="n">
-        <v>46254</v>
-      </c>
-      <c r="C193" s="4" t="n">
-        <v>0.2868055555555555</v>
-      </c>
-      <c r="D193" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>46263</v>
+      </c>
+      <c r="C193" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D193" s="4" t="n">
+        <v>0.7291666666666666</v>
       </c>
       <c r="E193" s="2" t="inlineStr">
         <is>
@@ -4558,17 +4403,17 @@
         </is>
       </c>
       <c r="B194" s="3" t="n">
-        <v>46253</v>
+        <v>46261</v>
       </c>
       <c r="C194" s="4" t="n">
-        <v>0.3166666666666667</v>
+        <v>0.2833333333333333</v>
       </c>
       <c r="D194" s="4" t="n">
-        <v>0.74375</v>
+        <v>0.8645833333333334</v>
       </c>
       <c r="E194" s="2" t="inlineStr">
         <is>
-          <t>extra punch: 08:01</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -4579,17 +4424,19 @@
         </is>
       </c>
       <c r="B195" s="3" t="n">
-        <v>46252</v>
-      </c>
-      <c r="C195" s="4" t="n">
-        <v>0.28125</v>
+        <v>46260</v>
+      </c>
+      <c r="C195" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D195" s="4" t="n">
-        <v>0.7645833333333333</v>
+        <v>0.6986111111111111</v>
       </c>
       <c r="E195" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
@@ -4600,13 +4447,13 @@
         </is>
       </c>
       <c r="B196" s="3" t="n">
-        <v>46251</v>
+        <v>46259</v>
       </c>
       <c r="C196" s="4" t="n">
-        <v>0.2833333333333333</v>
+        <v>0.2868055555555555</v>
       </c>
       <c r="D196" s="4" t="n">
-        <v>0.7326388888888888</v>
+        <v>0.6895833333333333</v>
       </c>
       <c r="E196" s="2" t="inlineStr">
         <is>
@@ -4621,17 +4468,19 @@
         </is>
       </c>
       <c r="B197" s="3" t="n">
-        <v>46250</v>
-      </c>
-      <c r="C197" s="4" t="n">
-        <v>0.3409722222222222</v>
+        <v>46258</v>
+      </c>
+      <c r="C197" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D197" s="4" t="n">
-        <v>0.7104166666666667</v>
+        <v>0.7506944444444444</v>
       </c>
       <c r="E197" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
@@ -4642,17 +4491,17 @@
         </is>
       </c>
       <c r="B198" s="3" t="n">
-        <v>46249</v>
+        <v>46257</v>
       </c>
       <c r="C198" s="4" t="n">
-        <v>0.2423611111111111</v>
+        <v>0.2548611111111111</v>
       </c>
       <c r="D198" s="4" t="n">
-        <v>0.7270833333333333</v>
+        <v>0.7569444444444444</v>
       </c>
       <c r="E198" s="2" t="inlineStr">
         <is>
-          <t>extra punches: 17:27 07:28</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -4663,17 +4512,19 @@
         </is>
       </c>
       <c r="B199" s="3" t="n">
-        <v>46247</v>
-      </c>
-      <c r="C199" s="4" t="n">
-        <v>0.3388888888888889</v>
+        <v>46256</v>
+      </c>
+      <c r="C199" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D199" s="4" t="n">
-        <v>0.7236111111111111</v>
+        <v>0.74375</v>
       </c>
       <c r="E199" s="2" t="inlineStr">
         <is>
-          <t>extra punch: 17:21</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
@@ -4684,17 +4535,19 @@
         </is>
       </c>
       <c r="B200" s="3" t="n">
-        <v>46246</v>
+        <v>46254</v>
       </c>
       <c r="C200" s="4" t="n">
-        <v>0.2548611111111111</v>
-      </c>
-      <c r="D200" s="4" t="n">
-        <v>0.7222222222222222</v>
+        <v>0.2868055555555555</v>
+      </c>
+      <c r="D200" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E200" s="2" t="inlineStr">
         <is>
-          <t>extra punches: 07:44 06:16</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
@@ -4705,17 +4558,17 @@
         </is>
       </c>
       <c r="B201" s="3" t="n">
-        <v>46245</v>
+        <v>46253</v>
       </c>
       <c r="C201" s="4" t="n">
-        <v>0.3</v>
+        <v>0.3166666666666667</v>
       </c>
       <c r="D201" s="4" t="n">
-        <v>0.7465277777777778</v>
+        <v>0.74375</v>
       </c>
       <c r="E201" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>extra punch: 08:01</t>
         </is>
       </c>
     </row>
@@ -4726,13 +4579,13 @@
         </is>
       </c>
       <c r="B202" s="3" t="n">
-        <v>46244</v>
+        <v>46252</v>
       </c>
       <c r="C202" s="4" t="n">
-        <v>0.2875</v>
+        <v>0.28125</v>
       </c>
       <c r="D202" s="4" t="n">
-        <v>0.7479166666666667</v>
+        <v>0.7645833333333333</v>
       </c>
       <c r="E202" s="2" t="inlineStr">
         <is>
@@ -4747,13 +4600,13 @@
         </is>
       </c>
       <c r="B203" s="3" t="n">
-        <v>46243</v>
+        <v>46251</v>
       </c>
       <c r="C203" s="4" t="n">
-        <v>0.2784722222222222</v>
+        <v>0.2833333333333333</v>
       </c>
       <c r="D203" s="4" t="n">
-        <v>0.7555555555555555</v>
+        <v>0.7326388888888888</v>
       </c>
       <c r="E203" s="2" t="inlineStr">
         <is>
@@ -4768,13 +4621,13 @@
         </is>
       </c>
       <c r="B204" s="3" t="n">
-        <v>46242</v>
+        <v>46250</v>
       </c>
       <c r="C204" s="4" t="n">
-        <v>0.2791666666666667</v>
+        <v>0.3409722222222222</v>
       </c>
       <c r="D204" s="4" t="n">
-        <v>0.7284722222222222</v>
+        <v>0.7104166666666667</v>
       </c>
       <c r="E204" s="2" t="inlineStr">
         <is>
@@ -4789,17 +4642,17 @@
         </is>
       </c>
       <c r="B205" s="3" t="n">
-        <v>46240</v>
+        <v>46249</v>
       </c>
       <c r="C205" s="4" t="n">
-        <v>0.3986111111111111</v>
+        <v>0.2423611111111111</v>
       </c>
       <c r="D205" s="4" t="n">
-        <v>0.7277777777777777</v>
+        <v>0.7270833333333333</v>
       </c>
       <c r="E205" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>extra punches: 17:27 07:28</t>
         </is>
       </c>
     </row>
@@ -4810,19 +4663,17 @@
         </is>
       </c>
       <c r="B206" s="3" t="n">
-        <v>46239</v>
-      </c>
-      <c r="C206" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>46247</v>
+      </c>
+      <c r="C206" s="4" t="n">
+        <v>0.3388888888888889</v>
       </c>
       <c r="D206" s="4" t="n">
-        <v>0.7715277777777778</v>
+        <v>0.7236111111111111</v>
       </c>
       <c r="E206" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>extra punch: 17:21</t>
         </is>
       </c>
     </row>
@@ -4833,17 +4684,17 @@
         </is>
       </c>
       <c r="B207" s="3" t="n">
-        <v>46238</v>
+        <v>46246</v>
       </c>
       <c r="C207" s="4" t="n">
-        <v>0.3305555555555555</v>
+        <v>0.2548611111111111</v>
       </c>
       <c r="D207" s="4" t="n">
-        <v>0.7263888888888889</v>
+        <v>0.7222222222222222</v>
       </c>
       <c r="E207" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>extra punches: 07:44 06:16</t>
         </is>
       </c>
     </row>
@@ -4854,13 +4705,13 @@
         </is>
       </c>
       <c r="B208" s="3" t="n">
-        <v>46237</v>
+        <v>46245</v>
       </c>
       <c r="C208" s="4" t="n">
-        <v>0.3291666666666667</v>
+        <v>0.3</v>
       </c>
       <c r="D208" s="4" t="n">
-        <v>0.7111111111111111</v>
+        <v>0.7465277777777778</v>
       </c>
       <c r="E208" s="2" t="inlineStr">
         <is>
@@ -4875,19 +4726,17 @@
         </is>
       </c>
       <c r="B209" s="3" t="n">
-        <v>46236</v>
-      </c>
-      <c r="C209" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>46244</v>
+      </c>
+      <c r="C209" s="4" t="n">
+        <v>0.2875</v>
       </c>
       <c r="D209" s="4" t="n">
-        <v>0.3583333333333333</v>
+        <v>0.7479166666666667</v>
       </c>
       <c r="E209" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -4898,55 +4747,55 @@
         </is>
       </c>
       <c r="B210" s="3" t="n">
-        <v>46235</v>
+        <v>46243</v>
       </c>
       <c r="C210" s="4" t="n">
-        <v>0.3305555555555555</v>
+        <v>0.2784722222222222</v>
       </c>
       <c r="D210" s="4" t="n">
-        <v>0.7347222222222223</v>
+        <v>0.7555555555555555</v>
       </c>
       <c r="E210" s="2" t="inlineStr">
         <is>
-          <t>last day of month; final record</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B211" s="3" t="n">
-        <v>46265</v>
+        <v>46242</v>
       </c>
       <c r="C211" s="4" t="n">
-        <v>0.2569444444444444</v>
+        <v>0.2791666666666667</v>
       </c>
       <c r="D211" s="4" t="n">
-        <v>0.7527777777777778</v>
+        <v>0.7284722222222222</v>
       </c>
       <c r="E211" s="2" t="inlineStr">
         <is>
-          <t>corrected from a clearer re-scan photo later in the album</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B212" s="3" t="n">
-        <v>46264</v>
+        <v>46240</v>
       </c>
       <c r="C212" s="4" t="n">
-        <v>0.2555555555555555</v>
+        <v>0.3986111111111111</v>
       </c>
       <c r="D212" s="4" t="n">
-        <v>0.7458333333333333</v>
+        <v>0.7277777777777777</v>
       </c>
       <c r="E212" s="2" t="inlineStr">
         <is>
@@ -4957,38 +4806,40 @@
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B213" s="3" t="n">
-        <v>46263</v>
-      </c>
-      <c r="C213" s="4" t="n">
-        <v>0.2201388888888889</v>
+        <v>46239</v>
+      </c>
+      <c r="C213" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D213" s="4" t="n">
-        <v>0.7444444444444445</v>
+        <v>0.7715277777777778</v>
       </c>
       <c r="E213" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B214" s="3" t="n">
-        <v>46261</v>
+        <v>46238</v>
       </c>
       <c r="C214" s="4" t="n">
-        <v>0.2722222222222222</v>
+        <v>0.3305555555555555</v>
       </c>
       <c r="D214" s="4" t="n">
-        <v>0.7569444444444444</v>
+        <v>0.7263888888888889</v>
       </c>
       <c r="E214" s="2" t="inlineStr">
         <is>
@@ -4999,17 +4850,17 @@
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B215" s="3" t="n">
-        <v>46260</v>
+        <v>46237</v>
       </c>
       <c r="C215" s="4" t="n">
-        <v>0.2555555555555555</v>
+        <v>0.3291666666666667</v>
       </c>
       <c r="D215" s="4" t="n">
-        <v>0.7541666666666667</v>
+        <v>0.7111111111111111</v>
       </c>
       <c r="E215" s="2" t="inlineStr">
         <is>
@@ -5020,63 +4871,44 @@
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B216" s="3" t="n">
-        <v>46259</v>
-      </c>
-      <c r="C216" s="4" t="n">
-        <v>0.3555555555555556</v>
+        <v>46236</v>
+      </c>
+      <c r="C216" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D216" s="4" t="n">
-        <v>0.7541666666666667</v>
+        <v>0.3583333333333333</v>
       </c>
       <c r="E216" s="2" t="inlineStr">
         <is>
-          <t>extra punch: 06:33</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B217" s="3" t="n">
-        <v>46258</v>
+        <v>46235</v>
       </c>
       <c r="C217" s="4" t="n">
-        <v>0.2319444444444445</v>
+        <v>0.3305555555555555</v>
       </c>
       <c r="D217" s="4" t="n">
-        <v>0.7513888888888889</v>
+        <v>0.7347222222222223</v>
       </c>
       <c r="E217" s="2" t="inlineStr">
         <is>
-          <t>extra punch: 18:02</t>
-        </is>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="B218" s="3" t="n">
-        <v>46257</v>
-      </c>
-      <c r="C218" s="4" t="n">
-        <v>0.2402777777777778</v>
-      </c>
-      <c r="D218" s="4" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="E218" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>last day of month; final record</t>
         </is>
       </c>
     </row>
@@ -5087,17 +4919,17 @@
         </is>
       </c>
       <c r="B219" s="3" t="n">
-        <v>46256</v>
+        <v>46265</v>
       </c>
       <c r="C219" s="4" t="n">
-        <v>0.2402777777777778</v>
+        <v>0.2569444444444444</v>
       </c>
       <c r="D219" s="4" t="n">
-        <v>0.74375</v>
+        <v>0.7527777777777778</v>
       </c>
       <c r="E219" s="2" t="inlineStr">
         <is>
-          <t>extra punches: 17:51 06:13</t>
+          <t>corrected from a clearer re-scan photo later in the album</t>
         </is>
       </c>
     </row>
@@ -5108,13 +4940,13 @@
         </is>
       </c>
       <c r="B220" s="3" t="n">
-        <v>46254</v>
+        <v>46264</v>
       </c>
       <c r="C220" s="4" t="n">
-        <v>0.2583333333333334</v>
+        <v>0.2555555555555555</v>
       </c>
       <c r="D220" s="4" t="n">
-        <v>0.7451388888888889</v>
+        <v>0.7458333333333333</v>
       </c>
       <c r="E220" s="2" t="inlineStr">
         <is>
@@ -5129,13 +4961,13 @@
         </is>
       </c>
       <c r="B221" s="3" t="n">
-        <v>46253</v>
+        <v>46263</v>
       </c>
       <c r="C221" s="4" t="n">
-        <v>0.2527777777777778</v>
+        <v>0.2201388888888889</v>
       </c>
       <c r="D221" s="4" t="n">
-        <v>0.7423611111111111</v>
+        <v>0.7444444444444445</v>
       </c>
       <c r="E221" s="2" t="inlineStr">
         <is>
@@ -5150,13 +4982,13 @@
         </is>
       </c>
       <c r="B222" s="3" t="n">
-        <v>46252</v>
+        <v>46261</v>
       </c>
       <c r="C222" s="4" t="n">
-        <v>0.2395833333333333</v>
+        <v>0.2722222222222222</v>
       </c>
       <c r="D222" s="4" t="n">
-        <v>0.7611111111111111</v>
+        <v>0.7569444444444444</v>
       </c>
       <c r="E222" s="2" t="inlineStr">
         <is>
@@ -5171,13 +5003,13 @@
         </is>
       </c>
       <c r="B223" s="3" t="n">
-        <v>46251</v>
+        <v>46260</v>
       </c>
       <c r="C223" s="4" t="n">
-        <v>0.2541666666666667</v>
+        <v>0.2555555555555555</v>
       </c>
       <c r="D223" s="4" t="n">
-        <v>0.7555555555555555</v>
+        <v>0.7541666666666667</v>
       </c>
       <c r="E223" s="2" t="inlineStr">
         <is>
@@ -5192,17 +5024,17 @@
         </is>
       </c>
       <c r="B224" s="3" t="n">
-        <v>46250</v>
+        <v>46259</v>
       </c>
       <c r="C224" s="4" t="n">
-        <v>0.25625</v>
+        <v>0.3555555555555556</v>
       </c>
       <c r="D224" s="4" t="n">
-        <v>0.7458333333333333</v>
+        <v>0.7541666666666667</v>
       </c>
       <c r="E224" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>extra punch: 06:33</t>
         </is>
       </c>
     </row>
@@ -5213,17 +5045,17 @@
         </is>
       </c>
       <c r="B225" s="3" t="n">
-        <v>46249</v>
+        <v>46258</v>
       </c>
       <c r="C225" s="4" t="n">
-        <v>0.2333333333333333</v>
+        <v>0.2319444444444445</v>
       </c>
       <c r="D225" s="4" t="n">
-        <v>0.7506944444444444</v>
+        <v>0.7513888888888889</v>
       </c>
       <c r="E225" s="2" t="inlineStr">
         <is>
-          <t>extra punch: 06:05</t>
+          <t>extra punch: 18:02</t>
         </is>
       </c>
     </row>
@@ -5234,10 +5066,10 @@
         </is>
       </c>
       <c r="B226" s="3" t="n">
-        <v>46247</v>
+        <v>46257</v>
       </c>
       <c r="C226" s="4" t="n">
-        <v>0.25625</v>
+        <v>0.2402777777777778</v>
       </c>
       <c r="D226" s="4" t="n">
         <v>0.75</v>
@@ -5255,17 +5087,17 @@
         </is>
       </c>
       <c r="B227" s="3" t="n">
-        <v>46246</v>
+        <v>46256</v>
       </c>
       <c r="C227" s="4" t="n">
-        <v>0.2618055555555556</v>
+        <v>0.2402777777777778</v>
       </c>
       <c r="D227" s="4" t="n">
-        <v>0.75</v>
+        <v>0.74375</v>
       </c>
       <c r="E227" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>extra punches: 17:51 06:13</t>
         </is>
       </c>
     </row>
@@ -5276,13 +5108,13 @@
         </is>
       </c>
       <c r="B228" s="3" t="n">
-        <v>46245</v>
+        <v>46254</v>
       </c>
       <c r="C228" s="4" t="n">
-        <v>0.2541666666666667</v>
+        <v>0.2583333333333334</v>
       </c>
       <c r="D228" s="4" t="n">
-        <v>0.7465277777777778</v>
+        <v>0.7451388888888889</v>
       </c>
       <c r="E228" s="2" t="inlineStr">
         <is>
@@ -5297,13 +5129,13 @@
         </is>
       </c>
       <c r="B229" s="3" t="n">
-        <v>46244</v>
+        <v>46253</v>
       </c>
       <c r="C229" s="4" t="n">
-        <v>0.2534722222222222</v>
+        <v>0.2527777777777778</v>
       </c>
       <c r="D229" s="4" t="n">
-        <v>0.7479166666666667</v>
+        <v>0.7423611111111111</v>
       </c>
       <c r="E229" s="2" t="inlineStr">
         <is>
@@ -5318,13 +5150,13 @@
         </is>
       </c>
       <c r="B230" s="3" t="n">
-        <v>46243</v>
+        <v>46252</v>
       </c>
       <c r="C230" s="4" t="n">
-        <v>0.2368055555555555</v>
+        <v>0.2395833333333333</v>
       </c>
       <c r="D230" s="4" t="n">
-        <v>0.6729166666666667</v>
+        <v>0.7611111111111111</v>
       </c>
       <c r="E230" s="2" t="inlineStr">
         <is>
@@ -5339,17 +5171,17 @@
         </is>
       </c>
       <c r="B231" s="3" t="n">
-        <v>46242</v>
+        <v>46251</v>
       </c>
       <c r="C231" s="4" t="n">
-        <v>0.2479166666666667</v>
+        <v>0.2541666666666667</v>
       </c>
       <c r="D231" s="4" t="n">
-        <v>0.7291666666666666</v>
+        <v>0.7555555555555555</v>
       </c>
       <c r="E231" s="2" t="inlineStr">
         <is>
-          <t>extra punch: 07:09</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -5360,13 +5192,13 @@
         </is>
       </c>
       <c r="B232" s="3" t="n">
-        <v>46240</v>
+        <v>46250</v>
       </c>
       <c r="C232" s="4" t="n">
-        <v>0.2277777777777778</v>
+        <v>0.25625</v>
       </c>
       <c r="D232" s="4" t="n">
-        <v>0.75625</v>
+        <v>0.7458333333333333</v>
       </c>
       <c r="E232" s="2" t="inlineStr">
         <is>
@@ -5381,17 +5213,17 @@
         </is>
       </c>
       <c r="B233" s="3" t="n">
-        <v>46239</v>
+        <v>46249</v>
       </c>
       <c r="C233" s="4" t="n">
         <v>0.2333333333333333</v>
       </c>
       <c r="D233" s="4" t="n">
-        <v>0.7611111111111111</v>
+        <v>0.7506944444444444</v>
       </c>
       <c r="E233" s="2" t="inlineStr">
         <is>
-          <t>extra punch: 18:16</t>
+          <t>extra punch: 06:05</t>
         </is>
       </c>
     </row>
@@ -5402,13 +5234,13 @@
         </is>
       </c>
       <c r="B234" s="3" t="n">
-        <v>46238</v>
+        <v>46247</v>
       </c>
       <c r="C234" s="4" t="n">
-        <v>0.2173611111111111</v>
+        <v>0.25625</v>
       </c>
       <c r="D234" s="4" t="n">
-        <v>0.7604166666666666</v>
+        <v>0.75</v>
       </c>
       <c r="E234" s="2" t="inlineStr">
         <is>
@@ -5423,17 +5255,17 @@
         </is>
       </c>
       <c r="B235" s="3" t="n">
-        <v>46237</v>
+        <v>46246</v>
       </c>
       <c r="C235" s="4" t="n">
-        <v>0.2472222222222222</v>
+        <v>0.2618055555555556</v>
       </c>
       <c r="D235" s="4" t="n">
-        <v>0.7402777777777778</v>
+        <v>0.75</v>
       </c>
       <c r="E235" s="2" t="inlineStr">
         <is>
-          <t>extra punch: 17:46</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -5444,13 +5276,13 @@
         </is>
       </c>
       <c r="B236" s="3" t="n">
-        <v>46236</v>
+        <v>46245</v>
       </c>
       <c r="C236" s="4" t="n">
-        <v>0.2201388888888889</v>
+        <v>0.2541666666666667</v>
       </c>
       <c r="D236" s="4" t="n">
-        <v>0.7381944444444445</v>
+        <v>0.7465277777777778</v>
       </c>
       <c r="E236" s="2" t="inlineStr">
         <is>
@@ -5465,34 +5297,34 @@
         </is>
       </c>
       <c r="B237" s="3" t="n">
-        <v>46235</v>
+        <v>46244</v>
       </c>
       <c r="C237" s="4" t="n">
-        <v>0.2569444444444444</v>
+        <v>0.2534722222222222</v>
       </c>
       <c r="D237" s="4" t="n">
-        <v>0.7430555555555556</v>
+        <v>0.7479166666666667</v>
       </c>
       <c r="E237" s="2" t="inlineStr">
         <is>
-          <t>extra punch: 17:55; last day of month; final record</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B238" s="3" t="n">
-        <v>46265</v>
+        <v>46243</v>
       </c>
       <c r="C238" s="4" t="n">
-        <v>0.2493055555555556</v>
+        <v>0.2368055555555555</v>
       </c>
       <c r="D238" s="4" t="n">
-        <v>0.7527777777777778</v>
+        <v>0.6729166666666667</v>
       </c>
       <c r="E238" s="2" t="inlineStr">
         <is>
@@ -5503,38 +5335,38 @@
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B239" s="3" t="n">
-        <v>46264</v>
+        <v>46242</v>
       </c>
       <c r="C239" s="4" t="n">
-        <v>0.3006944444444444</v>
+        <v>0.2479166666666667</v>
       </c>
       <c r="D239" s="4" t="n">
-        <v>0.7458333333333333</v>
+        <v>0.7291666666666666</v>
       </c>
       <c r="E239" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>extra punch: 07:09</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B240" s="3" t="n">
-        <v>46263</v>
+        <v>46240</v>
       </c>
       <c r="C240" s="4" t="n">
-        <v>0.30625</v>
+        <v>0.2277777777777778</v>
       </c>
       <c r="D240" s="4" t="n">
-        <v>0.6736111111111112</v>
+        <v>0.75625</v>
       </c>
       <c r="E240" s="2" t="inlineStr">
         <is>
@@ -5545,84 +5377,80 @@
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B241" s="3" t="n">
-        <v>46261</v>
+        <v>46239</v>
       </c>
       <c r="C241" s="4" t="n">
-        <v>0.2791666666666667</v>
+        <v>0.2333333333333333</v>
       </c>
       <c r="D241" s="4" t="n">
-        <v>0.6916666666666667</v>
+        <v>0.7611111111111111</v>
       </c>
       <c r="E241" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>extra punch: 18:16</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B242" s="3" t="n">
-        <v>46260</v>
-      </c>
-      <c r="C242" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D242" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>46238</v>
+      </c>
+      <c r="C242" s="4" t="n">
+        <v>0.2173611111111111</v>
+      </c>
+      <c r="D242" s="4" t="n">
+        <v>0.7604166666666666</v>
       </c>
       <c r="E242" s="2" t="inlineStr">
         <is>
-          <t>PLEASE VERIFY: check-in/out times not captured (gap between source photos)</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B243" s="3" t="n">
-        <v>46265</v>
+        <v>46237</v>
       </c>
       <c r="C243" s="4" t="n">
-        <v>0.2451388888888889</v>
+        <v>0.2472222222222222</v>
       </c>
       <c r="D243" s="4" t="n">
-        <v>0.7375</v>
+        <v>0.7402777777777778</v>
       </c>
       <c r="E243" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>extra punch: 17:46</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B244" s="3" t="n">
-        <v>46264</v>
+        <v>46236</v>
       </c>
       <c r="C244" s="4" t="n">
-        <v>0.25</v>
+        <v>0.2201388888888889</v>
       </c>
       <c r="D244" s="4" t="n">
-        <v>0.6888888888888889</v>
+        <v>0.7381944444444445</v>
       </c>
       <c r="E244" s="2" t="inlineStr">
         <is>
@@ -5633,107 +5461,80 @@
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B245" s="3" t="n">
-        <v>46263</v>
+        <v>46235</v>
       </c>
       <c r="C245" s="4" t="n">
-        <v>0.2465277777777778</v>
+        <v>0.2569444444444444</v>
       </c>
       <c r="D245" s="4" t="n">
-        <v>0.7083333333333334</v>
+        <v>0.7430555555555556</v>
       </c>
       <c r="E245" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B246" s="3" t="n">
-        <v>46261</v>
-      </c>
-      <c r="C246" s="4" t="n">
-        <v>0.2569444444444444</v>
-      </c>
-      <c r="D246" s="4" t="n">
-        <v>0.6986111111111111</v>
-      </c>
-      <c r="E246" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>extra punch: 17:55; last day of month; final record</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B247" s="3" t="n">
-        <v>46260</v>
-      </c>
-      <c r="C247" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D247" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>46265</v>
+      </c>
+      <c r="C247" s="4" t="n">
+        <v>0.2493055555555556</v>
+      </c>
+      <c r="D247" s="4" t="n">
+        <v>0.7527777777777778</v>
       </c>
       <c r="E247" s="2" t="inlineStr">
         <is>
-          <t>PLEASE VERIFY: check-in/out times not captured (gap between source photos)</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B248" s="3" t="n">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="C248" s="4" t="n">
-        <v>0.2986111111111111</v>
-      </c>
-      <c r="D248" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.3006944444444444</v>
+      </c>
+      <c r="D248" s="4" t="n">
+        <v>0.7458333333333333</v>
       </c>
       <c r="E248" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B249" s="3" t="n">
-        <v>46261</v>
+        <v>46263</v>
       </c>
       <c r="C249" s="4" t="n">
-        <v>0.3375</v>
+        <v>0.30625</v>
       </c>
       <c r="D249" s="4" t="n">
-        <v>0.8090277777777778</v>
+        <v>0.6736111111111112</v>
       </c>
       <c r="E249" s="2" t="inlineStr">
         <is>
@@ -5744,17 +5545,17 @@
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B250" s="3" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="C250" s="4" t="n">
-        <v>0.3854166666666667</v>
+        <v>0.2791666666666667</v>
       </c>
       <c r="D250" s="4" t="n">
-        <v>0.8083333333333333</v>
+        <v>0.6916666666666667</v>
       </c>
       <c r="E250" s="2" t="inlineStr">
         <is>
@@ -5765,59 +5566,42 @@
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B251" s="3" t="n">
-        <v>46259</v>
-      </c>
-      <c r="C251" s="4" t="n">
-        <v>0.2673611111111111</v>
-      </c>
-      <c r="D251" s="4" t="n">
-        <v>0.7506944444444444</v>
+        <v>46260</v>
+      </c>
+      <c r="C251" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D251" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E251" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B252" s="3" t="n">
-        <v>46265</v>
-      </c>
-      <c r="C252" s="4" t="n">
-        <v>0.2472222222222222</v>
-      </c>
-      <c r="D252" s="4" t="n">
-        <v>0.7555555555555555</v>
-      </c>
-      <c r="E252" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>PLEASE VERIFY: check-in/out times not captured (gap between source photos)</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B253" s="3" t="n">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="C253" s="4" t="n">
-        <v>0.30625</v>
+        <v>0.2451388888888889</v>
       </c>
       <c r="D253" s="4" t="n">
-        <v>0.6805555555555556</v>
+        <v>0.7375</v>
       </c>
       <c r="E253" s="2" t="inlineStr">
         <is>
@@ -5828,17 +5612,17 @@
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B254" s="3" t="n">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="C254" s="4" t="n">
-        <v>0.2993055555555555</v>
+        <v>0.25</v>
       </c>
       <c r="D254" s="4" t="n">
-        <v>0.7708333333333334</v>
+        <v>0.6888888888888889</v>
       </c>
       <c r="E254" s="2" t="inlineStr">
         <is>
@@ -5849,17 +5633,17 @@
     <row r="255">
       <c r="A255" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B255" s="3" t="n">
-        <v>46261</v>
+        <v>46263</v>
       </c>
       <c r="C255" s="4" t="n">
-        <v>0.2826388888888889</v>
+        <v>0.2465277777777778</v>
       </c>
       <c r="D255" s="4" t="n">
-        <v>0.7861111111111111</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="E255" s="2" t="inlineStr">
         <is>
@@ -5870,88 +5654,65 @@
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B256" s="3" t="n">
-        <v>46260</v>
-      </c>
-      <c r="C256" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D256" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>46261</v>
+      </c>
+      <c r="C256" s="4" t="n">
+        <v>0.2569444444444444</v>
+      </c>
+      <c r="D256" s="4" t="n">
+        <v>0.6986111111111111</v>
       </c>
       <c r="E256" s="2" t="inlineStr">
         <is>
-          <t>PLEASE VERIFY: check-in/out times not captured (gap between source photos)</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B257" s="3" t="n">
-        <v>46265</v>
-      </c>
-      <c r="C257" s="4" t="n">
-        <v>0.2805555555555556</v>
-      </c>
-      <c r="D257" s="4" t="n">
-        <v>0.7534722222222222</v>
+        <v>46260</v>
+      </c>
+      <c r="C257" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D257" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E257" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B258" s="3" t="n">
-        <v>46263</v>
-      </c>
-      <c r="C258" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D258" s="4" t="n">
-        <v>0.4041666666666667</v>
-      </c>
-      <c r="E258" s="2" t="inlineStr">
-        <is>
-          <t>single punch only</t>
+          <t>PLEASE VERIFY: check-in/out times not captured (gap between source photos)</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B259" s="3" t="n">
-        <v>46261</v>
-      </c>
-      <c r="C259" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D259" s="4" t="n">
-        <v>0.7395833333333334</v>
+        <v>46263</v>
+      </c>
+      <c r="C259" s="4" t="n">
+        <v>0.2986111111111111</v>
+      </c>
+      <c r="D259" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E259" s="2" t="inlineStr">
         <is>
@@ -5962,88 +5723,61 @@
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B260" s="3" t="n">
-        <v>46259</v>
-      </c>
-      <c r="C260" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>46261</v>
+      </c>
+      <c r="C260" s="4" t="n">
+        <v>0.3375</v>
       </c>
       <c r="D260" s="4" t="n">
-        <v>0.75</v>
+        <v>0.8090277777777778</v>
       </c>
       <c r="E260" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B261" s="3" t="n">
-        <v>46258</v>
-      </c>
-      <c r="C261" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D261" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>46260</v>
+      </c>
+      <c r="C261" s="4" t="n">
+        <v>0.3854166666666667</v>
+      </c>
+      <c r="D261" s="4" t="n">
+        <v>0.8083333333333333</v>
       </c>
       <c r="E261" s="2" t="inlineStr">
         <is>
-          <t>PLEASE VERIFY: check-in/out time not captured (gap between source photos)</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B262" s="3" t="n">
-        <v>46265</v>
+        <v>46259</v>
       </c>
       <c r="C262" s="4" t="n">
-        <v>0.3319444444444444</v>
+        <v>0.2673611111111111</v>
       </c>
       <c r="D262" s="4" t="n">
-        <v>0.7680555555555556</v>
+        <v>0.7506944444444444</v>
       </c>
       <c r="E262" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="B263" s="3" t="n">
-        <v>46264</v>
-      </c>
-      <c r="C263" s="4" t="n">
-        <v>0.3534722222222222</v>
-      </c>
-      <c r="D263" s="4" t="n">
-        <v>0.7534722222222222</v>
-      </c>
-      <c r="E263" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -6052,17 +5786,17 @@
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B264" s="3" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="C264" s="4" t="n">
-        <v>0.3652777777777778</v>
+        <v>0.2472222222222222</v>
       </c>
       <c r="D264" s="4" t="n">
-        <v>0.7569444444444444</v>
+        <v>0.7555555555555555</v>
       </c>
       <c r="E264" s="2" t="inlineStr">
         <is>
@@ -6073,17 +5807,17 @@
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B265" s="3" t="n">
-        <v>46261</v>
+        <v>46264</v>
       </c>
       <c r="C265" s="4" t="n">
-        <v>0.3652777777777778</v>
+        <v>0.30625</v>
       </c>
       <c r="D265" s="4" t="n">
-        <v>0.7395833333333334</v>
+        <v>0.6805555555555556</v>
       </c>
       <c r="E265" s="2" t="inlineStr">
         <is>
@@ -6094,42 +5828,38 @@
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B266" s="3" t="n">
-        <v>46260</v>
-      </c>
-      <c r="C266" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D266" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>46263</v>
+      </c>
+      <c r="C266" s="4" t="n">
+        <v>0.2993055555555555</v>
+      </c>
+      <c r="D266" s="4" t="n">
+        <v>0.7708333333333334</v>
       </c>
       <c r="E266" s="2" t="inlineStr">
         <is>
-          <t>PLEASE VERIFY: check-in/out times not captured (gap between source photos)</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B267" s="3" t="n">
-        <v>46265</v>
+        <v>46261</v>
       </c>
       <c r="C267" s="4" t="n">
-        <v>0.2631944444444445</v>
+        <v>0.2826388888888889</v>
       </c>
       <c r="D267" s="4" t="n">
-        <v>0.7555555555555555</v>
+        <v>0.7861111111111111</v>
       </c>
       <c r="E267" s="2" t="inlineStr">
         <is>
@@ -6140,59 +5870,42 @@
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B268" s="3" t="n">
-        <v>46264</v>
-      </c>
-      <c r="C268" s="4" t="n">
-        <v>0.3194444444444444</v>
-      </c>
-      <c r="D268" s="4" t="n">
-        <v>0.7493055555555556</v>
+        <v>46260</v>
+      </c>
+      <c r="C268" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D268" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E268" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="269">
-      <c r="A269" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="B269" s="3" t="n">
-        <v>46263</v>
-      </c>
-      <c r="C269" s="4" t="n">
-        <v>0.275</v>
-      </c>
-      <c r="D269" s="4" t="n">
-        <v>0.7513888888888889</v>
-      </c>
-      <c r="E269" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>PLEASE VERIFY: check-in/out times not captured (gap between source photos)</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B270" s="3" t="n">
-        <v>46261</v>
+        <v>46265</v>
       </c>
       <c r="C270" s="4" t="n">
-        <v>0.2909722222222222</v>
+        <v>0.2805555555555556</v>
       </c>
       <c r="D270" s="4" t="n">
-        <v>0.7430555555555556</v>
+        <v>0.7534722222222222</v>
       </c>
       <c r="E270" s="2" t="inlineStr">
         <is>
@@ -6203,147 +5916,132 @@
     <row r="271">
       <c r="A271" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B271" s="3" t="n">
-        <v>46260</v>
+        <v>46263</v>
       </c>
       <c r="C271" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D271" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D271" s="4" t="n">
+        <v>0.4041666666666667</v>
       </c>
       <c r="E271" s="2" t="inlineStr">
         <is>
-          <t>PLEASE VERIFY: check-in/out times not captured (gap between source photos)</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B272" s="3" t="n">
-        <v>46264</v>
-      </c>
-      <c r="C272" s="4" t="n">
-        <v>0.3208333333333334</v>
+        <v>46261</v>
+      </c>
+      <c r="C272" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D272" s="4" t="n">
-        <v>0.7354166666666667</v>
+        <v>0.7395833333333334</v>
       </c>
       <c r="E272" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B273" s="3" t="n">
-        <v>46263</v>
-      </c>
-      <c r="C273" s="4" t="n">
-        <v>0.3347222222222222</v>
+        <v>46259</v>
+      </c>
+      <c r="C273" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D273" s="4" t="n">
-        <v>0.8895833333333333</v>
+        <v>0.75</v>
       </c>
       <c r="E273" s="2" t="inlineStr">
         <is>
-          <t>extra punch: 08:02</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B274" s="3" t="n">
-        <v>46261</v>
-      </c>
-      <c r="C274" s="4" t="n">
-        <v>0.2798611111111111</v>
-      </c>
-      <c r="D274" s="4" t="n">
-        <v>0.7493055555555556</v>
+        <v>46258</v>
+      </c>
+      <c r="C274" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D274" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E274" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B275" s="3" t="n">
-        <v>46260</v>
-      </c>
-      <c r="C275" s="4" t="n">
-        <v>0.3055555555555556</v>
-      </c>
-      <c r="D275" s="4" t="n">
-        <v>0.8013888888888889</v>
-      </c>
-      <c r="E275" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>PLEASE VERIFY: check-in/out time not captured (gap between source photos)</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="2" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B276" s="3" t="n">
         <v>46265</v>
       </c>
       <c r="C276" s="4" t="n">
-        <v>0.1479166666666667</v>
+        <v>0.3319444444444444</v>
       </c>
       <c r="D276" s="4" t="n">
-        <v>0.9326388888888889</v>
+        <v>0.7680555555555556</v>
       </c>
       <c r="E276" s="2" t="inlineStr">
         <is>
-          <t>extra punch: 22:23</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="2" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B277" s="3" t="n">
         <v>46264</v>
       </c>
       <c r="C277" s="4" t="n">
-        <v>0.14375</v>
+        <v>0.3534722222222222</v>
       </c>
       <c r="D277" s="4" t="n">
-        <v>0.75625</v>
+        <v>0.7534722222222222</v>
       </c>
       <c r="E277" s="2" t="inlineStr">
         <is>
@@ -6354,17 +6052,17 @@
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B278" s="3" t="n">
         <v>46263</v>
       </c>
       <c r="C278" s="4" t="n">
-        <v>0.1451388888888889</v>
+        <v>0.3652777777777778</v>
       </c>
       <c r="D278" s="4" t="n">
-        <v>0.7479166666666667</v>
+        <v>0.7569444444444444</v>
       </c>
       <c r="E278" s="2" t="inlineStr">
         <is>
@@ -6375,17 +6073,17 @@
     <row r="279">
       <c r="A279" s="2" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B279" s="3" t="n">
-        <v>46262</v>
+        <v>46261</v>
       </c>
       <c r="C279" s="4" t="n">
-        <v>0.1493055555555556</v>
+        <v>0.3652777777777778</v>
       </c>
       <c r="D279" s="4" t="n">
-        <v>0.7159722222222222</v>
+        <v>0.7395833333333334</v>
       </c>
       <c r="E279" s="2" t="inlineStr">
         <is>
@@ -6396,59 +6094,42 @@
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B280" s="3" t="n">
-        <v>46265</v>
-      </c>
-      <c r="C280" s="4" t="n">
-        <v>0.1868055555555556</v>
-      </c>
-      <c r="D280" s="4" t="n">
-        <v>0.4131944444444444</v>
+        <v>46260</v>
+      </c>
+      <c r="C280" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D280" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E280" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="B281" s="3" t="n">
-        <v>46264</v>
-      </c>
-      <c r="C281" s="4" t="n">
-        <v>0.1847222222222222</v>
-      </c>
-      <c r="D281" s="4" t="n">
-        <v>0.5097222222222222</v>
-      </c>
-      <c r="E281" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>PLEASE VERIFY: check-in/out times not captured (gap between source photos)</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B282" s="3" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="C282" s="4" t="n">
-        <v>0.1847222222222222</v>
+        <v>0.2631944444444445</v>
       </c>
       <c r="D282" s="4" t="n">
-        <v>0.4527777777777778</v>
+        <v>0.7555555555555555</v>
       </c>
       <c r="E282" s="2" t="inlineStr">
         <is>
@@ -6459,17 +6140,17 @@
     <row r="283">
       <c r="A283" s="2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B283" s="3" t="n">
-        <v>46262</v>
+        <v>46264</v>
       </c>
       <c r="C283" s="4" t="n">
-        <v>0.1881944444444444</v>
+        <v>0.3194444444444444</v>
       </c>
       <c r="D283" s="4" t="n">
-        <v>0.4055555555555556</v>
+        <v>0.7493055555555556</v>
       </c>
       <c r="E283" s="2" t="inlineStr">
         <is>
@@ -6480,17 +6161,17 @@
     <row r="284">
       <c r="A284" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B284" s="3" t="n">
-        <v>46265</v>
+        <v>46263</v>
       </c>
       <c r="C284" s="4" t="n">
-        <v>0.2909722222222222</v>
+        <v>0.275</v>
       </c>
       <c r="D284" s="4" t="n">
-        <v>0.75</v>
+        <v>0.7513888888888889</v>
       </c>
       <c r="E284" s="2" t="inlineStr">
         <is>
@@ -6501,17 +6182,17 @@
     <row r="285">
       <c r="A285" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B285" s="3" t="n">
-        <v>46264</v>
+        <v>46261</v>
       </c>
       <c r="C285" s="4" t="n">
-        <v>0.2888888888888889</v>
+        <v>0.2909722222222222</v>
       </c>
       <c r="D285" s="4" t="n">
-        <v>0.75</v>
+        <v>0.7430555555555556</v>
       </c>
       <c r="E285" s="2" t="inlineStr">
         <is>
@@ -6522,63 +6203,382 @@
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B286" s="3" t="n">
-        <v>46263</v>
-      </c>
-      <c r="C286" s="4" t="n">
-        <v>0.2965277777777778</v>
-      </c>
-      <c r="D286" s="4" t="n">
-        <v>0.7472222222222222</v>
+        <v>46260</v>
+      </c>
+      <c r="C286" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D286" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E286" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="287">
-      <c r="A287" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="B287" s="3" t="n">
-        <v>46261</v>
-      </c>
-      <c r="C287" s="4" t="n">
-        <v>0.24375</v>
-      </c>
-      <c r="D287" s="4" t="n">
-        <v>0.6763888888888889</v>
-      </c>
-      <c r="E287" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>PLEASE VERIFY: check-in/out times not captured (gap between source photos)</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B288" s="3" t="n">
+        <v>46264</v>
+      </c>
+      <c r="C288" s="4" t="n">
+        <v>0.3208333333333334</v>
+      </c>
+      <c r="D288" s="4" t="n">
+        <v>0.7354166666666667</v>
+      </c>
+      <c r="E288" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B289" s="3" t="n">
+        <v>46263</v>
+      </c>
+      <c r="C289" s="4" t="n">
+        <v>0.3347222222222222</v>
+      </c>
+      <c r="D289" s="4" t="n">
+        <v>0.8895833333333333</v>
+      </c>
+      <c r="E289" s="2" t="inlineStr">
+        <is>
+          <t>extra punch: 08:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B290" s="3" t="n">
+        <v>46261</v>
+      </c>
+      <c r="C290" s="4" t="n">
+        <v>0.2798611111111111</v>
+      </c>
+      <c r="D290" s="4" t="n">
+        <v>0.7493055555555556</v>
+      </c>
+      <c r="E290" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B291" s="3" t="n">
+        <v>46260</v>
+      </c>
+      <c r="C291" s="4" t="n">
+        <v>0.3055555555555556</v>
+      </c>
+      <c r="D291" s="4" t="n">
+        <v>0.8013888888888889</v>
+      </c>
+      <c r="E291" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B293" s="3" t="n">
+        <v>46265</v>
+      </c>
+      <c r="C293" s="4" t="n">
+        <v>0.1479166666666667</v>
+      </c>
+      <c r="D293" s="4" t="n">
+        <v>0.9326388888888889</v>
+      </c>
+      <c r="E293" s="2" t="inlineStr">
+        <is>
+          <t>extra punch: 22:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B294" s="3" t="n">
+        <v>46264</v>
+      </c>
+      <c r="C294" s="4" t="n">
+        <v>0.14375</v>
+      </c>
+      <c r="D294" s="4" t="n">
+        <v>0.75625</v>
+      </c>
+      <c r="E294" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B295" s="3" t="n">
+        <v>46263</v>
+      </c>
+      <c r="C295" s="4" t="n">
+        <v>0.1451388888888889</v>
+      </c>
+      <c r="D295" s="4" t="n">
+        <v>0.7479166666666667</v>
+      </c>
+      <c r="E295" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B296" s="3" t="n">
+        <v>46262</v>
+      </c>
+      <c r="C296" s="4" t="n">
+        <v>0.1493055555555556</v>
+      </c>
+      <c r="D296" s="4" t="n">
+        <v>0.7159722222222222</v>
+      </c>
+      <c r="E296" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B298" s="3" t="n">
+        <v>46265</v>
+      </c>
+      <c r="C298" s="4" t="n">
+        <v>0.1868055555555556</v>
+      </c>
+      <c r="D298" s="4" t="n">
+        <v>0.4131944444444444</v>
+      </c>
+      <c r="E298" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B299" s="3" t="n">
+        <v>46264</v>
+      </c>
+      <c r="C299" s="4" t="n">
+        <v>0.1847222222222222</v>
+      </c>
+      <c r="D299" s="4" t="n">
+        <v>0.5097222222222222</v>
+      </c>
+      <c r="E299" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B300" s="3" t="n">
+        <v>46263</v>
+      </c>
+      <c r="C300" s="4" t="n">
+        <v>0.1847222222222222</v>
+      </c>
+      <c r="D300" s="4" t="n">
+        <v>0.4527777777777778</v>
+      </c>
+      <c r="E300" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B301" s="3" t="n">
+        <v>46262</v>
+      </c>
+      <c r="C301" s="4" t="n">
+        <v>0.1881944444444444</v>
+      </c>
+      <c r="D301" s="4" t="n">
+        <v>0.4055555555555556</v>
+      </c>
+      <c r="E301" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B303" s="3" t="n">
+        <v>46265</v>
+      </c>
+      <c r="C303" s="4" t="n">
+        <v>0.2909722222222222</v>
+      </c>
+      <c r="D303" s="4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E303" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B304" s="3" t="n">
+        <v>46264</v>
+      </c>
+      <c r="C304" s="4" t="n">
+        <v>0.2888888888888889</v>
+      </c>
+      <c r="D304" s="4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E304" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B305" s="3" t="n">
+        <v>46263</v>
+      </c>
+      <c r="C305" s="4" t="n">
+        <v>0.2965277777777778</v>
+      </c>
+      <c r="D305" s="4" t="n">
+        <v>0.7472222222222222</v>
+      </c>
+      <c r="E305" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B306" s="3" t="n">
+        <v>46261</v>
+      </c>
+      <c r="C306" s="4" t="n">
+        <v>0.24375</v>
+      </c>
+      <c r="D306" s="4" t="n">
+        <v>0.6763888888888889</v>
+      </c>
+      <c r="E306" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="B288" s="3" t="n">
+      <c r="B308" s="3" t="n">
         <v>46265</v>
       </c>
-      <c r="C288" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D288" s="4" t="n">
+      <c r="C308" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D308" s="4" t="n">
         <v>0.7097222222222223</v>
       </c>
-      <c r="E288" s="2" t="inlineStr">
+      <c r="E308" s="2" t="inlineStr">
         <is>
           <t>single punch only</t>
         </is>

--- a/output/timesheet.xlsx
+++ b/output/timesheet.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E308"/>
+  <dimension ref="A1:E306"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -476,14 +476,16 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>46265</v>
-      </c>
-      <c r="C2" s="4" t="n">
-        <v>0.2361111111111111</v>
+        <v>46260</v>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -492,47 +494,45 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>PLEASE VERIFY: check-in/out times not captured (gap between source photos)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>46264</v>
+        <v>46261</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>0.2340277777777778</v>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.2791666666666667</v>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>0.6916666666666667</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
         <v>46263</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>0.2270833333333333</v>
+        <v>0.30625</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>0.7347222222222223</v>
+        <v>0.6736111111111112</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
@@ -543,17 +543,17 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>46261</v>
+        <v>46264</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>0.2361111111111111</v>
+        <v>0.3006944444444444</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>0.7166666666666667</v>
+        <v>0.7458333333333333</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
@@ -564,40 +564,19 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>46260</v>
+        <v>46265</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0.2256944444444444</v>
+        <v>0.2493055555555556</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.7381944444444445</v>
+        <v>0.7527777777777778</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="n">
-        <v>46259</v>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>0.2375</v>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>0.725</v>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -606,40 +585,42 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>46258</v>
+        <v>46260</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D8" s="4" t="n">
-        <v>0.725</v>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>PLEASE VERIFY: check-in/out times not captured (gap between source photos)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>46257</v>
+        <v>46261</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0.2506944444444444</v>
+        <v>0.2569444444444444</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.7291666666666666</v>
+        <v>0.6986111111111111</v>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
@@ -650,17 +631,17 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>46256</v>
+        <v>46263</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.2388888888888889</v>
+        <v>0.2465277777777778</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.7541666666666667</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
@@ -671,17 +652,17 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>46254</v>
+        <v>46264</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.2222222222222222</v>
+        <v>0.25</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.7291666666666666</v>
+        <v>0.6888888888888889</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
@@ -692,61 +673,38 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>46253</v>
+        <v>46265</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.2215277777777778</v>
+        <v>0.2451388888888889</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.7305555555555555</v>
+        <v>0.7375</v>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
           <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="n">
-        <v>46252</v>
-      </c>
-      <c r="C13" s="4" t="n">
-        <v>0.2354166666666667</v>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>46251</v>
+        <v>46259</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.2472222222222222</v>
+        <v>0.2673611111111111</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.7402777777777778</v>
+        <v>0.7506944444444444</v>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
@@ -757,17 +715,17 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>46250</v>
+        <v>46260</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.2298611111111111</v>
+        <v>0.3854166666666667</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.7180555555555556</v>
+        <v>0.8083333333333333</v>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
@@ -778,103 +736,86 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>46249</v>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>46261</v>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>0.3375</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.7201388888888889</v>
+        <v>0.8090277777777778</v>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>46247</v>
+        <v>46263</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.2479166666666667</v>
-      </c>
-      <c r="D17" s="4" t="n">
-        <v>0.7243055555555555</v>
+        <v>0.2986111111111111</v>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="n">
-        <v>46246</v>
-      </c>
-      <c r="C18" s="4" t="n">
-        <v>0.2361111111111111</v>
-      </c>
-      <c r="D18" s="4" t="n">
-        <v>0.7402777777777778</v>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>46245</v>
-      </c>
-      <c r="C19" s="4" t="n">
-        <v>0.2215277777777778</v>
-      </c>
-      <c r="D19" s="4" t="n">
-        <v>0.7319444444444444</v>
+        <v>46260</v>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>PLEASE VERIFY: check-in/out times not captured (gap between source photos)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>46244</v>
+        <v>46261</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.2409722222222222</v>
+        <v>0.2826388888888889</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.7597222222222222</v>
+        <v>0.7861111111111111</v>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
@@ -885,17 +826,17 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>46243</v>
+        <v>46263</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.2402777777777778</v>
+        <v>0.2993055555555555</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.725</v>
+        <v>0.7708333333333334</v>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
@@ -906,17 +847,17 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>46242</v>
+        <v>46264</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0.2402777777777778</v>
+        <v>0.30625</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.7243055555555555</v>
+        <v>0.6805555555555556</v>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
@@ -927,189 +868,178 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>46240</v>
+        <v>46265</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.2326388888888889</v>
+        <v>0.2472222222222222</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.7576388888888889</v>
+        <v>0.7555555555555555</v>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
           <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="n">
-        <v>46239</v>
-      </c>
-      <c r="C24" s="4" t="n">
-        <v>0.2229166666666667</v>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>46238</v>
+        <v>46258</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D25" s="4" t="n">
-        <v>0.7458333333333333</v>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>PLEASE VERIFY: check-in/out time not captured (gap between source photos)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>46237</v>
-      </c>
-      <c r="C26" s="4" t="n">
-        <v>0.3097222222222222</v>
+        <v>46259</v>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D26" s="4" t="n">
-        <v>0.7444444444444445</v>
+        <v>0.75</v>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>46236</v>
-      </c>
-      <c r="C27" s="4" t="n">
-        <v>0.2604166666666667</v>
+        <v>46261</v>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D27" s="4" t="n">
-        <v>0.7534722222222222</v>
+        <v>0.7395833333333334</v>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>46235</v>
-      </c>
-      <c r="C28" s="4" t="n">
-        <v>0.2368055555555555</v>
+        <v>46263</v>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D28" s="4" t="n">
-        <v>0.7430555555555556</v>
+        <v>0.4041666666666667</v>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="n">
+          <t>single punch only</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
         <v>46265</v>
       </c>
-      <c r="C30" s="4" t="n">
-        <v>0.2527777777777778</v>
-      </c>
-      <c r="D30" s="4" t="n">
-        <v>0.7354166666666667</v>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>corrected from a clearer re-scan photo later in the album</t>
+      <c r="C29" s="4" t="n">
+        <v>0.2805555555555556</v>
+      </c>
+      <c r="D29" s="4" t="n">
+        <v>0.7534722222222222</v>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>46264</v>
-      </c>
-      <c r="C31" s="4" t="n">
-        <v>0.2659722222222222</v>
-      </c>
-      <c r="D31" s="4" t="n">
-        <v>0.7354166666666667</v>
+        <v>46260</v>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>PLEASE VERIFY: check-in/out times not captured (gap between source photos)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>46263</v>
+        <v>46261</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0.2541666666666667</v>
+        <v>0.3652777777777778</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>0.7479166666666667</v>
+        <v>0.7395833333333334</v>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
@@ -1120,17 +1050,17 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B33" s="3" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.2805555555555556</v>
+        <v>0.3652777777777778</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.7701388888888889</v>
+        <v>0.7569444444444444</v>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
@@ -1141,61 +1071,40 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>46261</v>
+        <v>46264</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.2555555555555555</v>
+        <v>0.3534722222222222</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>0.8506944444444444</v>
+        <v>0.7534722222222222</v>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>extra punches: 17:07 17:02</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B35" s="3" t="n">
-        <v>46260</v>
+        <v>46265</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>0.275</v>
+        <v>0.3319444444444444</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>0.8791666666666667</v>
+        <v>0.7680555555555556</v>
       </c>
       <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>extra punch: 17:56</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="B36" s="3" t="n">
-        <v>46259</v>
-      </c>
-      <c r="C36" s="4" t="n">
-        <v>0.2611111111111111</v>
-      </c>
-      <c r="D36" s="4" t="n">
-        <v>0.7298611111111111</v>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1204,38 +1113,42 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B37" s="3" t="n">
-        <v>46258</v>
-      </c>
-      <c r="C37" s="4" t="n">
-        <v>0.2631944444444445</v>
-      </c>
-      <c r="D37" s="4" t="n">
-        <v>0.7270833333333333</v>
+        <v>46260</v>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>PLEASE VERIFY: check-in/out times not captured (gap between source photos)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B38" s="3" t="n">
-        <v>46257</v>
+        <v>46261</v>
       </c>
       <c r="C38" s="4" t="n">
-        <v>0.24375</v>
+        <v>0.2909722222222222</v>
       </c>
       <c r="D38" s="4" t="n">
-        <v>0.7263888888888889</v>
+        <v>0.7430555555555556</v>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
@@ -1246,14 +1159,14 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B39" s="3" t="n">
-        <v>46256</v>
+        <v>46263</v>
       </c>
       <c r="C39" s="4" t="n">
-        <v>0.2611111111111111</v>
+        <v>0.275</v>
       </c>
       <c r="D39" s="4" t="n">
         <v>0.7513888888888889</v>
@@ -1267,17 +1180,17 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>46255</v>
+        <v>46264</v>
       </c>
       <c r="C40" s="4" t="n">
-        <v>0.275</v>
+        <v>0.3194444444444444</v>
       </c>
       <c r="D40" s="4" t="n">
-        <v>0.8354166666666667</v>
+        <v>0.7493055555555556</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
@@ -1288,40 +1201,19 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>46254</v>
+        <v>46265</v>
       </c>
       <c r="C41" s="4" t="n">
-        <v>0.2625</v>
+        <v>0.2631944444444445</v>
       </c>
       <c r="D41" s="4" t="n">
-        <v>0.7979166666666667</v>
+        <v>0.7555555555555555</v>
       </c>
       <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="B42" s="3" t="n">
-        <v>46253</v>
-      </c>
-      <c r="C42" s="4" t="n">
-        <v>0.2777777777777778</v>
-      </c>
-      <c r="D42" s="4" t="n">
-        <v>0.7451388888888889</v>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1330,17 +1222,17 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B43" s="3" t="n">
-        <v>46252</v>
+        <v>46260</v>
       </c>
       <c r="C43" s="4" t="n">
-        <v>0.25625</v>
+        <v>0.3055555555555556</v>
       </c>
       <c r="D43" s="4" t="n">
-        <v>0.7416666666666667</v>
+        <v>0.8013888888888889</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
@@ -1351,17 +1243,17 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B44" s="3" t="n">
-        <v>46251</v>
+        <v>46261</v>
       </c>
       <c r="C44" s="4" t="n">
-        <v>0.2333333333333333</v>
+        <v>0.2798611111111111</v>
       </c>
       <c r="D44" s="4" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.7493055555555556</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
@@ -1372,61 +1264,40 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B45" s="3" t="n">
-        <v>46250</v>
+        <v>46263</v>
       </c>
       <c r="C45" s="4" t="n">
-        <v>0.2708333333333333</v>
+        <v>0.3347222222222222</v>
       </c>
       <c r="D45" s="4" t="n">
-        <v>0.7229166666666667</v>
+        <v>0.8895833333333333</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>extra punch: 08:02</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B46" s="3" t="n">
-        <v>46249</v>
+        <v>46264</v>
       </c>
       <c r="C46" s="4" t="n">
-        <v>0.1513888888888889</v>
+        <v>0.3208333333333334</v>
       </c>
       <c r="D46" s="4" t="n">
-        <v>0.7277777777777777</v>
+        <v>0.7354166666666667</v>
       </c>
       <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="B47" s="3" t="n">
-        <v>46248</v>
-      </c>
-      <c r="C47" s="4" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="D47" s="4" t="n">
-        <v>0.7076388888888889</v>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1435,17 +1306,17 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>46247</v>
+        <v>46262</v>
       </c>
       <c r="C48" s="4" t="n">
-        <v>0.1423611111111111</v>
+        <v>0.1493055555555556</v>
       </c>
       <c r="D48" s="4" t="n">
-        <v>0.75</v>
+        <v>0.7159722222222222</v>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
@@ -1456,17 +1327,17 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B49" s="3" t="n">
-        <v>46246</v>
+        <v>46263</v>
       </c>
       <c r="C49" s="4" t="n">
-        <v>0.1430555555555555</v>
+        <v>0.1451388888888889</v>
       </c>
       <c r="D49" s="4" t="n">
-        <v>0.7409722222222223</v>
+        <v>0.7479166666666667</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -1477,17 +1348,17 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B50" s="3" t="n">
-        <v>46245</v>
+        <v>46264</v>
       </c>
       <c r="C50" s="4" t="n">
         <v>0.14375</v>
       </c>
       <c r="D50" s="4" t="n">
-        <v>0.7444444444444445</v>
+        <v>0.75625</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -1498,80 +1369,59 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B51" s="3" t="n">
-        <v>46244</v>
+        <v>46265</v>
       </c>
       <c r="C51" s="4" t="n">
-        <v>0.1354166666666667</v>
+        <v>0.1479166666666667</v>
       </c>
       <c r="D51" s="4" t="n">
-        <v>0.7638888888888888</v>
+        <v>0.9326388888888889</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="B52" s="3" t="n">
-        <v>46243</v>
-      </c>
-      <c r="C52" s="4" t="n">
-        <v>0.1444444444444444</v>
-      </c>
-      <c r="D52" s="4" t="n">
-        <v>0.8381944444444445</v>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>extra punch: 22:23</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B53" s="3" t="n">
-        <v>46242</v>
+        <v>46262</v>
       </c>
       <c r="C53" s="4" t="n">
-        <v>0.1388888888888889</v>
+        <v>0.1881944444444444</v>
       </c>
       <c r="D53" s="4" t="n">
-        <v>0.8090277777777778</v>
+        <v>0.4055555555555556</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>extra punch: 03:24</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B54" s="3" t="n">
-        <v>46241</v>
+        <v>46263</v>
       </c>
       <c r="C54" s="4" t="n">
-        <v>0.1451388888888889</v>
+        <v>0.1847222222222222</v>
       </c>
       <c r="D54" s="4" t="n">
-        <v>0.7298611111111111</v>
+        <v>0.4527777777777778</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -1582,17 +1432,17 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B55" s="3" t="n">
-        <v>46240</v>
+        <v>46264</v>
       </c>
       <c r="C55" s="4" t="n">
-        <v>0.1444444444444444</v>
+        <v>0.1847222222222222</v>
       </c>
       <c r="D55" s="4" t="n">
-        <v>0.7659722222222223</v>
+        <v>0.5097222222222222</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -1603,40 +1453,19 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B56" s="3" t="n">
-        <v>46239</v>
+        <v>46265</v>
       </c>
       <c r="C56" s="4" t="n">
-        <v>0.1444444444444444</v>
+        <v>0.1868055555555556</v>
       </c>
       <c r="D56" s="4" t="n">
-        <v>0.6881944444444444</v>
+        <v>0.4131944444444444</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="B57" s="3" t="n">
-        <v>46238</v>
-      </c>
-      <c r="C57" s="4" t="n">
-        <v>0.1451388888888889</v>
-      </c>
-      <c r="D57" s="4" t="n">
-        <v>0.7708333333333334</v>
-      </c>
-      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1645,17 +1474,17 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B58" s="3" t="n">
-        <v>46237</v>
+        <v>46235</v>
       </c>
       <c r="C58" s="4" t="n">
-        <v>0.1458333333333333</v>
+        <v>0.2368055555555555</v>
       </c>
       <c r="D58" s="4" t="n">
-        <v>0.7472222222222222</v>
+        <v>0.7430555555555556</v>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
@@ -1666,17 +1495,17 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B59" s="3" t="n">
         <v>46236</v>
       </c>
       <c r="C59" s="4" t="n">
-        <v>0.14375</v>
+        <v>0.2604166666666667</v>
       </c>
       <c r="D59" s="4" t="n">
-        <v>0.7395833333333334</v>
+        <v>0.7534722222222222</v>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
@@ -1687,59 +1516,84 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B60" s="3" t="n">
-        <v>46235</v>
+        <v>46237</v>
       </c>
       <c r="C60" s="4" t="n">
-        <v>0.14375</v>
+        <v>0.3097222222222222</v>
       </c>
       <c r="D60" s="4" t="n">
-        <v>0.7576388888888889</v>
+        <v>0.7444444444444445</v>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>last day of month; final record</t>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="n">
+        <v>46238</v>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D61" s="4" t="n">
+        <v>0.7458333333333333</v>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B62" s="3" t="n">
-        <v>46256</v>
+        <v>46239</v>
       </c>
       <c r="C62" s="4" t="n">
-        <v>0.2805555555555556</v>
-      </c>
-      <c r="D62" s="4" t="n">
-        <v>0.7513888888888889</v>
+        <v>0.2229166666666667</v>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B63" s="3" t="n">
-        <v>46254</v>
+        <v>46240</v>
       </c>
       <c r="C63" s="4" t="n">
-        <v>0.275</v>
+        <v>0.2326388888888889</v>
       </c>
       <c r="D63" s="4" t="n">
-        <v>0.7256944444444444</v>
+        <v>0.7576388888888889</v>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
@@ -1750,17 +1604,17 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>46253</v>
+        <v>46242</v>
       </c>
       <c r="C64" s="4" t="n">
-        <v>0.2763888888888889</v>
+        <v>0.2402777777777778</v>
       </c>
       <c r="D64" s="4" t="n">
-        <v>0.7298611111111111</v>
+        <v>0.7243055555555555</v>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
@@ -1771,17 +1625,17 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B65" s="3" t="n">
-        <v>46252</v>
+        <v>46243</v>
       </c>
       <c r="C65" s="4" t="n">
-        <v>0.2826388888888889</v>
+        <v>0.2402777777777778</v>
       </c>
       <c r="D65" s="4" t="n">
-        <v>0.7451388888888889</v>
+        <v>0.725</v>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
@@ -1792,17 +1646,17 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B66" s="3" t="n">
-        <v>46251</v>
+        <v>46244</v>
       </c>
       <c r="C66" s="4" t="n">
-        <v>0.2743055555555556</v>
+        <v>0.2409722222222222</v>
       </c>
       <c r="D66" s="4" t="n">
-        <v>0.7333333333333333</v>
+        <v>0.7597222222222222</v>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
@@ -1813,17 +1667,17 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>46250</v>
+        <v>46245</v>
       </c>
       <c r="C67" s="4" t="n">
-        <v>0.2902777777777778</v>
+        <v>0.2215277777777778</v>
       </c>
       <c r="D67" s="4" t="n">
-        <v>0.7236111111111111</v>
+        <v>0.7319444444444444</v>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
@@ -1834,17 +1688,17 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B68" s="3" t="n">
-        <v>46249</v>
+        <v>46246</v>
       </c>
       <c r="C68" s="4" t="n">
-        <v>0.2395833333333333</v>
+        <v>0.2361111111111111</v>
       </c>
       <c r="D68" s="4" t="n">
-        <v>0.7388888888888889</v>
+        <v>0.7402777777777778</v>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
@@ -1855,17 +1709,17 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B69" s="3" t="n">
         <v>46247</v>
       </c>
       <c r="C69" s="4" t="n">
-        <v>0.2465277777777778</v>
+        <v>0.2479166666666667</v>
       </c>
       <c r="D69" s="4" t="n">
-        <v>0.7270833333333333</v>
+        <v>0.7243055555555555</v>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
@@ -1876,38 +1730,40 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B70" s="3" t="n">
-        <v>46246</v>
-      </c>
-      <c r="C70" s="4" t="n">
-        <v>0.2340277777777778</v>
+        <v>46249</v>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D70" s="4" t="n">
-        <v>0.7493055555555556</v>
+        <v>0.7201388888888889</v>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B71" s="3" t="n">
-        <v>46245</v>
+        <v>46250</v>
       </c>
       <c r="C71" s="4" t="n">
-        <v>0.2381944444444444</v>
+        <v>0.2298611111111111</v>
       </c>
       <c r="D71" s="4" t="n">
-        <v>0.7402777777777778</v>
+        <v>0.7180555555555556</v>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
@@ -1918,61 +1774,61 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B72" s="3" t="n">
-        <v>46244</v>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>46251</v>
+      </c>
+      <c r="C72" s="4" t="n">
+        <v>0.2472222222222222</v>
       </c>
       <c r="D72" s="4" t="n">
-        <v>0.75625</v>
+        <v>0.7402777777777778</v>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B73" s="3" t="n">
-        <v>46243</v>
+        <v>46252</v>
       </c>
       <c r="C73" s="4" t="n">
-        <v>0.2381944444444444</v>
-      </c>
-      <c r="D73" s="4" t="n">
-        <v>0.75625</v>
+        <v>0.2354166666666667</v>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B74" s="3" t="n">
-        <v>46242</v>
+        <v>46253</v>
       </c>
       <c r="C74" s="4" t="n">
-        <v>0.2597222222222222</v>
+        <v>0.2215277777777778</v>
       </c>
       <c r="D74" s="4" t="n">
-        <v>0.7326388888888888</v>
+        <v>0.7305555555555555</v>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
@@ -1983,17 +1839,17 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B75" s="3" t="n">
-        <v>46240</v>
+        <v>46254</v>
       </c>
       <c r="C75" s="4" t="n">
-        <v>0.2701388888888889</v>
+        <v>0.2222222222222222</v>
       </c>
       <c r="D75" s="4" t="n">
-        <v>0.7423611111111111</v>
+        <v>0.7291666666666666</v>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
@@ -2004,17 +1860,17 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B76" s="3" t="n">
-        <v>46239</v>
+        <v>46256</v>
       </c>
       <c r="C76" s="4" t="n">
-        <v>0.25625</v>
+        <v>0.2388888888888889</v>
       </c>
       <c r="D76" s="4" t="n">
-        <v>0.7763888888888889</v>
+        <v>0.7541666666666667</v>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
@@ -2025,17 +1881,17 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B77" s="3" t="n">
-        <v>46238</v>
+        <v>46257</v>
       </c>
       <c r="C77" s="4" t="n">
-        <v>0.2527777777777778</v>
+        <v>0.2506944444444444</v>
       </c>
       <c r="D77" s="4" t="n">
-        <v>0.75</v>
+        <v>0.7291666666666666</v>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
@@ -2046,38 +1902,40 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B78" s="3" t="n">
-        <v>46237</v>
-      </c>
-      <c r="C78" s="4" t="n">
-        <v>0.2604166666666667</v>
+        <v>46258</v>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D78" s="4" t="n">
-        <v>0.7479166666666667</v>
+        <v>0.725</v>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B79" s="3" t="n">
-        <v>46236</v>
+        <v>46259</v>
       </c>
       <c r="C79" s="4" t="n">
-        <v>0.2645833333333333</v>
+        <v>0.2375</v>
       </c>
       <c r="D79" s="4" t="n">
-        <v>0.7493055555555556</v>
+        <v>0.725</v>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
@@ -2088,143 +1946,147 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B80" s="3" t="n">
-        <v>46235</v>
+        <v>46260</v>
       </c>
       <c r="C80" s="4" t="n">
-        <v>0.2625</v>
+        <v>0.2256944444444444</v>
       </c>
       <c r="D80" s="4" t="n">
-        <v>0.7444444444444445</v>
+        <v>0.7381944444444445</v>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>last day of month; final record</t>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="n">
+        <v>46261</v>
+      </c>
+      <c r="C81" s="4" t="n">
+        <v>0.2361111111111111</v>
+      </c>
+      <c r="D81" s="4" t="n">
+        <v>0.7166666666666667</v>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B82" s="3" t="n">
-        <v>46265</v>
+        <v>46263</v>
       </c>
       <c r="C82" s="4" t="n">
-        <v>0.2527777777777778</v>
+        <v>0.2270833333333333</v>
       </c>
       <c r="D82" s="4" t="n">
-        <v>0.7604166666666666</v>
+        <v>0.7347222222222223</v>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>corrected from a clearer re-scan photo later in the album</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B83" s="3" t="n">
         <v>46264</v>
       </c>
       <c r="C83" s="4" t="n">
-        <v>0.2965277777777778</v>
-      </c>
-      <c r="D83" s="4" t="n">
-        <v>0.75625</v>
+        <v>0.2340277777777778</v>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B84" s="3" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="C84" s="4" t="n">
-        <v>0.2965277777777778</v>
-      </c>
-      <c r="D84" s="4" t="n">
-        <v>0.7326388888888888</v>
+        <v>0.2361111111111111</v>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="B85" s="3" t="n">
-        <v>46261</v>
-      </c>
-      <c r="C85" s="4" t="n">
-        <v>0.2666666666666667</v>
-      </c>
-      <c r="D85" s="4" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="E85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B86" s="3" t="n">
-        <v>46260</v>
+        <v>46235</v>
       </c>
       <c r="C86" s="4" t="n">
-        <v>0.3243055555555556</v>
+        <v>0.14375</v>
       </c>
       <c r="D86" s="4" t="n">
-        <v>0.7534722222222222</v>
+        <v>0.7576388888888889</v>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>extra punch: 17:56</t>
+          <t>last day of month; final record</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B87" s="3" t="n">
-        <v>46259</v>
+        <v>46236</v>
       </c>
       <c r="C87" s="4" t="n">
-        <v>0.2763888888888889</v>
+        <v>0.14375</v>
       </c>
       <c r="D87" s="4" t="n">
-        <v>0.7548611111111111</v>
+        <v>0.7395833333333334</v>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
@@ -2235,17 +2097,17 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B88" s="3" t="n">
-        <v>46258</v>
+        <v>46237</v>
       </c>
       <c r="C88" s="4" t="n">
-        <v>0.3263888888888889</v>
+        <v>0.1458333333333333</v>
       </c>
       <c r="D88" s="4" t="n">
-        <v>0.7388888888888889</v>
+        <v>0.7472222222222222</v>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
@@ -2256,17 +2118,17 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B89" s="3" t="n">
-        <v>46257</v>
+        <v>46238</v>
       </c>
       <c r="C89" s="4" t="n">
-        <v>0.25</v>
+        <v>0.1451388888888889</v>
       </c>
       <c r="D89" s="4" t="n">
-        <v>0.7493055555555556</v>
+        <v>0.7708333333333334</v>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
@@ -2277,17 +2139,17 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B90" s="3" t="n">
-        <v>46256</v>
+        <v>46239</v>
       </c>
       <c r="C90" s="4" t="n">
-        <v>0.2069444444444444</v>
+        <v>0.1444444444444444</v>
       </c>
       <c r="D90" s="4" t="n">
-        <v>0.7243055555555555</v>
+        <v>0.6881944444444444</v>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
@@ -2298,40 +2160,38 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B91" s="3" t="n">
-        <v>46254</v>
+        <v>46240</v>
       </c>
       <c r="C91" s="4" t="n">
-        <v>0.3576388888888889</v>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.1444444444444444</v>
+      </c>
+      <c r="D91" s="4" t="n">
+        <v>0.7659722222222223</v>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>46253</v>
+        <v>46241</v>
       </c>
       <c r="C92" s="4" t="n">
-        <v>0.475</v>
+        <v>0.1451388888888889</v>
       </c>
       <c r="D92" s="4" t="n">
-        <v>0.7173611111111111</v>
+        <v>0.7298611111111111</v>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
@@ -2342,38 +2202,38 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B93" s="3" t="n">
-        <v>46252</v>
+        <v>46242</v>
       </c>
       <c r="C93" s="4" t="n">
-        <v>0.3083333333333333</v>
+        <v>0.1388888888888889</v>
       </c>
       <c r="D93" s="4" t="n">
-        <v>0.7583333333333333</v>
+        <v>0.8090277777777778</v>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>extra punch: 03:24</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B94" s="3" t="n">
-        <v>46251</v>
+        <v>46243</v>
       </c>
       <c r="C94" s="4" t="n">
-        <v>0.3979166666666666</v>
+        <v>0.1444444444444444</v>
       </c>
       <c r="D94" s="4" t="n">
-        <v>0.7680555555555556</v>
+        <v>0.8381944444444445</v>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
@@ -2384,17 +2244,17 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B95" s="3" t="n">
-        <v>46250</v>
+        <v>46244</v>
       </c>
       <c r="C95" s="4" t="n">
-        <v>0.325</v>
+        <v>0.1354166666666667</v>
       </c>
       <c r="D95" s="4" t="n">
-        <v>0.7722222222222223</v>
+        <v>0.7638888888888888</v>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
@@ -2405,17 +2265,17 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B96" s="3" t="n">
-        <v>46249</v>
+        <v>46245</v>
       </c>
       <c r="C96" s="4" t="n">
-        <v>0.2354166666666667</v>
+        <v>0.14375</v>
       </c>
       <c r="D96" s="4" t="n">
-        <v>0.75</v>
+        <v>0.7444444444444445</v>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
@@ -2426,86 +2286,80 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B97" s="3" t="n">
-        <v>46247</v>
+        <v>46246</v>
       </c>
       <c r="C97" s="4" t="n">
-        <v>0.3347222222222222</v>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.1430555555555555</v>
+      </c>
+      <c r="D97" s="4" t="n">
+        <v>0.7409722222222223</v>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B98" s="3" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="C98" s="4" t="n">
-        <v>0.2986111111111111</v>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.1423611111111111</v>
+      </c>
+      <c r="D98" s="4" t="n">
+        <v>0.75</v>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B99" s="3" t="n">
-        <v>46245</v>
+        <v>46248</v>
       </c>
       <c r="C99" s="4" t="n">
-        <v>0.3118055555555556</v>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.15</v>
+      </c>
+      <c r="D99" s="4" t="n">
+        <v>0.7076388888888889</v>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>46244</v>
+        <v>46249</v>
       </c>
       <c r="C100" s="4" t="n">
-        <v>0.2263888888888889</v>
+        <v>0.1513888888888889</v>
       </c>
       <c r="D100" s="4" t="n">
-        <v>0.75</v>
+        <v>0.7277777777777777</v>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
@@ -2516,17 +2370,17 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>46243</v>
+        <v>46250</v>
       </c>
       <c r="C101" s="4" t="n">
-        <v>0.2798611111111111</v>
+        <v>0.2708333333333333</v>
       </c>
       <c r="D101" s="4" t="n">
-        <v>0.75</v>
+        <v>0.7229166666666667</v>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
@@ -2537,17 +2391,17 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B102" s="3" t="n">
-        <v>46242</v>
+        <v>46251</v>
       </c>
       <c r="C102" s="4" t="n">
-        <v>0.3055555555555556</v>
+        <v>0.2333333333333333</v>
       </c>
       <c r="D102" s="4" t="n">
-        <v>0.7604166666666666</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
@@ -2558,17 +2412,17 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B103" s="3" t="n">
-        <v>46240</v>
+        <v>46252</v>
       </c>
       <c r="C103" s="4" t="n">
-        <v>0.30625</v>
+        <v>0.25625</v>
       </c>
       <c r="D103" s="4" t="n">
-        <v>0.7590277777777777</v>
+        <v>0.7416666666666667</v>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
@@ -2579,17 +2433,17 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B104" s="3" t="n">
-        <v>46239</v>
+        <v>46253</v>
       </c>
       <c r="C104" s="4" t="n">
-        <v>0.3222222222222222</v>
+        <v>0.2777777777777778</v>
       </c>
       <c r="D104" s="4" t="n">
-        <v>0.7715277777777778</v>
+        <v>0.7451388888888889</v>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
@@ -2600,17 +2454,17 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B105" s="3" t="n">
-        <v>46238</v>
+        <v>46254</v>
       </c>
       <c r="C105" s="4" t="n">
-        <v>0.2763888888888889</v>
+        <v>0.2625</v>
       </c>
       <c r="D105" s="4" t="n">
-        <v>0.7166666666666667</v>
+        <v>0.7979166666666667</v>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
@@ -2621,17 +2475,17 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>46237</v>
+        <v>46255</v>
       </c>
       <c r="C106" s="4" t="n">
-        <v>0.3034722222222222</v>
+        <v>0.275</v>
       </c>
       <c r="D106" s="4" t="n">
-        <v>0.7159722222222222</v>
+        <v>0.8354166666666667</v>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
@@ -2642,17 +2496,17 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B107" s="3" t="n">
-        <v>46236</v>
+        <v>46256</v>
       </c>
       <c r="C107" s="4" t="n">
-        <v>0.2958333333333333</v>
+        <v>0.2611111111111111</v>
       </c>
       <c r="D107" s="4" t="n">
-        <v>0.7430555555555556</v>
+        <v>0.7513888888888889</v>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
@@ -2663,124 +2517,143 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B108" s="3" t="n">
-        <v>46235</v>
+        <v>46257</v>
       </c>
       <c r="C108" s="4" t="n">
-        <v>0.2381944444444444</v>
+        <v>0.24375</v>
       </c>
       <c r="D108" s="4" t="n">
-        <v>0.7458333333333333</v>
+        <v>0.7263888888888889</v>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>last day of month; final record</t>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B109" s="3" t="n">
+        <v>46258</v>
+      </c>
+      <c r="C109" s="4" t="n">
+        <v>0.2631944444444445</v>
+      </c>
+      <c r="D109" s="4" t="n">
+        <v>0.7270833333333333</v>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B110" s="3" t="n">
-        <v>46265</v>
+        <v>46259</v>
       </c>
       <c r="C110" s="4" t="n">
-        <v>0.2777777777777778</v>
+        <v>0.2611111111111111</v>
       </c>
       <c r="D110" s="4" t="n">
-        <v>0.7513888888888889</v>
+        <v>0.7298611111111111</v>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>corrected from a clearer re-scan photo later in the album</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>46264</v>
+        <v>46260</v>
       </c>
       <c r="C111" s="4" t="n">
-        <v>0.2590277777777778</v>
+        <v>0.275</v>
       </c>
       <c r="D111" s="4" t="n">
-        <v>0.7541666666666667</v>
+        <v>0.8791666666666667</v>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>extra punch: 17:56</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B112" s="3" t="n">
-        <v>46263</v>
+        <v>46261</v>
       </c>
       <c r="C112" s="4" t="n">
-        <v>0.2569444444444444</v>
+        <v>0.2555555555555555</v>
       </c>
       <c r="D112" s="4" t="n">
-        <v>0.7458333333333333</v>
+        <v>0.8506944444444444</v>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>extra punch: 17:53</t>
+          <t>extra punches: 17:07 17:02</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B113" s="3" t="n">
         <v>46262</v>
       </c>
       <c r="C113" s="4" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="D113" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.2805555555555556</v>
+      </c>
+      <c r="D113" s="4" t="n">
+        <v>0.7701388888888889</v>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B114" s="3" t="n">
-        <v>46261</v>
+        <v>46263</v>
       </c>
       <c r="C114" s="4" t="n">
-        <v>0.2493055555555556</v>
+        <v>0.2541666666666667</v>
       </c>
       <c r="D114" s="4" t="n">
-        <v>0.7944444444444444</v>
+        <v>0.7479166666666667</v>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
@@ -2791,17 +2664,17 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B115" s="3" t="n">
-        <v>46260</v>
+        <v>46264</v>
       </c>
       <c r="C115" s="4" t="n">
-        <v>0.2479166666666667</v>
+        <v>0.2659722222222222</v>
       </c>
       <c r="D115" s="4" t="n">
-        <v>0.7555555555555555</v>
+        <v>0.7354166666666667</v>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
@@ -2812,103 +2685,80 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B116" s="3" t="n">
-        <v>46259</v>
+        <v>46265</v>
       </c>
       <c r="C116" s="4" t="n">
-        <v>0.2375</v>
+        <v>0.2527777777777778</v>
       </c>
       <c r="D116" s="4" t="n">
-        <v>0.7597222222222222</v>
+        <v>0.7354166666666667</v>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="B117" s="3" t="n">
-        <v>46258</v>
-      </c>
-      <c r="C117" s="4" t="n">
-        <v>0.2375</v>
-      </c>
-      <c r="D117" s="4" t="n">
-        <v>0.7506944444444444</v>
-      </c>
-      <c r="E117" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>corrected from a clearer re-scan photo later in the album</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>46257</v>
+        <v>46235</v>
       </c>
       <c r="C118" s="4" t="n">
-        <v>0.2479166666666667</v>
+        <v>0.2625</v>
       </c>
       <c r="D118" s="4" t="n">
-        <v>0.7618055555555555</v>
+        <v>0.7444444444444445</v>
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>last day of month; final record</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B119" s="3" t="n">
-        <v>46256</v>
+        <v>46236</v>
       </c>
       <c r="C119" s="4" t="n">
-        <v>0.2875</v>
-      </c>
-      <c r="D119" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.2645833333333333</v>
+      </c>
+      <c r="D119" s="4" t="n">
+        <v>0.7493055555555556</v>
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B120" s="3" t="n">
-        <v>46254</v>
+        <v>46237</v>
       </c>
       <c r="C120" s="4" t="n">
-        <v>0.2472222222222222</v>
+        <v>0.2604166666666667</v>
       </c>
       <c r="D120" s="4" t="n">
-        <v>0.7243055555555555</v>
+        <v>0.7479166666666667</v>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
@@ -2919,17 +2769,17 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B121" s="3" t="n">
-        <v>46253</v>
+        <v>46238</v>
       </c>
       <c r="C121" s="4" t="n">
-        <v>0.2395833333333333</v>
+        <v>0.2527777777777778</v>
       </c>
       <c r="D121" s="4" t="n">
-        <v>0.7416666666666667</v>
+        <v>0.75</v>
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
@@ -2940,17 +2790,17 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B122" s="3" t="n">
-        <v>46252</v>
+        <v>46239</v>
       </c>
       <c r="C122" s="4" t="n">
-        <v>0.2916666666666667</v>
+        <v>0.25625</v>
       </c>
       <c r="D122" s="4" t="n">
-        <v>0.7416666666666667</v>
+        <v>0.7763888888888889</v>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
@@ -2961,17 +2811,17 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B123" s="3" t="n">
-        <v>46251</v>
+        <v>46240</v>
       </c>
       <c r="C123" s="4" t="n">
-        <v>0.3416666666666667</v>
+        <v>0.2701388888888889</v>
       </c>
       <c r="D123" s="4" t="n">
-        <v>0.7326388888888888</v>
+        <v>0.7423611111111111</v>
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
@@ -2982,17 +2832,17 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B124" s="3" t="n">
-        <v>46250</v>
+        <v>46242</v>
       </c>
       <c r="C124" s="4" t="n">
-        <v>0.2409722222222222</v>
+        <v>0.2597222222222222</v>
       </c>
       <c r="D124" s="4" t="n">
-        <v>0.7381944444444445</v>
+        <v>0.7326388888888888</v>
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
@@ -3003,17 +2853,17 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B125" s="3" t="n">
-        <v>46249</v>
+        <v>46243</v>
       </c>
       <c r="C125" s="4" t="n">
-        <v>0.2354166666666667</v>
+        <v>0.2381944444444444</v>
       </c>
       <c r="D125" s="4" t="n">
-        <v>0.7611111111111111</v>
+        <v>0.75625</v>
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
@@ -3024,19 +2874,19 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B126" s="3" t="n">
-        <v>46247</v>
-      </c>
-      <c r="C126" s="4" t="n">
-        <v>0.4402777777777778</v>
-      </c>
-      <c r="D126" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>46244</v>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D126" s="4" t="n">
+        <v>0.75625</v>
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
@@ -3047,17 +2897,17 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B127" s="3" t="n">
-        <v>46246</v>
+        <v>46245</v>
       </c>
       <c r="C127" s="4" t="n">
-        <v>0.2284722222222222</v>
+        <v>0.2381944444444444</v>
       </c>
       <c r="D127" s="4" t="n">
-        <v>0.7423611111111111</v>
+        <v>0.7402777777777778</v>
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
@@ -3068,17 +2918,17 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B128" s="3" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="C128" s="4" t="n">
-        <v>0.2375</v>
+        <v>0.2340277777777778</v>
       </c>
       <c r="D128" s="4" t="n">
-        <v>0.7375</v>
+        <v>0.7493055555555556</v>
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
@@ -3089,17 +2939,17 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B129" s="3" t="n">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="C129" s="4" t="n">
-        <v>0.2256944444444444</v>
+        <v>0.2465277777777778</v>
       </c>
       <c r="D129" s="4" t="n">
-        <v>0.7611111111111111</v>
+        <v>0.7270833333333333</v>
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
@@ -3110,17 +2960,17 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B130" s="3" t="n">
-        <v>46243</v>
+        <v>46249</v>
       </c>
       <c r="C130" s="4" t="n">
         <v>0.2395833333333333</v>
       </c>
       <c r="D130" s="4" t="n">
-        <v>0.725</v>
+        <v>0.7388888888888889</v>
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
@@ -3131,17 +2981,17 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B131" s="3" t="n">
-        <v>46242</v>
+        <v>46250</v>
       </c>
       <c r="C131" s="4" t="n">
-        <v>0.2201388888888889</v>
+        <v>0.2902777777777778</v>
       </c>
       <c r="D131" s="4" t="n">
-        <v>0.7618055555555555</v>
+        <v>0.7236111111111111</v>
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
@@ -3152,17 +3002,17 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B132" s="3" t="n">
-        <v>46240</v>
+        <v>46251</v>
       </c>
       <c r="C132" s="4" t="n">
-        <v>0.2409722222222222</v>
+        <v>0.2743055555555556</v>
       </c>
       <c r="D132" s="4" t="n">
-        <v>0.7625</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
@@ -3173,17 +3023,17 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B133" s="3" t="n">
-        <v>46239</v>
+        <v>46252</v>
       </c>
       <c r="C133" s="4" t="n">
-        <v>0.4743055555555555</v>
+        <v>0.2826388888888889</v>
       </c>
       <c r="D133" s="4" t="n">
-        <v>0.7722222222222223</v>
+        <v>0.7451388888888889</v>
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
@@ -3194,17 +3044,17 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>46238</v>
+        <v>46253</v>
       </c>
       <c r="C134" s="4" t="n">
-        <v>0.4965277777777778</v>
+        <v>0.2763888888888889</v>
       </c>
       <c r="D134" s="4" t="n">
-        <v>0.7506944444444444</v>
+        <v>0.7298611111111111</v>
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
@@ -3215,17 +3065,17 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>46237</v>
+        <v>46254</v>
       </c>
       <c r="C135" s="4" t="n">
-        <v>0.2618055555555556</v>
+        <v>0.275</v>
       </c>
       <c r="D135" s="4" t="n">
-        <v>0.7472222222222222</v>
+        <v>0.7256944444444444</v>
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
@@ -3236,17 +3086,17 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B136" s="3" t="n">
-        <v>46236</v>
+        <v>46256</v>
       </c>
       <c r="C136" s="4" t="n">
-        <v>0.2972222222222222</v>
+        <v>0.2805555555555556</v>
       </c>
       <c r="D136" s="4" t="n">
-        <v>0.7430555555555556</v>
+        <v>0.7513888888888889</v>
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
@@ -3257,82 +3107,82 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B137" s="3" t="n">
-        <v>46235</v>
+        <v>46261</v>
       </c>
       <c r="C137" s="4" t="n">
-        <v>0.2590277777777778</v>
+        <v>0.24375</v>
       </c>
       <c r="D137" s="4" t="n">
-        <v>0.7319444444444444</v>
+        <v>0.6763888888888889</v>
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>last day of month; final record</t>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B138" s="3" t="n">
+        <v>46263</v>
+      </c>
+      <c r="C138" s="4" t="n">
+        <v>0.2965277777777778</v>
+      </c>
+      <c r="D138" s="4" t="n">
+        <v>0.7472222222222222</v>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B139" s="3" t="n">
-        <v>46265</v>
+        <v>46264</v>
       </c>
       <c r="C139" s="4" t="n">
-        <v>0.2361111111111111</v>
+        <v>0.2888888888888889</v>
       </c>
       <c r="D139" s="4" t="n">
-        <v>0.7520833333333333</v>
+        <v>0.75</v>
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>corrected from a clearer re-scan photo later in the album</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B140" s="3" t="n">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="C140" s="4" t="n">
-        <v>0.2423611111111111</v>
+        <v>0.2909722222222222</v>
       </c>
       <c r="D140" s="4" t="n">
-        <v>0.7513888888888889</v>
+        <v>0.75</v>
       </c>
       <c r="E140" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="B141" s="3" t="n">
-        <v>46263</v>
-      </c>
-      <c r="C141" s="4" t="n">
-        <v>0.2444444444444444</v>
-      </c>
-      <c r="D141" s="4" t="n">
-        <v>0.7548611111111111</v>
-      </c>
-      <c r="E141" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3341,38 +3191,38 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B142" s="3" t="n">
-        <v>46261</v>
+        <v>46235</v>
       </c>
       <c r="C142" s="4" t="n">
-        <v>0.2472222222222222</v>
+        <v>0.2381944444444444</v>
       </c>
       <c r="D142" s="4" t="n">
-        <v>0.7513888888888889</v>
+        <v>0.7458333333333333</v>
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>last day of month; final record</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B143" s="3" t="n">
-        <v>46260</v>
+        <v>46236</v>
       </c>
       <c r="C143" s="4" t="n">
-        <v>0.2465277777777778</v>
+        <v>0.2958333333333333</v>
       </c>
       <c r="D143" s="4" t="n">
-        <v>0.7555555555555555</v>
+        <v>0.7430555555555556</v>
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
@@ -3383,17 +3233,17 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B144" s="3" t="n">
-        <v>46259</v>
+        <v>46237</v>
       </c>
       <c r="C144" s="4" t="n">
-        <v>0.2368055555555555</v>
+        <v>0.3034722222222222</v>
       </c>
       <c r="D144" s="4" t="n">
-        <v>0.7506944444444444</v>
+        <v>0.7159722222222222</v>
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
@@ -3404,17 +3254,17 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B145" s="3" t="n">
-        <v>46258</v>
+        <v>46238</v>
       </c>
       <c r="C145" s="4" t="n">
-        <v>0.2347222222222222</v>
+        <v>0.2763888888888889</v>
       </c>
       <c r="D145" s="4" t="n">
-        <v>0.7520833333333333</v>
+        <v>0.7166666666666667</v>
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
@@ -3425,17 +3275,17 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B146" s="3" t="n">
-        <v>46257</v>
+        <v>46239</v>
       </c>
       <c r="C146" s="4" t="n">
-        <v>0.2458333333333333</v>
+        <v>0.3222222222222222</v>
       </c>
       <c r="D146" s="4" t="n">
-        <v>0.7527777777777778</v>
+        <v>0.7715277777777778</v>
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
@@ -3446,17 +3296,17 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B147" s="3" t="n">
-        <v>46256</v>
+        <v>46240</v>
       </c>
       <c r="C147" s="4" t="n">
-        <v>0.2402777777777778</v>
+        <v>0.30625</v>
       </c>
       <c r="D147" s="4" t="n">
-        <v>0.75</v>
+        <v>0.7590277777777777</v>
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
@@ -3467,17 +3317,17 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B148" s="3" t="n">
-        <v>46254</v>
+        <v>46242</v>
       </c>
       <c r="C148" s="4" t="n">
-        <v>0.2402777777777778</v>
+        <v>0.3055555555555556</v>
       </c>
       <c r="D148" s="4" t="n">
-        <v>0.7520833333333333</v>
+        <v>0.7604166666666666</v>
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
@@ -3488,17 +3338,17 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B149" s="3" t="n">
-        <v>46253</v>
+        <v>46243</v>
       </c>
       <c r="C149" s="4" t="n">
-        <v>0.2423611111111111</v>
+        <v>0.2798611111111111</v>
       </c>
       <c r="D149" s="4" t="n">
-        <v>0.7506944444444444</v>
+        <v>0.75</v>
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
@@ -3509,17 +3359,17 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B150" s="3" t="n">
-        <v>46252</v>
+        <v>46244</v>
       </c>
       <c r="C150" s="4" t="n">
-        <v>0.2451388888888889</v>
+        <v>0.2263888888888889</v>
       </c>
       <c r="D150" s="4" t="n">
-        <v>0.7527777777777778</v>
+        <v>0.75</v>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
@@ -3530,80 +3380,86 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B151" s="3" t="n">
-        <v>46251</v>
+        <v>46245</v>
       </c>
       <c r="C151" s="4" t="n">
-        <v>0.2395833333333333</v>
-      </c>
-      <c r="D151" s="4" t="n">
-        <v>0.7541666666666667</v>
+        <v>0.3118055555555556</v>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B152" s="3" t="n">
-        <v>46250</v>
+        <v>46246</v>
       </c>
       <c r="C152" s="4" t="n">
-        <v>0.2354166666666667</v>
-      </c>
-      <c r="D152" s="4" t="n">
-        <v>0.7520833333333333</v>
+        <v>0.2986111111111111</v>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B153" s="3" t="n">
-        <v>46249</v>
+        <v>46247</v>
       </c>
       <c r="C153" s="4" t="n">
-        <v>0.2381944444444444</v>
-      </c>
-      <c r="D153" s="4" t="n">
-        <v>0.7513888888888889</v>
+        <v>0.3347222222222222</v>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B154" s="3" t="n">
-        <v>46247</v>
+        <v>46249</v>
       </c>
       <c r="C154" s="4" t="n">
-        <v>0.2444444444444444</v>
+        <v>0.2354166666666667</v>
       </c>
       <c r="D154" s="4" t="n">
-        <v>0.7576388888888889</v>
+        <v>0.75</v>
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
@@ -3614,42 +3470,38 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B155" s="3" t="n">
-        <v>46246</v>
-      </c>
-      <c r="C155" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D155" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>46250</v>
+      </c>
+      <c r="C155" s="4" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="D155" s="4" t="n">
+        <v>0.7722222222222223</v>
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>PLEASE VERIFY: check-in/out times not captured (gap between source photos)</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B156" s="3" t="n">
-        <v>46242</v>
+        <v>46251</v>
       </c>
       <c r="C156" s="4" t="n">
-        <v>0.2430555555555556</v>
+        <v>0.3979166666666666</v>
       </c>
       <c r="D156" s="4" t="n">
-        <v>0.7548611111111111</v>
+        <v>0.7680555555555556</v>
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
@@ -3660,17 +3512,17 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B157" s="3" t="n">
-        <v>46240</v>
+        <v>46252</v>
       </c>
       <c r="C157" s="4" t="n">
-        <v>0.2402777777777778</v>
+        <v>0.3083333333333333</v>
       </c>
       <c r="D157" s="4" t="n">
-        <v>0.7513888888888889</v>
+        <v>0.7583333333333333</v>
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
@@ -3681,17 +3533,17 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B158" s="3" t="n">
-        <v>46239</v>
+        <v>46253</v>
       </c>
       <c r="C158" s="4" t="n">
-        <v>0.2368055555555555</v>
+        <v>0.475</v>
       </c>
       <c r="D158" s="4" t="n">
-        <v>0.7611111111111111</v>
+        <v>0.7173611111111111</v>
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
@@ -3702,38 +3554,40 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B159" s="3" t="n">
-        <v>46238</v>
+        <v>46254</v>
       </c>
       <c r="C159" s="4" t="n">
-        <v>0.2451388888888889</v>
-      </c>
-      <c r="D159" s="4" t="n">
-        <v>0.7520833333333333</v>
+        <v>0.3576388888888889</v>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B160" s="3" t="n">
-        <v>46237</v>
+        <v>46256</v>
       </c>
       <c r="C160" s="4" t="n">
-        <v>0.24375</v>
+        <v>0.2069444444444444</v>
       </c>
       <c r="D160" s="4" t="n">
-        <v>0.7527777777777778</v>
+        <v>0.7243055555555555</v>
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
@@ -3744,17 +3598,17 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B161" s="3" t="n">
-        <v>46236</v>
+        <v>46257</v>
       </c>
       <c r="C161" s="4" t="n">
-        <v>0.24375</v>
+        <v>0.25</v>
       </c>
       <c r="D161" s="4" t="n">
-        <v>0.7520833333333333</v>
+        <v>0.7493055555555556</v>
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
@@ -3765,59 +3619,80 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B162" s="3" t="n">
-        <v>46235</v>
+        <v>46258</v>
       </c>
       <c r="C162" s="4" t="n">
-        <v>0.2451388888888889</v>
+        <v>0.3263888888888889</v>
       </c>
       <c r="D162" s="4" t="n">
-        <v>0.7506944444444444</v>
+        <v>0.7388888888888889</v>
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>last day of month; final record</t>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B163" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="C163" s="4" t="n">
+        <v>0.2763888888888889</v>
+      </c>
+      <c r="D163" s="4" t="n">
+        <v>0.7548611111111111</v>
+      </c>
+      <c r="E163" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B164" s="3" t="n">
-        <v>46264</v>
+        <v>46260</v>
       </c>
       <c r="C164" s="4" t="n">
-        <v>0.2958333333333333</v>
+        <v>0.3243055555555556</v>
       </c>
       <c r="D164" s="4" t="n">
-        <v>0.7215277777777778</v>
+        <v>0.7534722222222222</v>
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>extra punch: 17:56</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B165" s="3" t="n">
-        <v>46263</v>
+        <v>46261</v>
       </c>
       <c r="C165" s="4" t="n">
-        <v>0.2513888888888889</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="D165" s="4" t="n">
-        <v>0.7104166666666667</v>
+        <v>0.75</v>
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
@@ -3828,17 +3703,17 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B166" s="3" t="n">
-        <v>46261</v>
+        <v>46263</v>
       </c>
       <c r="C166" s="4" t="n">
-        <v>0.4881944444444444</v>
+        <v>0.2965277777777778</v>
       </c>
       <c r="D166" s="4" t="n">
-        <v>0.7111111111111111</v>
+        <v>0.7326388888888888</v>
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
@@ -3849,17 +3724,17 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B167" s="3" t="n">
-        <v>46260</v>
+        <v>46264</v>
       </c>
       <c r="C167" s="4" t="n">
-        <v>0.2375</v>
+        <v>0.2965277777777778</v>
       </c>
       <c r="D167" s="4" t="n">
-        <v>0.7152777777777778</v>
+        <v>0.75625</v>
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
@@ -3870,80 +3745,59 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B168" s="3" t="n">
-        <v>46259</v>
+        <v>46265</v>
       </c>
       <c r="C168" s="4" t="n">
-        <v>0.2854166666666667</v>
+        <v>0.2527777777777778</v>
       </c>
       <c r="D168" s="4" t="n">
-        <v>0.7222222222222222</v>
+        <v>0.7604166666666666</v>
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="B169" s="3" t="n">
-        <v>46258</v>
-      </c>
-      <c r="C169" s="4" t="n">
-        <v>0.2784722222222222</v>
-      </c>
-      <c r="D169" s="4" t="n">
-        <v>0.7055555555555556</v>
-      </c>
-      <c r="E169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>corrected from a clearer re-scan photo later in the album</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B170" s="3" t="n">
-        <v>46257</v>
+        <v>46235</v>
       </c>
       <c r="C170" s="4" t="n">
-        <v>0.2444444444444444</v>
+        <v>0.2590277777777778</v>
       </c>
       <c r="D170" s="4" t="n">
-        <v>0.7076388888888889</v>
+        <v>0.7319444444444444</v>
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>last day of month; final record</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B171" s="3" t="n">
-        <v>46256</v>
+        <v>46236</v>
       </c>
       <c r="C171" s="4" t="n">
-        <v>0.2888888888888889</v>
+        <v>0.2972222222222222</v>
       </c>
       <c r="D171" s="4" t="n">
-        <v>0.7083333333333334</v>
+        <v>0.7430555555555556</v>
       </c>
       <c r="E171" s="2" t="inlineStr">
         <is>
@@ -3954,17 +3808,17 @@
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B172" s="3" t="n">
-        <v>46254</v>
+        <v>46237</v>
       </c>
       <c r="C172" s="4" t="n">
-        <v>0.4298611111111111</v>
+        <v>0.2618055555555556</v>
       </c>
       <c r="D172" s="4" t="n">
-        <v>0.70625</v>
+        <v>0.7472222222222222</v>
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
@@ -3975,17 +3829,17 @@
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B173" s="3" t="n">
-        <v>46253</v>
+        <v>46238</v>
       </c>
       <c r="C173" s="4" t="n">
-        <v>0.2944444444444445</v>
+        <v>0.4965277777777778</v>
       </c>
       <c r="D173" s="4" t="n">
-        <v>0.7305555555555555</v>
+        <v>0.7506944444444444</v>
       </c>
       <c r="E173" s="2" t="inlineStr">
         <is>
@@ -3996,17 +3850,17 @@
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B174" s="3" t="n">
-        <v>46252</v>
+        <v>46239</v>
       </c>
       <c r="C174" s="4" t="n">
-        <v>0.3659722222222222</v>
+        <v>0.4743055555555555</v>
       </c>
       <c r="D174" s="4" t="n">
-        <v>0.7208333333333333</v>
+        <v>0.7722222222222223</v>
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
@@ -4017,17 +3871,17 @@
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B175" s="3" t="n">
-        <v>46251</v>
+        <v>46240</v>
       </c>
       <c r="C175" s="4" t="n">
-        <v>0.3104166666666667</v>
+        <v>0.2409722222222222</v>
       </c>
       <c r="D175" s="4" t="n">
-        <v>0.7069444444444445</v>
+        <v>0.7625</v>
       </c>
       <c r="E175" s="2" t="inlineStr">
         <is>
@@ -4038,17 +3892,17 @@
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B176" s="3" t="n">
-        <v>46250</v>
+        <v>46242</v>
       </c>
       <c r="C176" s="4" t="n">
-        <v>0.3416666666666667</v>
+        <v>0.2201388888888889</v>
       </c>
       <c r="D176" s="4" t="n">
-        <v>0.7173611111111111</v>
+        <v>0.7618055555555555</v>
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
@@ -4059,17 +3913,17 @@
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B177" s="3" t="n">
-        <v>46249</v>
+        <v>46243</v>
       </c>
       <c r="C177" s="4" t="n">
-        <v>0.2680555555555555</v>
+        <v>0.2395833333333333</v>
       </c>
       <c r="D177" s="4" t="n">
-        <v>0.7625</v>
+        <v>0.725</v>
       </c>
       <c r="E177" s="2" t="inlineStr">
         <is>
@@ -4080,17 +3934,17 @@
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B178" s="3" t="n">
-        <v>46247</v>
+        <v>46244</v>
       </c>
       <c r="C178" s="4" t="n">
-        <v>0.3409722222222222</v>
+        <v>0.2256944444444444</v>
       </c>
       <c r="D178" s="4" t="n">
-        <v>0.7583333333333333</v>
+        <v>0.7611111111111111</v>
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
@@ -4101,17 +3955,17 @@
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B179" s="3" t="n">
-        <v>46246</v>
+        <v>46245</v>
       </c>
       <c r="C179" s="4" t="n">
-        <v>0.2694444444444444</v>
+        <v>0.2375</v>
       </c>
       <c r="D179" s="4" t="n">
-        <v>0.7222222222222222</v>
+        <v>0.7375</v>
       </c>
       <c r="E179" s="2" t="inlineStr">
         <is>
@@ -4122,17 +3976,17 @@
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B180" s="3" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="C180" s="4" t="n">
-        <v>0.275</v>
+        <v>0.2284722222222222</v>
       </c>
       <c r="D180" s="4" t="n">
-        <v>0.7618055555555555</v>
+        <v>0.7423611111111111</v>
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
@@ -4143,38 +3997,40 @@
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B181" s="3" t="n">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="C181" s="4" t="n">
-        <v>0.2298611111111111</v>
-      </c>
-      <c r="D181" s="4" t="n">
-        <v>0.75625</v>
+        <v>0.4402777777777778</v>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E181" s="2" t="inlineStr">
         <is>
-          <t>extra punch: 06:48</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B182" s="3" t="n">
-        <v>46243</v>
+        <v>46249</v>
       </c>
       <c r="C182" s="4" t="n">
-        <v>0.2451388888888889</v>
+        <v>0.2354166666666667</v>
       </c>
       <c r="D182" s="4" t="n">
-        <v>0.7694444444444445</v>
+        <v>0.7611111111111111</v>
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
@@ -4185,17 +4041,17 @@
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B183" s="3" t="n">
-        <v>46242</v>
+        <v>46250</v>
       </c>
       <c r="C183" s="4" t="n">
-        <v>0.2388888888888889</v>
+        <v>0.2409722222222222</v>
       </c>
       <c r="D183" s="4" t="n">
-        <v>0.6965277777777777</v>
+        <v>0.7381944444444445</v>
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
@@ -4206,40 +4062,38 @@
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B184" s="3" t="n">
-        <v>46240</v>
+        <v>46251</v>
       </c>
       <c r="C184" s="4" t="n">
-        <v>0.2715277777777778</v>
-      </c>
-      <c r="D184" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.3416666666666667</v>
+      </c>
+      <c r="D184" s="4" t="n">
+        <v>0.7326388888888888</v>
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B185" s="3" t="n">
-        <v>46239</v>
+        <v>46252</v>
       </c>
       <c r="C185" s="4" t="n">
-        <v>0.2756944444444445</v>
+        <v>0.2916666666666667</v>
       </c>
       <c r="D185" s="4" t="n">
-        <v>0.7152777777777778</v>
+        <v>0.7416666666666667</v>
       </c>
       <c r="E185" s="2" t="inlineStr">
         <is>
@@ -4250,17 +4104,17 @@
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B186" s="3" t="n">
-        <v>46238</v>
+        <v>46253</v>
       </c>
       <c r="C186" s="4" t="n">
-        <v>0.2729166666666666</v>
+        <v>0.2395833333333333</v>
       </c>
       <c r="D186" s="4" t="n">
-        <v>0.7527777777777778</v>
+        <v>0.7416666666666667</v>
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
@@ -4271,17 +4125,17 @@
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B187" s="3" t="n">
-        <v>46237</v>
+        <v>46254</v>
       </c>
       <c r="C187" s="4" t="n">
-        <v>0.2451388888888889</v>
+        <v>0.2472222222222222</v>
       </c>
       <c r="D187" s="4" t="n">
-        <v>0.7201388888888889</v>
+        <v>0.7243055555555555</v>
       </c>
       <c r="E187" s="2" t="inlineStr">
         <is>
@@ -4292,80 +4146,103 @@
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B188" s="3" t="n">
-        <v>46236</v>
+        <v>46256</v>
       </c>
       <c r="C188" s="4" t="n">
-        <v>0.2722222222222222</v>
-      </c>
-      <c r="D188" s="4" t="n">
-        <v>0.7722222222222223</v>
+        <v>0.2875</v>
+      </c>
+      <c r="D188" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B189" s="3" t="n">
-        <v>46235</v>
+        <v>46257</v>
       </c>
       <c r="C189" s="4" t="n">
-        <v>0.275</v>
+        <v>0.2479166666666667</v>
       </c>
       <c r="D189" s="4" t="n">
-        <v>0.7854166666666667</v>
+        <v>0.7618055555555555</v>
       </c>
       <c r="E189" s="2" t="inlineStr">
         <is>
-          <t>last day of month; final record</t>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B190" s="3" t="n">
+        <v>46258</v>
+      </c>
+      <c r="C190" s="4" t="n">
+        <v>0.2375</v>
+      </c>
+      <c r="D190" s="4" t="n">
+        <v>0.7506944444444444</v>
+      </c>
+      <c r="E190" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B191" s="3" t="n">
-        <v>46265</v>
+        <v>46259</v>
       </c>
       <c r="C191" s="4" t="n">
-        <v>0.3888888888888889</v>
+        <v>0.2375</v>
       </c>
       <c r="D191" s="4" t="n">
-        <v>0.7215277777777778</v>
+        <v>0.7597222222222222</v>
       </c>
       <c r="E191" s="2" t="inlineStr">
         <is>
-          <t>corrected from a clearer re-scan photo later in the album</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B192" s="3" t="n">
-        <v>46264</v>
+        <v>46260</v>
       </c>
       <c r="C192" s="4" t="n">
-        <v>0.2798611111111111</v>
+        <v>0.2479166666666667</v>
       </c>
       <c r="D192" s="4" t="n">
-        <v>0.7472222222222222</v>
+        <v>0.7555555555555555</v>
       </c>
       <c r="E192" s="2" t="inlineStr">
         <is>
@@ -4376,84 +4253,82 @@
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B193" s="3" t="n">
-        <v>46263</v>
-      </c>
-      <c r="C193" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>46261</v>
+      </c>
+      <c r="C193" s="4" t="n">
+        <v>0.2493055555555556</v>
       </c>
       <c r="D193" s="4" t="n">
-        <v>0.7291666666666666</v>
+        <v>0.7944444444444444</v>
       </c>
       <c r="E193" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B194" s="3" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="C194" s="4" t="n">
-        <v>0.2833333333333333</v>
-      </c>
-      <c r="D194" s="4" t="n">
-        <v>0.8645833333333334</v>
+        <v>0.25</v>
+      </c>
+      <c r="D194" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E194" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B195" s="3" t="n">
-        <v>46260</v>
-      </c>
-      <c r="C195" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>46263</v>
+      </c>
+      <c r="C195" s="4" t="n">
+        <v>0.2569444444444444</v>
       </c>
       <c r="D195" s="4" t="n">
-        <v>0.6986111111111111</v>
+        <v>0.7458333333333333</v>
       </c>
       <c r="E195" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>extra punch: 17:53</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B196" s="3" t="n">
-        <v>46259</v>
+        <v>46264</v>
       </c>
       <c r="C196" s="4" t="n">
-        <v>0.2868055555555555</v>
+        <v>0.2590277777777778</v>
       </c>
       <c r="D196" s="4" t="n">
-        <v>0.6895833333333333</v>
+        <v>0.7541666666666667</v>
       </c>
       <c r="E196" s="2" t="inlineStr">
         <is>
@@ -4464,128 +4339,101 @@
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B197" s="3" t="n">
-        <v>46258</v>
-      </c>
-      <c r="C197" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>46265</v>
+      </c>
+      <c r="C197" s="4" t="n">
+        <v>0.2777777777777778</v>
       </c>
       <c r="D197" s="4" t="n">
-        <v>0.7506944444444444</v>
+        <v>0.7513888888888889</v>
       </c>
       <c r="E197" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
-        </is>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="B198" s="3" t="n">
-        <v>46257</v>
-      </c>
-      <c r="C198" s="4" t="n">
-        <v>0.2548611111111111</v>
-      </c>
-      <c r="D198" s="4" t="n">
-        <v>0.7569444444444444</v>
-      </c>
-      <c r="E198" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>corrected from a clearer re-scan photo later in the album</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B199" s="3" t="n">
-        <v>46256</v>
-      </c>
-      <c r="C199" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>46235</v>
+      </c>
+      <c r="C199" s="4" t="n">
+        <v>0.2451388888888889</v>
       </c>
       <c r="D199" s="4" t="n">
-        <v>0.74375</v>
+        <v>0.7506944444444444</v>
       </c>
       <c r="E199" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>last day of month; final record</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B200" s="3" t="n">
-        <v>46254</v>
+        <v>46236</v>
       </c>
       <c r="C200" s="4" t="n">
-        <v>0.2868055555555555</v>
-      </c>
-      <c r="D200" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.24375</v>
+      </c>
+      <c r="D200" s="4" t="n">
+        <v>0.7520833333333333</v>
       </c>
       <c r="E200" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B201" s="3" t="n">
-        <v>46253</v>
+        <v>46237</v>
       </c>
       <c r="C201" s="4" t="n">
-        <v>0.3166666666666667</v>
+        <v>0.24375</v>
       </c>
       <c r="D201" s="4" t="n">
-        <v>0.74375</v>
+        <v>0.7527777777777778</v>
       </c>
       <c r="E201" s="2" t="inlineStr">
         <is>
-          <t>extra punch: 08:01</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B202" s="3" t="n">
-        <v>46252</v>
+        <v>46238</v>
       </c>
       <c r="C202" s="4" t="n">
-        <v>0.28125</v>
+        <v>0.2451388888888889</v>
       </c>
       <c r="D202" s="4" t="n">
-        <v>0.7645833333333333</v>
+        <v>0.7520833333333333</v>
       </c>
       <c r="E202" s="2" t="inlineStr">
         <is>
@@ -4596,17 +4444,17 @@
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B203" s="3" t="n">
-        <v>46251</v>
+        <v>46239</v>
       </c>
       <c r="C203" s="4" t="n">
-        <v>0.2833333333333333</v>
+        <v>0.2368055555555555</v>
       </c>
       <c r="D203" s="4" t="n">
-        <v>0.7326388888888888</v>
+        <v>0.7611111111111111</v>
       </c>
       <c r="E203" s="2" t="inlineStr">
         <is>
@@ -4617,17 +4465,17 @@
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B204" s="3" t="n">
-        <v>46250</v>
+        <v>46240</v>
       </c>
       <c r="C204" s="4" t="n">
-        <v>0.3409722222222222</v>
+        <v>0.2402777777777778</v>
       </c>
       <c r="D204" s="4" t="n">
-        <v>0.7104166666666667</v>
+        <v>0.7513888888888889</v>
       </c>
       <c r="E204" s="2" t="inlineStr">
         <is>
@@ -4638,80 +4486,84 @@
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B205" s="3" t="n">
-        <v>46249</v>
+        <v>46242</v>
       </c>
       <c r="C205" s="4" t="n">
-        <v>0.2423611111111111</v>
+        <v>0.2430555555555556</v>
       </c>
       <c r="D205" s="4" t="n">
-        <v>0.7270833333333333</v>
+        <v>0.7548611111111111</v>
       </c>
       <c r="E205" s="2" t="inlineStr">
         <is>
-          <t>extra punches: 17:27 07:28</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B206" s="3" t="n">
-        <v>46247</v>
-      </c>
-      <c r="C206" s="4" t="n">
-        <v>0.3388888888888889</v>
-      </c>
-      <c r="D206" s="4" t="n">
-        <v>0.7236111111111111</v>
+        <v>46246</v>
+      </c>
+      <c r="C206" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D206" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E206" s="2" t="inlineStr">
         <is>
-          <t>extra punch: 17:21</t>
+          <t>PLEASE VERIFY: check-in/out times not captured (gap between source photos)</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B207" s="3" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="C207" s="4" t="n">
-        <v>0.2548611111111111</v>
+        <v>0.2444444444444444</v>
       </c>
       <c r="D207" s="4" t="n">
-        <v>0.7222222222222222</v>
+        <v>0.7576388888888889</v>
       </c>
       <c r="E207" s="2" t="inlineStr">
         <is>
-          <t>extra punches: 07:44 06:16</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B208" s="3" t="n">
-        <v>46245</v>
+        <v>46249</v>
       </c>
       <c r="C208" s="4" t="n">
-        <v>0.3</v>
+        <v>0.2381944444444444</v>
       </c>
       <c r="D208" s="4" t="n">
-        <v>0.7465277777777778</v>
+        <v>0.7513888888888889</v>
       </c>
       <c r="E208" s="2" t="inlineStr">
         <is>
@@ -4722,17 +4574,17 @@
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B209" s="3" t="n">
-        <v>46244</v>
+        <v>46250</v>
       </c>
       <c r="C209" s="4" t="n">
-        <v>0.2875</v>
+        <v>0.2354166666666667</v>
       </c>
       <c r="D209" s="4" t="n">
-        <v>0.7479166666666667</v>
+        <v>0.7520833333333333</v>
       </c>
       <c r="E209" s="2" t="inlineStr">
         <is>
@@ -4743,17 +4595,17 @@
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B210" s="3" t="n">
-        <v>46243</v>
+        <v>46251</v>
       </c>
       <c r="C210" s="4" t="n">
-        <v>0.2784722222222222</v>
+        <v>0.2395833333333333</v>
       </c>
       <c r="D210" s="4" t="n">
-        <v>0.7555555555555555</v>
+        <v>0.7541666666666667</v>
       </c>
       <c r="E210" s="2" t="inlineStr">
         <is>
@@ -4764,17 +4616,17 @@
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B211" s="3" t="n">
-        <v>46242</v>
+        <v>46252</v>
       </c>
       <c r="C211" s="4" t="n">
-        <v>0.2791666666666667</v>
+        <v>0.2451388888888889</v>
       </c>
       <c r="D211" s="4" t="n">
-        <v>0.7284722222222222</v>
+        <v>0.7527777777777778</v>
       </c>
       <c r="E211" s="2" t="inlineStr">
         <is>
@@ -4785,17 +4637,17 @@
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B212" s="3" t="n">
-        <v>46240</v>
+        <v>46253</v>
       </c>
       <c r="C212" s="4" t="n">
-        <v>0.3986111111111111</v>
+        <v>0.2423611111111111</v>
       </c>
       <c r="D212" s="4" t="n">
-        <v>0.7277777777777777</v>
+        <v>0.7506944444444444</v>
       </c>
       <c r="E212" s="2" t="inlineStr">
         <is>
@@ -4806,40 +4658,38 @@
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B213" s="3" t="n">
-        <v>46239</v>
-      </c>
-      <c r="C213" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>46254</v>
+      </c>
+      <c r="C213" s="4" t="n">
+        <v>0.2402777777777778</v>
       </c>
       <c r="D213" s="4" t="n">
-        <v>0.7715277777777778</v>
+        <v>0.7520833333333333</v>
       </c>
       <c r="E213" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B214" s="3" t="n">
-        <v>46238</v>
+        <v>46256</v>
       </c>
       <c r="C214" s="4" t="n">
-        <v>0.3305555555555555</v>
+        <v>0.2402777777777778</v>
       </c>
       <c r="D214" s="4" t="n">
-        <v>0.7263888888888889</v>
+        <v>0.75</v>
       </c>
       <c r="E214" s="2" t="inlineStr">
         <is>
@@ -4850,17 +4700,17 @@
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B215" s="3" t="n">
-        <v>46237</v>
+        <v>46257</v>
       </c>
       <c r="C215" s="4" t="n">
-        <v>0.3291666666666667</v>
+        <v>0.2458333333333333</v>
       </c>
       <c r="D215" s="4" t="n">
-        <v>0.7111111111111111</v>
+        <v>0.7527777777777778</v>
       </c>
       <c r="E215" s="2" t="inlineStr">
         <is>
@@ -4871,82 +4721,101 @@
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B216" s="3" t="n">
-        <v>46236</v>
-      </c>
-      <c r="C216" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>46258</v>
+      </c>
+      <c r="C216" s="4" t="n">
+        <v>0.2347222222222222</v>
       </c>
       <c r="D216" s="4" t="n">
-        <v>0.3583333333333333</v>
+        <v>0.7520833333333333</v>
       </c>
       <c r="E216" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B217" s="3" t="n">
-        <v>46235</v>
+        <v>46259</v>
       </c>
       <c r="C217" s="4" t="n">
-        <v>0.3305555555555555</v>
+        <v>0.2368055555555555</v>
       </c>
       <c r="D217" s="4" t="n">
-        <v>0.7347222222222223</v>
+        <v>0.7506944444444444</v>
       </c>
       <c r="E217" s="2" t="inlineStr">
         <is>
-          <t>last day of month; final record</t>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B218" s="3" t="n">
+        <v>46260</v>
+      </c>
+      <c r="C218" s="4" t="n">
+        <v>0.2465277777777778</v>
+      </c>
+      <c r="D218" s="4" t="n">
+        <v>0.7555555555555555</v>
+      </c>
+      <c r="E218" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B219" s="3" t="n">
-        <v>46265</v>
+        <v>46261</v>
       </c>
       <c r="C219" s="4" t="n">
-        <v>0.2569444444444444</v>
+        <v>0.2472222222222222</v>
       </c>
       <c r="D219" s="4" t="n">
-        <v>0.7527777777777778</v>
+        <v>0.7513888888888889</v>
       </c>
       <c r="E219" s="2" t="inlineStr">
         <is>
-          <t>corrected from a clearer re-scan photo later in the album</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B220" s="3" t="n">
-        <v>46264</v>
+        <v>46263</v>
       </c>
       <c r="C220" s="4" t="n">
-        <v>0.2555555555555555</v>
+        <v>0.2444444444444444</v>
       </c>
       <c r="D220" s="4" t="n">
-        <v>0.7458333333333333</v>
+        <v>0.7548611111111111</v>
       </c>
       <c r="E220" s="2" t="inlineStr">
         <is>
@@ -4957,17 +4826,17 @@
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B221" s="3" t="n">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="C221" s="4" t="n">
-        <v>0.2201388888888889</v>
+        <v>0.2423611111111111</v>
       </c>
       <c r="D221" s="4" t="n">
-        <v>0.7444444444444445</v>
+        <v>0.7513888888888889</v>
       </c>
       <c r="E221" s="2" t="inlineStr">
         <is>
@@ -4978,101 +4847,80 @@
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B222" s="3" t="n">
-        <v>46261</v>
+        <v>46265</v>
       </c>
       <c r="C222" s="4" t="n">
-        <v>0.2722222222222222</v>
+        <v>0.2361111111111111</v>
       </c>
       <c r="D222" s="4" t="n">
-        <v>0.7569444444444444</v>
+        <v>0.7520833333333333</v>
       </c>
       <c r="E222" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="B223" s="3" t="n">
-        <v>46260</v>
-      </c>
-      <c r="C223" s="4" t="n">
-        <v>0.2555555555555555</v>
-      </c>
-      <c r="D223" s="4" t="n">
-        <v>0.7541666666666667</v>
-      </c>
-      <c r="E223" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>corrected from a clearer re-scan photo later in the album</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B224" s="3" t="n">
-        <v>46259</v>
+        <v>46235</v>
       </c>
       <c r="C224" s="4" t="n">
-        <v>0.3555555555555556</v>
+        <v>0.275</v>
       </c>
       <c r="D224" s="4" t="n">
-        <v>0.7541666666666667</v>
+        <v>0.7854166666666667</v>
       </c>
       <c r="E224" s="2" t="inlineStr">
         <is>
-          <t>extra punch: 06:33</t>
+          <t>last day of month; final record</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B225" s="3" t="n">
-        <v>46258</v>
+        <v>46236</v>
       </c>
       <c r="C225" s="4" t="n">
-        <v>0.2319444444444445</v>
+        <v>0.2722222222222222</v>
       </c>
       <c r="D225" s="4" t="n">
-        <v>0.7513888888888889</v>
+        <v>0.7722222222222223</v>
       </c>
       <c r="E225" s="2" t="inlineStr">
         <is>
-          <t>extra punch: 18:02</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B226" s="3" t="n">
-        <v>46257</v>
+        <v>46237</v>
       </c>
       <c r="C226" s="4" t="n">
-        <v>0.2402777777777778</v>
+        <v>0.2451388888888889</v>
       </c>
       <c r="D226" s="4" t="n">
-        <v>0.75</v>
+        <v>0.7201388888888889</v>
       </c>
       <c r="E226" s="2" t="inlineStr">
         <is>
@@ -5083,38 +4931,38 @@
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B227" s="3" t="n">
-        <v>46256</v>
+        <v>46238</v>
       </c>
       <c r="C227" s="4" t="n">
-        <v>0.2402777777777778</v>
+        <v>0.2729166666666666</v>
       </c>
       <c r="D227" s="4" t="n">
-        <v>0.74375</v>
+        <v>0.7527777777777778</v>
       </c>
       <c r="E227" s="2" t="inlineStr">
         <is>
-          <t>extra punches: 17:51 06:13</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B228" s="3" t="n">
-        <v>46254</v>
+        <v>46239</v>
       </c>
       <c r="C228" s="4" t="n">
-        <v>0.2583333333333334</v>
+        <v>0.2756944444444445</v>
       </c>
       <c r="D228" s="4" t="n">
-        <v>0.7451388888888889</v>
+        <v>0.7152777777777778</v>
       </c>
       <c r="E228" s="2" t="inlineStr">
         <is>
@@ -5125,38 +4973,40 @@
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B229" s="3" t="n">
-        <v>46253</v>
+        <v>46240</v>
       </c>
       <c r="C229" s="4" t="n">
-        <v>0.2527777777777778</v>
-      </c>
-      <c r="D229" s="4" t="n">
-        <v>0.7423611111111111</v>
+        <v>0.2715277777777778</v>
+      </c>
+      <c r="D229" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E229" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B230" s="3" t="n">
-        <v>46252</v>
+        <v>46242</v>
       </c>
       <c r="C230" s="4" t="n">
-        <v>0.2395833333333333</v>
+        <v>0.2388888888888889</v>
       </c>
       <c r="D230" s="4" t="n">
-        <v>0.7611111111111111</v>
+        <v>0.6965277777777777</v>
       </c>
       <c r="E230" s="2" t="inlineStr">
         <is>
@@ -5167,17 +5017,17 @@
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B231" s="3" t="n">
-        <v>46251</v>
+        <v>46243</v>
       </c>
       <c r="C231" s="4" t="n">
-        <v>0.2541666666666667</v>
+        <v>0.2451388888888889</v>
       </c>
       <c r="D231" s="4" t="n">
-        <v>0.7555555555555555</v>
+        <v>0.7694444444444445</v>
       </c>
       <c r="E231" s="2" t="inlineStr">
         <is>
@@ -5188,59 +5038,59 @@
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B232" s="3" t="n">
-        <v>46250</v>
+        <v>46244</v>
       </c>
       <c r="C232" s="4" t="n">
-        <v>0.25625</v>
+        <v>0.2298611111111111</v>
       </c>
       <c r="D232" s="4" t="n">
-        <v>0.7458333333333333</v>
+        <v>0.75625</v>
       </c>
       <c r="E232" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>extra punch: 06:48</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B233" s="3" t="n">
-        <v>46249</v>
+        <v>46245</v>
       </c>
       <c r="C233" s="4" t="n">
-        <v>0.2333333333333333</v>
+        <v>0.275</v>
       </c>
       <c r="D233" s="4" t="n">
-        <v>0.7506944444444444</v>
+        <v>0.7618055555555555</v>
       </c>
       <c r="E233" s="2" t="inlineStr">
         <is>
-          <t>extra punch: 06:05</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B234" s="3" t="n">
-        <v>46247</v>
+        <v>46246</v>
       </c>
       <c r="C234" s="4" t="n">
-        <v>0.25625</v>
+        <v>0.2694444444444444</v>
       </c>
       <c r="D234" s="4" t="n">
-        <v>0.75</v>
+        <v>0.7222222222222222</v>
       </c>
       <c r="E234" s="2" t="inlineStr">
         <is>
@@ -5251,17 +5101,17 @@
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B235" s="3" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="C235" s="4" t="n">
-        <v>0.2618055555555556</v>
+        <v>0.3409722222222222</v>
       </c>
       <c r="D235" s="4" t="n">
-        <v>0.75</v>
+        <v>0.7583333333333333</v>
       </c>
       <c r="E235" s="2" t="inlineStr">
         <is>
@@ -5272,17 +5122,17 @@
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B236" s="3" t="n">
-        <v>46245</v>
+        <v>46249</v>
       </c>
       <c r="C236" s="4" t="n">
-        <v>0.2541666666666667</v>
+        <v>0.2680555555555555</v>
       </c>
       <c r="D236" s="4" t="n">
-        <v>0.7465277777777778</v>
+        <v>0.7625</v>
       </c>
       <c r="E236" s="2" t="inlineStr">
         <is>
@@ -5293,17 +5143,17 @@
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B237" s="3" t="n">
-        <v>46244</v>
+        <v>46250</v>
       </c>
       <c r="C237" s="4" t="n">
-        <v>0.2534722222222222</v>
+        <v>0.3416666666666667</v>
       </c>
       <c r="D237" s="4" t="n">
-        <v>0.7479166666666667</v>
+        <v>0.7173611111111111</v>
       </c>
       <c r="E237" s="2" t="inlineStr">
         <is>
@@ -5314,17 +5164,17 @@
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B238" s="3" t="n">
-        <v>46243</v>
+        <v>46251</v>
       </c>
       <c r="C238" s="4" t="n">
-        <v>0.2368055555555555</v>
+        <v>0.3104166666666667</v>
       </c>
       <c r="D238" s="4" t="n">
-        <v>0.6729166666666667</v>
+        <v>0.7069444444444445</v>
       </c>
       <c r="E238" s="2" t="inlineStr">
         <is>
@@ -5335,38 +5185,38 @@
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B239" s="3" t="n">
-        <v>46242</v>
+        <v>46252</v>
       </c>
       <c r="C239" s="4" t="n">
-        <v>0.2479166666666667</v>
+        <v>0.3659722222222222</v>
       </c>
       <c r="D239" s="4" t="n">
-        <v>0.7291666666666666</v>
+        <v>0.7208333333333333</v>
       </c>
       <c r="E239" s="2" t="inlineStr">
         <is>
-          <t>extra punch: 07:09</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B240" s="3" t="n">
-        <v>46240</v>
+        <v>46253</v>
       </c>
       <c r="C240" s="4" t="n">
-        <v>0.2277777777777778</v>
+        <v>0.2944444444444445</v>
       </c>
       <c r="D240" s="4" t="n">
-        <v>0.75625</v>
+        <v>0.7305555555555555</v>
       </c>
       <c r="E240" s="2" t="inlineStr">
         <is>
@@ -5377,38 +5227,38 @@
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B241" s="3" t="n">
-        <v>46239</v>
+        <v>46254</v>
       </c>
       <c r="C241" s="4" t="n">
-        <v>0.2333333333333333</v>
+        <v>0.4298611111111111</v>
       </c>
       <c r="D241" s="4" t="n">
-        <v>0.7611111111111111</v>
+        <v>0.70625</v>
       </c>
       <c r="E241" s="2" t="inlineStr">
         <is>
-          <t>extra punch: 18:16</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B242" s="3" t="n">
-        <v>46238</v>
+        <v>46256</v>
       </c>
       <c r="C242" s="4" t="n">
-        <v>0.2173611111111111</v>
+        <v>0.2888888888888889</v>
       </c>
       <c r="D242" s="4" t="n">
-        <v>0.7604166666666666</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="E242" s="2" t="inlineStr">
         <is>
@@ -5419,38 +5269,38 @@
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B243" s="3" t="n">
-        <v>46237</v>
+        <v>46257</v>
       </c>
       <c r="C243" s="4" t="n">
-        <v>0.2472222222222222</v>
+        <v>0.2444444444444444</v>
       </c>
       <c r="D243" s="4" t="n">
-        <v>0.7402777777777778</v>
+        <v>0.7076388888888889</v>
       </c>
       <c r="E243" s="2" t="inlineStr">
         <is>
-          <t>extra punch: 17:46</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B244" s="3" t="n">
-        <v>46236</v>
+        <v>46258</v>
       </c>
       <c r="C244" s="4" t="n">
-        <v>0.2201388888888889</v>
+        <v>0.2784722222222222</v>
       </c>
       <c r="D244" s="4" t="n">
-        <v>0.7381944444444445</v>
+        <v>0.7055555555555556</v>
       </c>
       <c r="E244" s="2" t="inlineStr">
         <is>
@@ -5461,38 +5311,59 @@
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B245" s="3" t="n">
-        <v>46235</v>
+        <v>46259</v>
       </c>
       <c r="C245" s="4" t="n">
-        <v>0.2569444444444444</v>
+        <v>0.2854166666666667</v>
       </c>
       <c r="D245" s="4" t="n">
-        <v>0.7430555555555556</v>
+        <v>0.7222222222222222</v>
       </c>
       <c r="E245" s="2" t="inlineStr">
         <is>
-          <t>extra punch: 17:55; last day of month; final record</t>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B246" s="3" t="n">
+        <v>46260</v>
+      </c>
+      <c r="C246" s="4" t="n">
+        <v>0.2375</v>
+      </c>
+      <c r="D246" s="4" t="n">
+        <v>0.7152777777777778</v>
+      </c>
+      <c r="E246" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B247" s="3" t="n">
-        <v>46265</v>
+        <v>46261</v>
       </c>
       <c r="C247" s="4" t="n">
-        <v>0.2493055555555556</v>
+        <v>0.4881944444444444</v>
       </c>
       <c r="D247" s="4" t="n">
-        <v>0.7527777777777778</v>
+        <v>0.7111111111111111</v>
       </c>
       <c r="E247" s="2" t="inlineStr">
         <is>
@@ -5503,17 +5374,17 @@
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B248" s="3" t="n">
-        <v>46264</v>
+        <v>46263</v>
       </c>
       <c r="C248" s="4" t="n">
-        <v>0.3006944444444444</v>
+        <v>0.2513888888888889</v>
       </c>
       <c r="D248" s="4" t="n">
-        <v>0.7458333333333333</v>
+        <v>0.7104166666666667</v>
       </c>
       <c r="E248" s="2" t="inlineStr">
         <is>
@@ -5524,17 +5395,17 @@
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B249" s="3" t="n">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="C249" s="4" t="n">
-        <v>0.30625</v>
+        <v>0.2958333333333333</v>
       </c>
       <c r="D249" s="4" t="n">
-        <v>0.6736111111111112</v>
+        <v>0.7215277777777778</v>
       </c>
       <c r="E249" s="2" t="inlineStr">
         <is>
@@ -5545,84 +5416,84 @@
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B250" s="3" t="n">
-        <v>46261</v>
-      </c>
-      <c r="C250" s="4" t="n">
-        <v>0.2791666666666667</v>
+        <v>46265</v>
+      </c>
+      <c r="C250" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D250" s="4" t="n">
-        <v>0.6916666666666667</v>
+        <v>0.7097222222222223</v>
       </c>
       <c r="E250" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B251" s="3" t="n">
-        <v>46260</v>
-      </c>
-      <c r="C251" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D251" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E251" s="2" t="inlineStr">
-        <is>
-          <t>PLEASE VERIFY: check-in/out times not captured (gap between source photos)</t>
+          <t>single punch only</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B252" s="3" t="n">
+        <v>46235</v>
+      </c>
+      <c r="C252" s="4" t="n">
+        <v>0.3305555555555555</v>
+      </c>
+      <c r="D252" s="4" t="n">
+        <v>0.7347222222222223</v>
+      </c>
+      <c r="E252" s="2" t="inlineStr">
+        <is>
+          <t>last day of month; final record</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B253" s="3" t="n">
-        <v>46265</v>
-      </c>
-      <c r="C253" s="4" t="n">
-        <v>0.2451388888888889</v>
+        <v>46236</v>
+      </c>
+      <c r="C253" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D253" s="4" t="n">
-        <v>0.7375</v>
+        <v>0.3583333333333333</v>
       </c>
       <c r="E253" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B254" s="3" t="n">
-        <v>46264</v>
+        <v>46237</v>
       </c>
       <c r="C254" s="4" t="n">
-        <v>0.25</v>
+        <v>0.3291666666666667</v>
       </c>
       <c r="D254" s="4" t="n">
-        <v>0.6888888888888889</v>
+        <v>0.7111111111111111</v>
       </c>
       <c r="E254" s="2" t="inlineStr">
         <is>
@@ -5633,17 +5504,17 @@
     <row r="255">
       <c r="A255" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B255" s="3" t="n">
-        <v>46263</v>
+        <v>46238</v>
       </c>
       <c r="C255" s="4" t="n">
-        <v>0.2465277777777778</v>
+        <v>0.3305555555555555</v>
       </c>
       <c r="D255" s="4" t="n">
-        <v>0.7083333333333334</v>
+        <v>0.7263888888888889</v>
       </c>
       <c r="E255" s="2" t="inlineStr">
         <is>
@@ -5654,86 +5525,103 @@
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B256" s="3" t="n">
-        <v>46261</v>
-      </c>
-      <c r="C256" s="4" t="n">
-        <v>0.2569444444444444</v>
+        <v>46239</v>
+      </c>
+      <c r="C256" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D256" s="4" t="n">
-        <v>0.6986111111111111</v>
+        <v>0.7715277777777778</v>
       </c>
       <c r="E256" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B257" s="3" t="n">
-        <v>46260</v>
-      </c>
-      <c r="C257" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D257" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>46240</v>
+      </c>
+      <c r="C257" s="4" t="n">
+        <v>0.3986111111111111</v>
+      </c>
+      <c r="D257" s="4" t="n">
+        <v>0.7277777777777777</v>
       </c>
       <c r="E257" s="2" t="inlineStr">
         <is>
-          <t>PLEASE VERIFY: check-in/out times not captured (gap between source photos)</t>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B258" s="3" t="n">
+        <v>46242</v>
+      </c>
+      <c r="C258" s="4" t="n">
+        <v>0.2791666666666667</v>
+      </c>
+      <c r="D258" s="4" t="n">
+        <v>0.7284722222222222</v>
+      </c>
+      <c r="E258" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B259" s="3" t="n">
-        <v>46263</v>
+        <v>46243</v>
       </c>
       <c r="C259" s="4" t="n">
-        <v>0.2986111111111111</v>
-      </c>
-      <c r="D259" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.2784722222222222</v>
+      </c>
+      <c r="D259" s="4" t="n">
+        <v>0.7555555555555555</v>
       </c>
       <c r="E259" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B260" s="3" t="n">
-        <v>46261</v>
+        <v>46244</v>
       </c>
       <c r="C260" s="4" t="n">
-        <v>0.3375</v>
+        <v>0.2875</v>
       </c>
       <c r="D260" s="4" t="n">
-        <v>0.8090277777777778</v>
+        <v>0.7479166666666667</v>
       </c>
       <c r="E260" s="2" t="inlineStr">
         <is>
@@ -5744,17 +5632,17 @@
     <row r="261">
       <c r="A261" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B261" s="3" t="n">
-        <v>46260</v>
+        <v>46245</v>
       </c>
       <c r="C261" s="4" t="n">
-        <v>0.3854166666666667</v>
+        <v>0.3</v>
       </c>
       <c r="D261" s="4" t="n">
-        <v>0.8083333333333333</v>
+        <v>0.7465277777777778</v>
       </c>
       <c r="E261" s="2" t="inlineStr">
         <is>
@@ -5765,59 +5653,80 @@
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B262" s="3" t="n">
-        <v>46259</v>
+        <v>46246</v>
       </c>
       <c r="C262" s="4" t="n">
-        <v>0.2673611111111111</v>
+        <v>0.2548611111111111</v>
       </c>
       <c r="D262" s="4" t="n">
-        <v>0.7506944444444444</v>
+        <v>0.7222222222222222</v>
       </c>
       <c r="E262" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>extra punches: 07:44 06:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B263" s="3" t="n">
+        <v>46247</v>
+      </c>
+      <c r="C263" s="4" t="n">
+        <v>0.3388888888888889</v>
+      </c>
+      <c r="D263" s="4" t="n">
+        <v>0.7236111111111111</v>
+      </c>
+      <c r="E263" s="2" t="inlineStr">
+        <is>
+          <t>extra punch: 17:21</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B264" s="3" t="n">
-        <v>46265</v>
+        <v>46249</v>
       </c>
       <c r="C264" s="4" t="n">
-        <v>0.2472222222222222</v>
+        <v>0.2423611111111111</v>
       </c>
       <c r="D264" s="4" t="n">
-        <v>0.7555555555555555</v>
+        <v>0.7270833333333333</v>
       </c>
       <c r="E264" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>extra punches: 17:27 07:28</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B265" s="3" t="n">
-        <v>46264</v>
+        <v>46250</v>
       </c>
       <c r="C265" s="4" t="n">
-        <v>0.30625</v>
+        <v>0.3409722222222222</v>
       </c>
       <c r="D265" s="4" t="n">
-        <v>0.6805555555555556</v>
+        <v>0.7104166666666667</v>
       </c>
       <c r="E265" s="2" t="inlineStr">
         <is>
@@ -5828,17 +5737,17 @@
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B266" s="3" t="n">
-        <v>46263</v>
+        <v>46251</v>
       </c>
       <c r="C266" s="4" t="n">
-        <v>0.2993055555555555</v>
+        <v>0.2833333333333333</v>
       </c>
       <c r="D266" s="4" t="n">
-        <v>0.7708333333333334</v>
+        <v>0.7326388888888888</v>
       </c>
       <c r="E266" s="2" t="inlineStr">
         <is>
@@ -5849,17 +5758,17 @@
     <row r="267">
       <c r="A267" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B267" s="3" t="n">
-        <v>46261</v>
+        <v>46252</v>
       </c>
       <c r="C267" s="4" t="n">
-        <v>0.2826388888888889</v>
+        <v>0.28125</v>
       </c>
       <c r="D267" s="4" t="n">
-        <v>0.7861111111111111</v>
+        <v>0.7645833333333333</v>
       </c>
       <c r="E267" s="2" t="inlineStr">
         <is>
@@ -5870,80 +5779,99 @@
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B268" s="3" t="n">
-        <v>46260</v>
-      </c>
-      <c r="C268" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D268" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>46253</v>
+      </c>
+      <c r="C268" s="4" t="n">
+        <v>0.3166666666666667</v>
+      </c>
+      <c r="D268" s="4" t="n">
+        <v>0.74375</v>
       </c>
       <c r="E268" s="2" t="inlineStr">
         <is>
-          <t>PLEASE VERIFY: check-in/out times not captured (gap between source photos)</t>
+          <t>extra punch: 08:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B269" s="3" t="n">
+        <v>46254</v>
+      </c>
+      <c r="C269" s="4" t="n">
+        <v>0.2868055555555555</v>
+      </c>
+      <c r="D269" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E269" s="2" t="inlineStr">
+        <is>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B270" s="3" t="n">
-        <v>46265</v>
-      </c>
-      <c r="C270" s="4" t="n">
-        <v>0.2805555555555556</v>
+        <v>46256</v>
+      </c>
+      <c r="C270" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D270" s="4" t="n">
-        <v>0.7534722222222222</v>
+        <v>0.74375</v>
       </c>
       <c r="E270" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B271" s="3" t="n">
-        <v>46263</v>
-      </c>
-      <c r="C271" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>46257</v>
+      </c>
+      <c r="C271" s="4" t="n">
+        <v>0.2548611111111111</v>
       </c>
       <c r="D271" s="4" t="n">
-        <v>0.4041666666666667</v>
+        <v>0.7569444444444444</v>
       </c>
       <c r="E271" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B272" s="3" t="n">
-        <v>46261</v>
+        <v>46258</v>
       </c>
       <c r="C272" s="2" t="inlineStr">
         <is>
@@ -5951,7 +5879,7 @@
         </is>
       </c>
       <c r="D272" s="4" t="n">
-        <v>0.7395833333333334</v>
+        <v>0.7506944444444444</v>
       </c>
       <c r="E272" s="2" t="inlineStr">
         <is>
@@ -5962,86 +5890,105 @@
     <row r="273">
       <c r="A273" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B273" s="3" t="n">
         <v>46259</v>
       </c>
-      <c r="C273" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C273" s="4" t="n">
+        <v>0.2868055555555555</v>
       </c>
       <c r="D273" s="4" t="n">
-        <v>0.75</v>
+        <v>0.6895833333333333</v>
       </c>
       <c r="E273" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B274" s="3" t="n">
-        <v>46258</v>
+        <v>46260</v>
       </c>
       <c r="C274" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D274" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D274" s="4" t="n">
+        <v>0.6986111111111111</v>
       </c>
       <c r="E274" s="2" t="inlineStr">
         <is>
-          <t>PLEASE VERIFY: check-in/out time not captured (gap between source photos)</t>
+          <t>single punch only</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B275" s="3" t="n">
+        <v>46261</v>
+      </c>
+      <c r="C275" s="4" t="n">
+        <v>0.2833333333333333</v>
+      </c>
+      <c r="D275" s="4" t="n">
+        <v>0.8645833333333334</v>
+      </c>
+      <c r="E275" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B276" s="3" t="n">
-        <v>46265</v>
-      </c>
-      <c r="C276" s="4" t="n">
-        <v>0.3319444444444444</v>
+        <v>46263</v>
+      </c>
+      <c r="C276" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D276" s="4" t="n">
-        <v>0.7680555555555556</v>
+        <v>0.7291666666666666</v>
       </c>
       <c r="E276" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B277" s="3" t="n">
         <v>46264</v>
       </c>
       <c r="C277" s="4" t="n">
-        <v>0.3534722222222222</v>
+        <v>0.2798611111111111</v>
       </c>
       <c r="D277" s="4" t="n">
-        <v>0.7534722222222222</v>
+        <v>0.7472222222222222</v>
       </c>
       <c r="E277" s="2" t="inlineStr">
         <is>
@@ -6052,105 +5999,101 @@
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B278" s="3" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="C278" s="4" t="n">
-        <v>0.3652777777777778</v>
+        <v>0.3888888888888889</v>
       </c>
       <c r="D278" s="4" t="n">
-        <v>0.7569444444444444</v>
+        <v>0.7215277777777778</v>
       </c>
       <c r="E278" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="279">
-      <c r="A279" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="B279" s="3" t="n">
-        <v>46261</v>
-      </c>
-      <c r="C279" s="4" t="n">
-        <v>0.3652777777777778</v>
-      </c>
-      <c r="D279" s="4" t="n">
-        <v>0.7395833333333334</v>
-      </c>
-      <c r="E279" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>corrected from a clearer re-scan photo later in the album</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B280" s="3" t="n">
-        <v>46260</v>
-      </c>
-      <c r="C280" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D280" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>46235</v>
+      </c>
+      <c r="C280" s="4" t="n">
+        <v>0.2569444444444444</v>
+      </c>
+      <c r="D280" s="4" t="n">
+        <v>0.7430555555555556</v>
       </c>
       <c r="E280" s="2" t="inlineStr">
         <is>
-          <t>PLEASE VERIFY: check-in/out times not captured (gap between source photos)</t>
+          <t>extra punch: 17:55; last day of month; final record</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B281" s="3" t="n">
+        <v>46236</v>
+      </c>
+      <c r="C281" s="4" t="n">
+        <v>0.2201388888888889</v>
+      </c>
+      <c r="D281" s="4" t="n">
+        <v>0.7381944444444445</v>
+      </c>
+      <c r="E281" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B282" s="3" t="n">
-        <v>46265</v>
+        <v>46237</v>
       </c>
       <c r="C282" s="4" t="n">
-        <v>0.2631944444444445</v>
+        <v>0.2472222222222222</v>
       </c>
       <c r="D282" s="4" t="n">
-        <v>0.7555555555555555</v>
+        <v>0.7402777777777778</v>
       </c>
       <c r="E282" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>extra punch: 17:46</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B283" s="3" t="n">
-        <v>46264</v>
+        <v>46238</v>
       </c>
       <c r="C283" s="4" t="n">
-        <v>0.3194444444444444</v>
+        <v>0.2173611111111111</v>
       </c>
       <c r="D283" s="4" t="n">
-        <v>0.7493055555555556</v>
+        <v>0.7604166666666666</v>
       </c>
       <c r="E283" s="2" t="inlineStr">
         <is>
@@ -6161,38 +6104,38 @@
     <row r="284">
       <c r="A284" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B284" s="3" t="n">
-        <v>46263</v>
+        <v>46239</v>
       </c>
       <c r="C284" s="4" t="n">
-        <v>0.275</v>
+        <v>0.2333333333333333</v>
       </c>
       <c r="D284" s="4" t="n">
-        <v>0.7513888888888889</v>
+        <v>0.7611111111111111</v>
       </c>
       <c r="E284" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>extra punch: 18:16</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B285" s="3" t="n">
-        <v>46261</v>
+        <v>46240</v>
       </c>
       <c r="C285" s="4" t="n">
-        <v>0.2909722222222222</v>
+        <v>0.2277777777777778</v>
       </c>
       <c r="D285" s="4" t="n">
-        <v>0.7430555555555556</v>
+        <v>0.75625</v>
       </c>
       <c r="E285" s="2" t="inlineStr">
         <is>
@@ -6203,42 +6146,59 @@
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B286" s="3" t="n">
-        <v>46260</v>
-      </c>
-      <c r="C286" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D286" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>46242</v>
+      </c>
+      <c r="C286" s="4" t="n">
+        <v>0.2479166666666667</v>
+      </c>
+      <c r="D286" s="4" t="n">
+        <v>0.7291666666666666</v>
       </c>
       <c r="E286" s="2" t="inlineStr">
         <is>
-          <t>PLEASE VERIFY: check-in/out times not captured (gap between source photos)</t>
+          <t>extra punch: 07:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B287" s="3" t="n">
+        <v>46243</v>
+      </c>
+      <c r="C287" s="4" t="n">
+        <v>0.2368055555555555</v>
+      </c>
+      <c r="D287" s="4" t="n">
+        <v>0.6729166666666667</v>
+      </c>
+      <c r="E287" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B288" s="3" t="n">
-        <v>46264</v>
+        <v>46244</v>
       </c>
       <c r="C288" s="4" t="n">
-        <v>0.3208333333333334</v>
+        <v>0.2534722222222222</v>
       </c>
       <c r="D288" s="4" t="n">
-        <v>0.7354166666666667</v>
+        <v>0.7479166666666667</v>
       </c>
       <c r="E288" s="2" t="inlineStr">
         <is>
@@ -6249,38 +6209,38 @@
     <row r="289">
       <c r="A289" s="2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B289" s="3" t="n">
-        <v>46263</v>
+        <v>46245</v>
       </c>
       <c r="C289" s="4" t="n">
-        <v>0.3347222222222222</v>
+        <v>0.2541666666666667</v>
       </c>
       <c r="D289" s="4" t="n">
-        <v>0.8895833333333333</v>
+        <v>0.7465277777777778</v>
       </c>
       <c r="E289" s="2" t="inlineStr">
         <is>
-          <t>extra punch: 08:02</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B290" s="3" t="n">
-        <v>46261</v>
+        <v>46246</v>
       </c>
       <c r="C290" s="4" t="n">
-        <v>0.2798611111111111</v>
+        <v>0.2618055555555556</v>
       </c>
       <c r="D290" s="4" t="n">
-        <v>0.7493055555555556</v>
+        <v>0.75</v>
       </c>
       <c r="E290" s="2" t="inlineStr">
         <is>
@@ -6291,59 +6251,80 @@
     <row r="291">
       <c r="A291" s="2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B291" s="3" t="n">
-        <v>46260</v>
+        <v>46247</v>
       </c>
       <c r="C291" s="4" t="n">
-        <v>0.3055555555555556</v>
+        <v>0.25625</v>
       </c>
       <c r="D291" s="4" t="n">
-        <v>0.8013888888888889</v>
+        <v>0.75</v>
       </c>
       <c r="E291" s="2" t="inlineStr">
         <is>
           <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B292" s="3" t="n">
+        <v>46249</v>
+      </c>
+      <c r="C292" s="4" t="n">
+        <v>0.2333333333333333</v>
+      </c>
+      <c r="D292" s="4" t="n">
+        <v>0.7506944444444444</v>
+      </c>
+      <c r="E292" s="2" t="inlineStr">
+        <is>
+          <t>extra punch: 06:05</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="2" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B293" s="3" t="n">
-        <v>46265</v>
+        <v>46250</v>
       </c>
       <c r="C293" s="4" t="n">
-        <v>0.1479166666666667</v>
+        <v>0.25625</v>
       </c>
       <c r="D293" s="4" t="n">
-        <v>0.9326388888888889</v>
+        <v>0.7458333333333333</v>
       </c>
       <c r="E293" s="2" t="inlineStr">
         <is>
-          <t>extra punch: 22:23</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="2" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B294" s="3" t="n">
-        <v>46264</v>
+        <v>46251</v>
       </c>
       <c r="C294" s="4" t="n">
-        <v>0.14375</v>
+        <v>0.2541666666666667</v>
       </c>
       <c r="D294" s="4" t="n">
-        <v>0.75625</v>
+        <v>0.7555555555555555</v>
       </c>
       <c r="E294" s="2" t="inlineStr">
         <is>
@@ -6354,17 +6335,17 @@
     <row r="295">
       <c r="A295" s="2" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B295" s="3" t="n">
-        <v>46263</v>
+        <v>46252</v>
       </c>
       <c r="C295" s="4" t="n">
-        <v>0.1451388888888889</v>
+        <v>0.2395833333333333</v>
       </c>
       <c r="D295" s="4" t="n">
-        <v>0.7479166666666667</v>
+        <v>0.7611111111111111</v>
       </c>
       <c r="E295" s="2" t="inlineStr">
         <is>
@@ -6375,19 +6356,40 @@
     <row r="296">
       <c r="A296" s="2" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B296" s="3" t="n">
-        <v>46262</v>
+        <v>46253</v>
       </c>
       <c r="C296" s="4" t="n">
-        <v>0.1493055555555556</v>
+        <v>0.2527777777777778</v>
       </c>
       <c r="D296" s="4" t="n">
-        <v>0.7159722222222222</v>
+        <v>0.7423611111111111</v>
       </c>
       <c r="E296" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B297" s="3" t="n">
+        <v>46254</v>
+      </c>
+      <c r="C297" s="4" t="n">
+        <v>0.2583333333333334</v>
+      </c>
+      <c r="D297" s="4" t="n">
+        <v>0.7451388888888889</v>
+      </c>
+      <c r="E297" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -6396,38 +6398,38 @@
     <row r="298">
       <c r="A298" s="2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B298" s="3" t="n">
-        <v>46265</v>
+        <v>46256</v>
       </c>
       <c r="C298" s="4" t="n">
-        <v>0.1868055555555556</v>
+        <v>0.2402777777777778</v>
       </c>
       <c r="D298" s="4" t="n">
-        <v>0.4131944444444444</v>
+        <v>0.74375</v>
       </c>
       <c r="E298" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>extra punches: 17:51 06:13</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B299" s="3" t="n">
-        <v>46264</v>
+        <v>46257</v>
       </c>
       <c r="C299" s="4" t="n">
-        <v>0.1847222222222222</v>
+        <v>0.2402777777777778</v>
       </c>
       <c r="D299" s="4" t="n">
-        <v>0.5097222222222222</v>
+        <v>0.75</v>
       </c>
       <c r="E299" s="2" t="inlineStr">
         <is>
@@ -6438,40 +6440,61 @@
     <row r="300">
       <c r="A300" s="2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B300" s="3" t="n">
-        <v>46263</v>
+        <v>46258</v>
       </c>
       <c r="C300" s="4" t="n">
-        <v>0.1847222222222222</v>
+        <v>0.2319444444444445</v>
       </c>
       <c r="D300" s="4" t="n">
-        <v>0.4527777777777778</v>
+        <v>0.7513888888888889</v>
       </c>
       <c r="E300" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>extra punch: 18:02</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B301" s="3" t="n">
-        <v>46262</v>
+        <v>46259</v>
       </c>
       <c r="C301" s="4" t="n">
-        <v>0.1881944444444444</v>
+        <v>0.3555555555555556</v>
       </c>
       <c r="D301" s="4" t="n">
-        <v>0.4055555555555556</v>
+        <v>0.7541666666666667</v>
       </c>
       <c r="E301" s="2" t="inlineStr">
+        <is>
+          <t>extra punch: 06:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B302" s="3" t="n">
+        <v>46260</v>
+      </c>
+      <c r="C302" s="4" t="n">
+        <v>0.2555555555555555</v>
+      </c>
+      <c r="D302" s="4" t="n">
+        <v>0.7541666666666667</v>
+      </c>
+      <c r="E302" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -6480,17 +6503,17 @@
     <row r="303">
       <c r="A303" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B303" s="3" t="n">
-        <v>46265</v>
+        <v>46261</v>
       </c>
       <c r="C303" s="4" t="n">
-        <v>0.2909722222222222</v>
+        <v>0.2722222222222222</v>
       </c>
       <c r="D303" s="4" t="n">
-        <v>0.75</v>
+        <v>0.7569444444444444</v>
       </c>
       <c r="E303" s="2" t="inlineStr">
         <is>
@@ -6501,17 +6524,17 @@
     <row r="304">
       <c r="A304" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B304" s="3" t="n">
-        <v>46264</v>
+        <v>46263</v>
       </c>
       <c r="C304" s="4" t="n">
-        <v>0.2888888888888889</v>
+        <v>0.2201388888888889</v>
       </c>
       <c r="D304" s="4" t="n">
-        <v>0.75</v>
+        <v>0.7444444444444445</v>
       </c>
       <c r="E304" s="2" t="inlineStr">
         <is>
@@ -6522,17 +6545,17 @@
     <row r="305">
       <c r="A305" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B305" s="3" t="n">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="C305" s="4" t="n">
-        <v>0.2965277777777778</v>
+        <v>0.2555555555555555</v>
       </c>
       <c r="D305" s="4" t="n">
-        <v>0.7472222222222222</v>
+        <v>0.7458333333333333</v>
       </c>
       <c r="E305" s="2" t="inlineStr">
         <is>
@@ -6543,44 +6566,21 @@
     <row r="306">
       <c r="A306" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B306" s="3" t="n">
-        <v>46261</v>
+        <v>46265</v>
       </c>
       <c r="C306" s="4" t="n">
-        <v>0.24375</v>
+        <v>0.2569444444444444</v>
       </c>
       <c r="D306" s="4" t="n">
-        <v>0.6763888888888889</v>
+        <v>0.7527777777777778</v>
       </c>
       <c r="E306" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="308">
-      <c r="A308" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="B308" s="3" t="n">
-        <v>46265</v>
-      </c>
-      <c r="C308" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D308" s="4" t="n">
-        <v>0.7097222222222223</v>
-      </c>
-      <c r="E308" s="2" t="inlineStr">
-        <is>
-          <t>single punch only</t>
+          <t>corrected from a clearer re-scan photo later in the album</t>
         </is>
       </c>
     </row>

--- a/output/timesheet.xlsx
+++ b/output/timesheet.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E306"/>
+  <dimension ref="A1:E371"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -480,21 +480,17 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>46260</v>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>46235</v>
+      </c>
+      <c r="C2" s="4" t="n">
+        <v>0.2986111111111111</v>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>0.7152777777777778</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>PLEASE VERIFY: check-in/out times not captured (gap between source photos)</t>
+          <t>last day of month; final record</t>
         </is>
       </c>
     </row>
@@ -505,13 +501,13 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>46261</v>
+        <v>46236</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>0.2791666666666667</v>
+        <v>0.275</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>0.6916666666666667</v>
+        <v>0.7423611111111111</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
@@ -526,13 +522,13 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>46263</v>
+        <v>46237</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>0.30625</v>
+        <v>0.3041666666666666</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>0.6736111111111112</v>
+        <v>0.7125</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
@@ -547,17 +543,19 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>46264</v>
+        <v>46238</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>0.3006944444444444</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>0.7458333333333333</v>
+        <v>0.3027777777777778</v>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
@@ -568,15 +566,36 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>46265</v>
+        <v>46239</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0.2493055555555556</v>
+        <v>0.3020833333333333</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.7527777777777778</v>
+        <v>0.6958333333333333</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>46240</v>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>0.31875</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>0.8208333333333333</v>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -585,42 +604,38 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>46260</v>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>46242</v>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>0.3118055555555556</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>0.6965277777777777</v>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>PLEASE VERIFY: check-in/out times not captured (gap between source photos)</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>46261</v>
+        <v>46243</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0.2569444444444444</v>
+        <v>0.3395833333333333</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.6986111111111111</v>
+        <v>0.68125</v>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
@@ -631,17 +646,17 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>46263</v>
+        <v>46244</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.2465277777777778</v>
+        <v>0.2888888888888889</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.7083333333333334</v>
+        <v>0.7263888888888889</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
@@ -652,17 +667,17 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>46264</v>
+        <v>46245</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.25</v>
+        <v>0.3048611111111111</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.6888888888888889</v>
+        <v>0.74375</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
@@ -673,19 +688,40 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>46265</v>
+        <v>46246</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.2451388888888889</v>
+        <v>0.3020833333333333</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.7375</v>
+        <v>0.7833333333333333</v>
       </c>
       <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>46247</v>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>0.3291666666666667</v>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>0.6916666666666667</v>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -694,17 +730,17 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>46259</v>
+        <v>46249</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.2673611111111111</v>
+        <v>0.3138888888888889</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.7506944444444444</v>
+        <v>0.7055555555555556</v>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
@@ -715,17 +751,17 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>46260</v>
+        <v>46250</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.3854166666666667</v>
+        <v>0.3493055555555555</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.8083333333333333</v>
+        <v>0.7263888888888889</v>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
@@ -736,17 +772,17 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>46261</v>
+        <v>46251</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.3375</v>
+        <v>0.3145833333333333</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.8090277777777778</v>
+        <v>0.6951388888888889</v>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
@@ -757,21 +793,42 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>46263</v>
+        <v>46252</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.2986111111111111</v>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.2881944444444444</v>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>0.7590277777777777</v>
       </c>
       <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>46253</v>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>0.3020833333333333</v>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>single punch only</t>
         </is>
@@ -780,16 +837,14 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>46260</v>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>46254</v>
+      </c>
+      <c r="C19" s="4" t="n">
+        <v>0.29375</v>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
@@ -798,24 +853,24 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>PLEASE VERIFY: check-in/out times not captured (gap between source photos)</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>46261</v>
+        <v>46256</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.2826388888888889</v>
+        <v>0.2909722222222222</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.7861111111111111</v>
+        <v>0.6965277777777777</v>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
@@ -826,17 +881,17 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>46263</v>
+        <v>46257</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.2993055555555555</v>
+        <v>0.2486111111111111</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.7708333333333334</v>
+        <v>0.6965277777777777</v>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
@@ -847,17 +902,17 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>46264</v>
+        <v>46258</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0.30625</v>
+        <v>0.2993055555555555</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.6805555555555556</v>
+        <v>0.70625</v>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
@@ -868,19 +923,40 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>46265</v>
+        <v>46259</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.2472222222222222</v>
+        <v>0.2722222222222222</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.7555555555555555</v>
+        <v>0.6895833333333333</v>
       </c>
       <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>46260</v>
+      </c>
+      <c r="C24" s="4" t="n">
+        <v>0.3381944444444445</v>
+      </c>
+      <c r="D24" s="4" t="n">
+        <v>0.6944444444444444</v>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -889,157 +965,147 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>46258</v>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>46261</v>
+      </c>
+      <c r="C25" s="4" t="n">
+        <v>0.2791666666666667</v>
+      </c>
+      <c r="D25" s="4" t="n">
+        <v>0.6916666666666667</v>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>PLEASE VERIFY: check-in/out time not captured (gap between source photos)</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>46259</v>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>46263</v>
+      </c>
+      <c r="C26" s="4" t="n">
+        <v>0.30625</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>0.75</v>
+        <v>0.6736111111111112</v>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>46261</v>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>46264</v>
+      </c>
+      <c r="C27" s="4" t="n">
+        <v>0.3006944444444444</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>0.7395833333333334</v>
+        <v>0.7458333333333333</v>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>46263</v>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>46265</v>
+      </c>
+      <c r="C28" s="4" t="n">
+        <v>0.2493055555555556</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>0.4041666666666667</v>
+        <v>0.7527777777777778</v>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="n">
-        <v>46265</v>
-      </c>
-      <c r="C29" s="4" t="n">
-        <v>0.2805555555555556</v>
-      </c>
-      <c r="D29" s="4" t="n">
-        <v>0.7534722222222222</v>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>46235</v>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>PLEASE VERIFY: check-in/out times not captured; last day of month</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>46260</v>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>46236</v>
+      </c>
+      <c r="C31" s="4" t="n">
+        <v>0.2569444444444444</v>
+      </c>
+      <c r="D31" s="4" t="n">
+        <v>0.74375</v>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>PLEASE VERIFY: check-in/out times not captured (gap between source photos)</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>46261</v>
+        <v>46237</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0.3652777777777778</v>
+        <v>0.2430555555555556</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>0.7395833333333334</v>
+        <v>0.7208333333333333</v>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
@@ -1050,17 +1116,17 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B33" s="3" t="n">
-        <v>46263</v>
+        <v>46238</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.3652777777777778</v>
+        <v>0.24375</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.7569444444444444</v>
+        <v>0.75625</v>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
@@ -1071,84 +1137,103 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>46264</v>
+        <v>46239</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.3534722222222222</v>
-      </c>
-      <c r="D34" s="4" t="n">
-        <v>0.7534722222222222</v>
+        <v>0.2444444444444444</v>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B35" s="3" t="n">
-        <v>46265</v>
+        <v>46240</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>0.3319444444444444</v>
+        <v>0.2444444444444444</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>0.7680555555555556</v>
+        <v>0.7291666666666666</v>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
           <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>46242</v>
+      </c>
+      <c r="C36" s="4" t="n">
+        <v>0.24375</v>
+      </c>
+      <c r="D36" s="4" t="n">
+        <v>0.6722222222222223</v>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>extra punch: 18:02</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B37" s="3" t="n">
-        <v>46260</v>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>46243</v>
+      </c>
+      <c r="C37" s="4" t="n">
+        <v>0.2631944444444445</v>
+      </c>
+      <c r="D37" s="4" t="n">
+        <v>0.7222222222222222</v>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>PLEASE VERIFY: check-in/out times not captured (gap between source photos)</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B38" s="3" t="n">
-        <v>46261</v>
+        <v>46244</v>
       </c>
       <c r="C38" s="4" t="n">
-        <v>0.2909722222222222</v>
+        <v>0.2381944444444444</v>
       </c>
       <c r="D38" s="4" t="n">
-        <v>0.7430555555555556</v>
+        <v>0.8118055555555556</v>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
@@ -1159,38 +1244,38 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B39" s="3" t="n">
-        <v>46263</v>
+        <v>46245</v>
       </c>
       <c r="C39" s="4" t="n">
-        <v>0.275</v>
+        <v>0.2631944444444445</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>0.7513888888888889</v>
+        <v>0.74375</v>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>extra punch: 06:34</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>46264</v>
+        <v>46246</v>
       </c>
       <c r="C40" s="4" t="n">
-        <v>0.3194444444444444</v>
+        <v>0.2638888888888889</v>
       </c>
       <c r="D40" s="4" t="n">
-        <v>0.7493055555555556</v>
+        <v>0.7270833333333333</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
@@ -1201,19 +1286,40 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>46265</v>
+        <v>46247</v>
       </c>
       <c r="C41" s="4" t="n">
-        <v>0.2631944444444445</v>
+        <v>0.2604166666666667</v>
       </c>
       <c r="D41" s="4" t="n">
-        <v>0.7555555555555555</v>
+        <v>0.7291666666666666</v>
       </c>
       <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v>46249</v>
+      </c>
+      <c r="C42" s="4" t="n">
+        <v>0.2430555555555556</v>
+      </c>
+      <c r="D42" s="4" t="n">
+        <v>0.7354166666666667</v>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1222,17 +1328,17 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B43" s="3" t="n">
-        <v>46260</v>
+        <v>46250</v>
       </c>
       <c r="C43" s="4" t="n">
-        <v>0.3055555555555556</v>
+        <v>0.2583333333333334</v>
       </c>
       <c r="D43" s="4" t="n">
-        <v>0.8013888888888889</v>
+        <v>0.7402777777777778</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
@@ -1243,17 +1349,17 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B44" s="3" t="n">
-        <v>46261</v>
+        <v>46251</v>
       </c>
       <c r="C44" s="4" t="n">
-        <v>0.2798611111111111</v>
+        <v>0.2569444444444444</v>
       </c>
       <c r="D44" s="4" t="n">
-        <v>0.7493055555555556</v>
+        <v>0.7597222222222222</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
@@ -1264,40 +1370,61 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B45" s="3" t="n">
-        <v>46263</v>
+        <v>46252</v>
       </c>
       <c r="C45" s="4" t="n">
-        <v>0.3347222222222222</v>
+        <v>0.2423611111111111</v>
       </c>
       <c r="D45" s="4" t="n">
-        <v>0.8895833333333333</v>
+        <v>0.6951388888888889</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>extra punch: 08:02</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B46" s="3" t="n">
-        <v>46264</v>
+        <v>46253</v>
       </c>
       <c r="C46" s="4" t="n">
-        <v>0.3208333333333334</v>
+        <v>0.2555555555555555</v>
       </c>
       <c r="D46" s="4" t="n">
-        <v>0.7354166666666667</v>
+        <v>0.7263888888888889</v>
       </c>
       <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="n">
+        <v>46254</v>
+      </c>
+      <c r="C47" s="4" t="n">
+        <v>0.2569444444444444</v>
+      </c>
+      <c r="D47" s="4" t="n">
+        <v>0.8111111111111111</v>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1306,17 +1433,17 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>46262</v>
+        <v>46256</v>
       </c>
       <c r="C48" s="4" t="n">
-        <v>0.1493055555555556</v>
+        <v>0.2402777777777778</v>
       </c>
       <c r="D48" s="4" t="n">
-        <v>0.7159722222222222</v>
+        <v>0.7097222222222223</v>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
@@ -1327,17 +1454,17 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B49" s="3" t="n">
-        <v>46263</v>
+        <v>46257</v>
       </c>
       <c r="C49" s="4" t="n">
-        <v>0.1451388888888889</v>
+        <v>0.2506944444444444</v>
       </c>
       <c r="D49" s="4" t="n">
-        <v>0.7479166666666667</v>
+        <v>0.7270833333333333</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -1348,17 +1475,17 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B50" s="3" t="n">
-        <v>46264</v>
+        <v>46258</v>
       </c>
       <c r="C50" s="4" t="n">
-        <v>0.14375</v>
+        <v>0.2638888888888889</v>
       </c>
       <c r="D50" s="4" t="n">
-        <v>0.75625</v>
+        <v>0.6979166666666666</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -1369,38 +1496,59 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B51" s="3" t="n">
-        <v>46265</v>
+        <v>46259</v>
       </c>
       <c r="C51" s="4" t="n">
-        <v>0.1479166666666667</v>
+        <v>0.2631944444444445</v>
       </c>
       <c r="D51" s="4" t="n">
-        <v>0.9326388888888889</v>
+        <v>0.6895833333333333</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>extra punch: 22:23</t>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="n">
+        <v>46260</v>
+      </c>
+      <c r="C52" s="4" t="n">
+        <v>0.2534722222222222</v>
+      </c>
+      <c r="D52" s="4" t="n">
+        <v>0.7361111111111112</v>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B53" s="3" t="n">
-        <v>46262</v>
+        <v>46261</v>
       </c>
       <c r="C53" s="4" t="n">
-        <v>0.1881944444444444</v>
+        <v>0.2569444444444444</v>
       </c>
       <c r="D53" s="4" t="n">
-        <v>0.4055555555555556</v>
+        <v>0.6986111111111111</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -1411,17 +1559,17 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B54" s="3" t="n">
         <v>46263</v>
       </c>
       <c r="C54" s="4" t="n">
-        <v>0.1847222222222222</v>
+        <v>0.2465277777777778</v>
       </c>
       <c r="D54" s="4" t="n">
-        <v>0.4527777777777778</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -1432,17 +1580,17 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B55" s="3" t="n">
         <v>46264</v>
       </c>
       <c r="C55" s="4" t="n">
-        <v>0.1847222222222222</v>
+        <v>0.25</v>
       </c>
       <c r="D55" s="4" t="n">
-        <v>0.5097222222222222</v>
+        <v>0.6888888888888889</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -1453,17 +1601,17 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B56" s="3" t="n">
         <v>46265</v>
       </c>
       <c r="C56" s="4" t="n">
-        <v>0.1868055555555556</v>
+        <v>0.2451388888888889</v>
       </c>
       <c r="D56" s="4" t="n">
-        <v>0.4131944444444444</v>
+        <v>0.7375</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
@@ -1474,38 +1622,38 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B58" s="3" t="n">
         <v>46235</v>
       </c>
       <c r="C58" s="4" t="n">
-        <v>0.2368055555555555</v>
+        <v>0.2972222222222222</v>
       </c>
       <c r="D58" s="4" t="n">
-        <v>0.7430555555555556</v>
+        <v>0.7770833333333333</v>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>last day of month; final record</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B59" s="3" t="n">
         <v>46236</v>
       </c>
       <c r="C59" s="4" t="n">
-        <v>0.2604166666666667</v>
+        <v>0.2736111111111111</v>
       </c>
       <c r="D59" s="4" t="n">
-        <v>0.7534722222222222</v>
+        <v>0.75625</v>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
@@ -1516,17 +1664,17 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B60" s="3" t="n">
         <v>46237</v>
       </c>
       <c r="C60" s="4" t="n">
-        <v>0.3097222222222222</v>
+        <v>0.2881944444444444</v>
       </c>
       <c r="D60" s="4" t="n">
-        <v>0.7444444444444445</v>
+        <v>0.7375</v>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
@@ -1537,37 +1685,35 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B61" s="3" t="n">
         <v>46238</v>
       </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C61" s="4" t="n">
+        <v>0.2777777777777778</v>
       </c>
       <c r="D61" s="4" t="n">
-        <v>0.7458333333333333</v>
+        <v>0.7131944444444445</v>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B62" s="3" t="n">
         <v>46239</v>
       </c>
       <c r="C62" s="4" t="n">
-        <v>0.2229166666666667</v>
+        <v>0.2673611111111111</v>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
@@ -1583,17 +1729,17 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B63" s="3" t="n">
         <v>46240</v>
       </c>
       <c r="C63" s="4" t="n">
-        <v>0.2326388888888889</v>
+        <v>0.3229166666666667</v>
       </c>
       <c r="D63" s="4" t="n">
-        <v>0.7576388888888889</v>
+        <v>0.6986111111111111</v>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
@@ -1604,38 +1750,38 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B64" s="3" t="n">
         <v>46242</v>
       </c>
       <c r="C64" s="4" t="n">
-        <v>0.2402777777777778</v>
+        <v>0.2979166666666667</v>
       </c>
       <c r="D64" s="4" t="n">
-        <v>0.7243055555555555</v>
+        <v>0.8006944444444445</v>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>extra punch: 17:31</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B65" s="3" t="n">
         <v>46243</v>
       </c>
       <c r="C65" s="4" t="n">
-        <v>0.2402777777777778</v>
+        <v>0.3458333333333333</v>
       </c>
       <c r="D65" s="4" t="n">
-        <v>0.725</v>
+        <v>0.8048611111111111</v>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
@@ -1646,80 +1792,82 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B66" s="3" t="n">
         <v>46244</v>
       </c>
       <c r="C66" s="4" t="n">
-        <v>0.2409722222222222</v>
+        <v>0.23125</v>
       </c>
       <c r="D66" s="4" t="n">
-        <v>0.7597222222222222</v>
+        <v>0.8069444444444445</v>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>extra punch: 05:36</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B67" s="3" t="n">
         <v>46245</v>
       </c>
       <c r="C67" s="4" t="n">
-        <v>0.2215277777777778</v>
-      </c>
-      <c r="D67" s="4" t="n">
-        <v>0.7319444444444444</v>
+        <v>0.3041666666666666</v>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B68" s="3" t="n">
         <v>46246</v>
       </c>
       <c r="C68" s="4" t="n">
-        <v>0.2361111111111111</v>
+        <v>0.2611111111111111</v>
       </c>
       <c r="D68" s="4" t="n">
-        <v>0.7402777777777778</v>
+        <v>0.7</v>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>extra punch: 06:26</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B69" s="3" t="n">
         <v>46247</v>
       </c>
       <c r="C69" s="4" t="n">
-        <v>0.2479166666666667</v>
+        <v>0.3159722222222222</v>
       </c>
       <c r="D69" s="4" t="n">
-        <v>0.7243055555555555</v>
+        <v>0.7555555555555555</v>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
@@ -1730,40 +1878,38 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B70" s="3" t="n">
         <v>46249</v>
       </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C70" s="4" t="n">
+        <v>0.2784722222222222</v>
       </c>
       <c r="D70" s="4" t="n">
-        <v>0.7201388888888889</v>
+        <v>0.8034722222222223</v>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B71" s="3" t="n">
         <v>46250</v>
       </c>
       <c r="C71" s="4" t="n">
-        <v>0.2298611111111111</v>
+        <v>0.3194444444444444</v>
       </c>
       <c r="D71" s="4" t="n">
-        <v>0.7180555555555556</v>
+        <v>0.7166666666666667</v>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
@@ -1774,17 +1920,17 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B72" s="3" t="n">
         <v>46251</v>
       </c>
       <c r="C72" s="4" t="n">
-        <v>0.2472222222222222</v>
+        <v>0.2993055555555555</v>
       </c>
       <c r="D72" s="4" t="n">
-        <v>0.7402777777777778</v>
+        <v>0.7319444444444444</v>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
@@ -1795,40 +1941,38 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B73" s="3" t="n">
         <v>46252</v>
       </c>
       <c r="C73" s="4" t="n">
-        <v>0.2354166666666667</v>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.2756944444444445</v>
+      </c>
+      <c r="D73" s="4" t="n">
+        <v>0.8368055555555556</v>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B74" s="3" t="n">
         <v>46253</v>
       </c>
       <c r="C74" s="4" t="n">
-        <v>0.2215277777777778</v>
+        <v>0.3159722222222222</v>
       </c>
       <c r="D74" s="4" t="n">
-        <v>0.7305555555555555</v>
+        <v>0.7236111111111111</v>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
@@ -1839,17 +1983,17 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B75" s="3" t="n">
         <v>46254</v>
       </c>
       <c r="C75" s="4" t="n">
-        <v>0.2222222222222222</v>
+        <v>0.2840277777777778</v>
       </c>
       <c r="D75" s="4" t="n">
-        <v>0.7291666666666666</v>
+        <v>0.8111111111111111</v>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
@@ -1860,17 +2004,17 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B76" s="3" t="n">
         <v>46256</v>
       </c>
       <c r="C76" s="4" t="n">
-        <v>0.2388888888888889</v>
+        <v>0.2888888888888889</v>
       </c>
       <c r="D76" s="4" t="n">
-        <v>0.7541666666666667</v>
+        <v>0.7444444444444445</v>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
@@ -1881,17 +2025,17 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B77" s="3" t="n">
         <v>46257</v>
       </c>
       <c r="C77" s="4" t="n">
-        <v>0.2506944444444444</v>
+        <v>0.2513888888888889</v>
       </c>
       <c r="D77" s="4" t="n">
-        <v>0.7291666666666666</v>
+        <v>0.7277777777777777</v>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
@@ -1902,40 +2046,38 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B78" s="3" t="n">
         <v>46258</v>
       </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C78" s="4" t="n">
+        <v>0.2854166666666667</v>
       </c>
       <c r="D78" s="4" t="n">
-        <v>0.725</v>
+        <v>0.7534722222222222</v>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B79" s="3" t="n">
         <v>46259</v>
       </c>
       <c r="C79" s="4" t="n">
-        <v>0.2375</v>
+        <v>0.2673611111111111</v>
       </c>
       <c r="D79" s="4" t="n">
-        <v>0.725</v>
+        <v>0.7506944444444444</v>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
@@ -1946,17 +2088,17 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B80" s="3" t="n">
         <v>46260</v>
       </c>
       <c r="C80" s="4" t="n">
-        <v>0.2256944444444444</v>
+        <v>0.3854166666666667</v>
       </c>
       <c r="D80" s="4" t="n">
-        <v>0.7381944444444445</v>
+        <v>0.8083333333333333</v>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
@@ -1967,17 +2109,17 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B81" s="3" t="n">
         <v>46261</v>
       </c>
       <c r="C81" s="4" t="n">
-        <v>0.2361111111111111</v>
+        <v>0.3375</v>
       </c>
       <c r="D81" s="4" t="n">
-        <v>0.7166666666666667</v>
+        <v>0.8090277777777778</v>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
@@ -1988,42 +2130,21 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B82" s="3" t="n">
         <v>46263</v>
       </c>
       <c r="C82" s="4" t="n">
-        <v>0.2270833333333333</v>
-      </c>
-      <c r="D82" s="4" t="n">
-        <v>0.7347222222222223</v>
+        <v>0.2986111111111111</v>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="B83" s="3" t="n">
-        <v>46264</v>
-      </c>
-      <c r="C83" s="4" t="n">
-        <v>0.2340277777777778</v>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>single punch only</t>
         </is>
@@ -2032,14 +2153,16 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B84" s="3" t="n">
-        <v>46265</v>
-      </c>
-      <c r="C84" s="4" t="n">
-        <v>0.2361111111111111</v>
+        <v>46260</v>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
@@ -2048,45 +2171,66 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>PLEASE VERIFY: check-in/out times not captured (gap between source photos)</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="n">
+        <v>46261</v>
+      </c>
+      <c r="C85" s="4" t="n">
+        <v>0.2826388888888889</v>
+      </c>
+      <c r="D85" s="4" t="n">
+        <v>0.7861111111111111</v>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B86" s="3" t="n">
-        <v>46235</v>
+        <v>46263</v>
       </c>
       <c r="C86" s="4" t="n">
-        <v>0.14375</v>
+        <v>0.2993055555555555</v>
       </c>
       <c r="D86" s="4" t="n">
-        <v>0.7576388888888889</v>
+        <v>0.7708333333333334</v>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>last day of month; final record</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B87" s="3" t="n">
-        <v>46236</v>
+        <v>46264</v>
       </c>
       <c r="C87" s="4" t="n">
-        <v>0.14375</v>
+        <v>0.30625</v>
       </c>
       <c r="D87" s="4" t="n">
-        <v>0.7395833333333334</v>
+        <v>0.6805555555555556</v>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
@@ -2097,40 +2241,19 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B88" s="3" t="n">
-        <v>46237</v>
+        <v>46265</v>
       </c>
       <c r="C88" s="4" t="n">
-        <v>0.1458333333333333</v>
+        <v>0.2472222222222222</v>
       </c>
       <c r="D88" s="4" t="n">
-        <v>0.7472222222222222</v>
+        <v>0.7555555555555555</v>
       </c>
       <c r="E88" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="B89" s="3" t="n">
-        <v>46238</v>
-      </c>
-      <c r="C89" s="4" t="n">
-        <v>0.1451388888888889</v>
-      </c>
-      <c r="D89" s="4" t="n">
-        <v>0.7708333333333334</v>
-      </c>
-      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2139,124 +2262,113 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B90" s="3" t="n">
-        <v>46239</v>
-      </c>
-      <c r="C90" s="4" t="n">
-        <v>0.1444444444444444</v>
-      </c>
-      <c r="D90" s="4" t="n">
-        <v>0.6881944444444444</v>
+        <v>46258</v>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>PLEASE VERIFY: check-in/out time not captured (gap between source photos)</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B91" s="3" t="n">
-        <v>46240</v>
-      </c>
-      <c r="C91" s="4" t="n">
-        <v>0.1444444444444444</v>
+        <v>46259</v>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D91" s="4" t="n">
-        <v>0.7659722222222223</v>
+        <v>0.75</v>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>46241</v>
-      </c>
-      <c r="C92" s="4" t="n">
-        <v>0.1451388888888889</v>
+        <v>46261</v>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D92" s="4" t="n">
-        <v>0.7298611111111111</v>
+        <v>0.7395833333333334</v>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B93" s="3" t="n">
-        <v>46242</v>
-      </c>
-      <c r="C93" s="4" t="n">
-        <v>0.1388888888888889</v>
+        <v>46263</v>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D93" s="4" t="n">
-        <v>0.8090277777777778</v>
+        <v>0.4041666666666667</v>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>extra punch: 03:24</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B94" s="3" t="n">
-        <v>46243</v>
+        <v>46265</v>
       </c>
       <c r="C94" s="4" t="n">
-        <v>0.1444444444444444</v>
+        <v>0.2805555555555556</v>
       </c>
       <c r="D94" s="4" t="n">
-        <v>0.8381944444444445</v>
+        <v>0.7534722222222222</v>
       </c>
       <c r="E94" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="B95" s="3" t="n">
-        <v>46244</v>
-      </c>
-      <c r="C95" s="4" t="n">
-        <v>0.1354166666666667</v>
-      </c>
-      <c r="D95" s="4" t="n">
-        <v>0.7638888888888888</v>
-      </c>
-      <c r="E95" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2265,38 +2377,42 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B96" s="3" t="n">
-        <v>46245</v>
-      </c>
-      <c r="C96" s="4" t="n">
-        <v>0.14375</v>
-      </c>
-      <c r="D96" s="4" t="n">
-        <v>0.7444444444444445</v>
+        <v>46260</v>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>PLEASE VERIFY: check-in/out times not captured (gap between source photos)</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B97" s="3" t="n">
-        <v>46246</v>
+        <v>46261</v>
       </c>
       <c r="C97" s="4" t="n">
-        <v>0.1430555555555555</v>
+        <v>0.3652777777777778</v>
       </c>
       <c r="D97" s="4" t="n">
-        <v>0.7409722222222223</v>
+        <v>0.7395833333333334</v>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
@@ -2307,17 +2423,17 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B98" s="3" t="n">
-        <v>46247</v>
+        <v>46263</v>
       </c>
       <c r="C98" s="4" t="n">
-        <v>0.1423611111111111</v>
+        <v>0.3652777777777778</v>
       </c>
       <c r="D98" s="4" t="n">
-        <v>0.75</v>
+        <v>0.7569444444444444</v>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
@@ -2328,17 +2444,17 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B99" s="3" t="n">
-        <v>46248</v>
+        <v>46264</v>
       </c>
       <c r="C99" s="4" t="n">
-        <v>0.15</v>
+        <v>0.3534722222222222</v>
       </c>
       <c r="D99" s="4" t="n">
-        <v>0.7076388888888889</v>
+        <v>0.7534722222222222</v>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
@@ -2349,40 +2465,19 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>46249</v>
+        <v>46265</v>
       </c>
       <c r="C100" s="4" t="n">
-        <v>0.1513888888888889</v>
+        <v>0.3319444444444444</v>
       </c>
       <c r="D100" s="4" t="n">
-        <v>0.7277777777777777</v>
+        <v>0.7680555555555556</v>
       </c>
       <c r="E100" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="B101" s="3" t="n">
-        <v>46250</v>
-      </c>
-      <c r="C101" s="4" t="n">
-        <v>0.2708333333333333</v>
-      </c>
-      <c r="D101" s="4" t="n">
-        <v>0.7229166666666667</v>
-      </c>
-      <c r="E101" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2391,38 +2486,42 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B102" s="3" t="n">
-        <v>46251</v>
-      </c>
-      <c r="C102" s="4" t="n">
-        <v>0.2333333333333333</v>
-      </c>
-      <c r="D102" s="4" t="n">
-        <v>0.8888888888888888</v>
+        <v>46260</v>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>PLEASE VERIFY: check-in/out times not captured (gap between source photos)</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B103" s="3" t="n">
-        <v>46252</v>
+        <v>46261</v>
       </c>
       <c r="C103" s="4" t="n">
-        <v>0.25625</v>
+        <v>0.2909722222222222</v>
       </c>
       <c r="D103" s="4" t="n">
-        <v>0.7416666666666667</v>
+        <v>0.7430555555555556</v>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
@@ -2433,17 +2532,17 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B104" s="3" t="n">
-        <v>46253</v>
+        <v>46263</v>
       </c>
       <c r="C104" s="4" t="n">
-        <v>0.2777777777777778</v>
+        <v>0.275</v>
       </c>
       <c r="D104" s="4" t="n">
-        <v>0.7451388888888889</v>
+        <v>0.7513888888888889</v>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
@@ -2454,17 +2553,17 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B105" s="3" t="n">
-        <v>46254</v>
+        <v>46264</v>
       </c>
       <c r="C105" s="4" t="n">
-        <v>0.2625</v>
+        <v>0.3194444444444444</v>
       </c>
       <c r="D105" s="4" t="n">
-        <v>0.7979166666666667</v>
+        <v>0.7493055555555556</v>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
@@ -2475,40 +2574,19 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>46255</v>
+        <v>46265</v>
       </c>
       <c r="C106" s="4" t="n">
-        <v>0.275</v>
+        <v>0.2631944444444445</v>
       </c>
       <c r="D106" s="4" t="n">
-        <v>0.8354166666666667</v>
+        <v>0.7555555555555555</v>
       </c>
       <c r="E106" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="B107" s="3" t="n">
-        <v>46256</v>
-      </c>
-      <c r="C107" s="4" t="n">
-        <v>0.2611111111111111</v>
-      </c>
-      <c r="D107" s="4" t="n">
-        <v>0.7513888888888889</v>
-      </c>
-      <c r="E107" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2517,17 +2595,17 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B108" s="3" t="n">
-        <v>46257</v>
+        <v>46260</v>
       </c>
       <c r="C108" s="4" t="n">
-        <v>0.24375</v>
+        <v>0.3055555555555556</v>
       </c>
       <c r="D108" s="4" t="n">
-        <v>0.7263888888888889</v>
+        <v>0.8013888888888889</v>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
@@ -2538,17 +2616,17 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B109" s="3" t="n">
-        <v>46258</v>
+        <v>46261</v>
       </c>
       <c r="C109" s="4" t="n">
-        <v>0.2631944444444445</v>
+        <v>0.2798611111111111</v>
       </c>
       <c r="D109" s="4" t="n">
-        <v>0.7270833333333333</v>
+        <v>0.7493055555555556</v>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
@@ -2559,80 +2637,59 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B110" s="3" t="n">
-        <v>46259</v>
+        <v>46263</v>
       </c>
       <c r="C110" s="4" t="n">
-        <v>0.2611111111111111</v>
+        <v>0.3347222222222222</v>
       </c>
       <c r="D110" s="4" t="n">
-        <v>0.7298611111111111</v>
+        <v>0.8895833333333333</v>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>extra punch: 08:02</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>46260</v>
+        <v>46264</v>
       </c>
       <c r="C111" s="4" t="n">
-        <v>0.275</v>
+        <v>0.3208333333333334</v>
       </c>
       <c r="D111" s="4" t="n">
-        <v>0.8791666666666667</v>
+        <v>0.7354166666666667</v>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>extra punch: 17:56</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="B112" s="3" t="n">
-        <v>46261</v>
-      </c>
-      <c r="C112" s="4" t="n">
-        <v>0.2555555555555555</v>
-      </c>
-      <c r="D112" s="4" t="n">
-        <v>0.8506944444444444</v>
-      </c>
-      <c r="E112" s="2" t="inlineStr">
-        <is>
-          <t>extra punches: 17:07 17:02</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B113" s="3" t="n">
         <v>46262</v>
       </c>
       <c r="C113" s="4" t="n">
-        <v>0.2805555555555556</v>
+        <v>0.1493055555555556</v>
       </c>
       <c r="D113" s="4" t="n">
-        <v>0.7701388888888889</v>
+        <v>0.7159722222222222</v>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
@@ -2643,14 +2700,14 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B114" s="3" t="n">
         <v>46263</v>
       </c>
       <c r="C114" s="4" t="n">
-        <v>0.2541666666666667</v>
+        <v>0.1451388888888889</v>
       </c>
       <c r="D114" s="4" t="n">
         <v>0.7479166666666667</v>
@@ -2664,17 +2721,17 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B115" s="3" t="n">
         <v>46264</v>
       </c>
       <c r="C115" s="4" t="n">
-        <v>0.2659722222222222</v>
+        <v>0.14375</v>
       </c>
       <c r="D115" s="4" t="n">
-        <v>0.7354166666666667</v>
+        <v>0.75625</v>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
@@ -2685,59 +2742,59 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B116" s="3" t="n">
         <v>46265</v>
       </c>
       <c r="C116" s="4" t="n">
-        <v>0.2527777777777778</v>
+        <v>0.1479166666666667</v>
       </c>
       <c r="D116" s="4" t="n">
-        <v>0.7354166666666667</v>
+        <v>0.9326388888888889</v>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>corrected from a clearer re-scan photo later in the album</t>
+          <t>extra punch: 22:23</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>46235</v>
+        <v>46262</v>
       </c>
       <c r="C118" s="4" t="n">
-        <v>0.2625</v>
+        <v>0.1881944444444444</v>
       </c>
       <c r="D118" s="4" t="n">
-        <v>0.7444444444444445</v>
+        <v>0.4055555555555556</v>
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>last day of month; final record</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B119" s="3" t="n">
-        <v>46236</v>
+        <v>46263</v>
       </c>
       <c r="C119" s="4" t="n">
-        <v>0.2645833333333333</v>
+        <v>0.1847222222222222</v>
       </c>
       <c r="D119" s="4" t="n">
-        <v>0.7493055555555556</v>
+        <v>0.4527777777777778</v>
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
@@ -2748,17 +2805,17 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B120" s="3" t="n">
-        <v>46237</v>
+        <v>46264</v>
       </c>
       <c r="C120" s="4" t="n">
-        <v>0.2604166666666667</v>
+        <v>0.1847222222222222</v>
       </c>
       <c r="D120" s="4" t="n">
-        <v>0.7479166666666667</v>
+        <v>0.5097222222222222</v>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
@@ -2769,40 +2826,19 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B121" s="3" t="n">
-        <v>46238</v>
+        <v>46265</v>
       </c>
       <c r="C121" s="4" t="n">
-        <v>0.2527777777777778</v>
+        <v>0.1868055555555556</v>
       </c>
       <c r="D121" s="4" t="n">
-        <v>0.75</v>
+        <v>0.4131944444444444</v>
       </c>
       <c r="E121" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="B122" s="3" t="n">
-        <v>46239</v>
-      </c>
-      <c r="C122" s="4" t="n">
-        <v>0.25625</v>
-      </c>
-      <c r="D122" s="4" t="n">
-        <v>0.7763888888888889</v>
-      </c>
-      <c r="E122" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2811,17 +2847,17 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B123" s="3" t="n">
-        <v>46240</v>
+        <v>46235</v>
       </c>
       <c r="C123" s="4" t="n">
-        <v>0.2701388888888889</v>
+        <v>0.2368055555555555</v>
       </c>
       <c r="D123" s="4" t="n">
-        <v>0.7423611111111111</v>
+        <v>0.7430555555555556</v>
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
@@ -2832,17 +2868,17 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B124" s="3" t="n">
-        <v>46242</v>
+        <v>46236</v>
       </c>
       <c r="C124" s="4" t="n">
-        <v>0.2597222222222222</v>
+        <v>0.2604166666666667</v>
       </c>
       <c r="D124" s="4" t="n">
-        <v>0.7326388888888888</v>
+        <v>0.7534722222222222</v>
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
@@ -2853,17 +2889,17 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B125" s="3" t="n">
-        <v>46243</v>
+        <v>46237</v>
       </c>
       <c r="C125" s="4" t="n">
-        <v>0.2381944444444444</v>
+        <v>0.3097222222222222</v>
       </c>
       <c r="D125" s="4" t="n">
-        <v>0.75625</v>
+        <v>0.7444444444444445</v>
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
@@ -2874,11 +2910,11 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B126" s="3" t="n">
-        <v>46244</v>
+        <v>46238</v>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
@@ -2886,7 +2922,7 @@
         </is>
       </c>
       <c r="D126" s="4" t="n">
-        <v>0.75625</v>
+        <v>0.7458333333333333</v>
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
@@ -2897,38 +2933,40 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B127" s="3" t="n">
-        <v>46245</v>
+        <v>46239</v>
       </c>
       <c r="C127" s="4" t="n">
-        <v>0.2381944444444444</v>
-      </c>
-      <c r="D127" s="4" t="n">
-        <v>0.7402777777777778</v>
+        <v>0.2229166666666667</v>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B128" s="3" t="n">
-        <v>46246</v>
+        <v>46240</v>
       </c>
       <c r="C128" s="4" t="n">
-        <v>0.2340277777777778</v>
+        <v>0.2326388888888889</v>
       </c>
       <c r="D128" s="4" t="n">
-        <v>0.7493055555555556</v>
+        <v>0.7576388888888889</v>
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
@@ -2939,17 +2977,17 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B129" s="3" t="n">
-        <v>46247</v>
+        <v>46242</v>
       </c>
       <c r="C129" s="4" t="n">
-        <v>0.2465277777777778</v>
+        <v>0.2402777777777778</v>
       </c>
       <c r="D129" s="4" t="n">
-        <v>0.7270833333333333</v>
+        <v>0.7243055555555555</v>
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
@@ -2960,17 +2998,17 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B130" s="3" t="n">
-        <v>46249</v>
+        <v>46243</v>
       </c>
       <c r="C130" s="4" t="n">
-        <v>0.2395833333333333</v>
+        <v>0.2402777777777778</v>
       </c>
       <c r="D130" s="4" t="n">
-        <v>0.7388888888888889</v>
+        <v>0.725</v>
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
@@ -2981,17 +3019,17 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B131" s="3" t="n">
-        <v>46250</v>
+        <v>46244</v>
       </c>
       <c r="C131" s="4" t="n">
-        <v>0.2902777777777778</v>
+        <v>0.2409722222222222</v>
       </c>
       <c r="D131" s="4" t="n">
-        <v>0.7236111111111111</v>
+        <v>0.7597222222222222</v>
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
@@ -3002,17 +3040,17 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B132" s="3" t="n">
-        <v>46251</v>
+        <v>46245</v>
       </c>
       <c r="C132" s="4" t="n">
-        <v>0.2743055555555556</v>
+        <v>0.2215277777777778</v>
       </c>
       <c r="D132" s="4" t="n">
-        <v>0.7333333333333333</v>
+        <v>0.7319444444444444</v>
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
@@ -3023,17 +3061,17 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B133" s="3" t="n">
-        <v>46252</v>
+        <v>46246</v>
       </c>
       <c r="C133" s="4" t="n">
-        <v>0.2826388888888889</v>
+        <v>0.2361111111111111</v>
       </c>
       <c r="D133" s="4" t="n">
-        <v>0.7451388888888889</v>
+        <v>0.7402777777777778</v>
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
@@ -3044,17 +3082,17 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>46253</v>
+        <v>46247</v>
       </c>
       <c r="C134" s="4" t="n">
-        <v>0.2763888888888889</v>
+        <v>0.2479166666666667</v>
       </c>
       <c r="D134" s="4" t="n">
-        <v>0.7298611111111111</v>
+        <v>0.7243055555555555</v>
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
@@ -3065,38 +3103,40 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>46254</v>
-      </c>
-      <c r="C135" s="4" t="n">
-        <v>0.275</v>
+        <v>46249</v>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D135" s="4" t="n">
-        <v>0.7256944444444444</v>
+        <v>0.7201388888888889</v>
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B136" s="3" t="n">
-        <v>46256</v>
+        <v>46250</v>
       </c>
       <c r="C136" s="4" t="n">
-        <v>0.2805555555555556</v>
+        <v>0.2298611111111111</v>
       </c>
       <c r="D136" s="4" t="n">
-        <v>0.7513888888888889</v>
+        <v>0.7180555555555556</v>
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
@@ -3107,17 +3147,17 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B137" s="3" t="n">
-        <v>46261</v>
+        <v>46251</v>
       </c>
       <c r="C137" s="4" t="n">
-        <v>0.24375</v>
+        <v>0.2472222222222222</v>
       </c>
       <c r="D137" s="4" t="n">
-        <v>0.6763888888888889</v>
+        <v>0.7402777777777778</v>
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
@@ -3128,38 +3168,40 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B138" s="3" t="n">
-        <v>46263</v>
+        <v>46252</v>
       </c>
       <c r="C138" s="4" t="n">
-        <v>0.2965277777777778</v>
-      </c>
-      <c r="D138" s="4" t="n">
-        <v>0.7472222222222222</v>
+        <v>0.2354166666666667</v>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B139" s="3" t="n">
-        <v>46264</v>
+        <v>46253</v>
       </c>
       <c r="C139" s="4" t="n">
-        <v>0.2888888888888889</v>
+        <v>0.2215277777777778</v>
       </c>
       <c r="D139" s="4" t="n">
-        <v>0.75</v>
+        <v>0.7305555555555555</v>
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
@@ -3170,19 +3212,40 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B140" s="3" t="n">
-        <v>46265</v>
+        <v>46254</v>
       </c>
       <c r="C140" s="4" t="n">
-        <v>0.2909722222222222</v>
+        <v>0.2222222222222222</v>
       </c>
       <c r="D140" s="4" t="n">
-        <v>0.75</v>
+        <v>0.7291666666666666</v>
       </c>
       <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B141" s="3" t="n">
+        <v>46256</v>
+      </c>
+      <c r="C141" s="4" t="n">
+        <v>0.2388888888888889</v>
+      </c>
+      <c r="D141" s="4" t="n">
+        <v>0.7541666666666667</v>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3191,59 +3254,61 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B142" s="3" t="n">
-        <v>46235</v>
+        <v>46257</v>
       </c>
       <c r="C142" s="4" t="n">
-        <v>0.2381944444444444</v>
+        <v>0.2506944444444444</v>
       </c>
       <c r="D142" s="4" t="n">
-        <v>0.7458333333333333</v>
+        <v>0.7291666666666666</v>
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>last day of month; final record</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B143" s="3" t="n">
-        <v>46236</v>
-      </c>
-      <c r="C143" s="4" t="n">
-        <v>0.2958333333333333</v>
+        <v>46258</v>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D143" s="4" t="n">
-        <v>0.7430555555555556</v>
+        <v>0.725</v>
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B144" s="3" t="n">
-        <v>46237</v>
+        <v>46259</v>
       </c>
       <c r="C144" s="4" t="n">
-        <v>0.3034722222222222</v>
+        <v>0.2375</v>
       </c>
       <c r="D144" s="4" t="n">
-        <v>0.7159722222222222</v>
+        <v>0.725</v>
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
@@ -3254,17 +3319,17 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B145" s="3" t="n">
-        <v>46238</v>
+        <v>46260</v>
       </c>
       <c r="C145" s="4" t="n">
-        <v>0.2763888888888889</v>
+        <v>0.2256944444444444</v>
       </c>
       <c r="D145" s="4" t="n">
-        <v>0.7166666666666667</v>
+        <v>0.7381944444444445</v>
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
@@ -3275,17 +3340,17 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B146" s="3" t="n">
-        <v>46239</v>
+        <v>46261</v>
       </c>
       <c r="C146" s="4" t="n">
-        <v>0.3222222222222222</v>
+        <v>0.2361111111111111</v>
       </c>
       <c r="D146" s="4" t="n">
-        <v>0.7715277777777778</v>
+        <v>0.7166666666666667</v>
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
@@ -3296,17 +3361,17 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B147" s="3" t="n">
-        <v>46240</v>
+        <v>46263</v>
       </c>
       <c r="C147" s="4" t="n">
-        <v>0.30625</v>
+        <v>0.2270833333333333</v>
       </c>
       <c r="D147" s="4" t="n">
-        <v>0.7590277777777777</v>
+        <v>0.7347222222222223</v>
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
@@ -3317,149 +3382,126 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B148" s="3" t="n">
-        <v>46242</v>
+        <v>46264</v>
       </c>
       <c r="C148" s="4" t="n">
-        <v>0.3055555555555556</v>
-      </c>
-      <c r="D148" s="4" t="n">
-        <v>0.7604166666666666</v>
+        <v>0.2340277777777778</v>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B149" s="3" t="n">
-        <v>46243</v>
+        <v>46265</v>
       </c>
       <c r="C149" s="4" t="n">
-        <v>0.2798611111111111</v>
-      </c>
-      <c r="D149" s="4" t="n">
-        <v>0.75</v>
+        <v>0.2361111111111111</v>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="B150" s="3" t="n">
-        <v>46244</v>
-      </c>
-      <c r="C150" s="4" t="n">
-        <v>0.2263888888888889</v>
-      </c>
-      <c r="D150" s="4" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="E150" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B151" s="3" t="n">
-        <v>46245</v>
+        <v>46235</v>
       </c>
       <c r="C151" s="4" t="n">
-        <v>0.3118055555555556</v>
-      </c>
-      <c r="D151" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.14375</v>
+      </c>
+      <c r="D151" s="4" t="n">
+        <v>0.7576388888888889</v>
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>last day of month; final record</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B152" s="3" t="n">
-        <v>46246</v>
+        <v>46236</v>
       </c>
       <c r="C152" s="4" t="n">
-        <v>0.2986111111111111</v>
-      </c>
-      <c r="D152" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.14375</v>
+      </c>
+      <c r="D152" s="4" t="n">
+        <v>0.7395833333333334</v>
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B153" s="3" t="n">
-        <v>46247</v>
+        <v>46237</v>
       </c>
       <c r="C153" s="4" t="n">
-        <v>0.3347222222222222</v>
-      </c>
-      <c r="D153" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.1458333333333333</v>
+      </c>
+      <c r="D153" s="4" t="n">
+        <v>0.7472222222222222</v>
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B154" s="3" t="n">
-        <v>46249</v>
+        <v>46238</v>
       </c>
       <c r="C154" s="4" t="n">
-        <v>0.2354166666666667</v>
+        <v>0.1451388888888889</v>
       </c>
       <c r="D154" s="4" t="n">
-        <v>0.75</v>
+        <v>0.7708333333333334</v>
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
@@ -3470,17 +3512,17 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B155" s="3" t="n">
-        <v>46250</v>
+        <v>46239</v>
       </c>
       <c r="C155" s="4" t="n">
-        <v>0.325</v>
+        <v>0.1444444444444444</v>
       </c>
       <c r="D155" s="4" t="n">
-        <v>0.7722222222222223</v>
+        <v>0.6881944444444444</v>
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
@@ -3491,17 +3533,17 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B156" s="3" t="n">
-        <v>46251</v>
+        <v>46240</v>
       </c>
       <c r="C156" s="4" t="n">
-        <v>0.3979166666666666</v>
+        <v>0.1444444444444444</v>
       </c>
       <c r="D156" s="4" t="n">
-        <v>0.7680555555555556</v>
+        <v>0.7659722222222223</v>
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
@@ -3512,17 +3554,17 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B157" s="3" t="n">
-        <v>46252</v>
+        <v>46241</v>
       </c>
       <c r="C157" s="4" t="n">
-        <v>0.3083333333333333</v>
+        <v>0.1451388888888889</v>
       </c>
       <c r="D157" s="4" t="n">
-        <v>0.7583333333333333</v>
+        <v>0.7298611111111111</v>
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
@@ -3533,61 +3575,59 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B158" s="3" t="n">
-        <v>46253</v>
+        <v>46242</v>
       </c>
       <c r="C158" s="4" t="n">
-        <v>0.475</v>
+        <v>0.1388888888888889</v>
       </c>
       <c r="D158" s="4" t="n">
-        <v>0.7173611111111111</v>
+        <v>0.8090277777777778</v>
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>extra punch: 03:24</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B159" s="3" t="n">
-        <v>46254</v>
+        <v>46243</v>
       </c>
       <c r="C159" s="4" t="n">
-        <v>0.3576388888888889</v>
-      </c>
-      <c r="D159" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.1444444444444444</v>
+      </c>
+      <c r="D159" s="4" t="n">
+        <v>0.8381944444444445</v>
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B160" s="3" t="n">
-        <v>46256</v>
+        <v>46244</v>
       </c>
       <c r="C160" s="4" t="n">
-        <v>0.2069444444444444</v>
+        <v>0.1354166666666667</v>
       </c>
       <c r="D160" s="4" t="n">
-        <v>0.7243055555555555</v>
+        <v>0.7638888888888888</v>
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
@@ -3598,17 +3638,17 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B161" s="3" t="n">
-        <v>46257</v>
+        <v>46245</v>
       </c>
       <c r="C161" s="4" t="n">
-        <v>0.25</v>
+        <v>0.14375</v>
       </c>
       <c r="D161" s="4" t="n">
-        <v>0.7493055555555556</v>
+        <v>0.7444444444444445</v>
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
@@ -3619,17 +3659,17 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B162" s="3" t="n">
-        <v>46258</v>
+        <v>46246</v>
       </c>
       <c r="C162" s="4" t="n">
-        <v>0.3263888888888889</v>
+        <v>0.1430555555555555</v>
       </c>
       <c r="D162" s="4" t="n">
-        <v>0.7388888888888889</v>
+        <v>0.7409722222222223</v>
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
@@ -3640,17 +3680,17 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B163" s="3" t="n">
-        <v>46259</v>
+        <v>46247</v>
       </c>
       <c r="C163" s="4" t="n">
-        <v>0.2763888888888889</v>
+        <v>0.1423611111111111</v>
       </c>
       <c r="D163" s="4" t="n">
-        <v>0.7548611111111111</v>
+        <v>0.75</v>
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
@@ -3661,38 +3701,38 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B164" s="3" t="n">
-        <v>46260</v>
+        <v>46248</v>
       </c>
       <c r="C164" s="4" t="n">
-        <v>0.3243055555555556</v>
+        <v>0.15</v>
       </c>
       <c r="D164" s="4" t="n">
-        <v>0.7534722222222222</v>
+        <v>0.7076388888888889</v>
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>extra punch: 17:56</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B165" s="3" t="n">
-        <v>46261</v>
+        <v>46249</v>
       </c>
       <c r="C165" s="4" t="n">
-        <v>0.2666666666666667</v>
+        <v>0.1513888888888889</v>
       </c>
       <c r="D165" s="4" t="n">
-        <v>0.75</v>
+        <v>0.7277777777777777</v>
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
@@ -3703,17 +3743,17 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B166" s="3" t="n">
-        <v>46263</v>
+        <v>46250</v>
       </c>
       <c r="C166" s="4" t="n">
-        <v>0.2965277777777778</v>
+        <v>0.2708333333333333</v>
       </c>
       <c r="D166" s="4" t="n">
-        <v>0.7326388888888888</v>
+        <v>0.7229166666666667</v>
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
@@ -3724,17 +3764,17 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B167" s="3" t="n">
-        <v>46264</v>
+        <v>46251</v>
       </c>
       <c r="C167" s="4" t="n">
-        <v>0.2965277777777778</v>
+        <v>0.2333333333333333</v>
       </c>
       <c r="D167" s="4" t="n">
-        <v>0.75625</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
@@ -3745,59 +3785,80 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B168" s="3" t="n">
-        <v>46265</v>
+        <v>46252</v>
       </c>
       <c r="C168" s="4" t="n">
-        <v>0.2527777777777778</v>
+        <v>0.25625</v>
       </c>
       <c r="D168" s="4" t="n">
-        <v>0.7604166666666666</v>
+        <v>0.7416666666666667</v>
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>corrected from a clearer re-scan photo later in the album</t>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B169" s="3" t="n">
+        <v>46253</v>
+      </c>
+      <c r="C169" s="4" t="n">
+        <v>0.2777777777777778</v>
+      </c>
+      <c r="D169" s="4" t="n">
+        <v>0.7451388888888889</v>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B170" s="3" t="n">
-        <v>46235</v>
+        <v>46254</v>
       </c>
       <c r="C170" s="4" t="n">
-        <v>0.2590277777777778</v>
+        <v>0.2625</v>
       </c>
       <c r="D170" s="4" t="n">
-        <v>0.7319444444444444</v>
+        <v>0.7979166666666667</v>
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>last day of month; final record</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B171" s="3" t="n">
-        <v>46236</v>
+        <v>46255</v>
       </c>
       <c r="C171" s="4" t="n">
-        <v>0.2972222222222222</v>
+        <v>0.275</v>
       </c>
       <c r="D171" s="4" t="n">
-        <v>0.7430555555555556</v>
+        <v>0.8354166666666667</v>
       </c>
       <c r="E171" s="2" t="inlineStr">
         <is>
@@ -3808,17 +3869,17 @@
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B172" s="3" t="n">
-        <v>46237</v>
+        <v>46256</v>
       </c>
       <c r="C172" s="4" t="n">
-        <v>0.2618055555555556</v>
+        <v>0.2611111111111111</v>
       </c>
       <c r="D172" s="4" t="n">
-        <v>0.7472222222222222</v>
+        <v>0.7513888888888889</v>
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
@@ -3829,17 +3890,17 @@
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B173" s="3" t="n">
-        <v>46238</v>
+        <v>46257</v>
       </c>
       <c r="C173" s="4" t="n">
-        <v>0.4965277777777778</v>
+        <v>0.24375</v>
       </c>
       <c r="D173" s="4" t="n">
-        <v>0.7506944444444444</v>
+        <v>0.7263888888888889</v>
       </c>
       <c r="E173" s="2" t="inlineStr">
         <is>
@@ -3850,17 +3911,17 @@
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B174" s="3" t="n">
-        <v>46239</v>
+        <v>46258</v>
       </c>
       <c r="C174" s="4" t="n">
-        <v>0.4743055555555555</v>
+        <v>0.2631944444444445</v>
       </c>
       <c r="D174" s="4" t="n">
-        <v>0.7722222222222223</v>
+        <v>0.7270833333333333</v>
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
@@ -3871,17 +3932,17 @@
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B175" s="3" t="n">
-        <v>46240</v>
+        <v>46259</v>
       </c>
       <c r="C175" s="4" t="n">
-        <v>0.2409722222222222</v>
+        <v>0.2611111111111111</v>
       </c>
       <c r="D175" s="4" t="n">
-        <v>0.7625</v>
+        <v>0.7298611111111111</v>
       </c>
       <c r="E175" s="2" t="inlineStr">
         <is>
@@ -3892,59 +3953,59 @@
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B176" s="3" t="n">
-        <v>46242</v>
+        <v>46260</v>
       </c>
       <c r="C176" s="4" t="n">
-        <v>0.2201388888888889</v>
+        <v>0.275</v>
       </c>
       <c r="D176" s="4" t="n">
-        <v>0.7618055555555555</v>
+        <v>0.8791666666666667</v>
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>extra punch: 17:56</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B177" s="3" t="n">
-        <v>46243</v>
+        <v>46261</v>
       </c>
       <c r="C177" s="4" t="n">
-        <v>0.2395833333333333</v>
+        <v>0.2555555555555555</v>
       </c>
       <c r="D177" s="4" t="n">
-        <v>0.725</v>
+        <v>0.8506944444444444</v>
       </c>
       <c r="E177" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>extra punches: 17:07 17:02</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B178" s="3" t="n">
-        <v>46244</v>
+        <v>46262</v>
       </c>
       <c r="C178" s="4" t="n">
-        <v>0.2256944444444444</v>
+        <v>0.2805555555555556</v>
       </c>
       <c r="D178" s="4" t="n">
-        <v>0.7611111111111111</v>
+        <v>0.7701388888888889</v>
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
@@ -3955,17 +4016,17 @@
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B179" s="3" t="n">
-        <v>46245</v>
+        <v>46263</v>
       </c>
       <c r="C179" s="4" t="n">
-        <v>0.2375</v>
+        <v>0.2541666666666667</v>
       </c>
       <c r="D179" s="4" t="n">
-        <v>0.7375</v>
+        <v>0.7479166666666667</v>
       </c>
       <c r="E179" s="2" t="inlineStr">
         <is>
@@ -3976,17 +4037,17 @@
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B180" s="3" t="n">
-        <v>46246</v>
+        <v>46264</v>
       </c>
       <c r="C180" s="4" t="n">
-        <v>0.2284722222222222</v>
+        <v>0.2659722222222222</v>
       </c>
       <c r="D180" s="4" t="n">
-        <v>0.7423611111111111</v>
+        <v>0.7354166666666667</v>
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
@@ -3997,82 +4058,59 @@
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B181" s="3" t="n">
-        <v>46247</v>
+        <v>46265</v>
       </c>
       <c r="C181" s="4" t="n">
-        <v>0.4402777777777778</v>
-      </c>
-      <c r="D181" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.2527777777777778</v>
+      </c>
+      <c r="D181" s="4" t="n">
+        <v>0.7354166666666667</v>
       </c>
       <c r="E181" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="B182" s="3" t="n">
-        <v>46249</v>
-      </c>
-      <c r="C182" s="4" t="n">
-        <v>0.2354166666666667</v>
-      </c>
-      <c r="D182" s="4" t="n">
-        <v>0.7611111111111111</v>
-      </c>
-      <c r="E182" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>corrected from a clearer re-scan photo later in the album</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B183" s="3" t="n">
-        <v>46250</v>
+        <v>46235</v>
       </c>
       <c r="C183" s="4" t="n">
-        <v>0.2409722222222222</v>
+        <v>0.2625</v>
       </c>
       <c r="D183" s="4" t="n">
-        <v>0.7381944444444445</v>
+        <v>0.7444444444444445</v>
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>last day of month; final record</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B184" s="3" t="n">
-        <v>46251</v>
+        <v>46236</v>
       </c>
       <c r="C184" s="4" t="n">
-        <v>0.3416666666666667</v>
+        <v>0.2645833333333333</v>
       </c>
       <c r="D184" s="4" t="n">
-        <v>0.7326388888888888</v>
+        <v>0.7493055555555556</v>
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
@@ -4083,17 +4121,17 @@
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B185" s="3" t="n">
-        <v>46252</v>
+        <v>46237</v>
       </c>
       <c r="C185" s="4" t="n">
-        <v>0.2916666666666667</v>
+        <v>0.2604166666666667</v>
       </c>
       <c r="D185" s="4" t="n">
-        <v>0.7416666666666667</v>
+        <v>0.7479166666666667</v>
       </c>
       <c r="E185" s="2" t="inlineStr">
         <is>
@@ -4104,17 +4142,17 @@
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B186" s="3" t="n">
-        <v>46253</v>
+        <v>46238</v>
       </c>
       <c r="C186" s="4" t="n">
-        <v>0.2395833333333333</v>
+        <v>0.2527777777777778</v>
       </c>
       <c r="D186" s="4" t="n">
-        <v>0.7416666666666667</v>
+        <v>0.75</v>
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
@@ -4125,17 +4163,17 @@
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B187" s="3" t="n">
-        <v>46254</v>
+        <v>46239</v>
       </c>
       <c r="C187" s="4" t="n">
-        <v>0.2472222222222222</v>
+        <v>0.25625</v>
       </c>
       <c r="D187" s="4" t="n">
-        <v>0.7243055555555555</v>
+        <v>0.7763888888888889</v>
       </c>
       <c r="E187" s="2" t="inlineStr">
         <is>
@@ -4146,40 +4184,38 @@
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B188" s="3" t="n">
-        <v>46256</v>
+        <v>46240</v>
       </c>
       <c r="C188" s="4" t="n">
-        <v>0.2875</v>
-      </c>
-      <c r="D188" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.2701388888888889</v>
+      </c>
+      <c r="D188" s="4" t="n">
+        <v>0.7423611111111111</v>
       </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B189" s="3" t="n">
-        <v>46257</v>
+        <v>46242</v>
       </c>
       <c r="C189" s="4" t="n">
-        <v>0.2479166666666667</v>
+        <v>0.2597222222222222</v>
       </c>
       <c r="D189" s="4" t="n">
-        <v>0.7618055555555555</v>
+        <v>0.7326388888888888</v>
       </c>
       <c r="E189" s="2" t="inlineStr">
         <is>
@@ -4190,17 +4226,17 @@
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B190" s="3" t="n">
-        <v>46258</v>
+        <v>46243</v>
       </c>
       <c r="C190" s="4" t="n">
-        <v>0.2375</v>
+        <v>0.2381944444444444</v>
       </c>
       <c r="D190" s="4" t="n">
-        <v>0.7506944444444444</v>
+        <v>0.75625</v>
       </c>
       <c r="E190" s="2" t="inlineStr">
         <is>
@@ -4211,38 +4247,40 @@
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B191" s="3" t="n">
-        <v>46259</v>
-      </c>
-      <c r="C191" s="4" t="n">
-        <v>0.2375</v>
+        <v>46244</v>
+      </c>
+      <c r="C191" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D191" s="4" t="n">
-        <v>0.7597222222222222</v>
+        <v>0.75625</v>
       </c>
       <c r="E191" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B192" s="3" t="n">
-        <v>46260</v>
+        <v>46245</v>
       </c>
       <c r="C192" s="4" t="n">
-        <v>0.2479166666666667</v>
+        <v>0.2381944444444444</v>
       </c>
       <c r="D192" s="4" t="n">
-        <v>0.7555555555555555</v>
+        <v>0.7402777777777778</v>
       </c>
       <c r="E192" s="2" t="inlineStr">
         <is>
@@ -4253,17 +4291,17 @@
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B193" s="3" t="n">
-        <v>46261</v>
+        <v>46246</v>
       </c>
       <c r="C193" s="4" t="n">
-        <v>0.2493055555555556</v>
+        <v>0.2340277777777778</v>
       </c>
       <c r="D193" s="4" t="n">
-        <v>0.7944444444444444</v>
+        <v>0.7493055555555556</v>
       </c>
       <c r="E193" s="2" t="inlineStr">
         <is>
@@ -4274,61 +4312,59 @@
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B194" s="3" t="n">
-        <v>46262</v>
+        <v>46247</v>
       </c>
       <c r="C194" s="4" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="D194" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.2465277777777778</v>
+      </c>
+      <c r="D194" s="4" t="n">
+        <v>0.7270833333333333</v>
       </c>
       <c r="E194" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B195" s="3" t="n">
-        <v>46263</v>
+        <v>46249</v>
       </c>
       <c r="C195" s="4" t="n">
-        <v>0.2569444444444444</v>
+        <v>0.2395833333333333</v>
       </c>
       <c r="D195" s="4" t="n">
-        <v>0.7458333333333333</v>
+        <v>0.7388888888888889</v>
       </c>
       <c r="E195" s="2" t="inlineStr">
         <is>
-          <t>extra punch: 17:53</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B196" s="3" t="n">
-        <v>46264</v>
+        <v>46250</v>
       </c>
       <c r="C196" s="4" t="n">
-        <v>0.2590277777777778</v>
+        <v>0.2902777777777778</v>
       </c>
       <c r="D196" s="4" t="n">
-        <v>0.7541666666666667</v>
+        <v>0.7236111111111111</v>
       </c>
       <c r="E196" s="2" t="inlineStr">
         <is>
@@ -4339,59 +4375,80 @@
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B197" s="3" t="n">
-        <v>46265</v>
+        <v>46251</v>
       </c>
       <c r="C197" s="4" t="n">
-        <v>0.2777777777777778</v>
+        <v>0.2743055555555556</v>
       </c>
       <c r="D197" s="4" t="n">
-        <v>0.7513888888888889</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="E197" s="2" t="inlineStr">
         <is>
-          <t>corrected from a clearer re-scan photo later in the album</t>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B198" s="3" t="n">
+        <v>46252</v>
+      </c>
+      <c r="C198" s="4" t="n">
+        <v>0.2826388888888889</v>
+      </c>
+      <c r="D198" s="4" t="n">
+        <v>0.7451388888888889</v>
+      </c>
+      <c r="E198" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B199" s="3" t="n">
-        <v>46235</v>
+        <v>46253</v>
       </c>
       <c r="C199" s="4" t="n">
-        <v>0.2451388888888889</v>
+        <v>0.2763888888888889</v>
       </c>
       <c r="D199" s="4" t="n">
-        <v>0.7506944444444444</v>
+        <v>0.7298611111111111</v>
       </c>
       <c r="E199" s="2" t="inlineStr">
         <is>
-          <t>last day of month; final record</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B200" s="3" t="n">
-        <v>46236</v>
+        <v>46254</v>
       </c>
       <c r="C200" s="4" t="n">
-        <v>0.24375</v>
+        <v>0.275</v>
       </c>
       <c r="D200" s="4" t="n">
-        <v>0.7520833333333333</v>
+        <v>0.7256944444444444</v>
       </c>
       <c r="E200" s="2" t="inlineStr">
         <is>
@@ -4402,17 +4459,17 @@
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B201" s="3" t="n">
-        <v>46237</v>
+        <v>46256</v>
       </c>
       <c r="C201" s="4" t="n">
-        <v>0.24375</v>
+        <v>0.2805555555555556</v>
       </c>
       <c r="D201" s="4" t="n">
-        <v>0.7527777777777778</v>
+        <v>0.7513888888888889</v>
       </c>
       <c r="E201" s="2" t="inlineStr">
         <is>
@@ -4423,17 +4480,17 @@
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B202" s="3" t="n">
-        <v>46238</v>
+        <v>46261</v>
       </c>
       <c r="C202" s="4" t="n">
-        <v>0.2451388888888889</v>
+        <v>0.24375</v>
       </c>
       <c r="D202" s="4" t="n">
-        <v>0.7520833333333333</v>
+        <v>0.6763888888888889</v>
       </c>
       <c r="E202" s="2" t="inlineStr">
         <is>
@@ -4444,17 +4501,17 @@
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B203" s="3" t="n">
-        <v>46239</v>
+        <v>46263</v>
       </c>
       <c r="C203" s="4" t="n">
-        <v>0.2368055555555555</v>
+        <v>0.2965277777777778</v>
       </c>
       <c r="D203" s="4" t="n">
-        <v>0.7611111111111111</v>
+        <v>0.7472222222222222</v>
       </c>
       <c r="E203" s="2" t="inlineStr">
         <is>
@@ -4465,17 +4522,17 @@
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B204" s="3" t="n">
-        <v>46240</v>
+        <v>46264</v>
       </c>
       <c r="C204" s="4" t="n">
-        <v>0.2402777777777778</v>
+        <v>0.2888888888888889</v>
       </c>
       <c r="D204" s="4" t="n">
-        <v>0.7513888888888889</v>
+        <v>0.75</v>
       </c>
       <c r="E204" s="2" t="inlineStr">
         <is>
@@ -4486,84 +4543,59 @@
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B205" s="3" t="n">
-        <v>46242</v>
+        <v>46265</v>
       </c>
       <c r="C205" s="4" t="n">
-        <v>0.2430555555555556</v>
+        <v>0.2909722222222222</v>
       </c>
       <c r="D205" s="4" t="n">
-        <v>0.7548611111111111</v>
+        <v>0.75</v>
       </c>
       <c r="E205" s="2" t="inlineStr">
         <is>
           <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="B206" s="3" t="n">
-        <v>46246</v>
-      </c>
-      <c r="C206" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D206" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E206" s="2" t="inlineStr">
-        <is>
-          <t>PLEASE VERIFY: check-in/out times not captured (gap between source photos)</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B207" s="3" t="n">
-        <v>46247</v>
+        <v>46235</v>
       </c>
       <c r="C207" s="4" t="n">
-        <v>0.2444444444444444</v>
+        <v>0.2381944444444444</v>
       </c>
       <c r="D207" s="4" t="n">
-        <v>0.7576388888888889</v>
+        <v>0.7458333333333333</v>
       </c>
       <c r="E207" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>last day of month; final record</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B208" s="3" t="n">
-        <v>46249</v>
+        <v>46236</v>
       </c>
       <c r="C208" s="4" t="n">
-        <v>0.2381944444444444</v>
+        <v>0.2958333333333333</v>
       </c>
       <c r="D208" s="4" t="n">
-        <v>0.7513888888888889</v>
+        <v>0.7430555555555556</v>
       </c>
       <c r="E208" s="2" t="inlineStr">
         <is>
@@ -4574,17 +4606,17 @@
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B209" s="3" t="n">
-        <v>46250</v>
+        <v>46237</v>
       </c>
       <c r="C209" s="4" t="n">
-        <v>0.2354166666666667</v>
+        <v>0.3034722222222222</v>
       </c>
       <c r="D209" s="4" t="n">
-        <v>0.7520833333333333</v>
+        <v>0.7159722222222222</v>
       </c>
       <c r="E209" s="2" t="inlineStr">
         <is>
@@ -4595,17 +4627,17 @@
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B210" s="3" t="n">
-        <v>46251</v>
+        <v>46238</v>
       </c>
       <c r="C210" s="4" t="n">
-        <v>0.2395833333333333</v>
+        <v>0.2763888888888889</v>
       </c>
       <c r="D210" s="4" t="n">
-        <v>0.7541666666666667</v>
+        <v>0.7166666666666667</v>
       </c>
       <c r="E210" s="2" t="inlineStr">
         <is>
@@ -4616,17 +4648,17 @@
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B211" s="3" t="n">
-        <v>46252</v>
+        <v>46239</v>
       </c>
       <c r="C211" s="4" t="n">
-        <v>0.2451388888888889</v>
+        <v>0.3222222222222222</v>
       </c>
       <c r="D211" s="4" t="n">
-        <v>0.7527777777777778</v>
+        <v>0.7715277777777778</v>
       </c>
       <c r="E211" s="2" t="inlineStr">
         <is>
@@ -4637,17 +4669,17 @@
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B212" s="3" t="n">
-        <v>46253</v>
+        <v>46240</v>
       </c>
       <c r="C212" s="4" t="n">
-        <v>0.2423611111111111</v>
+        <v>0.30625</v>
       </c>
       <c r="D212" s="4" t="n">
-        <v>0.7506944444444444</v>
+        <v>0.7590277777777777</v>
       </c>
       <c r="E212" s="2" t="inlineStr">
         <is>
@@ -4658,17 +4690,17 @@
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B213" s="3" t="n">
-        <v>46254</v>
+        <v>46242</v>
       </c>
       <c r="C213" s="4" t="n">
-        <v>0.2402777777777778</v>
+        <v>0.3055555555555556</v>
       </c>
       <c r="D213" s="4" t="n">
-        <v>0.7520833333333333</v>
+        <v>0.7604166666666666</v>
       </c>
       <c r="E213" s="2" t="inlineStr">
         <is>
@@ -4679,14 +4711,14 @@
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B214" s="3" t="n">
-        <v>46256</v>
+        <v>46243</v>
       </c>
       <c r="C214" s="4" t="n">
-        <v>0.2402777777777778</v>
+        <v>0.2798611111111111</v>
       </c>
       <c r="D214" s="4" t="n">
         <v>0.75</v>
@@ -4700,17 +4732,17 @@
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B215" s="3" t="n">
-        <v>46257</v>
+        <v>46244</v>
       </c>
       <c r="C215" s="4" t="n">
-        <v>0.2458333333333333</v>
+        <v>0.2263888888888889</v>
       </c>
       <c r="D215" s="4" t="n">
-        <v>0.7527777777777778</v>
+        <v>0.75</v>
       </c>
       <c r="E215" s="2" t="inlineStr">
         <is>
@@ -4721,80 +4753,86 @@
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B216" s="3" t="n">
-        <v>46258</v>
+        <v>46245</v>
       </c>
       <c r="C216" s="4" t="n">
-        <v>0.2347222222222222</v>
-      </c>
-      <c r="D216" s="4" t="n">
-        <v>0.7520833333333333</v>
+        <v>0.3118055555555556</v>
+      </c>
+      <c r="D216" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E216" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B217" s="3" t="n">
-        <v>46259</v>
+        <v>46246</v>
       </c>
       <c r="C217" s="4" t="n">
-        <v>0.2368055555555555</v>
-      </c>
-      <c r="D217" s="4" t="n">
-        <v>0.7506944444444444</v>
+        <v>0.2986111111111111</v>
+      </c>
+      <c r="D217" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E217" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B218" s="3" t="n">
-        <v>46260</v>
+        <v>46247</v>
       </c>
       <c r="C218" s="4" t="n">
-        <v>0.2465277777777778</v>
-      </c>
-      <c r="D218" s="4" t="n">
-        <v>0.7555555555555555</v>
+        <v>0.3347222222222222</v>
+      </c>
+      <c r="D218" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E218" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B219" s="3" t="n">
-        <v>46261</v>
+        <v>46249</v>
       </c>
       <c r="C219" s="4" t="n">
-        <v>0.2472222222222222</v>
+        <v>0.2354166666666667</v>
       </c>
       <c r="D219" s="4" t="n">
-        <v>0.7513888888888889</v>
+        <v>0.75</v>
       </c>
       <c r="E219" s="2" t="inlineStr">
         <is>
@@ -4805,17 +4843,17 @@
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B220" s="3" t="n">
-        <v>46263</v>
+        <v>46250</v>
       </c>
       <c r="C220" s="4" t="n">
-        <v>0.2444444444444444</v>
+        <v>0.325</v>
       </c>
       <c r="D220" s="4" t="n">
-        <v>0.7548611111111111</v>
+        <v>0.7722222222222223</v>
       </c>
       <c r="E220" s="2" t="inlineStr">
         <is>
@@ -4826,17 +4864,17 @@
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B221" s="3" t="n">
-        <v>46264</v>
+        <v>46251</v>
       </c>
       <c r="C221" s="4" t="n">
-        <v>0.2423611111111111</v>
+        <v>0.3979166666666666</v>
       </c>
       <c r="D221" s="4" t="n">
-        <v>0.7513888888888889</v>
+        <v>0.7680555555555556</v>
       </c>
       <c r="E221" s="2" t="inlineStr">
         <is>
@@ -4847,59 +4885,82 @@
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B222" s="3" t="n">
-        <v>46265</v>
+        <v>46252</v>
       </c>
       <c r="C222" s="4" t="n">
-        <v>0.2361111111111111</v>
+        <v>0.3083333333333333</v>
       </c>
       <c r="D222" s="4" t="n">
-        <v>0.7520833333333333</v>
+        <v>0.7583333333333333</v>
       </c>
       <c r="E222" s="2" t="inlineStr">
         <is>
-          <t>corrected from a clearer re-scan photo later in the album</t>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B223" s="3" t="n">
+        <v>46253</v>
+      </c>
+      <c r="C223" s="4" t="n">
+        <v>0.475</v>
+      </c>
+      <c r="D223" s="4" t="n">
+        <v>0.7173611111111111</v>
+      </c>
+      <c r="E223" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B224" s="3" t="n">
-        <v>46235</v>
+        <v>46254</v>
       </c>
       <c r="C224" s="4" t="n">
-        <v>0.275</v>
-      </c>
-      <c r="D224" s="4" t="n">
-        <v>0.7854166666666667</v>
+        <v>0.3576388888888889</v>
+      </c>
+      <c r="D224" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E224" s="2" t="inlineStr">
         <is>
-          <t>last day of month; final record</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B225" s="3" t="n">
-        <v>46236</v>
+        <v>46256</v>
       </c>
       <c r="C225" s="4" t="n">
-        <v>0.2722222222222222</v>
+        <v>0.2069444444444444</v>
       </c>
       <c r="D225" s="4" t="n">
-        <v>0.7722222222222223</v>
+        <v>0.7243055555555555</v>
       </c>
       <c r="E225" s="2" t="inlineStr">
         <is>
@@ -4910,17 +4971,17 @@
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B226" s="3" t="n">
-        <v>46237</v>
+        <v>46257</v>
       </c>
       <c r="C226" s="4" t="n">
-        <v>0.2451388888888889</v>
+        <v>0.25</v>
       </c>
       <c r="D226" s="4" t="n">
-        <v>0.7201388888888889</v>
+        <v>0.7493055555555556</v>
       </c>
       <c r="E226" s="2" t="inlineStr">
         <is>
@@ -4931,17 +4992,17 @@
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B227" s="3" t="n">
-        <v>46238</v>
+        <v>46258</v>
       </c>
       <c r="C227" s="4" t="n">
-        <v>0.2729166666666666</v>
+        <v>0.3263888888888889</v>
       </c>
       <c r="D227" s="4" t="n">
-        <v>0.7527777777777778</v>
+        <v>0.7388888888888889</v>
       </c>
       <c r="E227" s="2" t="inlineStr">
         <is>
@@ -4952,17 +5013,17 @@
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B228" s="3" t="n">
-        <v>46239</v>
+        <v>46259</v>
       </c>
       <c r="C228" s="4" t="n">
-        <v>0.2756944444444445</v>
+        <v>0.2763888888888889</v>
       </c>
       <c r="D228" s="4" t="n">
-        <v>0.7152777777777778</v>
+        <v>0.7548611111111111</v>
       </c>
       <c r="E228" s="2" t="inlineStr">
         <is>
@@ -4973,40 +5034,38 @@
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B229" s="3" t="n">
-        <v>46240</v>
+        <v>46260</v>
       </c>
       <c r="C229" s="4" t="n">
-        <v>0.2715277777777778</v>
-      </c>
-      <c r="D229" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.3243055555555556</v>
+      </c>
+      <c r="D229" s="4" t="n">
+        <v>0.7534722222222222</v>
       </c>
       <c r="E229" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>extra punch: 17:56</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B230" s="3" t="n">
-        <v>46242</v>
+        <v>46261</v>
       </c>
       <c r="C230" s="4" t="n">
-        <v>0.2388888888888889</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="D230" s="4" t="n">
-        <v>0.6965277777777777</v>
+        <v>0.75</v>
       </c>
       <c r="E230" s="2" t="inlineStr">
         <is>
@@ -5017,17 +5076,17 @@
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B231" s="3" t="n">
-        <v>46243</v>
+        <v>46263</v>
       </c>
       <c r="C231" s="4" t="n">
-        <v>0.2451388888888889</v>
+        <v>0.2965277777777778</v>
       </c>
       <c r="D231" s="4" t="n">
-        <v>0.7694444444444445</v>
+        <v>0.7326388888888888</v>
       </c>
       <c r="E231" s="2" t="inlineStr">
         <is>
@@ -5038,101 +5097,80 @@
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B232" s="3" t="n">
-        <v>46244</v>
+        <v>46264</v>
       </c>
       <c r="C232" s="4" t="n">
-        <v>0.2298611111111111</v>
+        <v>0.2965277777777778</v>
       </c>
       <c r="D232" s="4" t="n">
         <v>0.75625</v>
       </c>
       <c r="E232" s="2" t="inlineStr">
         <is>
-          <t>extra punch: 06:48</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B233" s="3" t="n">
-        <v>46245</v>
+        <v>46265</v>
       </c>
       <c r="C233" s="4" t="n">
-        <v>0.275</v>
+        <v>0.2527777777777778</v>
       </c>
       <c r="D233" s="4" t="n">
-        <v>0.7618055555555555</v>
+        <v>0.7604166666666666</v>
       </c>
       <c r="E233" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="B234" s="3" t="n">
-        <v>46246</v>
-      </c>
-      <c r="C234" s="4" t="n">
-        <v>0.2694444444444444</v>
-      </c>
-      <c r="D234" s="4" t="n">
-        <v>0.7222222222222222</v>
-      </c>
-      <c r="E234" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>corrected from a clearer re-scan photo later in the album</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B235" s="3" t="n">
-        <v>46247</v>
+        <v>46235</v>
       </c>
       <c r="C235" s="4" t="n">
-        <v>0.3409722222222222</v>
+        <v>0.2590277777777778</v>
       </c>
       <c r="D235" s="4" t="n">
-        <v>0.7583333333333333</v>
+        <v>0.7319444444444444</v>
       </c>
       <c r="E235" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>last day of month; final record</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B236" s="3" t="n">
-        <v>46249</v>
+        <v>46236</v>
       </c>
       <c r="C236" s="4" t="n">
-        <v>0.2680555555555555</v>
+        <v>0.2972222222222222</v>
       </c>
       <c r="D236" s="4" t="n">
-        <v>0.7625</v>
+        <v>0.7430555555555556</v>
       </c>
       <c r="E236" s="2" t="inlineStr">
         <is>
@@ -5143,17 +5181,17 @@
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B237" s="3" t="n">
-        <v>46250</v>
+        <v>46237</v>
       </c>
       <c r="C237" s="4" t="n">
-        <v>0.3416666666666667</v>
+        <v>0.2618055555555556</v>
       </c>
       <c r="D237" s="4" t="n">
-        <v>0.7173611111111111</v>
+        <v>0.7472222222222222</v>
       </c>
       <c r="E237" s="2" t="inlineStr">
         <is>
@@ -5164,17 +5202,17 @@
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B238" s="3" t="n">
-        <v>46251</v>
+        <v>46238</v>
       </c>
       <c r="C238" s="4" t="n">
-        <v>0.3104166666666667</v>
+        <v>0.4965277777777778</v>
       </c>
       <c r="D238" s="4" t="n">
-        <v>0.7069444444444445</v>
+        <v>0.7506944444444444</v>
       </c>
       <c r="E238" s="2" t="inlineStr">
         <is>
@@ -5185,17 +5223,17 @@
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B239" s="3" t="n">
-        <v>46252</v>
+        <v>46239</v>
       </c>
       <c r="C239" s="4" t="n">
-        <v>0.3659722222222222</v>
+        <v>0.4743055555555555</v>
       </c>
       <c r="D239" s="4" t="n">
-        <v>0.7208333333333333</v>
+        <v>0.7722222222222223</v>
       </c>
       <c r="E239" s="2" t="inlineStr">
         <is>
@@ -5206,17 +5244,17 @@
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B240" s="3" t="n">
-        <v>46253</v>
+        <v>46240</v>
       </c>
       <c r="C240" s="4" t="n">
-        <v>0.2944444444444445</v>
+        <v>0.2409722222222222</v>
       </c>
       <c r="D240" s="4" t="n">
-        <v>0.7305555555555555</v>
+        <v>0.7625</v>
       </c>
       <c r="E240" s="2" t="inlineStr">
         <is>
@@ -5227,17 +5265,17 @@
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B241" s="3" t="n">
-        <v>46254</v>
+        <v>46242</v>
       </c>
       <c r="C241" s="4" t="n">
-        <v>0.4298611111111111</v>
+        <v>0.2201388888888889</v>
       </c>
       <c r="D241" s="4" t="n">
-        <v>0.70625</v>
+        <v>0.7618055555555555</v>
       </c>
       <c r="E241" s="2" t="inlineStr">
         <is>
@@ -5248,17 +5286,17 @@
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B242" s="3" t="n">
-        <v>46256</v>
+        <v>46243</v>
       </c>
       <c r="C242" s="4" t="n">
-        <v>0.2888888888888889</v>
+        <v>0.2395833333333333</v>
       </c>
       <c r="D242" s="4" t="n">
-        <v>0.7083333333333334</v>
+        <v>0.725</v>
       </c>
       <c r="E242" s="2" t="inlineStr">
         <is>
@@ -5269,17 +5307,17 @@
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B243" s="3" t="n">
-        <v>46257</v>
+        <v>46244</v>
       </c>
       <c r="C243" s="4" t="n">
-        <v>0.2444444444444444</v>
+        <v>0.2256944444444444</v>
       </c>
       <c r="D243" s="4" t="n">
-        <v>0.7076388888888889</v>
+        <v>0.7611111111111111</v>
       </c>
       <c r="E243" s="2" t="inlineStr">
         <is>
@@ -5290,17 +5328,17 @@
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B244" s="3" t="n">
-        <v>46258</v>
+        <v>46245</v>
       </c>
       <c r="C244" s="4" t="n">
-        <v>0.2784722222222222</v>
+        <v>0.2375</v>
       </c>
       <c r="D244" s="4" t="n">
-        <v>0.7055555555555556</v>
+        <v>0.7375</v>
       </c>
       <c r="E244" s="2" t="inlineStr">
         <is>
@@ -5311,17 +5349,17 @@
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B245" s="3" t="n">
-        <v>46259</v>
+        <v>46246</v>
       </c>
       <c r="C245" s="4" t="n">
-        <v>0.2854166666666667</v>
+        <v>0.2284722222222222</v>
       </c>
       <c r="D245" s="4" t="n">
-        <v>0.7222222222222222</v>
+        <v>0.7423611111111111</v>
       </c>
       <c r="E245" s="2" t="inlineStr">
         <is>
@@ -5332,38 +5370,40 @@
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B246" s="3" t="n">
-        <v>46260</v>
+        <v>46247</v>
       </c>
       <c r="C246" s="4" t="n">
-        <v>0.2375</v>
-      </c>
-      <c r="D246" s="4" t="n">
-        <v>0.7152777777777778</v>
+        <v>0.4402777777777778</v>
+      </c>
+      <c r="D246" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E246" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B247" s="3" t="n">
-        <v>46261</v>
+        <v>46249</v>
       </c>
       <c r="C247" s="4" t="n">
-        <v>0.4881944444444444</v>
+        <v>0.2354166666666667</v>
       </c>
       <c r="D247" s="4" t="n">
-        <v>0.7111111111111111</v>
+        <v>0.7611111111111111</v>
       </c>
       <c r="E247" s="2" t="inlineStr">
         <is>
@@ -5374,17 +5414,17 @@
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B248" s="3" t="n">
-        <v>46263</v>
+        <v>46250</v>
       </c>
       <c r="C248" s="4" t="n">
-        <v>0.2513888888888889</v>
+        <v>0.2409722222222222</v>
       </c>
       <c r="D248" s="4" t="n">
-        <v>0.7104166666666667</v>
+        <v>0.7381944444444445</v>
       </c>
       <c r="E248" s="2" t="inlineStr">
         <is>
@@ -5395,17 +5435,17 @@
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B249" s="3" t="n">
-        <v>46264</v>
+        <v>46251</v>
       </c>
       <c r="C249" s="4" t="n">
-        <v>0.2958333333333333</v>
+        <v>0.3416666666666667</v>
       </c>
       <c r="D249" s="4" t="n">
-        <v>0.7215277777777778</v>
+        <v>0.7326388888888888</v>
       </c>
       <c r="E249" s="2" t="inlineStr">
         <is>
@@ -5416,63 +5456,82 @@
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B250" s="3" t="n">
-        <v>46265</v>
-      </c>
-      <c r="C250" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>46252</v>
+      </c>
+      <c r="C250" s="4" t="n">
+        <v>0.2916666666666667</v>
       </c>
       <c r="D250" s="4" t="n">
-        <v>0.7097222222222223</v>
+        <v>0.7416666666666667</v>
       </c>
       <c r="E250" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B251" s="3" t="n">
+        <v>46253</v>
+      </c>
+      <c r="C251" s="4" t="n">
+        <v>0.2395833333333333</v>
+      </c>
+      <c r="D251" s="4" t="n">
+        <v>0.7416666666666667</v>
+      </c>
+      <c r="E251" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B252" s="3" t="n">
-        <v>46235</v>
+        <v>46254</v>
       </c>
       <c r="C252" s="4" t="n">
-        <v>0.3305555555555555</v>
+        <v>0.2472222222222222</v>
       </c>
       <c r="D252" s="4" t="n">
-        <v>0.7347222222222223</v>
+        <v>0.7243055555555555</v>
       </c>
       <c r="E252" s="2" t="inlineStr">
         <is>
-          <t>last day of month; final record</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B253" s="3" t="n">
-        <v>46236</v>
-      </c>
-      <c r="C253" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D253" s="4" t="n">
-        <v>0.3583333333333333</v>
+        <v>46256</v>
+      </c>
+      <c r="C253" s="4" t="n">
+        <v>0.2875</v>
+      </c>
+      <c r="D253" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E253" s="2" t="inlineStr">
         <is>
@@ -5483,17 +5542,17 @@
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B254" s="3" t="n">
-        <v>46237</v>
+        <v>46257</v>
       </c>
       <c r="C254" s="4" t="n">
-        <v>0.3291666666666667</v>
+        <v>0.2479166666666667</v>
       </c>
       <c r="D254" s="4" t="n">
-        <v>0.7111111111111111</v>
+        <v>0.7618055555555555</v>
       </c>
       <c r="E254" s="2" t="inlineStr">
         <is>
@@ -5504,17 +5563,17 @@
     <row r="255">
       <c r="A255" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B255" s="3" t="n">
-        <v>46238</v>
+        <v>46258</v>
       </c>
       <c r="C255" s="4" t="n">
-        <v>0.3305555555555555</v>
+        <v>0.2375</v>
       </c>
       <c r="D255" s="4" t="n">
-        <v>0.7263888888888889</v>
+        <v>0.7506944444444444</v>
       </c>
       <c r="E255" s="2" t="inlineStr">
         <is>
@@ -5525,40 +5584,38 @@
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B256" s="3" t="n">
-        <v>46239</v>
-      </c>
-      <c r="C256" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>46259</v>
+      </c>
+      <c r="C256" s="4" t="n">
+        <v>0.2375</v>
       </c>
       <c r="D256" s="4" t="n">
-        <v>0.7715277777777778</v>
+        <v>0.7597222222222222</v>
       </c>
       <c r="E256" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B257" s="3" t="n">
-        <v>46240</v>
+        <v>46260</v>
       </c>
       <c r="C257" s="4" t="n">
-        <v>0.3986111111111111</v>
+        <v>0.2479166666666667</v>
       </c>
       <c r="D257" s="4" t="n">
-        <v>0.7277777777777777</v>
+        <v>0.7555555555555555</v>
       </c>
       <c r="E257" s="2" t="inlineStr">
         <is>
@@ -5569,17 +5626,17 @@
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B258" s="3" t="n">
-        <v>46242</v>
+        <v>46261</v>
       </c>
       <c r="C258" s="4" t="n">
-        <v>0.2791666666666667</v>
+        <v>0.2493055555555556</v>
       </c>
       <c r="D258" s="4" t="n">
-        <v>0.7284722222222222</v>
+        <v>0.7944444444444444</v>
       </c>
       <c r="E258" s="2" t="inlineStr">
         <is>
@@ -5590,59 +5647,61 @@
     <row r="259">
       <c r="A259" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B259" s="3" t="n">
-        <v>46243</v>
+        <v>46262</v>
       </c>
       <c r="C259" s="4" t="n">
-        <v>0.2784722222222222</v>
-      </c>
-      <c r="D259" s="4" t="n">
-        <v>0.7555555555555555</v>
+        <v>0.25</v>
+      </c>
+      <c r="D259" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E259" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B260" s="3" t="n">
-        <v>46244</v>
+        <v>46263</v>
       </c>
       <c r="C260" s="4" t="n">
-        <v>0.2875</v>
+        <v>0.2569444444444444</v>
       </c>
       <c r="D260" s="4" t="n">
-        <v>0.7479166666666667</v>
+        <v>0.7458333333333333</v>
       </c>
       <c r="E260" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>extra punch: 17:53</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B261" s="3" t="n">
-        <v>46245</v>
+        <v>46264</v>
       </c>
       <c r="C261" s="4" t="n">
-        <v>0.3</v>
+        <v>0.2590277777777778</v>
       </c>
       <c r="D261" s="4" t="n">
-        <v>0.7465277777777778</v>
+        <v>0.7541666666666667</v>
       </c>
       <c r="E261" s="2" t="inlineStr">
         <is>
@@ -5653,80 +5712,59 @@
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B262" s="3" t="n">
-        <v>46246</v>
+        <v>46265</v>
       </c>
       <c r="C262" s="4" t="n">
-        <v>0.2548611111111111</v>
+        <v>0.2777777777777778</v>
       </c>
       <c r="D262" s="4" t="n">
-        <v>0.7222222222222222</v>
+        <v>0.7513888888888889</v>
       </c>
       <c r="E262" s="2" t="inlineStr">
         <is>
-          <t>extra punches: 07:44 06:16</t>
-        </is>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="B263" s="3" t="n">
-        <v>46247</v>
-      </c>
-      <c r="C263" s="4" t="n">
-        <v>0.3388888888888889</v>
-      </c>
-      <c r="D263" s="4" t="n">
-        <v>0.7236111111111111</v>
-      </c>
-      <c r="E263" s="2" t="inlineStr">
-        <is>
-          <t>extra punch: 17:21</t>
+          <t>corrected from a clearer re-scan photo later in the album</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B264" s="3" t="n">
-        <v>46249</v>
+        <v>46235</v>
       </c>
       <c r="C264" s="4" t="n">
-        <v>0.2423611111111111</v>
+        <v>0.2451388888888889</v>
       </c>
       <c r="D264" s="4" t="n">
-        <v>0.7270833333333333</v>
+        <v>0.7506944444444444</v>
       </c>
       <c r="E264" s="2" t="inlineStr">
         <is>
-          <t>extra punches: 17:27 07:28</t>
+          <t>last day of month; final record</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B265" s="3" t="n">
-        <v>46250</v>
+        <v>46236</v>
       </c>
       <c r="C265" s="4" t="n">
-        <v>0.3409722222222222</v>
+        <v>0.24375</v>
       </c>
       <c r="D265" s="4" t="n">
-        <v>0.7104166666666667</v>
+        <v>0.7520833333333333</v>
       </c>
       <c r="E265" s="2" t="inlineStr">
         <is>
@@ -5737,17 +5775,17 @@
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B266" s="3" t="n">
-        <v>46251</v>
+        <v>46237</v>
       </c>
       <c r="C266" s="4" t="n">
-        <v>0.2833333333333333</v>
+        <v>0.24375</v>
       </c>
       <c r="D266" s="4" t="n">
-        <v>0.7326388888888888</v>
+        <v>0.7527777777777778</v>
       </c>
       <c r="E266" s="2" t="inlineStr">
         <is>
@@ -5758,17 +5796,17 @@
     <row r="267">
       <c r="A267" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B267" s="3" t="n">
-        <v>46252</v>
+        <v>46238</v>
       </c>
       <c r="C267" s="4" t="n">
-        <v>0.28125</v>
+        <v>0.2451388888888889</v>
       </c>
       <c r="D267" s="4" t="n">
-        <v>0.7645833333333333</v>
+        <v>0.7520833333333333</v>
       </c>
       <c r="E267" s="2" t="inlineStr">
         <is>
@@ -5779,128 +5817,126 @@
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B268" s="3" t="n">
-        <v>46253</v>
+        <v>46239</v>
       </c>
       <c r="C268" s="4" t="n">
-        <v>0.3166666666666667</v>
+        <v>0.2368055555555555</v>
       </c>
       <c r="D268" s="4" t="n">
-        <v>0.74375</v>
+        <v>0.7611111111111111</v>
       </c>
       <c r="E268" s="2" t="inlineStr">
         <is>
-          <t>extra punch: 08:01</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B269" s="3" t="n">
-        <v>46254</v>
+        <v>46240</v>
       </c>
       <c r="C269" s="4" t="n">
-        <v>0.2868055555555555</v>
-      </c>
-      <c r="D269" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.2402777777777778</v>
+      </c>
+      <c r="D269" s="4" t="n">
+        <v>0.7513888888888889</v>
       </c>
       <c r="E269" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B270" s="3" t="n">
-        <v>46256</v>
-      </c>
-      <c r="C270" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>46242</v>
+      </c>
+      <c r="C270" s="4" t="n">
+        <v>0.2430555555555556</v>
       </c>
       <c r="D270" s="4" t="n">
-        <v>0.74375</v>
+        <v>0.7548611111111111</v>
       </c>
       <c r="E270" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B271" s="3" t="n">
-        <v>46257</v>
-      </c>
-      <c r="C271" s="4" t="n">
-        <v>0.2548611111111111</v>
-      </c>
-      <c r="D271" s="4" t="n">
-        <v>0.7569444444444444</v>
+        <v>46246</v>
+      </c>
+      <c r="C271" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D271" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E271" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>PLEASE VERIFY: check-in/out times not captured (gap between source photos)</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B272" s="3" t="n">
-        <v>46258</v>
-      </c>
-      <c r="C272" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>46247</v>
+      </c>
+      <c r="C272" s="4" t="n">
+        <v>0.2444444444444444</v>
       </c>
       <c r="D272" s="4" t="n">
-        <v>0.7506944444444444</v>
+        <v>0.7576388888888889</v>
       </c>
       <c r="E272" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B273" s="3" t="n">
-        <v>46259</v>
+        <v>46249</v>
       </c>
       <c r="C273" s="4" t="n">
-        <v>0.2868055555555555</v>
+        <v>0.2381944444444444</v>
       </c>
       <c r="D273" s="4" t="n">
-        <v>0.6895833333333333</v>
+        <v>0.7513888888888889</v>
       </c>
       <c r="E273" s="2" t="inlineStr">
         <is>
@@ -5911,40 +5947,38 @@
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B274" s="3" t="n">
-        <v>46260</v>
-      </c>
-      <c r="C274" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>46250</v>
+      </c>
+      <c r="C274" s="4" t="n">
+        <v>0.2354166666666667</v>
       </c>
       <c r="D274" s="4" t="n">
-        <v>0.6986111111111111</v>
+        <v>0.7520833333333333</v>
       </c>
       <c r="E274" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B275" s="3" t="n">
-        <v>46261</v>
+        <v>46251</v>
       </c>
       <c r="C275" s="4" t="n">
-        <v>0.2833333333333333</v>
+        <v>0.2395833333333333</v>
       </c>
       <c r="D275" s="4" t="n">
-        <v>0.8645833333333334</v>
+        <v>0.7541666666666667</v>
       </c>
       <c r="E275" s="2" t="inlineStr">
         <is>
@@ -5955,40 +5989,38 @@
     <row r="276">
       <c r="A276" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B276" s="3" t="n">
-        <v>46263</v>
-      </c>
-      <c r="C276" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>46252</v>
+      </c>
+      <c r="C276" s="4" t="n">
+        <v>0.2451388888888889</v>
       </c>
       <c r="D276" s="4" t="n">
-        <v>0.7291666666666666</v>
+        <v>0.7527777777777778</v>
       </c>
       <c r="E276" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B277" s="3" t="n">
-        <v>46264</v>
+        <v>46253</v>
       </c>
       <c r="C277" s="4" t="n">
-        <v>0.2798611111111111</v>
+        <v>0.2423611111111111</v>
       </c>
       <c r="D277" s="4" t="n">
-        <v>0.7472222222222222</v>
+        <v>0.7506944444444444</v>
       </c>
       <c r="E277" s="2" t="inlineStr">
         <is>
@@ -5999,59 +6031,80 @@
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B278" s="3" t="n">
-        <v>46265</v>
+        <v>46254</v>
       </c>
       <c r="C278" s="4" t="n">
-        <v>0.3888888888888889</v>
+        <v>0.2402777777777778</v>
       </c>
       <c r="D278" s="4" t="n">
-        <v>0.7215277777777778</v>
+        <v>0.7520833333333333</v>
       </c>
       <c r="E278" s="2" t="inlineStr">
         <is>
-          <t>corrected from a clearer re-scan photo later in the album</t>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B279" s="3" t="n">
+        <v>46256</v>
+      </c>
+      <c r="C279" s="4" t="n">
+        <v>0.2402777777777778</v>
+      </c>
+      <c r="D279" s="4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E279" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B280" s="3" t="n">
-        <v>46235</v>
+        <v>46257</v>
       </c>
       <c r="C280" s="4" t="n">
-        <v>0.2569444444444444</v>
+        <v>0.2458333333333333</v>
       </c>
       <c r="D280" s="4" t="n">
-        <v>0.7430555555555556</v>
+        <v>0.7527777777777778</v>
       </c>
       <c r="E280" s="2" t="inlineStr">
         <is>
-          <t>extra punch: 17:55; last day of month; final record</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B281" s="3" t="n">
-        <v>46236</v>
+        <v>46258</v>
       </c>
       <c r="C281" s="4" t="n">
-        <v>0.2201388888888889</v>
+        <v>0.2347222222222222</v>
       </c>
       <c r="D281" s="4" t="n">
-        <v>0.7381944444444445</v>
+        <v>0.7520833333333333</v>
       </c>
       <c r="E281" s="2" t="inlineStr">
         <is>
@@ -6062,38 +6115,38 @@
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B282" s="3" t="n">
-        <v>46237</v>
+        <v>46259</v>
       </c>
       <c r="C282" s="4" t="n">
-        <v>0.2472222222222222</v>
+        <v>0.2368055555555555</v>
       </c>
       <c r="D282" s="4" t="n">
-        <v>0.7402777777777778</v>
+        <v>0.7506944444444444</v>
       </c>
       <c r="E282" s="2" t="inlineStr">
         <is>
-          <t>extra punch: 17:46</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B283" s="3" t="n">
-        <v>46238</v>
+        <v>46260</v>
       </c>
       <c r="C283" s="4" t="n">
-        <v>0.2173611111111111</v>
+        <v>0.2465277777777778</v>
       </c>
       <c r="D283" s="4" t="n">
-        <v>0.7604166666666666</v>
+        <v>0.7555555555555555</v>
       </c>
       <c r="E283" s="2" t="inlineStr">
         <is>
@@ -6104,38 +6157,38 @@
     <row r="284">
       <c r="A284" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B284" s="3" t="n">
-        <v>46239</v>
+        <v>46261</v>
       </c>
       <c r="C284" s="4" t="n">
-        <v>0.2333333333333333</v>
+        <v>0.2472222222222222</v>
       </c>
       <c r="D284" s="4" t="n">
-        <v>0.7611111111111111</v>
+        <v>0.7513888888888889</v>
       </c>
       <c r="E284" s="2" t="inlineStr">
         <is>
-          <t>extra punch: 18:16</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B285" s="3" t="n">
-        <v>46240</v>
+        <v>46263</v>
       </c>
       <c r="C285" s="4" t="n">
-        <v>0.2277777777777778</v>
+        <v>0.2444444444444444</v>
       </c>
       <c r="D285" s="4" t="n">
-        <v>0.75625</v>
+        <v>0.7548611111111111</v>
       </c>
       <c r="E285" s="2" t="inlineStr">
         <is>
@@ -6146,101 +6199,80 @@
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B286" s="3" t="n">
-        <v>46242</v>
+        <v>46264</v>
       </c>
       <c r="C286" s="4" t="n">
-        <v>0.2479166666666667</v>
+        <v>0.2423611111111111</v>
       </c>
       <c r="D286" s="4" t="n">
-        <v>0.7291666666666666</v>
+        <v>0.7513888888888889</v>
       </c>
       <c r="E286" s="2" t="inlineStr">
         <is>
-          <t>extra punch: 07:09</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B287" s="3" t="n">
-        <v>46243</v>
+        <v>46265</v>
       </c>
       <c r="C287" s="4" t="n">
-        <v>0.2368055555555555</v>
+        <v>0.2361111111111111</v>
       </c>
       <c r="D287" s="4" t="n">
-        <v>0.6729166666666667</v>
+        <v>0.7520833333333333</v>
       </c>
       <c r="E287" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="288">
-      <c r="A288" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="B288" s="3" t="n">
-        <v>46244</v>
-      </c>
-      <c r="C288" s="4" t="n">
-        <v>0.2534722222222222</v>
-      </c>
-      <c r="D288" s="4" t="n">
-        <v>0.7479166666666667</v>
-      </c>
-      <c r="E288" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>corrected from a clearer re-scan photo later in the album</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B289" s="3" t="n">
-        <v>46245</v>
+        <v>46235</v>
       </c>
       <c r="C289" s="4" t="n">
-        <v>0.2541666666666667</v>
+        <v>0.275</v>
       </c>
       <c r="D289" s="4" t="n">
-        <v>0.7465277777777778</v>
+        <v>0.7854166666666667</v>
       </c>
       <c r="E289" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>last day of month; final record</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B290" s="3" t="n">
-        <v>46246</v>
+        <v>46236</v>
       </c>
       <c r="C290" s="4" t="n">
-        <v>0.2618055555555556</v>
+        <v>0.2722222222222222</v>
       </c>
       <c r="D290" s="4" t="n">
-        <v>0.75</v>
+        <v>0.7722222222222223</v>
       </c>
       <c r="E290" s="2" t="inlineStr">
         <is>
@@ -6251,17 +6283,17 @@
     <row r="291">
       <c r="A291" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B291" s="3" t="n">
-        <v>46247</v>
+        <v>46237</v>
       </c>
       <c r="C291" s="4" t="n">
-        <v>0.25625</v>
+        <v>0.2451388888888889</v>
       </c>
       <c r="D291" s="4" t="n">
-        <v>0.75</v>
+        <v>0.7201388888888889</v>
       </c>
       <c r="E291" s="2" t="inlineStr">
         <is>
@@ -6272,38 +6304,38 @@
     <row r="292">
       <c r="A292" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B292" s="3" t="n">
-        <v>46249</v>
+        <v>46238</v>
       </c>
       <c r="C292" s="4" t="n">
-        <v>0.2333333333333333</v>
+        <v>0.2729166666666666</v>
       </c>
       <c r="D292" s="4" t="n">
-        <v>0.7506944444444444</v>
+        <v>0.7527777777777778</v>
       </c>
       <c r="E292" s="2" t="inlineStr">
         <is>
-          <t>extra punch: 06:05</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B293" s="3" t="n">
-        <v>46250</v>
+        <v>46239</v>
       </c>
       <c r="C293" s="4" t="n">
-        <v>0.25625</v>
+        <v>0.2756944444444445</v>
       </c>
       <c r="D293" s="4" t="n">
-        <v>0.7458333333333333</v>
+        <v>0.7152777777777778</v>
       </c>
       <c r="E293" s="2" t="inlineStr">
         <is>
@@ -6314,38 +6346,40 @@
     <row r="294">
       <c r="A294" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B294" s="3" t="n">
-        <v>46251</v>
+        <v>46240</v>
       </c>
       <c r="C294" s="4" t="n">
-        <v>0.2541666666666667</v>
-      </c>
-      <c r="D294" s="4" t="n">
-        <v>0.7555555555555555</v>
+        <v>0.2715277777777778</v>
+      </c>
+      <c r="D294" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E294" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B295" s="3" t="n">
-        <v>46252</v>
+        <v>46242</v>
       </c>
       <c r="C295" s="4" t="n">
-        <v>0.2395833333333333</v>
+        <v>0.2388888888888889</v>
       </c>
       <c r="D295" s="4" t="n">
-        <v>0.7611111111111111</v>
+        <v>0.6965277777777777</v>
       </c>
       <c r="E295" s="2" t="inlineStr">
         <is>
@@ -6356,17 +6390,17 @@
     <row r="296">
       <c r="A296" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B296" s="3" t="n">
-        <v>46253</v>
+        <v>46243</v>
       </c>
       <c r="C296" s="4" t="n">
-        <v>0.2527777777777778</v>
+        <v>0.2451388888888889</v>
       </c>
       <c r="D296" s="4" t="n">
-        <v>0.7423611111111111</v>
+        <v>0.7694444444444445</v>
       </c>
       <c r="E296" s="2" t="inlineStr">
         <is>
@@ -6377,59 +6411,59 @@
     <row r="297">
       <c r="A297" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B297" s="3" t="n">
-        <v>46254</v>
+        <v>46244</v>
       </c>
       <c r="C297" s="4" t="n">
-        <v>0.2583333333333334</v>
+        <v>0.2298611111111111</v>
       </c>
       <c r="D297" s="4" t="n">
-        <v>0.7451388888888889</v>
+        <v>0.75625</v>
       </c>
       <c r="E297" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>extra punch: 06:48</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B298" s="3" t="n">
-        <v>46256</v>
+        <v>46245</v>
       </c>
       <c r="C298" s="4" t="n">
-        <v>0.2402777777777778</v>
+        <v>0.275</v>
       </c>
       <c r="D298" s="4" t="n">
-        <v>0.74375</v>
+        <v>0.7618055555555555</v>
       </c>
       <c r="E298" s="2" t="inlineStr">
         <is>
-          <t>extra punches: 17:51 06:13</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B299" s="3" t="n">
-        <v>46257</v>
+        <v>46246</v>
       </c>
       <c r="C299" s="4" t="n">
-        <v>0.2402777777777778</v>
+        <v>0.2694444444444444</v>
       </c>
       <c r="D299" s="4" t="n">
-        <v>0.75</v>
+        <v>0.7222222222222222</v>
       </c>
       <c r="E299" s="2" t="inlineStr">
         <is>
@@ -6440,59 +6474,59 @@
     <row r="300">
       <c r="A300" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B300" s="3" t="n">
-        <v>46258</v>
+        <v>46247</v>
       </c>
       <c r="C300" s="4" t="n">
-        <v>0.2319444444444445</v>
+        <v>0.3409722222222222</v>
       </c>
       <c r="D300" s="4" t="n">
-        <v>0.7513888888888889</v>
+        <v>0.7583333333333333</v>
       </c>
       <c r="E300" s="2" t="inlineStr">
         <is>
-          <t>extra punch: 18:02</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B301" s="3" t="n">
-        <v>46259</v>
+        <v>46249</v>
       </c>
       <c r="C301" s="4" t="n">
-        <v>0.3555555555555556</v>
+        <v>0.2680555555555555</v>
       </c>
       <c r="D301" s="4" t="n">
-        <v>0.7541666666666667</v>
+        <v>0.7625</v>
       </c>
       <c r="E301" s="2" t="inlineStr">
         <is>
-          <t>extra punch: 06:33</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B302" s="3" t="n">
-        <v>46260</v>
+        <v>46250</v>
       </c>
       <c r="C302" s="4" t="n">
-        <v>0.2555555555555555</v>
+        <v>0.3416666666666667</v>
       </c>
       <c r="D302" s="4" t="n">
-        <v>0.7541666666666667</v>
+        <v>0.7173611111111111</v>
       </c>
       <c r="E302" s="2" t="inlineStr">
         <is>
@@ -6503,17 +6537,17 @@
     <row r="303">
       <c r="A303" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B303" s="3" t="n">
-        <v>46261</v>
+        <v>46251</v>
       </c>
       <c r="C303" s="4" t="n">
-        <v>0.2722222222222222</v>
+        <v>0.3104166666666667</v>
       </c>
       <c r="D303" s="4" t="n">
-        <v>0.7569444444444444</v>
+        <v>0.7069444444444445</v>
       </c>
       <c r="E303" s="2" t="inlineStr">
         <is>
@@ -6524,17 +6558,17 @@
     <row r="304">
       <c r="A304" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B304" s="3" t="n">
-        <v>46263</v>
+        <v>46252</v>
       </c>
       <c r="C304" s="4" t="n">
-        <v>0.2201388888888889</v>
+        <v>0.3659722222222222</v>
       </c>
       <c r="D304" s="4" t="n">
-        <v>0.7444444444444445</v>
+        <v>0.7208333333333333</v>
       </c>
       <c r="E304" s="2" t="inlineStr">
         <is>
@@ -6545,17 +6579,17 @@
     <row r="305">
       <c r="A305" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B305" s="3" t="n">
-        <v>46264</v>
+        <v>46253</v>
       </c>
       <c r="C305" s="4" t="n">
-        <v>0.2555555555555555</v>
+        <v>0.2944444444444445</v>
       </c>
       <c r="D305" s="4" t="n">
-        <v>0.7458333333333333</v>
+        <v>0.7305555555555555</v>
       </c>
       <c r="E305" s="2" t="inlineStr">
         <is>
@@ -6566,19 +6600,1358 @@
     <row r="306">
       <c r="A306" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B306" s="3" t="n">
+        <v>46254</v>
+      </c>
+      <c r="C306" s="4" t="n">
+        <v>0.4298611111111111</v>
+      </c>
+      <c r="D306" s="4" t="n">
+        <v>0.70625</v>
+      </c>
+      <c r="E306" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B307" s="3" t="n">
+        <v>46256</v>
+      </c>
+      <c r="C307" s="4" t="n">
+        <v>0.2888888888888889</v>
+      </c>
+      <c r="D307" s="4" t="n">
+        <v>0.7083333333333334</v>
+      </c>
+      <c r="E307" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B308" s="3" t="n">
+        <v>46257</v>
+      </c>
+      <c r="C308" s="4" t="n">
+        <v>0.2444444444444444</v>
+      </c>
+      <c r="D308" s="4" t="n">
+        <v>0.7076388888888889</v>
+      </c>
+      <c r="E308" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B309" s="3" t="n">
+        <v>46258</v>
+      </c>
+      <c r="C309" s="4" t="n">
+        <v>0.2784722222222222</v>
+      </c>
+      <c r="D309" s="4" t="n">
+        <v>0.7055555555555556</v>
+      </c>
+      <c r="E309" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B310" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="C310" s="4" t="n">
+        <v>0.2854166666666667</v>
+      </c>
+      <c r="D310" s="4" t="n">
+        <v>0.7222222222222222</v>
+      </c>
+      <c r="E310" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B311" s="3" t="n">
+        <v>46260</v>
+      </c>
+      <c r="C311" s="4" t="n">
+        <v>0.2375</v>
+      </c>
+      <c r="D311" s="4" t="n">
+        <v>0.7152777777777778</v>
+      </c>
+      <c r="E311" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B312" s="3" t="n">
+        <v>46261</v>
+      </c>
+      <c r="C312" s="4" t="n">
+        <v>0.4881944444444444</v>
+      </c>
+      <c r="D312" s="4" t="n">
+        <v>0.7111111111111111</v>
+      </c>
+      <c r="E312" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B313" s="3" t="n">
+        <v>46263</v>
+      </c>
+      <c r="C313" s="4" t="n">
+        <v>0.2513888888888889</v>
+      </c>
+      <c r="D313" s="4" t="n">
+        <v>0.7104166666666667</v>
+      </c>
+      <c r="E313" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B314" s="3" t="n">
+        <v>46264</v>
+      </c>
+      <c r="C314" s="4" t="n">
+        <v>0.2958333333333333</v>
+      </c>
+      <c r="D314" s="4" t="n">
+        <v>0.7215277777777778</v>
+      </c>
+      <c r="E314" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B315" s="3" t="n">
+        <v>46265</v>
+      </c>
+      <c r="C315" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D315" s="4" t="n">
+        <v>0.7097222222222223</v>
+      </c>
+      <c r="E315" s="2" t="inlineStr">
+        <is>
+          <t>single punch only</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B317" s="3" t="n">
+        <v>46235</v>
+      </c>
+      <c r="C317" s="4" t="n">
+        <v>0.3305555555555555</v>
+      </c>
+      <c r="D317" s="4" t="n">
+        <v>0.7347222222222223</v>
+      </c>
+      <c r="E317" s="2" t="inlineStr">
+        <is>
+          <t>last day of month; final record</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B318" s="3" t="n">
+        <v>46236</v>
+      </c>
+      <c r="C318" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D318" s="4" t="n">
+        <v>0.3583333333333333</v>
+      </c>
+      <c r="E318" s="2" t="inlineStr">
+        <is>
+          <t>single punch only</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B319" s="3" t="n">
+        <v>46237</v>
+      </c>
+      <c r="C319" s="4" t="n">
+        <v>0.3291666666666667</v>
+      </c>
+      <c r="D319" s="4" t="n">
+        <v>0.7111111111111111</v>
+      </c>
+      <c r="E319" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B320" s="3" t="n">
+        <v>46238</v>
+      </c>
+      <c r="C320" s="4" t="n">
+        <v>0.3305555555555555</v>
+      </c>
+      <c r="D320" s="4" t="n">
+        <v>0.7263888888888889</v>
+      </c>
+      <c r="E320" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B321" s="3" t="n">
+        <v>46239</v>
+      </c>
+      <c r="C321" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D321" s="4" t="n">
+        <v>0.7715277777777778</v>
+      </c>
+      <c r="E321" s="2" t="inlineStr">
+        <is>
+          <t>single punch only</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B322" s="3" t="n">
+        <v>46240</v>
+      </c>
+      <c r="C322" s="4" t="n">
+        <v>0.3986111111111111</v>
+      </c>
+      <c r="D322" s="4" t="n">
+        <v>0.7277777777777777</v>
+      </c>
+      <c r="E322" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B323" s="3" t="n">
+        <v>46242</v>
+      </c>
+      <c r="C323" s="4" t="n">
+        <v>0.2791666666666667</v>
+      </c>
+      <c r="D323" s="4" t="n">
+        <v>0.7284722222222222</v>
+      </c>
+      <c r="E323" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B324" s="3" t="n">
+        <v>46243</v>
+      </c>
+      <c r="C324" s="4" t="n">
+        <v>0.2784722222222222</v>
+      </c>
+      <c r="D324" s="4" t="n">
+        <v>0.7555555555555555</v>
+      </c>
+      <c r="E324" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B325" s="3" t="n">
+        <v>46244</v>
+      </c>
+      <c r="C325" s="4" t="n">
+        <v>0.2875</v>
+      </c>
+      <c r="D325" s="4" t="n">
+        <v>0.7479166666666667</v>
+      </c>
+      <c r="E325" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B326" s="3" t="n">
+        <v>46245</v>
+      </c>
+      <c r="C326" s="4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D326" s="4" t="n">
+        <v>0.7465277777777778</v>
+      </c>
+      <c r="E326" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B327" s="3" t="n">
+        <v>46246</v>
+      </c>
+      <c r="C327" s="4" t="n">
+        <v>0.2548611111111111</v>
+      </c>
+      <c r="D327" s="4" t="n">
+        <v>0.7222222222222222</v>
+      </c>
+      <c r="E327" s="2" t="inlineStr">
+        <is>
+          <t>extra punches: 07:44 06:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B328" s="3" t="n">
+        <v>46247</v>
+      </c>
+      <c r="C328" s="4" t="n">
+        <v>0.3388888888888889</v>
+      </c>
+      <c r="D328" s="4" t="n">
+        <v>0.7236111111111111</v>
+      </c>
+      <c r="E328" s="2" t="inlineStr">
+        <is>
+          <t>extra punch: 17:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B329" s="3" t="n">
+        <v>46249</v>
+      </c>
+      <c r="C329" s="4" t="n">
+        <v>0.2423611111111111</v>
+      </c>
+      <c r="D329" s="4" t="n">
+        <v>0.7270833333333333</v>
+      </c>
+      <c r="E329" s="2" t="inlineStr">
+        <is>
+          <t>extra punches: 17:27 07:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B330" s="3" t="n">
+        <v>46250</v>
+      </c>
+      <c r="C330" s="4" t="n">
+        <v>0.3409722222222222</v>
+      </c>
+      <c r="D330" s="4" t="n">
+        <v>0.7104166666666667</v>
+      </c>
+      <c r="E330" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B331" s="3" t="n">
+        <v>46251</v>
+      </c>
+      <c r="C331" s="4" t="n">
+        <v>0.2833333333333333</v>
+      </c>
+      <c r="D331" s="4" t="n">
+        <v>0.7326388888888888</v>
+      </c>
+      <c r="E331" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B332" s="3" t="n">
+        <v>46252</v>
+      </c>
+      <c r="C332" s="4" t="n">
+        <v>0.28125</v>
+      </c>
+      <c r="D332" s="4" t="n">
+        <v>0.7645833333333333</v>
+      </c>
+      <c r="E332" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B333" s="3" t="n">
+        <v>46253</v>
+      </c>
+      <c r="C333" s="4" t="n">
+        <v>0.3166666666666667</v>
+      </c>
+      <c r="D333" s="4" t="n">
+        <v>0.74375</v>
+      </c>
+      <c r="E333" s="2" t="inlineStr">
+        <is>
+          <t>extra punch: 08:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B334" s="3" t="n">
+        <v>46254</v>
+      </c>
+      <c r="C334" s="4" t="n">
+        <v>0.2868055555555555</v>
+      </c>
+      <c r="D334" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E334" s="2" t="inlineStr">
+        <is>
+          <t>single punch only</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B335" s="3" t="n">
+        <v>46256</v>
+      </c>
+      <c r="C335" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D335" s="4" t="n">
+        <v>0.74375</v>
+      </c>
+      <c r="E335" s="2" t="inlineStr">
+        <is>
+          <t>single punch only</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B336" s="3" t="n">
+        <v>46257</v>
+      </c>
+      <c r="C336" s="4" t="n">
+        <v>0.2548611111111111</v>
+      </c>
+      <c r="D336" s="4" t="n">
+        <v>0.7569444444444444</v>
+      </c>
+      <c r="E336" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B337" s="3" t="n">
+        <v>46258</v>
+      </c>
+      <c r="C337" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D337" s="4" t="n">
+        <v>0.7506944444444444</v>
+      </c>
+      <c r="E337" s="2" t="inlineStr">
+        <is>
+          <t>single punch only</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B338" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="C338" s="4" t="n">
+        <v>0.2868055555555555</v>
+      </c>
+      <c r="D338" s="4" t="n">
+        <v>0.6895833333333333</v>
+      </c>
+      <c r="E338" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B339" s="3" t="n">
+        <v>46260</v>
+      </c>
+      <c r="C339" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D339" s="4" t="n">
+        <v>0.6986111111111111</v>
+      </c>
+      <c r="E339" s="2" t="inlineStr">
+        <is>
+          <t>single punch only</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B340" s="3" t="n">
+        <v>46261</v>
+      </c>
+      <c r="C340" s="4" t="n">
+        <v>0.2833333333333333</v>
+      </c>
+      <c r="D340" s="4" t="n">
+        <v>0.8645833333333334</v>
+      </c>
+      <c r="E340" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B341" s="3" t="n">
+        <v>46263</v>
+      </c>
+      <c r="C341" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D341" s="4" t="n">
+        <v>0.7291666666666666</v>
+      </c>
+      <c r="E341" s="2" t="inlineStr">
+        <is>
+          <t>single punch only</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B342" s="3" t="n">
+        <v>46264</v>
+      </c>
+      <c r="C342" s="4" t="n">
+        <v>0.2798611111111111</v>
+      </c>
+      <c r="D342" s="4" t="n">
+        <v>0.7472222222222222</v>
+      </c>
+      <c r="E342" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B343" s="3" t="n">
+        <v>46265</v>
+      </c>
+      <c r="C343" s="4" t="n">
+        <v>0.3888888888888889</v>
+      </c>
+      <c r="D343" s="4" t="n">
+        <v>0.7215277777777778</v>
+      </c>
+      <c r="E343" s="2" t="inlineStr">
+        <is>
+          <t>corrected from a clearer re-scan photo later in the album</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="B306" s="3" t="n">
+      <c r="B345" s="3" t="n">
+        <v>46235</v>
+      </c>
+      <c r="C345" s="4" t="n">
+        <v>0.2569444444444444</v>
+      </c>
+      <c r="D345" s="4" t="n">
+        <v>0.7430555555555556</v>
+      </c>
+      <c r="E345" s="2" t="inlineStr">
+        <is>
+          <t>extra punch: 17:55; last day of month; final record</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B346" s="3" t="n">
+        <v>46236</v>
+      </c>
+      <c r="C346" s="4" t="n">
+        <v>0.2201388888888889</v>
+      </c>
+      <c r="D346" s="4" t="n">
+        <v>0.7381944444444445</v>
+      </c>
+      <c r="E346" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B347" s="3" t="n">
+        <v>46237</v>
+      </c>
+      <c r="C347" s="4" t="n">
+        <v>0.2472222222222222</v>
+      </c>
+      <c r="D347" s="4" t="n">
+        <v>0.7402777777777778</v>
+      </c>
+      <c r="E347" s="2" t="inlineStr">
+        <is>
+          <t>extra punch: 17:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B348" s="3" t="n">
+        <v>46238</v>
+      </c>
+      <c r="C348" s="4" t="n">
+        <v>0.2173611111111111</v>
+      </c>
+      <c r="D348" s="4" t="n">
+        <v>0.7604166666666666</v>
+      </c>
+      <c r="E348" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B349" s="3" t="n">
+        <v>46239</v>
+      </c>
+      <c r="C349" s="4" t="n">
+        <v>0.2333333333333333</v>
+      </c>
+      <c r="D349" s="4" t="n">
+        <v>0.7611111111111111</v>
+      </c>
+      <c r="E349" s="2" t="inlineStr">
+        <is>
+          <t>extra punch: 18:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B350" s="3" t="n">
+        <v>46240</v>
+      </c>
+      <c r="C350" s="4" t="n">
+        <v>0.2277777777777778</v>
+      </c>
+      <c r="D350" s="4" t="n">
+        <v>0.75625</v>
+      </c>
+      <c r="E350" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B351" s="3" t="n">
+        <v>46242</v>
+      </c>
+      <c r="C351" s="4" t="n">
+        <v>0.2479166666666667</v>
+      </c>
+      <c r="D351" s="4" t="n">
+        <v>0.7291666666666666</v>
+      </c>
+      <c r="E351" s="2" t="inlineStr">
+        <is>
+          <t>extra punch: 07:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B352" s="3" t="n">
+        <v>46243</v>
+      </c>
+      <c r="C352" s="4" t="n">
+        <v>0.2368055555555555</v>
+      </c>
+      <c r="D352" s="4" t="n">
+        <v>0.6729166666666667</v>
+      </c>
+      <c r="E352" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B353" s="3" t="n">
+        <v>46244</v>
+      </c>
+      <c r="C353" s="4" t="n">
+        <v>0.2534722222222222</v>
+      </c>
+      <c r="D353" s="4" t="n">
+        <v>0.7479166666666667</v>
+      </c>
+      <c r="E353" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B354" s="3" t="n">
+        <v>46245</v>
+      </c>
+      <c r="C354" s="4" t="n">
+        <v>0.2541666666666667</v>
+      </c>
+      <c r="D354" s="4" t="n">
+        <v>0.7465277777777778</v>
+      </c>
+      <c r="E354" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B355" s="3" t="n">
+        <v>46246</v>
+      </c>
+      <c r="C355" s="4" t="n">
+        <v>0.2618055555555556</v>
+      </c>
+      <c r="D355" s="4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E355" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B356" s="3" t="n">
+        <v>46247</v>
+      </c>
+      <c r="C356" s="4" t="n">
+        <v>0.25625</v>
+      </c>
+      <c r="D356" s="4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E356" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B357" s="3" t="n">
+        <v>46249</v>
+      </c>
+      <c r="C357" s="4" t="n">
+        <v>0.2333333333333333</v>
+      </c>
+      <c r="D357" s="4" t="n">
+        <v>0.7506944444444444</v>
+      </c>
+      <c r="E357" s="2" t="inlineStr">
+        <is>
+          <t>extra punch: 06:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B358" s="3" t="n">
+        <v>46250</v>
+      </c>
+      <c r="C358" s="4" t="n">
+        <v>0.25625</v>
+      </c>
+      <c r="D358" s="4" t="n">
+        <v>0.7458333333333333</v>
+      </c>
+      <c r="E358" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B359" s="3" t="n">
+        <v>46251</v>
+      </c>
+      <c r="C359" s="4" t="n">
+        <v>0.2541666666666667</v>
+      </c>
+      <c r="D359" s="4" t="n">
+        <v>0.7555555555555555</v>
+      </c>
+      <c r="E359" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B360" s="3" t="n">
+        <v>46252</v>
+      </c>
+      <c r="C360" s="4" t="n">
+        <v>0.2395833333333333</v>
+      </c>
+      <c r="D360" s="4" t="n">
+        <v>0.7611111111111111</v>
+      </c>
+      <c r="E360" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B361" s="3" t="n">
+        <v>46253</v>
+      </c>
+      <c r="C361" s="4" t="n">
+        <v>0.2527777777777778</v>
+      </c>
+      <c r="D361" s="4" t="n">
+        <v>0.7423611111111111</v>
+      </c>
+      <c r="E361" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B362" s="3" t="n">
+        <v>46254</v>
+      </c>
+      <c r="C362" s="4" t="n">
+        <v>0.2583333333333334</v>
+      </c>
+      <c r="D362" s="4" t="n">
+        <v>0.7451388888888889</v>
+      </c>
+      <c r="E362" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B363" s="3" t="n">
+        <v>46256</v>
+      </c>
+      <c r="C363" s="4" t="n">
+        <v>0.2402777777777778</v>
+      </c>
+      <c r="D363" s="4" t="n">
+        <v>0.74375</v>
+      </c>
+      <c r="E363" s="2" t="inlineStr">
+        <is>
+          <t>extra punches: 17:51 06:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B364" s="3" t="n">
+        <v>46257</v>
+      </c>
+      <c r="C364" s="4" t="n">
+        <v>0.2402777777777778</v>
+      </c>
+      <c r="D364" s="4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E364" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B365" s="3" t="n">
+        <v>46258</v>
+      </c>
+      <c r="C365" s="4" t="n">
+        <v>0.2319444444444445</v>
+      </c>
+      <c r="D365" s="4" t="n">
+        <v>0.7513888888888889</v>
+      </c>
+      <c r="E365" s="2" t="inlineStr">
+        <is>
+          <t>extra punch: 18:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B366" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="C366" s="4" t="n">
+        <v>0.3555555555555556</v>
+      </c>
+      <c r="D366" s="4" t="n">
+        <v>0.7541666666666667</v>
+      </c>
+      <c r="E366" s="2" t="inlineStr">
+        <is>
+          <t>extra punch: 06:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B367" s="3" t="n">
+        <v>46260</v>
+      </c>
+      <c r="C367" s="4" t="n">
+        <v>0.2555555555555555</v>
+      </c>
+      <c r="D367" s="4" t="n">
+        <v>0.7541666666666667</v>
+      </c>
+      <c r="E367" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B368" s="3" t="n">
+        <v>46261</v>
+      </c>
+      <c r="C368" s="4" t="n">
+        <v>0.2722222222222222</v>
+      </c>
+      <c r="D368" s="4" t="n">
+        <v>0.7569444444444444</v>
+      </c>
+      <c r="E368" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B369" s="3" t="n">
+        <v>46263</v>
+      </c>
+      <c r="C369" s="4" t="n">
+        <v>0.2201388888888889</v>
+      </c>
+      <c r="D369" s="4" t="n">
+        <v>0.7444444444444445</v>
+      </c>
+      <c r="E369" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B370" s="3" t="n">
+        <v>46264</v>
+      </c>
+      <c r="C370" s="4" t="n">
+        <v>0.2555555555555555</v>
+      </c>
+      <c r="D370" s="4" t="n">
+        <v>0.7458333333333333</v>
+      </c>
+      <c r="E370" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B371" s="3" t="n">
         <v>46265</v>
       </c>
-      <c r="C306" s="4" t="n">
+      <c r="C371" s="4" t="n">
         <v>0.2569444444444444</v>
       </c>
-      <c r="D306" s="4" t="n">
+      <c r="D371" s="4" t="n">
         <v>0.7527777777777778</v>
       </c>
-      <c r="E306" s="2" t="inlineStr">
+      <c r="E371" s="2" t="inlineStr">
         <is>
           <t>corrected from a clearer re-scan photo later in the album</t>
         </is>

--- a/output/timesheet.xlsx
+++ b/output/timesheet.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E371"/>
+  <dimension ref="A1:E444"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2157,21 +2157,17 @@
         </is>
       </c>
       <c r="B84" s="3" t="n">
-        <v>46260</v>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>46235</v>
+      </c>
+      <c r="C84" s="4" t="n">
+        <v>0.3034722222222222</v>
+      </c>
+      <c r="D84" s="4" t="n">
+        <v>0.7076388888888889</v>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>PLEASE VERIFY: check-in/out times not captured (gap between source photos)</t>
+          <t>last day of month; final record</t>
         </is>
       </c>
     </row>
@@ -2182,13 +2178,13 @@
         </is>
       </c>
       <c r="B85" s="3" t="n">
-        <v>46261</v>
+        <v>46236</v>
       </c>
       <c r="C85" s="4" t="n">
-        <v>0.2826388888888889</v>
+        <v>0.2916666666666667</v>
       </c>
       <c r="D85" s="4" t="n">
-        <v>0.7861111111111111</v>
+        <v>0.7986111111111112</v>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
@@ -2203,13 +2199,13 @@
         </is>
       </c>
       <c r="B86" s="3" t="n">
-        <v>46263</v>
+        <v>46237</v>
       </c>
       <c r="C86" s="4" t="n">
-        <v>0.2993055555555555</v>
+        <v>0.3291666666666667</v>
       </c>
       <c r="D86" s="4" t="n">
-        <v>0.7708333333333334</v>
+        <v>0.7520833333333333</v>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
@@ -2224,13 +2220,13 @@
         </is>
       </c>
       <c r="B87" s="3" t="n">
-        <v>46264</v>
+        <v>46238</v>
       </c>
       <c r="C87" s="4" t="n">
-        <v>0.30625</v>
+        <v>0.3041666666666666</v>
       </c>
       <c r="D87" s="4" t="n">
-        <v>0.6805555555555556</v>
+        <v>0.7597222222222222</v>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
@@ -2245,15 +2241,36 @@
         </is>
       </c>
       <c r="B88" s="3" t="n">
-        <v>46265</v>
+        <v>46239</v>
       </c>
       <c r="C88" s="4" t="n">
-        <v>0.2472222222222222</v>
+        <v>0.3076388888888889</v>
       </c>
       <c r="D88" s="4" t="n">
-        <v>0.7555555555555555</v>
+        <v>0.7715277777777778</v>
       </c>
       <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B89" s="3" t="n">
+        <v>46240</v>
+      </c>
+      <c r="C89" s="4" t="n">
+        <v>0.2993055555555555</v>
+      </c>
+      <c r="D89" s="4" t="n">
+        <v>0.7493055555555556</v>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2262,113 +2279,124 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B90" s="3" t="n">
-        <v>46258</v>
-      </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>46242</v>
+      </c>
+      <c r="C90" s="4" t="n">
+        <v>0.3138888888888889</v>
+      </c>
+      <c r="D90" s="4" t="n">
+        <v>0.7673611111111112</v>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>PLEASE VERIFY: check-in/out time not captured (gap between source photos)</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B91" s="3" t="n">
-        <v>46259</v>
-      </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>46243</v>
+      </c>
+      <c r="C91" s="4" t="n">
+        <v>0.3041666666666666</v>
       </c>
       <c r="D91" s="4" t="n">
-        <v>0.75</v>
+        <v>0.6972222222222222</v>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>46261</v>
-      </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>46244</v>
+      </c>
+      <c r="C92" s="4" t="n">
+        <v>0.2326388888888889</v>
       </c>
       <c r="D92" s="4" t="n">
-        <v>0.7395833333333334</v>
+        <v>0.7472222222222222</v>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B93" s="3" t="n">
-        <v>46263</v>
-      </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>46245</v>
+      </c>
+      <c r="C93" s="4" t="n">
+        <v>0.2326388888888889</v>
       </c>
       <c r="D93" s="4" t="n">
-        <v>0.4041666666666667</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B94" s="3" t="n">
-        <v>46265</v>
+        <v>46246</v>
       </c>
       <c r="C94" s="4" t="n">
-        <v>0.2805555555555556</v>
+        <v>0.3034722222222222</v>
       </c>
       <c r="D94" s="4" t="n">
-        <v>0.7534722222222222</v>
+        <v>0.7486111111111111</v>
       </c>
       <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B95" s="3" t="n">
+        <v>46247</v>
+      </c>
+      <c r="C95" s="4" t="n">
+        <v>0.2423611111111111</v>
+      </c>
+      <c r="D95" s="4" t="n">
+        <v>0.73125</v>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2377,42 +2405,38 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B96" s="3" t="n">
-        <v>46260</v>
-      </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>46249</v>
+      </c>
+      <c r="C96" s="4" t="n">
+        <v>0.2979166666666667</v>
+      </c>
+      <c r="D96" s="4" t="n">
+        <v>0.7868055555555555</v>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>PLEASE VERIFY: check-in/out times not captured (gap between source photos)</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B97" s="3" t="n">
-        <v>46261</v>
+        <v>46250</v>
       </c>
       <c r="C97" s="4" t="n">
-        <v>0.3652777777777778</v>
+        <v>0.2756944444444445</v>
       </c>
       <c r="D97" s="4" t="n">
-        <v>0.7395833333333334</v>
+        <v>0.7180555555555556</v>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
@@ -2423,17 +2447,17 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B98" s="3" t="n">
-        <v>46263</v>
+        <v>46251</v>
       </c>
       <c r="C98" s="4" t="n">
-        <v>0.3652777777777778</v>
+        <v>0.2826388888888889</v>
       </c>
       <c r="D98" s="4" t="n">
-        <v>0.7569444444444444</v>
+        <v>0.7472222222222222</v>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
@@ -2444,17 +2468,17 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B99" s="3" t="n">
-        <v>46264</v>
+        <v>46252</v>
       </c>
       <c r="C99" s="4" t="n">
-        <v>0.3534722222222222</v>
+        <v>0.2569444444444444</v>
       </c>
       <c r="D99" s="4" t="n">
-        <v>0.7534722222222222</v>
+        <v>0.7576388888888889</v>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
@@ -2465,19 +2489,40 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>46265</v>
+        <v>46253</v>
       </c>
       <c r="C100" s="4" t="n">
-        <v>0.3319444444444444</v>
+        <v>0.3479166666666667</v>
       </c>
       <c r="D100" s="4" t="n">
-        <v>0.7680555555555556</v>
+        <v>0.7576388888888889</v>
       </c>
       <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B101" s="3" t="n">
+        <v>46254</v>
+      </c>
+      <c r="C101" s="4" t="n">
+        <v>0.2784722222222222</v>
+      </c>
+      <c r="D101" s="4" t="n">
+        <v>0.7458333333333333</v>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2486,42 +2531,38 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B102" s="3" t="n">
-        <v>46260</v>
-      </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>46256</v>
+      </c>
+      <c r="C102" s="4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D102" s="4" t="n">
+        <v>0.7548611111111111</v>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>PLEASE VERIFY: check-in/out times not captured (gap between source photos)</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B103" s="3" t="n">
-        <v>46261</v>
+        <v>46257</v>
       </c>
       <c r="C103" s="4" t="n">
-        <v>0.2909722222222222</v>
+        <v>0.2506944444444444</v>
       </c>
       <c r="D103" s="4" t="n">
-        <v>0.7430555555555556</v>
+        <v>0.7555555555555555</v>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
@@ -2532,17 +2573,17 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B104" s="3" t="n">
-        <v>46263</v>
+        <v>46258</v>
       </c>
       <c r="C104" s="4" t="n">
-        <v>0.275</v>
+        <v>0.3090277777777778</v>
       </c>
       <c r="D104" s="4" t="n">
-        <v>0.7513888888888889</v>
+        <v>0.7541666666666667</v>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
@@ -2553,17 +2594,17 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B105" s="3" t="n">
-        <v>46264</v>
+        <v>46259</v>
       </c>
       <c r="C105" s="4" t="n">
-        <v>0.3194444444444444</v>
+        <v>0.2493055555555556</v>
       </c>
       <c r="D105" s="4" t="n">
-        <v>0.7493055555555556</v>
+        <v>0.7486111111111111</v>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
@@ -2574,19 +2615,40 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>46265</v>
+        <v>46260</v>
       </c>
       <c r="C106" s="4" t="n">
-        <v>0.2631944444444445</v>
+        <v>0.2347222222222222</v>
       </c>
       <c r="D106" s="4" t="n">
-        <v>0.7555555555555555</v>
+        <v>0.7701388888888889</v>
       </c>
       <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B107" s="3" t="n">
+        <v>46261</v>
+      </c>
+      <c r="C107" s="4" t="n">
+        <v>0.2826388888888889</v>
+      </c>
+      <c r="D107" s="4" t="n">
+        <v>0.7861111111111111</v>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2595,17 +2657,17 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B108" s="3" t="n">
-        <v>46260</v>
+        <v>46263</v>
       </c>
       <c r="C108" s="4" t="n">
-        <v>0.3055555555555556</v>
+        <v>0.2993055555555555</v>
       </c>
       <c r="D108" s="4" t="n">
-        <v>0.8013888888888889</v>
+        <v>0.7708333333333334</v>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
@@ -2616,17 +2678,17 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B109" s="3" t="n">
-        <v>46261</v>
+        <v>46264</v>
       </c>
       <c r="C109" s="4" t="n">
-        <v>0.2798611111111111</v>
+        <v>0.30625</v>
       </c>
       <c r="D109" s="4" t="n">
-        <v>0.7493055555555556</v>
+        <v>0.6805555555555556</v>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
@@ -2637,164 +2699,199 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B110" s="3" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="C110" s="4" t="n">
-        <v>0.3347222222222222</v>
+        <v>0.2472222222222222</v>
       </c>
       <c r="D110" s="4" t="n">
-        <v>0.8895833333333333</v>
+        <v>0.7555555555555555</v>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>extra punch: 08:02</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B111" s="3" t="n">
-        <v>46264</v>
-      </c>
-      <c r="C111" s="4" t="n">
-        <v>0.3208333333333334</v>
-      </c>
-      <c r="D111" s="4" t="n">
-        <v>0.7354166666666667</v>
-      </c>
-      <c r="E111" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B112" s="3" t="n">
+        <v>46235</v>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D112" s="4" t="n">
+        <v>0.7486111111111111</v>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>single punch only; last day of month</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B113" s="3" t="n">
-        <v>46262</v>
+        <v>46236</v>
       </c>
       <c r="C113" s="4" t="n">
-        <v>0.1493055555555556</v>
-      </c>
-      <c r="D113" s="4" t="n">
-        <v>0.7159722222222222</v>
+        <v>0.2125</v>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B114" s="3" t="n">
-        <v>46263</v>
-      </c>
-      <c r="C114" s="4" t="n">
-        <v>0.1451388888888889</v>
+        <v>46237</v>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D114" s="4" t="n">
-        <v>0.7479166666666667</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B115" s="3" t="n">
-        <v>46264</v>
-      </c>
-      <c r="C115" s="4" t="n">
-        <v>0.14375</v>
+        <v>46238</v>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D115" s="4" t="n">
-        <v>0.75625</v>
+        <v>0.7618055555555555</v>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B116" s="3" t="n">
-        <v>46265</v>
-      </c>
-      <c r="C116" s="4" t="n">
-        <v>0.1479166666666667</v>
+        <v>46239</v>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D116" s="4" t="n">
-        <v>0.9326388888888889</v>
+        <v>0.7611111111111111</v>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>extra punch: 22:23</t>
+          <t>single punch only</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B117" s="3" t="n">
+        <v>46240</v>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D117" s="4" t="n">
+        <v>0.8284722222222223</v>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>46262</v>
-      </c>
-      <c r="C118" s="4" t="n">
-        <v>0.1881944444444444</v>
+        <v>46242</v>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D118" s="4" t="n">
-        <v>0.4055555555555556</v>
+        <v>0.7486111111111111</v>
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B119" s="3" t="n">
-        <v>46263</v>
+        <v>46243</v>
       </c>
       <c r="C119" s="4" t="n">
-        <v>0.1847222222222222</v>
+        <v>0.2868055555555555</v>
       </c>
       <c r="D119" s="4" t="n">
-        <v>0.4527777777777778</v>
+        <v>0.7277777777777777</v>
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
@@ -2805,17 +2902,17 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B120" s="3" t="n">
-        <v>46264</v>
+        <v>46244</v>
       </c>
       <c r="C120" s="4" t="n">
-        <v>0.1847222222222222</v>
+        <v>0.2354166666666667</v>
       </c>
       <c r="D120" s="4" t="n">
-        <v>0.5097222222222222</v>
+        <v>0.7555555555555555</v>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
@@ -2826,19 +2923,42 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B121" s="3" t="n">
-        <v>46265</v>
+        <v>46245</v>
       </c>
       <c r="C121" s="4" t="n">
-        <v>0.1868055555555556</v>
-      </c>
-      <c r="D121" s="4" t="n">
-        <v>0.4131944444444444</v>
+        <v>0.2875</v>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>single punch only</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B122" s="3" t="n">
+        <v>46246</v>
+      </c>
+      <c r="C122" s="4" t="n">
+        <v>0.2173611111111111</v>
+      </c>
+      <c r="D122" s="4" t="n">
+        <v>0.7673611111111112</v>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2847,59 +2967,63 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B123" s="3" t="n">
-        <v>46235</v>
-      </c>
-      <c r="C123" s="4" t="n">
-        <v>0.2368055555555555</v>
+        <v>46247</v>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D123" s="4" t="n">
-        <v>0.7430555555555556</v>
+        <v>0.8034722222222223</v>
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B124" s="3" t="n">
-        <v>46236</v>
-      </c>
-      <c r="C124" s="4" t="n">
-        <v>0.2604166666666667</v>
+        <v>46248</v>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D124" s="4" t="n">
-        <v>0.7534722222222222</v>
+        <v>0.7708333333333334</v>
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B125" s="3" t="n">
-        <v>46237</v>
+        <v>46249</v>
       </c>
       <c r="C125" s="4" t="n">
-        <v>0.3097222222222222</v>
+        <v>0.3013888888888889</v>
       </c>
       <c r="D125" s="4" t="n">
-        <v>0.7444444444444445</v>
+        <v>0.7375</v>
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
@@ -2910,11 +3034,11 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B126" s="3" t="n">
-        <v>46238</v>
+        <v>46250</v>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
@@ -2922,7 +3046,7 @@
         </is>
       </c>
       <c r="D126" s="4" t="n">
-        <v>0.7458333333333333</v>
+        <v>0.7180555555555556</v>
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
@@ -2933,19 +3057,19 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B127" s="3" t="n">
-        <v>46239</v>
-      </c>
-      <c r="C127" s="4" t="n">
-        <v>0.2229166666666667</v>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>46251</v>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D127" s="4" t="n">
+        <v>0.7576388888888889</v>
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
@@ -2956,101 +3080,109 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B128" s="3" t="n">
-        <v>46240</v>
-      </c>
-      <c r="C128" s="4" t="n">
-        <v>0.2326388888888889</v>
+        <v>46252</v>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D128" s="4" t="n">
-        <v>0.7576388888888889</v>
+        <v>0.7159722222222222</v>
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B129" s="3" t="n">
-        <v>46242</v>
+        <v>46253</v>
       </c>
       <c r="C129" s="4" t="n">
-        <v>0.2402777777777778</v>
-      </c>
-      <c r="D129" s="4" t="n">
-        <v>0.7243055555555555</v>
+        <v>0.2854166666666667</v>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B130" s="3" t="n">
-        <v>46243</v>
-      </c>
-      <c r="C130" s="4" t="n">
-        <v>0.2402777777777778</v>
+        <v>46254</v>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D130" s="4" t="n">
-        <v>0.725</v>
+        <v>0.7652777777777777</v>
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B131" s="3" t="n">
-        <v>46244</v>
-      </c>
-      <c r="C131" s="4" t="n">
-        <v>0.2409722222222222</v>
+        <v>46255</v>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D131" s="4" t="n">
-        <v>0.7597222222222222</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B132" s="3" t="n">
-        <v>46245</v>
+        <v>46256</v>
       </c>
       <c r="C132" s="4" t="n">
-        <v>0.2215277777777778</v>
+        <v>0.2965277777777778</v>
       </c>
       <c r="D132" s="4" t="n">
-        <v>0.7319444444444444</v>
+        <v>0.7305555555555555</v>
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
@@ -3061,17 +3193,17 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B133" s="3" t="n">
-        <v>46246</v>
+        <v>46257</v>
       </c>
       <c r="C133" s="4" t="n">
-        <v>0.2361111111111111</v>
+        <v>0.2513888888888889</v>
       </c>
       <c r="D133" s="4" t="n">
-        <v>0.7402777777777778</v>
+        <v>0.7222222222222222</v>
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
@@ -3082,32 +3214,34 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>46247</v>
-      </c>
-      <c r="C134" s="4" t="n">
-        <v>0.2479166666666667</v>
+        <v>46258</v>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D134" s="4" t="n">
-        <v>0.7243055555555555</v>
+        <v>0.7201388888888889</v>
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>46249</v>
+        <v>46259</v>
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
@@ -3115,7 +3249,7 @@
         </is>
       </c>
       <c r="D135" s="4" t="n">
-        <v>0.7201388888888889</v>
+        <v>0.75</v>
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
@@ -3126,84 +3260,65 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B136" s="3" t="n">
-        <v>46250</v>
-      </c>
-      <c r="C136" s="4" t="n">
-        <v>0.2298611111111111</v>
+        <v>46261</v>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D136" s="4" t="n">
-        <v>0.7180555555555556</v>
+        <v>0.7395833333333334</v>
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B137" s="3" t="n">
-        <v>46251</v>
-      </c>
-      <c r="C137" s="4" t="n">
-        <v>0.2472222222222222</v>
+        <v>46263</v>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D137" s="4" t="n">
-        <v>0.7402777777777778</v>
+        <v>0.4041666666666667</v>
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B138" s="3" t="n">
-        <v>46252</v>
+        <v>46265</v>
       </c>
       <c r="C138" s="4" t="n">
-        <v>0.2354166666666667</v>
-      </c>
-      <c r="D138" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.2805555555555556</v>
+      </c>
+      <c r="D138" s="4" t="n">
+        <v>0.7534722222222222</v>
       </c>
       <c r="E138" s="2" t="inlineStr">
-        <is>
-          <t>single punch only</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="B139" s="3" t="n">
-        <v>46253</v>
-      </c>
-      <c r="C139" s="4" t="n">
-        <v>0.2215277777777778</v>
-      </c>
-      <c r="D139" s="4" t="n">
-        <v>0.7305555555555555</v>
-      </c>
-      <c r="E139" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3212,59 +3327,61 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B140" s="3" t="n">
-        <v>46254</v>
+        <v>46235</v>
       </c>
       <c r="C140" s="4" t="n">
-        <v>0.2222222222222222</v>
+        <v>0.3083333333333333</v>
       </c>
       <c r="D140" s="4" t="n">
-        <v>0.7291666666666666</v>
+        <v>0.7486111111111111</v>
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>last day of month; final record</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B141" s="3" t="n">
-        <v>46256</v>
+        <v>46236</v>
       </c>
       <c r="C141" s="4" t="n">
-        <v>0.2388888888888889</v>
-      </c>
-      <c r="D141" s="4" t="n">
-        <v>0.7541666666666667</v>
+        <v>0.2847222222222222</v>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B142" s="3" t="n">
-        <v>46257</v>
+        <v>46237</v>
       </c>
       <c r="C142" s="4" t="n">
-        <v>0.2506944444444444</v>
+        <v>0.3465277777777778</v>
       </c>
       <c r="D142" s="4" t="n">
-        <v>0.7291666666666666</v>
+        <v>0.7736111111111111</v>
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
@@ -3275,40 +3392,38 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B143" s="3" t="n">
-        <v>46258</v>
-      </c>
-      <c r="C143" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>46238</v>
+      </c>
+      <c r="C143" s="4" t="n">
+        <v>0.3590277777777778</v>
       </c>
       <c r="D143" s="4" t="n">
-        <v>0.725</v>
+        <v>0.7597222222222222</v>
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B144" s="3" t="n">
-        <v>46259</v>
+        <v>46239</v>
       </c>
       <c r="C144" s="4" t="n">
-        <v>0.2375</v>
+        <v>0.3430555555555556</v>
       </c>
       <c r="D144" s="4" t="n">
-        <v>0.725</v>
+        <v>0.7944444444444444</v>
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
@@ -3319,17 +3434,17 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B145" s="3" t="n">
-        <v>46260</v>
+        <v>46240</v>
       </c>
       <c r="C145" s="4" t="n">
-        <v>0.2256944444444444</v>
+        <v>0.3701388888888889</v>
       </c>
       <c r="D145" s="4" t="n">
-        <v>0.7381944444444445</v>
+        <v>0.7673611111111112</v>
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
@@ -3340,17 +3455,17 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B146" s="3" t="n">
-        <v>46261</v>
+        <v>46242</v>
       </c>
       <c r="C146" s="4" t="n">
-        <v>0.2361111111111111</v>
+        <v>0.3541666666666667</v>
       </c>
       <c r="D146" s="4" t="n">
-        <v>0.7166666666666667</v>
+        <v>0.7666666666666667</v>
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
@@ -3361,17 +3476,17 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B147" s="3" t="n">
-        <v>46263</v>
+        <v>46243</v>
       </c>
       <c r="C147" s="4" t="n">
-        <v>0.2270833333333333</v>
+        <v>0.3541666666666667</v>
       </c>
       <c r="D147" s="4" t="n">
-        <v>0.7347222222222223</v>
+        <v>0.7319444444444444</v>
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
@@ -3382,84 +3497,101 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B148" s="3" t="n">
-        <v>46264</v>
+        <v>46244</v>
       </c>
       <c r="C148" s="4" t="n">
-        <v>0.2340277777777778</v>
-      </c>
-      <c r="D148" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.2277777777777778</v>
+      </c>
+      <c r="D148" s="4" t="n">
+        <v>0.7652777777777777</v>
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B149" s="3" t="n">
-        <v>46265</v>
+        <v>46245</v>
       </c>
       <c r="C149" s="4" t="n">
-        <v>0.2361111111111111</v>
-      </c>
-      <c r="D149" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.36875</v>
+      </c>
+      <c r="D149" s="4" t="n">
+        <v>0.7409722222222223</v>
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B150" s="3" t="n">
+        <v>46246</v>
+      </c>
+      <c r="C150" s="4" t="n">
+        <v>0.3513888888888889</v>
+      </c>
+      <c r="D150" s="4" t="n">
+        <v>0.7368055555555556</v>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B151" s="3" t="n">
-        <v>46235</v>
+        <v>46247</v>
       </c>
       <c r="C151" s="4" t="n">
-        <v>0.14375</v>
+        <v>0.3659722222222222</v>
       </c>
       <c r="D151" s="4" t="n">
-        <v>0.7576388888888889</v>
+        <v>0.7756944444444445</v>
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>last day of month; final record</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B152" s="3" t="n">
-        <v>46236</v>
+        <v>46249</v>
       </c>
       <c r="C152" s="4" t="n">
-        <v>0.14375</v>
+        <v>0.3840277777777778</v>
       </c>
       <c r="D152" s="4" t="n">
-        <v>0.7395833333333334</v>
+        <v>0.7701388888888889</v>
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
@@ -3470,17 +3602,17 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B153" s="3" t="n">
-        <v>46237</v>
+        <v>46250</v>
       </c>
       <c r="C153" s="4" t="n">
-        <v>0.1458333333333333</v>
+        <v>0.3243055555555556</v>
       </c>
       <c r="D153" s="4" t="n">
-        <v>0.7472222222222222</v>
+        <v>0.7673611111111112</v>
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
@@ -3491,38 +3623,40 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B154" s="3" t="n">
-        <v>46238</v>
+        <v>46251</v>
       </c>
       <c r="C154" s="4" t="n">
-        <v>0.1451388888888889</v>
-      </c>
-      <c r="D154" s="4" t="n">
-        <v>0.7708333333333334</v>
+        <v>0.3097222222222222</v>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B155" s="3" t="n">
-        <v>46239</v>
+        <v>46252</v>
       </c>
       <c r="C155" s="4" t="n">
-        <v>0.1444444444444444</v>
+        <v>0.3527777777777778</v>
       </c>
       <c r="D155" s="4" t="n">
-        <v>0.6881944444444444</v>
+        <v>0.7694444444444445</v>
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
@@ -3533,17 +3667,17 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B156" s="3" t="n">
-        <v>46240</v>
+        <v>46253</v>
       </c>
       <c r="C156" s="4" t="n">
-        <v>0.1444444444444444</v>
+        <v>0.3395833333333333</v>
       </c>
       <c r="D156" s="4" t="n">
-        <v>0.7659722222222223</v>
+        <v>0.7604166666666666</v>
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
@@ -3554,17 +3688,17 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B157" s="3" t="n">
-        <v>46241</v>
+        <v>46254</v>
       </c>
       <c r="C157" s="4" t="n">
-        <v>0.1451388888888889</v>
+        <v>0.3576388888888889</v>
       </c>
       <c r="D157" s="4" t="n">
-        <v>0.7298611111111111</v>
+        <v>0.7673611111111112</v>
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
@@ -3575,38 +3709,38 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B158" s="3" t="n">
-        <v>46242</v>
+        <v>46256</v>
       </c>
       <c r="C158" s="4" t="n">
-        <v>0.1388888888888889</v>
+        <v>0.2951388888888889</v>
       </c>
       <c r="D158" s="4" t="n">
-        <v>0.8090277777777778</v>
+        <v>0.7569444444444444</v>
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>extra punch: 03:24</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B159" s="3" t="n">
-        <v>46243</v>
+        <v>46257</v>
       </c>
       <c r="C159" s="4" t="n">
-        <v>0.1444444444444444</v>
+        <v>0.2520833333333333</v>
       </c>
       <c r="D159" s="4" t="n">
-        <v>0.8381944444444445</v>
+        <v>0.7694444444444445</v>
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
@@ -3617,17 +3751,17 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B160" s="3" t="n">
-        <v>46244</v>
+        <v>46258</v>
       </c>
       <c r="C160" s="4" t="n">
-        <v>0.1354166666666667</v>
+        <v>0.3631944444444444</v>
       </c>
       <c r="D160" s="4" t="n">
-        <v>0.7638888888888888</v>
+        <v>0.7729166666666667</v>
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
@@ -3638,17 +3772,17 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B161" s="3" t="n">
-        <v>46245</v>
+        <v>46259</v>
       </c>
       <c r="C161" s="4" t="n">
-        <v>0.14375</v>
+        <v>0.3479166666666667</v>
       </c>
       <c r="D161" s="4" t="n">
-        <v>0.7444444444444445</v>
+        <v>0.7361111111111112</v>
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
@@ -3659,17 +3793,17 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B162" s="3" t="n">
-        <v>46246</v>
+        <v>46260</v>
       </c>
       <c r="C162" s="4" t="n">
-        <v>0.1430555555555555</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D162" s="4" t="n">
-        <v>0.7409722222222223</v>
+        <v>0.7611111111111111</v>
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
@@ -3680,17 +3814,17 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B163" s="3" t="n">
-        <v>46247</v>
+        <v>46261</v>
       </c>
       <c r="C163" s="4" t="n">
-        <v>0.1423611111111111</v>
+        <v>0.3652777777777778</v>
       </c>
       <c r="D163" s="4" t="n">
-        <v>0.75</v>
+        <v>0.7395833333333334</v>
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
@@ -3701,17 +3835,17 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B164" s="3" t="n">
-        <v>46248</v>
+        <v>46263</v>
       </c>
       <c r="C164" s="4" t="n">
-        <v>0.15</v>
+        <v>0.3652777777777778</v>
       </c>
       <c r="D164" s="4" t="n">
-        <v>0.7076388888888889</v>
+        <v>0.7569444444444444</v>
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
@@ -3722,17 +3856,17 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B165" s="3" t="n">
-        <v>46249</v>
+        <v>46264</v>
       </c>
       <c r="C165" s="4" t="n">
-        <v>0.1513888888888889</v>
+        <v>0.3534722222222222</v>
       </c>
       <c r="D165" s="4" t="n">
-        <v>0.7277777777777777</v>
+        <v>0.7534722222222222</v>
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
@@ -3743,40 +3877,19 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B166" s="3" t="n">
-        <v>46250</v>
+        <v>46265</v>
       </c>
       <c r="C166" s="4" t="n">
-        <v>0.2708333333333333</v>
+        <v>0.3319444444444444</v>
       </c>
       <c r="D166" s="4" t="n">
-        <v>0.7229166666666667</v>
+        <v>0.7680555555555556</v>
       </c>
       <c r="E166" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="B167" s="3" t="n">
-        <v>46251</v>
-      </c>
-      <c r="C167" s="4" t="n">
-        <v>0.2333333333333333</v>
-      </c>
-      <c r="D167" s="4" t="n">
-        <v>0.8888888888888888</v>
-      </c>
-      <c r="E167" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3785,17 +3898,17 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B168" s="3" t="n">
         <v>46252</v>
       </c>
       <c r="C168" s="4" t="n">
-        <v>0.25625</v>
+        <v>0.2652777777777778</v>
       </c>
       <c r="D168" s="4" t="n">
-        <v>0.7416666666666667</v>
+        <v>0.7569444444444444</v>
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
@@ -3806,17 +3919,17 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B169" s="3" t="n">
         <v>46253</v>
       </c>
       <c r="C169" s="4" t="n">
-        <v>0.2777777777777778</v>
+        <v>0.26875</v>
       </c>
       <c r="D169" s="4" t="n">
-        <v>0.7451388888888889</v>
+        <v>0.7506944444444444</v>
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
@@ -3827,17 +3940,17 @@
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B170" s="3" t="n">
         <v>46254</v>
       </c>
       <c r="C170" s="4" t="n">
-        <v>0.2625</v>
+        <v>0.2611111111111111</v>
       </c>
       <c r="D170" s="4" t="n">
-        <v>0.7979166666666667</v>
+        <v>0.7451388888888889</v>
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
@@ -3848,17 +3961,17 @@
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B171" s="3" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="C171" s="4" t="n">
-        <v>0.275</v>
+        <v>0.3006944444444444</v>
       </c>
       <c r="D171" s="4" t="n">
-        <v>0.8354166666666667</v>
+        <v>0.7541666666666667</v>
       </c>
       <c r="E171" s="2" t="inlineStr">
         <is>
@@ -3869,17 +3982,17 @@
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B172" s="3" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="C172" s="4" t="n">
-        <v>0.2611111111111111</v>
+        <v>0.2541666666666667</v>
       </c>
       <c r="D172" s="4" t="n">
-        <v>0.7513888888888889</v>
+        <v>0.74375</v>
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
@@ -3890,17 +4003,17 @@
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B173" s="3" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="C173" s="4" t="n">
-        <v>0.24375</v>
+        <v>0.25625</v>
       </c>
       <c r="D173" s="4" t="n">
-        <v>0.7263888888888889</v>
+        <v>0.7472222222222222</v>
       </c>
       <c r="E173" s="2" t="inlineStr">
         <is>
@@ -3911,17 +4024,17 @@
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B174" s="3" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C174" s="4" t="n">
-        <v>0.2631944444444445</v>
+        <v>0.2555555555555555</v>
       </c>
       <c r="D174" s="4" t="n">
-        <v>0.7270833333333333</v>
+        <v>0.7479166666666667</v>
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
@@ -3932,17 +4045,17 @@
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B175" s="3" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C175" s="4" t="n">
-        <v>0.2611111111111111</v>
+        <v>0.2708333333333333</v>
       </c>
       <c r="D175" s="4" t="n">
-        <v>0.7298611111111111</v>
+        <v>0.7416666666666667</v>
       </c>
       <c r="E175" s="2" t="inlineStr">
         <is>
@@ -3953,59 +4066,59 @@
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B176" s="3" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="C176" s="4" t="n">
-        <v>0.275</v>
+        <v>0.2909722222222222</v>
       </c>
       <c r="D176" s="4" t="n">
-        <v>0.8791666666666667</v>
+        <v>0.7430555555555556</v>
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>extra punch: 17:56</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B177" s="3" t="n">
-        <v>46261</v>
+        <v>46263</v>
       </c>
       <c r="C177" s="4" t="n">
-        <v>0.2555555555555555</v>
+        <v>0.275</v>
       </c>
       <c r="D177" s="4" t="n">
-        <v>0.8506944444444444</v>
+        <v>0.7513888888888889</v>
       </c>
       <c r="E177" s="2" t="inlineStr">
         <is>
-          <t>extra punches: 17:07 17:02</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B178" s="3" t="n">
-        <v>46262</v>
+        <v>46264</v>
       </c>
       <c r="C178" s="4" t="n">
-        <v>0.2805555555555556</v>
+        <v>0.3194444444444444</v>
       </c>
       <c r="D178" s="4" t="n">
-        <v>0.7701388888888889</v>
+        <v>0.7493055555555556</v>
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
@@ -4016,40 +4129,19 @@
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B179" s="3" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="C179" s="4" t="n">
-        <v>0.2541666666666667</v>
+        <v>0.2631944444444445</v>
       </c>
       <c r="D179" s="4" t="n">
-        <v>0.7479166666666667</v>
+        <v>0.7555555555555555</v>
       </c>
       <c r="E179" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="B180" s="3" t="n">
-        <v>46264</v>
-      </c>
-      <c r="C180" s="4" t="n">
-        <v>0.2659722222222222</v>
-      </c>
-      <c r="D180" s="4" t="n">
-        <v>0.7354166666666667</v>
-      </c>
-      <c r="E180" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4058,82 +4150,82 @@
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B181" s="3" t="n">
-        <v>46265</v>
+        <v>46260</v>
       </c>
       <c r="C181" s="4" t="n">
-        <v>0.2527777777777778</v>
+        <v>0.3055555555555556</v>
       </c>
       <c r="D181" s="4" t="n">
-        <v>0.7354166666666667</v>
+        <v>0.8013888888888889</v>
       </c>
       <c r="E181" s="2" t="inlineStr">
         <is>
-          <t>corrected from a clearer re-scan photo later in the album</t>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B182" s="3" t="n">
+        <v>46261</v>
+      </c>
+      <c r="C182" s="4" t="n">
+        <v>0.2798611111111111</v>
+      </c>
+      <c r="D182" s="4" t="n">
+        <v>0.7493055555555556</v>
+      </c>
+      <c r="E182" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B183" s="3" t="n">
-        <v>46235</v>
+        <v>46263</v>
       </c>
       <c r="C183" s="4" t="n">
-        <v>0.2625</v>
+        <v>0.3347222222222222</v>
       </c>
       <c r="D183" s="4" t="n">
-        <v>0.7444444444444445</v>
+        <v>0.8895833333333333</v>
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
-          <t>last day of month; final record</t>
+          <t>extra punch: 08:02</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B184" s="3" t="n">
-        <v>46236</v>
+        <v>46264</v>
       </c>
       <c r="C184" s="4" t="n">
-        <v>0.2645833333333333</v>
+        <v>0.3208333333333334</v>
       </c>
       <c r="D184" s="4" t="n">
-        <v>0.7493055555555556</v>
+        <v>0.7354166666666667</v>
       </c>
       <c r="E184" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="B185" s="3" t="n">
-        <v>46237</v>
-      </c>
-      <c r="C185" s="4" t="n">
-        <v>0.2604166666666667</v>
-      </c>
-      <c r="D185" s="4" t="n">
-        <v>0.7479166666666667</v>
-      </c>
-      <c r="E185" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4142,17 +4234,17 @@
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B186" s="3" t="n">
-        <v>46238</v>
+        <v>46262</v>
       </c>
       <c r="C186" s="4" t="n">
-        <v>0.2527777777777778</v>
+        <v>0.1493055555555556</v>
       </c>
       <c r="D186" s="4" t="n">
-        <v>0.75</v>
+        <v>0.7159722222222222</v>
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
@@ -4163,17 +4255,17 @@
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B187" s="3" t="n">
-        <v>46239</v>
+        <v>46263</v>
       </c>
       <c r="C187" s="4" t="n">
-        <v>0.25625</v>
+        <v>0.1451388888888889</v>
       </c>
       <c r="D187" s="4" t="n">
-        <v>0.7763888888888889</v>
+        <v>0.7479166666666667</v>
       </c>
       <c r="E187" s="2" t="inlineStr">
         <is>
@@ -4184,17 +4276,17 @@
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B188" s="3" t="n">
-        <v>46240</v>
+        <v>46264</v>
       </c>
       <c r="C188" s="4" t="n">
-        <v>0.2701388888888889</v>
+        <v>0.14375</v>
       </c>
       <c r="D188" s="4" t="n">
-        <v>0.7423611111111111</v>
+        <v>0.75625</v>
       </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
@@ -4205,82 +4297,59 @@
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B189" s="3" t="n">
-        <v>46242</v>
+        <v>46265</v>
       </c>
       <c r="C189" s="4" t="n">
-        <v>0.2597222222222222</v>
+        <v>0.1479166666666667</v>
       </c>
       <c r="D189" s="4" t="n">
-        <v>0.7326388888888888</v>
+        <v>0.9326388888888889</v>
       </c>
       <c r="E189" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="B190" s="3" t="n">
-        <v>46243</v>
-      </c>
-      <c r="C190" s="4" t="n">
-        <v>0.2381944444444444</v>
-      </c>
-      <c r="D190" s="4" t="n">
-        <v>0.75625</v>
-      </c>
-      <c r="E190" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>extra punch: 22:23</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B191" s="3" t="n">
-        <v>46244</v>
-      </c>
-      <c r="C191" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>46262</v>
+      </c>
+      <c r="C191" s="4" t="n">
+        <v>0.1881944444444444</v>
       </c>
       <c r="D191" s="4" t="n">
-        <v>0.75625</v>
+        <v>0.4055555555555556</v>
       </c>
       <c r="E191" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B192" s="3" t="n">
-        <v>46245</v>
+        <v>46263</v>
       </c>
       <c r="C192" s="4" t="n">
-        <v>0.2381944444444444</v>
+        <v>0.1847222222222222</v>
       </c>
       <c r="D192" s="4" t="n">
-        <v>0.7402777777777778</v>
+        <v>0.4527777777777778</v>
       </c>
       <c r="E192" s="2" t="inlineStr">
         <is>
@@ -4291,17 +4360,17 @@
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B193" s="3" t="n">
-        <v>46246</v>
+        <v>46264</v>
       </c>
       <c r="C193" s="4" t="n">
-        <v>0.2340277777777778</v>
+        <v>0.1847222222222222</v>
       </c>
       <c r="D193" s="4" t="n">
-        <v>0.7493055555555556</v>
+        <v>0.5097222222222222</v>
       </c>
       <c r="E193" s="2" t="inlineStr">
         <is>
@@ -4312,40 +4381,19 @@
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B194" s="3" t="n">
-        <v>46247</v>
+        <v>46265</v>
       </c>
       <c r="C194" s="4" t="n">
-        <v>0.2465277777777778</v>
+        <v>0.1868055555555556</v>
       </c>
       <c r="D194" s="4" t="n">
-        <v>0.7270833333333333</v>
+        <v>0.4131944444444444</v>
       </c>
       <c r="E194" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="B195" s="3" t="n">
-        <v>46249</v>
-      </c>
-      <c r="C195" s="4" t="n">
-        <v>0.2395833333333333</v>
-      </c>
-      <c r="D195" s="4" t="n">
-        <v>0.7388888888888889</v>
-      </c>
-      <c r="E195" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4354,17 +4402,17 @@
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B196" s="3" t="n">
-        <v>46250</v>
+        <v>46235</v>
       </c>
       <c r="C196" s="4" t="n">
-        <v>0.2902777777777778</v>
+        <v>0.2368055555555555</v>
       </c>
       <c r="D196" s="4" t="n">
-        <v>0.7236111111111111</v>
+        <v>0.7430555555555556</v>
       </c>
       <c r="E196" s="2" t="inlineStr">
         <is>
@@ -4375,17 +4423,17 @@
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B197" s="3" t="n">
-        <v>46251</v>
+        <v>46236</v>
       </c>
       <c r="C197" s="4" t="n">
-        <v>0.2743055555555556</v>
+        <v>0.2604166666666667</v>
       </c>
       <c r="D197" s="4" t="n">
-        <v>0.7333333333333333</v>
+        <v>0.7534722222222222</v>
       </c>
       <c r="E197" s="2" t="inlineStr">
         <is>
@@ -4396,17 +4444,17 @@
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B198" s="3" t="n">
-        <v>46252</v>
+        <v>46237</v>
       </c>
       <c r="C198" s="4" t="n">
-        <v>0.2826388888888889</v>
+        <v>0.3097222222222222</v>
       </c>
       <c r="D198" s="4" t="n">
-        <v>0.7451388888888889</v>
+        <v>0.7444444444444445</v>
       </c>
       <c r="E198" s="2" t="inlineStr">
         <is>
@@ -4417,59 +4465,63 @@
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B199" s="3" t="n">
-        <v>46253</v>
-      </c>
-      <c r="C199" s="4" t="n">
-        <v>0.2763888888888889</v>
+        <v>46238</v>
+      </c>
+      <c r="C199" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D199" s="4" t="n">
-        <v>0.7298611111111111</v>
+        <v>0.7458333333333333</v>
       </c>
       <c r="E199" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B200" s="3" t="n">
-        <v>46254</v>
+        <v>46239</v>
       </c>
       <c r="C200" s="4" t="n">
-        <v>0.275</v>
-      </c>
-      <c r="D200" s="4" t="n">
-        <v>0.7256944444444444</v>
+        <v>0.2229166666666667</v>
+      </c>
+      <c r="D200" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E200" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B201" s="3" t="n">
-        <v>46256</v>
+        <v>46240</v>
       </c>
       <c r="C201" s="4" t="n">
-        <v>0.2805555555555556</v>
+        <v>0.2326388888888889</v>
       </c>
       <c r="D201" s="4" t="n">
-        <v>0.7513888888888889</v>
+        <v>0.7576388888888889</v>
       </c>
       <c r="E201" s="2" t="inlineStr">
         <is>
@@ -4480,17 +4532,17 @@
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B202" s="3" t="n">
-        <v>46261</v>
+        <v>46242</v>
       </c>
       <c r="C202" s="4" t="n">
-        <v>0.24375</v>
+        <v>0.2402777777777778</v>
       </c>
       <c r="D202" s="4" t="n">
-        <v>0.6763888888888889</v>
+        <v>0.7243055555555555</v>
       </c>
       <c r="E202" s="2" t="inlineStr">
         <is>
@@ -4501,17 +4553,17 @@
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B203" s="3" t="n">
-        <v>46263</v>
+        <v>46243</v>
       </c>
       <c r="C203" s="4" t="n">
-        <v>0.2965277777777778</v>
+        <v>0.2402777777777778</v>
       </c>
       <c r="D203" s="4" t="n">
-        <v>0.7472222222222222</v>
+        <v>0.725</v>
       </c>
       <c r="E203" s="2" t="inlineStr">
         <is>
@@ -4522,17 +4574,17 @@
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B204" s="3" t="n">
-        <v>46264</v>
+        <v>46244</v>
       </c>
       <c r="C204" s="4" t="n">
-        <v>0.2888888888888889</v>
+        <v>0.2409722222222222</v>
       </c>
       <c r="D204" s="4" t="n">
-        <v>0.75</v>
+        <v>0.7597222222222222</v>
       </c>
       <c r="E204" s="2" t="inlineStr">
         <is>
@@ -4543,19 +4595,40 @@
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B205" s="3" t="n">
-        <v>46265</v>
+        <v>46245</v>
       </c>
       <c r="C205" s="4" t="n">
-        <v>0.2909722222222222</v>
+        <v>0.2215277777777778</v>
       </c>
       <c r="D205" s="4" t="n">
-        <v>0.75</v>
+        <v>0.7319444444444444</v>
       </c>
       <c r="E205" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B206" s="3" t="n">
+        <v>46246</v>
+      </c>
+      <c r="C206" s="4" t="n">
+        <v>0.2361111111111111</v>
+      </c>
+      <c r="D206" s="4" t="n">
+        <v>0.7402777777777778</v>
+      </c>
+      <c r="E206" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4564,59 +4637,61 @@
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B207" s="3" t="n">
-        <v>46235</v>
+        <v>46247</v>
       </c>
       <c r="C207" s="4" t="n">
-        <v>0.2381944444444444</v>
+        <v>0.2479166666666667</v>
       </c>
       <c r="D207" s="4" t="n">
-        <v>0.7458333333333333</v>
+        <v>0.7243055555555555</v>
       </c>
       <c r="E207" s="2" t="inlineStr">
         <is>
-          <t>last day of month; final record</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B208" s="3" t="n">
-        <v>46236</v>
-      </c>
-      <c r="C208" s="4" t="n">
-        <v>0.2958333333333333</v>
+        <v>46249</v>
+      </c>
+      <c r="C208" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D208" s="4" t="n">
-        <v>0.7430555555555556</v>
+        <v>0.7201388888888889</v>
       </c>
       <c r="E208" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B209" s="3" t="n">
-        <v>46237</v>
+        <v>46250</v>
       </c>
       <c r="C209" s="4" t="n">
-        <v>0.3034722222222222</v>
+        <v>0.2298611111111111</v>
       </c>
       <c r="D209" s="4" t="n">
-        <v>0.7159722222222222</v>
+        <v>0.7180555555555556</v>
       </c>
       <c r="E209" s="2" t="inlineStr">
         <is>
@@ -4627,17 +4702,17 @@
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B210" s="3" t="n">
-        <v>46238</v>
+        <v>46251</v>
       </c>
       <c r="C210" s="4" t="n">
-        <v>0.2763888888888889</v>
+        <v>0.2472222222222222</v>
       </c>
       <c r="D210" s="4" t="n">
-        <v>0.7166666666666667</v>
+        <v>0.7402777777777778</v>
       </c>
       <c r="E210" s="2" t="inlineStr">
         <is>
@@ -4648,38 +4723,40 @@
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B211" s="3" t="n">
-        <v>46239</v>
+        <v>46252</v>
       </c>
       <c r="C211" s="4" t="n">
-        <v>0.3222222222222222</v>
-      </c>
-      <c r="D211" s="4" t="n">
-        <v>0.7715277777777778</v>
+        <v>0.2354166666666667</v>
+      </c>
+      <c r="D211" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E211" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B212" s="3" t="n">
-        <v>46240</v>
+        <v>46253</v>
       </c>
       <c r="C212" s="4" t="n">
-        <v>0.30625</v>
+        <v>0.2215277777777778</v>
       </c>
       <c r="D212" s="4" t="n">
-        <v>0.7590277777777777</v>
+        <v>0.7305555555555555</v>
       </c>
       <c r="E212" s="2" t="inlineStr">
         <is>
@@ -4690,17 +4767,17 @@
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B213" s="3" t="n">
-        <v>46242</v>
+        <v>46254</v>
       </c>
       <c r="C213" s="4" t="n">
-        <v>0.3055555555555556</v>
+        <v>0.2222222222222222</v>
       </c>
       <c r="D213" s="4" t="n">
-        <v>0.7604166666666666</v>
+        <v>0.7291666666666666</v>
       </c>
       <c r="E213" s="2" t="inlineStr">
         <is>
@@ -4711,17 +4788,17 @@
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B214" s="3" t="n">
-        <v>46243</v>
+        <v>46256</v>
       </c>
       <c r="C214" s="4" t="n">
-        <v>0.2798611111111111</v>
+        <v>0.2388888888888889</v>
       </c>
       <c r="D214" s="4" t="n">
-        <v>0.75</v>
+        <v>0.7541666666666667</v>
       </c>
       <c r="E214" s="2" t="inlineStr">
         <is>
@@ -4732,17 +4809,17 @@
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B215" s="3" t="n">
-        <v>46244</v>
+        <v>46257</v>
       </c>
       <c r="C215" s="4" t="n">
-        <v>0.2263888888888889</v>
+        <v>0.2506944444444444</v>
       </c>
       <c r="D215" s="4" t="n">
-        <v>0.75</v>
+        <v>0.7291666666666666</v>
       </c>
       <c r="E215" s="2" t="inlineStr">
         <is>
@@ -4753,19 +4830,19 @@
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B216" s="3" t="n">
-        <v>46245</v>
-      </c>
-      <c r="C216" s="4" t="n">
-        <v>0.3118055555555556</v>
-      </c>
-      <c r="D216" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>46258</v>
+      </c>
+      <c r="C216" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D216" s="4" t="n">
+        <v>0.725</v>
       </c>
       <c r="E216" s="2" t="inlineStr">
         <is>
@@ -4776,63 +4853,59 @@
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B217" s="3" t="n">
-        <v>46246</v>
+        <v>46259</v>
       </c>
       <c r="C217" s="4" t="n">
-        <v>0.2986111111111111</v>
-      </c>
-      <c r="D217" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.2375</v>
+      </c>
+      <c r="D217" s="4" t="n">
+        <v>0.725</v>
       </c>
       <c r="E217" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B218" s="3" t="n">
-        <v>46247</v>
+        <v>46260</v>
       </c>
       <c r="C218" s="4" t="n">
-        <v>0.3347222222222222</v>
-      </c>
-      <c r="D218" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.2256944444444444</v>
+      </c>
+      <c r="D218" s="4" t="n">
+        <v>0.7381944444444445</v>
       </c>
       <c r="E218" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B219" s="3" t="n">
-        <v>46249</v>
+        <v>46261</v>
       </c>
       <c r="C219" s="4" t="n">
-        <v>0.2354166666666667</v>
+        <v>0.2361111111111111</v>
       </c>
       <c r="D219" s="4" t="n">
-        <v>0.75</v>
+        <v>0.7166666666666667</v>
       </c>
       <c r="E219" s="2" t="inlineStr">
         <is>
@@ -4843,17 +4916,17 @@
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B220" s="3" t="n">
-        <v>46250</v>
+        <v>46263</v>
       </c>
       <c r="C220" s="4" t="n">
-        <v>0.325</v>
+        <v>0.2270833333333333</v>
       </c>
       <c r="D220" s="4" t="n">
-        <v>0.7722222222222223</v>
+        <v>0.7347222222222223</v>
       </c>
       <c r="E220" s="2" t="inlineStr">
         <is>
@@ -4864,103 +4937,84 @@
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B221" s="3" t="n">
-        <v>46251</v>
+        <v>46264</v>
       </c>
       <c r="C221" s="4" t="n">
-        <v>0.3979166666666666</v>
-      </c>
-      <c r="D221" s="4" t="n">
-        <v>0.7680555555555556</v>
+        <v>0.2340277777777778</v>
+      </c>
+      <c r="D221" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E221" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B222" s="3" t="n">
-        <v>46252</v>
+        <v>46265</v>
       </c>
       <c r="C222" s="4" t="n">
-        <v>0.3083333333333333</v>
-      </c>
-      <c r="D222" s="4" t="n">
-        <v>0.7583333333333333</v>
+        <v>0.2361111111111111</v>
+      </c>
+      <c r="D222" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E222" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="B223" s="3" t="n">
-        <v>46253</v>
-      </c>
-      <c r="C223" s="4" t="n">
-        <v>0.475</v>
-      </c>
-      <c r="D223" s="4" t="n">
-        <v>0.7173611111111111</v>
-      </c>
-      <c r="E223" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B224" s="3" t="n">
-        <v>46254</v>
+        <v>46235</v>
       </c>
       <c r="C224" s="4" t="n">
-        <v>0.3576388888888889</v>
-      </c>
-      <c r="D224" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.14375</v>
+      </c>
+      <c r="D224" s="4" t="n">
+        <v>0.7576388888888889</v>
       </c>
       <c r="E224" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>last day of month; final record</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B225" s="3" t="n">
-        <v>46256</v>
+        <v>46236</v>
       </c>
       <c r="C225" s="4" t="n">
-        <v>0.2069444444444444</v>
+        <v>0.14375</v>
       </c>
       <c r="D225" s="4" t="n">
-        <v>0.7243055555555555</v>
+        <v>0.7395833333333334</v>
       </c>
       <c r="E225" s="2" t="inlineStr">
         <is>
@@ -4971,17 +5025,17 @@
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B226" s="3" t="n">
-        <v>46257</v>
+        <v>46237</v>
       </c>
       <c r="C226" s="4" t="n">
-        <v>0.25</v>
+        <v>0.1458333333333333</v>
       </c>
       <c r="D226" s="4" t="n">
-        <v>0.7493055555555556</v>
+        <v>0.7472222222222222</v>
       </c>
       <c r="E226" s="2" t="inlineStr">
         <is>
@@ -4992,17 +5046,17 @@
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B227" s="3" t="n">
-        <v>46258</v>
+        <v>46238</v>
       </c>
       <c r="C227" s="4" t="n">
-        <v>0.3263888888888889</v>
+        <v>0.1451388888888889</v>
       </c>
       <c r="D227" s="4" t="n">
-        <v>0.7388888888888889</v>
+        <v>0.7708333333333334</v>
       </c>
       <c r="E227" s="2" t="inlineStr">
         <is>
@@ -5013,17 +5067,17 @@
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B228" s="3" t="n">
-        <v>46259</v>
+        <v>46239</v>
       </c>
       <c r="C228" s="4" t="n">
-        <v>0.2763888888888889</v>
+        <v>0.1444444444444444</v>
       </c>
       <c r="D228" s="4" t="n">
-        <v>0.7548611111111111</v>
+        <v>0.6881944444444444</v>
       </c>
       <c r="E228" s="2" t="inlineStr">
         <is>
@@ -5034,38 +5088,38 @@
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B229" s="3" t="n">
-        <v>46260</v>
+        <v>46240</v>
       </c>
       <c r="C229" s="4" t="n">
-        <v>0.3243055555555556</v>
+        <v>0.1444444444444444</v>
       </c>
       <c r="D229" s="4" t="n">
-        <v>0.7534722222222222</v>
+        <v>0.7659722222222223</v>
       </c>
       <c r="E229" s="2" t="inlineStr">
         <is>
-          <t>extra punch: 17:56</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B230" s="3" t="n">
-        <v>46261</v>
+        <v>46241</v>
       </c>
       <c r="C230" s="4" t="n">
-        <v>0.2666666666666667</v>
+        <v>0.1451388888888889</v>
       </c>
       <c r="D230" s="4" t="n">
-        <v>0.75</v>
+        <v>0.7298611111111111</v>
       </c>
       <c r="E230" s="2" t="inlineStr">
         <is>
@@ -5076,38 +5130,38 @@
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B231" s="3" t="n">
-        <v>46263</v>
+        <v>46242</v>
       </c>
       <c r="C231" s="4" t="n">
-        <v>0.2965277777777778</v>
+        <v>0.1388888888888889</v>
       </c>
       <c r="D231" s="4" t="n">
-        <v>0.7326388888888888</v>
+        <v>0.8090277777777778</v>
       </c>
       <c r="E231" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>extra punch: 03:24</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B232" s="3" t="n">
-        <v>46264</v>
+        <v>46243</v>
       </c>
       <c r="C232" s="4" t="n">
-        <v>0.2965277777777778</v>
+        <v>0.1444444444444444</v>
       </c>
       <c r="D232" s="4" t="n">
-        <v>0.75625</v>
+        <v>0.8381944444444445</v>
       </c>
       <c r="E232" s="2" t="inlineStr">
         <is>
@@ -5118,59 +5172,80 @@
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B233" s="3" t="n">
-        <v>46265</v>
+        <v>46244</v>
       </c>
       <c r="C233" s="4" t="n">
-        <v>0.2527777777777778</v>
+        <v>0.1354166666666667</v>
       </c>
       <c r="D233" s="4" t="n">
-        <v>0.7604166666666666</v>
+        <v>0.7638888888888888</v>
       </c>
       <c r="E233" s="2" t="inlineStr">
         <is>
-          <t>corrected from a clearer re-scan photo later in the album</t>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B234" s="3" t="n">
+        <v>46245</v>
+      </c>
+      <c r="C234" s="4" t="n">
+        <v>0.14375</v>
+      </c>
+      <c r="D234" s="4" t="n">
+        <v>0.7444444444444445</v>
+      </c>
+      <c r="E234" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B235" s="3" t="n">
-        <v>46235</v>
+        <v>46246</v>
       </c>
       <c r="C235" s="4" t="n">
-        <v>0.2590277777777778</v>
+        <v>0.1430555555555555</v>
       </c>
       <c r="D235" s="4" t="n">
-        <v>0.7319444444444444</v>
+        <v>0.7409722222222223</v>
       </c>
       <c r="E235" s="2" t="inlineStr">
         <is>
-          <t>last day of month; final record</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B236" s="3" t="n">
-        <v>46236</v>
+        <v>46247</v>
       </c>
       <c r="C236" s="4" t="n">
-        <v>0.2972222222222222</v>
+        <v>0.1423611111111111</v>
       </c>
       <c r="D236" s="4" t="n">
-        <v>0.7430555555555556</v>
+        <v>0.75</v>
       </c>
       <c r="E236" s="2" t="inlineStr">
         <is>
@@ -5181,17 +5256,17 @@
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B237" s="3" t="n">
-        <v>46237</v>
+        <v>46248</v>
       </c>
       <c r="C237" s="4" t="n">
-        <v>0.2618055555555556</v>
+        <v>0.15</v>
       </c>
       <c r="D237" s="4" t="n">
-        <v>0.7472222222222222</v>
+        <v>0.7076388888888889</v>
       </c>
       <c r="E237" s="2" t="inlineStr">
         <is>
@@ -5202,17 +5277,17 @@
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B238" s="3" t="n">
-        <v>46238</v>
+        <v>46249</v>
       </c>
       <c r="C238" s="4" t="n">
-        <v>0.4965277777777778</v>
+        <v>0.1513888888888889</v>
       </c>
       <c r="D238" s="4" t="n">
-        <v>0.7506944444444444</v>
+        <v>0.7277777777777777</v>
       </c>
       <c r="E238" s="2" t="inlineStr">
         <is>
@@ -5223,17 +5298,17 @@
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B239" s="3" t="n">
-        <v>46239</v>
+        <v>46250</v>
       </c>
       <c r="C239" s="4" t="n">
-        <v>0.4743055555555555</v>
+        <v>0.2708333333333333</v>
       </c>
       <c r="D239" s="4" t="n">
-        <v>0.7722222222222223</v>
+        <v>0.7229166666666667</v>
       </c>
       <c r="E239" s="2" t="inlineStr">
         <is>
@@ -5244,17 +5319,17 @@
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B240" s="3" t="n">
-        <v>46240</v>
+        <v>46251</v>
       </c>
       <c r="C240" s="4" t="n">
-        <v>0.2409722222222222</v>
+        <v>0.2333333333333333</v>
       </c>
       <c r="D240" s="4" t="n">
-        <v>0.7625</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="E240" s="2" t="inlineStr">
         <is>
@@ -5265,17 +5340,17 @@
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B241" s="3" t="n">
-        <v>46242</v>
+        <v>46252</v>
       </c>
       <c r="C241" s="4" t="n">
-        <v>0.2201388888888889</v>
+        <v>0.25625</v>
       </c>
       <c r="D241" s="4" t="n">
-        <v>0.7618055555555555</v>
+        <v>0.7416666666666667</v>
       </c>
       <c r="E241" s="2" t="inlineStr">
         <is>
@@ -5286,17 +5361,17 @@
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B242" s="3" t="n">
-        <v>46243</v>
+        <v>46253</v>
       </c>
       <c r="C242" s="4" t="n">
-        <v>0.2395833333333333</v>
+        <v>0.2777777777777778</v>
       </c>
       <c r="D242" s="4" t="n">
-        <v>0.725</v>
+        <v>0.7451388888888889</v>
       </c>
       <c r="E242" s="2" t="inlineStr">
         <is>
@@ -5307,17 +5382,17 @@
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B243" s="3" t="n">
-        <v>46244</v>
+        <v>46254</v>
       </c>
       <c r="C243" s="4" t="n">
-        <v>0.2256944444444444</v>
+        <v>0.2625</v>
       </c>
       <c r="D243" s="4" t="n">
-        <v>0.7611111111111111</v>
+        <v>0.7979166666666667</v>
       </c>
       <c r="E243" s="2" t="inlineStr">
         <is>
@@ -5328,17 +5403,17 @@
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B244" s="3" t="n">
-        <v>46245</v>
+        <v>46255</v>
       </c>
       <c r="C244" s="4" t="n">
-        <v>0.2375</v>
+        <v>0.275</v>
       </c>
       <c r="D244" s="4" t="n">
-        <v>0.7375</v>
+        <v>0.8354166666666667</v>
       </c>
       <c r="E244" s="2" t="inlineStr">
         <is>
@@ -5349,17 +5424,17 @@
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B245" s="3" t="n">
-        <v>46246</v>
+        <v>46256</v>
       </c>
       <c r="C245" s="4" t="n">
-        <v>0.2284722222222222</v>
+        <v>0.2611111111111111</v>
       </c>
       <c r="D245" s="4" t="n">
-        <v>0.7423611111111111</v>
+        <v>0.7513888888888889</v>
       </c>
       <c r="E245" s="2" t="inlineStr">
         <is>
@@ -5370,40 +5445,38 @@
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B246" s="3" t="n">
-        <v>46247</v>
+        <v>46257</v>
       </c>
       <c r="C246" s="4" t="n">
-        <v>0.4402777777777778</v>
-      </c>
-      <c r="D246" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.24375</v>
+      </c>
+      <c r="D246" s="4" t="n">
+        <v>0.7263888888888889</v>
       </c>
       <c r="E246" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B247" s="3" t="n">
-        <v>46249</v>
+        <v>46258</v>
       </c>
       <c r="C247" s="4" t="n">
-        <v>0.2354166666666667</v>
+        <v>0.2631944444444445</v>
       </c>
       <c r="D247" s="4" t="n">
-        <v>0.7611111111111111</v>
+        <v>0.7270833333333333</v>
       </c>
       <c r="E247" s="2" t="inlineStr">
         <is>
@@ -5414,17 +5487,17 @@
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B248" s="3" t="n">
-        <v>46250</v>
+        <v>46259</v>
       </c>
       <c r="C248" s="4" t="n">
-        <v>0.2409722222222222</v>
+        <v>0.2611111111111111</v>
       </c>
       <c r="D248" s="4" t="n">
-        <v>0.7381944444444445</v>
+        <v>0.7298611111111111</v>
       </c>
       <c r="E248" s="2" t="inlineStr">
         <is>
@@ -5435,59 +5508,59 @@
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B249" s="3" t="n">
-        <v>46251</v>
+        <v>46260</v>
       </c>
       <c r="C249" s="4" t="n">
-        <v>0.3416666666666667</v>
+        <v>0.275</v>
       </c>
       <c r="D249" s="4" t="n">
-        <v>0.7326388888888888</v>
+        <v>0.8791666666666667</v>
       </c>
       <c r="E249" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>extra punch: 17:56</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B250" s="3" t="n">
-        <v>46252</v>
+        <v>46261</v>
       </c>
       <c r="C250" s="4" t="n">
-        <v>0.2916666666666667</v>
+        <v>0.2555555555555555</v>
       </c>
       <c r="D250" s="4" t="n">
-        <v>0.7416666666666667</v>
+        <v>0.8506944444444444</v>
       </c>
       <c r="E250" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>extra punches: 17:07 17:02</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B251" s="3" t="n">
-        <v>46253</v>
+        <v>46262</v>
       </c>
       <c r="C251" s="4" t="n">
-        <v>0.2395833333333333</v>
+        <v>0.2805555555555556</v>
       </c>
       <c r="D251" s="4" t="n">
-        <v>0.7416666666666667</v>
+        <v>0.7701388888888889</v>
       </c>
       <c r="E251" s="2" t="inlineStr">
         <is>
@@ -5498,17 +5571,17 @@
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B252" s="3" t="n">
-        <v>46254</v>
+        <v>46263</v>
       </c>
       <c r="C252" s="4" t="n">
-        <v>0.2472222222222222</v>
+        <v>0.2541666666666667</v>
       </c>
       <c r="D252" s="4" t="n">
-        <v>0.7243055555555555</v>
+        <v>0.7479166666666667</v>
       </c>
       <c r="E252" s="2" t="inlineStr">
         <is>
@@ -5519,103 +5592,80 @@
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B253" s="3" t="n">
-        <v>46256</v>
+        <v>46264</v>
       </c>
       <c r="C253" s="4" t="n">
-        <v>0.2875</v>
-      </c>
-      <c r="D253" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.2659722222222222</v>
+      </c>
+      <c r="D253" s="4" t="n">
+        <v>0.7354166666666667</v>
       </c>
       <c r="E253" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B254" s="3" t="n">
-        <v>46257</v>
+        <v>46265</v>
       </c>
       <c r="C254" s="4" t="n">
-        <v>0.2479166666666667</v>
+        <v>0.2527777777777778</v>
       </c>
       <c r="D254" s="4" t="n">
-        <v>0.7618055555555555</v>
+        <v>0.7354166666666667</v>
       </c>
       <c r="E254" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="B255" s="3" t="n">
-        <v>46258</v>
-      </c>
-      <c r="C255" s="4" t="n">
-        <v>0.2375</v>
-      </c>
-      <c r="D255" s="4" t="n">
-        <v>0.7506944444444444</v>
-      </c>
-      <c r="E255" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>corrected from a clearer re-scan photo later in the album</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B256" s="3" t="n">
-        <v>46259</v>
+        <v>46235</v>
       </c>
       <c r="C256" s="4" t="n">
-        <v>0.2375</v>
+        <v>0.2625</v>
       </c>
       <c r="D256" s="4" t="n">
-        <v>0.7597222222222222</v>
+        <v>0.7444444444444445</v>
       </c>
       <c r="E256" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>last day of month; final record</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B257" s="3" t="n">
-        <v>46260</v>
+        <v>46236</v>
       </c>
       <c r="C257" s="4" t="n">
-        <v>0.2479166666666667</v>
+        <v>0.2645833333333333</v>
       </c>
       <c r="D257" s="4" t="n">
-        <v>0.7555555555555555</v>
+        <v>0.7493055555555556</v>
       </c>
       <c r="E257" s="2" t="inlineStr">
         <is>
@@ -5626,17 +5676,17 @@
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B258" s="3" t="n">
-        <v>46261</v>
+        <v>46237</v>
       </c>
       <c r="C258" s="4" t="n">
-        <v>0.2493055555555556</v>
+        <v>0.2604166666666667</v>
       </c>
       <c r="D258" s="4" t="n">
-        <v>0.7944444444444444</v>
+        <v>0.7479166666666667</v>
       </c>
       <c r="E258" s="2" t="inlineStr">
         <is>
@@ -5647,61 +5697,59 @@
     <row r="259">
       <c r="A259" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B259" s="3" t="n">
-        <v>46262</v>
+        <v>46238</v>
       </c>
       <c r="C259" s="4" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="D259" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.2527777777777778</v>
+      </c>
+      <c r="D259" s="4" t="n">
+        <v>0.75</v>
       </c>
       <c r="E259" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B260" s="3" t="n">
-        <v>46263</v>
+        <v>46239</v>
       </c>
       <c r="C260" s="4" t="n">
-        <v>0.2569444444444444</v>
+        <v>0.25625</v>
       </c>
       <c r="D260" s="4" t="n">
-        <v>0.7458333333333333</v>
+        <v>0.7763888888888889</v>
       </c>
       <c r="E260" s="2" t="inlineStr">
         <is>
-          <t>extra punch: 17:53</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B261" s="3" t="n">
-        <v>46264</v>
+        <v>46240</v>
       </c>
       <c r="C261" s="4" t="n">
-        <v>0.2590277777777778</v>
+        <v>0.2701388888888889</v>
       </c>
       <c r="D261" s="4" t="n">
-        <v>0.7541666666666667</v>
+        <v>0.7423611111111111</v>
       </c>
       <c r="E261" s="2" t="inlineStr">
         <is>
@@ -5712,59 +5760,82 @@
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B262" s="3" t="n">
-        <v>46265</v>
+        <v>46242</v>
       </c>
       <c r="C262" s="4" t="n">
-        <v>0.2777777777777778</v>
+        <v>0.2597222222222222</v>
       </c>
       <c r="D262" s="4" t="n">
-        <v>0.7513888888888889</v>
+        <v>0.7326388888888888</v>
       </c>
       <c r="E262" s="2" t="inlineStr">
         <is>
-          <t>corrected from a clearer re-scan photo later in the album</t>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B263" s="3" t="n">
+        <v>46243</v>
+      </c>
+      <c r="C263" s="4" t="n">
+        <v>0.2381944444444444</v>
+      </c>
+      <c r="D263" s="4" t="n">
+        <v>0.75625</v>
+      </c>
+      <c r="E263" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B264" s="3" t="n">
-        <v>46235</v>
-      </c>
-      <c r="C264" s="4" t="n">
-        <v>0.2451388888888889</v>
+        <v>46244</v>
+      </c>
+      <c r="C264" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D264" s="4" t="n">
-        <v>0.7506944444444444</v>
+        <v>0.75625</v>
       </c>
       <c r="E264" s="2" t="inlineStr">
         <is>
-          <t>last day of month; final record</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B265" s="3" t="n">
-        <v>46236</v>
+        <v>46245</v>
       </c>
       <c r="C265" s="4" t="n">
-        <v>0.24375</v>
+        <v>0.2381944444444444</v>
       </c>
       <c r="D265" s="4" t="n">
-        <v>0.7520833333333333</v>
+        <v>0.7402777777777778</v>
       </c>
       <c r="E265" s="2" t="inlineStr">
         <is>
@@ -5775,17 +5846,17 @@
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B266" s="3" t="n">
-        <v>46237</v>
+        <v>46246</v>
       </c>
       <c r="C266" s="4" t="n">
-        <v>0.24375</v>
+        <v>0.2340277777777778</v>
       </c>
       <c r="D266" s="4" t="n">
-        <v>0.7527777777777778</v>
+        <v>0.7493055555555556</v>
       </c>
       <c r="E266" s="2" t="inlineStr">
         <is>
@@ -5796,17 +5867,17 @@
     <row r="267">
       <c r="A267" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B267" s="3" t="n">
-        <v>46238</v>
+        <v>46247</v>
       </c>
       <c r="C267" s="4" t="n">
-        <v>0.2451388888888889</v>
+        <v>0.2465277777777778</v>
       </c>
       <c r="D267" s="4" t="n">
-        <v>0.7520833333333333</v>
+        <v>0.7270833333333333</v>
       </c>
       <c r="E267" s="2" t="inlineStr">
         <is>
@@ -5817,17 +5888,17 @@
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B268" s="3" t="n">
-        <v>46239</v>
+        <v>46249</v>
       </c>
       <c r="C268" s="4" t="n">
-        <v>0.2368055555555555</v>
+        <v>0.2395833333333333</v>
       </c>
       <c r="D268" s="4" t="n">
-        <v>0.7611111111111111</v>
+        <v>0.7388888888888889</v>
       </c>
       <c r="E268" s="2" t="inlineStr">
         <is>
@@ -5838,17 +5909,17 @@
     <row r="269">
       <c r="A269" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B269" s="3" t="n">
-        <v>46240</v>
+        <v>46250</v>
       </c>
       <c r="C269" s="4" t="n">
-        <v>0.2402777777777778</v>
+        <v>0.2902777777777778</v>
       </c>
       <c r="D269" s="4" t="n">
-        <v>0.7513888888888889</v>
+        <v>0.7236111111111111</v>
       </c>
       <c r="E269" s="2" t="inlineStr">
         <is>
@@ -5859,17 +5930,17 @@
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B270" s="3" t="n">
-        <v>46242</v>
+        <v>46251</v>
       </c>
       <c r="C270" s="4" t="n">
-        <v>0.2430555555555556</v>
+        <v>0.2743055555555556</v>
       </c>
       <c r="D270" s="4" t="n">
-        <v>0.7548611111111111</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="E270" s="2" t="inlineStr">
         <is>
@@ -5880,42 +5951,38 @@
     <row r="271">
       <c r="A271" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B271" s="3" t="n">
-        <v>46246</v>
-      </c>
-      <c r="C271" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D271" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>46252</v>
+      </c>
+      <c r="C271" s="4" t="n">
+        <v>0.2826388888888889</v>
+      </c>
+      <c r="D271" s="4" t="n">
+        <v>0.7451388888888889</v>
       </c>
       <c r="E271" s="2" t="inlineStr">
         <is>
-          <t>PLEASE VERIFY: check-in/out times not captured (gap between source photos)</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B272" s="3" t="n">
-        <v>46247</v>
+        <v>46253</v>
       </c>
       <c r="C272" s="4" t="n">
-        <v>0.2444444444444444</v>
+        <v>0.2763888888888889</v>
       </c>
       <c r="D272" s="4" t="n">
-        <v>0.7576388888888889</v>
+        <v>0.7298611111111111</v>
       </c>
       <c r="E272" s="2" t="inlineStr">
         <is>
@@ -5926,17 +5993,17 @@
     <row r="273">
       <c r="A273" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B273" s="3" t="n">
-        <v>46249</v>
+        <v>46254</v>
       </c>
       <c r="C273" s="4" t="n">
-        <v>0.2381944444444444</v>
+        <v>0.275</v>
       </c>
       <c r="D273" s="4" t="n">
-        <v>0.7513888888888889</v>
+        <v>0.7256944444444444</v>
       </c>
       <c r="E273" s="2" t="inlineStr">
         <is>
@@ -5947,17 +6014,17 @@
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B274" s="3" t="n">
-        <v>46250</v>
+        <v>46256</v>
       </c>
       <c r="C274" s="4" t="n">
-        <v>0.2354166666666667</v>
+        <v>0.2805555555555556</v>
       </c>
       <c r="D274" s="4" t="n">
-        <v>0.7520833333333333</v>
+        <v>0.7513888888888889</v>
       </c>
       <c r="E274" s="2" t="inlineStr">
         <is>
@@ -5968,17 +6035,17 @@
     <row r="275">
       <c r="A275" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B275" s="3" t="n">
-        <v>46251</v>
+        <v>46261</v>
       </c>
       <c r="C275" s="4" t="n">
-        <v>0.2395833333333333</v>
+        <v>0.24375</v>
       </c>
       <c r="D275" s="4" t="n">
-        <v>0.7541666666666667</v>
+        <v>0.6763888888888889</v>
       </c>
       <c r="E275" s="2" t="inlineStr">
         <is>
@@ -5989,17 +6056,17 @@
     <row r="276">
       <c r="A276" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B276" s="3" t="n">
-        <v>46252</v>
+        <v>46263</v>
       </c>
       <c r="C276" s="4" t="n">
-        <v>0.2451388888888889</v>
+        <v>0.2965277777777778</v>
       </c>
       <c r="D276" s="4" t="n">
-        <v>0.7527777777777778</v>
+        <v>0.7472222222222222</v>
       </c>
       <c r="E276" s="2" t="inlineStr">
         <is>
@@ -6010,17 +6077,17 @@
     <row r="277">
       <c r="A277" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B277" s="3" t="n">
-        <v>46253</v>
+        <v>46264</v>
       </c>
       <c r="C277" s="4" t="n">
-        <v>0.2423611111111111</v>
+        <v>0.2888888888888889</v>
       </c>
       <c r="D277" s="4" t="n">
-        <v>0.7506944444444444</v>
+        <v>0.75</v>
       </c>
       <c r="E277" s="2" t="inlineStr">
         <is>
@@ -6031,40 +6098,19 @@
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B278" s="3" t="n">
-        <v>46254</v>
+        <v>46265</v>
       </c>
       <c r="C278" s="4" t="n">
-        <v>0.2402777777777778</v>
+        <v>0.2909722222222222</v>
       </c>
       <c r="D278" s="4" t="n">
-        <v>0.7520833333333333</v>
+        <v>0.75</v>
       </c>
       <c r="E278" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="279">
-      <c r="A279" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="B279" s="3" t="n">
-        <v>46256</v>
-      </c>
-      <c r="C279" s="4" t="n">
-        <v>0.2402777777777778</v>
-      </c>
-      <c r="D279" s="4" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="E279" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -6073,38 +6119,38 @@
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B280" s="3" t="n">
-        <v>46257</v>
+        <v>46235</v>
       </c>
       <c r="C280" s="4" t="n">
-        <v>0.2458333333333333</v>
+        <v>0.2381944444444444</v>
       </c>
       <c r="D280" s="4" t="n">
-        <v>0.7527777777777778</v>
+        <v>0.7458333333333333</v>
       </c>
       <c r="E280" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>last day of month; final record</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B281" s="3" t="n">
-        <v>46258</v>
+        <v>46236</v>
       </c>
       <c r="C281" s="4" t="n">
-        <v>0.2347222222222222</v>
+        <v>0.2958333333333333</v>
       </c>
       <c r="D281" s="4" t="n">
-        <v>0.7520833333333333</v>
+        <v>0.7430555555555556</v>
       </c>
       <c r="E281" s="2" t="inlineStr">
         <is>
@@ -6115,17 +6161,17 @@
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B282" s="3" t="n">
-        <v>46259</v>
+        <v>46237</v>
       </c>
       <c r="C282" s="4" t="n">
-        <v>0.2368055555555555</v>
+        <v>0.3034722222222222</v>
       </c>
       <c r="D282" s="4" t="n">
-        <v>0.7506944444444444</v>
+        <v>0.7159722222222222</v>
       </c>
       <c r="E282" s="2" t="inlineStr">
         <is>
@@ -6136,17 +6182,17 @@
     <row r="283">
       <c r="A283" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B283" s="3" t="n">
-        <v>46260</v>
+        <v>46238</v>
       </c>
       <c r="C283" s="4" t="n">
-        <v>0.2465277777777778</v>
+        <v>0.2763888888888889</v>
       </c>
       <c r="D283" s="4" t="n">
-        <v>0.7555555555555555</v>
+        <v>0.7166666666666667</v>
       </c>
       <c r="E283" s="2" t="inlineStr">
         <is>
@@ -6157,17 +6203,17 @@
     <row r="284">
       <c r="A284" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B284" s="3" t="n">
-        <v>46261</v>
+        <v>46239</v>
       </c>
       <c r="C284" s="4" t="n">
-        <v>0.2472222222222222</v>
+        <v>0.3222222222222222</v>
       </c>
       <c r="D284" s="4" t="n">
-        <v>0.7513888888888889</v>
+        <v>0.7715277777777778</v>
       </c>
       <c r="E284" s="2" t="inlineStr">
         <is>
@@ -6178,17 +6224,17 @@
     <row r="285">
       <c r="A285" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B285" s="3" t="n">
-        <v>46263</v>
+        <v>46240</v>
       </c>
       <c r="C285" s="4" t="n">
-        <v>0.2444444444444444</v>
+        <v>0.30625</v>
       </c>
       <c r="D285" s="4" t="n">
-        <v>0.7548611111111111</v>
+        <v>0.7590277777777777</v>
       </c>
       <c r="E285" s="2" t="inlineStr">
         <is>
@@ -6199,17 +6245,17 @@
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B286" s="3" t="n">
-        <v>46264</v>
+        <v>46242</v>
       </c>
       <c r="C286" s="4" t="n">
-        <v>0.2423611111111111</v>
+        <v>0.3055555555555556</v>
       </c>
       <c r="D286" s="4" t="n">
-        <v>0.7513888888888889</v>
+        <v>0.7604166666666666</v>
       </c>
       <c r="E286" s="2" t="inlineStr">
         <is>
@@ -6220,101 +6266,128 @@
     <row r="287">
       <c r="A287" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B287" s="3" t="n">
-        <v>46265</v>
+        <v>46243</v>
       </c>
       <c r="C287" s="4" t="n">
-        <v>0.2361111111111111</v>
+        <v>0.2798611111111111</v>
       </c>
       <c r="D287" s="4" t="n">
-        <v>0.7520833333333333</v>
+        <v>0.75</v>
       </c>
       <c r="E287" s="2" t="inlineStr">
         <is>
-          <t>corrected from a clearer re-scan photo later in the album</t>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B288" s="3" t="n">
+        <v>46244</v>
+      </c>
+      <c r="C288" s="4" t="n">
+        <v>0.2263888888888889</v>
+      </c>
+      <c r="D288" s="4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E288" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B289" s="3" t="n">
-        <v>46235</v>
+        <v>46245</v>
       </c>
       <c r="C289" s="4" t="n">
-        <v>0.275</v>
-      </c>
-      <c r="D289" s="4" t="n">
-        <v>0.7854166666666667</v>
+        <v>0.3118055555555556</v>
+      </c>
+      <c r="D289" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E289" s="2" t="inlineStr">
         <is>
-          <t>last day of month; final record</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B290" s="3" t="n">
-        <v>46236</v>
+        <v>46246</v>
       </c>
       <c r="C290" s="4" t="n">
-        <v>0.2722222222222222</v>
-      </c>
-      <c r="D290" s="4" t="n">
-        <v>0.7722222222222223</v>
+        <v>0.2986111111111111</v>
+      </c>
+      <c r="D290" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E290" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B291" s="3" t="n">
-        <v>46237</v>
+        <v>46247</v>
       </c>
       <c r="C291" s="4" t="n">
-        <v>0.2451388888888889</v>
-      </c>
-      <c r="D291" s="4" t="n">
-        <v>0.7201388888888889</v>
+        <v>0.3347222222222222</v>
+      </c>
+      <c r="D291" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E291" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B292" s="3" t="n">
-        <v>46238</v>
+        <v>46249</v>
       </c>
       <c r="C292" s="4" t="n">
-        <v>0.2729166666666666</v>
+        <v>0.2354166666666667</v>
       </c>
       <c r="D292" s="4" t="n">
-        <v>0.7527777777777778</v>
+        <v>0.75</v>
       </c>
       <c r="E292" s="2" t="inlineStr">
         <is>
@@ -6325,17 +6398,17 @@
     <row r="293">
       <c r="A293" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B293" s="3" t="n">
-        <v>46239</v>
+        <v>46250</v>
       </c>
       <c r="C293" s="4" t="n">
-        <v>0.2756944444444445</v>
+        <v>0.325</v>
       </c>
       <c r="D293" s="4" t="n">
-        <v>0.7152777777777778</v>
+        <v>0.7722222222222223</v>
       </c>
       <c r="E293" s="2" t="inlineStr">
         <is>
@@ -6346,40 +6419,38 @@
     <row r="294">
       <c r="A294" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B294" s="3" t="n">
-        <v>46240</v>
+        <v>46251</v>
       </c>
       <c r="C294" s="4" t="n">
-        <v>0.2715277777777778</v>
-      </c>
-      <c r="D294" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.3979166666666666</v>
+      </c>
+      <c r="D294" s="4" t="n">
+        <v>0.7680555555555556</v>
       </c>
       <c r="E294" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B295" s="3" t="n">
-        <v>46242</v>
+        <v>46252</v>
       </c>
       <c r="C295" s="4" t="n">
-        <v>0.2388888888888889</v>
+        <v>0.3083333333333333</v>
       </c>
       <c r="D295" s="4" t="n">
-        <v>0.6965277777777777</v>
+        <v>0.7583333333333333</v>
       </c>
       <c r="E295" s="2" t="inlineStr">
         <is>
@@ -6390,17 +6461,17 @@
     <row r="296">
       <c r="A296" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B296" s="3" t="n">
-        <v>46243</v>
+        <v>46253</v>
       </c>
       <c r="C296" s="4" t="n">
-        <v>0.2451388888888889</v>
+        <v>0.475</v>
       </c>
       <c r="D296" s="4" t="n">
-        <v>0.7694444444444445</v>
+        <v>0.7173611111111111</v>
       </c>
       <c r="E296" s="2" t="inlineStr">
         <is>
@@ -6411,38 +6482,40 @@
     <row r="297">
       <c r="A297" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B297" s="3" t="n">
-        <v>46244</v>
+        <v>46254</v>
       </c>
       <c r="C297" s="4" t="n">
-        <v>0.2298611111111111</v>
-      </c>
-      <c r="D297" s="4" t="n">
-        <v>0.75625</v>
+        <v>0.3576388888888889</v>
+      </c>
+      <c r="D297" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E297" s="2" t="inlineStr">
         <is>
-          <t>extra punch: 06:48</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B298" s="3" t="n">
-        <v>46245</v>
+        <v>46256</v>
       </c>
       <c r="C298" s="4" t="n">
-        <v>0.275</v>
+        <v>0.2069444444444444</v>
       </c>
       <c r="D298" s="4" t="n">
-        <v>0.7618055555555555</v>
+        <v>0.7243055555555555</v>
       </c>
       <c r="E298" s="2" t="inlineStr">
         <is>
@@ -6453,17 +6526,17 @@
     <row r="299">
       <c r="A299" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B299" s="3" t="n">
-        <v>46246</v>
+        <v>46257</v>
       </c>
       <c r="C299" s="4" t="n">
-        <v>0.2694444444444444</v>
+        <v>0.25</v>
       </c>
       <c r="D299" s="4" t="n">
-        <v>0.7222222222222222</v>
+        <v>0.7493055555555556</v>
       </c>
       <c r="E299" s="2" t="inlineStr">
         <is>
@@ -6474,17 +6547,17 @@
     <row r="300">
       <c r="A300" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B300" s="3" t="n">
-        <v>46247</v>
+        <v>46258</v>
       </c>
       <c r="C300" s="4" t="n">
-        <v>0.3409722222222222</v>
+        <v>0.3263888888888889</v>
       </c>
       <c r="D300" s="4" t="n">
-        <v>0.7583333333333333</v>
+        <v>0.7388888888888889</v>
       </c>
       <c r="E300" s="2" t="inlineStr">
         <is>
@@ -6495,17 +6568,17 @@
     <row r="301">
       <c r="A301" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B301" s="3" t="n">
-        <v>46249</v>
+        <v>46259</v>
       </c>
       <c r="C301" s="4" t="n">
-        <v>0.2680555555555555</v>
+        <v>0.2763888888888889</v>
       </c>
       <c r="D301" s="4" t="n">
-        <v>0.7625</v>
+        <v>0.7548611111111111</v>
       </c>
       <c r="E301" s="2" t="inlineStr">
         <is>
@@ -6516,38 +6589,38 @@
     <row r="302">
       <c r="A302" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B302" s="3" t="n">
-        <v>46250</v>
+        <v>46260</v>
       </c>
       <c r="C302" s="4" t="n">
-        <v>0.3416666666666667</v>
+        <v>0.3243055555555556</v>
       </c>
       <c r="D302" s="4" t="n">
-        <v>0.7173611111111111</v>
+        <v>0.7534722222222222</v>
       </c>
       <c r="E302" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>extra punch: 17:56</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B303" s="3" t="n">
-        <v>46251</v>
+        <v>46261</v>
       </c>
       <c r="C303" s="4" t="n">
-        <v>0.3104166666666667</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="D303" s="4" t="n">
-        <v>0.7069444444444445</v>
+        <v>0.75</v>
       </c>
       <c r="E303" s="2" t="inlineStr">
         <is>
@@ -6558,17 +6631,17 @@
     <row r="304">
       <c r="A304" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B304" s="3" t="n">
-        <v>46252</v>
+        <v>46263</v>
       </c>
       <c r="C304" s="4" t="n">
-        <v>0.3659722222222222</v>
+        <v>0.2965277777777778</v>
       </c>
       <c r="D304" s="4" t="n">
-        <v>0.7208333333333333</v>
+        <v>0.7326388888888888</v>
       </c>
       <c r="E304" s="2" t="inlineStr">
         <is>
@@ -6579,17 +6652,17 @@
     <row r="305">
       <c r="A305" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B305" s="3" t="n">
-        <v>46253</v>
+        <v>46264</v>
       </c>
       <c r="C305" s="4" t="n">
-        <v>0.2944444444444445</v>
+        <v>0.2965277777777778</v>
       </c>
       <c r="D305" s="4" t="n">
-        <v>0.7305555555555555</v>
+        <v>0.75625</v>
       </c>
       <c r="E305" s="2" t="inlineStr">
         <is>
@@ -6600,80 +6673,59 @@
     <row r="306">
       <c r="A306" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B306" s="3" t="n">
-        <v>46254</v>
+        <v>46265</v>
       </c>
       <c r="C306" s="4" t="n">
-        <v>0.4298611111111111</v>
+        <v>0.2527777777777778</v>
       </c>
       <c r="D306" s="4" t="n">
-        <v>0.70625</v>
+        <v>0.7604166666666666</v>
       </c>
       <c r="E306" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="307">
-      <c r="A307" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="B307" s="3" t="n">
-        <v>46256</v>
-      </c>
-      <c r="C307" s="4" t="n">
-        <v>0.2888888888888889</v>
-      </c>
-      <c r="D307" s="4" t="n">
-        <v>0.7083333333333334</v>
-      </c>
-      <c r="E307" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>corrected from a clearer re-scan photo later in the album</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B308" s="3" t="n">
-        <v>46257</v>
+        <v>46235</v>
       </c>
       <c r="C308" s="4" t="n">
-        <v>0.2444444444444444</v>
+        <v>0.2590277777777778</v>
       </c>
       <c r="D308" s="4" t="n">
-        <v>0.7076388888888889</v>
+        <v>0.7319444444444444</v>
       </c>
       <c r="E308" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>last day of month; final record</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B309" s="3" t="n">
-        <v>46258</v>
+        <v>46236</v>
       </c>
       <c r="C309" s="4" t="n">
-        <v>0.2784722222222222</v>
+        <v>0.2972222222222222</v>
       </c>
       <c r="D309" s="4" t="n">
-        <v>0.7055555555555556</v>
+        <v>0.7430555555555556</v>
       </c>
       <c r="E309" s="2" t="inlineStr">
         <is>
@@ -6684,17 +6736,17 @@
     <row r="310">
       <c r="A310" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B310" s="3" t="n">
-        <v>46259</v>
+        <v>46237</v>
       </c>
       <c r="C310" s="4" t="n">
-        <v>0.2854166666666667</v>
+        <v>0.2618055555555556</v>
       </c>
       <c r="D310" s="4" t="n">
-        <v>0.7222222222222222</v>
+        <v>0.7472222222222222</v>
       </c>
       <c r="E310" s="2" t="inlineStr">
         <is>
@@ -6705,17 +6757,17 @@
     <row r="311">
       <c r="A311" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B311" s="3" t="n">
-        <v>46260</v>
+        <v>46238</v>
       </c>
       <c r="C311" s="4" t="n">
-        <v>0.2375</v>
+        <v>0.4965277777777778</v>
       </c>
       <c r="D311" s="4" t="n">
-        <v>0.7152777777777778</v>
+        <v>0.7506944444444444</v>
       </c>
       <c r="E311" s="2" t="inlineStr">
         <is>
@@ -6726,17 +6778,17 @@
     <row r="312">
       <c r="A312" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B312" s="3" t="n">
-        <v>46261</v>
+        <v>46239</v>
       </c>
       <c r="C312" s="4" t="n">
-        <v>0.4881944444444444</v>
+        <v>0.4743055555555555</v>
       </c>
       <c r="D312" s="4" t="n">
-        <v>0.7111111111111111</v>
+        <v>0.7722222222222223</v>
       </c>
       <c r="E312" s="2" t="inlineStr">
         <is>
@@ -6747,17 +6799,17 @@
     <row r="313">
       <c r="A313" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B313" s="3" t="n">
-        <v>46263</v>
+        <v>46240</v>
       </c>
       <c r="C313" s="4" t="n">
-        <v>0.2513888888888889</v>
+        <v>0.2409722222222222</v>
       </c>
       <c r="D313" s="4" t="n">
-        <v>0.7104166666666667</v>
+        <v>0.7625</v>
       </c>
       <c r="E313" s="2" t="inlineStr">
         <is>
@@ -6768,17 +6820,17 @@
     <row r="314">
       <c r="A314" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B314" s="3" t="n">
-        <v>46264</v>
+        <v>46242</v>
       </c>
       <c r="C314" s="4" t="n">
-        <v>0.2958333333333333</v>
+        <v>0.2201388888888889</v>
       </c>
       <c r="D314" s="4" t="n">
-        <v>0.7215277777777778</v>
+        <v>0.7618055555555555</v>
       </c>
       <c r="E314" s="2" t="inlineStr">
         <is>
@@ -6789,105 +6841,124 @@
     <row r="315">
       <c r="A315" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B315" s="3" t="n">
-        <v>46265</v>
-      </c>
-      <c r="C315" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>46243</v>
+      </c>
+      <c r="C315" s="4" t="n">
+        <v>0.2395833333333333</v>
       </c>
       <c r="D315" s="4" t="n">
-        <v>0.7097222222222223</v>
+        <v>0.725</v>
       </c>
       <c r="E315" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B316" s="3" t="n">
+        <v>46244</v>
+      </c>
+      <c r="C316" s="4" t="n">
+        <v>0.2256944444444444</v>
+      </c>
+      <c r="D316" s="4" t="n">
+        <v>0.7611111111111111</v>
+      </c>
+      <c r="E316" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B317" s="3" t="n">
-        <v>46235</v>
+        <v>46245</v>
       </c>
       <c r="C317" s="4" t="n">
-        <v>0.3305555555555555</v>
+        <v>0.2375</v>
       </c>
       <c r="D317" s="4" t="n">
-        <v>0.7347222222222223</v>
+        <v>0.7375</v>
       </c>
       <c r="E317" s="2" t="inlineStr">
         <is>
-          <t>last day of month; final record</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B318" s="3" t="n">
-        <v>46236</v>
-      </c>
-      <c r="C318" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>46246</v>
+      </c>
+      <c r="C318" s="4" t="n">
+        <v>0.2284722222222222</v>
       </c>
       <c r="D318" s="4" t="n">
-        <v>0.3583333333333333</v>
+        <v>0.7423611111111111</v>
       </c>
       <c r="E318" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B319" s="3" t="n">
-        <v>46237</v>
+        <v>46247</v>
       </c>
       <c r="C319" s="4" t="n">
-        <v>0.3291666666666667</v>
-      </c>
-      <c r="D319" s="4" t="n">
-        <v>0.7111111111111111</v>
+        <v>0.4402777777777778</v>
+      </c>
+      <c r="D319" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E319" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B320" s="3" t="n">
-        <v>46238</v>
+        <v>46249</v>
       </c>
       <c r="C320" s="4" t="n">
-        <v>0.3305555555555555</v>
+        <v>0.2354166666666667</v>
       </c>
       <c r="D320" s="4" t="n">
-        <v>0.7263888888888889</v>
+        <v>0.7611111111111111</v>
       </c>
       <c r="E320" s="2" t="inlineStr">
         <is>
@@ -6898,40 +6969,38 @@
     <row r="321">
       <c r="A321" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B321" s="3" t="n">
-        <v>46239</v>
-      </c>
-      <c r="C321" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>46250</v>
+      </c>
+      <c r="C321" s="4" t="n">
+        <v>0.2409722222222222</v>
       </c>
       <c r="D321" s="4" t="n">
-        <v>0.7715277777777778</v>
+        <v>0.7381944444444445</v>
       </c>
       <c r="E321" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B322" s="3" t="n">
-        <v>46240</v>
+        <v>46251</v>
       </c>
       <c r="C322" s="4" t="n">
-        <v>0.3986111111111111</v>
+        <v>0.3416666666666667</v>
       </c>
       <c r="D322" s="4" t="n">
-        <v>0.7277777777777777</v>
+        <v>0.7326388888888888</v>
       </c>
       <c r="E322" s="2" t="inlineStr">
         <is>
@@ -6942,17 +7011,17 @@
     <row r="323">
       <c r="A323" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B323" s="3" t="n">
-        <v>46242</v>
+        <v>46252</v>
       </c>
       <c r="C323" s="4" t="n">
-        <v>0.2791666666666667</v>
+        <v>0.2916666666666667</v>
       </c>
       <c r="D323" s="4" t="n">
-        <v>0.7284722222222222</v>
+        <v>0.7416666666666667</v>
       </c>
       <c r="E323" s="2" t="inlineStr">
         <is>
@@ -6963,17 +7032,17 @@
     <row r="324">
       <c r="A324" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B324" s="3" t="n">
-        <v>46243</v>
+        <v>46253</v>
       </c>
       <c r="C324" s="4" t="n">
-        <v>0.2784722222222222</v>
+        <v>0.2395833333333333</v>
       </c>
       <c r="D324" s="4" t="n">
-        <v>0.7555555555555555</v>
+        <v>0.7416666666666667</v>
       </c>
       <c r="E324" s="2" t="inlineStr">
         <is>
@@ -6984,17 +7053,17 @@
     <row r="325">
       <c r="A325" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B325" s="3" t="n">
-        <v>46244</v>
+        <v>46254</v>
       </c>
       <c r="C325" s="4" t="n">
-        <v>0.2875</v>
+        <v>0.2472222222222222</v>
       </c>
       <c r="D325" s="4" t="n">
-        <v>0.7479166666666667</v>
+        <v>0.7243055555555555</v>
       </c>
       <c r="E325" s="2" t="inlineStr">
         <is>
@@ -7005,101 +7074,103 @@
     <row r="326">
       <c r="A326" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B326" s="3" t="n">
-        <v>46245</v>
+        <v>46256</v>
       </c>
       <c r="C326" s="4" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="D326" s="4" t="n">
-        <v>0.7465277777777778</v>
+        <v>0.2875</v>
+      </c>
+      <c r="D326" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E326" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B327" s="3" t="n">
-        <v>46246</v>
+        <v>46257</v>
       </c>
       <c r="C327" s="4" t="n">
-        <v>0.2548611111111111</v>
+        <v>0.2479166666666667</v>
       </c>
       <c r="D327" s="4" t="n">
-        <v>0.7222222222222222</v>
+        <v>0.7618055555555555</v>
       </c>
       <c r="E327" s="2" t="inlineStr">
         <is>
-          <t>extra punches: 07:44 06:16</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B328" s="3" t="n">
-        <v>46247</v>
+        <v>46258</v>
       </c>
       <c r="C328" s="4" t="n">
-        <v>0.3388888888888889</v>
+        <v>0.2375</v>
       </c>
       <c r="D328" s="4" t="n">
-        <v>0.7236111111111111</v>
+        <v>0.7506944444444444</v>
       </c>
       <c r="E328" s="2" t="inlineStr">
         <is>
-          <t>extra punch: 17:21</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B329" s="3" t="n">
-        <v>46249</v>
+        <v>46259</v>
       </c>
       <c r="C329" s="4" t="n">
-        <v>0.2423611111111111</v>
+        <v>0.2375</v>
       </c>
       <c r="D329" s="4" t="n">
-        <v>0.7270833333333333</v>
+        <v>0.7597222222222222</v>
       </c>
       <c r="E329" s="2" t="inlineStr">
         <is>
-          <t>extra punches: 17:27 07:28</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B330" s="3" t="n">
-        <v>46250</v>
+        <v>46260</v>
       </c>
       <c r="C330" s="4" t="n">
-        <v>0.3409722222222222</v>
+        <v>0.2479166666666667</v>
       </c>
       <c r="D330" s="4" t="n">
-        <v>0.7104166666666667</v>
+        <v>0.7555555555555555</v>
       </c>
       <c r="E330" s="2" t="inlineStr">
         <is>
@@ -7110,17 +7181,17 @@
     <row r="331">
       <c r="A331" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B331" s="3" t="n">
-        <v>46251</v>
+        <v>46261</v>
       </c>
       <c r="C331" s="4" t="n">
-        <v>0.2833333333333333</v>
+        <v>0.2493055555555556</v>
       </c>
       <c r="D331" s="4" t="n">
-        <v>0.7326388888888888</v>
+        <v>0.7944444444444444</v>
       </c>
       <c r="E331" s="2" t="inlineStr">
         <is>
@@ -7131,149 +7202,124 @@
     <row r="332">
       <c r="A332" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B332" s="3" t="n">
-        <v>46252</v>
+        <v>46262</v>
       </c>
       <c r="C332" s="4" t="n">
-        <v>0.28125</v>
-      </c>
-      <c r="D332" s="4" t="n">
-        <v>0.7645833333333333</v>
+        <v>0.25</v>
+      </c>
+      <c r="D332" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E332" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B333" s="3" t="n">
-        <v>46253</v>
+        <v>46263</v>
       </c>
       <c r="C333" s="4" t="n">
-        <v>0.3166666666666667</v>
+        <v>0.2569444444444444</v>
       </c>
       <c r="D333" s="4" t="n">
-        <v>0.74375</v>
+        <v>0.7458333333333333</v>
       </c>
       <c r="E333" s="2" t="inlineStr">
         <is>
-          <t>extra punch: 08:01</t>
+          <t>extra punch: 17:53</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B334" s="3" t="n">
-        <v>46254</v>
+        <v>46264</v>
       </c>
       <c r="C334" s="4" t="n">
-        <v>0.2868055555555555</v>
-      </c>
-      <c r="D334" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.2590277777777778</v>
+      </c>
+      <c r="D334" s="4" t="n">
+        <v>0.7541666666666667</v>
       </c>
       <c r="E334" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B335" s="3" t="n">
-        <v>46256</v>
-      </c>
-      <c r="C335" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>46265</v>
+      </c>
+      <c r="C335" s="4" t="n">
+        <v>0.2777777777777778</v>
       </c>
       <c r="D335" s="4" t="n">
-        <v>0.74375</v>
+        <v>0.7513888888888889</v>
       </c>
       <c r="E335" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
-        </is>
-      </c>
-    </row>
-    <row r="336">
-      <c r="A336" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="B336" s="3" t="n">
-        <v>46257</v>
-      </c>
-      <c r="C336" s="4" t="n">
-        <v>0.2548611111111111</v>
-      </c>
-      <c r="D336" s="4" t="n">
-        <v>0.7569444444444444</v>
-      </c>
-      <c r="E336" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>corrected from a clearer re-scan photo later in the album</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B337" s="3" t="n">
-        <v>46258</v>
-      </c>
-      <c r="C337" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>46235</v>
+      </c>
+      <c r="C337" s="4" t="n">
+        <v>0.2451388888888889</v>
       </c>
       <c r="D337" s="4" t="n">
         <v>0.7506944444444444</v>
       </c>
       <c r="E337" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>last day of month; final record</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B338" s="3" t="n">
-        <v>46259</v>
+        <v>46236</v>
       </c>
       <c r="C338" s="4" t="n">
-        <v>0.2868055555555555</v>
+        <v>0.24375</v>
       </c>
       <c r="D338" s="4" t="n">
-        <v>0.6895833333333333</v>
+        <v>0.7520833333333333</v>
       </c>
       <c r="E338" s="2" t="inlineStr">
         <is>
@@ -7284,40 +7330,38 @@
     <row r="339">
       <c r="A339" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B339" s="3" t="n">
-        <v>46260</v>
-      </c>
-      <c r="C339" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>46237</v>
+      </c>
+      <c r="C339" s="4" t="n">
+        <v>0.24375</v>
       </c>
       <c r="D339" s="4" t="n">
-        <v>0.6986111111111111</v>
+        <v>0.7527777777777778</v>
       </c>
       <c r="E339" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B340" s="3" t="n">
-        <v>46261</v>
+        <v>46238</v>
       </c>
       <c r="C340" s="4" t="n">
-        <v>0.2833333333333333</v>
+        <v>0.2451388888888889</v>
       </c>
       <c r="D340" s="4" t="n">
-        <v>0.8645833333333334</v>
+        <v>0.7520833333333333</v>
       </c>
       <c r="E340" s="2" t="inlineStr">
         <is>
@@ -7328,40 +7372,38 @@
     <row r="341">
       <c r="A341" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B341" s="3" t="n">
-        <v>46263</v>
-      </c>
-      <c r="C341" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>46239</v>
+      </c>
+      <c r="C341" s="4" t="n">
+        <v>0.2368055555555555</v>
       </c>
       <c r="D341" s="4" t="n">
-        <v>0.7291666666666666</v>
+        <v>0.7611111111111111</v>
       </c>
       <c r="E341" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B342" s="3" t="n">
-        <v>46264</v>
+        <v>46240</v>
       </c>
       <c r="C342" s="4" t="n">
-        <v>0.2798611111111111</v>
+        <v>0.2402777777777778</v>
       </c>
       <c r="D342" s="4" t="n">
-        <v>0.7472222222222222</v>
+        <v>0.7513888888888889</v>
       </c>
       <c r="E342" s="2" t="inlineStr">
         <is>
@@ -7372,59 +7414,84 @@
     <row r="343">
       <c r="A343" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B343" s="3" t="n">
-        <v>46265</v>
+        <v>46242</v>
       </c>
       <c r="C343" s="4" t="n">
-        <v>0.3888888888888889</v>
+        <v>0.2430555555555556</v>
       </c>
       <c r="D343" s="4" t="n">
-        <v>0.7215277777777778</v>
+        <v>0.7548611111111111</v>
       </c>
       <c r="E343" s="2" t="inlineStr">
         <is>
-          <t>corrected from a clearer re-scan photo later in the album</t>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B344" s="3" t="n">
+        <v>46246</v>
+      </c>
+      <c r="C344" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D344" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E344" s="2" t="inlineStr">
+        <is>
+          <t>PLEASE VERIFY: check-in/out times not captured (gap between source photos)</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B345" s="3" t="n">
-        <v>46235</v>
+        <v>46247</v>
       </c>
       <c r="C345" s="4" t="n">
-        <v>0.2569444444444444</v>
+        <v>0.2444444444444444</v>
       </c>
       <c r="D345" s="4" t="n">
-        <v>0.7430555555555556</v>
+        <v>0.7576388888888889</v>
       </c>
       <c r="E345" s="2" t="inlineStr">
         <is>
-          <t>extra punch: 17:55; last day of month; final record</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B346" s="3" t="n">
-        <v>46236</v>
+        <v>46249</v>
       </c>
       <c r="C346" s="4" t="n">
-        <v>0.2201388888888889</v>
+        <v>0.2381944444444444</v>
       </c>
       <c r="D346" s="4" t="n">
-        <v>0.7381944444444445</v>
+        <v>0.7513888888888889</v>
       </c>
       <c r="E346" s="2" t="inlineStr">
         <is>
@@ -7435,38 +7502,38 @@
     <row r="347">
       <c r="A347" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B347" s="3" t="n">
-        <v>46237</v>
+        <v>46250</v>
       </c>
       <c r="C347" s="4" t="n">
-        <v>0.2472222222222222</v>
+        <v>0.2354166666666667</v>
       </c>
       <c r="D347" s="4" t="n">
-        <v>0.7402777777777778</v>
+        <v>0.7520833333333333</v>
       </c>
       <c r="E347" s="2" t="inlineStr">
         <is>
-          <t>extra punch: 17:46</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B348" s="3" t="n">
-        <v>46238</v>
+        <v>46251</v>
       </c>
       <c r="C348" s="4" t="n">
-        <v>0.2173611111111111</v>
+        <v>0.2395833333333333</v>
       </c>
       <c r="D348" s="4" t="n">
-        <v>0.7604166666666666</v>
+        <v>0.7541666666666667</v>
       </c>
       <c r="E348" s="2" t="inlineStr">
         <is>
@@ -7477,38 +7544,38 @@
     <row r="349">
       <c r="A349" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B349" s="3" t="n">
-        <v>46239</v>
+        <v>46252</v>
       </c>
       <c r="C349" s="4" t="n">
-        <v>0.2333333333333333</v>
+        <v>0.2451388888888889</v>
       </c>
       <c r="D349" s="4" t="n">
-        <v>0.7611111111111111</v>
+        <v>0.7527777777777778</v>
       </c>
       <c r="E349" s="2" t="inlineStr">
         <is>
-          <t>extra punch: 18:16</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B350" s="3" t="n">
-        <v>46240</v>
+        <v>46253</v>
       </c>
       <c r="C350" s="4" t="n">
-        <v>0.2277777777777778</v>
+        <v>0.2423611111111111</v>
       </c>
       <c r="D350" s="4" t="n">
-        <v>0.75625</v>
+        <v>0.7506944444444444</v>
       </c>
       <c r="E350" s="2" t="inlineStr">
         <is>
@@ -7519,38 +7586,38 @@
     <row r="351">
       <c r="A351" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B351" s="3" t="n">
-        <v>46242</v>
+        <v>46254</v>
       </c>
       <c r="C351" s="4" t="n">
-        <v>0.2479166666666667</v>
+        <v>0.2402777777777778</v>
       </c>
       <c r="D351" s="4" t="n">
-        <v>0.7291666666666666</v>
+        <v>0.7520833333333333</v>
       </c>
       <c r="E351" s="2" t="inlineStr">
         <is>
-          <t>extra punch: 07:09</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B352" s="3" t="n">
-        <v>46243</v>
+        <v>46256</v>
       </c>
       <c r="C352" s="4" t="n">
-        <v>0.2368055555555555</v>
+        <v>0.2402777777777778</v>
       </c>
       <c r="D352" s="4" t="n">
-        <v>0.6729166666666667</v>
+        <v>0.75</v>
       </c>
       <c r="E352" s="2" t="inlineStr">
         <is>
@@ -7561,17 +7628,17 @@
     <row r="353">
       <c r="A353" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B353" s="3" t="n">
-        <v>46244</v>
+        <v>46257</v>
       </c>
       <c r="C353" s="4" t="n">
-        <v>0.2534722222222222</v>
+        <v>0.2458333333333333</v>
       </c>
       <c r="D353" s="4" t="n">
-        <v>0.7479166666666667</v>
+        <v>0.7527777777777778</v>
       </c>
       <c r="E353" s="2" t="inlineStr">
         <is>
@@ -7582,17 +7649,17 @@
     <row r="354">
       <c r="A354" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B354" s="3" t="n">
-        <v>46245</v>
+        <v>46258</v>
       </c>
       <c r="C354" s="4" t="n">
-        <v>0.2541666666666667</v>
+        <v>0.2347222222222222</v>
       </c>
       <c r="D354" s="4" t="n">
-        <v>0.7465277777777778</v>
+        <v>0.7520833333333333</v>
       </c>
       <c r="E354" s="2" t="inlineStr">
         <is>
@@ -7603,17 +7670,17 @@
     <row r="355">
       <c r="A355" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B355" s="3" t="n">
-        <v>46246</v>
+        <v>46259</v>
       </c>
       <c r="C355" s="4" t="n">
-        <v>0.2618055555555556</v>
+        <v>0.2368055555555555</v>
       </c>
       <c r="D355" s="4" t="n">
-        <v>0.75</v>
+        <v>0.7506944444444444</v>
       </c>
       <c r="E355" s="2" t="inlineStr">
         <is>
@@ -7624,17 +7691,17 @@
     <row r="356">
       <c r="A356" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B356" s="3" t="n">
-        <v>46247</v>
+        <v>46260</v>
       </c>
       <c r="C356" s="4" t="n">
-        <v>0.25625</v>
+        <v>0.2465277777777778</v>
       </c>
       <c r="D356" s="4" t="n">
-        <v>0.75</v>
+        <v>0.7555555555555555</v>
       </c>
       <c r="E356" s="2" t="inlineStr">
         <is>
@@ -7645,38 +7712,38 @@
     <row r="357">
       <c r="A357" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B357" s="3" t="n">
-        <v>46249</v>
+        <v>46261</v>
       </c>
       <c r="C357" s="4" t="n">
-        <v>0.2333333333333333</v>
+        <v>0.2472222222222222</v>
       </c>
       <c r="D357" s="4" t="n">
-        <v>0.7506944444444444</v>
+        <v>0.7513888888888889</v>
       </c>
       <c r="E357" s="2" t="inlineStr">
         <is>
-          <t>extra punch: 06:05</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B358" s="3" t="n">
-        <v>46250</v>
+        <v>46263</v>
       </c>
       <c r="C358" s="4" t="n">
-        <v>0.25625</v>
+        <v>0.2444444444444444</v>
       </c>
       <c r="D358" s="4" t="n">
-        <v>0.7458333333333333</v>
+        <v>0.7548611111111111</v>
       </c>
       <c r="E358" s="2" t="inlineStr">
         <is>
@@ -7687,17 +7754,17 @@
     <row r="359">
       <c r="A359" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B359" s="3" t="n">
-        <v>46251</v>
+        <v>46264</v>
       </c>
       <c r="C359" s="4" t="n">
-        <v>0.2541666666666667</v>
+        <v>0.2423611111111111</v>
       </c>
       <c r="D359" s="4" t="n">
-        <v>0.7555555555555555</v>
+        <v>0.7513888888888889</v>
       </c>
       <c r="E359" s="2" t="inlineStr">
         <is>
@@ -7708,101 +7775,80 @@
     <row r="360">
       <c r="A360" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B360" s="3" t="n">
-        <v>46252</v>
+        <v>46265</v>
       </c>
       <c r="C360" s="4" t="n">
-        <v>0.2395833333333333</v>
+        <v>0.2361111111111111</v>
       </c>
       <c r="D360" s="4" t="n">
-        <v>0.7611111111111111</v>
+        <v>0.7520833333333333</v>
       </c>
       <c r="E360" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="361">
-      <c r="A361" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="B361" s="3" t="n">
-        <v>46253</v>
-      </c>
-      <c r="C361" s="4" t="n">
-        <v>0.2527777777777778</v>
-      </c>
-      <c r="D361" s="4" t="n">
-        <v>0.7423611111111111</v>
-      </c>
-      <c r="E361" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>corrected from a clearer re-scan photo later in the album</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B362" s="3" t="n">
-        <v>46254</v>
+        <v>46235</v>
       </c>
       <c r="C362" s="4" t="n">
-        <v>0.2583333333333334</v>
+        <v>0.275</v>
       </c>
       <c r="D362" s="4" t="n">
-        <v>0.7451388888888889</v>
+        <v>0.7854166666666667</v>
       </c>
       <c r="E362" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>last day of month; final record</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B363" s="3" t="n">
-        <v>46256</v>
+        <v>46236</v>
       </c>
       <c r="C363" s="4" t="n">
-        <v>0.2402777777777778</v>
+        <v>0.2722222222222222</v>
       </c>
       <c r="D363" s="4" t="n">
-        <v>0.74375</v>
+        <v>0.7722222222222223</v>
       </c>
       <c r="E363" s="2" t="inlineStr">
         <is>
-          <t>extra punches: 17:51 06:13</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B364" s="3" t="n">
-        <v>46257</v>
+        <v>46237</v>
       </c>
       <c r="C364" s="4" t="n">
-        <v>0.2402777777777778</v>
+        <v>0.2451388888888889</v>
       </c>
       <c r="D364" s="4" t="n">
-        <v>0.75</v>
+        <v>0.7201388888888889</v>
       </c>
       <c r="E364" s="2" t="inlineStr">
         <is>
@@ -7813,80 +7859,82 @@
     <row r="365">
       <c r="A365" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B365" s="3" t="n">
-        <v>46258</v>
+        <v>46238</v>
       </c>
       <c r="C365" s="4" t="n">
-        <v>0.2319444444444445</v>
+        <v>0.2729166666666666</v>
       </c>
       <c r="D365" s="4" t="n">
-        <v>0.7513888888888889</v>
+        <v>0.7527777777777778</v>
       </c>
       <c r="E365" s="2" t="inlineStr">
         <is>
-          <t>extra punch: 18:02</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B366" s="3" t="n">
-        <v>46259</v>
+        <v>46239</v>
       </c>
       <c r="C366" s="4" t="n">
-        <v>0.3555555555555556</v>
+        <v>0.2756944444444445</v>
       </c>
       <c r="D366" s="4" t="n">
-        <v>0.7541666666666667</v>
+        <v>0.7152777777777778</v>
       </c>
       <c r="E366" s="2" t="inlineStr">
         <is>
-          <t>extra punch: 06:33</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B367" s="3" t="n">
-        <v>46260</v>
+        <v>46240</v>
       </c>
       <c r="C367" s="4" t="n">
-        <v>0.2555555555555555</v>
-      </c>
-      <c r="D367" s="4" t="n">
-        <v>0.7541666666666667</v>
+        <v>0.2715277777777778</v>
+      </c>
+      <c r="D367" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E367" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B368" s="3" t="n">
-        <v>46261</v>
+        <v>46242</v>
       </c>
       <c r="C368" s="4" t="n">
-        <v>0.2722222222222222</v>
+        <v>0.2388888888888889</v>
       </c>
       <c r="D368" s="4" t="n">
-        <v>0.7569444444444444</v>
+        <v>0.6965277777777777</v>
       </c>
       <c r="E368" s="2" t="inlineStr">
         <is>
@@ -7897,17 +7945,17 @@
     <row r="369">
       <c r="A369" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B369" s="3" t="n">
-        <v>46263</v>
+        <v>46243</v>
       </c>
       <c r="C369" s="4" t="n">
-        <v>0.2201388888888889</v>
+        <v>0.2451388888888889</v>
       </c>
       <c r="D369" s="4" t="n">
-        <v>0.7444444444444445</v>
+        <v>0.7694444444444445</v>
       </c>
       <c r="E369" s="2" t="inlineStr">
         <is>
@@ -7918,40 +7966,1547 @@
     <row r="370">
       <c r="A370" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B370" s="3" t="n">
-        <v>46264</v>
+        <v>46244</v>
       </c>
       <c r="C370" s="4" t="n">
-        <v>0.2555555555555555</v>
+        <v>0.2298611111111111</v>
       </c>
       <c r="D370" s="4" t="n">
-        <v>0.7458333333333333</v>
+        <v>0.75625</v>
       </c>
       <c r="E370" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>extra punch: 06:48</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B371" s="3" t="n">
+        <v>46245</v>
+      </c>
+      <c r="C371" s="4" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="D371" s="4" t="n">
+        <v>0.7618055555555555</v>
+      </c>
+      <c r="E371" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B372" s="3" t="n">
+        <v>46246</v>
+      </c>
+      <c r="C372" s="4" t="n">
+        <v>0.2694444444444444</v>
+      </c>
+      <c r="D372" s="4" t="n">
+        <v>0.7222222222222222</v>
+      </c>
+      <c r="E372" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B373" s="3" t="n">
+        <v>46247</v>
+      </c>
+      <c r="C373" s="4" t="n">
+        <v>0.3409722222222222</v>
+      </c>
+      <c r="D373" s="4" t="n">
+        <v>0.7583333333333333</v>
+      </c>
+      <c r="E373" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B374" s="3" t="n">
+        <v>46249</v>
+      </c>
+      <c r="C374" s="4" t="n">
+        <v>0.2680555555555555</v>
+      </c>
+      <c r="D374" s="4" t="n">
+        <v>0.7625</v>
+      </c>
+      <c r="E374" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B375" s="3" t="n">
+        <v>46250</v>
+      </c>
+      <c r="C375" s="4" t="n">
+        <v>0.3416666666666667</v>
+      </c>
+      <c r="D375" s="4" t="n">
+        <v>0.7173611111111111</v>
+      </c>
+      <c r="E375" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B376" s="3" t="n">
+        <v>46251</v>
+      </c>
+      <c r="C376" s="4" t="n">
+        <v>0.3104166666666667</v>
+      </c>
+      <c r="D376" s="4" t="n">
+        <v>0.7069444444444445</v>
+      </c>
+      <c r="E376" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B377" s="3" t="n">
+        <v>46252</v>
+      </c>
+      <c r="C377" s="4" t="n">
+        <v>0.3659722222222222</v>
+      </c>
+      <c r="D377" s="4" t="n">
+        <v>0.7208333333333333</v>
+      </c>
+      <c r="E377" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B378" s="3" t="n">
+        <v>46253</v>
+      </c>
+      <c r="C378" s="4" t="n">
+        <v>0.2944444444444445</v>
+      </c>
+      <c r="D378" s="4" t="n">
+        <v>0.7305555555555555</v>
+      </c>
+      <c r="E378" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B379" s="3" t="n">
+        <v>46254</v>
+      </c>
+      <c r="C379" s="4" t="n">
+        <v>0.4298611111111111</v>
+      </c>
+      <c r="D379" s="4" t="n">
+        <v>0.70625</v>
+      </c>
+      <c r="E379" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B380" s="3" t="n">
+        <v>46256</v>
+      </c>
+      <c r="C380" s="4" t="n">
+        <v>0.2888888888888889</v>
+      </c>
+      <c r="D380" s="4" t="n">
+        <v>0.7083333333333334</v>
+      </c>
+      <c r="E380" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B381" s="3" t="n">
+        <v>46257</v>
+      </c>
+      <c r="C381" s="4" t="n">
+        <v>0.2444444444444444</v>
+      </c>
+      <c r="D381" s="4" t="n">
+        <v>0.7076388888888889</v>
+      </c>
+      <c r="E381" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B382" s="3" t="n">
+        <v>46258</v>
+      </c>
+      <c r="C382" s="4" t="n">
+        <v>0.2784722222222222</v>
+      </c>
+      <c r="D382" s="4" t="n">
+        <v>0.7055555555555556</v>
+      </c>
+      <c r="E382" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B383" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="C383" s="4" t="n">
+        <v>0.2854166666666667</v>
+      </c>
+      <c r="D383" s="4" t="n">
+        <v>0.7222222222222222</v>
+      </c>
+      <c r="E383" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B384" s="3" t="n">
+        <v>46260</v>
+      </c>
+      <c r="C384" s="4" t="n">
+        <v>0.2375</v>
+      </c>
+      <c r="D384" s="4" t="n">
+        <v>0.7152777777777778</v>
+      </c>
+      <c r="E384" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B385" s="3" t="n">
+        <v>46261</v>
+      </c>
+      <c r="C385" s="4" t="n">
+        <v>0.4881944444444444</v>
+      </c>
+      <c r="D385" s="4" t="n">
+        <v>0.7111111111111111</v>
+      </c>
+      <c r="E385" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B386" s="3" t="n">
+        <v>46263</v>
+      </c>
+      <c r="C386" s="4" t="n">
+        <v>0.2513888888888889</v>
+      </c>
+      <c r="D386" s="4" t="n">
+        <v>0.7104166666666667</v>
+      </c>
+      <c r="E386" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B387" s="3" t="n">
+        <v>46264</v>
+      </c>
+      <c r="C387" s="4" t="n">
+        <v>0.2958333333333333</v>
+      </c>
+      <c r="D387" s="4" t="n">
+        <v>0.7215277777777778</v>
+      </c>
+      <c r="E387" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B388" s="3" t="n">
+        <v>46265</v>
+      </c>
+      <c r="C388" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D388" s="4" t="n">
+        <v>0.7097222222222223</v>
+      </c>
+      <c r="E388" s="2" t="inlineStr">
+        <is>
+          <t>single punch only</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B390" s="3" t="n">
+        <v>46235</v>
+      </c>
+      <c r="C390" s="4" t="n">
+        <v>0.3305555555555555</v>
+      </c>
+      <c r="D390" s="4" t="n">
+        <v>0.7347222222222223</v>
+      </c>
+      <c r="E390" s="2" t="inlineStr">
+        <is>
+          <t>last day of month; final record</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B391" s="3" t="n">
+        <v>46236</v>
+      </c>
+      <c r="C391" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D391" s="4" t="n">
+        <v>0.3583333333333333</v>
+      </c>
+      <c r="E391" s="2" t="inlineStr">
+        <is>
+          <t>single punch only</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B392" s="3" t="n">
+        <v>46237</v>
+      </c>
+      <c r="C392" s="4" t="n">
+        <v>0.3291666666666667</v>
+      </c>
+      <c r="D392" s="4" t="n">
+        <v>0.7111111111111111</v>
+      </c>
+      <c r="E392" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B393" s="3" t="n">
+        <v>46238</v>
+      </c>
+      <c r="C393" s="4" t="n">
+        <v>0.3305555555555555</v>
+      </c>
+      <c r="D393" s="4" t="n">
+        <v>0.7263888888888889</v>
+      </c>
+      <c r="E393" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B394" s="3" t="n">
+        <v>46239</v>
+      </c>
+      <c r="C394" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D394" s="4" t="n">
+        <v>0.7715277777777778</v>
+      </c>
+      <c r="E394" s="2" t="inlineStr">
+        <is>
+          <t>single punch only</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B395" s="3" t="n">
+        <v>46240</v>
+      </c>
+      <c r="C395" s="4" t="n">
+        <v>0.3986111111111111</v>
+      </c>
+      <c r="D395" s="4" t="n">
+        <v>0.7277777777777777</v>
+      </c>
+      <c r="E395" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B396" s="3" t="n">
+        <v>46242</v>
+      </c>
+      <c r="C396" s="4" t="n">
+        <v>0.2791666666666667</v>
+      </c>
+      <c r="D396" s="4" t="n">
+        <v>0.7284722222222222</v>
+      </c>
+      <c r="E396" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B397" s="3" t="n">
+        <v>46243</v>
+      </c>
+      <c r="C397" s="4" t="n">
+        <v>0.2784722222222222</v>
+      </c>
+      <c r="D397" s="4" t="n">
+        <v>0.7555555555555555</v>
+      </c>
+      <c r="E397" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B398" s="3" t="n">
+        <v>46244</v>
+      </c>
+      <c r="C398" s="4" t="n">
+        <v>0.2875</v>
+      </c>
+      <c r="D398" s="4" t="n">
+        <v>0.7479166666666667</v>
+      </c>
+      <c r="E398" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B399" s="3" t="n">
+        <v>46245</v>
+      </c>
+      <c r="C399" s="4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D399" s="4" t="n">
+        <v>0.7465277777777778</v>
+      </c>
+      <c r="E399" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B400" s="3" t="n">
+        <v>46246</v>
+      </c>
+      <c r="C400" s="4" t="n">
+        <v>0.2548611111111111</v>
+      </c>
+      <c r="D400" s="4" t="n">
+        <v>0.7222222222222222</v>
+      </c>
+      <c r="E400" s="2" t="inlineStr">
+        <is>
+          <t>extra punches: 07:44 06:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B401" s="3" t="n">
+        <v>46247</v>
+      </c>
+      <c r="C401" s="4" t="n">
+        <v>0.3388888888888889</v>
+      </c>
+      <c r="D401" s="4" t="n">
+        <v>0.7236111111111111</v>
+      </c>
+      <c r="E401" s="2" t="inlineStr">
+        <is>
+          <t>extra punch: 17:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B402" s="3" t="n">
+        <v>46249</v>
+      </c>
+      <c r="C402" s="4" t="n">
+        <v>0.2423611111111111</v>
+      </c>
+      <c r="D402" s="4" t="n">
+        <v>0.7270833333333333</v>
+      </c>
+      <c r="E402" s="2" t="inlineStr">
+        <is>
+          <t>extra punches: 17:27 07:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B403" s="3" t="n">
+        <v>46250</v>
+      </c>
+      <c r="C403" s="4" t="n">
+        <v>0.3409722222222222</v>
+      </c>
+      <c r="D403" s="4" t="n">
+        <v>0.7104166666666667</v>
+      </c>
+      <c r="E403" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B404" s="3" t="n">
+        <v>46251</v>
+      </c>
+      <c r="C404" s="4" t="n">
+        <v>0.2833333333333333</v>
+      </c>
+      <c r="D404" s="4" t="n">
+        <v>0.7326388888888888</v>
+      </c>
+      <c r="E404" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B405" s="3" t="n">
+        <v>46252</v>
+      </c>
+      <c r="C405" s="4" t="n">
+        <v>0.28125</v>
+      </c>
+      <c r="D405" s="4" t="n">
+        <v>0.7645833333333333</v>
+      </c>
+      <c r="E405" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B406" s="3" t="n">
+        <v>46253</v>
+      </c>
+      <c r="C406" s="4" t="n">
+        <v>0.3166666666666667</v>
+      </c>
+      <c r="D406" s="4" t="n">
+        <v>0.74375</v>
+      </c>
+      <c r="E406" s="2" t="inlineStr">
+        <is>
+          <t>extra punch: 08:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B407" s="3" t="n">
+        <v>46254</v>
+      </c>
+      <c r="C407" s="4" t="n">
+        <v>0.2868055555555555</v>
+      </c>
+      <c r="D407" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E407" s="2" t="inlineStr">
+        <is>
+          <t>single punch only</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B408" s="3" t="n">
+        <v>46256</v>
+      </c>
+      <c r="C408" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D408" s="4" t="n">
+        <v>0.74375</v>
+      </c>
+      <c r="E408" s="2" t="inlineStr">
+        <is>
+          <t>single punch only</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B409" s="3" t="n">
+        <v>46257</v>
+      </c>
+      <c r="C409" s="4" t="n">
+        <v>0.2548611111111111</v>
+      </c>
+      <c r="D409" s="4" t="n">
+        <v>0.7569444444444444</v>
+      </c>
+      <c r="E409" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B410" s="3" t="n">
+        <v>46258</v>
+      </c>
+      <c r="C410" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D410" s="4" t="n">
+        <v>0.7506944444444444</v>
+      </c>
+      <c r="E410" s="2" t="inlineStr">
+        <is>
+          <t>single punch only</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B411" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="C411" s="4" t="n">
+        <v>0.2868055555555555</v>
+      </c>
+      <c r="D411" s="4" t="n">
+        <v>0.6895833333333333</v>
+      </c>
+      <c r="E411" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B412" s="3" t="n">
+        <v>46260</v>
+      </c>
+      <c r="C412" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D412" s="4" t="n">
+        <v>0.6986111111111111</v>
+      </c>
+      <c r="E412" s="2" t="inlineStr">
+        <is>
+          <t>single punch only</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B413" s="3" t="n">
+        <v>46261</v>
+      </c>
+      <c r="C413" s="4" t="n">
+        <v>0.2833333333333333</v>
+      </c>
+      <c r="D413" s="4" t="n">
+        <v>0.8645833333333334</v>
+      </c>
+      <c r="E413" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B414" s="3" t="n">
+        <v>46263</v>
+      </c>
+      <c r="C414" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D414" s="4" t="n">
+        <v>0.7291666666666666</v>
+      </c>
+      <c r="E414" s="2" t="inlineStr">
+        <is>
+          <t>single punch only</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B415" s="3" t="n">
+        <v>46264</v>
+      </c>
+      <c r="C415" s="4" t="n">
+        <v>0.2798611111111111</v>
+      </c>
+      <c r="D415" s="4" t="n">
+        <v>0.7472222222222222</v>
+      </c>
+      <c r="E415" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B416" s="3" t="n">
+        <v>46265</v>
+      </c>
+      <c r="C416" s="4" t="n">
+        <v>0.3888888888888889</v>
+      </c>
+      <c r="D416" s="4" t="n">
+        <v>0.7215277777777778</v>
+      </c>
+      <c r="E416" s="2" t="inlineStr">
+        <is>
+          <t>corrected from a clearer re-scan photo later in the album</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="B371" s="3" t="n">
+      <c r="B418" s="3" t="n">
+        <v>46235</v>
+      </c>
+      <c r="C418" s="4" t="n">
+        <v>0.2569444444444444</v>
+      </c>
+      <c r="D418" s="4" t="n">
+        <v>0.7430555555555556</v>
+      </c>
+      <c r="E418" s="2" t="inlineStr">
+        <is>
+          <t>extra punch: 17:55; last day of month; final record</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B419" s="3" t="n">
+        <v>46236</v>
+      </c>
+      <c r="C419" s="4" t="n">
+        <v>0.2201388888888889</v>
+      </c>
+      <c r="D419" s="4" t="n">
+        <v>0.7381944444444445</v>
+      </c>
+      <c r="E419" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B420" s="3" t="n">
+        <v>46237</v>
+      </c>
+      <c r="C420" s="4" t="n">
+        <v>0.2472222222222222</v>
+      </c>
+      <c r="D420" s="4" t="n">
+        <v>0.7402777777777778</v>
+      </c>
+      <c r="E420" s="2" t="inlineStr">
+        <is>
+          <t>extra punch: 17:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B421" s="3" t="n">
+        <v>46238</v>
+      </c>
+      <c r="C421" s="4" t="n">
+        <v>0.2173611111111111</v>
+      </c>
+      <c r="D421" s="4" t="n">
+        <v>0.7604166666666666</v>
+      </c>
+      <c r="E421" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B422" s="3" t="n">
+        <v>46239</v>
+      </c>
+      <c r="C422" s="4" t="n">
+        <v>0.2333333333333333</v>
+      </c>
+      <c r="D422" s="4" t="n">
+        <v>0.7611111111111111</v>
+      </c>
+      <c r="E422" s="2" t="inlineStr">
+        <is>
+          <t>extra punch: 18:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B423" s="3" t="n">
+        <v>46240</v>
+      </c>
+      <c r="C423" s="4" t="n">
+        <v>0.2277777777777778</v>
+      </c>
+      <c r="D423" s="4" t="n">
+        <v>0.75625</v>
+      </c>
+      <c r="E423" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B424" s="3" t="n">
+        <v>46242</v>
+      </c>
+      <c r="C424" s="4" t="n">
+        <v>0.2479166666666667</v>
+      </c>
+      <c r="D424" s="4" t="n">
+        <v>0.7291666666666666</v>
+      </c>
+      <c r="E424" s="2" t="inlineStr">
+        <is>
+          <t>extra punch: 07:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B425" s="3" t="n">
+        <v>46243</v>
+      </c>
+      <c r="C425" s="4" t="n">
+        <v>0.2368055555555555</v>
+      </c>
+      <c r="D425" s="4" t="n">
+        <v>0.6729166666666667</v>
+      </c>
+      <c r="E425" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B426" s="3" t="n">
+        <v>46244</v>
+      </c>
+      <c r="C426" s="4" t="n">
+        <v>0.2534722222222222</v>
+      </c>
+      <c r="D426" s="4" t="n">
+        <v>0.7479166666666667</v>
+      </c>
+      <c r="E426" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B427" s="3" t="n">
+        <v>46245</v>
+      </c>
+      <c r="C427" s="4" t="n">
+        <v>0.2541666666666667</v>
+      </c>
+      <c r="D427" s="4" t="n">
+        <v>0.7465277777777778</v>
+      </c>
+      <c r="E427" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B428" s="3" t="n">
+        <v>46246</v>
+      </c>
+      <c r="C428" s="4" t="n">
+        <v>0.2618055555555556</v>
+      </c>
+      <c r="D428" s="4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E428" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B429" s="3" t="n">
+        <v>46247</v>
+      </c>
+      <c r="C429" s="4" t="n">
+        <v>0.25625</v>
+      </c>
+      <c r="D429" s="4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E429" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B430" s="3" t="n">
+        <v>46249</v>
+      </c>
+      <c r="C430" s="4" t="n">
+        <v>0.2333333333333333</v>
+      </c>
+      <c r="D430" s="4" t="n">
+        <v>0.7506944444444444</v>
+      </c>
+      <c r="E430" s="2" t="inlineStr">
+        <is>
+          <t>extra punch: 06:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B431" s="3" t="n">
+        <v>46250</v>
+      </c>
+      <c r="C431" s="4" t="n">
+        <v>0.25625</v>
+      </c>
+      <c r="D431" s="4" t="n">
+        <v>0.7458333333333333</v>
+      </c>
+      <c r="E431" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B432" s="3" t="n">
+        <v>46251</v>
+      </c>
+      <c r="C432" s="4" t="n">
+        <v>0.2541666666666667</v>
+      </c>
+      <c r="D432" s="4" t="n">
+        <v>0.7555555555555555</v>
+      </c>
+      <c r="E432" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B433" s="3" t="n">
+        <v>46252</v>
+      </c>
+      <c r="C433" s="4" t="n">
+        <v>0.2395833333333333</v>
+      </c>
+      <c r="D433" s="4" t="n">
+        <v>0.7611111111111111</v>
+      </c>
+      <c r="E433" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B434" s="3" t="n">
+        <v>46253</v>
+      </c>
+      <c r="C434" s="4" t="n">
+        <v>0.2527777777777778</v>
+      </c>
+      <c r="D434" s="4" t="n">
+        <v>0.7423611111111111</v>
+      </c>
+      <c r="E434" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B435" s="3" t="n">
+        <v>46254</v>
+      </c>
+      <c r="C435" s="4" t="n">
+        <v>0.2583333333333334</v>
+      </c>
+      <c r="D435" s="4" t="n">
+        <v>0.7451388888888889</v>
+      </c>
+      <c r="E435" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B436" s="3" t="n">
+        <v>46256</v>
+      </c>
+      <c r="C436" s="4" t="n">
+        <v>0.2402777777777778</v>
+      </c>
+      <c r="D436" s="4" t="n">
+        <v>0.74375</v>
+      </c>
+      <c r="E436" s="2" t="inlineStr">
+        <is>
+          <t>extra punches: 17:51 06:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B437" s="3" t="n">
+        <v>46257</v>
+      </c>
+      <c r="C437" s="4" t="n">
+        <v>0.2402777777777778</v>
+      </c>
+      <c r="D437" s="4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E437" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B438" s="3" t="n">
+        <v>46258</v>
+      </c>
+      <c r="C438" s="4" t="n">
+        <v>0.2319444444444445</v>
+      </c>
+      <c r="D438" s="4" t="n">
+        <v>0.7513888888888889</v>
+      </c>
+      <c r="E438" s="2" t="inlineStr">
+        <is>
+          <t>extra punch: 18:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B439" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="C439" s="4" t="n">
+        <v>0.3555555555555556</v>
+      </c>
+      <c r="D439" s="4" t="n">
+        <v>0.7541666666666667</v>
+      </c>
+      <c r="E439" s="2" t="inlineStr">
+        <is>
+          <t>extra punch: 06:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B440" s="3" t="n">
+        <v>46260</v>
+      </c>
+      <c r="C440" s="4" t="n">
+        <v>0.2555555555555555</v>
+      </c>
+      <c r="D440" s="4" t="n">
+        <v>0.7541666666666667</v>
+      </c>
+      <c r="E440" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B441" s="3" t="n">
+        <v>46261</v>
+      </c>
+      <c r="C441" s="4" t="n">
+        <v>0.2722222222222222</v>
+      </c>
+      <c r="D441" s="4" t="n">
+        <v>0.7569444444444444</v>
+      </c>
+      <c r="E441" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B442" s="3" t="n">
+        <v>46263</v>
+      </c>
+      <c r="C442" s="4" t="n">
+        <v>0.2201388888888889</v>
+      </c>
+      <c r="D442" s="4" t="n">
+        <v>0.7444444444444445</v>
+      </c>
+      <c r="E442" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B443" s="3" t="n">
+        <v>46264</v>
+      </c>
+      <c r="C443" s="4" t="n">
+        <v>0.2555555555555555</v>
+      </c>
+      <c r="D443" s="4" t="n">
+        <v>0.7458333333333333</v>
+      </c>
+      <c r="E443" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B444" s="3" t="n">
         <v>46265</v>
       </c>
-      <c r="C371" s="4" t="n">
+      <c r="C444" s="4" t="n">
         <v>0.2569444444444444</v>
       </c>
-      <c r="D371" s="4" t="n">
+      <c r="D444" s="4" t="n">
         <v>0.7527777777777778</v>
       </c>
-      <c r="E371" s="2" t="inlineStr">
+      <c r="E444" s="2" t="inlineStr">
         <is>
           <t>corrected from a clearer re-scan photo later in the album</t>
         </is>

--- a/output/timesheet.xlsx
+++ b/output/timesheet.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E444"/>
+  <dimension ref="A1:E508"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3902,13 +3902,13 @@
         </is>
       </c>
       <c r="B168" s="3" t="n">
-        <v>46252</v>
+        <v>46236</v>
       </c>
       <c r="C168" s="4" t="n">
-        <v>0.2652777777777778</v>
+        <v>0.2916666666666667</v>
       </c>
       <c r="D168" s="4" t="n">
-        <v>0.7569444444444444</v>
+        <v>0.775</v>
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
@@ -3923,13 +3923,13 @@
         </is>
       </c>
       <c r="B169" s="3" t="n">
-        <v>46253</v>
+        <v>46237</v>
       </c>
       <c r="C169" s="4" t="n">
-        <v>0.26875</v>
+        <v>0.3291666666666667</v>
       </c>
       <c r="D169" s="4" t="n">
-        <v>0.7506944444444444</v>
+        <v>0.7041666666666667</v>
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
@@ -3944,13 +3944,13 @@
         </is>
       </c>
       <c r="B170" s="3" t="n">
-        <v>46254</v>
+        <v>46238</v>
       </c>
       <c r="C170" s="4" t="n">
-        <v>0.2611111111111111</v>
+        <v>0.3048611111111111</v>
       </c>
       <c r="D170" s="4" t="n">
-        <v>0.7451388888888889</v>
+        <v>0.7597222222222222</v>
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
@@ -3965,13 +3965,13 @@
         </is>
       </c>
       <c r="B171" s="3" t="n">
-        <v>46256</v>
+        <v>46239</v>
       </c>
       <c r="C171" s="4" t="n">
-        <v>0.3006944444444444</v>
+        <v>0.29375</v>
       </c>
       <c r="D171" s="4" t="n">
-        <v>0.7541666666666667</v>
+        <v>0.7715277777777778</v>
       </c>
       <c r="E171" s="2" t="inlineStr">
         <is>
@@ -3986,13 +3986,13 @@
         </is>
       </c>
       <c r="B172" s="3" t="n">
-        <v>46257</v>
+        <v>46240</v>
       </c>
       <c r="C172" s="4" t="n">
-        <v>0.2541666666666667</v>
+        <v>0.2993055555555555</v>
       </c>
       <c r="D172" s="4" t="n">
-        <v>0.74375</v>
+        <v>0.7458333333333333</v>
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
@@ -4007,13 +4007,13 @@
         </is>
       </c>
       <c r="B173" s="3" t="n">
-        <v>46258</v>
+        <v>46242</v>
       </c>
       <c r="C173" s="4" t="n">
-        <v>0.25625</v>
+        <v>0.3131944444444444</v>
       </c>
       <c r="D173" s="4" t="n">
-        <v>0.7472222222222222</v>
+        <v>0.7666666666666667</v>
       </c>
       <c r="E173" s="2" t="inlineStr">
         <is>
@@ -4028,13 +4028,13 @@
         </is>
       </c>
       <c r="B174" s="3" t="n">
-        <v>46259</v>
+        <v>46243</v>
       </c>
       <c r="C174" s="4" t="n">
-        <v>0.2555555555555555</v>
+        <v>0.3041666666666666</v>
       </c>
       <c r="D174" s="4" t="n">
-        <v>0.7479166666666667</v>
+        <v>0.7694444444444445</v>
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
@@ -4049,13 +4049,13 @@
         </is>
       </c>
       <c r="B175" s="3" t="n">
-        <v>46260</v>
+        <v>46244</v>
       </c>
       <c r="C175" s="4" t="n">
-        <v>0.2708333333333333</v>
+        <v>0.2319444444444445</v>
       </c>
       <c r="D175" s="4" t="n">
-        <v>0.7416666666666667</v>
+        <v>0.7479166666666667</v>
       </c>
       <c r="E175" s="2" t="inlineStr">
         <is>
@@ -4070,13 +4070,13 @@
         </is>
       </c>
       <c r="B176" s="3" t="n">
-        <v>46261</v>
+        <v>46245</v>
       </c>
       <c r="C176" s="4" t="n">
-        <v>0.2909722222222222</v>
+        <v>0.2395833333333333</v>
       </c>
       <c r="D176" s="4" t="n">
-        <v>0.7430555555555556</v>
+        <v>0.7458333333333333</v>
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
@@ -4091,13 +4091,13 @@
         </is>
       </c>
       <c r="B177" s="3" t="n">
-        <v>46263</v>
+        <v>46246</v>
       </c>
       <c r="C177" s="4" t="n">
-        <v>0.275</v>
+        <v>0.3034722222222222</v>
       </c>
       <c r="D177" s="4" t="n">
-        <v>0.7513888888888889</v>
+        <v>0.70625</v>
       </c>
       <c r="E177" s="2" t="inlineStr">
         <is>
@@ -4112,13 +4112,13 @@
         </is>
       </c>
       <c r="B178" s="3" t="n">
-        <v>46264</v>
+        <v>46247</v>
       </c>
       <c r="C178" s="4" t="n">
-        <v>0.3194444444444444</v>
+        <v>0.2645833333333333</v>
       </c>
       <c r="D178" s="4" t="n">
-        <v>0.7493055555555556</v>
+        <v>0.7631944444444444</v>
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
@@ -4133,15 +4133,36 @@
         </is>
       </c>
       <c r="B179" s="3" t="n">
-        <v>46265</v>
+        <v>46249</v>
       </c>
       <c r="C179" s="4" t="n">
-        <v>0.2631944444444445</v>
+        <v>0.2694444444444444</v>
       </c>
       <c r="D179" s="4" t="n">
-        <v>0.7555555555555555</v>
+        <v>0.7638888888888888</v>
       </c>
       <c r="E179" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B180" s="3" t="n">
+        <v>46250</v>
+      </c>
+      <c r="C180" s="4" t="n">
+        <v>0.2826388888888889</v>
+      </c>
+      <c r="D180" s="4" t="n">
+        <v>0.7180555555555556</v>
+      </c>
+      <c r="E180" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4150,17 +4171,17 @@
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B181" s="3" t="n">
-        <v>46260</v>
+        <v>46251</v>
       </c>
       <c r="C181" s="4" t="n">
-        <v>0.3055555555555556</v>
+        <v>0.2756944444444445</v>
       </c>
       <c r="D181" s="4" t="n">
-        <v>0.8013888888888889</v>
+        <v>0.7465277777777778</v>
       </c>
       <c r="E181" s="2" t="inlineStr">
         <is>
@@ -4171,17 +4192,17 @@
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B182" s="3" t="n">
-        <v>46261</v>
+        <v>46252</v>
       </c>
       <c r="C182" s="4" t="n">
-        <v>0.2798611111111111</v>
+        <v>0.2652777777777778</v>
       </c>
       <c r="D182" s="4" t="n">
-        <v>0.7493055555555556</v>
+        <v>0.7569444444444444</v>
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
@@ -4192,40 +4213,61 @@
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B183" s="3" t="n">
-        <v>46263</v>
+        <v>46253</v>
       </c>
       <c r="C183" s="4" t="n">
-        <v>0.3347222222222222</v>
+        <v>0.26875</v>
       </c>
       <c r="D183" s="4" t="n">
-        <v>0.8895833333333333</v>
+        <v>0.7506944444444444</v>
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
-          <t>extra punch: 08:02</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B184" s="3" t="n">
-        <v>46264</v>
+        <v>46254</v>
       </c>
       <c r="C184" s="4" t="n">
-        <v>0.3208333333333334</v>
+        <v>0.2611111111111111</v>
       </c>
       <c r="D184" s="4" t="n">
-        <v>0.7354166666666667</v>
+        <v>0.7451388888888889</v>
       </c>
       <c r="E184" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B185" s="3" t="n">
+        <v>46256</v>
+      </c>
+      <c r="C185" s="4" t="n">
+        <v>0.3006944444444444</v>
+      </c>
+      <c r="D185" s="4" t="n">
+        <v>0.7541666666666667</v>
+      </c>
+      <c r="E185" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4234,17 +4276,17 @@
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B186" s="3" t="n">
-        <v>46262</v>
+        <v>46257</v>
       </c>
       <c r="C186" s="4" t="n">
-        <v>0.1493055555555556</v>
+        <v>0.2541666666666667</v>
       </c>
       <c r="D186" s="4" t="n">
-        <v>0.7159722222222222</v>
+        <v>0.74375</v>
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
@@ -4255,17 +4297,17 @@
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B187" s="3" t="n">
-        <v>46263</v>
+        <v>46258</v>
       </c>
       <c r="C187" s="4" t="n">
-        <v>0.1451388888888889</v>
+        <v>0.25625</v>
       </c>
       <c r="D187" s="4" t="n">
-        <v>0.7479166666666667</v>
+        <v>0.7472222222222222</v>
       </c>
       <c r="E187" s="2" t="inlineStr">
         <is>
@@ -4276,17 +4318,17 @@
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B188" s="3" t="n">
-        <v>46264</v>
+        <v>46259</v>
       </c>
       <c r="C188" s="4" t="n">
-        <v>0.14375</v>
+        <v>0.2555555555555555</v>
       </c>
       <c r="D188" s="4" t="n">
-        <v>0.75625</v>
+        <v>0.7479166666666667</v>
       </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
@@ -4297,38 +4339,59 @@
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B189" s="3" t="n">
-        <v>46265</v>
+        <v>46260</v>
       </c>
       <c r="C189" s="4" t="n">
-        <v>0.1479166666666667</v>
+        <v>0.2708333333333333</v>
       </c>
       <c r="D189" s="4" t="n">
-        <v>0.9326388888888889</v>
+        <v>0.7416666666666667</v>
       </c>
       <c r="E189" s="2" t="inlineStr">
         <is>
-          <t>extra punch: 22:23</t>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B190" s="3" t="n">
+        <v>46261</v>
+      </c>
+      <c r="C190" s="4" t="n">
+        <v>0.2909722222222222</v>
+      </c>
+      <c r="D190" s="4" t="n">
+        <v>0.7430555555555556</v>
+      </c>
+      <c r="E190" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B191" s="3" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="C191" s="4" t="n">
-        <v>0.1881944444444444</v>
+        <v>0.275</v>
       </c>
       <c r="D191" s="4" t="n">
-        <v>0.4055555555555556</v>
+        <v>0.7513888888888889</v>
       </c>
       <c r="E191" s="2" t="inlineStr">
         <is>
@@ -4339,17 +4402,17 @@
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B192" s="3" t="n">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="C192" s="4" t="n">
-        <v>0.1847222222222222</v>
+        <v>0.3194444444444444</v>
       </c>
       <c r="D192" s="4" t="n">
-        <v>0.4527777777777778</v>
+        <v>0.7493055555555556</v>
       </c>
       <c r="E192" s="2" t="inlineStr">
         <is>
@@ -4360,17 +4423,17 @@
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B193" s="3" t="n">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="C193" s="4" t="n">
-        <v>0.1847222222222222</v>
+        <v>0.2631944444444445</v>
       </c>
       <c r="D193" s="4" t="n">
-        <v>0.5097222222222222</v>
+        <v>0.7555555555555555</v>
       </c>
       <c r="E193" s="2" t="inlineStr">
         <is>
@@ -4378,83 +4441,87 @@
         </is>
       </c>
     </row>
-    <row r="194">
-      <c r="A194" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="B194" s="3" t="n">
-        <v>46265</v>
-      </c>
-      <c r="C194" s="4" t="n">
-        <v>0.1868055555555556</v>
-      </c>
-      <c r="D194" s="4" t="n">
-        <v>0.4131944444444444</v>
-      </c>
-      <c r="E194" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+    <row r="195">
+      <c r="A195" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B195" s="3" t="n">
+        <v>46235</v>
+      </c>
+      <c r="C195" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D195" s="4" t="n">
+        <v>0.8215277777777777</v>
+      </c>
+      <c r="E195" s="2" t="inlineStr">
+        <is>
+          <t>single punch only; last day of month</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B196" s="3" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="C196" s="4" t="n">
-        <v>0.2368055555555555</v>
-      </c>
-      <c r="D196" s="4" t="n">
-        <v>0.7430555555555556</v>
+        <v>0.2180555555555556</v>
+      </c>
+      <c r="D196" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E196" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B197" s="3" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="C197" s="4" t="n">
-        <v>0.2604166666666667</v>
+        <v>0.35</v>
       </c>
       <c r="D197" s="4" t="n">
-        <v>0.7534722222222222</v>
+        <v>0.74375</v>
       </c>
       <c r="E197" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>extra punch: 17:50</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B198" s="3" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C198" s="4" t="n">
-        <v>0.3097222222222222</v>
+        <v>0.3861111111111111</v>
       </c>
       <c r="D198" s="4" t="n">
-        <v>0.7444444444444445</v>
+        <v>0.7701388888888889</v>
       </c>
       <c r="E198" s="2" t="inlineStr">
         <is>
@@ -4465,19 +4532,19 @@
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B199" s="3" t="n">
-        <v>46238</v>
-      </c>
-      <c r="C199" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D199" s="4" t="n">
-        <v>0.7458333333333333</v>
+        <v>46240</v>
+      </c>
+      <c r="C199" s="4" t="n">
+        <v>0.2736111111111111</v>
+      </c>
+      <c r="D199" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E199" s="2" t="inlineStr">
         <is>
@@ -4488,61 +4555,61 @@
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B200" s="3" t="n">
-        <v>46239</v>
+        <v>46241</v>
       </c>
       <c r="C200" s="4" t="n">
-        <v>0.2229166666666667</v>
-      </c>
-      <c r="D200" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.7666666666666667</v>
+      </c>
+      <c r="D200" s="4" t="n">
+        <v>0.7708333333333334</v>
       </c>
       <c r="E200" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B201" s="3" t="n">
-        <v>46240</v>
+        <v>46242</v>
       </c>
       <c r="C201" s="4" t="n">
-        <v>0.2326388888888889</v>
-      </c>
-      <c r="D201" s="4" t="n">
-        <v>0.7576388888888889</v>
+        <v>0.4444444444444444</v>
+      </c>
+      <c r="D201" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E201" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B202" s="3" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="C202" s="4" t="n">
-        <v>0.2402777777777778</v>
+        <v>0.5465277777777777</v>
       </c>
       <c r="D202" s="4" t="n">
-        <v>0.7243055555555555</v>
+        <v>0.7222222222222222</v>
       </c>
       <c r="E202" s="2" t="inlineStr">
         <is>
@@ -4553,17 +4620,17 @@
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B203" s="3" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="C203" s="4" t="n">
-        <v>0.2402777777777778</v>
+        <v>0.2291666666666667</v>
       </c>
       <c r="D203" s="4" t="n">
-        <v>0.725</v>
+        <v>0.7555555555555555</v>
       </c>
       <c r="E203" s="2" t="inlineStr">
         <is>
@@ -4574,38 +4641,40 @@
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B204" s="3" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="C204" s="4" t="n">
-        <v>0.2409722222222222</v>
-      </c>
-      <c r="D204" s="4" t="n">
-        <v>0.7597222222222222</v>
+        <v>0.4069444444444444</v>
+      </c>
+      <c r="D204" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E204" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B205" s="3" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="C205" s="4" t="n">
-        <v>0.2215277777777778</v>
+        <v>0.3305555555555555</v>
       </c>
       <c r="D205" s="4" t="n">
-        <v>0.7319444444444444</v>
+        <v>0.7659722222222223</v>
       </c>
       <c r="E205" s="2" t="inlineStr">
         <is>
@@ -4616,17 +4685,17 @@
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B206" s="3" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="C206" s="4" t="n">
-        <v>0.2361111111111111</v>
+        <v>0.2715277777777778</v>
       </c>
       <c r="D206" s="4" t="n">
-        <v>0.7402777777777778</v>
+        <v>0.7569444444444444</v>
       </c>
       <c r="E206" s="2" t="inlineStr">
         <is>
@@ -4637,79 +4706,79 @@
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B207" s="3" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="C207" s="4" t="n">
-        <v>0.2479166666666667</v>
+        <v>0.2354166666666667</v>
       </c>
       <c r="D207" s="4" t="n">
-        <v>0.7243055555555555</v>
+        <v>0.7611111111111111</v>
       </c>
       <c r="E207" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>extra punches: 05:39 05:39 05:39 05:39 (repeated - device anomaly</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B208" s="3" t="n">
         <v>46249</v>
       </c>
-      <c r="C208" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C208" s="4" t="n">
+        <v>0.2395833333333333</v>
       </c>
       <c r="D208" s="4" t="n">
-        <v>0.7201388888888889</v>
+        <v>0.7125</v>
       </c>
       <c r="E208" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>extra punch: 09:31</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B209" s="3" t="n">
         <v>46250</v>
       </c>
       <c r="C209" s="4" t="n">
-        <v>0.2298611111111111</v>
-      </c>
-      <c r="D209" s="4" t="n">
-        <v>0.7180555555555556</v>
+        <v>0.6194444444444445</v>
+      </c>
+      <c r="D209" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E209" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B210" s="3" t="n">
         <v>46251</v>
       </c>
       <c r="C210" s="4" t="n">
-        <v>0.2472222222222222</v>
+        <v>0.3423611111111111</v>
       </c>
       <c r="D210" s="4" t="n">
         <v>0.7402777777777778</v>
@@ -4723,147 +4792,145 @@
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B211" s="3" t="n">
         <v>46252</v>
       </c>
       <c r="C211" s="4" t="n">
-        <v>0.2354166666666667</v>
-      </c>
-      <c r="D211" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.28125</v>
+      </c>
+      <c r="D211" s="4" t="n">
+        <v>0.7923611111111111</v>
       </c>
       <c r="E211" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B212" s="3" t="n">
         <v>46253</v>
       </c>
       <c r="C212" s="4" t="n">
-        <v>0.2215277777777778</v>
+        <v>0.31875</v>
       </c>
       <c r="D212" s="4" t="n">
-        <v>0.7305555555555555</v>
+        <v>0.7215277777777778</v>
       </c>
       <c r="E212" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>extra punch: 17:19</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B213" s="3" t="n">
         <v>46254</v>
       </c>
       <c r="C213" s="4" t="n">
-        <v>0.2222222222222222</v>
-      </c>
-      <c r="D213" s="4" t="n">
-        <v>0.7291666666666666</v>
+        <v>0.3465277777777778</v>
+      </c>
+      <c r="D213" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E213" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B214" s="3" t="n">
-        <v>46256</v>
+        <v>46255</v>
       </c>
       <c r="C214" s="4" t="n">
-        <v>0.2388888888888889</v>
+        <v>0.7590277777777777</v>
       </c>
       <c r="D214" s="4" t="n">
-        <v>0.7541666666666667</v>
+        <v>0.7590277777777777</v>
       </c>
       <c r="E214" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>PLEASE VERIFY: in/out times read identical - likely OCR error</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B215" s="3" t="n">
-        <v>46257</v>
+        <v>46256</v>
       </c>
       <c r="C215" s="4" t="n">
-        <v>0.2506944444444444</v>
+        <v>0.2395833333333333</v>
       </c>
       <c r="D215" s="4" t="n">
-        <v>0.7291666666666666</v>
+        <v>0.7729166666666667</v>
       </c>
       <c r="E215" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>extra punch: 05:45</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B216" s="3" t="n">
-        <v>46258</v>
-      </c>
-      <c r="C216" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>46257</v>
+      </c>
+      <c r="C216" s="4" t="n">
+        <v>0.2722222222222222</v>
       </c>
       <c r="D216" s="4" t="n">
-        <v>0.725</v>
+        <v>0.7430555555555556</v>
       </c>
       <c r="E216" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B217" s="3" t="n">
-        <v>46259</v>
+        <v>46258</v>
       </c>
       <c r="C217" s="4" t="n">
-        <v>0.2375</v>
+        <v>0.5076388888888889</v>
       </c>
       <c r="D217" s="4" t="n">
-        <v>0.725</v>
+        <v>0.8027777777777778</v>
       </c>
       <c r="E217" s="2" t="inlineStr">
         <is>
@@ -4874,17 +4941,17 @@
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B218" s="3" t="n">
-        <v>46260</v>
+        <v>46259</v>
       </c>
       <c r="C218" s="4" t="n">
-        <v>0.2256944444444444</v>
+        <v>0.2076388888888889</v>
       </c>
       <c r="D218" s="4" t="n">
-        <v>0.7381944444444445</v>
+        <v>0.7840277777777778</v>
       </c>
       <c r="E218" s="2" t="inlineStr">
         <is>
@@ -4895,17 +4962,17 @@
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B219" s="3" t="n">
-        <v>46261</v>
+        <v>46260</v>
       </c>
       <c r="C219" s="4" t="n">
-        <v>0.2361111111111111</v>
+        <v>0.3055555555555556</v>
       </c>
       <c r="D219" s="4" t="n">
-        <v>0.7166666666666667</v>
+        <v>0.8013888888888889</v>
       </c>
       <c r="E219" s="2" t="inlineStr">
         <is>
@@ -4916,17 +4983,17 @@
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B220" s="3" t="n">
-        <v>46263</v>
+        <v>46261</v>
       </c>
       <c r="C220" s="4" t="n">
-        <v>0.2270833333333333</v>
+        <v>0.2798611111111111</v>
       </c>
       <c r="D220" s="4" t="n">
-        <v>0.7347222222222223</v>
+        <v>0.7493055555555556</v>
       </c>
       <c r="E220" s="2" t="inlineStr">
         <is>
@@ -4937,84 +5004,80 @@
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B221" s="3" t="n">
-        <v>46264</v>
+        <v>46263</v>
       </c>
       <c r="C221" s="4" t="n">
-        <v>0.2340277777777778</v>
-      </c>
-      <c r="D221" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.3347222222222222</v>
+      </c>
+      <c r="D221" s="4" t="n">
+        <v>0.8895833333333333</v>
       </c>
       <c r="E221" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>extra punch: 08:02</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B222" s="3" t="n">
-        <v>46265</v>
+        <v>46264</v>
       </c>
       <c r="C222" s="4" t="n">
-        <v>0.2361111111111111</v>
-      </c>
-      <c r="D222" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.3208333333333334</v>
+      </c>
+      <c r="D222" s="4" t="n">
+        <v>0.7354166666666667</v>
       </c>
       <c r="E222" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B224" s="3" t="n">
         <v>46235</v>
       </c>
       <c r="C224" s="4" t="n">
-        <v>0.14375</v>
+        <v>0.2381944444444444</v>
       </c>
       <c r="D224" s="4" t="n">
-        <v>0.7576388888888889</v>
+        <v>0.9923611111111111</v>
       </c>
       <c r="E224" s="2" t="inlineStr">
         <is>
-          <t>last day of month; final record</t>
+          <t>extra punches: 20:11 16:59; last day of month</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B225" s="3" t="n">
         <v>46236</v>
       </c>
       <c r="C225" s="4" t="n">
-        <v>0.14375</v>
+        <v>0.2430555555555556</v>
       </c>
       <c r="D225" s="4" t="n">
-        <v>0.7395833333333334</v>
+        <v>0.8208333333333333</v>
       </c>
       <c r="E225" s="2" t="inlineStr">
         <is>
@@ -5025,17 +5088,17 @@
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B226" s="3" t="n">
         <v>46237</v>
       </c>
       <c r="C226" s="4" t="n">
-        <v>0.1458333333333333</v>
+        <v>0.2340277777777778</v>
       </c>
       <c r="D226" s="4" t="n">
-        <v>0.7472222222222222</v>
+        <v>0.7423611111111111</v>
       </c>
       <c r="E226" s="2" t="inlineStr">
         <is>
@@ -5046,17 +5109,17 @@
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B227" s="3" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C227" s="4" t="n">
-        <v>0.1451388888888889</v>
+        <v>0.1930555555555556</v>
       </c>
       <c r="D227" s="4" t="n">
-        <v>0.7708333333333334</v>
+        <v>0.7756944444444445</v>
       </c>
       <c r="E227" s="2" t="inlineStr">
         <is>
@@ -5067,17 +5130,17 @@
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B228" s="3" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C228" s="4" t="n">
-        <v>0.1444444444444444</v>
+        <v>0.2520833333333333</v>
       </c>
       <c r="D228" s="4" t="n">
-        <v>0.6881944444444444</v>
+        <v>0.7229166666666667</v>
       </c>
       <c r="E228" s="2" t="inlineStr">
         <is>
@@ -5088,17 +5151,17 @@
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B229" s="3" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C229" s="4" t="n">
-        <v>0.1444444444444444</v>
+        <v>0.1486111111111111</v>
       </c>
       <c r="D229" s="4" t="n">
-        <v>0.7659722222222223</v>
+        <v>0.7201388888888889</v>
       </c>
       <c r="E229" s="2" t="inlineStr">
         <is>
@@ -5109,17 +5172,17 @@
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B230" s="3" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="C230" s="4" t="n">
-        <v>0.1451388888888889</v>
+        <v>0.2430555555555556</v>
       </c>
       <c r="D230" s="4" t="n">
-        <v>0.7298611111111111</v>
+        <v>0.7305555555555555</v>
       </c>
       <c r="E230" s="2" t="inlineStr">
         <is>
@@ -5130,101 +5193,101 @@
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B231" s="3" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="C231" s="4" t="n">
-        <v>0.1388888888888889</v>
+        <v>0.1486111111111111</v>
       </c>
       <c r="D231" s="4" t="n">
-        <v>0.8090277777777778</v>
+        <v>0.8013888888888889</v>
       </c>
       <c r="E231" s="2" t="inlineStr">
         <is>
-          <t>extra punch: 03:24</t>
+          <t>extra punch: 03:39</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B232" s="3" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="C232" s="4" t="n">
-        <v>0.1444444444444444</v>
+        <v>0.2069444444444444</v>
       </c>
       <c r="D232" s="4" t="n">
-        <v>0.8381944444444445</v>
+        <v>0.7868055555555555</v>
       </c>
       <c r="E232" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>extra punch: 18:20</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B233" s="3" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="C233" s="4" t="n">
-        <v>0.1354166666666667</v>
+        <v>0.2236111111111111</v>
       </c>
       <c r="D233" s="4" t="n">
-        <v>0.7638888888888888</v>
+        <v>0.7354166666666667</v>
       </c>
       <c r="E233" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>extra punch: 06:13</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B234" s="3" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="C234" s="4" t="n">
-        <v>0.14375</v>
+        <v>0.2083333333333333</v>
       </c>
       <c r="D234" s="4" t="n">
-        <v>0.7444444444444445</v>
+        <v>0.8291666666666667</v>
       </c>
       <c r="E234" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>extra punches: 18:57 05:15</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B235" s="3" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="C235" s="4" t="n">
-        <v>0.1430555555555555</v>
+        <v>0.25</v>
       </c>
       <c r="D235" s="4" t="n">
-        <v>0.7409722222222223</v>
+        <v>0.7291666666666666</v>
       </c>
       <c r="E235" s="2" t="inlineStr">
         <is>
@@ -5235,80 +5298,80 @@
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B236" s="3" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="C236" s="4" t="n">
-        <v>0.1423611111111111</v>
+        <v>0.2361111111111111</v>
       </c>
       <c r="D236" s="4" t="n">
-        <v>0.75</v>
+        <v>0.7972222222222223</v>
       </c>
       <c r="E236" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>extra punch: 17:01</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B237" s="3" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="C237" s="4" t="n">
-        <v>0.15</v>
+        <v>0.2965277777777778</v>
       </c>
       <c r="D237" s="4" t="n">
-        <v>0.7076388888888889</v>
+        <v>0.7340277777777777</v>
       </c>
       <c r="E237" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>extra punches: 17:20 17:05</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B238" s="3" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="C238" s="4" t="n">
-        <v>0.1513888888888889</v>
+        <v>0.1506944444444444</v>
       </c>
       <c r="D238" s="4" t="n">
-        <v>0.7277777777777777</v>
+        <v>0.7256944444444444</v>
       </c>
       <c r="E238" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>extra punch: 04:52</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B239" s="3" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="C239" s="4" t="n">
-        <v>0.2708333333333333</v>
+        <v>0.1729166666666667</v>
       </c>
       <c r="D239" s="4" t="n">
-        <v>0.7229166666666667</v>
+        <v>0.7319444444444444</v>
       </c>
       <c r="E239" s="2" t="inlineStr">
         <is>
@@ -5319,38 +5382,38 @@
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B240" s="3" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="C240" s="4" t="n">
-        <v>0.2333333333333333</v>
+        <v>0.1506944444444444</v>
       </c>
       <c r="D240" s="4" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.7173611111111111</v>
       </c>
       <c r="E240" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>extra punch: 03:41</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B241" s="3" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="C241" s="4" t="n">
-        <v>0.25625</v>
+        <v>0.1506944444444444</v>
       </c>
       <c r="D241" s="4" t="n">
-        <v>0.7416666666666667</v>
+        <v>0.7305555555555555</v>
       </c>
       <c r="E241" s="2" t="inlineStr">
         <is>
@@ -5361,38 +5424,38 @@
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B242" s="3" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C242" s="4" t="n">
-        <v>0.2777777777777778</v>
+        <v>0.1513888888888889</v>
       </c>
       <c r="D242" s="4" t="n">
-        <v>0.7451388888888889</v>
+        <v>0.7319444444444444</v>
       </c>
       <c r="E242" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>extra punches: 17:24 05:12</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B243" s="3" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C243" s="4" t="n">
-        <v>0.2625</v>
+        <v>0.1493055555555556</v>
       </c>
       <c r="D243" s="4" t="n">
-        <v>0.7979166666666667</v>
+        <v>0.7236111111111111</v>
       </c>
       <c r="E243" s="2" t="inlineStr">
         <is>
@@ -5403,59 +5466,59 @@
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B244" s="3" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="C244" s="4" t="n">
-        <v>0.275</v>
+        <v>0.1479166666666667</v>
       </c>
       <c r="D244" s="4" t="n">
-        <v>0.8354166666666667</v>
+        <v>0.7520833333333333</v>
       </c>
       <c r="E244" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>extra punch: 03:39</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B245" s="3" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="C245" s="4" t="n">
-        <v>0.2611111111111111</v>
+        <v>0.1506944444444444</v>
       </c>
       <c r="D245" s="4" t="n">
-        <v>0.7513888888888889</v>
+        <v>0.7111111111111111</v>
       </c>
       <c r="E245" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>extra punch: 03:38</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B246" s="3" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="C246" s="4" t="n">
-        <v>0.24375</v>
+        <v>0.1541666666666667</v>
       </c>
       <c r="D246" s="4" t="n">
-        <v>0.7263888888888889</v>
+        <v>0.7111111111111111</v>
       </c>
       <c r="E246" s="2" t="inlineStr">
         <is>
@@ -5466,38 +5529,38 @@
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B247" s="3" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C247" s="4" t="n">
-        <v>0.2631944444444445</v>
+        <v>0.1513888888888889</v>
       </c>
       <c r="D247" s="4" t="n">
-        <v>0.7270833333333333</v>
+        <v>0.7180555555555556</v>
       </c>
       <c r="E247" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>extra punch: 17:14</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B248" s="3" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C248" s="4" t="n">
-        <v>0.2611111111111111</v>
+        <v>0.1444444444444444</v>
       </c>
       <c r="D248" s="4" t="n">
-        <v>0.7298611111111111</v>
+        <v>0.7006944444444444</v>
       </c>
       <c r="E248" s="2" t="inlineStr">
         <is>
@@ -5508,59 +5571,59 @@
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B249" s="3" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="C249" s="4" t="n">
-        <v>0.275</v>
+        <v>0.1444444444444444</v>
       </c>
       <c r="D249" s="4" t="n">
-        <v>0.8791666666666667</v>
+        <v>0.7104166666666667</v>
       </c>
       <c r="E249" s="2" t="inlineStr">
         <is>
-          <t>extra punch: 17:56</t>
+          <t>extra punch: 03:30</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B250" s="3" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="C250" s="4" t="n">
-        <v>0.2555555555555555</v>
+        <v>0.1493055555555556</v>
       </c>
       <c r="D250" s="4" t="n">
-        <v>0.8506944444444444</v>
+        <v>0.7159722222222222</v>
       </c>
       <c r="E250" s="2" t="inlineStr">
         <is>
-          <t>extra punches: 17:07 17:02</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B251" s="3" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="C251" s="4" t="n">
-        <v>0.2805555555555556</v>
+        <v>0.1451388888888889</v>
       </c>
       <c r="D251" s="4" t="n">
-        <v>0.7701388888888889</v>
+        <v>0.7479166666666667</v>
       </c>
       <c r="E251" s="2" t="inlineStr">
         <is>
@@ -5571,17 +5634,17 @@
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B252" s="3" t="n">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="C252" s="4" t="n">
-        <v>0.2541666666666667</v>
+        <v>0.14375</v>
       </c>
       <c r="D252" s="4" t="n">
-        <v>0.7479166666666667</v>
+        <v>0.75625</v>
       </c>
       <c r="E252" s="2" t="inlineStr">
         <is>
@@ -5592,80 +5655,80 @@
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B253" s="3" t="n">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="C253" s="4" t="n">
-        <v>0.2659722222222222</v>
+        <v>0.1479166666666667</v>
       </c>
       <c r="D253" s="4" t="n">
-        <v>0.7354166666666667</v>
+        <v>0.9326388888888889</v>
       </c>
       <c r="E253" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="B254" s="3" t="n">
-        <v>46265</v>
-      </c>
-      <c r="C254" s="4" t="n">
-        <v>0.2527777777777778</v>
-      </c>
-      <c r="D254" s="4" t="n">
-        <v>0.7354166666666667</v>
-      </c>
-      <c r="E254" s="2" t="inlineStr">
-        <is>
-          <t>corrected from a clearer re-scan photo later in the album</t>
+          <t>extra punch: 22:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B255" s="3" t="n">
+        <v>46262</v>
+      </c>
+      <c r="C255" s="4" t="n">
+        <v>0.1881944444444444</v>
+      </c>
+      <c r="D255" s="4" t="n">
+        <v>0.4055555555555556</v>
+      </c>
+      <c r="E255" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B256" s="3" t="n">
-        <v>46235</v>
+        <v>46263</v>
       </c>
       <c r="C256" s="4" t="n">
-        <v>0.2625</v>
+        <v>0.1847222222222222</v>
       </c>
       <c r="D256" s="4" t="n">
-        <v>0.7444444444444445</v>
+        <v>0.4527777777777778</v>
       </c>
       <c r="E256" s="2" t="inlineStr">
         <is>
-          <t>last day of month; final record</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B257" s="3" t="n">
-        <v>46236</v>
+        <v>46264</v>
       </c>
       <c r="C257" s="4" t="n">
-        <v>0.2645833333333333</v>
+        <v>0.1847222222222222</v>
       </c>
       <c r="D257" s="4" t="n">
-        <v>0.7493055555555556</v>
+        <v>0.5097222222222222</v>
       </c>
       <c r="E257" s="2" t="inlineStr">
         <is>
@@ -5676,40 +5739,19 @@
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B258" s="3" t="n">
-        <v>46237</v>
+        <v>46265</v>
       </c>
       <c r="C258" s="4" t="n">
-        <v>0.2604166666666667</v>
+        <v>0.1868055555555556</v>
       </c>
       <c r="D258" s="4" t="n">
-        <v>0.7479166666666667</v>
+        <v>0.4131944444444444</v>
       </c>
       <c r="E258" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="259">
-      <c r="A259" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="B259" s="3" t="n">
-        <v>46238</v>
-      </c>
-      <c r="C259" s="4" t="n">
-        <v>0.2527777777777778</v>
-      </c>
-      <c r="D259" s="4" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="E259" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -5718,17 +5760,17 @@
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B260" s="3" t="n">
-        <v>46239</v>
+        <v>46235</v>
       </c>
       <c r="C260" s="4" t="n">
-        <v>0.25625</v>
+        <v>0.2368055555555555</v>
       </c>
       <c r="D260" s="4" t="n">
-        <v>0.7763888888888889</v>
+        <v>0.7430555555555556</v>
       </c>
       <c r="E260" s="2" t="inlineStr">
         <is>
@@ -5739,17 +5781,17 @@
     <row r="261">
       <c r="A261" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B261" s="3" t="n">
-        <v>46240</v>
+        <v>46236</v>
       </c>
       <c r="C261" s="4" t="n">
-        <v>0.2701388888888889</v>
+        <v>0.2604166666666667</v>
       </c>
       <c r="D261" s="4" t="n">
-        <v>0.7423611111111111</v>
+        <v>0.7534722222222222</v>
       </c>
       <c r="E261" s="2" t="inlineStr">
         <is>
@@ -5760,17 +5802,17 @@
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B262" s="3" t="n">
-        <v>46242</v>
+        <v>46237</v>
       </c>
       <c r="C262" s="4" t="n">
-        <v>0.2597222222222222</v>
+        <v>0.3097222222222222</v>
       </c>
       <c r="D262" s="4" t="n">
-        <v>0.7326388888888888</v>
+        <v>0.7444444444444445</v>
       </c>
       <c r="E262" s="2" t="inlineStr">
         <is>
@@ -5781,40 +5823,42 @@
     <row r="263">
       <c r="A263" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B263" s="3" t="n">
-        <v>46243</v>
-      </c>
-      <c r="C263" s="4" t="n">
-        <v>0.2381944444444444</v>
+        <v>46238</v>
+      </c>
+      <c r="C263" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D263" s="4" t="n">
-        <v>0.75625</v>
+        <v>0.7458333333333333</v>
       </c>
       <c r="E263" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B264" s="3" t="n">
-        <v>46244</v>
-      </c>
-      <c r="C264" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D264" s="4" t="n">
-        <v>0.75625</v>
+        <v>46239</v>
+      </c>
+      <c r="C264" s="4" t="n">
+        <v>0.2229166666666667</v>
+      </c>
+      <c r="D264" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E264" s="2" t="inlineStr">
         <is>
@@ -5825,17 +5869,17 @@
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B265" s="3" t="n">
-        <v>46245</v>
+        <v>46240</v>
       </c>
       <c r="C265" s="4" t="n">
-        <v>0.2381944444444444</v>
+        <v>0.2326388888888889</v>
       </c>
       <c r="D265" s="4" t="n">
-        <v>0.7402777777777778</v>
+        <v>0.7576388888888889</v>
       </c>
       <c r="E265" s="2" t="inlineStr">
         <is>
@@ -5846,17 +5890,17 @@
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B266" s="3" t="n">
-        <v>46246</v>
+        <v>46242</v>
       </c>
       <c r="C266" s="4" t="n">
-        <v>0.2340277777777778</v>
+        <v>0.2402777777777778</v>
       </c>
       <c r="D266" s="4" t="n">
-        <v>0.7493055555555556</v>
+        <v>0.7243055555555555</v>
       </c>
       <c r="E266" s="2" t="inlineStr">
         <is>
@@ -5867,17 +5911,17 @@
     <row r="267">
       <c r="A267" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B267" s="3" t="n">
-        <v>46247</v>
+        <v>46243</v>
       </c>
       <c r="C267" s="4" t="n">
-        <v>0.2465277777777778</v>
+        <v>0.2402777777777778</v>
       </c>
       <c r="D267" s="4" t="n">
-        <v>0.7270833333333333</v>
+        <v>0.725</v>
       </c>
       <c r="E267" s="2" t="inlineStr">
         <is>
@@ -5888,17 +5932,17 @@
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B268" s="3" t="n">
-        <v>46249</v>
+        <v>46244</v>
       </c>
       <c r="C268" s="4" t="n">
-        <v>0.2395833333333333</v>
+        <v>0.2409722222222222</v>
       </c>
       <c r="D268" s="4" t="n">
-        <v>0.7388888888888889</v>
+        <v>0.7597222222222222</v>
       </c>
       <c r="E268" s="2" t="inlineStr">
         <is>
@@ -5909,17 +5953,17 @@
     <row r="269">
       <c r="A269" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B269" s="3" t="n">
-        <v>46250</v>
+        <v>46245</v>
       </c>
       <c r="C269" s="4" t="n">
-        <v>0.2902777777777778</v>
+        <v>0.2215277777777778</v>
       </c>
       <c r="D269" s="4" t="n">
-        <v>0.7236111111111111</v>
+        <v>0.7319444444444444</v>
       </c>
       <c r="E269" s="2" t="inlineStr">
         <is>
@@ -5930,17 +5974,17 @@
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B270" s="3" t="n">
-        <v>46251</v>
+        <v>46246</v>
       </c>
       <c r="C270" s="4" t="n">
-        <v>0.2743055555555556</v>
+        <v>0.2361111111111111</v>
       </c>
       <c r="D270" s="4" t="n">
-        <v>0.7333333333333333</v>
+        <v>0.7402777777777778</v>
       </c>
       <c r="E270" s="2" t="inlineStr">
         <is>
@@ -5951,17 +5995,17 @@
     <row r="271">
       <c r="A271" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B271" s="3" t="n">
-        <v>46252</v>
+        <v>46247</v>
       </c>
       <c r="C271" s="4" t="n">
-        <v>0.2826388888888889</v>
+        <v>0.2479166666666667</v>
       </c>
       <c r="D271" s="4" t="n">
-        <v>0.7451388888888889</v>
+        <v>0.7243055555555555</v>
       </c>
       <c r="E271" s="2" t="inlineStr">
         <is>
@@ -5972,38 +6016,40 @@
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B272" s="3" t="n">
-        <v>46253</v>
-      </c>
-      <c r="C272" s="4" t="n">
-        <v>0.2763888888888889</v>
+        <v>46249</v>
+      </c>
+      <c r="C272" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D272" s="4" t="n">
-        <v>0.7298611111111111</v>
+        <v>0.7201388888888889</v>
       </c>
       <c r="E272" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B273" s="3" t="n">
-        <v>46254</v>
+        <v>46250</v>
       </c>
       <c r="C273" s="4" t="n">
-        <v>0.275</v>
+        <v>0.2298611111111111</v>
       </c>
       <c r="D273" s="4" t="n">
-        <v>0.7256944444444444</v>
+        <v>0.7180555555555556</v>
       </c>
       <c r="E273" s="2" t="inlineStr">
         <is>
@@ -6014,17 +6060,17 @@
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B274" s="3" t="n">
-        <v>46256</v>
+        <v>46251</v>
       </c>
       <c r="C274" s="4" t="n">
-        <v>0.2805555555555556</v>
+        <v>0.2472222222222222</v>
       </c>
       <c r="D274" s="4" t="n">
-        <v>0.7513888888888889</v>
+        <v>0.7402777777777778</v>
       </c>
       <c r="E274" s="2" t="inlineStr">
         <is>
@@ -6035,38 +6081,40 @@
     <row r="275">
       <c r="A275" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B275" s="3" t="n">
-        <v>46261</v>
+        <v>46252</v>
       </c>
       <c r="C275" s="4" t="n">
-        <v>0.24375</v>
-      </c>
-      <c r="D275" s="4" t="n">
-        <v>0.6763888888888889</v>
+        <v>0.2354166666666667</v>
+      </c>
+      <c r="D275" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E275" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B276" s="3" t="n">
-        <v>46263</v>
+        <v>46253</v>
       </c>
       <c r="C276" s="4" t="n">
-        <v>0.2965277777777778</v>
+        <v>0.2215277777777778</v>
       </c>
       <c r="D276" s="4" t="n">
-        <v>0.7472222222222222</v>
+        <v>0.7305555555555555</v>
       </c>
       <c r="E276" s="2" t="inlineStr">
         <is>
@@ -6077,17 +6125,17 @@
     <row r="277">
       <c r="A277" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B277" s="3" t="n">
-        <v>46264</v>
+        <v>46254</v>
       </c>
       <c r="C277" s="4" t="n">
-        <v>0.2888888888888889</v>
+        <v>0.2222222222222222</v>
       </c>
       <c r="D277" s="4" t="n">
-        <v>0.75</v>
+        <v>0.7291666666666666</v>
       </c>
       <c r="E277" s="2" t="inlineStr">
         <is>
@@ -6098,19 +6146,40 @@
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B278" s="3" t="n">
-        <v>46265</v>
+        <v>46256</v>
       </c>
       <c r="C278" s="4" t="n">
-        <v>0.2909722222222222</v>
+        <v>0.2388888888888889</v>
       </c>
       <c r="D278" s="4" t="n">
-        <v>0.75</v>
+        <v>0.7541666666666667</v>
       </c>
       <c r="E278" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B279" s="3" t="n">
+        <v>46257</v>
+      </c>
+      <c r="C279" s="4" t="n">
+        <v>0.2506944444444444</v>
+      </c>
+      <c r="D279" s="4" t="n">
+        <v>0.7291666666666666</v>
+      </c>
+      <c r="E279" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -6119,38 +6188,40 @@
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B280" s="3" t="n">
-        <v>46235</v>
-      </c>
-      <c r="C280" s="4" t="n">
-        <v>0.2381944444444444</v>
+        <v>46258</v>
+      </c>
+      <c r="C280" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D280" s="4" t="n">
-        <v>0.7458333333333333</v>
+        <v>0.725</v>
       </c>
       <c r="E280" s="2" t="inlineStr">
         <is>
-          <t>last day of month; final record</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B281" s="3" t="n">
-        <v>46236</v>
+        <v>46259</v>
       </c>
       <c r="C281" s="4" t="n">
-        <v>0.2958333333333333</v>
+        <v>0.2375</v>
       </c>
       <c r="D281" s="4" t="n">
-        <v>0.7430555555555556</v>
+        <v>0.725</v>
       </c>
       <c r="E281" s="2" t="inlineStr">
         <is>
@@ -6161,17 +6232,17 @@
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B282" s="3" t="n">
-        <v>46237</v>
+        <v>46260</v>
       </c>
       <c r="C282" s="4" t="n">
-        <v>0.3034722222222222</v>
+        <v>0.2256944444444444</v>
       </c>
       <c r="D282" s="4" t="n">
-        <v>0.7159722222222222</v>
+        <v>0.7381944444444445</v>
       </c>
       <c r="E282" s="2" t="inlineStr">
         <is>
@@ -6182,14 +6253,14 @@
     <row r="283">
       <c r="A283" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B283" s="3" t="n">
-        <v>46238</v>
+        <v>46261</v>
       </c>
       <c r="C283" s="4" t="n">
-        <v>0.2763888888888889</v>
+        <v>0.2361111111111111</v>
       </c>
       <c r="D283" s="4" t="n">
         <v>0.7166666666666667</v>
@@ -6203,17 +6274,17 @@
     <row r="284">
       <c r="A284" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B284" s="3" t="n">
-        <v>46239</v>
+        <v>46263</v>
       </c>
       <c r="C284" s="4" t="n">
-        <v>0.3222222222222222</v>
+        <v>0.2270833333333333</v>
       </c>
       <c r="D284" s="4" t="n">
-        <v>0.7715277777777778</v>
+        <v>0.7347222222222223</v>
       </c>
       <c r="E284" s="2" t="inlineStr">
         <is>
@@ -6224,170 +6295,147 @@
     <row r="285">
       <c r="A285" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B285" s="3" t="n">
-        <v>46240</v>
+        <v>46264</v>
       </c>
       <c r="C285" s="4" t="n">
-        <v>0.30625</v>
-      </c>
-      <c r="D285" s="4" t="n">
-        <v>0.7590277777777777</v>
+        <v>0.2340277777777778</v>
+      </c>
+      <c r="D285" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E285" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B286" s="3" t="n">
-        <v>46242</v>
+        <v>46265</v>
       </c>
       <c r="C286" s="4" t="n">
-        <v>0.3055555555555556</v>
-      </c>
-      <c r="D286" s="4" t="n">
-        <v>0.7604166666666666</v>
+        <v>0.2361111111111111</v>
+      </c>
+      <c r="D286" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E286" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="287">
-      <c r="A287" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="B287" s="3" t="n">
-        <v>46243</v>
-      </c>
-      <c r="C287" s="4" t="n">
-        <v>0.2798611111111111</v>
-      </c>
-      <c r="D287" s="4" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="E287" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B288" s="3" t="n">
-        <v>46244</v>
+        <v>46235</v>
       </c>
       <c r="C288" s="4" t="n">
-        <v>0.2263888888888889</v>
+        <v>0.14375</v>
       </c>
       <c r="D288" s="4" t="n">
-        <v>0.75</v>
+        <v>0.7576388888888889</v>
       </c>
       <c r="E288" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>last day of month; final record</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B289" s="3" t="n">
-        <v>46245</v>
+        <v>46236</v>
       </c>
       <c r="C289" s="4" t="n">
-        <v>0.3118055555555556</v>
-      </c>
-      <c r="D289" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.14375</v>
+      </c>
+      <c r="D289" s="4" t="n">
+        <v>0.7395833333333334</v>
       </c>
       <c r="E289" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B290" s="3" t="n">
-        <v>46246</v>
+        <v>46237</v>
       </c>
       <c r="C290" s="4" t="n">
-        <v>0.2986111111111111</v>
-      </c>
-      <c r="D290" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.1458333333333333</v>
+      </c>
+      <c r="D290" s="4" t="n">
+        <v>0.7472222222222222</v>
       </c>
       <c r="E290" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B291" s="3" t="n">
-        <v>46247</v>
+        <v>46238</v>
       </c>
       <c r="C291" s="4" t="n">
-        <v>0.3347222222222222</v>
-      </c>
-      <c r="D291" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.1451388888888889</v>
+      </c>
+      <c r="D291" s="4" t="n">
+        <v>0.7708333333333334</v>
       </c>
       <c r="E291" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B292" s="3" t="n">
-        <v>46249</v>
+        <v>46239</v>
       </c>
       <c r="C292" s="4" t="n">
-        <v>0.2354166666666667</v>
+        <v>0.1444444444444444</v>
       </c>
       <c r="D292" s="4" t="n">
-        <v>0.75</v>
+        <v>0.6881944444444444</v>
       </c>
       <c r="E292" s="2" t="inlineStr">
         <is>
@@ -6398,17 +6446,17 @@
     <row r="293">
       <c r="A293" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B293" s="3" t="n">
-        <v>46250</v>
+        <v>46240</v>
       </c>
       <c r="C293" s="4" t="n">
-        <v>0.325</v>
+        <v>0.1444444444444444</v>
       </c>
       <c r="D293" s="4" t="n">
-        <v>0.7722222222222223</v>
+        <v>0.7659722222222223</v>
       </c>
       <c r="E293" s="2" t="inlineStr">
         <is>
@@ -6419,17 +6467,17 @@
     <row r="294">
       <c r="A294" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B294" s="3" t="n">
-        <v>46251</v>
+        <v>46241</v>
       </c>
       <c r="C294" s="4" t="n">
-        <v>0.3979166666666666</v>
+        <v>0.1451388888888889</v>
       </c>
       <c r="D294" s="4" t="n">
-        <v>0.7680555555555556</v>
+        <v>0.7298611111111111</v>
       </c>
       <c r="E294" s="2" t="inlineStr">
         <is>
@@ -6440,38 +6488,38 @@
     <row r="295">
       <c r="A295" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B295" s="3" t="n">
-        <v>46252</v>
+        <v>46242</v>
       </c>
       <c r="C295" s="4" t="n">
-        <v>0.3083333333333333</v>
+        <v>0.1388888888888889</v>
       </c>
       <c r="D295" s="4" t="n">
-        <v>0.7583333333333333</v>
+        <v>0.8090277777777778</v>
       </c>
       <c r="E295" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>extra punch: 03:24</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B296" s="3" t="n">
-        <v>46253</v>
+        <v>46243</v>
       </c>
       <c r="C296" s="4" t="n">
-        <v>0.475</v>
+        <v>0.1444444444444444</v>
       </c>
       <c r="D296" s="4" t="n">
-        <v>0.7173611111111111</v>
+        <v>0.8381944444444445</v>
       </c>
       <c r="E296" s="2" t="inlineStr">
         <is>
@@ -6482,40 +6530,38 @@
     <row r="297">
       <c r="A297" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B297" s="3" t="n">
-        <v>46254</v>
+        <v>46244</v>
       </c>
       <c r="C297" s="4" t="n">
-        <v>0.3576388888888889</v>
-      </c>
-      <c r="D297" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.1354166666666667</v>
+      </c>
+      <c r="D297" s="4" t="n">
+        <v>0.7638888888888888</v>
       </c>
       <c r="E297" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B298" s="3" t="n">
-        <v>46256</v>
+        <v>46245</v>
       </c>
       <c r="C298" s="4" t="n">
-        <v>0.2069444444444444</v>
+        <v>0.14375</v>
       </c>
       <c r="D298" s="4" t="n">
-        <v>0.7243055555555555</v>
+        <v>0.7444444444444445</v>
       </c>
       <c r="E298" s="2" t="inlineStr">
         <is>
@@ -6526,17 +6572,17 @@
     <row r="299">
       <c r="A299" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B299" s="3" t="n">
-        <v>46257</v>
+        <v>46246</v>
       </c>
       <c r="C299" s="4" t="n">
-        <v>0.25</v>
+        <v>0.1430555555555555</v>
       </c>
       <c r="D299" s="4" t="n">
-        <v>0.7493055555555556</v>
+        <v>0.7409722222222223</v>
       </c>
       <c r="E299" s="2" t="inlineStr">
         <is>
@@ -6547,17 +6593,17 @@
     <row r="300">
       <c r="A300" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B300" s="3" t="n">
-        <v>46258</v>
+        <v>46247</v>
       </c>
       <c r="C300" s="4" t="n">
-        <v>0.3263888888888889</v>
+        <v>0.1423611111111111</v>
       </c>
       <c r="D300" s="4" t="n">
-        <v>0.7388888888888889</v>
+        <v>0.75</v>
       </c>
       <c r="E300" s="2" t="inlineStr">
         <is>
@@ -6568,17 +6614,17 @@
     <row r="301">
       <c r="A301" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B301" s="3" t="n">
-        <v>46259</v>
+        <v>46248</v>
       </c>
       <c r="C301" s="4" t="n">
-        <v>0.2763888888888889</v>
+        <v>0.15</v>
       </c>
       <c r="D301" s="4" t="n">
-        <v>0.7548611111111111</v>
+        <v>0.7076388888888889</v>
       </c>
       <c r="E301" s="2" t="inlineStr">
         <is>
@@ -6589,38 +6635,38 @@
     <row r="302">
       <c r="A302" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B302" s="3" t="n">
-        <v>46260</v>
+        <v>46249</v>
       </c>
       <c r="C302" s="4" t="n">
-        <v>0.3243055555555556</v>
+        <v>0.1513888888888889</v>
       </c>
       <c r="D302" s="4" t="n">
-        <v>0.7534722222222222</v>
+        <v>0.7277777777777777</v>
       </c>
       <c r="E302" s="2" t="inlineStr">
         <is>
-          <t>extra punch: 17:56</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B303" s="3" t="n">
-        <v>46261</v>
+        <v>46250</v>
       </c>
       <c r="C303" s="4" t="n">
-        <v>0.2666666666666667</v>
+        <v>0.2708333333333333</v>
       </c>
       <c r="D303" s="4" t="n">
-        <v>0.75</v>
+        <v>0.7229166666666667</v>
       </c>
       <c r="E303" s="2" t="inlineStr">
         <is>
@@ -6631,17 +6677,17 @@
     <row r="304">
       <c r="A304" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B304" s="3" t="n">
-        <v>46263</v>
+        <v>46251</v>
       </c>
       <c r="C304" s="4" t="n">
-        <v>0.2965277777777778</v>
+        <v>0.2333333333333333</v>
       </c>
       <c r="D304" s="4" t="n">
-        <v>0.7326388888888888</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="E304" s="2" t="inlineStr">
         <is>
@@ -6652,17 +6698,17 @@
     <row r="305">
       <c r="A305" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B305" s="3" t="n">
-        <v>46264</v>
+        <v>46252</v>
       </c>
       <c r="C305" s="4" t="n">
-        <v>0.2965277777777778</v>
+        <v>0.25625</v>
       </c>
       <c r="D305" s="4" t="n">
-        <v>0.75625</v>
+        <v>0.7416666666666667</v>
       </c>
       <c r="E305" s="2" t="inlineStr">
         <is>
@@ -6673,59 +6719,80 @@
     <row r="306">
       <c r="A306" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B306" s="3" t="n">
-        <v>46265</v>
+        <v>46253</v>
       </c>
       <c r="C306" s="4" t="n">
-        <v>0.2527777777777778</v>
+        <v>0.2777777777777778</v>
       </c>
       <c r="D306" s="4" t="n">
-        <v>0.7604166666666666</v>
+        <v>0.7451388888888889</v>
       </c>
       <c r="E306" s="2" t="inlineStr">
         <is>
-          <t>corrected from a clearer re-scan photo later in the album</t>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B307" s="3" t="n">
+        <v>46254</v>
+      </c>
+      <c r="C307" s="4" t="n">
+        <v>0.2625</v>
+      </c>
+      <c r="D307" s="4" t="n">
+        <v>0.7979166666666667</v>
+      </c>
+      <c r="E307" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B308" s="3" t="n">
-        <v>46235</v>
+        <v>46255</v>
       </c>
       <c r="C308" s="4" t="n">
-        <v>0.2590277777777778</v>
+        <v>0.275</v>
       </c>
       <c r="D308" s="4" t="n">
-        <v>0.7319444444444444</v>
+        <v>0.8354166666666667</v>
       </c>
       <c r="E308" s="2" t="inlineStr">
         <is>
-          <t>last day of month; final record</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B309" s="3" t="n">
-        <v>46236</v>
+        <v>46256</v>
       </c>
       <c r="C309" s="4" t="n">
-        <v>0.2972222222222222</v>
+        <v>0.2611111111111111</v>
       </c>
       <c r="D309" s="4" t="n">
-        <v>0.7430555555555556</v>
+        <v>0.7513888888888889</v>
       </c>
       <c r="E309" s="2" t="inlineStr">
         <is>
@@ -6736,17 +6803,17 @@
     <row r="310">
       <c r="A310" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B310" s="3" t="n">
-        <v>46237</v>
+        <v>46257</v>
       </c>
       <c r="C310" s="4" t="n">
-        <v>0.2618055555555556</v>
+        <v>0.24375</v>
       </c>
       <c r="D310" s="4" t="n">
-        <v>0.7472222222222222</v>
+        <v>0.7263888888888889</v>
       </c>
       <c r="E310" s="2" t="inlineStr">
         <is>
@@ -6757,17 +6824,17 @@
     <row r="311">
       <c r="A311" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B311" s="3" t="n">
-        <v>46238</v>
+        <v>46258</v>
       </c>
       <c r="C311" s="4" t="n">
-        <v>0.4965277777777778</v>
+        <v>0.2631944444444445</v>
       </c>
       <c r="D311" s="4" t="n">
-        <v>0.7506944444444444</v>
+        <v>0.7270833333333333</v>
       </c>
       <c r="E311" s="2" t="inlineStr">
         <is>
@@ -6778,17 +6845,17 @@
     <row r="312">
       <c r="A312" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B312" s="3" t="n">
-        <v>46239</v>
+        <v>46259</v>
       </c>
       <c r="C312" s="4" t="n">
-        <v>0.4743055555555555</v>
+        <v>0.2611111111111111</v>
       </c>
       <c r="D312" s="4" t="n">
-        <v>0.7722222222222223</v>
+        <v>0.7298611111111111</v>
       </c>
       <c r="E312" s="2" t="inlineStr">
         <is>
@@ -6799,59 +6866,59 @@
     <row r="313">
       <c r="A313" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B313" s="3" t="n">
-        <v>46240</v>
+        <v>46260</v>
       </c>
       <c r="C313" s="4" t="n">
-        <v>0.2409722222222222</v>
+        <v>0.275</v>
       </c>
       <c r="D313" s="4" t="n">
-        <v>0.7625</v>
+        <v>0.8791666666666667</v>
       </c>
       <c r="E313" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>extra punch: 17:56</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B314" s="3" t="n">
-        <v>46242</v>
+        <v>46261</v>
       </c>
       <c r="C314" s="4" t="n">
-        <v>0.2201388888888889</v>
+        <v>0.2555555555555555</v>
       </c>
       <c r="D314" s="4" t="n">
-        <v>0.7618055555555555</v>
+        <v>0.8506944444444444</v>
       </c>
       <c r="E314" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>extra punches: 17:07 17:02</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B315" s="3" t="n">
-        <v>46243</v>
+        <v>46262</v>
       </c>
       <c r="C315" s="4" t="n">
-        <v>0.2395833333333333</v>
+        <v>0.2805555555555556</v>
       </c>
       <c r="D315" s="4" t="n">
-        <v>0.725</v>
+        <v>0.7701388888888889</v>
       </c>
       <c r="E315" s="2" t="inlineStr">
         <is>
@@ -6862,17 +6929,17 @@
     <row r="316">
       <c r="A316" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B316" s="3" t="n">
-        <v>46244</v>
+        <v>46263</v>
       </c>
       <c r="C316" s="4" t="n">
-        <v>0.2256944444444444</v>
+        <v>0.2541666666666667</v>
       </c>
       <c r="D316" s="4" t="n">
-        <v>0.7611111111111111</v>
+        <v>0.7479166666666667</v>
       </c>
       <c r="E316" s="2" t="inlineStr">
         <is>
@@ -6883,17 +6950,17 @@
     <row r="317">
       <c r="A317" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B317" s="3" t="n">
-        <v>46245</v>
+        <v>46264</v>
       </c>
       <c r="C317" s="4" t="n">
-        <v>0.2375</v>
+        <v>0.2659722222222222</v>
       </c>
       <c r="D317" s="4" t="n">
-        <v>0.7375</v>
+        <v>0.7354166666666667</v>
       </c>
       <c r="E317" s="2" t="inlineStr">
         <is>
@@ -6904,82 +6971,59 @@
     <row r="318">
       <c r="A318" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B318" s="3" t="n">
-        <v>46246</v>
+        <v>46265</v>
       </c>
       <c r="C318" s="4" t="n">
-        <v>0.2284722222222222</v>
+        <v>0.2527777777777778</v>
       </c>
       <c r="D318" s="4" t="n">
-        <v>0.7423611111111111</v>
+        <v>0.7354166666666667</v>
       </c>
       <c r="E318" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="319">
-      <c r="A319" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="B319" s="3" t="n">
-        <v>46247</v>
-      </c>
-      <c r="C319" s="4" t="n">
-        <v>0.4402777777777778</v>
-      </c>
-      <c r="D319" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E319" s="2" t="inlineStr">
-        <is>
-          <t>single punch only</t>
+          <t>corrected from a clearer re-scan photo later in the album</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B320" s="3" t="n">
-        <v>46249</v>
+        <v>46235</v>
       </c>
       <c r="C320" s="4" t="n">
-        <v>0.2354166666666667</v>
+        <v>0.2625</v>
       </c>
       <c r="D320" s="4" t="n">
-        <v>0.7611111111111111</v>
+        <v>0.7444444444444445</v>
       </c>
       <c r="E320" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>last day of month; final record</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B321" s="3" t="n">
-        <v>46250</v>
+        <v>46236</v>
       </c>
       <c r="C321" s="4" t="n">
-        <v>0.2409722222222222</v>
+        <v>0.2645833333333333</v>
       </c>
       <c r="D321" s="4" t="n">
-        <v>0.7381944444444445</v>
+        <v>0.7493055555555556</v>
       </c>
       <c r="E321" s="2" t="inlineStr">
         <is>
@@ -6990,17 +7034,17 @@
     <row r="322">
       <c r="A322" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B322" s="3" t="n">
-        <v>46251</v>
+        <v>46237</v>
       </c>
       <c r="C322" s="4" t="n">
-        <v>0.3416666666666667</v>
+        <v>0.2604166666666667</v>
       </c>
       <c r="D322" s="4" t="n">
-        <v>0.7326388888888888</v>
+        <v>0.7479166666666667</v>
       </c>
       <c r="E322" s="2" t="inlineStr">
         <is>
@@ -7011,17 +7055,17 @@
     <row r="323">
       <c r="A323" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B323" s="3" t="n">
-        <v>46252</v>
+        <v>46238</v>
       </c>
       <c r="C323" s="4" t="n">
-        <v>0.2916666666666667</v>
+        <v>0.2527777777777778</v>
       </c>
       <c r="D323" s="4" t="n">
-        <v>0.7416666666666667</v>
+        <v>0.75</v>
       </c>
       <c r="E323" s="2" t="inlineStr">
         <is>
@@ -7032,17 +7076,17 @@
     <row r="324">
       <c r="A324" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B324" s="3" t="n">
-        <v>46253</v>
+        <v>46239</v>
       </c>
       <c r="C324" s="4" t="n">
-        <v>0.2395833333333333</v>
+        <v>0.25625</v>
       </c>
       <c r="D324" s="4" t="n">
-        <v>0.7416666666666667</v>
+        <v>0.7763888888888889</v>
       </c>
       <c r="E324" s="2" t="inlineStr">
         <is>
@@ -7053,17 +7097,17 @@
     <row r="325">
       <c r="A325" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B325" s="3" t="n">
-        <v>46254</v>
+        <v>46240</v>
       </c>
       <c r="C325" s="4" t="n">
-        <v>0.2472222222222222</v>
+        <v>0.2701388888888889</v>
       </c>
       <c r="D325" s="4" t="n">
-        <v>0.7243055555555555</v>
+        <v>0.7423611111111111</v>
       </c>
       <c r="E325" s="2" t="inlineStr">
         <is>
@@ -7074,40 +7118,38 @@
     <row r="326">
       <c r="A326" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B326" s="3" t="n">
-        <v>46256</v>
+        <v>46242</v>
       </c>
       <c r="C326" s="4" t="n">
-        <v>0.2875</v>
-      </c>
-      <c r="D326" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.2597222222222222</v>
+      </c>
+      <c r="D326" s="4" t="n">
+        <v>0.7326388888888888</v>
       </c>
       <c r="E326" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B327" s="3" t="n">
-        <v>46257</v>
+        <v>46243</v>
       </c>
       <c r="C327" s="4" t="n">
-        <v>0.2479166666666667</v>
+        <v>0.2381944444444444</v>
       </c>
       <c r="D327" s="4" t="n">
-        <v>0.7618055555555555</v>
+        <v>0.75625</v>
       </c>
       <c r="E327" s="2" t="inlineStr">
         <is>
@@ -7118,38 +7160,40 @@
     <row r="328">
       <c r="A328" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B328" s="3" t="n">
-        <v>46258</v>
-      </c>
-      <c r="C328" s="4" t="n">
-        <v>0.2375</v>
+        <v>46244</v>
+      </c>
+      <c r="C328" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D328" s="4" t="n">
-        <v>0.7506944444444444</v>
+        <v>0.75625</v>
       </c>
       <c r="E328" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B329" s="3" t="n">
-        <v>46259</v>
+        <v>46245</v>
       </c>
       <c r="C329" s="4" t="n">
-        <v>0.2375</v>
+        <v>0.2381944444444444</v>
       </c>
       <c r="D329" s="4" t="n">
-        <v>0.7597222222222222</v>
+        <v>0.7402777777777778</v>
       </c>
       <c r="E329" s="2" t="inlineStr">
         <is>
@@ -7160,17 +7204,17 @@
     <row r="330">
       <c r="A330" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B330" s="3" t="n">
-        <v>46260</v>
+        <v>46246</v>
       </c>
       <c r="C330" s="4" t="n">
-        <v>0.2479166666666667</v>
+        <v>0.2340277777777778</v>
       </c>
       <c r="D330" s="4" t="n">
-        <v>0.7555555555555555</v>
+        <v>0.7493055555555556</v>
       </c>
       <c r="E330" s="2" t="inlineStr">
         <is>
@@ -7181,17 +7225,17 @@
     <row r="331">
       <c r="A331" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B331" s="3" t="n">
-        <v>46261</v>
+        <v>46247</v>
       </c>
       <c r="C331" s="4" t="n">
-        <v>0.2493055555555556</v>
+        <v>0.2465277777777778</v>
       </c>
       <c r="D331" s="4" t="n">
-        <v>0.7944444444444444</v>
+        <v>0.7270833333333333</v>
       </c>
       <c r="E331" s="2" t="inlineStr">
         <is>
@@ -7202,61 +7246,59 @@
     <row r="332">
       <c r="A332" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B332" s="3" t="n">
-        <v>46262</v>
+        <v>46249</v>
       </c>
       <c r="C332" s="4" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="D332" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.2395833333333333</v>
+      </c>
+      <c r="D332" s="4" t="n">
+        <v>0.7388888888888889</v>
       </c>
       <c r="E332" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B333" s="3" t="n">
-        <v>46263</v>
+        <v>46250</v>
       </c>
       <c r="C333" s="4" t="n">
-        <v>0.2569444444444444</v>
+        <v>0.2902777777777778</v>
       </c>
       <c r="D333" s="4" t="n">
-        <v>0.7458333333333333</v>
+        <v>0.7236111111111111</v>
       </c>
       <c r="E333" s="2" t="inlineStr">
         <is>
-          <t>extra punch: 17:53</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B334" s="3" t="n">
-        <v>46264</v>
+        <v>46251</v>
       </c>
       <c r="C334" s="4" t="n">
-        <v>0.2590277777777778</v>
+        <v>0.2743055555555556</v>
       </c>
       <c r="D334" s="4" t="n">
-        <v>0.7541666666666667</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="E334" s="2" t="inlineStr">
         <is>
@@ -7267,59 +7309,80 @@
     <row r="335">
       <c r="A335" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B335" s="3" t="n">
-        <v>46265</v>
+        <v>46252</v>
       </c>
       <c r="C335" s="4" t="n">
-        <v>0.2777777777777778</v>
+        <v>0.2826388888888889</v>
       </c>
       <c r="D335" s="4" t="n">
-        <v>0.7513888888888889</v>
+        <v>0.7451388888888889</v>
       </c>
       <c r="E335" s="2" t="inlineStr">
         <is>
-          <t>corrected from a clearer re-scan photo later in the album</t>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B336" s="3" t="n">
+        <v>46253</v>
+      </c>
+      <c r="C336" s="4" t="n">
+        <v>0.2763888888888889</v>
+      </c>
+      <c r="D336" s="4" t="n">
+        <v>0.7298611111111111</v>
+      </c>
+      <c r="E336" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B337" s="3" t="n">
-        <v>46235</v>
+        <v>46254</v>
       </c>
       <c r="C337" s="4" t="n">
-        <v>0.2451388888888889</v>
+        <v>0.275</v>
       </c>
       <c r="D337" s="4" t="n">
-        <v>0.7506944444444444</v>
+        <v>0.7256944444444444</v>
       </c>
       <c r="E337" s="2" t="inlineStr">
         <is>
-          <t>last day of month; final record</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B338" s="3" t="n">
-        <v>46236</v>
+        <v>46256</v>
       </c>
       <c r="C338" s="4" t="n">
-        <v>0.24375</v>
+        <v>0.2805555555555556</v>
       </c>
       <c r="D338" s="4" t="n">
-        <v>0.7520833333333333</v>
+        <v>0.7513888888888889</v>
       </c>
       <c r="E338" s="2" t="inlineStr">
         <is>
@@ -7330,17 +7393,17 @@
     <row r="339">
       <c r="A339" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B339" s="3" t="n">
-        <v>46237</v>
+        <v>46261</v>
       </c>
       <c r="C339" s="4" t="n">
         <v>0.24375</v>
       </c>
       <c r="D339" s="4" t="n">
-        <v>0.7527777777777778</v>
+        <v>0.6763888888888889</v>
       </c>
       <c r="E339" s="2" t="inlineStr">
         <is>
@@ -7351,17 +7414,17 @@
     <row r="340">
       <c r="A340" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B340" s="3" t="n">
-        <v>46238</v>
+        <v>46263</v>
       </c>
       <c r="C340" s="4" t="n">
-        <v>0.2451388888888889</v>
+        <v>0.2965277777777778</v>
       </c>
       <c r="D340" s="4" t="n">
-        <v>0.7520833333333333</v>
+        <v>0.7472222222222222</v>
       </c>
       <c r="E340" s="2" t="inlineStr">
         <is>
@@ -7372,17 +7435,17 @@
     <row r="341">
       <c r="A341" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B341" s="3" t="n">
-        <v>46239</v>
+        <v>46264</v>
       </c>
       <c r="C341" s="4" t="n">
-        <v>0.2368055555555555</v>
+        <v>0.2888888888888889</v>
       </c>
       <c r="D341" s="4" t="n">
-        <v>0.7611111111111111</v>
+        <v>0.75</v>
       </c>
       <c r="E341" s="2" t="inlineStr">
         <is>
@@ -7393,40 +7456,19 @@
     <row r="342">
       <c r="A342" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B342" s="3" t="n">
-        <v>46240</v>
+        <v>46265</v>
       </c>
       <c r="C342" s="4" t="n">
-        <v>0.2402777777777778</v>
+        <v>0.2909722222222222</v>
       </c>
       <c r="D342" s="4" t="n">
-        <v>0.7513888888888889</v>
+        <v>0.75</v>
       </c>
       <c r="E342" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="343">
-      <c r="A343" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="B343" s="3" t="n">
-        <v>46242</v>
-      </c>
-      <c r="C343" s="4" t="n">
-        <v>0.2430555555555556</v>
-      </c>
-      <c r="D343" s="4" t="n">
-        <v>0.7548611111111111</v>
-      </c>
-      <c r="E343" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -7435,42 +7477,38 @@
     <row r="344">
       <c r="A344" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B344" s="3" t="n">
-        <v>46246</v>
-      </c>
-      <c r="C344" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D344" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>46235</v>
+      </c>
+      <c r="C344" s="4" t="n">
+        <v>0.2381944444444444</v>
+      </c>
+      <c r="D344" s="4" t="n">
+        <v>0.7458333333333333</v>
       </c>
       <c r="E344" s="2" t="inlineStr">
         <is>
-          <t>PLEASE VERIFY: check-in/out times not captured (gap between source photos)</t>
+          <t>last day of month; final record</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B345" s="3" t="n">
-        <v>46247</v>
+        <v>46236</v>
       </c>
       <c r="C345" s="4" t="n">
-        <v>0.2444444444444444</v>
+        <v>0.2958333333333333</v>
       </c>
       <c r="D345" s="4" t="n">
-        <v>0.7576388888888889</v>
+        <v>0.7430555555555556</v>
       </c>
       <c r="E345" s="2" t="inlineStr">
         <is>
@@ -7481,17 +7519,17 @@
     <row r="346">
       <c r="A346" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B346" s="3" t="n">
-        <v>46249</v>
+        <v>46237</v>
       </c>
       <c r="C346" s="4" t="n">
-        <v>0.2381944444444444</v>
+        <v>0.3034722222222222</v>
       </c>
       <c r="D346" s="4" t="n">
-        <v>0.7513888888888889</v>
+        <v>0.7159722222222222</v>
       </c>
       <c r="E346" s="2" t="inlineStr">
         <is>
@@ -7502,17 +7540,17 @@
     <row r="347">
       <c r="A347" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B347" s="3" t="n">
-        <v>46250</v>
+        <v>46238</v>
       </c>
       <c r="C347" s="4" t="n">
-        <v>0.2354166666666667</v>
+        <v>0.2763888888888889</v>
       </c>
       <c r="D347" s="4" t="n">
-        <v>0.7520833333333333</v>
+        <v>0.7166666666666667</v>
       </c>
       <c r="E347" s="2" t="inlineStr">
         <is>
@@ -7523,17 +7561,17 @@
     <row r="348">
       <c r="A348" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B348" s="3" t="n">
-        <v>46251</v>
+        <v>46239</v>
       </c>
       <c r="C348" s="4" t="n">
-        <v>0.2395833333333333</v>
+        <v>0.3222222222222222</v>
       </c>
       <c r="D348" s="4" t="n">
-        <v>0.7541666666666667</v>
+        <v>0.7715277777777778</v>
       </c>
       <c r="E348" s="2" t="inlineStr">
         <is>
@@ -7544,17 +7582,17 @@
     <row r="349">
       <c r="A349" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B349" s="3" t="n">
-        <v>46252</v>
+        <v>46240</v>
       </c>
       <c r="C349" s="4" t="n">
-        <v>0.2451388888888889</v>
+        <v>0.30625</v>
       </c>
       <c r="D349" s="4" t="n">
-        <v>0.7527777777777778</v>
+        <v>0.7590277777777777</v>
       </c>
       <c r="E349" s="2" t="inlineStr">
         <is>
@@ -7565,17 +7603,17 @@
     <row r="350">
       <c r="A350" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B350" s="3" t="n">
-        <v>46253</v>
+        <v>46242</v>
       </c>
       <c r="C350" s="4" t="n">
-        <v>0.2423611111111111</v>
+        <v>0.3055555555555556</v>
       </c>
       <c r="D350" s="4" t="n">
-        <v>0.7506944444444444</v>
+        <v>0.7604166666666666</v>
       </c>
       <c r="E350" s="2" t="inlineStr">
         <is>
@@ -7586,17 +7624,17 @@
     <row r="351">
       <c r="A351" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B351" s="3" t="n">
-        <v>46254</v>
+        <v>46243</v>
       </c>
       <c r="C351" s="4" t="n">
-        <v>0.2402777777777778</v>
+        <v>0.2798611111111111</v>
       </c>
       <c r="D351" s="4" t="n">
-        <v>0.7520833333333333</v>
+        <v>0.75</v>
       </c>
       <c r="E351" s="2" t="inlineStr">
         <is>
@@ -7607,14 +7645,14 @@
     <row r="352">
       <c r="A352" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B352" s="3" t="n">
-        <v>46256</v>
+        <v>46244</v>
       </c>
       <c r="C352" s="4" t="n">
-        <v>0.2402777777777778</v>
+        <v>0.2263888888888889</v>
       </c>
       <c r="D352" s="4" t="n">
         <v>0.75</v>
@@ -7628,80 +7666,86 @@
     <row r="353">
       <c r="A353" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B353" s="3" t="n">
-        <v>46257</v>
+        <v>46245</v>
       </c>
       <c r="C353" s="4" t="n">
-        <v>0.2458333333333333</v>
-      </c>
-      <c r="D353" s="4" t="n">
-        <v>0.7527777777777778</v>
+        <v>0.3118055555555556</v>
+      </c>
+      <c r="D353" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E353" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B354" s="3" t="n">
-        <v>46258</v>
+        <v>46246</v>
       </c>
       <c r="C354" s="4" t="n">
-        <v>0.2347222222222222</v>
-      </c>
-      <c r="D354" s="4" t="n">
-        <v>0.7520833333333333</v>
+        <v>0.2986111111111111</v>
+      </c>
+      <c r="D354" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E354" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B355" s="3" t="n">
-        <v>46259</v>
+        <v>46247</v>
       </c>
       <c r="C355" s="4" t="n">
-        <v>0.2368055555555555</v>
-      </c>
-      <c r="D355" s="4" t="n">
-        <v>0.7506944444444444</v>
+        <v>0.3347222222222222</v>
+      </c>
+      <c r="D355" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E355" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B356" s="3" t="n">
-        <v>46260</v>
+        <v>46249</v>
       </c>
       <c r="C356" s="4" t="n">
-        <v>0.2465277777777778</v>
+        <v>0.2354166666666667</v>
       </c>
       <c r="D356" s="4" t="n">
-        <v>0.7555555555555555</v>
+        <v>0.75</v>
       </c>
       <c r="E356" s="2" t="inlineStr">
         <is>
@@ -7712,17 +7756,17 @@
     <row r="357">
       <c r="A357" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B357" s="3" t="n">
-        <v>46261</v>
+        <v>46250</v>
       </c>
       <c r="C357" s="4" t="n">
-        <v>0.2472222222222222</v>
+        <v>0.325</v>
       </c>
       <c r="D357" s="4" t="n">
-        <v>0.7513888888888889</v>
+        <v>0.7722222222222223</v>
       </c>
       <c r="E357" s="2" t="inlineStr">
         <is>
@@ -7733,17 +7777,17 @@
     <row r="358">
       <c r="A358" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B358" s="3" t="n">
-        <v>46263</v>
+        <v>46251</v>
       </c>
       <c r="C358" s="4" t="n">
-        <v>0.2444444444444444</v>
+        <v>0.3979166666666666</v>
       </c>
       <c r="D358" s="4" t="n">
-        <v>0.7548611111111111</v>
+        <v>0.7680555555555556</v>
       </c>
       <c r="E358" s="2" t="inlineStr">
         <is>
@@ -7754,17 +7798,17 @@
     <row r="359">
       <c r="A359" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B359" s="3" t="n">
-        <v>46264</v>
+        <v>46252</v>
       </c>
       <c r="C359" s="4" t="n">
-        <v>0.2423611111111111</v>
+        <v>0.3083333333333333</v>
       </c>
       <c r="D359" s="4" t="n">
-        <v>0.7513888888888889</v>
+        <v>0.7583333333333333</v>
       </c>
       <c r="E359" s="2" t="inlineStr">
         <is>
@@ -7775,59 +7819,82 @@
     <row r="360">
       <c r="A360" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B360" s="3" t="n">
-        <v>46265</v>
+        <v>46253</v>
       </c>
       <c r="C360" s="4" t="n">
-        <v>0.2361111111111111</v>
+        <v>0.475</v>
       </c>
       <c r="D360" s="4" t="n">
-        <v>0.7520833333333333</v>
+        <v>0.7173611111111111</v>
       </c>
       <c r="E360" s="2" t="inlineStr">
         <is>
-          <t>corrected from a clearer re-scan photo later in the album</t>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B361" s="3" t="n">
+        <v>46254</v>
+      </c>
+      <c r="C361" s="4" t="n">
+        <v>0.3576388888888889</v>
+      </c>
+      <c r="D361" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E361" s="2" t="inlineStr">
+        <is>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B362" s="3" t="n">
-        <v>46235</v>
+        <v>46256</v>
       </c>
       <c r="C362" s="4" t="n">
-        <v>0.275</v>
+        <v>0.2069444444444444</v>
       </c>
       <c r="D362" s="4" t="n">
-        <v>0.7854166666666667</v>
+        <v>0.7243055555555555</v>
       </c>
       <c r="E362" s="2" t="inlineStr">
         <is>
-          <t>last day of month; final record</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B363" s="3" t="n">
-        <v>46236</v>
+        <v>46257</v>
       </c>
       <c r="C363" s="4" t="n">
-        <v>0.2722222222222222</v>
+        <v>0.25</v>
       </c>
       <c r="D363" s="4" t="n">
-        <v>0.7722222222222223</v>
+        <v>0.7493055555555556</v>
       </c>
       <c r="E363" s="2" t="inlineStr">
         <is>
@@ -7838,17 +7905,17 @@
     <row r="364">
       <c r="A364" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B364" s="3" t="n">
-        <v>46237</v>
+        <v>46258</v>
       </c>
       <c r="C364" s="4" t="n">
-        <v>0.2451388888888889</v>
+        <v>0.3263888888888889</v>
       </c>
       <c r="D364" s="4" t="n">
-        <v>0.7201388888888889</v>
+        <v>0.7388888888888889</v>
       </c>
       <c r="E364" s="2" t="inlineStr">
         <is>
@@ -7859,17 +7926,17 @@
     <row r="365">
       <c r="A365" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B365" s="3" t="n">
-        <v>46238</v>
+        <v>46259</v>
       </c>
       <c r="C365" s="4" t="n">
-        <v>0.2729166666666666</v>
+        <v>0.2763888888888889</v>
       </c>
       <c r="D365" s="4" t="n">
-        <v>0.7527777777777778</v>
+        <v>0.7548611111111111</v>
       </c>
       <c r="E365" s="2" t="inlineStr">
         <is>
@@ -7880,61 +7947,59 @@
     <row r="366">
       <c r="A366" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B366" s="3" t="n">
-        <v>46239</v>
+        <v>46260</v>
       </c>
       <c r="C366" s="4" t="n">
-        <v>0.2756944444444445</v>
+        <v>0.3243055555555556</v>
       </c>
       <c r="D366" s="4" t="n">
-        <v>0.7152777777777778</v>
+        <v>0.7534722222222222</v>
       </c>
       <c r="E366" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>extra punch: 17:56</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B367" s="3" t="n">
-        <v>46240</v>
+        <v>46261</v>
       </c>
       <c r="C367" s="4" t="n">
-        <v>0.2715277777777778</v>
-      </c>
-      <c r="D367" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.2666666666666667</v>
+      </c>
+      <c r="D367" s="4" t="n">
+        <v>0.75</v>
       </c>
       <c r="E367" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B368" s="3" t="n">
-        <v>46242</v>
+        <v>46263</v>
       </c>
       <c r="C368" s="4" t="n">
-        <v>0.2388888888888889</v>
+        <v>0.2965277777777778</v>
       </c>
       <c r="D368" s="4" t="n">
-        <v>0.6965277777777777</v>
+        <v>0.7326388888888888</v>
       </c>
       <c r="E368" s="2" t="inlineStr">
         <is>
@@ -7945,17 +8010,17 @@
     <row r="369">
       <c r="A369" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B369" s="3" t="n">
-        <v>46243</v>
+        <v>46264</v>
       </c>
       <c r="C369" s="4" t="n">
-        <v>0.2451388888888889</v>
+        <v>0.2965277777777778</v>
       </c>
       <c r="D369" s="4" t="n">
-        <v>0.7694444444444445</v>
+        <v>0.75625</v>
       </c>
       <c r="E369" s="2" t="inlineStr">
         <is>
@@ -7966,80 +8031,59 @@
     <row r="370">
       <c r="A370" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B370" s="3" t="n">
-        <v>46244</v>
+        <v>46265</v>
       </c>
       <c r="C370" s="4" t="n">
-        <v>0.2298611111111111</v>
+        <v>0.2527777777777778</v>
       </c>
       <c r="D370" s="4" t="n">
-        <v>0.75625</v>
+        <v>0.7604166666666666</v>
       </c>
       <c r="E370" s="2" t="inlineStr">
         <is>
-          <t>extra punch: 06:48</t>
-        </is>
-      </c>
-    </row>
-    <row r="371">
-      <c r="A371" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="B371" s="3" t="n">
-        <v>46245</v>
-      </c>
-      <c r="C371" s="4" t="n">
-        <v>0.275</v>
-      </c>
-      <c r="D371" s="4" t="n">
-        <v>0.7618055555555555</v>
-      </c>
-      <c r="E371" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>corrected from a clearer re-scan photo later in the album</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B372" s="3" t="n">
-        <v>46246</v>
+        <v>46235</v>
       </c>
       <c r="C372" s="4" t="n">
-        <v>0.2694444444444444</v>
+        <v>0.2590277777777778</v>
       </c>
       <c r="D372" s="4" t="n">
-        <v>0.7222222222222222</v>
+        <v>0.7319444444444444</v>
       </c>
       <c r="E372" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>last day of month; final record</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B373" s="3" t="n">
-        <v>46247</v>
+        <v>46236</v>
       </c>
       <c r="C373" s="4" t="n">
-        <v>0.3409722222222222</v>
+        <v>0.2972222222222222</v>
       </c>
       <c r="D373" s="4" t="n">
-        <v>0.7583333333333333</v>
+        <v>0.7430555555555556</v>
       </c>
       <c r="E373" s="2" t="inlineStr">
         <is>
@@ -8050,17 +8094,17 @@
     <row r="374">
       <c r="A374" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B374" s="3" t="n">
-        <v>46249</v>
+        <v>46237</v>
       </c>
       <c r="C374" s="4" t="n">
-        <v>0.2680555555555555</v>
+        <v>0.2618055555555556</v>
       </c>
       <c r="D374" s="4" t="n">
-        <v>0.7625</v>
+        <v>0.7472222222222222</v>
       </c>
       <c r="E374" s="2" t="inlineStr">
         <is>
@@ -8071,17 +8115,17 @@
     <row r="375">
       <c r="A375" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B375" s="3" t="n">
-        <v>46250</v>
+        <v>46238</v>
       </c>
       <c r="C375" s="4" t="n">
-        <v>0.3416666666666667</v>
+        <v>0.4965277777777778</v>
       </c>
       <c r="D375" s="4" t="n">
-        <v>0.7173611111111111</v>
+        <v>0.7506944444444444</v>
       </c>
       <c r="E375" s="2" t="inlineStr">
         <is>
@@ -8092,17 +8136,17 @@
     <row r="376">
       <c r="A376" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B376" s="3" t="n">
-        <v>46251</v>
+        <v>46239</v>
       </c>
       <c r="C376" s="4" t="n">
-        <v>0.3104166666666667</v>
+        <v>0.4743055555555555</v>
       </c>
       <c r="D376" s="4" t="n">
-        <v>0.7069444444444445</v>
+        <v>0.7722222222222223</v>
       </c>
       <c r="E376" s="2" t="inlineStr">
         <is>
@@ -8113,17 +8157,17 @@
     <row r="377">
       <c r="A377" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B377" s="3" t="n">
-        <v>46252</v>
+        <v>46240</v>
       </c>
       <c r="C377" s="4" t="n">
-        <v>0.3659722222222222</v>
+        <v>0.2409722222222222</v>
       </c>
       <c r="D377" s="4" t="n">
-        <v>0.7208333333333333</v>
+        <v>0.7625</v>
       </c>
       <c r="E377" s="2" t="inlineStr">
         <is>
@@ -8134,17 +8178,17 @@
     <row r="378">
       <c r="A378" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B378" s="3" t="n">
-        <v>46253</v>
+        <v>46242</v>
       </c>
       <c r="C378" s="4" t="n">
-        <v>0.2944444444444445</v>
+        <v>0.2201388888888889</v>
       </c>
       <c r="D378" s="4" t="n">
-        <v>0.7305555555555555</v>
+        <v>0.7618055555555555</v>
       </c>
       <c r="E378" s="2" t="inlineStr">
         <is>
@@ -8155,17 +8199,17 @@
     <row r="379">
       <c r="A379" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B379" s="3" t="n">
-        <v>46254</v>
+        <v>46243</v>
       </c>
       <c r="C379" s="4" t="n">
-        <v>0.4298611111111111</v>
+        <v>0.2395833333333333</v>
       </c>
       <c r="D379" s="4" t="n">
-        <v>0.70625</v>
+        <v>0.725</v>
       </c>
       <c r="E379" s="2" t="inlineStr">
         <is>
@@ -8176,17 +8220,17 @@
     <row r="380">
       <c r="A380" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B380" s="3" t="n">
-        <v>46256</v>
+        <v>46244</v>
       </c>
       <c r="C380" s="4" t="n">
-        <v>0.2888888888888889</v>
+        <v>0.2256944444444444</v>
       </c>
       <c r="D380" s="4" t="n">
-        <v>0.7083333333333334</v>
+        <v>0.7611111111111111</v>
       </c>
       <c r="E380" s="2" t="inlineStr">
         <is>
@@ -8197,17 +8241,17 @@
     <row r="381">
       <c r="A381" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B381" s="3" t="n">
-        <v>46257</v>
+        <v>46245</v>
       </c>
       <c r="C381" s="4" t="n">
-        <v>0.2444444444444444</v>
+        <v>0.2375</v>
       </c>
       <c r="D381" s="4" t="n">
-        <v>0.7076388888888889</v>
+        <v>0.7375</v>
       </c>
       <c r="E381" s="2" t="inlineStr">
         <is>
@@ -8218,17 +8262,17 @@
     <row r="382">
       <c r="A382" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B382" s="3" t="n">
-        <v>46258</v>
+        <v>46246</v>
       </c>
       <c r="C382" s="4" t="n">
-        <v>0.2784722222222222</v>
+        <v>0.2284722222222222</v>
       </c>
       <c r="D382" s="4" t="n">
-        <v>0.7055555555555556</v>
+        <v>0.7423611111111111</v>
       </c>
       <c r="E382" s="2" t="inlineStr">
         <is>
@@ -8239,38 +8283,40 @@
     <row r="383">
       <c r="A383" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B383" s="3" t="n">
-        <v>46259</v>
+        <v>46247</v>
       </c>
       <c r="C383" s="4" t="n">
-        <v>0.2854166666666667</v>
-      </c>
-      <c r="D383" s="4" t="n">
-        <v>0.7222222222222222</v>
+        <v>0.4402777777777778</v>
+      </c>
+      <c r="D383" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E383" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B384" s="3" t="n">
-        <v>46260</v>
+        <v>46249</v>
       </c>
       <c r="C384" s="4" t="n">
-        <v>0.2375</v>
+        <v>0.2354166666666667</v>
       </c>
       <c r="D384" s="4" t="n">
-        <v>0.7152777777777778</v>
+        <v>0.7611111111111111</v>
       </c>
       <c r="E384" s="2" t="inlineStr">
         <is>
@@ -8281,17 +8327,17 @@
     <row r="385">
       <c r="A385" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B385" s="3" t="n">
-        <v>46261</v>
+        <v>46250</v>
       </c>
       <c r="C385" s="4" t="n">
-        <v>0.4881944444444444</v>
+        <v>0.2409722222222222</v>
       </c>
       <c r="D385" s="4" t="n">
-        <v>0.7111111111111111</v>
+        <v>0.7381944444444445</v>
       </c>
       <c r="E385" s="2" t="inlineStr">
         <is>
@@ -8302,17 +8348,17 @@
     <row r="386">
       <c r="A386" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B386" s="3" t="n">
-        <v>46263</v>
+        <v>46251</v>
       </c>
       <c r="C386" s="4" t="n">
-        <v>0.2513888888888889</v>
+        <v>0.3416666666666667</v>
       </c>
       <c r="D386" s="4" t="n">
-        <v>0.7104166666666667</v>
+        <v>0.7326388888888888</v>
       </c>
       <c r="E386" s="2" t="inlineStr">
         <is>
@@ -8323,17 +8369,17 @@
     <row r="387">
       <c r="A387" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B387" s="3" t="n">
-        <v>46264</v>
+        <v>46252</v>
       </c>
       <c r="C387" s="4" t="n">
-        <v>0.2958333333333333</v>
+        <v>0.2916666666666667</v>
       </c>
       <c r="D387" s="4" t="n">
-        <v>0.7215277777777778</v>
+        <v>0.7416666666666667</v>
       </c>
       <c r="E387" s="2" t="inlineStr">
         <is>
@@ -8344,84 +8390,103 @@
     <row r="388">
       <c r="A388" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B388" s="3" t="n">
-        <v>46265</v>
-      </c>
-      <c r="C388" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>46253</v>
+      </c>
+      <c r="C388" s="4" t="n">
+        <v>0.2395833333333333</v>
       </c>
       <c r="D388" s="4" t="n">
-        <v>0.7097222222222223</v>
+        <v>0.7416666666666667</v>
       </c>
       <c r="E388" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B389" s="3" t="n">
+        <v>46254</v>
+      </c>
+      <c r="C389" s="4" t="n">
+        <v>0.2472222222222222</v>
+      </c>
+      <c r="D389" s="4" t="n">
+        <v>0.7243055555555555</v>
+      </c>
+      <c r="E389" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B390" s="3" t="n">
-        <v>46235</v>
+        <v>46256</v>
       </c>
       <c r="C390" s="4" t="n">
-        <v>0.3305555555555555</v>
-      </c>
-      <c r="D390" s="4" t="n">
-        <v>0.7347222222222223</v>
+        <v>0.2875</v>
+      </c>
+      <c r="D390" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E390" s="2" t="inlineStr">
         <is>
-          <t>last day of month; final record</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B391" s="3" t="n">
-        <v>46236</v>
-      </c>
-      <c r="C391" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>46257</v>
+      </c>
+      <c r="C391" s="4" t="n">
+        <v>0.2479166666666667</v>
       </c>
       <c r="D391" s="4" t="n">
-        <v>0.3583333333333333</v>
+        <v>0.7618055555555555</v>
       </c>
       <c r="E391" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B392" s="3" t="n">
-        <v>46237</v>
+        <v>46258</v>
       </c>
       <c r="C392" s="4" t="n">
-        <v>0.3291666666666667</v>
+        <v>0.2375</v>
       </c>
       <c r="D392" s="4" t="n">
-        <v>0.7111111111111111</v>
+        <v>0.7506944444444444</v>
       </c>
       <c r="E392" s="2" t="inlineStr">
         <is>
@@ -8432,17 +8497,17 @@
     <row r="393">
       <c r="A393" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B393" s="3" t="n">
-        <v>46238</v>
+        <v>46259</v>
       </c>
       <c r="C393" s="4" t="n">
-        <v>0.3305555555555555</v>
+        <v>0.2375</v>
       </c>
       <c r="D393" s="4" t="n">
-        <v>0.7263888888888889</v>
+        <v>0.7597222222222222</v>
       </c>
       <c r="E393" s="2" t="inlineStr">
         <is>
@@ -8453,40 +8518,38 @@
     <row r="394">
       <c r="A394" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B394" s="3" t="n">
-        <v>46239</v>
-      </c>
-      <c r="C394" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>46260</v>
+      </c>
+      <c r="C394" s="4" t="n">
+        <v>0.2479166666666667</v>
       </c>
       <c r="D394" s="4" t="n">
-        <v>0.7715277777777778</v>
+        <v>0.7555555555555555</v>
       </c>
       <c r="E394" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B395" s="3" t="n">
-        <v>46240</v>
+        <v>46261</v>
       </c>
       <c r="C395" s="4" t="n">
-        <v>0.3986111111111111</v>
+        <v>0.2493055555555556</v>
       </c>
       <c r="D395" s="4" t="n">
-        <v>0.7277777777777777</v>
+        <v>0.7944444444444444</v>
       </c>
       <c r="E395" s="2" t="inlineStr">
         <is>
@@ -8497,59 +8560,61 @@
     <row r="396">
       <c r="A396" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B396" s="3" t="n">
-        <v>46242</v>
+        <v>46262</v>
       </c>
       <c r="C396" s="4" t="n">
-        <v>0.2791666666666667</v>
-      </c>
-      <c r="D396" s="4" t="n">
-        <v>0.7284722222222222</v>
+        <v>0.25</v>
+      </c>
+      <c r="D396" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E396" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B397" s="3" t="n">
-        <v>46243</v>
+        <v>46263</v>
       </c>
       <c r="C397" s="4" t="n">
-        <v>0.2784722222222222</v>
+        <v>0.2569444444444444</v>
       </c>
       <c r="D397" s="4" t="n">
-        <v>0.7555555555555555</v>
+        <v>0.7458333333333333</v>
       </c>
       <c r="E397" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>extra punch: 17:53</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B398" s="3" t="n">
-        <v>46244</v>
+        <v>46264</v>
       </c>
       <c r="C398" s="4" t="n">
-        <v>0.2875</v>
+        <v>0.2590277777777778</v>
       </c>
       <c r="D398" s="4" t="n">
-        <v>0.7479166666666667</v>
+        <v>0.7541666666666667</v>
       </c>
       <c r="E398" s="2" t="inlineStr">
         <is>
@@ -8560,101 +8625,80 @@
     <row r="399">
       <c r="A399" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B399" s="3" t="n">
-        <v>46245</v>
+        <v>46265</v>
       </c>
       <c r="C399" s="4" t="n">
-        <v>0.3</v>
+        <v>0.2777777777777778</v>
       </c>
       <c r="D399" s="4" t="n">
-        <v>0.7465277777777778</v>
+        <v>0.7513888888888889</v>
       </c>
       <c r="E399" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="400">
-      <c r="A400" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="B400" s="3" t="n">
-        <v>46246</v>
-      </c>
-      <c r="C400" s="4" t="n">
-        <v>0.2548611111111111</v>
-      </c>
-      <c r="D400" s="4" t="n">
-        <v>0.7222222222222222</v>
-      </c>
-      <c r="E400" s="2" t="inlineStr">
-        <is>
-          <t>extra punches: 07:44 06:16</t>
+          <t>corrected from a clearer re-scan photo later in the album</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B401" s="3" t="n">
-        <v>46247</v>
+        <v>46235</v>
       </c>
       <c r="C401" s="4" t="n">
-        <v>0.3388888888888889</v>
+        <v>0.2451388888888889</v>
       </c>
       <c r="D401" s="4" t="n">
-        <v>0.7236111111111111</v>
+        <v>0.7506944444444444</v>
       </c>
       <c r="E401" s="2" t="inlineStr">
         <is>
-          <t>extra punch: 17:21</t>
+          <t>last day of month; final record</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B402" s="3" t="n">
-        <v>46249</v>
+        <v>46236</v>
       </c>
       <c r="C402" s="4" t="n">
-        <v>0.2423611111111111</v>
+        <v>0.24375</v>
       </c>
       <c r="D402" s="4" t="n">
-        <v>0.7270833333333333</v>
+        <v>0.7520833333333333</v>
       </c>
       <c r="E402" s="2" t="inlineStr">
         <is>
-          <t>extra punches: 17:27 07:28</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B403" s="3" t="n">
-        <v>46250</v>
+        <v>46237</v>
       </c>
       <c r="C403" s="4" t="n">
-        <v>0.3409722222222222</v>
+        <v>0.24375</v>
       </c>
       <c r="D403" s="4" t="n">
-        <v>0.7104166666666667</v>
+        <v>0.7527777777777778</v>
       </c>
       <c r="E403" s="2" t="inlineStr">
         <is>
@@ -8665,17 +8709,17 @@
     <row r="404">
       <c r="A404" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B404" s="3" t="n">
-        <v>46251</v>
+        <v>46238</v>
       </c>
       <c r="C404" s="4" t="n">
-        <v>0.2833333333333333</v>
+        <v>0.2451388888888889</v>
       </c>
       <c r="D404" s="4" t="n">
-        <v>0.7326388888888888</v>
+        <v>0.7520833333333333</v>
       </c>
       <c r="E404" s="2" t="inlineStr">
         <is>
@@ -8686,17 +8730,17 @@
     <row r="405">
       <c r="A405" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B405" s="3" t="n">
-        <v>46252</v>
+        <v>46239</v>
       </c>
       <c r="C405" s="4" t="n">
-        <v>0.28125</v>
+        <v>0.2368055555555555</v>
       </c>
       <c r="D405" s="4" t="n">
-        <v>0.7645833333333333</v>
+        <v>0.7611111111111111</v>
       </c>
       <c r="E405" s="2" t="inlineStr">
         <is>
@@ -8707,84 +8751,84 @@
     <row r="406">
       <c r="A406" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B406" s="3" t="n">
-        <v>46253</v>
+        <v>46240</v>
       </c>
       <c r="C406" s="4" t="n">
-        <v>0.3166666666666667</v>
+        <v>0.2402777777777778</v>
       </c>
       <c r="D406" s="4" t="n">
-        <v>0.74375</v>
+        <v>0.7513888888888889</v>
       </c>
       <c r="E406" s="2" t="inlineStr">
         <is>
-          <t>extra punch: 08:01</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B407" s="3" t="n">
-        <v>46254</v>
+        <v>46242</v>
       </c>
       <c r="C407" s="4" t="n">
-        <v>0.2868055555555555</v>
-      </c>
-      <c r="D407" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.2430555555555556</v>
+      </c>
+      <c r="D407" s="4" t="n">
+        <v>0.7548611111111111</v>
       </c>
       <c r="E407" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B408" s="3" t="n">
-        <v>46256</v>
+        <v>46246</v>
       </c>
       <c r="C408" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D408" s="4" t="n">
-        <v>0.74375</v>
+      <c r="D408" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E408" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>PLEASE VERIFY: check-in/out times not captured (gap between source photos)</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B409" s="3" t="n">
-        <v>46257</v>
+        <v>46247</v>
       </c>
       <c r="C409" s="4" t="n">
-        <v>0.2548611111111111</v>
+        <v>0.2444444444444444</v>
       </c>
       <c r="D409" s="4" t="n">
-        <v>0.7569444444444444</v>
+        <v>0.7576388888888889</v>
       </c>
       <c r="E409" s="2" t="inlineStr">
         <is>
@@ -8795,40 +8839,38 @@
     <row r="410">
       <c r="A410" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B410" s="3" t="n">
-        <v>46258</v>
-      </c>
-      <c r="C410" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>46249</v>
+      </c>
+      <c r="C410" s="4" t="n">
+        <v>0.2381944444444444</v>
       </c>
       <c r="D410" s="4" t="n">
-        <v>0.7506944444444444</v>
+        <v>0.7513888888888889</v>
       </c>
       <c r="E410" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B411" s="3" t="n">
-        <v>46259</v>
+        <v>46250</v>
       </c>
       <c r="C411" s="4" t="n">
-        <v>0.2868055555555555</v>
+        <v>0.2354166666666667</v>
       </c>
       <c r="D411" s="4" t="n">
-        <v>0.6895833333333333</v>
+        <v>0.7520833333333333</v>
       </c>
       <c r="E411" s="2" t="inlineStr">
         <is>
@@ -8839,40 +8881,38 @@
     <row r="412">
       <c r="A412" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B412" s="3" t="n">
-        <v>46260</v>
-      </c>
-      <c r="C412" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>46251</v>
+      </c>
+      <c r="C412" s="4" t="n">
+        <v>0.2395833333333333</v>
       </c>
       <c r="D412" s="4" t="n">
-        <v>0.6986111111111111</v>
+        <v>0.7541666666666667</v>
       </c>
       <c r="E412" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B413" s="3" t="n">
-        <v>46261</v>
+        <v>46252</v>
       </c>
       <c r="C413" s="4" t="n">
-        <v>0.2833333333333333</v>
+        <v>0.2451388888888889</v>
       </c>
       <c r="D413" s="4" t="n">
-        <v>0.8645833333333334</v>
+        <v>0.7527777777777778</v>
       </c>
       <c r="E413" s="2" t="inlineStr">
         <is>
@@ -8883,40 +8923,38 @@
     <row r="414">
       <c r="A414" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B414" s="3" t="n">
-        <v>46263</v>
-      </c>
-      <c r="C414" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>46253</v>
+      </c>
+      <c r="C414" s="4" t="n">
+        <v>0.2423611111111111</v>
       </c>
       <c r="D414" s="4" t="n">
-        <v>0.7291666666666666</v>
+        <v>0.7506944444444444</v>
       </c>
       <c r="E414" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B415" s="3" t="n">
-        <v>46264</v>
+        <v>46254</v>
       </c>
       <c r="C415" s="4" t="n">
-        <v>0.2798611111111111</v>
+        <v>0.2402777777777778</v>
       </c>
       <c r="D415" s="4" t="n">
-        <v>0.7472222222222222</v>
+        <v>0.7520833333333333</v>
       </c>
       <c r="E415" s="2" t="inlineStr">
         <is>
@@ -8927,59 +8965,80 @@
     <row r="416">
       <c r="A416" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B416" s="3" t="n">
-        <v>46265</v>
+        <v>46256</v>
       </c>
       <c r="C416" s="4" t="n">
-        <v>0.3888888888888889</v>
+        <v>0.2402777777777778</v>
       </c>
       <c r="D416" s="4" t="n">
-        <v>0.7215277777777778</v>
+        <v>0.75</v>
       </c>
       <c r="E416" s="2" t="inlineStr">
         <is>
-          <t>corrected from a clearer re-scan photo later in the album</t>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B417" s="3" t="n">
+        <v>46257</v>
+      </c>
+      <c r="C417" s="4" t="n">
+        <v>0.2458333333333333</v>
+      </c>
+      <c r="D417" s="4" t="n">
+        <v>0.7527777777777778</v>
+      </c>
+      <c r="E417" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B418" s="3" t="n">
-        <v>46235</v>
+        <v>46258</v>
       </c>
       <c r="C418" s="4" t="n">
-        <v>0.2569444444444444</v>
+        <v>0.2347222222222222</v>
       </c>
       <c r="D418" s="4" t="n">
-        <v>0.7430555555555556</v>
+        <v>0.7520833333333333</v>
       </c>
       <c r="E418" s="2" t="inlineStr">
         <is>
-          <t>extra punch: 17:55; last day of month; final record</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B419" s="3" t="n">
-        <v>46236</v>
+        <v>46259</v>
       </c>
       <c r="C419" s="4" t="n">
-        <v>0.2201388888888889</v>
+        <v>0.2368055555555555</v>
       </c>
       <c r="D419" s="4" t="n">
-        <v>0.7381944444444445</v>
+        <v>0.7506944444444444</v>
       </c>
       <c r="E419" s="2" t="inlineStr">
         <is>
@@ -8990,38 +9049,38 @@
     <row r="420">
       <c r="A420" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B420" s="3" t="n">
-        <v>46237</v>
+        <v>46260</v>
       </c>
       <c r="C420" s="4" t="n">
-        <v>0.2472222222222222</v>
+        <v>0.2465277777777778</v>
       </c>
       <c r="D420" s="4" t="n">
-        <v>0.7402777777777778</v>
+        <v>0.7555555555555555</v>
       </c>
       <c r="E420" s="2" t="inlineStr">
         <is>
-          <t>extra punch: 17:46</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B421" s="3" t="n">
-        <v>46238</v>
+        <v>46261</v>
       </c>
       <c r="C421" s="4" t="n">
-        <v>0.2173611111111111</v>
+        <v>0.2472222222222222</v>
       </c>
       <c r="D421" s="4" t="n">
-        <v>0.7604166666666666</v>
+        <v>0.7513888888888889</v>
       </c>
       <c r="E421" s="2" t="inlineStr">
         <is>
@@ -9032,38 +9091,38 @@
     <row r="422">
       <c r="A422" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B422" s="3" t="n">
-        <v>46239</v>
+        <v>46263</v>
       </c>
       <c r="C422" s="4" t="n">
-        <v>0.2333333333333333</v>
+        <v>0.2444444444444444</v>
       </c>
       <c r="D422" s="4" t="n">
-        <v>0.7611111111111111</v>
+        <v>0.7548611111111111</v>
       </c>
       <c r="E422" s="2" t="inlineStr">
         <is>
-          <t>extra punch: 18:16</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B423" s="3" t="n">
-        <v>46240</v>
+        <v>46264</v>
       </c>
       <c r="C423" s="4" t="n">
-        <v>0.2277777777777778</v>
+        <v>0.2423611111111111</v>
       </c>
       <c r="D423" s="4" t="n">
-        <v>0.75625</v>
+        <v>0.7513888888888889</v>
       </c>
       <c r="E423" s="2" t="inlineStr">
         <is>
@@ -9074,80 +9133,59 @@
     <row r="424">
       <c r="A424" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B424" s="3" t="n">
-        <v>46242</v>
+        <v>46265</v>
       </c>
       <c r="C424" s="4" t="n">
-        <v>0.2479166666666667</v>
+        <v>0.2361111111111111</v>
       </c>
       <c r="D424" s="4" t="n">
-        <v>0.7291666666666666</v>
+        <v>0.7520833333333333</v>
       </c>
       <c r="E424" s="2" t="inlineStr">
         <is>
-          <t>extra punch: 07:09</t>
-        </is>
-      </c>
-    </row>
-    <row r="425">
-      <c r="A425" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="B425" s="3" t="n">
-        <v>46243</v>
-      </c>
-      <c r="C425" s="4" t="n">
-        <v>0.2368055555555555</v>
-      </c>
-      <c r="D425" s="4" t="n">
-        <v>0.6729166666666667</v>
-      </c>
-      <c r="E425" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>corrected from a clearer re-scan photo later in the album</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B426" s="3" t="n">
-        <v>46244</v>
+        <v>46235</v>
       </c>
       <c r="C426" s="4" t="n">
-        <v>0.2534722222222222</v>
+        <v>0.275</v>
       </c>
       <c r="D426" s="4" t="n">
-        <v>0.7479166666666667</v>
+        <v>0.7854166666666667</v>
       </c>
       <c r="E426" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>last day of month; final record</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B427" s="3" t="n">
-        <v>46245</v>
+        <v>46236</v>
       </c>
       <c r="C427" s="4" t="n">
-        <v>0.2541666666666667</v>
+        <v>0.2722222222222222</v>
       </c>
       <c r="D427" s="4" t="n">
-        <v>0.7465277777777778</v>
+        <v>0.7722222222222223</v>
       </c>
       <c r="E427" s="2" t="inlineStr">
         <is>
@@ -9158,17 +9196,17 @@
     <row r="428">
       <c r="A428" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B428" s="3" t="n">
-        <v>46246</v>
+        <v>46237</v>
       </c>
       <c r="C428" s="4" t="n">
-        <v>0.2618055555555556</v>
+        <v>0.2451388888888889</v>
       </c>
       <c r="D428" s="4" t="n">
-        <v>0.75</v>
+        <v>0.7201388888888889</v>
       </c>
       <c r="E428" s="2" t="inlineStr">
         <is>
@@ -9179,17 +9217,17 @@
     <row r="429">
       <c r="A429" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B429" s="3" t="n">
-        <v>46247</v>
+        <v>46238</v>
       </c>
       <c r="C429" s="4" t="n">
-        <v>0.25625</v>
+        <v>0.2729166666666666</v>
       </c>
       <c r="D429" s="4" t="n">
-        <v>0.75</v>
+        <v>0.7527777777777778</v>
       </c>
       <c r="E429" s="2" t="inlineStr">
         <is>
@@ -9200,59 +9238,61 @@
     <row r="430">
       <c r="A430" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B430" s="3" t="n">
-        <v>46249</v>
+        <v>46239</v>
       </c>
       <c r="C430" s="4" t="n">
-        <v>0.2333333333333333</v>
+        <v>0.2756944444444445</v>
       </c>
       <c r="D430" s="4" t="n">
-        <v>0.7506944444444444</v>
+        <v>0.7152777777777778</v>
       </c>
       <c r="E430" s="2" t="inlineStr">
         <is>
-          <t>extra punch: 06:05</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B431" s="3" t="n">
-        <v>46250</v>
+        <v>46240</v>
       </c>
       <c r="C431" s="4" t="n">
-        <v>0.25625</v>
-      </c>
-      <c r="D431" s="4" t="n">
-        <v>0.7458333333333333</v>
+        <v>0.2715277777777778</v>
+      </c>
+      <c r="D431" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E431" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B432" s="3" t="n">
-        <v>46251</v>
+        <v>46242</v>
       </c>
       <c r="C432" s="4" t="n">
-        <v>0.2541666666666667</v>
+        <v>0.2388888888888889</v>
       </c>
       <c r="D432" s="4" t="n">
-        <v>0.7555555555555555</v>
+        <v>0.6965277777777777</v>
       </c>
       <c r="E432" s="2" t="inlineStr">
         <is>
@@ -9263,17 +9303,17 @@
     <row r="433">
       <c r="A433" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B433" s="3" t="n">
-        <v>46252</v>
+        <v>46243</v>
       </c>
       <c r="C433" s="4" t="n">
-        <v>0.2395833333333333</v>
+        <v>0.2451388888888889</v>
       </c>
       <c r="D433" s="4" t="n">
-        <v>0.7611111111111111</v>
+        <v>0.7694444444444445</v>
       </c>
       <c r="E433" s="2" t="inlineStr">
         <is>
@@ -9284,38 +9324,38 @@
     <row r="434">
       <c r="A434" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B434" s="3" t="n">
-        <v>46253</v>
+        <v>46244</v>
       </c>
       <c r="C434" s="4" t="n">
-        <v>0.2527777777777778</v>
+        <v>0.2298611111111111</v>
       </c>
       <c r="D434" s="4" t="n">
-        <v>0.7423611111111111</v>
+        <v>0.75625</v>
       </c>
       <c r="E434" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>extra punch: 06:48</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B435" s="3" t="n">
-        <v>46254</v>
+        <v>46245</v>
       </c>
       <c r="C435" s="4" t="n">
-        <v>0.2583333333333334</v>
+        <v>0.275</v>
       </c>
       <c r="D435" s="4" t="n">
-        <v>0.7451388888888889</v>
+        <v>0.7618055555555555</v>
       </c>
       <c r="E435" s="2" t="inlineStr">
         <is>
@@ -9326,38 +9366,38 @@
     <row r="436">
       <c r="A436" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B436" s="3" t="n">
-        <v>46256</v>
+        <v>46246</v>
       </c>
       <c r="C436" s="4" t="n">
-        <v>0.2402777777777778</v>
+        <v>0.2694444444444444</v>
       </c>
       <c r="D436" s="4" t="n">
-        <v>0.74375</v>
+        <v>0.7222222222222222</v>
       </c>
       <c r="E436" s="2" t="inlineStr">
         <is>
-          <t>extra punches: 17:51 06:13</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B437" s="3" t="n">
-        <v>46257</v>
+        <v>46247</v>
       </c>
       <c r="C437" s="4" t="n">
-        <v>0.2402777777777778</v>
+        <v>0.3409722222222222</v>
       </c>
       <c r="D437" s="4" t="n">
-        <v>0.75</v>
+        <v>0.7583333333333333</v>
       </c>
       <c r="E437" s="2" t="inlineStr">
         <is>
@@ -9368,59 +9408,59 @@
     <row r="438">
       <c r="A438" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B438" s="3" t="n">
-        <v>46258</v>
+        <v>46249</v>
       </c>
       <c r="C438" s="4" t="n">
-        <v>0.2319444444444445</v>
+        <v>0.2680555555555555</v>
       </c>
       <c r="D438" s="4" t="n">
-        <v>0.7513888888888889</v>
+        <v>0.7625</v>
       </c>
       <c r="E438" s="2" t="inlineStr">
         <is>
-          <t>extra punch: 18:02</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B439" s="3" t="n">
-        <v>46259</v>
+        <v>46250</v>
       </c>
       <c r="C439" s="4" t="n">
-        <v>0.3555555555555556</v>
+        <v>0.3416666666666667</v>
       </c>
       <c r="D439" s="4" t="n">
-        <v>0.7541666666666667</v>
+        <v>0.7173611111111111</v>
       </c>
       <c r="E439" s="2" t="inlineStr">
         <is>
-          <t>extra punch: 06:33</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B440" s="3" t="n">
-        <v>46260</v>
+        <v>46251</v>
       </c>
       <c r="C440" s="4" t="n">
-        <v>0.2555555555555555</v>
+        <v>0.3104166666666667</v>
       </c>
       <c r="D440" s="4" t="n">
-        <v>0.7541666666666667</v>
+        <v>0.7069444444444445</v>
       </c>
       <c r="E440" s="2" t="inlineStr">
         <is>
@@ -9431,17 +9471,17 @@
     <row r="441">
       <c r="A441" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B441" s="3" t="n">
-        <v>46261</v>
+        <v>46252</v>
       </c>
       <c r="C441" s="4" t="n">
-        <v>0.2722222222222222</v>
+        <v>0.3659722222222222</v>
       </c>
       <c r="D441" s="4" t="n">
-        <v>0.7569444444444444</v>
+        <v>0.7208333333333333</v>
       </c>
       <c r="E441" s="2" t="inlineStr">
         <is>
@@ -9452,17 +9492,17 @@
     <row r="442">
       <c r="A442" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B442" s="3" t="n">
-        <v>46263</v>
+        <v>46253</v>
       </c>
       <c r="C442" s="4" t="n">
-        <v>0.2201388888888889</v>
+        <v>0.2944444444444445</v>
       </c>
       <c r="D442" s="4" t="n">
-        <v>0.7444444444444445</v>
+        <v>0.7305555555555555</v>
       </c>
       <c r="E442" s="2" t="inlineStr">
         <is>
@@ -9473,17 +9513,17 @@
     <row r="443">
       <c r="A443" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B443" s="3" t="n">
-        <v>46264</v>
+        <v>46254</v>
       </c>
       <c r="C443" s="4" t="n">
-        <v>0.2555555555555555</v>
+        <v>0.4298611111111111</v>
       </c>
       <c r="D443" s="4" t="n">
-        <v>0.7458333333333333</v>
+        <v>0.70625</v>
       </c>
       <c r="E443" s="2" t="inlineStr">
         <is>
@@ -9494,19 +9534,1337 @@
     <row r="444">
       <c r="A444" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B444" s="3" t="n">
+        <v>46256</v>
+      </c>
+      <c r="C444" s="4" t="n">
+        <v>0.2888888888888889</v>
+      </c>
+      <c r="D444" s="4" t="n">
+        <v>0.7083333333333334</v>
+      </c>
+      <c r="E444" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B445" s="3" t="n">
+        <v>46257</v>
+      </c>
+      <c r="C445" s="4" t="n">
+        <v>0.2444444444444444</v>
+      </c>
+      <c r="D445" s="4" t="n">
+        <v>0.7076388888888889</v>
+      </c>
+      <c r="E445" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B446" s="3" t="n">
+        <v>46258</v>
+      </c>
+      <c r="C446" s="4" t="n">
+        <v>0.2784722222222222</v>
+      </c>
+      <c r="D446" s="4" t="n">
+        <v>0.7055555555555556</v>
+      </c>
+      <c r="E446" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B447" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="C447" s="4" t="n">
+        <v>0.2854166666666667</v>
+      </c>
+      <c r="D447" s="4" t="n">
+        <v>0.7222222222222222</v>
+      </c>
+      <c r="E447" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B448" s="3" t="n">
+        <v>46260</v>
+      </c>
+      <c r="C448" s="4" t="n">
+        <v>0.2375</v>
+      </c>
+      <c r="D448" s="4" t="n">
+        <v>0.7152777777777778</v>
+      </c>
+      <c r="E448" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B449" s="3" t="n">
+        <v>46261</v>
+      </c>
+      <c r="C449" s="4" t="n">
+        <v>0.4881944444444444</v>
+      </c>
+      <c r="D449" s="4" t="n">
+        <v>0.7111111111111111</v>
+      </c>
+      <c r="E449" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B450" s="3" t="n">
+        <v>46263</v>
+      </c>
+      <c r="C450" s="4" t="n">
+        <v>0.2513888888888889</v>
+      </c>
+      <c r="D450" s="4" t="n">
+        <v>0.7104166666666667</v>
+      </c>
+      <c r="E450" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B451" s="3" t="n">
+        <v>46264</v>
+      </c>
+      <c r="C451" s="4" t="n">
+        <v>0.2958333333333333</v>
+      </c>
+      <c r="D451" s="4" t="n">
+        <v>0.7215277777777778</v>
+      </c>
+      <c r="E451" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B452" s="3" t="n">
+        <v>46265</v>
+      </c>
+      <c r="C452" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D452" s="4" t="n">
+        <v>0.7097222222222223</v>
+      </c>
+      <c r="E452" s="2" t="inlineStr">
+        <is>
+          <t>single punch only</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B454" s="3" t="n">
+        <v>46235</v>
+      </c>
+      <c r="C454" s="4" t="n">
+        <v>0.3305555555555555</v>
+      </c>
+      <c r="D454" s="4" t="n">
+        <v>0.7347222222222223</v>
+      </c>
+      <c r="E454" s="2" t="inlineStr">
+        <is>
+          <t>last day of month; final record</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B455" s="3" t="n">
+        <v>46236</v>
+      </c>
+      <c r="C455" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D455" s="4" t="n">
+        <v>0.3583333333333333</v>
+      </c>
+      <c r="E455" s="2" t="inlineStr">
+        <is>
+          <t>single punch only</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B456" s="3" t="n">
+        <v>46237</v>
+      </c>
+      <c r="C456" s="4" t="n">
+        <v>0.3291666666666667</v>
+      </c>
+      <c r="D456" s="4" t="n">
+        <v>0.7111111111111111</v>
+      </c>
+      <c r="E456" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B457" s="3" t="n">
+        <v>46238</v>
+      </c>
+      <c r="C457" s="4" t="n">
+        <v>0.3305555555555555</v>
+      </c>
+      <c r="D457" s="4" t="n">
+        <v>0.7263888888888889</v>
+      </c>
+      <c r="E457" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B458" s="3" t="n">
+        <v>46239</v>
+      </c>
+      <c r="C458" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D458" s="4" t="n">
+        <v>0.7715277777777778</v>
+      </c>
+      <c r="E458" s="2" t="inlineStr">
+        <is>
+          <t>single punch only</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B459" s="3" t="n">
+        <v>46240</v>
+      </c>
+      <c r="C459" s="4" t="n">
+        <v>0.3986111111111111</v>
+      </c>
+      <c r="D459" s="4" t="n">
+        <v>0.7277777777777777</v>
+      </c>
+      <c r="E459" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B460" s="3" t="n">
+        <v>46242</v>
+      </c>
+      <c r="C460" s="4" t="n">
+        <v>0.2791666666666667</v>
+      </c>
+      <c r="D460" s="4" t="n">
+        <v>0.7284722222222222</v>
+      </c>
+      <c r="E460" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B461" s="3" t="n">
+        <v>46243</v>
+      </c>
+      <c r="C461" s="4" t="n">
+        <v>0.2784722222222222</v>
+      </c>
+      <c r="D461" s="4" t="n">
+        <v>0.7555555555555555</v>
+      </c>
+      <c r="E461" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B462" s="3" t="n">
+        <v>46244</v>
+      </c>
+      <c r="C462" s="4" t="n">
+        <v>0.2875</v>
+      </c>
+      <c r="D462" s="4" t="n">
+        <v>0.7479166666666667</v>
+      </c>
+      <c r="E462" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B463" s="3" t="n">
+        <v>46245</v>
+      </c>
+      <c r="C463" s="4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D463" s="4" t="n">
+        <v>0.7465277777777778</v>
+      </c>
+      <c r="E463" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B464" s="3" t="n">
+        <v>46246</v>
+      </c>
+      <c r="C464" s="4" t="n">
+        <v>0.2548611111111111</v>
+      </c>
+      <c r="D464" s="4" t="n">
+        <v>0.7222222222222222</v>
+      </c>
+      <c r="E464" s="2" t="inlineStr">
+        <is>
+          <t>extra punches: 07:44 06:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B465" s="3" t="n">
+        <v>46247</v>
+      </c>
+      <c r="C465" s="4" t="n">
+        <v>0.3388888888888889</v>
+      </c>
+      <c r="D465" s="4" t="n">
+        <v>0.7236111111111111</v>
+      </c>
+      <c r="E465" s="2" t="inlineStr">
+        <is>
+          <t>extra punch: 17:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B466" s="3" t="n">
+        <v>46249</v>
+      </c>
+      <c r="C466" s="4" t="n">
+        <v>0.2423611111111111</v>
+      </c>
+      <c r="D466" s="4" t="n">
+        <v>0.7270833333333333</v>
+      </c>
+      <c r="E466" s="2" t="inlineStr">
+        <is>
+          <t>extra punches: 17:27 07:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B467" s="3" t="n">
+        <v>46250</v>
+      </c>
+      <c r="C467" s="4" t="n">
+        <v>0.3409722222222222</v>
+      </c>
+      <c r="D467" s="4" t="n">
+        <v>0.7104166666666667</v>
+      </c>
+      <c r="E467" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B468" s="3" t="n">
+        <v>46251</v>
+      </c>
+      <c r="C468" s="4" t="n">
+        <v>0.2833333333333333</v>
+      </c>
+      <c r="D468" s="4" t="n">
+        <v>0.7326388888888888</v>
+      </c>
+      <c r="E468" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B469" s="3" t="n">
+        <v>46252</v>
+      </c>
+      <c r="C469" s="4" t="n">
+        <v>0.28125</v>
+      </c>
+      <c r="D469" s="4" t="n">
+        <v>0.7645833333333333</v>
+      </c>
+      <c r="E469" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B470" s="3" t="n">
+        <v>46253</v>
+      </c>
+      <c r="C470" s="4" t="n">
+        <v>0.3166666666666667</v>
+      </c>
+      <c r="D470" s="4" t="n">
+        <v>0.74375</v>
+      </c>
+      <c r="E470" s="2" t="inlineStr">
+        <is>
+          <t>extra punch: 08:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B471" s="3" t="n">
+        <v>46254</v>
+      </c>
+      <c r="C471" s="4" t="n">
+        <v>0.2868055555555555</v>
+      </c>
+      <c r="D471" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E471" s="2" t="inlineStr">
+        <is>
+          <t>single punch only</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B472" s="3" t="n">
+        <v>46256</v>
+      </c>
+      <c r="C472" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D472" s="4" t="n">
+        <v>0.74375</v>
+      </c>
+      <c r="E472" s="2" t="inlineStr">
+        <is>
+          <t>single punch only</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B473" s="3" t="n">
+        <v>46257</v>
+      </c>
+      <c r="C473" s="4" t="n">
+        <v>0.2548611111111111</v>
+      </c>
+      <c r="D473" s="4" t="n">
+        <v>0.7569444444444444</v>
+      </c>
+      <c r="E473" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B474" s="3" t="n">
+        <v>46258</v>
+      </c>
+      <c r="C474" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D474" s="4" t="n">
+        <v>0.7506944444444444</v>
+      </c>
+      <c r="E474" s="2" t="inlineStr">
+        <is>
+          <t>single punch only</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B475" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="C475" s="4" t="n">
+        <v>0.2868055555555555</v>
+      </c>
+      <c r="D475" s="4" t="n">
+        <v>0.6895833333333333</v>
+      </c>
+      <c r="E475" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B476" s="3" t="n">
+        <v>46260</v>
+      </c>
+      <c r="C476" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D476" s="4" t="n">
+        <v>0.6986111111111111</v>
+      </c>
+      <c r="E476" s="2" t="inlineStr">
+        <is>
+          <t>single punch only</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B477" s="3" t="n">
+        <v>46261</v>
+      </c>
+      <c r="C477" s="4" t="n">
+        <v>0.2833333333333333</v>
+      </c>
+      <c r="D477" s="4" t="n">
+        <v>0.8645833333333334</v>
+      </c>
+      <c r="E477" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B478" s="3" t="n">
+        <v>46263</v>
+      </c>
+      <c r="C478" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D478" s="4" t="n">
+        <v>0.7291666666666666</v>
+      </c>
+      <c r="E478" s="2" t="inlineStr">
+        <is>
+          <t>single punch only</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B479" s="3" t="n">
+        <v>46264</v>
+      </c>
+      <c r="C479" s="4" t="n">
+        <v>0.2798611111111111</v>
+      </c>
+      <c r="D479" s="4" t="n">
+        <v>0.7472222222222222</v>
+      </c>
+      <c r="E479" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B480" s="3" t="n">
+        <v>46265</v>
+      </c>
+      <c r="C480" s="4" t="n">
+        <v>0.3888888888888889</v>
+      </c>
+      <c r="D480" s="4" t="n">
+        <v>0.7215277777777778</v>
+      </c>
+      <c r="E480" s="2" t="inlineStr">
+        <is>
+          <t>corrected from a clearer re-scan photo later in the album</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="B444" s="3" t="n">
+      <c r="B482" s="3" t="n">
+        <v>46235</v>
+      </c>
+      <c r="C482" s="4" t="n">
+        <v>0.2569444444444444</v>
+      </c>
+      <c r="D482" s="4" t="n">
+        <v>0.7430555555555556</v>
+      </c>
+      <c r="E482" s="2" t="inlineStr">
+        <is>
+          <t>extra punch: 17:55; last day of month; final record</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B483" s="3" t="n">
+        <v>46236</v>
+      </c>
+      <c r="C483" s="4" t="n">
+        <v>0.2201388888888889</v>
+      </c>
+      <c r="D483" s="4" t="n">
+        <v>0.7381944444444445</v>
+      </c>
+      <c r="E483" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B484" s="3" t="n">
+        <v>46237</v>
+      </c>
+      <c r="C484" s="4" t="n">
+        <v>0.2472222222222222</v>
+      </c>
+      <c r="D484" s="4" t="n">
+        <v>0.7402777777777778</v>
+      </c>
+      <c r="E484" s="2" t="inlineStr">
+        <is>
+          <t>extra punch: 17:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B485" s="3" t="n">
+        <v>46238</v>
+      </c>
+      <c r="C485" s="4" t="n">
+        <v>0.2173611111111111</v>
+      </c>
+      <c r="D485" s="4" t="n">
+        <v>0.7604166666666666</v>
+      </c>
+      <c r="E485" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B486" s="3" t="n">
+        <v>46239</v>
+      </c>
+      <c r="C486" s="4" t="n">
+        <v>0.2333333333333333</v>
+      </c>
+      <c r="D486" s="4" t="n">
+        <v>0.7611111111111111</v>
+      </c>
+      <c r="E486" s="2" t="inlineStr">
+        <is>
+          <t>extra punch: 18:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B487" s="3" t="n">
+        <v>46240</v>
+      </c>
+      <c r="C487" s="4" t="n">
+        <v>0.2277777777777778</v>
+      </c>
+      <c r="D487" s="4" t="n">
+        <v>0.75625</v>
+      </c>
+      <c r="E487" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B488" s="3" t="n">
+        <v>46242</v>
+      </c>
+      <c r="C488" s="4" t="n">
+        <v>0.2479166666666667</v>
+      </c>
+      <c r="D488" s="4" t="n">
+        <v>0.7291666666666666</v>
+      </c>
+      <c r="E488" s="2" t="inlineStr">
+        <is>
+          <t>extra punch: 07:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B489" s="3" t="n">
+        <v>46243</v>
+      </c>
+      <c r="C489" s="4" t="n">
+        <v>0.2368055555555555</v>
+      </c>
+      <c r="D489" s="4" t="n">
+        <v>0.6729166666666667</v>
+      </c>
+      <c r="E489" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B490" s="3" t="n">
+        <v>46244</v>
+      </c>
+      <c r="C490" s="4" t="n">
+        <v>0.2534722222222222</v>
+      </c>
+      <c r="D490" s="4" t="n">
+        <v>0.7479166666666667</v>
+      </c>
+      <c r="E490" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B491" s="3" t="n">
+        <v>46245</v>
+      </c>
+      <c r="C491" s="4" t="n">
+        <v>0.2541666666666667</v>
+      </c>
+      <c r="D491" s="4" t="n">
+        <v>0.7465277777777778</v>
+      </c>
+      <c r="E491" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B492" s="3" t="n">
+        <v>46246</v>
+      </c>
+      <c r="C492" s="4" t="n">
+        <v>0.2618055555555556</v>
+      </c>
+      <c r="D492" s="4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E492" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B493" s="3" t="n">
+        <v>46247</v>
+      </c>
+      <c r="C493" s="4" t="n">
+        <v>0.25625</v>
+      </c>
+      <c r="D493" s="4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E493" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B494" s="3" t="n">
+        <v>46249</v>
+      </c>
+      <c r="C494" s="4" t="n">
+        <v>0.2333333333333333</v>
+      </c>
+      <c r="D494" s="4" t="n">
+        <v>0.7506944444444444</v>
+      </c>
+      <c r="E494" s="2" t="inlineStr">
+        <is>
+          <t>extra punch: 06:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B495" s="3" t="n">
+        <v>46250</v>
+      </c>
+      <c r="C495" s="4" t="n">
+        <v>0.25625</v>
+      </c>
+      <c r="D495" s="4" t="n">
+        <v>0.7458333333333333</v>
+      </c>
+      <c r="E495" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B496" s="3" t="n">
+        <v>46251</v>
+      </c>
+      <c r="C496" s="4" t="n">
+        <v>0.2541666666666667</v>
+      </c>
+      <c r="D496" s="4" t="n">
+        <v>0.7555555555555555</v>
+      </c>
+      <c r="E496" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B497" s="3" t="n">
+        <v>46252</v>
+      </c>
+      <c r="C497" s="4" t="n">
+        <v>0.2395833333333333</v>
+      </c>
+      <c r="D497" s="4" t="n">
+        <v>0.7611111111111111</v>
+      </c>
+      <c r="E497" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B498" s="3" t="n">
+        <v>46253</v>
+      </c>
+      <c r="C498" s="4" t="n">
+        <v>0.2527777777777778</v>
+      </c>
+      <c r="D498" s="4" t="n">
+        <v>0.7423611111111111</v>
+      </c>
+      <c r="E498" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B499" s="3" t="n">
+        <v>46254</v>
+      </c>
+      <c r="C499" s="4" t="n">
+        <v>0.2583333333333334</v>
+      </c>
+      <c r="D499" s="4" t="n">
+        <v>0.7451388888888889</v>
+      </c>
+      <c r="E499" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B500" s="3" t="n">
+        <v>46256</v>
+      </c>
+      <c r="C500" s="4" t="n">
+        <v>0.2402777777777778</v>
+      </c>
+      <c r="D500" s="4" t="n">
+        <v>0.74375</v>
+      </c>
+      <c r="E500" s="2" t="inlineStr">
+        <is>
+          <t>extra punches: 17:51 06:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B501" s="3" t="n">
+        <v>46257</v>
+      </c>
+      <c r="C501" s="4" t="n">
+        <v>0.2402777777777778</v>
+      </c>
+      <c r="D501" s="4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E501" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B502" s="3" t="n">
+        <v>46258</v>
+      </c>
+      <c r="C502" s="4" t="n">
+        <v>0.2319444444444445</v>
+      </c>
+      <c r="D502" s="4" t="n">
+        <v>0.7513888888888889</v>
+      </c>
+      <c r="E502" s="2" t="inlineStr">
+        <is>
+          <t>extra punch: 18:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B503" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="C503" s="4" t="n">
+        <v>0.3555555555555556</v>
+      </c>
+      <c r="D503" s="4" t="n">
+        <v>0.7541666666666667</v>
+      </c>
+      <c r="E503" s="2" t="inlineStr">
+        <is>
+          <t>extra punch: 06:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B504" s="3" t="n">
+        <v>46260</v>
+      </c>
+      <c r="C504" s="4" t="n">
+        <v>0.2555555555555555</v>
+      </c>
+      <c r="D504" s="4" t="n">
+        <v>0.7541666666666667</v>
+      </c>
+      <c r="E504" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B505" s="3" t="n">
+        <v>46261</v>
+      </c>
+      <c r="C505" s="4" t="n">
+        <v>0.2722222222222222</v>
+      </c>
+      <c r="D505" s="4" t="n">
+        <v>0.7569444444444444</v>
+      </c>
+      <c r="E505" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B506" s="3" t="n">
+        <v>46263</v>
+      </c>
+      <c r="C506" s="4" t="n">
+        <v>0.2201388888888889</v>
+      </c>
+      <c r="D506" s="4" t="n">
+        <v>0.7444444444444445</v>
+      </c>
+      <c r="E506" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B507" s="3" t="n">
+        <v>46264</v>
+      </c>
+      <c r="C507" s="4" t="n">
+        <v>0.2555555555555555</v>
+      </c>
+      <c r="D507" s="4" t="n">
+        <v>0.7458333333333333</v>
+      </c>
+      <c r="E507" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B508" s="3" t="n">
         <v>46265</v>
       </c>
-      <c r="C444" s="4" t="n">
+      <c r="C508" s="4" t="n">
         <v>0.2569444444444444</v>
       </c>
-      <c r="D444" s="4" t="n">
+      <c r="D508" s="4" t="n">
         <v>0.7527777777777778</v>
       </c>
-      <c r="E444" s="2" t="inlineStr">
+      <c r="E508" s="2" t="inlineStr">
         <is>
           <t>corrected from a clearer re-scan photo later in the album</t>
         </is>

--- a/output/timesheet.xlsx
+++ b/output/timesheet.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E508"/>
+  <dimension ref="A1:E532"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4720,7 +4720,7 @@
       </c>
       <c r="E207" s="2" t="inlineStr">
         <is>
-          <t>extra punches: 05:39 05:39 05:39 05:39 (repeated - device anomaly</t>
+          <t>PLEASE VERIFY: extra punches 05:39 05:39 05:39 05:39 repeated - possible device anomaly</t>
         </is>
       </c>
     </row>
@@ -5680,17 +5680,21 @@
         </is>
       </c>
       <c r="B255" s="3" t="n">
-        <v>46262</v>
-      </c>
-      <c r="C255" s="4" t="n">
-        <v>0.1881944444444444</v>
-      </c>
-      <c r="D255" s="4" t="n">
-        <v>0.4055555555555556</v>
+        <v>46238</v>
+      </c>
+      <c r="C255" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D255" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E255" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>PLEASE VERIFY: check-in/out times not captured (last image in album; sequence ends here)</t>
         </is>
       </c>
     </row>
@@ -5701,17 +5705,17 @@
         </is>
       </c>
       <c r="B256" s="3" t="n">
-        <v>46263</v>
+        <v>46239</v>
       </c>
       <c r="C256" s="4" t="n">
-        <v>0.1847222222222222</v>
+        <v>0.1854166666666667</v>
       </c>
       <c r="D256" s="4" t="n">
-        <v>0.4527777777777778</v>
+        <v>0.5354166666666667</v>
       </c>
       <c r="E256" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>extra punch: 04:27</t>
         </is>
       </c>
     </row>
@@ -5722,13 +5726,13 @@
         </is>
       </c>
       <c r="B257" s="3" t="n">
-        <v>46264</v>
+        <v>46240</v>
       </c>
       <c r="C257" s="4" t="n">
-        <v>0.1847222222222222</v>
+        <v>0.1819444444444444</v>
       </c>
       <c r="D257" s="4" t="n">
-        <v>0.5097222222222222</v>
+        <v>0.4840277777777778</v>
       </c>
       <c r="E257" s="2" t="inlineStr">
         <is>
@@ -5743,15 +5747,36 @@
         </is>
       </c>
       <c r="B258" s="3" t="n">
-        <v>46265</v>
+        <v>46241</v>
       </c>
       <c r="C258" s="4" t="n">
-        <v>0.1868055555555556</v>
+        <v>0.1791666666666667</v>
       </c>
       <c r="D258" s="4" t="n">
-        <v>0.4131944444444444</v>
+        <v>0.5618055555555556</v>
       </c>
       <c r="E258" s="2" t="inlineStr">
+        <is>
+          <t>extra punch: 04:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B259" s="3" t="n">
+        <v>46242</v>
+      </c>
+      <c r="C259" s="4" t="n">
+        <v>0.1805555555555556</v>
+      </c>
+      <c r="D259" s="4" t="n">
+        <v>0.5006944444444444</v>
+      </c>
+      <c r="E259" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -5760,17 +5785,17 @@
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B260" s="3" t="n">
-        <v>46235</v>
+        <v>46243</v>
       </c>
       <c r="C260" s="4" t="n">
-        <v>0.2368055555555555</v>
+        <v>0.1729166666666667</v>
       </c>
       <c r="D260" s="4" t="n">
-        <v>0.7430555555555556</v>
+        <v>0.5284722222222222</v>
       </c>
       <c r="E260" s="2" t="inlineStr">
         <is>
@@ -5781,17 +5806,17 @@
     <row r="261">
       <c r="A261" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B261" s="3" t="n">
-        <v>46236</v>
+        <v>46244</v>
       </c>
       <c r="C261" s="4" t="n">
-        <v>0.2604166666666667</v>
+        <v>0.1715277777777778</v>
       </c>
       <c r="D261" s="4" t="n">
-        <v>0.7534722222222222</v>
+        <v>0.5208333333333334</v>
       </c>
       <c r="E261" s="2" t="inlineStr">
         <is>
@@ -5802,17 +5827,17 @@
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B262" s="3" t="n">
-        <v>46237</v>
+        <v>46245</v>
       </c>
       <c r="C262" s="4" t="n">
-        <v>0.3097222222222222</v>
+        <v>0.1715277777777778</v>
       </c>
       <c r="D262" s="4" t="n">
-        <v>0.7444444444444445</v>
+        <v>0.4430555555555555</v>
       </c>
       <c r="E262" s="2" t="inlineStr">
         <is>
@@ -5823,63 +5848,59 @@
     <row r="263">
       <c r="A263" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B263" s="3" t="n">
-        <v>46238</v>
-      </c>
-      <c r="C263" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>46246</v>
+      </c>
+      <c r="C263" s="4" t="n">
+        <v>0.1743055555555555</v>
       </c>
       <c r="D263" s="4" t="n">
-        <v>0.7458333333333333</v>
+        <v>0.5118055555555555</v>
       </c>
       <c r="E263" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B264" s="3" t="n">
-        <v>46239</v>
+        <v>46247</v>
       </c>
       <c r="C264" s="4" t="n">
-        <v>0.2229166666666667</v>
-      </c>
-      <c r="D264" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.1854166666666667</v>
+      </c>
+      <c r="D264" s="4" t="n">
+        <v>0.5076388888888889</v>
       </c>
       <c r="E264" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B265" s="3" t="n">
-        <v>46240</v>
+        <v>46248</v>
       </c>
       <c r="C265" s="4" t="n">
-        <v>0.2326388888888889</v>
+        <v>0.1743055555555555</v>
       </c>
       <c r="D265" s="4" t="n">
-        <v>0.7576388888888889</v>
+        <v>0.5298611111111111</v>
       </c>
       <c r="E265" s="2" t="inlineStr">
         <is>
@@ -5890,17 +5911,17 @@
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B266" s="3" t="n">
-        <v>46242</v>
+        <v>46249</v>
       </c>
       <c r="C266" s="4" t="n">
-        <v>0.2402777777777778</v>
+        <v>0.1833333333333333</v>
       </c>
       <c r="D266" s="4" t="n">
-        <v>0.7243055555555555</v>
+        <v>0.5354166666666667</v>
       </c>
       <c r="E266" s="2" t="inlineStr">
         <is>
@@ -5911,17 +5932,17 @@
     <row r="267">
       <c r="A267" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B267" s="3" t="n">
-        <v>46243</v>
+        <v>46250</v>
       </c>
       <c r="C267" s="4" t="n">
-        <v>0.2402777777777778</v>
+        <v>0.1868055555555556</v>
       </c>
       <c r="D267" s="4" t="n">
-        <v>0.725</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="E267" s="2" t="inlineStr">
         <is>
@@ -5932,17 +5953,17 @@
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B268" s="3" t="n">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="C268" s="4" t="n">
-        <v>0.2409722222222222</v>
+        <v>0.1951388888888889</v>
       </c>
       <c r="D268" s="4" t="n">
-        <v>0.7597222222222222</v>
+        <v>0.5027777777777778</v>
       </c>
       <c r="E268" s="2" t="inlineStr">
         <is>
@@ -5953,17 +5974,17 @@
     <row r="269">
       <c r="A269" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B269" s="3" t="n">
-        <v>46245</v>
+        <v>46252</v>
       </c>
       <c r="C269" s="4" t="n">
-        <v>0.2215277777777778</v>
+        <v>0.1881944444444444</v>
       </c>
       <c r="D269" s="4" t="n">
-        <v>0.7319444444444444</v>
+        <v>0.41875</v>
       </c>
       <c r="E269" s="2" t="inlineStr">
         <is>
@@ -5974,17 +5995,17 @@
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B270" s="3" t="n">
-        <v>46246</v>
+        <v>46253</v>
       </c>
       <c r="C270" s="4" t="n">
-        <v>0.2361111111111111</v>
+        <v>0.1902777777777778</v>
       </c>
       <c r="D270" s="4" t="n">
-        <v>0.7402777777777778</v>
+        <v>0.5173611111111112</v>
       </c>
       <c r="E270" s="2" t="inlineStr">
         <is>
@@ -5995,17 +6016,17 @@
     <row r="271">
       <c r="A271" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B271" s="3" t="n">
-        <v>46247</v>
+        <v>46254</v>
       </c>
       <c r="C271" s="4" t="n">
-        <v>0.2479166666666667</v>
+        <v>0.1854166666666667</v>
       </c>
       <c r="D271" s="4" t="n">
-        <v>0.7243055555555555</v>
+        <v>0.5048611111111111</v>
       </c>
       <c r="E271" s="2" t="inlineStr">
         <is>
@@ -6016,40 +6037,38 @@
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B272" s="3" t="n">
-        <v>46249</v>
-      </c>
-      <c r="C272" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>46255</v>
+      </c>
+      <c r="C272" s="4" t="n">
+        <v>0.1854166666666667</v>
       </c>
       <c r="D272" s="4" t="n">
-        <v>0.7201388888888889</v>
+        <v>0.5319444444444444</v>
       </c>
       <c r="E272" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B273" s="3" t="n">
-        <v>46250</v>
+        <v>46256</v>
       </c>
       <c r="C273" s="4" t="n">
-        <v>0.2298611111111111</v>
+        <v>0.1854166666666667</v>
       </c>
       <c r="D273" s="4" t="n">
-        <v>0.7180555555555556</v>
+        <v>0.5159722222222223</v>
       </c>
       <c r="E273" s="2" t="inlineStr">
         <is>
@@ -6060,17 +6079,17 @@
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B274" s="3" t="n">
-        <v>46251</v>
+        <v>46257</v>
       </c>
       <c r="C274" s="4" t="n">
-        <v>0.2472222222222222</v>
+        <v>0.1868055555555556</v>
       </c>
       <c r="D274" s="4" t="n">
-        <v>0.7402777777777778</v>
+        <v>0.4256944444444444</v>
       </c>
       <c r="E274" s="2" t="inlineStr">
         <is>
@@ -6081,40 +6100,38 @@
     <row r="275">
       <c r="A275" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B275" s="3" t="n">
-        <v>46252</v>
+        <v>46258</v>
       </c>
       <c r="C275" s="4" t="n">
-        <v>0.2354166666666667</v>
-      </c>
-      <c r="D275" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.1861111111111111</v>
+      </c>
+      <c r="D275" s="4" t="n">
+        <v>0.4930555555555556</v>
       </c>
       <c r="E275" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B276" s="3" t="n">
-        <v>46253</v>
+        <v>46259</v>
       </c>
       <c r="C276" s="4" t="n">
-        <v>0.2215277777777778</v>
+        <v>0.1847222222222222</v>
       </c>
       <c r="D276" s="4" t="n">
-        <v>0.7305555555555555</v>
+        <v>0.4881944444444444</v>
       </c>
       <c r="E276" s="2" t="inlineStr">
         <is>
@@ -6125,17 +6142,17 @@
     <row r="277">
       <c r="A277" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B277" s="3" t="n">
-        <v>46254</v>
+        <v>46260</v>
       </c>
       <c r="C277" s="4" t="n">
-        <v>0.2222222222222222</v>
+        <v>0.1965277777777778</v>
       </c>
       <c r="D277" s="4" t="n">
-        <v>0.7291666666666666</v>
+        <v>0.5048611111111111</v>
       </c>
       <c r="E277" s="2" t="inlineStr">
         <is>
@@ -6146,17 +6163,17 @@
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B278" s="3" t="n">
-        <v>46256</v>
+        <v>46261</v>
       </c>
       <c r="C278" s="4" t="n">
-        <v>0.2388888888888889</v>
+        <v>0.1798611111111111</v>
       </c>
       <c r="D278" s="4" t="n">
-        <v>0.7541666666666667</v>
+        <v>0.4979166666666667</v>
       </c>
       <c r="E278" s="2" t="inlineStr">
         <is>
@@ -6167,17 +6184,17 @@
     <row r="279">
       <c r="A279" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B279" s="3" t="n">
-        <v>46257</v>
+        <v>46262</v>
       </c>
       <c r="C279" s="4" t="n">
-        <v>0.2506944444444444</v>
+        <v>0.1881944444444444</v>
       </c>
       <c r="D279" s="4" t="n">
-        <v>0.7291666666666666</v>
+        <v>0.4055555555555556</v>
       </c>
       <c r="E279" s="2" t="inlineStr">
         <is>
@@ -6188,40 +6205,38 @@
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B280" s="3" t="n">
-        <v>46258</v>
-      </c>
-      <c r="C280" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>46263</v>
+      </c>
+      <c r="C280" s="4" t="n">
+        <v>0.1847222222222222</v>
       </c>
       <c r="D280" s="4" t="n">
-        <v>0.725</v>
+        <v>0.4527777777777778</v>
       </c>
       <c r="E280" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B281" s="3" t="n">
-        <v>46259</v>
+        <v>46264</v>
       </c>
       <c r="C281" s="4" t="n">
-        <v>0.2375</v>
+        <v>0.1847222222222222</v>
       </c>
       <c r="D281" s="4" t="n">
-        <v>0.725</v>
+        <v>0.5097222222222222</v>
       </c>
       <c r="E281" s="2" t="inlineStr">
         <is>
@@ -6232,40 +6247,19 @@
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B282" s="3" t="n">
-        <v>46260</v>
+        <v>46265</v>
       </c>
       <c r="C282" s="4" t="n">
-        <v>0.2256944444444444</v>
+        <v>0.1868055555555556</v>
       </c>
       <c r="D282" s="4" t="n">
-        <v>0.7381944444444445</v>
+        <v>0.4131944444444444</v>
       </c>
       <c r="E282" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="283">
-      <c r="A283" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="B283" s="3" t="n">
-        <v>46261</v>
-      </c>
-      <c r="C283" s="4" t="n">
-        <v>0.2361111111111111</v>
-      </c>
-      <c r="D283" s="4" t="n">
-        <v>0.7166666666666667</v>
-      </c>
-      <c r="E283" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -6278,13 +6272,13 @@
         </is>
       </c>
       <c r="B284" s="3" t="n">
-        <v>46263</v>
+        <v>46235</v>
       </c>
       <c r="C284" s="4" t="n">
-        <v>0.2270833333333333</v>
+        <v>0.2368055555555555</v>
       </c>
       <c r="D284" s="4" t="n">
-        <v>0.7347222222222223</v>
+        <v>0.7430555555555556</v>
       </c>
       <c r="E284" s="2" t="inlineStr">
         <is>
@@ -6299,19 +6293,17 @@
         </is>
       </c>
       <c r="B285" s="3" t="n">
-        <v>46264</v>
+        <v>46236</v>
       </c>
       <c r="C285" s="4" t="n">
-        <v>0.2340277777777778</v>
-      </c>
-      <c r="D285" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.2604166666666667</v>
+      </c>
+      <c r="D285" s="4" t="n">
+        <v>0.7534722222222222</v>
       </c>
       <c r="E285" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -6322,17 +6314,38 @@
         </is>
       </c>
       <c r="B286" s="3" t="n">
-        <v>46265</v>
+        <v>46237</v>
       </c>
       <c r="C286" s="4" t="n">
-        <v>0.2361111111111111</v>
-      </c>
-      <c r="D286" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.3097222222222222</v>
+      </c>
+      <c r="D286" s="4" t="n">
+        <v>0.7444444444444445</v>
       </c>
       <c r="E286" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B287" s="3" t="n">
+        <v>46238</v>
+      </c>
+      <c r="C287" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D287" s="4" t="n">
+        <v>0.7458333333333333</v>
+      </c>
+      <c r="E287" s="2" t="inlineStr">
         <is>
           <t>single punch only</t>
         </is>
@@ -6341,38 +6354,40 @@
     <row r="288">
       <c r="A288" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B288" s="3" t="n">
-        <v>46235</v>
+        <v>46239</v>
       </c>
       <c r="C288" s="4" t="n">
-        <v>0.14375</v>
-      </c>
-      <c r="D288" s="4" t="n">
-        <v>0.7576388888888889</v>
+        <v>0.2229166666666667</v>
+      </c>
+      <c r="D288" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E288" s="2" t="inlineStr">
         <is>
-          <t>last day of month; final record</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B289" s="3" t="n">
-        <v>46236</v>
+        <v>46240</v>
       </c>
       <c r="C289" s="4" t="n">
-        <v>0.14375</v>
+        <v>0.2326388888888889</v>
       </c>
       <c r="D289" s="4" t="n">
-        <v>0.7395833333333334</v>
+        <v>0.7576388888888889</v>
       </c>
       <c r="E289" s="2" t="inlineStr">
         <is>
@@ -6383,17 +6398,17 @@
     <row r="290">
       <c r="A290" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B290" s="3" t="n">
-        <v>46237</v>
+        <v>46242</v>
       </c>
       <c r="C290" s="4" t="n">
-        <v>0.1458333333333333</v>
+        <v>0.2402777777777778</v>
       </c>
       <c r="D290" s="4" t="n">
-        <v>0.7472222222222222</v>
+        <v>0.7243055555555555</v>
       </c>
       <c r="E290" s="2" t="inlineStr">
         <is>
@@ -6404,17 +6419,17 @@
     <row r="291">
       <c r="A291" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B291" s="3" t="n">
-        <v>46238</v>
+        <v>46243</v>
       </c>
       <c r="C291" s="4" t="n">
-        <v>0.1451388888888889</v>
+        <v>0.2402777777777778</v>
       </c>
       <c r="D291" s="4" t="n">
-        <v>0.7708333333333334</v>
+        <v>0.725</v>
       </c>
       <c r="E291" s="2" t="inlineStr">
         <is>
@@ -6425,17 +6440,17 @@
     <row r="292">
       <c r="A292" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B292" s="3" t="n">
-        <v>46239</v>
+        <v>46244</v>
       </c>
       <c r="C292" s="4" t="n">
-        <v>0.1444444444444444</v>
+        <v>0.2409722222222222</v>
       </c>
       <c r="D292" s="4" t="n">
-        <v>0.6881944444444444</v>
+        <v>0.7597222222222222</v>
       </c>
       <c r="E292" s="2" t="inlineStr">
         <is>
@@ -6446,17 +6461,17 @@
     <row r="293">
       <c r="A293" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B293" s="3" t="n">
-        <v>46240</v>
+        <v>46245</v>
       </c>
       <c r="C293" s="4" t="n">
-        <v>0.1444444444444444</v>
+        <v>0.2215277777777778</v>
       </c>
       <c r="D293" s="4" t="n">
-        <v>0.7659722222222223</v>
+        <v>0.7319444444444444</v>
       </c>
       <c r="E293" s="2" t="inlineStr">
         <is>
@@ -6467,17 +6482,17 @@
     <row r="294">
       <c r="A294" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B294" s="3" t="n">
-        <v>46241</v>
+        <v>46246</v>
       </c>
       <c r="C294" s="4" t="n">
-        <v>0.1451388888888889</v>
+        <v>0.2361111111111111</v>
       </c>
       <c r="D294" s="4" t="n">
-        <v>0.7298611111111111</v>
+        <v>0.7402777777777778</v>
       </c>
       <c r="E294" s="2" t="inlineStr">
         <is>
@@ -6488,59 +6503,61 @@
     <row r="295">
       <c r="A295" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B295" s="3" t="n">
-        <v>46242</v>
+        <v>46247</v>
       </c>
       <c r="C295" s="4" t="n">
-        <v>0.1388888888888889</v>
+        <v>0.2479166666666667</v>
       </c>
       <c r="D295" s="4" t="n">
-        <v>0.8090277777777778</v>
+        <v>0.7243055555555555</v>
       </c>
       <c r="E295" s="2" t="inlineStr">
         <is>
-          <t>extra punch: 03:24</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B296" s="3" t="n">
-        <v>46243</v>
-      </c>
-      <c r="C296" s="4" t="n">
-        <v>0.1444444444444444</v>
+        <v>46249</v>
+      </c>
+      <c r="C296" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D296" s="4" t="n">
-        <v>0.8381944444444445</v>
+        <v>0.7201388888888889</v>
       </c>
       <c r="E296" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B297" s="3" t="n">
-        <v>46244</v>
+        <v>46250</v>
       </c>
       <c r="C297" s="4" t="n">
-        <v>0.1354166666666667</v>
+        <v>0.2298611111111111</v>
       </c>
       <c r="D297" s="4" t="n">
-        <v>0.7638888888888888</v>
+        <v>0.7180555555555556</v>
       </c>
       <c r="E297" s="2" t="inlineStr">
         <is>
@@ -6551,17 +6568,17 @@
     <row r="298">
       <c r="A298" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B298" s="3" t="n">
-        <v>46245</v>
+        <v>46251</v>
       </c>
       <c r="C298" s="4" t="n">
-        <v>0.14375</v>
+        <v>0.2472222222222222</v>
       </c>
       <c r="D298" s="4" t="n">
-        <v>0.7444444444444445</v>
+        <v>0.7402777777777778</v>
       </c>
       <c r="E298" s="2" t="inlineStr">
         <is>
@@ -6572,38 +6589,40 @@
     <row r="299">
       <c r="A299" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B299" s="3" t="n">
-        <v>46246</v>
+        <v>46252</v>
       </c>
       <c r="C299" s="4" t="n">
-        <v>0.1430555555555555</v>
-      </c>
-      <c r="D299" s="4" t="n">
-        <v>0.7409722222222223</v>
+        <v>0.2354166666666667</v>
+      </c>
+      <c r="D299" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E299" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B300" s="3" t="n">
-        <v>46247</v>
+        <v>46253</v>
       </c>
       <c r="C300" s="4" t="n">
-        <v>0.1423611111111111</v>
+        <v>0.2215277777777778</v>
       </c>
       <c r="D300" s="4" t="n">
-        <v>0.75</v>
+        <v>0.7305555555555555</v>
       </c>
       <c r="E300" s="2" t="inlineStr">
         <is>
@@ -6614,17 +6633,17 @@
     <row r="301">
       <c r="A301" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B301" s="3" t="n">
-        <v>46248</v>
+        <v>46254</v>
       </c>
       <c r="C301" s="4" t="n">
-        <v>0.15</v>
+        <v>0.2222222222222222</v>
       </c>
       <c r="D301" s="4" t="n">
-        <v>0.7076388888888889</v>
+        <v>0.7291666666666666</v>
       </c>
       <c r="E301" s="2" t="inlineStr">
         <is>
@@ -6635,17 +6654,17 @@
     <row r="302">
       <c r="A302" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B302" s="3" t="n">
-        <v>46249</v>
+        <v>46256</v>
       </c>
       <c r="C302" s="4" t="n">
-        <v>0.1513888888888889</v>
+        <v>0.2388888888888889</v>
       </c>
       <c r="D302" s="4" t="n">
-        <v>0.7277777777777777</v>
+        <v>0.7541666666666667</v>
       </c>
       <c r="E302" s="2" t="inlineStr">
         <is>
@@ -6656,17 +6675,17 @@
     <row r="303">
       <c r="A303" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B303" s="3" t="n">
-        <v>46250</v>
+        <v>46257</v>
       </c>
       <c r="C303" s="4" t="n">
-        <v>0.2708333333333333</v>
+        <v>0.2506944444444444</v>
       </c>
       <c r="D303" s="4" t="n">
-        <v>0.7229166666666667</v>
+        <v>0.7291666666666666</v>
       </c>
       <c r="E303" s="2" t="inlineStr">
         <is>
@@ -6677,38 +6696,40 @@
     <row r="304">
       <c r="A304" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B304" s="3" t="n">
-        <v>46251</v>
-      </c>
-      <c r="C304" s="4" t="n">
-        <v>0.2333333333333333</v>
+        <v>46258</v>
+      </c>
+      <c r="C304" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D304" s="4" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.725</v>
       </c>
       <c r="E304" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B305" s="3" t="n">
-        <v>46252</v>
+        <v>46259</v>
       </c>
       <c r="C305" s="4" t="n">
-        <v>0.25625</v>
+        <v>0.2375</v>
       </c>
       <c r="D305" s="4" t="n">
-        <v>0.7416666666666667</v>
+        <v>0.725</v>
       </c>
       <c r="E305" s="2" t="inlineStr">
         <is>
@@ -6719,17 +6740,17 @@
     <row r="306">
       <c r="A306" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B306" s="3" t="n">
-        <v>46253</v>
+        <v>46260</v>
       </c>
       <c r="C306" s="4" t="n">
-        <v>0.2777777777777778</v>
+        <v>0.2256944444444444</v>
       </c>
       <c r="D306" s="4" t="n">
-        <v>0.7451388888888889</v>
+        <v>0.7381944444444445</v>
       </c>
       <c r="E306" s="2" t="inlineStr">
         <is>
@@ -6740,17 +6761,17 @@
     <row r="307">
       <c r="A307" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B307" s="3" t="n">
-        <v>46254</v>
+        <v>46261</v>
       </c>
       <c r="C307" s="4" t="n">
-        <v>0.2625</v>
+        <v>0.2361111111111111</v>
       </c>
       <c r="D307" s="4" t="n">
-        <v>0.7979166666666667</v>
+        <v>0.7166666666666667</v>
       </c>
       <c r="E307" s="2" t="inlineStr">
         <is>
@@ -6761,17 +6782,17 @@
     <row r="308">
       <c r="A308" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B308" s="3" t="n">
-        <v>46255</v>
+        <v>46263</v>
       </c>
       <c r="C308" s="4" t="n">
-        <v>0.275</v>
+        <v>0.2270833333333333</v>
       </c>
       <c r="D308" s="4" t="n">
-        <v>0.8354166666666667</v>
+        <v>0.7347222222222223</v>
       </c>
       <c r="E308" s="2" t="inlineStr">
         <is>
@@ -6782,63 +6803,46 @@
     <row r="309">
       <c r="A309" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B309" s="3" t="n">
-        <v>46256</v>
+        <v>46264</v>
       </c>
       <c r="C309" s="4" t="n">
-        <v>0.2611111111111111</v>
-      </c>
-      <c r="D309" s="4" t="n">
-        <v>0.7513888888888889</v>
+        <v>0.2340277777777778</v>
+      </c>
+      <c r="D309" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E309" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B310" s="3" t="n">
-        <v>46257</v>
+        <v>46265</v>
       </c>
       <c r="C310" s="4" t="n">
-        <v>0.24375</v>
-      </c>
-      <c r="D310" s="4" t="n">
-        <v>0.7263888888888889</v>
+        <v>0.2361111111111111</v>
+      </c>
+      <c r="D310" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E310" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="311">
-      <c r="A311" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="B311" s="3" t="n">
-        <v>46258</v>
-      </c>
-      <c r="C311" s="4" t="n">
-        <v>0.2631944444444445</v>
-      </c>
-      <c r="D311" s="4" t="n">
-        <v>0.7270833333333333</v>
-      </c>
-      <c r="E311" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
@@ -6849,17 +6853,17 @@
         </is>
       </c>
       <c r="B312" s="3" t="n">
-        <v>46259</v>
+        <v>46235</v>
       </c>
       <c r="C312" s="4" t="n">
-        <v>0.2611111111111111</v>
+        <v>0.14375</v>
       </c>
       <c r="D312" s="4" t="n">
-        <v>0.7298611111111111</v>
+        <v>0.7576388888888889</v>
       </c>
       <c r="E312" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>last day of month; final record</t>
         </is>
       </c>
     </row>
@@ -6870,17 +6874,17 @@
         </is>
       </c>
       <c r="B313" s="3" t="n">
-        <v>46260</v>
+        <v>46236</v>
       </c>
       <c r="C313" s="4" t="n">
-        <v>0.275</v>
+        <v>0.14375</v>
       </c>
       <c r="D313" s="4" t="n">
-        <v>0.8791666666666667</v>
+        <v>0.7395833333333334</v>
       </c>
       <c r="E313" s="2" t="inlineStr">
         <is>
-          <t>extra punch: 17:56</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -6891,17 +6895,17 @@
         </is>
       </c>
       <c r="B314" s="3" t="n">
-        <v>46261</v>
+        <v>46237</v>
       </c>
       <c r="C314" s="4" t="n">
-        <v>0.2555555555555555</v>
+        <v>0.1458333333333333</v>
       </c>
       <c r="D314" s="4" t="n">
-        <v>0.8506944444444444</v>
+        <v>0.7472222222222222</v>
       </c>
       <c r="E314" s="2" t="inlineStr">
         <is>
-          <t>extra punches: 17:07 17:02</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -6912,13 +6916,13 @@
         </is>
       </c>
       <c r="B315" s="3" t="n">
-        <v>46262</v>
+        <v>46238</v>
       </c>
       <c r="C315" s="4" t="n">
-        <v>0.2805555555555556</v>
+        <v>0.1451388888888889</v>
       </c>
       <c r="D315" s="4" t="n">
-        <v>0.7701388888888889</v>
+        <v>0.7708333333333334</v>
       </c>
       <c r="E315" s="2" t="inlineStr">
         <is>
@@ -6933,13 +6937,13 @@
         </is>
       </c>
       <c r="B316" s="3" t="n">
-        <v>46263</v>
+        <v>46239</v>
       </c>
       <c r="C316" s="4" t="n">
-        <v>0.2541666666666667</v>
+        <v>0.1444444444444444</v>
       </c>
       <c r="D316" s="4" t="n">
-        <v>0.7479166666666667</v>
+        <v>0.6881944444444444</v>
       </c>
       <c r="E316" s="2" t="inlineStr">
         <is>
@@ -6954,13 +6958,13 @@
         </is>
       </c>
       <c r="B317" s="3" t="n">
-        <v>46264</v>
+        <v>46240</v>
       </c>
       <c r="C317" s="4" t="n">
-        <v>0.2659722222222222</v>
+        <v>0.1444444444444444</v>
       </c>
       <c r="D317" s="4" t="n">
-        <v>0.7354166666666667</v>
+        <v>0.7659722222222223</v>
       </c>
       <c r="E317" s="2" t="inlineStr">
         <is>
@@ -6975,55 +6979,76 @@
         </is>
       </c>
       <c r="B318" s="3" t="n">
-        <v>46265</v>
+        <v>46241</v>
       </c>
       <c r="C318" s="4" t="n">
-        <v>0.2527777777777778</v>
+        <v>0.1451388888888889</v>
       </c>
       <c r="D318" s="4" t="n">
-        <v>0.7354166666666667</v>
+        <v>0.7298611111111111</v>
       </c>
       <c r="E318" s="2" t="inlineStr">
         <is>
-          <t>corrected from a clearer re-scan photo later in the album</t>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B319" s="3" t="n">
+        <v>46242</v>
+      </c>
+      <c r="C319" s="4" t="n">
+        <v>0.1388888888888889</v>
+      </c>
+      <c r="D319" s="4" t="n">
+        <v>0.8090277777777778</v>
+      </c>
+      <c r="E319" s="2" t="inlineStr">
+        <is>
+          <t>extra punch: 03:24</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B320" s="3" t="n">
-        <v>46235</v>
+        <v>46243</v>
       </c>
       <c r="C320" s="4" t="n">
-        <v>0.2625</v>
+        <v>0.1444444444444444</v>
       </c>
       <c r="D320" s="4" t="n">
-        <v>0.7444444444444445</v>
+        <v>0.8381944444444445</v>
       </c>
       <c r="E320" s="2" t="inlineStr">
         <is>
-          <t>last day of month; final record</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B321" s="3" t="n">
-        <v>46236</v>
+        <v>46244</v>
       </c>
       <c r="C321" s="4" t="n">
-        <v>0.2645833333333333</v>
+        <v>0.1354166666666667</v>
       </c>
       <c r="D321" s="4" t="n">
-        <v>0.7493055555555556</v>
+        <v>0.7638888888888888</v>
       </c>
       <c r="E321" s="2" t="inlineStr">
         <is>
@@ -7034,17 +7059,17 @@
     <row r="322">
       <c r="A322" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B322" s="3" t="n">
-        <v>46237</v>
+        <v>46245</v>
       </c>
       <c r="C322" s="4" t="n">
-        <v>0.2604166666666667</v>
+        <v>0.14375</v>
       </c>
       <c r="D322" s="4" t="n">
-        <v>0.7479166666666667</v>
+        <v>0.7444444444444445</v>
       </c>
       <c r="E322" s="2" t="inlineStr">
         <is>
@@ -7055,17 +7080,17 @@
     <row r="323">
       <c r="A323" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B323" s="3" t="n">
-        <v>46238</v>
+        <v>46246</v>
       </c>
       <c r="C323" s="4" t="n">
-        <v>0.2527777777777778</v>
+        <v>0.1430555555555555</v>
       </c>
       <c r="D323" s="4" t="n">
-        <v>0.75</v>
+        <v>0.7409722222222223</v>
       </c>
       <c r="E323" s="2" t="inlineStr">
         <is>
@@ -7076,17 +7101,17 @@
     <row r="324">
       <c r="A324" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B324" s="3" t="n">
-        <v>46239</v>
+        <v>46247</v>
       </c>
       <c r="C324" s="4" t="n">
-        <v>0.25625</v>
+        <v>0.1423611111111111</v>
       </c>
       <c r="D324" s="4" t="n">
-        <v>0.7763888888888889</v>
+        <v>0.75</v>
       </c>
       <c r="E324" s="2" t="inlineStr">
         <is>
@@ -7097,17 +7122,17 @@
     <row r="325">
       <c r="A325" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B325" s="3" t="n">
-        <v>46240</v>
+        <v>46248</v>
       </c>
       <c r="C325" s="4" t="n">
-        <v>0.2701388888888889</v>
+        <v>0.15</v>
       </c>
       <c r="D325" s="4" t="n">
-        <v>0.7423611111111111</v>
+        <v>0.7076388888888889</v>
       </c>
       <c r="E325" s="2" t="inlineStr">
         <is>
@@ -7118,17 +7143,17 @@
     <row r="326">
       <c r="A326" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B326" s="3" t="n">
-        <v>46242</v>
+        <v>46249</v>
       </c>
       <c r="C326" s="4" t="n">
-        <v>0.2597222222222222</v>
+        <v>0.1513888888888889</v>
       </c>
       <c r="D326" s="4" t="n">
-        <v>0.7326388888888888</v>
+        <v>0.7277777777777777</v>
       </c>
       <c r="E326" s="2" t="inlineStr">
         <is>
@@ -7139,17 +7164,17 @@
     <row r="327">
       <c r="A327" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B327" s="3" t="n">
-        <v>46243</v>
+        <v>46250</v>
       </c>
       <c r="C327" s="4" t="n">
-        <v>0.2381944444444444</v>
+        <v>0.2708333333333333</v>
       </c>
       <c r="D327" s="4" t="n">
-        <v>0.75625</v>
+        <v>0.7229166666666667</v>
       </c>
       <c r="E327" s="2" t="inlineStr">
         <is>
@@ -7160,40 +7185,38 @@
     <row r="328">
       <c r="A328" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B328" s="3" t="n">
-        <v>46244</v>
-      </c>
-      <c r="C328" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>46251</v>
+      </c>
+      <c r="C328" s="4" t="n">
+        <v>0.2333333333333333</v>
       </c>
       <c r="D328" s="4" t="n">
-        <v>0.75625</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="E328" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B329" s="3" t="n">
-        <v>46245</v>
+        <v>46252</v>
       </c>
       <c r="C329" s="4" t="n">
-        <v>0.2381944444444444</v>
+        <v>0.25625</v>
       </c>
       <c r="D329" s="4" t="n">
-        <v>0.7402777777777778</v>
+        <v>0.7416666666666667</v>
       </c>
       <c r="E329" s="2" t="inlineStr">
         <is>
@@ -7204,17 +7227,17 @@
     <row r="330">
       <c r="A330" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B330" s="3" t="n">
-        <v>46246</v>
+        <v>46253</v>
       </c>
       <c r="C330" s="4" t="n">
-        <v>0.2340277777777778</v>
+        <v>0.2777777777777778</v>
       </c>
       <c r="D330" s="4" t="n">
-        <v>0.7493055555555556</v>
+        <v>0.7451388888888889</v>
       </c>
       <c r="E330" s="2" t="inlineStr">
         <is>
@@ -7225,17 +7248,17 @@
     <row r="331">
       <c r="A331" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B331" s="3" t="n">
-        <v>46247</v>
+        <v>46254</v>
       </c>
       <c r="C331" s="4" t="n">
-        <v>0.2465277777777778</v>
+        <v>0.2625</v>
       </c>
       <c r="D331" s="4" t="n">
-        <v>0.7270833333333333</v>
+        <v>0.7979166666666667</v>
       </c>
       <c r="E331" s="2" t="inlineStr">
         <is>
@@ -7246,17 +7269,17 @@
     <row r="332">
       <c r="A332" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B332" s="3" t="n">
-        <v>46249</v>
+        <v>46255</v>
       </c>
       <c r="C332" s="4" t="n">
-        <v>0.2395833333333333</v>
+        <v>0.275</v>
       </c>
       <c r="D332" s="4" t="n">
-        <v>0.7388888888888889</v>
+        <v>0.8354166666666667</v>
       </c>
       <c r="E332" s="2" t="inlineStr">
         <is>
@@ -7267,17 +7290,17 @@
     <row r="333">
       <c r="A333" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B333" s="3" t="n">
-        <v>46250</v>
+        <v>46256</v>
       </c>
       <c r="C333" s="4" t="n">
-        <v>0.2902777777777778</v>
+        <v>0.2611111111111111</v>
       </c>
       <c r="D333" s="4" t="n">
-        <v>0.7236111111111111</v>
+        <v>0.7513888888888889</v>
       </c>
       <c r="E333" s="2" t="inlineStr">
         <is>
@@ -7288,17 +7311,17 @@
     <row r="334">
       <c r="A334" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B334" s="3" t="n">
-        <v>46251</v>
+        <v>46257</v>
       </c>
       <c r="C334" s="4" t="n">
-        <v>0.2743055555555556</v>
+        <v>0.24375</v>
       </c>
       <c r="D334" s="4" t="n">
-        <v>0.7333333333333333</v>
+        <v>0.7263888888888889</v>
       </c>
       <c r="E334" s="2" t="inlineStr">
         <is>
@@ -7309,17 +7332,17 @@
     <row r="335">
       <c r="A335" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B335" s="3" t="n">
-        <v>46252</v>
+        <v>46258</v>
       </c>
       <c r="C335" s="4" t="n">
-        <v>0.2826388888888889</v>
+        <v>0.2631944444444445</v>
       </c>
       <c r="D335" s="4" t="n">
-        <v>0.7451388888888889</v>
+        <v>0.7270833333333333</v>
       </c>
       <c r="E335" s="2" t="inlineStr">
         <is>
@@ -7330,14 +7353,14 @@
     <row r="336">
       <c r="A336" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B336" s="3" t="n">
-        <v>46253</v>
+        <v>46259</v>
       </c>
       <c r="C336" s="4" t="n">
-        <v>0.2763888888888889</v>
+        <v>0.2611111111111111</v>
       </c>
       <c r="D336" s="4" t="n">
         <v>0.7298611111111111</v>
@@ -7351,59 +7374,59 @@
     <row r="337">
       <c r="A337" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B337" s="3" t="n">
-        <v>46254</v>
+        <v>46260</v>
       </c>
       <c r="C337" s="4" t="n">
         <v>0.275</v>
       </c>
       <c r="D337" s="4" t="n">
-        <v>0.7256944444444444</v>
+        <v>0.8791666666666667</v>
       </c>
       <c r="E337" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>extra punch: 17:56</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B338" s="3" t="n">
-        <v>46256</v>
+        <v>46261</v>
       </c>
       <c r="C338" s="4" t="n">
-        <v>0.2805555555555556</v>
+        <v>0.2555555555555555</v>
       </c>
       <c r="D338" s="4" t="n">
-        <v>0.7513888888888889</v>
+        <v>0.8506944444444444</v>
       </c>
       <c r="E338" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>extra punches: 17:07 17:02</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B339" s="3" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="C339" s="4" t="n">
-        <v>0.24375</v>
+        <v>0.2805555555555556</v>
       </c>
       <c r="D339" s="4" t="n">
-        <v>0.6763888888888889</v>
+        <v>0.7701388888888889</v>
       </c>
       <c r="E339" s="2" t="inlineStr">
         <is>
@@ -7414,17 +7437,17 @@
     <row r="340">
       <c r="A340" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B340" s="3" t="n">
         <v>46263</v>
       </c>
       <c r="C340" s="4" t="n">
-        <v>0.2965277777777778</v>
+        <v>0.2541666666666667</v>
       </c>
       <c r="D340" s="4" t="n">
-        <v>0.7472222222222222</v>
+        <v>0.7479166666666667</v>
       </c>
       <c r="E340" s="2" t="inlineStr">
         <is>
@@ -7435,17 +7458,17 @@
     <row r="341">
       <c r="A341" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B341" s="3" t="n">
         <v>46264</v>
       </c>
       <c r="C341" s="4" t="n">
-        <v>0.2888888888888889</v>
+        <v>0.2659722222222222</v>
       </c>
       <c r="D341" s="4" t="n">
-        <v>0.75</v>
+        <v>0.7354166666666667</v>
       </c>
       <c r="E341" s="2" t="inlineStr">
         <is>
@@ -7456,38 +7479,38 @@
     <row r="342">
       <c r="A342" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B342" s="3" t="n">
         <v>46265</v>
       </c>
       <c r="C342" s="4" t="n">
-        <v>0.2909722222222222</v>
+        <v>0.2527777777777778</v>
       </c>
       <c r="D342" s="4" t="n">
-        <v>0.75</v>
+        <v>0.7354166666666667</v>
       </c>
       <c r="E342" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>corrected from a clearer re-scan photo later in the album</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B344" s="3" t="n">
         <v>46235</v>
       </c>
       <c r="C344" s="4" t="n">
-        <v>0.2381944444444444</v>
+        <v>0.2625</v>
       </c>
       <c r="D344" s="4" t="n">
-        <v>0.7458333333333333</v>
+        <v>0.7444444444444445</v>
       </c>
       <c r="E344" s="2" t="inlineStr">
         <is>
@@ -7498,17 +7521,17 @@
     <row r="345">
       <c r="A345" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B345" s="3" t="n">
         <v>46236</v>
       </c>
       <c r="C345" s="4" t="n">
-        <v>0.2958333333333333</v>
+        <v>0.2645833333333333</v>
       </c>
       <c r="D345" s="4" t="n">
-        <v>0.7430555555555556</v>
+        <v>0.7493055555555556</v>
       </c>
       <c r="E345" s="2" t="inlineStr">
         <is>
@@ -7519,17 +7542,17 @@
     <row r="346">
       <c r="A346" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B346" s="3" t="n">
         <v>46237</v>
       </c>
       <c r="C346" s="4" t="n">
-        <v>0.3034722222222222</v>
+        <v>0.2604166666666667</v>
       </c>
       <c r="D346" s="4" t="n">
-        <v>0.7159722222222222</v>
+        <v>0.7479166666666667</v>
       </c>
       <c r="E346" s="2" t="inlineStr">
         <is>
@@ -7540,17 +7563,17 @@
     <row r="347">
       <c r="A347" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B347" s="3" t="n">
         <v>46238</v>
       </c>
       <c r="C347" s="4" t="n">
-        <v>0.2763888888888889</v>
+        <v>0.2527777777777778</v>
       </c>
       <c r="D347" s="4" t="n">
-        <v>0.7166666666666667</v>
+        <v>0.75</v>
       </c>
       <c r="E347" s="2" t="inlineStr">
         <is>
@@ -7561,17 +7584,17 @@
     <row r="348">
       <c r="A348" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B348" s="3" t="n">
         <v>46239</v>
       </c>
       <c r="C348" s="4" t="n">
-        <v>0.3222222222222222</v>
+        <v>0.25625</v>
       </c>
       <c r="D348" s="4" t="n">
-        <v>0.7715277777777778</v>
+        <v>0.7763888888888889</v>
       </c>
       <c r="E348" s="2" t="inlineStr">
         <is>
@@ -7582,17 +7605,17 @@
     <row r="349">
       <c r="A349" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B349" s="3" t="n">
         <v>46240</v>
       </c>
       <c r="C349" s="4" t="n">
-        <v>0.30625</v>
+        <v>0.2701388888888889</v>
       </c>
       <c r="D349" s="4" t="n">
-        <v>0.7590277777777777</v>
+        <v>0.7423611111111111</v>
       </c>
       <c r="E349" s="2" t="inlineStr">
         <is>
@@ -7603,17 +7626,17 @@
     <row r="350">
       <c r="A350" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B350" s="3" t="n">
         <v>46242</v>
       </c>
       <c r="C350" s="4" t="n">
-        <v>0.3055555555555556</v>
+        <v>0.2597222222222222</v>
       </c>
       <c r="D350" s="4" t="n">
-        <v>0.7604166666666666</v>
+        <v>0.7326388888888888</v>
       </c>
       <c r="E350" s="2" t="inlineStr">
         <is>
@@ -7624,17 +7647,17 @@
     <row r="351">
       <c r="A351" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B351" s="3" t="n">
         <v>46243</v>
       </c>
       <c r="C351" s="4" t="n">
-        <v>0.2798611111111111</v>
+        <v>0.2381944444444444</v>
       </c>
       <c r="D351" s="4" t="n">
-        <v>0.75</v>
+        <v>0.75625</v>
       </c>
       <c r="E351" s="2" t="inlineStr">
         <is>
@@ -7645,107 +7668,103 @@
     <row r="352">
       <c r="A352" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B352" s="3" t="n">
         <v>46244</v>
       </c>
-      <c r="C352" s="4" t="n">
-        <v>0.2263888888888889</v>
+      <c r="C352" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D352" s="4" t="n">
-        <v>0.75</v>
+        <v>0.75625</v>
       </c>
       <c r="E352" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B353" s="3" t="n">
         <v>46245</v>
       </c>
       <c r="C353" s="4" t="n">
-        <v>0.3118055555555556</v>
-      </c>
-      <c r="D353" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.2381944444444444</v>
+      </c>
+      <c r="D353" s="4" t="n">
+        <v>0.7402777777777778</v>
       </c>
       <c r="E353" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B354" s="3" t="n">
         <v>46246</v>
       </c>
       <c r="C354" s="4" t="n">
-        <v>0.2986111111111111</v>
-      </c>
-      <c r="D354" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.2340277777777778</v>
+      </c>
+      <c r="D354" s="4" t="n">
+        <v>0.7493055555555556</v>
       </c>
       <c r="E354" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B355" s="3" t="n">
         <v>46247</v>
       </c>
       <c r="C355" s="4" t="n">
-        <v>0.3347222222222222</v>
-      </c>
-      <c r="D355" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.2465277777777778</v>
+      </c>
+      <c r="D355" s="4" t="n">
+        <v>0.7270833333333333</v>
       </c>
       <c r="E355" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B356" s="3" t="n">
         <v>46249</v>
       </c>
       <c r="C356" s="4" t="n">
-        <v>0.2354166666666667</v>
+        <v>0.2395833333333333</v>
       </c>
       <c r="D356" s="4" t="n">
-        <v>0.75</v>
+        <v>0.7388888888888889</v>
       </c>
       <c r="E356" s="2" t="inlineStr">
         <is>
@@ -7756,17 +7775,17 @@
     <row r="357">
       <c r="A357" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B357" s="3" t="n">
         <v>46250</v>
       </c>
       <c r="C357" s="4" t="n">
-        <v>0.325</v>
+        <v>0.2902777777777778</v>
       </c>
       <c r="D357" s="4" t="n">
-        <v>0.7722222222222223</v>
+        <v>0.7236111111111111</v>
       </c>
       <c r="E357" s="2" t="inlineStr">
         <is>
@@ -7777,17 +7796,17 @@
     <row r="358">
       <c r="A358" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B358" s="3" t="n">
         <v>46251</v>
       </c>
       <c r="C358" s="4" t="n">
-        <v>0.3979166666666666</v>
+        <v>0.2743055555555556</v>
       </c>
       <c r="D358" s="4" t="n">
-        <v>0.7680555555555556</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="E358" s="2" t="inlineStr">
         <is>
@@ -7798,17 +7817,17 @@
     <row r="359">
       <c r="A359" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B359" s="3" t="n">
         <v>46252</v>
       </c>
       <c r="C359" s="4" t="n">
-        <v>0.3083333333333333</v>
+        <v>0.2826388888888889</v>
       </c>
       <c r="D359" s="4" t="n">
-        <v>0.7583333333333333</v>
+        <v>0.7451388888888889</v>
       </c>
       <c r="E359" s="2" t="inlineStr">
         <is>
@@ -7819,17 +7838,17 @@
     <row r="360">
       <c r="A360" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B360" s="3" t="n">
         <v>46253</v>
       </c>
       <c r="C360" s="4" t="n">
-        <v>0.475</v>
+        <v>0.2763888888888889</v>
       </c>
       <c r="D360" s="4" t="n">
-        <v>0.7173611111111111</v>
+        <v>0.7298611111111111</v>
       </c>
       <c r="E360" s="2" t="inlineStr">
         <is>
@@ -7840,40 +7859,38 @@
     <row r="361">
       <c r="A361" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B361" s="3" t="n">
         <v>46254</v>
       </c>
       <c r="C361" s="4" t="n">
-        <v>0.3576388888888889</v>
-      </c>
-      <c r="D361" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.275</v>
+      </c>
+      <c r="D361" s="4" t="n">
+        <v>0.7256944444444444</v>
       </c>
       <c r="E361" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B362" s="3" t="n">
         <v>46256</v>
       </c>
       <c r="C362" s="4" t="n">
-        <v>0.2069444444444444</v>
+        <v>0.2805555555555556</v>
       </c>
       <c r="D362" s="4" t="n">
-        <v>0.7243055555555555</v>
+        <v>0.7513888888888889</v>
       </c>
       <c r="E362" s="2" t="inlineStr">
         <is>
@@ -7884,17 +7901,17 @@
     <row r="363">
       <c r="A363" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B363" s="3" t="n">
-        <v>46257</v>
+        <v>46261</v>
       </c>
       <c r="C363" s="4" t="n">
-        <v>0.25</v>
+        <v>0.24375</v>
       </c>
       <c r="D363" s="4" t="n">
-        <v>0.7493055555555556</v>
+        <v>0.6763888888888889</v>
       </c>
       <c r="E363" s="2" t="inlineStr">
         <is>
@@ -7905,17 +7922,17 @@
     <row r="364">
       <c r="A364" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B364" s="3" t="n">
-        <v>46258</v>
+        <v>46263</v>
       </c>
       <c r="C364" s="4" t="n">
-        <v>0.3263888888888889</v>
+        <v>0.2965277777777778</v>
       </c>
       <c r="D364" s="4" t="n">
-        <v>0.7388888888888889</v>
+        <v>0.7472222222222222</v>
       </c>
       <c r="E364" s="2" t="inlineStr">
         <is>
@@ -7926,17 +7943,17 @@
     <row r="365">
       <c r="A365" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B365" s="3" t="n">
-        <v>46259</v>
+        <v>46264</v>
       </c>
       <c r="C365" s="4" t="n">
-        <v>0.2763888888888889</v>
+        <v>0.2888888888888889</v>
       </c>
       <c r="D365" s="4" t="n">
-        <v>0.7548611111111111</v>
+        <v>0.75</v>
       </c>
       <c r="E365" s="2" t="inlineStr">
         <is>
@@ -7947,40 +7964,19 @@
     <row r="366">
       <c r="A366" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B366" s="3" t="n">
-        <v>46260</v>
+        <v>46265</v>
       </c>
       <c r="C366" s="4" t="n">
-        <v>0.3243055555555556</v>
+        <v>0.2909722222222222</v>
       </c>
       <c r="D366" s="4" t="n">
-        <v>0.7534722222222222</v>
+        <v>0.75</v>
       </c>
       <c r="E366" s="2" t="inlineStr">
-        <is>
-          <t>extra punch: 17:56</t>
-        </is>
-      </c>
-    </row>
-    <row r="367">
-      <c r="A367" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="B367" s="3" t="n">
-        <v>46261</v>
-      </c>
-      <c r="C367" s="4" t="n">
-        <v>0.2666666666666667</v>
-      </c>
-      <c r="D367" s="4" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="E367" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -7993,17 +7989,17 @@
         </is>
       </c>
       <c r="B368" s="3" t="n">
-        <v>46263</v>
+        <v>46235</v>
       </c>
       <c r="C368" s="4" t="n">
-        <v>0.2965277777777778</v>
+        <v>0.2381944444444444</v>
       </c>
       <c r="D368" s="4" t="n">
-        <v>0.7326388888888888</v>
+        <v>0.7458333333333333</v>
       </c>
       <c r="E368" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>last day of month; final record</t>
         </is>
       </c>
     </row>
@@ -8014,13 +8010,13 @@
         </is>
       </c>
       <c r="B369" s="3" t="n">
-        <v>46264</v>
+        <v>46236</v>
       </c>
       <c r="C369" s="4" t="n">
-        <v>0.2965277777777778</v>
+        <v>0.2958333333333333</v>
       </c>
       <c r="D369" s="4" t="n">
-        <v>0.75625</v>
+        <v>0.7430555555555556</v>
       </c>
       <c r="E369" s="2" t="inlineStr">
         <is>
@@ -8035,55 +8031,76 @@
         </is>
       </c>
       <c r="B370" s="3" t="n">
-        <v>46265</v>
+        <v>46237</v>
       </c>
       <c r="C370" s="4" t="n">
-        <v>0.2527777777777778</v>
+        <v>0.3034722222222222</v>
       </c>
       <c r="D370" s="4" t="n">
-        <v>0.7604166666666666</v>
+        <v>0.7159722222222222</v>
       </c>
       <c r="E370" s="2" t="inlineStr">
         <is>
-          <t>corrected from a clearer re-scan photo later in the album</t>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B371" s="3" t="n">
+        <v>46238</v>
+      </c>
+      <c r="C371" s="4" t="n">
+        <v>0.2763888888888889</v>
+      </c>
+      <c r="D371" s="4" t="n">
+        <v>0.7166666666666667</v>
+      </c>
+      <c r="E371" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B372" s="3" t="n">
-        <v>46235</v>
+        <v>46239</v>
       </c>
       <c r="C372" s="4" t="n">
-        <v>0.2590277777777778</v>
+        <v>0.3222222222222222</v>
       </c>
       <c r="D372" s="4" t="n">
-        <v>0.7319444444444444</v>
+        <v>0.7715277777777778</v>
       </c>
       <c r="E372" s="2" t="inlineStr">
         <is>
-          <t>last day of month; final record</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B373" s="3" t="n">
-        <v>46236</v>
+        <v>46240</v>
       </c>
       <c r="C373" s="4" t="n">
-        <v>0.2972222222222222</v>
+        <v>0.30625</v>
       </c>
       <c r="D373" s="4" t="n">
-        <v>0.7430555555555556</v>
+        <v>0.7590277777777777</v>
       </c>
       <c r="E373" s="2" t="inlineStr">
         <is>
@@ -8094,17 +8111,17 @@
     <row r="374">
       <c r="A374" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B374" s="3" t="n">
-        <v>46237</v>
+        <v>46242</v>
       </c>
       <c r="C374" s="4" t="n">
-        <v>0.2618055555555556</v>
+        <v>0.3055555555555556</v>
       </c>
       <c r="D374" s="4" t="n">
-        <v>0.7472222222222222</v>
+        <v>0.7604166666666666</v>
       </c>
       <c r="E374" s="2" t="inlineStr">
         <is>
@@ -8115,17 +8132,17 @@
     <row r="375">
       <c r="A375" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B375" s="3" t="n">
-        <v>46238</v>
+        <v>46243</v>
       </c>
       <c r="C375" s="4" t="n">
-        <v>0.4965277777777778</v>
+        <v>0.2798611111111111</v>
       </c>
       <c r="D375" s="4" t="n">
-        <v>0.7506944444444444</v>
+        <v>0.75</v>
       </c>
       <c r="E375" s="2" t="inlineStr">
         <is>
@@ -8136,17 +8153,17 @@
     <row r="376">
       <c r="A376" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B376" s="3" t="n">
-        <v>46239</v>
+        <v>46244</v>
       </c>
       <c r="C376" s="4" t="n">
-        <v>0.4743055555555555</v>
+        <v>0.2263888888888889</v>
       </c>
       <c r="D376" s="4" t="n">
-        <v>0.7722222222222223</v>
+        <v>0.75</v>
       </c>
       <c r="E376" s="2" t="inlineStr">
         <is>
@@ -8157,80 +8174,86 @@
     <row r="377">
       <c r="A377" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B377" s="3" t="n">
-        <v>46240</v>
+        <v>46245</v>
       </c>
       <c r="C377" s="4" t="n">
-        <v>0.2409722222222222</v>
-      </c>
-      <c r="D377" s="4" t="n">
-        <v>0.7625</v>
+        <v>0.3118055555555556</v>
+      </c>
+      <c r="D377" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E377" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B378" s="3" t="n">
-        <v>46242</v>
+        <v>46246</v>
       </c>
       <c r="C378" s="4" t="n">
-        <v>0.2201388888888889</v>
-      </c>
-      <c r="D378" s="4" t="n">
-        <v>0.7618055555555555</v>
+        <v>0.2986111111111111</v>
+      </c>
+      <c r="D378" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E378" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B379" s="3" t="n">
-        <v>46243</v>
+        <v>46247</v>
       </c>
       <c r="C379" s="4" t="n">
-        <v>0.2395833333333333</v>
-      </c>
-      <c r="D379" s="4" t="n">
-        <v>0.725</v>
+        <v>0.3347222222222222</v>
+      </c>
+      <c r="D379" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E379" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B380" s="3" t="n">
-        <v>46244</v>
+        <v>46249</v>
       </c>
       <c r="C380" s="4" t="n">
-        <v>0.2256944444444444</v>
+        <v>0.2354166666666667</v>
       </c>
       <c r="D380" s="4" t="n">
-        <v>0.7611111111111111</v>
+        <v>0.75</v>
       </c>
       <c r="E380" s="2" t="inlineStr">
         <is>
@@ -8241,17 +8264,17 @@
     <row r="381">
       <c r="A381" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B381" s="3" t="n">
-        <v>46245</v>
+        <v>46250</v>
       </c>
       <c r="C381" s="4" t="n">
-        <v>0.2375</v>
+        <v>0.325</v>
       </c>
       <c r="D381" s="4" t="n">
-        <v>0.7375</v>
+        <v>0.7722222222222223</v>
       </c>
       <c r="E381" s="2" t="inlineStr">
         <is>
@@ -8262,17 +8285,17 @@
     <row r="382">
       <c r="A382" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B382" s="3" t="n">
-        <v>46246</v>
+        <v>46251</v>
       </c>
       <c r="C382" s="4" t="n">
-        <v>0.2284722222222222</v>
+        <v>0.3979166666666666</v>
       </c>
       <c r="D382" s="4" t="n">
-        <v>0.7423611111111111</v>
+        <v>0.7680555555555556</v>
       </c>
       <c r="E382" s="2" t="inlineStr">
         <is>
@@ -8283,40 +8306,38 @@
     <row r="383">
       <c r="A383" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B383" s="3" t="n">
-        <v>46247</v>
+        <v>46252</v>
       </c>
       <c r="C383" s="4" t="n">
-        <v>0.4402777777777778</v>
-      </c>
-      <c r="D383" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.3083333333333333</v>
+      </c>
+      <c r="D383" s="4" t="n">
+        <v>0.7583333333333333</v>
       </c>
       <c r="E383" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B384" s="3" t="n">
-        <v>46249</v>
+        <v>46253</v>
       </c>
       <c r="C384" s="4" t="n">
-        <v>0.2354166666666667</v>
+        <v>0.475</v>
       </c>
       <c r="D384" s="4" t="n">
-        <v>0.7611111111111111</v>
+        <v>0.7173611111111111</v>
       </c>
       <c r="E384" s="2" t="inlineStr">
         <is>
@@ -8327,38 +8348,40 @@
     <row r="385">
       <c r="A385" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B385" s="3" t="n">
-        <v>46250</v>
+        <v>46254</v>
       </c>
       <c r="C385" s="4" t="n">
-        <v>0.2409722222222222</v>
-      </c>
-      <c r="D385" s="4" t="n">
-        <v>0.7381944444444445</v>
+        <v>0.3576388888888889</v>
+      </c>
+      <c r="D385" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E385" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B386" s="3" t="n">
-        <v>46251</v>
+        <v>46256</v>
       </c>
       <c r="C386" s="4" t="n">
-        <v>0.3416666666666667</v>
+        <v>0.2069444444444444</v>
       </c>
       <c r="D386" s="4" t="n">
-        <v>0.7326388888888888</v>
+        <v>0.7243055555555555</v>
       </c>
       <c r="E386" s="2" t="inlineStr">
         <is>
@@ -8369,17 +8392,17 @@
     <row r="387">
       <c r="A387" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B387" s="3" t="n">
-        <v>46252</v>
+        <v>46257</v>
       </c>
       <c r="C387" s="4" t="n">
-        <v>0.2916666666666667</v>
+        <v>0.25</v>
       </c>
       <c r="D387" s="4" t="n">
-        <v>0.7416666666666667</v>
+        <v>0.7493055555555556</v>
       </c>
       <c r="E387" s="2" t="inlineStr">
         <is>
@@ -8390,17 +8413,17 @@
     <row r="388">
       <c r="A388" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B388" s="3" t="n">
-        <v>46253</v>
+        <v>46258</v>
       </c>
       <c r="C388" s="4" t="n">
-        <v>0.2395833333333333</v>
+        <v>0.3263888888888889</v>
       </c>
       <c r="D388" s="4" t="n">
-        <v>0.7416666666666667</v>
+        <v>0.7388888888888889</v>
       </c>
       <c r="E388" s="2" t="inlineStr">
         <is>
@@ -8411,17 +8434,17 @@
     <row r="389">
       <c r="A389" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B389" s="3" t="n">
-        <v>46254</v>
+        <v>46259</v>
       </c>
       <c r="C389" s="4" t="n">
-        <v>0.2472222222222222</v>
+        <v>0.2763888888888889</v>
       </c>
       <c r="D389" s="4" t="n">
-        <v>0.7243055555555555</v>
+        <v>0.7548611111111111</v>
       </c>
       <c r="E389" s="2" t="inlineStr">
         <is>
@@ -8432,40 +8455,38 @@
     <row r="390">
       <c r="A390" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B390" s="3" t="n">
-        <v>46256</v>
+        <v>46260</v>
       </c>
       <c r="C390" s="4" t="n">
-        <v>0.2875</v>
-      </c>
-      <c r="D390" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.3243055555555556</v>
+      </c>
+      <c r="D390" s="4" t="n">
+        <v>0.7534722222222222</v>
       </c>
       <c r="E390" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>extra punch: 17:56</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B391" s="3" t="n">
-        <v>46257</v>
+        <v>46261</v>
       </c>
       <c r="C391" s="4" t="n">
-        <v>0.2479166666666667</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="D391" s="4" t="n">
-        <v>0.7618055555555555</v>
+        <v>0.75</v>
       </c>
       <c r="E391" s="2" t="inlineStr">
         <is>
@@ -8476,17 +8497,17 @@
     <row r="392">
       <c r="A392" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B392" s="3" t="n">
-        <v>46258</v>
+        <v>46263</v>
       </c>
       <c r="C392" s="4" t="n">
-        <v>0.2375</v>
+        <v>0.2965277777777778</v>
       </c>
       <c r="D392" s="4" t="n">
-        <v>0.7506944444444444</v>
+        <v>0.7326388888888888</v>
       </c>
       <c r="E392" s="2" t="inlineStr">
         <is>
@@ -8497,17 +8518,17 @@
     <row r="393">
       <c r="A393" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B393" s="3" t="n">
-        <v>46259</v>
+        <v>46264</v>
       </c>
       <c r="C393" s="4" t="n">
-        <v>0.2375</v>
+        <v>0.2965277777777778</v>
       </c>
       <c r="D393" s="4" t="n">
-        <v>0.7597222222222222</v>
+        <v>0.75625</v>
       </c>
       <c r="E393" s="2" t="inlineStr">
         <is>
@@ -8518,42 +8539,21 @@
     <row r="394">
       <c r="A394" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B394" s="3" t="n">
-        <v>46260</v>
+        <v>46265</v>
       </c>
       <c r="C394" s="4" t="n">
-        <v>0.2479166666666667</v>
+        <v>0.2527777777777778</v>
       </c>
       <c r="D394" s="4" t="n">
-        <v>0.7555555555555555</v>
+        <v>0.7604166666666666</v>
       </c>
       <c r="E394" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="395">
-      <c r="A395" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="B395" s="3" t="n">
-        <v>46261</v>
-      </c>
-      <c r="C395" s="4" t="n">
-        <v>0.2493055555555556</v>
-      </c>
-      <c r="D395" s="4" t="n">
-        <v>0.7944444444444444</v>
-      </c>
-      <c r="E395" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>corrected from a clearer re-scan photo later in the album</t>
         </is>
       </c>
     </row>
@@ -8564,19 +8564,17 @@
         </is>
       </c>
       <c r="B396" s="3" t="n">
-        <v>46262</v>
+        <v>46235</v>
       </c>
       <c r="C396" s="4" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="D396" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.2590277777777778</v>
+      </c>
+      <c r="D396" s="4" t="n">
+        <v>0.7319444444444444</v>
       </c>
       <c r="E396" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>last day of month; final record</t>
         </is>
       </c>
     </row>
@@ -8587,17 +8585,17 @@
         </is>
       </c>
       <c r="B397" s="3" t="n">
-        <v>46263</v>
+        <v>46236</v>
       </c>
       <c r="C397" s="4" t="n">
-        <v>0.2569444444444444</v>
+        <v>0.2972222222222222</v>
       </c>
       <c r="D397" s="4" t="n">
-        <v>0.7458333333333333</v>
+        <v>0.7430555555555556</v>
       </c>
       <c r="E397" s="2" t="inlineStr">
         <is>
-          <t>extra punch: 17:53</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -8608,13 +8606,13 @@
         </is>
       </c>
       <c r="B398" s="3" t="n">
-        <v>46264</v>
+        <v>46237</v>
       </c>
       <c r="C398" s="4" t="n">
-        <v>0.2590277777777778</v>
+        <v>0.2618055555555556</v>
       </c>
       <c r="D398" s="4" t="n">
-        <v>0.7541666666666667</v>
+        <v>0.7472222222222222</v>
       </c>
       <c r="E398" s="2" t="inlineStr">
         <is>
@@ -8629,55 +8627,76 @@
         </is>
       </c>
       <c r="B399" s="3" t="n">
-        <v>46265</v>
+        <v>46238</v>
       </c>
       <c r="C399" s="4" t="n">
-        <v>0.2777777777777778</v>
+        <v>0.4965277777777778</v>
       </c>
       <c r="D399" s="4" t="n">
-        <v>0.7513888888888889</v>
+        <v>0.7506944444444444</v>
       </c>
       <c r="E399" s="2" t="inlineStr">
         <is>
-          <t>corrected from a clearer re-scan photo later in the album</t>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B400" s="3" t="n">
+        <v>46239</v>
+      </c>
+      <c r="C400" s="4" t="n">
+        <v>0.4743055555555555</v>
+      </c>
+      <c r="D400" s="4" t="n">
+        <v>0.7722222222222223</v>
+      </c>
+      <c r="E400" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B401" s="3" t="n">
-        <v>46235</v>
+        <v>46240</v>
       </c>
       <c r="C401" s="4" t="n">
-        <v>0.2451388888888889</v>
+        <v>0.2409722222222222</v>
       </c>
       <c r="D401" s="4" t="n">
-        <v>0.7506944444444444</v>
+        <v>0.7625</v>
       </c>
       <c r="E401" s="2" t="inlineStr">
         <is>
-          <t>last day of month; final record</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B402" s="3" t="n">
-        <v>46236</v>
+        <v>46242</v>
       </c>
       <c r="C402" s="4" t="n">
-        <v>0.24375</v>
+        <v>0.2201388888888889</v>
       </c>
       <c r="D402" s="4" t="n">
-        <v>0.7520833333333333</v>
+        <v>0.7618055555555555</v>
       </c>
       <c r="E402" s="2" t="inlineStr">
         <is>
@@ -8688,17 +8707,17 @@
     <row r="403">
       <c r="A403" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B403" s="3" t="n">
-        <v>46237</v>
+        <v>46243</v>
       </c>
       <c r="C403" s="4" t="n">
-        <v>0.24375</v>
+        <v>0.2395833333333333</v>
       </c>
       <c r="D403" s="4" t="n">
-        <v>0.7527777777777778</v>
+        <v>0.725</v>
       </c>
       <c r="E403" s="2" t="inlineStr">
         <is>
@@ -8709,17 +8728,17 @@
     <row r="404">
       <c r="A404" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B404" s="3" t="n">
-        <v>46238</v>
+        <v>46244</v>
       </c>
       <c r="C404" s="4" t="n">
-        <v>0.2451388888888889</v>
+        <v>0.2256944444444444</v>
       </c>
       <c r="D404" s="4" t="n">
-        <v>0.7520833333333333</v>
+        <v>0.7611111111111111</v>
       </c>
       <c r="E404" s="2" t="inlineStr">
         <is>
@@ -8730,17 +8749,17 @@
     <row r="405">
       <c r="A405" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B405" s="3" t="n">
-        <v>46239</v>
+        <v>46245</v>
       </c>
       <c r="C405" s="4" t="n">
-        <v>0.2368055555555555</v>
+        <v>0.2375</v>
       </c>
       <c r="D405" s="4" t="n">
-        <v>0.7611111111111111</v>
+        <v>0.7375</v>
       </c>
       <c r="E405" s="2" t="inlineStr">
         <is>
@@ -8751,17 +8770,17 @@
     <row r="406">
       <c r="A406" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B406" s="3" t="n">
-        <v>46240</v>
+        <v>46246</v>
       </c>
       <c r="C406" s="4" t="n">
-        <v>0.2402777777777778</v>
+        <v>0.2284722222222222</v>
       </c>
       <c r="D406" s="4" t="n">
-        <v>0.7513888888888889</v>
+        <v>0.7423611111111111</v>
       </c>
       <c r="E406" s="2" t="inlineStr">
         <is>
@@ -8772,63 +8791,61 @@
     <row r="407">
       <c r="A407" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B407" s="3" t="n">
-        <v>46242</v>
+        <v>46247</v>
       </c>
       <c r="C407" s="4" t="n">
-        <v>0.2430555555555556</v>
-      </c>
-      <c r="D407" s="4" t="n">
-        <v>0.7548611111111111</v>
+        <v>0.4402777777777778</v>
+      </c>
+      <c r="D407" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E407" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B408" s="3" t="n">
-        <v>46246</v>
-      </c>
-      <c r="C408" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D408" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>46249</v>
+      </c>
+      <c r="C408" s="4" t="n">
+        <v>0.2354166666666667</v>
+      </c>
+      <c r="D408" s="4" t="n">
+        <v>0.7611111111111111</v>
       </c>
       <c r="E408" s="2" t="inlineStr">
         <is>
-          <t>PLEASE VERIFY: check-in/out times not captured (gap between source photos)</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B409" s="3" t="n">
-        <v>46247</v>
+        <v>46250</v>
       </c>
       <c r="C409" s="4" t="n">
-        <v>0.2444444444444444</v>
+        <v>0.2409722222222222</v>
       </c>
       <c r="D409" s="4" t="n">
-        <v>0.7576388888888889</v>
+        <v>0.7381944444444445</v>
       </c>
       <c r="E409" s="2" t="inlineStr">
         <is>
@@ -8839,17 +8856,17 @@
     <row r="410">
       <c r="A410" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B410" s="3" t="n">
-        <v>46249</v>
+        <v>46251</v>
       </c>
       <c r="C410" s="4" t="n">
-        <v>0.2381944444444444</v>
+        <v>0.3416666666666667</v>
       </c>
       <c r="D410" s="4" t="n">
-        <v>0.7513888888888889</v>
+        <v>0.7326388888888888</v>
       </c>
       <c r="E410" s="2" t="inlineStr">
         <is>
@@ -8860,17 +8877,17 @@
     <row r="411">
       <c r="A411" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B411" s="3" t="n">
-        <v>46250</v>
+        <v>46252</v>
       </c>
       <c r="C411" s="4" t="n">
-        <v>0.2354166666666667</v>
+        <v>0.2916666666666667</v>
       </c>
       <c r="D411" s="4" t="n">
-        <v>0.7520833333333333</v>
+        <v>0.7416666666666667</v>
       </c>
       <c r="E411" s="2" t="inlineStr">
         <is>
@@ -8881,17 +8898,17 @@
     <row r="412">
       <c r="A412" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B412" s="3" t="n">
-        <v>46251</v>
+        <v>46253</v>
       </c>
       <c r="C412" s="4" t="n">
         <v>0.2395833333333333</v>
       </c>
       <c r="D412" s="4" t="n">
-        <v>0.7541666666666667</v>
+        <v>0.7416666666666667</v>
       </c>
       <c r="E412" s="2" t="inlineStr">
         <is>
@@ -8902,17 +8919,17 @@
     <row r="413">
       <c r="A413" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B413" s="3" t="n">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="C413" s="4" t="n">
-        <v>0.2451388888888889</v>
+        <v>0.2472222222222222</v>
       </c>
       <c r="D413" s="4" t="n">
-        <v>0.7527777777777778</v>
+        <v>0.7243055555555555</v>
       </c>
       <c r="E413" s="2" t="inlineStr">
         <is>
@@ -8923,38 +8940,40 @@
     <row r="414">
       <c r="A414" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B414" s="3" t="n">
-        <v>46253</v>
+        <v>46256</v>
       </c>
       <c r="C414" s="4" t="n">
-        <v>0.2423611111111111</v>
-      </c>
-      <c r="D414" s="4" t="n">
-        <v>0.7506944444444444</v>
+        <v>0.2875</v>
+      </c>
+      <c r="D414" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E414" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B415" s="3" t="n">
-        <v>46254</v>
+        <v>46257</v>
       </c>
       <c r="C415" s="4" t="n">
-        <v>0.2402777777777778</v>
+        <v>0.2479166666666667</v>
       </c>
       <c r="D415" s="4" t="n">
-        <v>0.7520833333333333</v>
+        <v>0.7618055555555555</v>
       </c>
       <c r="E415" s="2" t="inlineStr">
         <is>
@@ -8965,17 +8984,17 @@
     <row r="416">
       <c r="A416" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B416" s="3" t="n">
-        <v>46256</v>
+        <v>46258</v>
       </c>
       <c r="C416" s="4" t="n">
-        <v>0.2402777777777778</v>
+        <v>0.2375</v>
       </c>
       <c r="D416" s="4" t="n">
-        <v>0.75</v>
+        <v>0.7506944444444444</v>
       </c>
       <c r="E416" s="2" t="inlineStr">
         <is>
@@ -8986,17 +9005,17 @@
     <row r="417">
       <c r="A417" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B417" s="3" t="n">
-        <v>46257</v>
+        <v>46259</v>
       </c>
       <c r="C417" s="4" t="n">
-        <v>0.2458333333333333</v>
+        <v>0.2375</v>
       </c>
       <c r="D417" s="4" t="n">
-        <v>0.7527777777777778</v>
+        <v>0.7597222222222222</v>
       </c>
       <c r="E417" s="2" t="inlineStr">
         <is>
@@ -9007,17 +9026,17 @@
     <row r="418">
       <c r="A418" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B418" s="3" t="n">
-        <v>46258</v>
+        <v>46260</v>
       </c>
       <c r="C418" s="4" t="n">
-        <v>0.2347222222222222</v>
+        <v>0.2479166666666667</v>
       </c>
       <c r="D418" s="4" t="n">
-        <v>0.7520833333333333</v>
+        <v>0.7555555555555555</v>
       </c>
       <c r="E418" s="2" t="inlineStr">
         <is>
@@ -9028,17 +9047,17 @@
     <row r="419">
       <c r="A419" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B419" s="3" t="n">
-        <v>46259</v>
+        <v>46261</v>
       </c>
       <c r="C419" s="4" t="n">
-        <v>0.2368055555555555</v>
+        <v>0.2493055555555556</v>
       </c>
       <c r="D419" s="4" t="n">
-        <v>0.7506944444444444</v>
+        <v>0.7944444444444444</v>
       </c>
       <c r="E419" s="2" t="inlineStr">
         <is>
@@ -9049,59 +9068,61 @@
     <row r="420">
       <c r="A420" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B420" s="3" t="n">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="C420" s="4" t="n">
-        <v>0.2465277777777778</v>
-      </c>
-      <c r="D420" s="4" t="n">
-        <v>0.7555555555555555</v>
+        <v>0.25</v>
+      </c>
+      <c r="D420" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E420" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B421" s="3" t="n">
-        <v>46261</v>
+        <v>46263</v>
       </c>
       <c r="C421" s="4" t="n">
-        <v>0.2472222222222222</v>
+        <v>0.2569444444444444</v>
       </c>
       <c r="D421" s="4" t="n">
-        <v>0.7513888888888889</v>
+        <v>0.7458333333333333</v>
       </c>
       <c r="E421" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>extra punch: 17:53</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B422" s="3" t="n">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="C422" s="4" t="n">
-        <v>0.2444444444444444</v>
+        <v>0.2590277777777778</v>
       </c>
       <c r="D422" s="4" t="n">
-        <v>0.7548611111111111</v>
+        <v>0.7541666666666667</v>
       </c>
       <c r="E422" s="2" t="inlineStr">
         <is>
@@ -9112,80 +9133,80 @@
     <row r="423">
       <c r="A423" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B423" s="3" t="n">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="C423" s="4" t="n">
-        <v>0.2423611111111111</v>
+        <v>0.2777777777777778</v>
       </c>
       <c r="D423" s="4" t="n">
         <v>0.7513888888888889</v>
       </c>
       <c r="E423" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="424">
-      <c r="A424" s="2" t="inlineStr">
+          <t>corrected from a clearer re-scan photo later in the album</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" s="2" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="B424" s="3" t="n">
-        <v>46265</v>
-      </c>
-      <c r="C424" s="4" t="n">
-        <v>0.2361111111111111</v>
-      </c>
-      <c r="D424" s="4" t="n">
-        <v>0.7520833333333333</v>
-      </c>
-      <c r="E424" s="2" t="inlineStr">
-        <is>
-          <t>corrected from a clearer re-scan photo later in the album</t>
+      <c r="B425" s="3" t="n">
+        <v>46235</v>
+      </c>
+      <c r="C425" s="4" t="n">
+        <v>0.2451388888888889</v>
+      </c>
+      <c r="D425" s="4" t="n">
+        <v>0.7506944444444444</v>
+      </c>
+      <c r="E425" s="2" t="inlineStr">
+        <is>
+          <t>last day of month; final record</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B426" s="3" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="C426" s="4" t="n">
-        <v>0.275</v>
+        <v>0.24375</v>
       </c>
       <c r="D426" s="4" t="n">
-        <v>0.7854166666666667</v>
+        <v>0.7520833333333333</v>
       </c>
       <c r="E426" s="2" t="inlineStr">
         <is>
-          <t>last day of month; final record</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B427" s="3" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="C427" s="4" t="n">
-        <v>0.2722222222222222</v>
+        <v>0.24375</v>
       </c>
       <c r="D427" s="4" t="n">
-        <v>0.7722222222222223</v>
+        <v>0.7527777777777778</v>
       </c>
       <c r="E427" s="2" t="inlineStr">
         <is>
@@ -9196,17 +9217,17 @@
     <row r="428">
       <c r="A428" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B428" s="3" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C428" s="4" t="n">
         <v>0.2451388888888889</v>
       </c>
       <c r="D428" s="4" t="n">
-        <v>0.7201388888888889</v>
+        <v>0.7520833333333333</v>
       </c>
       <c r="E428" s="2" t="inlineStr">
         <is>
@@ -9217,17 +9238,17 @@
     <row r="429">
       <c r="A429" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B429" s="3" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C429" s="4" t="n">
-        <v>0.2729166666666666</v>
+        <v>0.2368055555555555</v>
       </c>
       <c r="D429" s="4" t="n">
-        <v>0.7527777777777778</v>
+        <v>0.7611111111111111</v>
       </c>
       <c r="E429" s="2" t="inlineStr">
         <is>
@@ -9238,17 +9259,17 @@
     <row r="430">
       <c r="A430" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B430" s="3" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C430" s="4" t="n">
-        <v>0.2756944444444445</v>
+        <v>0.2402777777777778</v>
       </c>
       <c r="D430" s="4" t="n">
-        <v>0.7152777777777778</v>
+        <v>0.7513888888888889</v>
       </c>
       <c r="E430" s="2" t="inlineStr">
         <is>
@@ -9259,61 +9280,63 @@
     <row r="431">
       <c r="A431" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B431" s="3" t="n">
-        <v>46240</v>
+        <v>46242</v>
       </c>
       <c r="C431" s="4" t="n">
-        <v>0.2715277777777778</v>
-      </c>
-      <c r="D431" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.2430555555555556</v>
+      </c>
+      <c r="D431" s="4" t="n">
+        <v>0.7548611111111111</v>
       </c>
       <c r="E431" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B432" s="3" t="n">
-        <v>46242</v>
-      </c>
-      <c r="C432" s="4" t="n">
-        <v>0.2388888888888889</v>
-      </c>
-      <c r="D432" s="4" t="n">
-        <v>0.6965277777777777</v>
+        <v>46246</v>
+      </c>
+      <c r="C432" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D432" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E432" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>PLEASE VERIFY: check-in/out times not captured (gap between source photos)</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B433" s="3" t="n">
-        <v>46243</v>
+        <v>46247</v>
       </c>
       <c r="C433" s="4" t="n">
-        <v>0.2451388888888889</v>
+        <v>0.2444444444444444</v>
       </c>
       <c r="D433" s="4" t="n">
-        <v>0.7694444444444445</v>
+        <v>0.7576388888888889</v>
       </c>
       <c r="E433" s="2" t="inlineStr">
         <is>
@@ -9324,38 +9347,38 @@
     <row r="434">
       <c r="A434" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B434" s="3" t="n">
-        <v>46244</v>
+        <v>46249</v>
       </c>
       <c r="C434" s="4" t="n">
-        <v>0.2298611111111111</v>
+        <v>0.2381944444444444</v>
       </c>
       <c r="D434" s="4" t="n">
-        <v>0.75625</v>
+        <v>0.7513888888888889</v>
       </c>
       <c r="E434" s="2" t="inlineStr">
         <is>
-          <t>extra punch: 06:48</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B435" s="3" t="n">
-        <v>46245</v>
+        <v>46250</v>
       </c>
       <c r="C435" s="4" t="n">
-        <v>0.275</v>
+        <v>0.2354166666666667</v>
       </c>
       <c r="D435" s="4" t="n">
-        <v>0.7618055555555555</v>
+        <v>0.7520833333333333</v>
       </c>
       <c r="E435" s="2" t="inlineStr">
         <is>
@@ -9366,17 +9389,17 @@
     <row r="436">
       <c r="A436" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B436" s="3" t="n">
-        <v>46246</v>
+        <v>46251</v>
       </c>
       <c r="C436" s="4" t="n">
-        <v>0.2694444444444444</v>
+        <v>0.2395833333333333</v>
       </c>
       <c r="D436" s="4" t="n">
-        <v>0.7222222222222222</v>
+        <v>0.7541666666666667</v>
       </c>
       <c r="E436" s="2" t="inlineStr">
         <is>
@@ -9387,17 +9410,17 @@
     <row r="437">
       <c r="A437" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B437" s="3" t="n">
-        <v>46247</v>
+        <v>46252</v>
       </c>
       <c r="C437" s="4" t="n">
-        <v>0.3409722222222222</v>
+        <v>0.2451388888888889</v>
       </c>
       <c r="D437" s="4" t="n">
-        <v>0.7583333333333333</v>
+        <v>0.7527777777777778</v>
       </c>
       <c r="E437" s="2" t="inlineStr">
         <is>
@@ -9408,17 +9431,17 @@
     <row r="438">
       <c r="A438" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B438" s="3" t="n">
-        <v>46249</v>
+        <v>46253</v>
       </c>
       <c r="C438" s="4" t="n">
-        <v>0.2680555555555555</v>
+        <v>0.2423611111111111</v>
       </c>
       <c r="D438" s="4" t="n">
-        <v>0.7625</v>
+        <v>0.7506944444444444</v>
       </c>
       <c r="E438" s="2" t="inlineStr">
         <is>
@@ -9429,17 +9452,17 @@
     <row r="439">
       <c r="A439" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B439" s="3" t="n">
-        <v>46250</v>
+        <v>46254</v>
       </c>
       <c r="C439" s="4" t="n">
-        <v>0.3416666666666667</v>
+        <v>0.2402777777777778</v>
       </c>
       <c r="D439" s="4" t="n">
-        <v>0.7173611111111111</v>
+        <v>0.7520833333333333</v>
       </c>
       <c r="E439" s="2" t="inlineStr">
         <is>
@@ -9450,17 +9473,17 @@
     <row r="440">
       <c r="A440" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B440" s="3" t="n">
-        <v>46251</v>
+        <v>46256</v>
       </c>
       <c r="C440" s="4" t="n">
-        <v>0.3104166666666667</v>
+        <v>0.2402777777777778</v>
       </c>
       <c r="D440" s="4" t="n">
-        <v>0.7069444444444445</v>
+        <v>0.75</v>
       </c>
       <c r="E440" s="2" t="inlineStr">
         <is>
@@ -9471,17 +9494,17 @@
     <row r="441">
       <c r="A441" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B441" s="3" t="n">
-        <v>46252</v>
+        <v>46257</v>
       </c>
       <c r="C441" s="4" t="n">
-        <v>0.3659722222222222</v>
+        <v>0.2458333333333333</v>
       </c>
       <c r="D441" s="4" t="n">
-        <v>0.7208333333333333</v>
+        <v>0.7527777777777778</v>
       </c>
       <c r="E441" s="2" t="inlineStr">
         <is>
@@ -9492,17 +9515,17 @@
     <row r="442">
       <c r="A442" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B442" s="3" t="n">
-        <v>46253</v>
+        <v>46258</v>
       </c>
       <c r="C442" s="4" t="n">
-        <v>0.2944444444444445</v>
+        <v>0.2347222222222222</v>
       </c>
       <c r="D442" s="4" t="n">
-        <v>0.7305555555555555</v>
+        <v>0.7520833333333333</v>
       </c>
       <c r="E442" s="2" t="inlineStr">
         <is>
@@ -9513,17 +9536,17 @@
     <row r="443">
       <c r="A443" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B443" s="3" t="n">
-        <v>46254</v>
+        <v>46259</v>
       </c>
       <c r="C443" s="4" t="n">
-        <v>0.4298611111111111</v>
+        <v>0.2368055555555555</v>
       </c>
       <c r="D443" s="4" t="n">
-        <v>0.70625</v>
+        <v>0.7506944444444444</v>
       </c>
       <c r="E443" s="2" t="inlineStr">
         <is>
@@ -9534,17 +9557,17 @@
     <row r="444">
       <c r="A444" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B444" s="3" t="n">
-        <v>46256</v>
+        <v>46260</v>
       </c>
       <c r="C444" s="4" t="n">
-        <v>0.2888888888888889</v>
+        <v>0.2465277777777778</v>
       </c>
       <c r="D444" s="4" t="n">
-        <v>0.7083333333333334</v>
+        <v>0.7555555555555555</v>
       </c>
       <c r="E444" s="2" t="inlineStr">
         <is>
@@ -9555,17 +9578,17 @@
     <row r="445">
       <c r="A445" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B445" s="3" t="n">
-        <v>46257</v>
+        <v>46261</v>
       </c>
       <c r="C445" s="4" t="n">
-        <v>0.2444444444444444</v>
+        <v>0.2472222222222222</v>
       </c>
       <c r="D445" s="4" t="n">
-        <v>0.7076388888888889</v>
+        <v>0.7513888888888889</v>
       </c>
       <c r="E445" s="2" t="inlineStr">
         <is>
@@ -9576,17 +9599,17 @@
     <row r="446">
       <c r="A446" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B446" s="3" t="n">
-        <v>46258</v>
+        <v>46263</v>
       </c>
       <c r="C446" s="4" t="n">
-        <v>0.2784722222222222</v>
+        <v>0.2444444444444444</v>
       </c>
       <c r="D446" s="4" t="n">
-        <v>0.7055555555555556</v>
+        <v>0.7548611111111111</v>
       </c>
       <c r="E446" s="2" t="inlineStr">
         <is>
@@ -9597,17 +9620,17 @@
     <row r="447">
       <c r="A447" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B447" s="3" t="n">
-        <v>46259</v>
+        <v>46264</v>
       </c>
       <c r="C447" s="4" t="n">
-        <v>0.2854166666666667</v>
+        <v>0.2423611111111111</v>
       </c>
       <c r="D447" s="4" t="n">
-        <v>0.7222222222222222</v>
+        <v>0.7513888888888889</v>
       </c>
       <c r="E447" s="2" t="inlineStr">
         <is>
@@ -9618,42 +9641,21 @@
     <row r="448">
       <c r="A448" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B448" s="3" t="n">
-        <v>46260</v>
+        <v>46265</v>
       </c>
       <c r="C448" s="4" t="n">
-        <v>0.2375</v>
+        <v>0.2361111111111111</v>
       </c>
       <c r="D448" s="4" t="n">
-        <v>0.7152777777777778</v>
+        <v>0.7520833333333333</v>
       </c>
       <c r="E448" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="449">
-      <c r="A449" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="B449" s="3" t="n">
-        <v>46261</v>
-      </c>
-      <c r="C449" s="4" t="n">
-        <v>0.4881944444444444</v>
-      </c>
-      <c r="D449" s="4" t="n">
-        <v>0.7111111111111111</v>
-      </c>
-      <c r="E449" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>corrected from a clearer re-scan photo later in the album</t>
         </is>
       </c>
     </row>
@@ -9664,17 +9666,17 @@
         </is>
       </c>
       <c r="B450" s="3" t="n">
-        <v>46263</v>
+        <v>46235</v>
       </c>
       <c r="C450" s="4" t="n">
-        <v>0.2513888888888889</v>
+        <v>0.275</v>
       </c>
       <c r="D450" s="4" t="n">
-        <v>0.7104166666666667</v>
+        <v>0.7854166666666667</v>
       </c>
       <c r="E450" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>last day of month; final record</t>
         </is>
       </c>
     </row>
@@ -9685,13 +9687,13 @@
         </is>
       </c>
       <c r="B451" s="3" t="n">
-        <v>46264</v>
+        <v>46236</v>
       </c>
       <c r="C451" s="4" t="n">
-        <v>0.2958333333333333</v>
+        <v>0.2722222222222222</v>
       </c>
       <c r="D451" s="4" t="n">
-        <v>0.7215277777777778</v>
+        <v>0.7722222222222223</v>
       </c>
       <c r="E451" s="2" t="inlineStr">
         <is>
@@ -9706,59 +9708,78 @@
         </is>
       </c>
       <c r="B452" s="3" t="n">
-        <v>46265</v>
-      </c>
-      <c r="C452" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>46237</v>
+      </c>
+      <c r="C452" s="4" t="n">
+        <v>0.2451388888888889</v>
       </c>
       <c r="D452" s="4" t="n">
-        <v>0.7097222222222223</v>
+        <v>0.7201388888888889</v>
       </c>
       <c r="E452" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B453" s="3" t="n">
+        <v>46238</v>
+      </c>
+      <c r="C453" s="4" t="n">
+        <v>0.2729166666666666</v>
+      </c>
+      <c r="D453" s="4" t="n">
+        <v>0.7527777777777778</v>
+      </c>
+      <c r="E453" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B454" s="3" t="n">
-        <v>46235</v>
+        <v>46239</v>
       </c>
       <c r="C454" s="4" t="n">
-        <v>0.3305555555555555</v>
+        <v>0.2756944444444445</v>
       </c>
       <c r="D454" s="4" t="n">
-        <v>0.7347222222222223</v>
+        <v>0.7152777777777778</v>
       </c>
       <c r="E454" s="2" t="inlineStr">
         <is>
-          <t>last day of month; final record</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="A455" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B455" s="3" t="n">
-        <v>46236</v>
-      </c>
-      <c r="C455" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D455" s="4" t="n">
-        <v>0.3583333333333333</v>
+        <v>46240</v>
+      </c>
+      <c r="C455" s="4" t="n">
+        <v>0.2715277777777778</v>
+      </c>
+      <c r="D455" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E455" s="2" t="inlineStr">
         <is>
@@ -9769,17 +9790,17 @@
     <row r="456">
       <c r="A456" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B456" s="3" t="n">
-        <v>46237</v>
+        <v>46242</v>
       </c>
       <c r="C456" s="4" t="n">
-        <v>0.3291666666666667</v>
+        <v>0.2388888888888889</v>
       </c>
       <c r="D456" s="4" t="n">
-        <v>0.7111111111111111</v>
+        <v>0.6965277777777777</v>
       </c>
       <c r="E456" s="2" t="inlineStr">
         <is>
@@ -9790,17 +9811,17 @@
     <row r="457">
       <c r="A457" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B457" s="3" t="n">
-        <v>46238</v>
+        <v>46243</v>
       </c>
       <c r="C457" s="4" t="n">
-        <v>0.3305555555555555</v>
+        <v>0.2451388888888889</v>
       </c>
       <c r="D457" s="4" t="n">
-        <v>0.7263888888888889</v>
+        <v>0.7694444444444445</v>
       </c>
       <c r="E457" s="2" t="inlineStr">
         <is>
@@ -9811,40 +9832,38 @@
     <row r="458">
       <c r="A458" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B458" s="3" t="n">
-        <v>46239</v>
-      </c>
-      <c r="C458" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>46244</v>
+      </c>
+      <c r="C458" s="4" t="n">
+        <v>0.2298611111111111</v>
       </c>
       <c r="D458" s="4" t="n">
-        <v>0.7715277777777778</v>
+        <v>0.75625</v>
       </c>
       <c r="E458" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>extra punch: 06:48</t>
         </is>
       </c>
     </row>
     <row r="459">
       <c r="A459" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B459" s="3" t="n">
-        <v>46240</v>
+        <v>46245</v>
       </c>
       <c r="C459" s="4" t="n">
-        <v>0.3986111111111111</v>
+        <v>0.275</v>
       </c>
       <c r="D459" s="4" t="n">
-        <v>0.7277777777777777</v>
+        <v>0.7618055555555555</v>
       </c>
       <c r="E459" s="2" t="inlineStr">
         <is>
@@ -9855,17 +9874,17 @@
     <row r="460">
       <c r="A460" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B460" s="3" t="n">
-        <v>46242</v>
+        <v>46246</v>
       </c>
       <c r="C460" s="4" t="n">
-        <v>0.2791666666666667</v>
+        <v>0.2694444444444444</v>
       </c>
       <c r="D460" s="4" t="n">
-        <v>0.7284722222222222</v>
+        <v>0.7222222222222222</v>
       </c>
       <c r="E460" s="2" t="inlineStr">
         <is>
@@ -9876,17 +9895,17 @@
     <row r="461">
       <c r="A461" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B461" s="3" t="n">
-        <v>46243</v>
+        <v>46247</v>
       </c>
       <c r="C461" s="4" t="n">
-        <v>0.2784722222222222</v>
+        <v>0.3409722222222222</v>
       </c>
       <c r="D461" s="4" t="n">
-        <v>0.7555555555555555</v>
+        <v>0.7583333333333333</v>
       </c>
       <c r="E461" s="2" t="inlineStr">
         <is>
@@ -9897,17 +9916,17 @@
     <row r="462">
       <c r="A462" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B462" s="3" t="n">
-        <v>46244</v>
+        <v>46249</v>
       </c>
       <c r="C462" s="4" t="n">
-        <v>0.2875</v>
+        <v>0.2680555555555555</v>
       </c>
       <c r="D462" s="4" t="n">
-        <v>0.7479166666666667</v>
+        <v>0.7625</v>
       </c>
       <c r="E462" s="2" t="inlineStr">
         <is>
@@ -9918,17 +9937,17 @@
     <row r="463">
       <c r="A463" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B463" s="3" t="n">
-        <v>46245</v>
+        <v>46250</v>
       </c>
       <c r="C463" s="4" t="n">
-        <v>0.3</v>
+        <v>0.3416666666666667</v>
       </c>
       <c r="D463" s="4" t="n">
-        <v>0.7465277777777778</v>
+        <v>0.7173611111111111</v>
       </c>
       <c r="E463" s="2" t="inlineStr">
         <is>
@@ -9939,80 +9958,80 @@
     <row r="464">
       <c r="A464" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B464" s="3" t="n">
-        <v>46246</v>
+        <v>46251</v>
       </c>
       <c r="C464" s="4" t="n">
-        <v>0.2548611111111111</v>
+        <v>0.3104166666666667</v>
       </c>
       <c r="D464" s="4" t="n">
-        <v>0.7222222222222222</v>
+        <v>0.7069444444444445</v>
       </c>
       <c r="E464" s="2" t="inlineStr">
         <is>
-          <t>extra punches: 07:44 06:16</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="465">
       <c r="A465" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B465" s="3" t="n">
-        <v>46247</v>
+        <v>46252</v>
       </c>
       <c r="C465" s="4" t="n">
-        <v>0.3388888888888889</v>
+        <v>0.3659722222222222</v>
       </c>
       <c r="D465" s="4" t="n">
-        <v>0.7236111111111111</v>
+        <v>0.7208333333333333</v>
       </c>
       <c r="E465" s="2" t="inlineStr">
         <is>
-          <t>extra punch: 17:21</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="466">
       <c r="A466" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B466" s="3" t="n">
-        <v>46249</v>
+        <v>46253</v>
       </c>
       <c r="C466" s="4" t="n">
-        <v>0.2423611111111111</v>
+        <v>0.2944444444444445</v>
       </c>
       <c r="D466" s="4" t="n">
-        <v>0.7270833333333333</v>
+        <v>0.7305555555555555</v>
       </c>
       <c r="E466" s="2" t="inlineStr">
         <is>
-          <t>extra punches: 17:27 07:28</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="467">
       <c r="A467" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B467" s="3" t="n">
-        <v>46250</v>
+        <v>46254</v>
       </c>
       <c r="C467" s="4" t="n">
-        <v>0.3409722222222222</v>
+        <v>0.4298611111111111</v>
       </c>
       <c r="D467" s="4" t="n">
-        <v>0.7104166666666667</v>
+        <v>0.70625</v>
       </c>
       <c r="E467" s="2" t="inlineStr">
         <is>
@@ -10023,17 +10042,17 @@
     <row r="468">
       <c r="A468" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B468" s="3" t="n">
-        <v>46251</v>
+        <v>46256</v>
       </c>
       <c r="C468" s="4" t="n">
-        <v>0.2833333333333333</v>
+        <v>0.2888888888888889</v>
       </c>
       <c r="D468" s="4" t="n">
-        <v>0.7326388888888888</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="E468" s="2" t="inlineStr">
         <is>
@@ -10044,17 +10063,17 @@
     <row r="469">
       <c r="A469" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B469" s="3" t="n">
-        <v>46252</v>
+        <v>46257</v>
       </c>
       <c r="C469" s="4" t="n">
-        <v>0.28125</v>
+        <v>0.2444444444444444</v>
       </c>
       <c r="D469" s="4" t="n">
-        <v>0.7645833333333333</v>
+        <v>0.7076388888888889</v>
       </c>
       <c r="E469" s="2" t="inlineStr">
         <is>
@@ -10065,84 +10084,80 @@
     <row r="470">
       <c r="A470" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B470" s="3" t="n">
-        <v>46253</v>
+        <v>46258</v>
       </c>
       <c r="C470" s="4" t="n">
-        <v>0.3166666666666667</v>
+        <v>0.2784722222222222</v>
       </c>
       <c r="D470" s="4" t="n">
-        <v>0.74375</v>
+        <v>0.7055555555555556</v>
       </c>
       <c r="E470" s="2" t="inlineStr">
         <is>
-          <t>extra punch: 08:01</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="471">
       <c r="A471" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B471" s="3" t="n">
-        <v>46254</v>
+        <v>46259</v>
       </c>
       <c r="C471" s="4" t="n">
-        <v>0.2868055555555555</v>
-      </c>
-      <c r="D471" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.2854166666666667</v>
+      </c>
+      <c r="D471" s="4" t="n">
+        <v>0.7222222222222222</v>
       </c>
       <c r="E471" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="A472" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B472" s="3" t="n">
-        <v>46256</v>
-      </c>
-      <c r="C472" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>46260</v>
+      </c>
+      <c r="C472" s="4" t="n">
+        <v>0.2375</v>
       </c>
       <c r="D472" s="4" t="n">
-        <v>0.74375</v>
+        <v>0.7152777777777778</v>
       </c>
       <c r="E472" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="473">
       <c r="A473" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B473" s="3" t="n">
-        <v>46257</v>
+        <v>46261</v>
       </c>
       <c r="C473" s="4" t="n">
-        <v>0.2548611111111111</v>
+        <v>0.4881944444444444</v>
       </c>
       <c r="D473" s="4" t="n">
-        <v>0.7569444444444444</v>
+        <v>0.7111111111111111</v>
       </c>
       <c r="E473" s="2" t="inlineStr">
         <is>
@@ -10153,40 +10168,38 @@
     <row r="474">
       <c r="A474" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B474" s="3" t="n">
-        <v>46258</v>
-      </c>
-      <c r="C474" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>46263</v>
+      </c>
+      <c r="C474" s="4" t="n">
+        <v>0.2513888888888889</v>
       </c>
       <c r="D474" s="4" t="n">
-        <v>0.7506944444444444</v>
+        <v>0.7104166666666667</v>
       </c>
       <c r="E474" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="475">
       <c r="A475" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B475" s="3" t="n">
-        <v>46259</v>
+        <v>46264</v>
       </c>
       <c r="C475" s="4" t="n">
-        <v>0.2868055555555555</v>
+        <v>0.2958333333333333</v>
       </c>
       <c r="D475" s="4" t="n">
-        <v>0.6895833333333333</v>
+        <v>0.7215277777777778</v>
       </c>
       <c r="E475" s="2" t="inlineStr">
         <is>
@@ -10197,11 +10210,11 @@
     <row r="476">
       <c r="A476" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B476" s="3" t="n">
-        <v>46260</v>
+        <v>46265</v>
       </c>
       <c r="C476" s="2" t="inlineStr">
         <is>
@@ -10209,32 +10222,11 @@
         </is>
       </c>
       <c r="D476" s="4" t="n">
-        <v>0.6986111111111111</v>
+        <v>0.7097222222222223</v>
       </c>
       <c r="E476" s="2" t="inlineStr">
         <is>
           <t>single punch only</t>
-        </is>
-      </c>
-    </row>
-    <row r="477">
-      <c r="A477" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="B477" s="3" t="n">
-        <v>46261</v>
-      </c>
-      <c r="C477" s="4" t="n">
-        <v>0.2833333333333333</v>
-      </c>
-      <c r="D477" s="4" t="n">
-        <v>0.8645833333333334</v>
-      </c>
-      <c r="E477" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
         </is>
       </c>
     </row>
@@ -10245,19 +10237,17 @@
         </is>
       </c>
       <c r="B478" s="3" t="n">
-        <v>46263</v>
-      </c>
-      <c r="C478" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>46235</v>
+      </c>
+      <c r="C478" s="4" t="n">
+        <v>0.3305555555555555</v>
       </c>
       <c r="D478" s="4" t="n">
-        <v>0.7291666666666666</v>
+        <v>0.7347222222222223</v>
       </c>
       <c r="E478" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>last day of month; final record</t>
         </is>
       </c>
     </row>
@@ -10268,17 +10258,19 @@
         </is>
       </c>
       <c r="B479" s="3" t="n">
-        <v>46264</v>
-      </c>
-      <c r="C479" s="4" t="n">
-        <v>0.2798611111111111</v>
+        <v>46236</v>
+      </c>
+      <c r="C479" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D479" s="4" t="n">
-        <v>0.7472222222222222</v>
+        <v>0.3583333333333333</v>
       </c>
       <c r="E479" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
@@ -10289,55 +10281,78 @@
         </is>
       </c>
       <c r="B480" s="3" t="n">
-        <v>46265</v>
+        <v>46237</v>
       </c>
       <c r="C480" s="4" t="n">
-        <v>0.3888888888888889</v>
+        <v>0.3291666666666667</v>
       </c>
       <c r="D480" s="4" t="n">
-        <v>0.7215277777777778</v>
+        <v>0.7111111111111111</v>
       </c>
       <c r="E480" s="2" t="inlineStr">
         <is>
-          <t>corrected from a clearer re-scan photo later in the album</t>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B481" s="3" t="n">
+        <v>46238</v>
+      </c>
+      <c r="C481" s="4" t="n">
+        <v>0.3305555555555555</v>
+      </c>
+      <c r="D481" s="4" t="n">
+        <v>0.7263888888888889</v>
+      </c>
+      <c r="E481" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="482">
       <c r="A482" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B482" s="3" t="n">
-        <v>46235</v>
-      </c>
-      <c r="C482" s="4" t="n">
-        <v>0.2569444444444444</v>
+        <v>46239</v>
+      </c>
+      <c r="C482" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D482" s="4" t="n">
-        <v>0.7430555555555556</v>
+        <v>0.7715277777777778</v>
       </c>
       <c r="E482" s="2" t="inlineStr">
         <is>
-          <t>extra punch: 17:55; last day of month; final record</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="483">
       <c r="A483" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B483" s="3" t="n">
-        <v>46236</v>
+        <v>46240</v>
       </c>
       <c r="C483" s="4" t="n">
-        <v>0.2201388888888889</v>
+        <v>0.3986111111111111</v>
       </c>
       <c r="D483" s="4" t="n">
-        <v>0.7381944444444445</v>
+        <v>0.7277777777777777</v>
       </c>
       <c r="E483" s="2" t="inlineStr">
         <is>
@@ -10348,38 +10363,38 @@
     <row r="484">
       <c r="A484" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B484" s="3" t="n">
-        <v>46237</v>
+        <v>46242</v>
       </c>
       <c r="C484" s="4" t="n">
-        <v>0.2472222222222222</v>
+        <v>0.2791666666666667</v>
       </c>
       <c r="D484" s="4" t="n">
-        <v>0.7402777777777778</v>
+        <v>0.7284722222222222</v>
       </c>
       <c r="E484" s="2" t="inlineStr">
         <is>
-          <t>extra punch: 17:46</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="485">
       <c r="A485" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B485" s="3" t="n">
-        <v>46238</v>
+        <v>46243</v>
       </c>
       <c r="C485" s="4" t="n">
-        <v>0.2173611111111111</v>
+        <v>0.2784722222222222</v>
       </c>
       <c r="D485" s="4" t="n">
-        <v>0.7604166666666666</v>
+        <v>0.7555555555555555</v>
       </c>
       <c r="E485" s="2" t="inlineStr">
         <is>
@@ -10390,38 +10405,38 @@
     <row r="486">
       <c r="A486" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B486" s="3" t="n">
-        <v>46239</v>
+        <v>46244</v>
       </c>
       <c r="C486" s="4" t="n">
-        <v>0.2333333333333333</v>
+        <v>0.2875</v>
       </c>
       <c r="D486" s="4" t="n">
-        <v>0.7611111111111111</v>
+        <v>0.7479166666666667</v>
       </c>
       <c r="E486" s="2" t="inlineStr">
         <is>
-          <t>extra punch: 18:16</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="487">
       <c r="A487" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B487" s="3" t="n">
-        <v>46240</v>
+        <v>46245</v>
       </c>
       <c r="C487" s="4" t="n">
-        <v>0.2277777777777778</v>
+        <v>0.3</v>
       </c>
       <c r="D487" s="4" t="n">
-        <v>0.75625</v>
+        <v>0.7465277777777778</v>
       </c>
       <c r="E487" s="2" t="inlineStr">
         <is>
@@ -10432,80 +10447,80 @@
     <row r="488">
       <c r="A488" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B488" s="3" t="n">
-        <v>46242</v>
+        <v>46246</v>
       </c>
       <c r="C488" s="4" t="n">
-        <v>0.2479166666666667</v>
+        <v>0.2548611111111111</v>
       </c>
       <c r="D488" s="4" t="n">
-        <v>0.7291666666666666</v>
+        <v>0.7222222222222222</v>
       </c>
       <c r="E488" s="2" t="inlineStr">
         <is>
-          <t>extra punch: 07:09</t>
+          <t>extra punches: 07:44 06:16</t>
         </is>
       </c>
     </row>
     <row r="489">
       <c r="A489" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B489" s="3" t="n">
-        <v>46243</v>
+        <v>46247</v>
       </c>
       <c r="C489" s="4" t="n">
-        <v>0.2368055555555555</v>
+        <v>0.3388888888888889</v>
       </c>
       <c r="D489" s="4" t="n">
-        <v>0.6729166666666667</v>
+        <v>0.7236111111111111</v>
       </c>
       <c r="E489" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>extra punch: 17:21</t>
         </is>
       </c>
     </row>
     <row r="490">
       <c r="A490" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B490" s="3" t="n">
-        <v>46244</v>
+        <v>46249</v>
       </c>
       <c r="C490" s="4" t="n">
-        <v>0.2534722222222222</v>
+        <v>0.2423611111111111</v>
       </c>
       <c r="D490" s="4" t="n">
-        <v>0.7479166666666667</v>
+        <v>0.7270833333333333</v>
       </c>
       <c r="E490" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>extra punches: 17:27 07:28</t>
         </is>
       </c>
     </row>
     <row r="491">
       <c r="A491" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B491" s="3" t="n">
-        <v>46245</v>
+        <v>46250</v>
       </c>
       <c r="C491" s="4" t="n">
-        <v>0.2541666666666667</v>
+        <v>0.3409722222222222</v>
       </c>
       <c r="D491" s="4" t="n">
-        <v>0.7465277777777778</v>
+        <v>0.7104166666666667</v>
       </c>
       <c r="E491" s="2" t="inlineStr">
         <is>
@@ -10516,17 +10531,17 @@
     <row r="492">
       <c r="A492" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B492" s="3" t="n">
-        <v>46246</v>
+        <v>46251</v>
       </c>
       <c r="C492" s="4" t="n">
-        <v>0.2618055555555556</v>
+        <v>0.2833333333333333</v>
       </c>
       <c r="D492" s="4" t="n">
-        <v>0.75</v>
+        <v>0.7326388888888888</v>
       </c>
       <c r="E492" s="2" t="inlineStr">
         <is>
@@ -10537,17 +10552,17 @@
     <row r="493">
       <c r="A493" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B493" s="3" t="n">
-        <v>46247</v>
+        <v>46252</v>
       </c>
       <c r="C493" s="4" t="n">
-        <v>0.25625</v>
+        <v>0.28125</v>
       </c>
       <c r="D493" s="4" t="n">
-        <v>0.75</v>
+        <v>0.7645833333333333</v>
       </c>
       <c r="E493" s="2" t="inlineStr">
         <is>
@@ -10558,80 +10573,84 @@
     <row r="494">
       <c r="A494" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B494" s="3" t="n">
-        <v>46249</v>
+        <v>46253</v>
       </c>
       <c r="C494" s="4" t="n">
-        <v>0.2333333333333333</v>
+        <v>0.3166666666666667</v>
       </c>
       <c r="D494" s="4" t="n">
-        <v>0.7506944444444444</v>
+        <v>0.74375</v>
       </c>
       <c r="E494" s="2" t="inlineStr">
         <is>
-          <t>extra punch: 06:05</t>
+          <t>extra punch: 08:01</t>
         </is>
       </c>
     </row>
     <row r="495">
       <c r="A495" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B495" s="3" t="n">
-        <v>46250</v>
+        <v>46254</v>
       </c>
       <c r="C495" s="4" t="n">
-        <v>0.25625</v>
-      </c>
-      <c r="D495" s="4" t="n">
-        <v>0.7458333333333333</v>
+        <v>0.2868055555555555</v>
+      </c>
+      <c r="D495" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E495" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="496">
       <c r="A496" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B496" s="3" t="n">
-        <v>46251</v>
-      </c>
-      <c r="C496" s="4" t="n">
-        <v>0.2541666666666667</v>
+        <v>46256</v>
+      </c>
+      <c r="C496" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D496" s="4" t="n">
-        <v>0.7555555555555555</v>
+        <v>0.74375</v>
       </c>
       <c r="E496" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="497">
       <c r="A497" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B497" s="3" t="n">
-        <v>46252</v>
+        <v>46257</v>
       </c>
       <c r="C497" s="4" t="n">
-        <v>0.2395833333333333</v>
+        <v>0.2548611111111111</v>
       </c>
       <c r="D497" s="4" t="n">
-        <v>0.7611111111111111</v>
+        <v>0.7569444444444444</v>
       </c>
       <c r="E497" s="2" t="inlineStr">
         <is>
@@ -10642,38 +10661,40 @@
     <row r="498">
       <c r="A498" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B498" s="3" t="n">
-        <v>46253</v>
-      </c>
-      <c r="C498" s="4" t="n">
-        <v>0.2527777777777778</v>
+        <v>46258</v>
+      </c>
+      <c r="C498" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D498" s="4" t="n">
-        <v>0.7423611111111111</v>
+        <v>0.7506944444444444</v>
       </c>
       <c r="E498" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="499">
       <c r="A499" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B499" s="3" t="n">
-        <v>46254</v>
+        <v>46259</v>
       </c>
       <c r="C499" s="4" t="n">
-        <v>0.2583333333333334</v>
+        <v>0.2868055555555555</v>
       </c>
       <c r="D499" s="4" t="n">
-        <v>0.7451388888888889</v>
+        <v>0.6895833333333333</v>
       </c>
       <c r="E499" s="2" t="inlineStr">
         <is>
@@ -10684,38 +10705,40 @@
     <row r="500">
       <c r="A500" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B500" s="3" t="n">
-        <v>46256</v>
-      </c>
-      <c r="C500" s="4" t="n">
-        <v>0.2402777777777778</v>
+        <v>46260</v>
+      </c>
+      <c r="C500" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D500" s="4" t="n">
-        <v>0.74375</v>
+        <v>0.6986111111111111</v>
       </c>
       <c r="E500" s="2" t="inlineStr">
         <is>
-          <t>extra punches: 17:51 06:13</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="501">
       <c r="A501" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B501" s="3" t="n">
-        <v>46257</v>
+        <v>46261</v>
       </c>
       <c r="C501" s="4" t="n">
-        <v>0.2402777777777778</v>
+        <v>0.2833333333333333</v>
       </c>
       <c r="D501" s="4" t="n">
-        <v>0.75</v>
+        <v>0.8645833333333334</v>
       </c>
       <c r="E501" s="2" t="inlineStr">
         <is>
@@ -10726,84 +10749,65 @@
     <row r="502">
       <c r="A502" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B502" s="3" t="n">
-        <v>46258</v>
-      </c>
-      <c r="C502" s="4" t="n">
-        <v>0.2319444444444445</v>
+        <v>46263</v>
+      </c>
+      <c r="C502" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D502" s="4" t="n">
-        <v>0.7513888888888889</v>
+        <v>0.7291666666666666</v>
       </c>
       <c r="E502" s="2" t="inlineStr">
         <is>
-          <t>extra punch: 18:02</t>
+          <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="503">
       <c r="A503" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B503" s="3" t="n">
-        <v>46259</v>
+        <v>46264</v>
       </c>
       <c r="C503" s="4" t="n">
-        <v>0.3555555555555556</v>
+        <v>0.2798611111111111</v>
       </c>
       <c r="D503" s="4" t="n">
-        <v>0.7541666666666667</v>
+        <v>0.7472222222222222</v>
       </c>
       <c r="E503" s="2" t="inlineStr">
         <is>
-          <t>extra punch: 06:33</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="504">
       <c r="A504" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B504" s="3" t="n">
-        <v>46260</v>
+        <v>46265</v>
       </c>
       <c r="C504" s="4" t="n">
-        <v>0.2555555555555555</v>
+        <v>0.3888888888888889</v>
       </c>
       <c r="D504" s="4" t="n">
-        <v>0.7541666666666667</v>
+        <v>0.7215277777777778</v>
       </c>
       <c r="E504" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="505">
-      <c r="A505" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="B505" s="3" t="n">
-        <v>46261</v>
-      </c>
-      <c r="C505" s="4" t="n">
-        <v>0.2722222222222222</v>
-      </c>
-      <c r="D505" s="4" t="n">
-        <v>0.7569444444444444</v>
-      </c>
-      <c r="E505" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>corrected from a clearer re-scan photo later in the album</t>
         </is>
       </c>
     </row>
@@ -10814,17 +10818,17 @@
         </is>
       </c>
       <c r="B506" s="3" t="n">
-        <v>46263</v>
+        <v>46235</v>
       </c>
       <c r="C506" s="4" t="n">
-        <v>0.2201388888888889</v>
+        <v>0.2569444444444444</v>
       </c>
       <c r="D506" s="4" t="n">
-        <v>0.7444444444444445</v>
+        <v>0.7430555555555556</v>
       </c>
       <c r="E506" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>extra punch: 17:55; last day of month; final record</t>
         </is>
       </c>
     </row>
@@ -10835,13 +10839,13 @@
         </is>
       </c>
       <c r="B507" s="3" t="n">
-        <v>46264</v>
+        <v>46236</v>
       </c>
       <c r="C507" s="4" t="n">
-        <v>0.2555555555555555</v>
+        <v>0.2201388888888889</v>
       </c>
       <c r="D507" s="4" t="n">
-        <v>0.7458333333333333</v>
+        <v>0.7381944444444445</v>
       </c>
       <c r="E507" s="2" t="inlineStr">
         <is>
@@ -10856,15 +10860,519 @@
         </is>
       </c>
       <c r="B508" s="3" t="n">
+        <v>46237</v>
+      </c>
+      <c r="C508" s="4" t="n">
+        <v>0.2472222222222222</v>
+      </c>
+      <c r="D508" s="4" t="n">
+        <v>0.7402777777777778</v>
+      </c>
+      <c r="E508" s="2" t="inlineStr">
+        <is>
+          <t>extra punch: 17:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B509" s="3" t="n">
+        <v>46238</v>
+      </c>
+      <c r="C509" s="4" t="n">
+        <v>0.2173611111111111</v>
+      </c>
+      <c r="D509" s="4" t="n">
+        <v>0.7604166666666666</v>
+      </c>
+      <c r="E509" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B510" s="3" t="n">
+        <v>46239</v>
+      </c>
+      <c r="C510" s="4" t="n">
+        <v>0.2333333333333333</v>
+      </c>
+      <c r="D510" s="4" t="n">
+        <v>0.7611111111111111</v>
+      </c>
+      <c r="E510" s="2" t="inlineStr">
+        <is>
+          <t>extra punch: 18:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B511" s="3" t="n">
+        <v>46240</v>
+      </c>
+      <c r="C511" s="4" t="n">
+        <v>0.2277777777777778</v>
+      </c>
+      <c r="D511" s="4" t="n">
+        <v>0.75625</v>
+      </c>
+      <c r="E511" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B512" s="3" t="n">
+        <v>46242</v>
+      </c>
+      <c r="C512" s="4" t="n">
+        <v>0.2479166666666667</v>
+      </c>
+      <c r="D512" s="4" t="n">
+        <v>0.7291666666666666</v>
+      </c>
+      <c r="E512" s="2" t="inlineStr">
+        <is>
+          <t>extra punch: 07:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B513" s="3" t="n">
+        <v>46243</v>
+      </c>
+      <c r="C513" s="4" t="n">
+        <v>0.2368055555555555</v>
+      </c>
+      <c r="D513" s="4" t="n">
+        <v>0.6729166666666667</v>
+      </c>
+      <c r="E513" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B514" s="3" t="n">
+        <v>46244</v>
+      </c>
+      <c r="C514" s="4" t="n">
+        <v>0.2534722222222222</v>
+      </c>
+      <c r="D514" s="4" t="n">
+        <v>0.7479166666666667</v>
+      </c>
+      <c r="E514" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B515" s="3" t="n">
+        <v>46245</v>
+      </c>
+      <c r="C515" s="4" t="n">
+        <v>0.2541666666666667</v>
+      </c>
+      <c r="D515" s="4" t="n">
+        <v>0.7465277777777778</v>
+      </c>
+      <c r="E515" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B516" s="3" t="n">
+        <v>46246</v>
+      </c>
+      <c r="C516" s="4" t="n">
+        <v>0.2618055555555556</v>
+      </c>
+      <c r="D516" s="4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E516" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B517" s="3" t="n">
+        <v>46247</v>
+      </c>
+      <c r="C517" s="4" t="n">
+        <v>0.25625</v>
+      </c>
+      <c r="D517" s="4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E517" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B518" s="3" t="n">
+        <v>46249</v>
+      </c>
+      <c r="C518" s="4" t="n">
+        <v>0.2333333333333333</v>
+      </c>
+      <c r="D518" s="4" t="n">
+        <v>0.7506944444444444</v>
+      </c>
+      <c r="E518" s="2" t="inlineStr">
+        <is>
+          <t>extra punch: 06:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B519" s="3" t="n">
+        <v>46250</v>
+      </c>
+      <c r="C519" s="4" t="n">
+        <v>0.25625</v>
+      </c>
+      <c r="D519" s="4" t="n">
+        <v>0.7458333333333333</v>
+      </c>
+      <c r="E519" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B520" s="3" t="n">
+        <v>46251</v>
+      </c>
+      <c r="C520" s="4" t="n">
+        <v>0.2541666666666667</v>
+      </c>
+      <c r="D520" s="4" t="n">
+        <v>0.7555555555555555</v>
+      </c>
+      <c r="E520" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B521" s="3" t="n">
+        <v>46252</v>
+      </c>
+      <c r="C521" s="4" t="n">
+        <v>0.2395833333333333</v>
+      </c>
+      <c r="D521" s="4" t="n">
+        <v>0.7611111111111111</v>
+      </c>
+      <c r="E521" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B522" s="3" t="n">
+        <v>46253</v>
+      </c>
+      <c r="C522" s="4" t="n">
+        <v>0.2527777777777778</v>
+      </c>
+      <c r="D522" s="4" t="n">
+        <v>0.7423611111111111</v>
+      </c>
+      <c r="E522" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B523" s="3" t="n">
+        <v>46254</v>
+      </c>
+      <c r="C523" s="4" t="n">
+        <v>0.2583333333333334</v>
+      </c>
+      <c r="D523" s="4" t="n">
+        <v>0.7451388888888889</v>
+      </c>
+      <c r="E523" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B524" s="3" t="n">
+        <v>46256</v>
+      </c>
+      <c r="C524" s="4" t="n">
+        <v>0.2402777777777778</v>
+      </c>
+      <c r="D524" s="4" t="n">
+        <v>0.74375</v>
+      </c>
+      <c r="E524" s="2" t="inlineStr">
+        <is>
+          <t>extra punches: 17:51 06:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B525" s="3" t="n">
+        <v>46257</v>
+      </c>
+      <c r="C525" s="4" t="n">
+        <v>0.2402777777777778</v>
+      </c>
+      <c r="D525" s="4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E525" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B526" s="3" t="n">
+        <v>46258</v>
+      </c>
+      <c r="C526" s="4" t="n">
+        <v>0.2319444444444445</v>
+      </c>
+      <c r="D526" s="4" t="n">
+        <v>0.7513888888888889</v>
+      </c>
+      <c r="E526" s="2" t="inlineStr">
+        <is>
+          <t>extra punch: 18:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B527" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="C527" s="4" t="n">
+        <v>0.3555555555555556</v>
+      </c>
+      <c r="D527" s="4" t="n">
+        <v>0.7541666666666667</v>
+      </c>
+      <c r="E527" s="2" t="inlineStr">
+        <is>
+          <t>extra punch: 06:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B528" s="3" t="n">
+        <v>46260</v>
+      </c>
+      <c r="C528" s="4" t="n">
+        <v>0.2555555555555555</v>
+      </c>
+      <c r="D528" s="4" t="n">
+        <v>0.7541666666666667</v>
+      </c>
+      <c r="E528" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B529" s="3" t="n">
+        <v>46261</v>
+      </c>
+      <c r="C529" s="4" t="n">
+        <v>0.2722222222222222</v>
+      </c>
+      <c r="D529" s="4" t="n">
+        <v>0.7569444444444444</v>
+      </c>
+      <c r="E529" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B530" s="3" t="n">
+        <v>46263</v>
+      </c>
+      <c r="C530" s="4" t="n">
+        <v>0.2201388888888889</v>
+      </c>
+      <c r="D530" s="4" t="n">
+        <v>0.7444444444444445</v>
+      </c>
+      <c r="E530" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B531" s="3" t="n">
+        <v>46264</v>
+      </c>
+      <c r="C531" s="4" t="n">
+        <v>0.2555555555555555</v>
+      </c>
+      <c r="D531" s="4" t="n">
+        <v>0.7458333333333333</v>
+      </c>
+      <c r="E531" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B532" s="3" t="n">
         <v>46265</v>
       </c>
-      <c r="C508" s="4" t="n">
+      <c r="C532" s="4" t="n">
         <v>0.2569444444444444</v>
       </c>
-      <c r="D508" s="4" t="n">
+      <c r="D532" s="4" t="n">
         <v>0.7527777777777778</v>
       </c>
-      <c r="E508" s="2" t="inlineStr">
+      <c r="E532" s="2" t="inlineStr">
         <is>
           <t>corrected from a clearer re-scan photo later in the album</t>
         </is>

--- a/output/timesheet.xlsx
+++ b/output/timesheet.xlsx
@@ -4460,7 +4460,7 @@
       </c>
       <c r="E195" s="2" t="inlineStr">
         <is>
-          <t>single punch only; last day of month</t>
+          <t>Night Security; single punch only; last day of month</t>
         </is>
       </c>
     </row>
@@ -4483,7 +4483,7 @@
       </c>
       <c r="E196" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>Night Security; single punch only</t>
         </is>
       </c>
     </row>
@@ -4504,7 +4504,7 @@
       </c>
       <c r="E197" s="2" t="inlineStr">
         <is>
-          <t>extra punch: 17:50</t>
+          <t>Night Security; extra punch: 17:50</t>
         </is>
       </c>
     </row>
@@ -4525,7 +4525,7 @@
       </c>
       <c r="E198" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Night Security</t>
         </is>
       </c>
     </row>
@@ -4548,7 +4548,7 @@
       </c>
       <c r="E199" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>Night Security; single punch only</t>
         </is>
       </c>
     </row>
@@ -4569,7 +4569,7 @@
       </c>
       <c r="E200" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Night Security</t>
         </is>
       </c>
     </row>
@@ -4592,7 +4592,7 @@
       </c>
       <c r="E201" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>Night Security; single punch only</t>
         </is>
       </c>
     </row>
@@ -4613,7 +4613,7 @@
       </c>
       <c r="E202" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Night Security</t>
         </is>
       </c>
     </row>
@@ -4634,7 +4634,7 @@
       </c>
       <c r="E203" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Night Security</t>
         </is>
       </c>
     </row>
@@ -4657,7 +4657,7 @@
       </c>
       <c r="E204" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>Night Security; single punch only</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="E205" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Night Security</t>
         </is>
       </c>
     </row>
@@ -4699,7 +4699,7 @@
       </c>
       <c r="E206" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Night Security</t>
         </is>
       </c>
     </row>
@@ -4720,7 +4720,7 @@
       </c>
       <c r="E207" s="2" t="inlineStr">
         <is>
-          <t>PLEASE VERIFY: extra punches 05:39 05:39 05:39 05:39 repeated - possible device anomaly</t>
+          <t>Night Security; PLEASE VERIFY: extra punches 05:39 05:39 05:39 05:39 repeated - possible device anomaly</t>
         </is>
       </c>
     </row>
@@ -4741,7 +4741,7 @@
       </c>
       <c r="E208" s="2" t="inlineStr">
         <is>
-          <t>extra punch: 09:31</t>
+          <t>Night Security; extra punch: 09:31</t>
         </is>
       </c>
     </row>
@@ -4764,7 +4764,7 @@
       </c>
       <c r="E209" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>Night Security; single punch only</t>
         </is>
       </c>
     </row>
@@ -4785,7 +4785,7 @@
       </c>
       <c r="E210" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Night Security</t>
         </is>
       </c>
     </row>
@@ -4806,7 +4806,7 @@
       </c>
       <c r="E211" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Night Security</t>
         </is>
       </c>
     </row>
@@ -4827,7 +4827,7 @@
       </c>
       <c r="E212" s="2" t="inlineStr">
         <is>
-          <t>extra punch: 17:19</t>
+          <t>Night Security; extra punch: 17:19</t>
         </is>
       </c>
     </row>
@@ -4850,7 +4850,7 @@
       </c>
       <c r="E213" s="2" t="inlineStr">
         <is>
-          <t>single punch only</t>
+          <t>Night Security; single punch only</t>
         </is>
       </c>
     </row>
@@ -4871,7 +4871,7 @@
       </c>
       <c r="E214" s="2" t="inlineStr">
         <is>
-          <t>PLEASE VERIFY: in/out times read identical - likely OCR error</t>
+          <t>Night Security; PLEASE VERIFY: in/out times read identical - likely OCR error</t>
         </is>
       </c>
     </row>
@@ -4892,7 +4892,7 @@
       </c>
       <c r="E215" s="2" t="inlineStr">
         <is>
-          <t>extra punch: 05:45</t>
+          <t>Night Security; extra punch: 05:45</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="E216" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Night Security</t>
         </is>
       </c>
     </row>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="E217" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Night Security</t>
         </is>
       </c>
     </row>
@@ -4955,7 +4955,7 @@
       </c>
       <c r="E218" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Night Security</t>
         </is>
       </c>
     </row>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="E219" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Night Security</t>
         </is>
       </c>
     </row>
@@ -4997,7 +4997,7 @@
       </c>
       <c r="E220" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Night Security</t>
         </is>
       </c>
     </row>
@@ -5018,7 +5018,7 @@
       </c>
       <c r="E221" s="2" t="inlineStr">
         <is>
-          <t>extra punch: 08:02</t>
+          <t>Night Security; extra punch: 08:02</t>
         </is>
       </c>
     </row>
@@ -5039,7 +5039,7 @@
       </c>
       <c r="E222" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Night Security</t>
         </is>
       </c>
     </row>

--- a/output/timesheet.xlsx
+++ b/output/timesheet.xlsx
@@ -37,7 +37,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -48,6 +48,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="001F4E78"/>
         <bgColor rgb="001F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFF00"/>
+        <bgColor rgb="00FFFF00"/>
       </patternFill>
     </fill>
   </fills>
@@ -63,7 +69,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -71,6 +77,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2988,23 +2997,23 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="2" t="inlineStr">
+      <c r="A124" s="5" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B124" s="3" t="n">
+      <c r="B124" s="6" t="n">
         <v>46248</v>
       </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D124" s="4" t="n">
+      <c r="C124" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D124" s="7" t="n">
         <v>0.7708333333333334</v>
       </c>
-      <c r="E124" s="2" t="inlineStr">
+      <c r="E124" s="5" t="inlineStr">
         <is>
           <t>single punch only</t>
         </is>
@@ -3147,23 +3156,23 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="2" t="inlineStr">
+      <c r="A131" s="5" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B131" s="3" t="n">
+      <c r="B131" s="6" t="n">
         <v>46255</v>
       </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D131" s="4" t="n">
+      <c r="C131" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D131" s="7" t="n">
         <v>0.7333333333333333</v>
       </c>
-      <c r="E131" s="2" t="inlineStr">
+      <c r="E131" s="5" t="inlineStr">
         <is>
           <t>single punch only</t>
         </is>
@@ -4553,21 +4562,21 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="2" t="inlineStr">
+      <c r="A200" s="5" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="B200" s="3" t="n">
+      <c r="B200" s="6" t="n">
         <v>46241</v>
       </c>
-      <c r="C200" s="4" t="n">
+      <c r="C200" s="7" t="n">
         <v>0.7666666666666667</v>
       </c>
-      <c r="D200" s="4" t="n">
+      <c r="D200" s="7" t="n">
         <v>0.7708333333333334</v>
       </c>
-      <c r="E200" s="2" t="inlineStr">
+      <c r="E200" s="5" t="inlineStr">
         <is>
           <t>Night Security</t>
         </is>
@@ -4704,21 +4713,21 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="2" t="inlineStr">
+      <c r="A207" s="5" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="B207" s="3" t="n">
+      <c r="B207" s="6" t="n">
         <v>46248</v>
       </c>
-      <c r="C207" s="4" t="n">
+      <c r="C207" s="7" t="n">
         <v>0.2354166666666667</v>
       </c>
-      <c r="D207" s="4" t="n">
+      <c r="D207" s="7" t="n">
         <v>0.7611111111111111</v>
       </c>
-      <c r="E207" s="2" t="inlineStr">
+      <c r="E207" s="5" t="inlineStr">
         <is>
           <t>Night Security; PLEASE VERIFY: extra punches 05:39 05:39 05:39 05:39 repeated - possible device anomaly</t>
         </is>
@@ -4855,21 +4864,21 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="2" t="inlineStr">
+      <c r="A214" s="5" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="B214" s="3" t="n">
+      <c r="B214" s="6" t="n">
         <v>46255</v>
       </c>
-      <c r="C214" s="4" t="n">
+      <c r="C214" s="7" t="n">
         <v>0.7590277777777777</v>
       </c>
-      <c r="D214" s="4" t="n">
+      <c r="D214" s="7" t="n">
         <v>0.7590277777777777</v>
       </c>
-      <c r="E214" s="2" t="inlineStr">
+      <c r="E214" s="5" t="inlineStr">
         <is>
           <t>Night Security; PLEASE VERIFY: in/out times read identical - likely OCR error</t>
         </is>
@@ -5149,21 +5158,21 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="2" t="inlineStr">
+      <c r="A229" s="5" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="B229" s="3" t="n">
+      <c r="B229" s="6" t="n">
         <v>46241</v>
       </c>
-      <c r="C229" s="4" t="n">
+      <c r="C229" s="7" t="n">
         <v>0.1486111111111111</v>
       </c>
-      <c r="D229" s="4" t="n">
+      <c r="D229" s="7" t="n">
         <v>0.7201388888888889</v>
       </c>
-      <c r="E229" s="2" t="inlineStr">
+      <c r="E229" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -5296,21 +5305,21 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="2" t="inlineStr">
+      <c r="A236" s="5" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="B236" s="3" t="n">
+      <c r="B236" s="6" t="n">
         <v>46248</v>
       </c>
-      <c r="C236" s="4" t="n">
+      <c r="C236" s="7" t="n">
         <v>0.2361111111111111</v>
       </c>
-      <c r="D236" s="4" t="n">
+      <c r="D236" s="7" t="n">
         <v>0.7972222222222223</v>
       </c>
-      <c r="E236" s="2" t="inlineStr">
+      <c r="E236" s="5" t="inlineStr">
         <is>
           <t>extra punch: 17:01</t>
         </is>
@@ -5443,21 +5452,21 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="2" t="inlineStr">
+      <c r="A243" s="5" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="B243" s="3" t="n">
+      <c r="B243" s="6" t="n">
         <v>46255</v>
       </c>
-      <c r="C243" s="4" t="n">
+      <c r="C243" s="7" t="n">
         <v>0.1493055555555556</v>
       </c>
-      <c r="D243" s="4" t="n">
+      <c r="D243" s="7" t="n">
         <v>0.7236111111111111</v>
       </c>
-      <c r="E243" s="2" t="inlineStr">
+      <c r="E243" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -5590,21 +5599,21 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="2" t="inlineStr">
+      <c r="A250" s="5" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="B250" s="3" t="n">
+      <c r="B250" s="6" t="n">
         <v>46262</v>
       </c>
-      <c r="C250" s="4" t="n">
+      <c r="C250" s="7" t="n">
         <v>0.1493055555555556</v>
       </c>
-      <c r="D250" s="4" t="n">
+      <c r="D250" s="7" t="n">
         <v>0.7159722222222222</v>
       </c>
-      <c r="E250" s="2" t="inlineStr">
+      <c r="E250" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -5741,21 +5750,21 @@
       </c>
     </row>
     <row r="258">
-      <c r="A258" s="2" t="inlineStr">
+      <c r="A258" s="5" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="B258" s="3" t="n">
+      <c r="B258" s="6" t="n">
         <v>46241</v>
       </c>
-      <c r="C258" s="4" t="n">
+      <c r="C258" s="7" t="n">
         <v>0.1791666666666667</v>
       </c>
-      <c r="D258" s="4" t="n">
+      <c r="D258" s="7" t="n">
         <v>0.5618055555555556</v>
       </c>
-      <c r="E258" s="2" t="inlineStr">
+      <c r="E258" s="5" t="inlineStr">
         <is>
           <t>extra punch: 04:18</t>
         </is>
@@ -5888,21 +5897,21 @@
       </c>
     </row>
     <row r="265">
-      <c r="A265" s="2" t="inlineStr">
+      <c r="A265" s="5" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="B265" s="3" t="n">
+      <c r="B265" s="6" t="n">
         <v>46248</v>
       </c>
-      <c r="C265" s="4" t="n">
+      <c r="C265" s="7" t="n">
         <v>0.1743055555555555</v>
       </c>
-      <c r="D265" s="4" t="n">
+      <c r="D265" s="7" t="n">
         <v>0.5298611111111111</v>
       </c>
-      <c r="E265" s="2" t="inlineStr">
+      <c r="E265" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -6035,21 +6044,21 @@
       </c>
     </row>
     <row r="272">
-      <c r="A272" s="2" t="inlineStr">
+      <c r="A272" s="5" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="B272" s="3" t="n">
+      <c r="B272" s="6" t="n">
         <v>46255</v>
       </c>
-      <c r="C272" s="4" t="n">
+      <c r="C272" s="7" t="n">
         <v>0.1854166666666667</v>
       </c>
-      <c r="D272" s="4" t="n">
+      <c r="D272" s="7" t="n">
         <v>0.5319444444444444</v>
       </c>
-      <c r="E272" s="2" t="inlineStr">
+      <c r="E272" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -6182,21 +6191,21 @@
       </c>
     </row>
     <row r="279">
-      <c r="A279" s="2" t="inlineStr">
+      <c r="A279" s="5" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="B279" s="3" t="n">
+      <c r="B279" s="6" t="n">
         <v>46262</v>
       </c>
-      <c r="C279" s="4" t="n">
+      <c r="C279" s="7" t="n">
         <v>0.1881944444444444</v>
       </c>
-      <c r="D279" s="4" t="n">
+      <c r="D279" s="7" t="n">
         <v>0.4055555555555556</v>
       </c>
-      <c r="E279" s="2" t="inlineStr">
+      <c r="E279" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -6973,21 +6982,21 @@
       </c>
     </row>
     <row r="318">
-      <c r="A318" s="2" t="inlineStr">
+      <c r="A318" s="5" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="B318" s="3" t="n">
+      <c r="B318" s="6" t="n">
         <v>46241</v>
       </c>
-      <c r="C318" s="4" t="n">
+      <c r="C318" s="7" t="n">
         <v>0.1451388888888889</v>
       </c>
-      <c r="D318" s="4" t="n">
+      <c r="D318" s="7" t="n">
         <v>0.7298611111111111</v>
       </c>
-      <c r="E318" s="2" t="inlineStr">
+      <c r="E318" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -7120,21 +7129,21 @@
       </c>
     </row>
     <row r="325">
-      <c r="A325" s="2" t="inlineStr">
+      <c r="A325" s="5" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="B325" s="3" t="n">
+      <c r="B325" s="6" t="n">
         <v>46248</v>
       </c>
-      <c r="C325" s="4" t="n">
+      <c r="C325" s="7" t="n">
         <v>0.15</v>
       </c>
-      <c r="D325" s="4" t="n">
+      <c r="D325" s="7" t="n">
         <v>0.7076388888888889</v>
       </c>
-      <c r="E325" s="2" t="inlineStr">
+      <c r="E325" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -7267,21 +7276,21 @@
       </c>
     </row>
     <row r="332">
-      <c r="A332" s="2" t="inlineStr">
+      <c r="A332" s="5" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="B332" s="3" t="n">
+      <c r="B332" s="6" t="n">
         <v>46255</v>
       </c>
-      <c r="C332" s="4" t="n">
+      <c r="C332" s="7" t="n">
         <v>0.275</v>
       </c>
-      <c r="D332" s="4" t="n">
+      <c r="D332" s="7" t="n">
         <v>0.8354166666666667</v>
       </c>
-      <c r="E332" s="2" t="inlineStr">
+      <c r="E332" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -7414,21 +7423,21 @@
       </c>
     </row>
     <row r="339">
-      <c r="A339" s="2" t="inlineStr">
+      <c r="A339" s="5" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="B339" s="3" t="n">
+      <c r="B339" s="6" t="n">
         <v>46262</v>
       </c>
-      <c r="C339" s="4" t="n">
+      <c r="C339" s="7" t="n">
         <v>0.2805555555555556</v>
       </c>
-      <c r="D339" s="4" t="n">
+      <c r="D339" s="7" t="n">
         <v>0.7701388888888889</v>
       </c>
-      <c r="E339" s="2" t="inlineStr">
+      <c r="E339" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -9066,23 +9075,23 @@
       </c>
     </row>
     <row r="420">
-      <c r="A420" s="2" t="inlineStr">
+      <c r="A420" s="5" t="inlineStr">
         <is>
           <t>39</t>
         </is>
       </c>
-      <c r="B420" s="3" t="n">
+      <c r="B420" s="6" t="n">
         <v>46262</v>
       </c>
-      <c r="C420" s="4" t="n">
+      <c r="C420" s="7" t="n">
         <v>0.25</v>
       </c>
-      <c r="D420" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E420" s="2" t="inlineStr">
+      <c r="D420" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E420" s="5" t="inlineStr">
         <is>
           <t>single punch only</t>
         </is>

--- a/output/timesheet.xlsx
+++ b/output/timesheet.xlsx
@@ -69,7 +69,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -77,9 +77,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -445,14 +447,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E608"/>
+  <dimension ref="A1:F608"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -478,6 +481,11 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Total Hours</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Notes</t>
         </is>
       </c>
@@ -497,7 +505,10 @@
       <c r="D2" s="4" t="n">
         <v>0.7152777777777778</v>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>last day of month; final record</t>
         </is>
@@ -518,7 +529,10 @@
       <c r="D3" s="4" t="n">
         <v>0.7423611111111111</v>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="5" t="n">
+        <v>12.78</v>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -539,7 +553,10 @@
       <c r="D4" s="4" t="n">
         <v>0.7125</v>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" s="5" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -564,6 +581,11 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>single punch only</t>
         </is>
       </c>
@@ -583,7 +605,10 @@
       <c r="D6" s="4" t="n">
         <v>0.6958333333333333</v>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" s="5" t="n">
+        <v>14.55</v>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -604,32 +629,40 @@
       <c r="D7" s="4" t="n">
         <v>0.8208333333333333</v>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E7" s="5" t="n">
+        <v>11.95</v>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B8" s="6" t="n">
+      <c r="B8" s="7" t="n">
         <v>46241</v>
       </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
         <is>
           <t>No entry</t>
         </is>
@@ -650,7 +683,10 @@
       <c r="D9" s="4" t="n">
         <v>0.6965277777777777</v>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E9" s="5" t="n">
+        <v>14.77</v>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -671,7 +707,10 @@
       <c r="D10" s="4" t="n">
         <v>0.68125</v>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E10" s="5" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -692,7 +731,10 @@
       <c r="D11" s="4" t="n">
         <v>0.7263888888888889</v>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E11" s="5" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -713,7 +755,10 @@
       <c r="D12" s="4" t="n">
         <v>0.74375</v>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E12" s="5" t="n">
+        <v>13.47</v>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -734,7 +779,10 @@
       <c r="D13" s="4" t="n">
         <v>0.7833333333333333</v>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E13" s="5" t="n">
+        <v>12.45</v>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -755,32 +803,40 @@
       <c r="D14" s="4" t="n">
         <v>0.6916666666666667</v>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E14" s="5" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B15" s="6" t="n">
+      <c r="B15" s="7" t="n">
         <v>46248</v>
       </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
         <is>
           <t>No entry</t>
         </is>
@@ -801,7 +857,10 @@
       <c r="D16" s="4" t="n">
         <v>0.7055555555555556</v>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E16" s="5" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -822,7 +881,10 @@
       <c r="D17" s="4" t="n">
         <v>0.7263888888888889</v>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E17" s="5" t="n">
+        <v>14.95</v>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -843,7 +905,10 @@
       <c r="D18" s="4" t="n">
         <v>0.6951388888888889</v>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E18" s="5" t="n">
+        <v>14.87</v>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -864,7 +929,10 @@
       <c r="D19" s="4" t="n">
         <v>0.7590277777777777</v>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E19" s="5" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -889,6 +957,11 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>single punch only</t>
         </is>
       </c>
@@ -912,30 +985,40 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
           <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B22" s="6" t="n">
+      <c r="B22" s="7" t="n">
         <v>46255</v>
       </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="inlineStr">
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
         <is>
           <t>No entry</t>
         </is>
@@ -956,7 +1039,10 @@
       <c r="D23" s="4" t="n">
         <v>0.6965277777777777</v>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E23" s="5" t="n">
+        <v>14.27</v>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -977,7 +1063,10 @@
       <c r="D24" s="4" t="n">
         <v>0.6965277777777777</v>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E24" s="5" t="n">
+        <v>13.25</v>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -998,7 +1087,10 @@
       <c r="D25" s="4" t="n">
         <v>0.70625</v>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E25" s="5" t="n">
+        <v>14.23</v>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1019,7 +1111,10 @@
       <c r="D26" s="4" t="n">
         <v>0.6895833333333333</v>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E26" s="5" t="n">
+        <v>13.98</v>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1040,7 +1135,10 @@
       <c r="D27" s="4" t="n">
         <v>0.6944444444444444</v>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E27" s="5" t="n">
+        <v>15.45</v>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1061,32 +1159,40 @@
       <c r="D28" s="4" t="n">
         <v>0.6916666666666667</v>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E28" s="5" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="inlineStr">
+      <c r="A29" s="6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B29" s="6" t="n">
+      <c r="B29" s="7" t="n">
         <v>46262</v>
       </c>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E29" s="5" t="inlineStr">
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
         <is>
           <t>No entry</t>
         </is>
@@ -1107,7 +1213,10 @@
       <c r="D30" s="4" t="n">
         <v>0.6736111111111112</v>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E30" s="5" t="n">
+        <v>15.18</v>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1128,7 +1237,10 @@
       <c r="D31" s="4" t="n">
         <v>0.7458333333333333</v>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E31" s="5" t="n">
+        <v>13.32</v>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1149,7 +1261,10 @@
       <c r="D32" s="4" t="n">
         <v>0.7527777777777778</v>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E32" s="5" t="n">
+        <v>11.92</v>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1176,6 +1291,11 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>PLEASE VERIFY: check-in/out times not captured; last day of month</t>
         </is>
       </c>
@@ -1195,7 +1315,10 @@
       <c r="D35" s="4" t="n">
         <v>0.74375</v>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E35" s="5" t="n">
+        <v>12.32</v>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1216,7 +1339,10 @@
       <c r="D36" s="4" t="n">
         <v>0.7208333333333333</v>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E36" s="5" t="n">
+        <v>12.53</v>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1237,7 +1363,10 @@
       <c r="D37" s="4" t="n">
         <v>0.75625</v>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E37" s="5" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1262,6 +1391,11 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
           <t>single punch only</t>
         </is>
       </c>
@@ -1281,32 +1415,40 @@
       <c r="D39" s="4" t="n">
         <v>0.7291666666666666</v>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E39" s="5" t="n">
+        <v>12.37</v>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="5" t="inlineStr">
+      <c r="A40" s="6" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B40" s="6" t="n">
+      <c r="B40" s="7" t="n">
         <v>46241</v>
       </c>
-      <c r="C40" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D40" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E40" s="5" t="inlineStr">
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E40" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F40" s="6" t="inlineStr">
         <is>
           <t>No entry</t>
         </is>
@@ -1327,7 +1469,10 @@
       <c r="D41" s="4" t="n">
         <v>0.6722222222222223</v>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E41" s="5" t="n">
+        <v>13.72</v>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>extra punch: 18:02</t>
         </is>
@@ -1348,7 +1493,10 @@
       <c r="D42" s="4" t="n">
         <v>0.7222222222222222</v>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E42" s="5" t="n">
+        <v>12.98</v>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1369,7 +1517,10 @@
       <c r="D43" s="4" t="n">
         <v>0.8118055555555556</v>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E43" s="5" t="n">
+        <v>10.23</v>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1390,7 +1541,10 @@
       <c r="D44" s="4" t="n">
         <v>0.74375</v>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E44" s="5" t="n">
+        <v>12.47</v>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>extra punch: 06:34</t>
         </is>
@@ -1411,7 +1565,10 @@
       <c r="D45" s="4" t="n">
         <v>0.7270833333333333</v>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E45" s="5" t="n">
+        <v>12.88</v>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1432,32 +1589,40 @@
       <c r="D46" s="4" t="n">
         <v>0.7291666666666666</v>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E46" s="5" t="n">
+        <v>12.75</v>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="5" t="inlineStr">
+      <c r="A47" s="6" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B47" s="6" t="n">
+      <c r="B47" s="7" t="n">
         <v>46248</v>
       </c>
-      <c r="C47" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D47" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E47" s="5" t="inlineStr">
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E47" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F47" s="6" t="inlineStr">
         <is>
           <t>No entry</t>
         </is>
@@ -1478,7 +1643,10 @@
       <c r="D48" s="4" t="n">
         <v>0.7354166666666667</v>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E48" s="5" t="n">
+        <v>12.18</v>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1499,7 +1667,10 @@
       <c r="D49" s="4" t="n">
         <v>0.7402777777777778</v>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E49" s="5" t="n">
+        <v>12.43</v>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1520,7 +1691,10 @@
       <c r="D50" s="4" t="n">
         <v>0.7597222222222222</v>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E50" s="5" t="n">
+        <v>11.93</v>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1541,7 +1715,10 @@
       <c r="D51" s="4" t="n">
         <v>0.6951388888888889</v>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E51" s="5" t="n">
+        <v>13.13</v>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1562,7 +1739,10 @@
       <c r="D52" s="4" t="n">
         <v>0.7263888888888889</v>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E52" s="5" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1583,32 +1763,40 @@
       <c r="D53" s="4" t="n">
         <v>0.8111111111111111</v>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E53" s="5" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="5" t="inlineStr">
+      <c r="A54" s="6" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B54" s="6" t="n">
+      <c r="B54" s="7" t="n">
         <v>46255</v>
       </c>
-      <c r="C54" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D54" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E54" s="5" t="inlineStr">
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E54" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F54" s="6" t="inlineStr">
         <is>
           <t>No entry</t>
         </is>
@@ -1629,7 +1817,10 @@
       <c r="D55" s="4" t="n">
         <v>0.7097222222222223</v>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E55" s="5" t="n">
+        <v>12.73</v>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1650,7 +1841,10 @@
       <c r="D56" s="4" t="n">
         <v>0.7270833333333333</v>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E56" s="5" t="n">
+        <v>12.57</v>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1671,7 +1865,10 @@
       <c r="D57" s="4" t="n">
         <v>0.6979166666666666</v>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E57" s="5" t="n">
+        <v>13.58</v>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1692,7 +1889,10 @@
       <c r="D58" s="4" t="n">
         <v>0.6895833333333333</v>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E58" s="5" t="n">
+        <v>13.77</v>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1713,7 +1913,10 @@
       <c r="D59" s="4" t="n">
         <v>0.7361111111111112</v>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E59" s="5" t="n">
+        <v>12.42</v>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1734,32 +1937,40 @@
       <c r="D60" s="4" t="n">
         <v>0.6986111111111111</v>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E60" s="5" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="5" t="inlineStr">
+      <c r="A61" s="6" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B61" s="6" t="n">
+      <c r="B61" s="7" t="n">
         <v>46262</v>
       </c>
-      <c r="C61" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D61" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E61" s="5" t="inlineStr">
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D61" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E61" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F61" s="6" t="inlineStr">
         <is>
           <t>No entry</t>
         </is>
@@ -1780,7 +1991,10 @@
       <c r="D62" s="4" t="n">
         <v>0.7083333333333334</v>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E62" s="5" t="n">
+        <v>12.92</v>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1801,7 +2015,10 @@
       <c r="D63" s="4" t="n">
         <v>0.6888888888888889</v>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E63" s="5" t="n">
+        <v>13.47</v>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1822,7 +2039,10 @@
       <c r="D64" s="4" t="n">
         <v>0.7375</v>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E64" s="5" t="n">
+        <v>12.18</v>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1843,7 +2063,10 @@
       <c r="D66" s="4" t="n">
         <v>0.7770833333333333</v>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E66" s="5" t="n">
+        <v>12.48</v>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>last day of month; final record</t>
         </is>
@@ -1864,7 +2087,10 @@
       <c r="D67" s="4" t="n">
         <v>0.75625</v>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E67" s="5" t="n">
+        <v>12.42</v>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1885,7 +2111,10 @@
       <c r="D68" s="4" t="n">
         <v>0.7375</v>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E68" s="5" t="n">
+        <v>13.22</v>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1906,7 +2135,10 @@
       <c r="D69" s="4" t="n">
         <v>0.7131944444444445</v>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E69" s="5" t="n">
+        <v>13.55</v>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1931,6 +2163,11 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
           <t>single punch only</t>
         </is>
       </c>
@@ -1950,32 +2187,40 @@
       <c r="D71" s="4" t="n">
         <v>0.6986111111111111</v>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E71" s="5" t="n">
+        <v>14.98</v>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="5" t="inlineStr">
+      <c r="A72" s="6" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B72" s="6" t="n">
+      <c r="B72" s="7" t="n">
         <v>46241</v>
       </c>
-      <c r="C72" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D72" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E72" s="5" t="inlineStr">
+      <c r="C72" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D72" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E72" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F72" s="6" t="inlineStr">
         <is>
           <t>No entry</t>
         </is>
@@ -1996,7 +2241,10 @@
       <c r="D73" s="4" t="n">
         <v>0.8006944444444445</v>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E73" s="5" t="n">
+        <v>11.93</v>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>extra punch: 17:31</t>
         </is>
@@ -2017,7 +2265,10 @@
       <c r="D74" s="4" t="n">
         <v>0.8048611111111111</v>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E74" s="5" t="n">
+        <v>12.98</v>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2038,7 +2289,10 @@
       <c r="D75" s="4" t="n">
         <v>0.8069444444444445</v>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E75" s="5" t="n">
+        <v>10.18</v>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>extra punch: 05:36</t>
         </is>
@@ -2063,6 +2317,11 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
           <t>single punch only</t>
         </is>
       </c>
@@ -2082,7 +2341,10 @@
       <c r="D77" s="4" t="n">
         <v>0.7</v>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E77" s="5" t="n">
+        <v>13.47</v>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>extra punch: 06:26</t>
         </is>
@@ -2103,32 +2365,40 @@
       <c r="D78" s="4" t="n">
         <v>0.7555555555555555</v>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E78" s="5" t="n">
+        <v>13.45</v>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="5" t="inlineStr">
+      <c r="A79" s="6" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B79" s="6" t="n">
+      <c r="B79" s="7" t="n">
         <v>46248</v>
       </c>
-      <c r="C79" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D79" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E79" s="5" t="inlineStr">
+      <c r="C79" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D79" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E79" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F79" s="6" t="inlineStr">
         <is>
           <t>No entry</t>
         </is>
@@ -2149,7 +2419,10 @@
       <c r="D80" s="4" t="n">
         <v>0.8034722222222223</v>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E80" s="5" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2170,7 +2443,10 @@
       <c r="D81" s="4" t="n">
         <v>0.7166666666666667</v>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E81" s="5" t="n">
+        <v>14.47</v>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2191,7 +2467,10 @@
       <c r="D82" s="4" t="n">
         <v>0.7319444444444444</v>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E82" s="5" t="n">
+        <v>13.62</v>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2212,7 +2491,10 @@
       <c r="D83" s="4" t="n">
         <v>0.8368055555555556</v>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E83" s="5" t="n">
+        <v>10.53</v>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2233,7 +2515,10 @@
       <c r="D84" s="4" t="n">
         <v>0.7236111111111111</v>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E84" s="5" t="n">
+        <v>14.22</v>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2254,32 +2539,40 @@
       <c r="D85" s="4" t="n">
         <v>0.8111111111111111</v>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="E85" s="5" t="n">
+        <v>11.35</v>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="5" t="inlineStr">
+      <c r="A86" s="6" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B86" s="6" t="n">
+      <c r="B86" s="7" t="n">
         <v>46255</v>
       </c>
-      <c r="C86" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D86" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E86" s="5" t="inlineStr">
+      <c r="C86" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D86" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E86" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F86" s="6" t="inlineStr">
         <is>
           <t>No entry</t>
         </is>
@@ -2300,7 +2593,10 @@
       <c r="D87" s="4" t="n">
         <v>0.7444444444444445</v>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="E87" s="5" t="n">
+        <v>13.07</v>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2321,7 +2617,10 @@
       <c r="D88" s="4" t="n">
         <v>0.7277777777777777</v>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="E88" s="5" t="n">
+        <v>12.57</v>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2342,7 +2641,10 @@
       <c r="D89" s="4" t="n">
         <v>0.7534722222222222</v>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="E89" s="5" t="n">
+        <v>12.77</v>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2363,7 +2665,10 @@
       <c r="D90" s="4" t="n">
         <v>0.7506944444444444</v>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="E90" s="5" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2384,7 +2689,10 @@
       <c r="D91" s="4" t="n">
         <v>0.8083333333333333</v>
       </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="E91" s="5" t="n">
+        <v>13.85</v>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2405,32 +2713,40 @@
       <c r="D92" s="4" t="n">
         <v>0.8090277777777778</v>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="E92" s="5" t="n">
+        <v>12.68</v>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="5" t="inlineStr">
+      <c r="A93" s="6" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B93" s="6" t="n">
+      <c r="B93" s="7" t="n">
         <v>46262</v>
       </c>
-      <c r="C93" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D93" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E93" s="5" t="inlineStr">
+      <c r="C93" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D93" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E93" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F93" s="6" t="inlineStr">
         <is>
           <t>No entry</t>
         </is>
@@ -2455,6 +2771,11 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
           <t>single punch only</t>
         </is>
       </c>
@@ -2480,6 +2801,11 @@
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
           <t>No entry</t>
         </is>
       </c>
@@ -2505,6 +2831,11 @@
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
           <t>No entry</t>
         </is>
       </c>
@@ -2524,7 +2855,10 @@
       <c r="D98" s="4" t="n">
         <v>0.7076388888888889</v>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="E98" s="5" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
         <is>
           <t>last day of month; final record</t>
         </is>
@@ -2545,7 +2879,10 @@
       <c r="D99" s="4" t="n">
         <v>0.7986111111111112</v>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="E99" s="5" t="n">
+        <v>11.83</v>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2566,7 +2903,10 @@
       <c r="D100" s="4" t="n">
         <v>0.7520833333333333</v>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="E100" s="5" t="n">
+        <v>13.85</v>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2587,7 +2927,10 @@
       <c r="D101" s="4" t="n">
         <v>0.7597222222222222</v>
       </c>
-      <c r="E101" s="2" t="inlineStr">
+      <c r="E101" s="5" t="n">
+        <v>13.07</v>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2608,7 +2951,10 @@
       <c r="D102" s="4" t="n">
         <v>0.7715277777777778</v>
       </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="E102" s="5" t="n">
+        <v>12.87</v>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2629,32 +2975,40 @@
       <c r="D103" s="4" t="n">
         <v>0.7493055555555556</v>
       </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="E103" s="5" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="5" t="inlineStr">
+      <c r="A104" s="6" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="B104" s="6" t="n">
+      <c r="B104" s="7" t="n">
         <v>46241</v>
       </c>
-      <c r="C104" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D104" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E104" s="5" t="inlineStr">
+      <c r="C104" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D104" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E104" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F104" s="6" t="inlineStr">
         <is>
           <t>No entry</t>
         </is>
@@ -2675,7 +3029,10 @@
       <c r="D105" s="4" t="n">
         <v>0.7673611111111112</v>
       </c>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="E105" s="5" t="n">
+        <v>13.12</v>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2696,7 +3053,10 @@
       <c r="D106" s="4" t="n">
         <v>0.6972222222222222</v>
       </c>
-      <c r="E106" s="2" t="inlineStr">
+      <c r="E106" s="5" t="n">
+        <v>14.57</v>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2717,7 +3077,10 @@
       <c r="D107" s="4" t="n">
         <v>0.7472222222222222</v>
       </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="E107" s="5" t="n">
+        <v>11.65</v>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2738,7 +3101,10 @@
       <c r="D108" s="4" t="n">
         <v>0.7083333333333334</v>
       </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="E108" s="5" t="n">
+        <v>12.58</v>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2759,7 +3125,10 @@
       <c r="D109" s="4" t="n">
         <v>0.7486111111111111</v>
       </c>
-      <c r="E109" s="2" t="inlineStr">
+      <c r="E109" s="5" t="n">
+        <v>13.32</v>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2780,32 +3149,40 @@
       <c r="D110" s="4" t="n">
         <v>0.73125</v>
       </c>
-      <c r="E110" s="2" t="inlineStr">
+      <c r="E110" s="5" t="n">
+        <v>12.27</v>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="5" t="inlineStr">
+      <c r="A111" s="6" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="B111" s="6" t="n">
+      <c r="B111" s="7" t="n">
         <v>46248</v>
       </c>
-      <c r="C111" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D111" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E111" s="5" t="inlineStr">
+      <c r="C111" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D111" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E111" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F111" s="6" t="inlineStr">
         <is>
           <t>No entry</t>
         </is>
@@ -2826,7 +3203,10 @@
       <c r="D112" s="4" t="n">
         <v>0.7868055555555555</v>
       </c>
-      <c r="E112" s="2" t="inlineStr">
+      <c r="E112" s="5" t="n">
+        <v>12.27</v>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2847,7 +3227,10 @@
       <c r="D113" s="4" t="n">
         <v>0.7180555555555556</v>
       </c>
-      <c r="E113" s="2" t="inlineStr">
+      <c r="E113" s="5" t="n">
+        <v>13.38</v>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2868,7 +3251,10 @@
       <c r="D114" s="4" t="n">
         <v>0.7472222222222222</v>
       </c>
-      <c r="E114" s="2" t="inlineStr">
+      <c r="E114" s="5" t="n">
+        <v>12.85</v>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2889,7 +3275,10 @@
       <c r="D115" s="4" t="n">
         <v>0.7576388888888889</v>
       </c>
-      <c r="E115" s="2" t="inlineStr">
+      <c r="E115" s="5" t="n">
+        <v>11.98</v>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2910,7 +3299,10 @@
       <c r="D116" s="4" t="n">
         <v>0.7576388888888889</v>
       </c>
-      <c r="E116" s="2" t="inlineStr">
+      <c r="E116" s="5" t="n">
+        <v>14.17</v>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2931,32 +3323,40 @@
       <c r="D117" s="4" t="n">
         <v>0.7458333333333333</v>
       </c>
-      <c r="E117" s="2" t="inlineStr">
+      <c r="E117" s="5" t="n">
+        <v>12.78</v>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="5" t="inlineStr">
+      <c r="A118" s="6" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="B118" s="6" t="n">
+      <c r="B118" s="7" t="n">
         <v>46255</v>
       </c>
-      <c r="C118" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D118" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E118" s="5" t="inlineStr">
+      <c r="C118" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D118" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E118" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F118" s="6" t="inlineStr">
         <is>
           <t>No entry</t>
         </is>
@@ -2977,7 +3377,10 @@
       <c r="D119" s="4" t="n">
         <v>0.7548611111111111</v>
       </c>
-      <c r="E119" s="2" t="inlineStr">
+      <c r="E119" s="5" t="n">
+        <v>13.08</v>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2998,7 +3401,10 @@
       <c r="D120" s="4" t="n">
         <v>0.7555555555555555</v>
       </c>
-      <c r="E120" s="2" t="inlineStr">
+      <c r="E120" s="5" t="n">
+        <v>11.88</v>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3019,7 +3425,10 @@
       <c r="D121" s="4" t="n">
         <v>0.7541666666666667</v>
       </c>
-      <c r="E121" s="2" t="inlineStr">
+      <c r="E121" s="5" t="n">
+        <v>13.32</v>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3040,7 +3449,10 @@
       <c r="D122" s="4" t="n">
         <v>0.7486111111111111</v>
       </c>
-      <c r="E122" s="2" t="inlineStr">
+      <c r="E122" s="5" t="n">
+        <v>12.02</v>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3061,7 +3473,10 @@
       <c r="D123" s="4" t="n">
         <v>0.7701388888888889</v>
       </c>
-      <c r="E123" s="2" t="inlineStr">
+      <c r="E123" s="5" t="n">
+        <v>11.15</v>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3082,32 +3497,40 @@
       <c r="D124" s="4" t="n">
         <v>0.7861111111111111</v>
       </c>
-      <c r="E124" s="2" t="inlineStr">
+      <c r="E124" s="5" t="n">
+        <v>11.92</v>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="5" t="inlineStr">
+      <c r="A125" s="6" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="B125" s="6" t="n">
+      <c r="B125" s="7" t="n">
         <v>46262</v>
       </c>
-      <c r="C125" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D125" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E125" s="5" t="inlineStr">
+      <c r="C125" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D125" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E125" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F125" s="6" t="inlineStr">
         <is>
           <t>No entry</t>
         </is>
@@ -3128,7 +3551,10 @@
       <c r="D126" s="4" t="n">
         <v>0.7708333333333334</v>
       </c>
-      <c r="E126" s="2" t="inlineStr">
+      <c r="E126" s="5" t="n">
+        <v>12.68</v>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3149,7 +3575,10 @@
       <c r="D127" s="4" t="n">
         <v>0.6805555555555556</v>
       </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="E127" s="5" t="n">
+        <v>15.02</v>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3170,7 +3599,10 @@
       <c r="D128" s="4" t="n">
         <v>0.7555555555555555</v>
       </c>
-      <c r="E128" s="2" t="inlineStr">
+      <c r="E128" s="5" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3195,6 +3627,11 @@
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
           <t>single punch only; last day of month</t>
         </is>
       </c>
@@ -3218,6 +3655,11 @@
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
           <t>single punch only</t>
         </is>
       </c>
@@ -3241,6 +3683,11 @@
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
           <t>single punch only</t>
         </is>
       </c>
@@ -3264,6 +3711,11 @@
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
           <t>single punch only</t>
         </is>
       </c>
@@ -3287,6 +3739,11 @@
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
           <t>single punch only</t>
         </is>
       </c>
@@ -3310,30 +3767,40 @@
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
           <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="5" t="inlineStr">
+      <c r="A136" s="6" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B136" s="6" t="n">
+      <c r="B136" s="7" t="n">
         <v>46241</v>
       </c>
-      <c r="C136" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D136" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E136" s="5" t="inlineStr">
+      <c r="C136" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D136" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E136" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F136" s="6" t="inlineStr">
         <is>
           <t>No entry</t>
         </is>
@@ -3358,6 +3825,11 @@
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
           <t>single punch only</t>
         </is>
       </c>
@@ -3377,7 +3849,10 @@
       <c r="D138" s="4" t="n">
         <v>0.7277777777777777</v>
       </c>
-      <c r="E138" s="2" t="inlineStr">
+      <c r="E138" s="5" t="n">
+        <v>13.42</v>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3398,7 +3873,10 @@
       <c r="D139" s="4" t="n">
         <v>0.7555555555555555</v>
       </c>
-      <c r="E139" s="2" t="inlineStr">
+      <c r="E139" s="5" t="n">
+        <v>11.52</v>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3423,6 +3901,11 @@
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
           <t>single punch only</t>
         </is>
       </c>
@@ -3442,7 +3925,10 @@
       <c r="D141" s="4" t="n">
         <v>0.7673611111111112</v>
       </c>
-      <c r="E141" s="2" t="inlineStr">
+      <c r="E141" s="5" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3467,28 +3953,38 @@
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
           <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="5" t="inlineStr">
+      <c r="A143" s="6" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B143" s="6" t="n">
+      <c r="B143" s="7" t="n">
         <v>46248</v>
       </c>
-      <c r="C143" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D143" s="7" t="n">
+      <c r="C143" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D143" s="8" t="n">
         <v>0.7708333333333334</v>
       </c>
-      <c r="E143" s="5" t="inlineStr">
+      <c r="E143" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F143" s="6" t="inlineStr">
         <is>
           <t>single punch only</t>
         </is>
@@ -3509,7 +4005,10 @@
       <c r="D144" s="4" t="n">
         <v>0.7375</v>
       </c>
-      <c r="E144" s="2" t="inlineStr">
+      <c r="E144" s="5" t="n">
+        <v>13.53</v>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3534,6 +4033,11 @@
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
           <t>single punch only</t>
         </is>
       </c>
@@ -3557,6 +4061,11 @@
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
           <t>single punch only</t>
         </is>
       </c>
@@ -3580,6 +4089,11 @@
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
           <t>single punch only</t>
         </is>
       </c>
@@ -3603,6 +4117,11 @@
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
           <t>single punch only</t>
         </is>
       </c>
@@ -3626,28 +4145,38 @@
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
           <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="5" t="inlineStr">
+      <c r="A150" s="6" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B150" s="6" t="n">
+      <c r="B150" s="7" t="n">
         <v>46255</v>
       </c>
-      <c r="C150" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D150" s="7" t="n">
+      <c r="C150" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D150" s="8" t="n">
         <v>0.7333333333333333</v>
       </c>
-      <c r="E150" s="5" t="inlineStr">
+      <c r="E150" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F150" s="6" t="inlineStr">
         <is>
           <t>single punch only</t>
         </is>
@@ -3668,7 +4197,10 @@
       <c r="D151" s="4" t="n">
         <v>0.7305555555555555</v>
       </c>
-      <c r="E151" s="2" t="inlineStr">
+      <c r="E151" s="5" t="n">
+        <v>13.58</v>
+      </c>
+      <c r="F151" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3689,7 +4221,10 @@
       <c r="D152" s="4" t="n">
         <v>0.7222222222222222</v>
       </c>
-      <c r="E152" s="2" t="inlineStr">
+      <c r="E152" s="5" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3714,6 +4249,11 @@
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
           <t>single punch only</t>
         </is>
       </c>
@@ -3737,6 +4277,11 @@
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
           <t>single punch only</t>
         </is>
       </c>
@@ -3762,6 +4307,11 @@
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
           <t>No entry</t>
         </is>
       </c>
@@ -3785,30 +4335,40 @@
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
           <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="5" t="inlineStr">
+      <c r="A157" s="6" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B157" s="6" t="n">
+      <c r="B157" s="7" t="n">
         <v>46262</v>
       </c>
-      <c r="C157" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D157" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E157" s="5" t="inlineStr">
+      <c r="C157" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D157" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E157" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F157" s="6" t="inlineStr">
         <is>
           <t>No entry</t>
         </is>
@@ -3833,6 +4393,11 @@
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
           <t>single punch only</t>
         </is>
       </c>
@@ -3858,6 +4423,11 @@
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
           <t>No entry</t>
         </is>
       </c>
@@ -3877,7 +4447,10 @@
       <c r="D160" s="4" t="n">
         <v>0.7534722222222222</v>
       </c>
-      <c r="E160" s="2" t="inlineStr">
+      <c r="E160" s="5" t="n">
+        <v>12.65</v>
+      </c>
+      <c r="F160" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3898,7 +4471,10 @@
       <c r="D162" s="4" t="n">
         <v>0.7486111111111111</v>
       </c>
-      <c r="E162" s="2" t="inlineStr">
+      <c r="E162" s="5" t="n">
+        <v>13.43</v>
+      </c>
+      <c r="F162" s="2" t="inlineStr">
         <is>
           <t>last day of month; final record</t>
         </is>
@@ -3923,6 +4499,11 @@
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F163" s="2" t="inlineStr">
+        <is>
           <t>single punch only</t>
         </is>
       </c>
@@ -3942,7 +4523,10 @@
       <c r="D164" s="4" t="n">
         <v>0.7736111111111111</v>
       </c>
-      <c r="E164" s="2" t="inlineStr">
+      <c r="E164" s="5" t="n">
+        <v>13.75</v>
+      </c>
+      <c r="F164" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3963,7 +4547,10 @@
       <c r="D165" s="4" t="n">
         <v>0.7597222222222222</v>
       </c>
-      <c r="E165" s="2" t="inlineStr">
+      <c r="E165" s="5" t="n">
+        <v>14.38</v>
+      </c>
+      <c r="F165" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3984,7 +4571,10 @@
       <c r="D166" s="4" t="n">
         <v>0.7944444444444444</v>
       </c>
-      <c r="E166" s="2" t="inlineStr">
+      <c r="E166" s="5" t="n">
+        <v>13.17</v>
+      </c>
+      <c r="F166" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4005,32 +4595,40 @@
       <c r="D167" s="4" t="n">
         <v>0.7673611111111112</v>
       </c>
-      <c r="E167" s="2" t="inlineStr">
+      <c r="E167" s="5" t="n">
+        <v>14.47</v>
+      </c>
+      <c r="F167" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="5" t="inlineStr">
+      <c r="A168" s="6" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="B168" s="6" t="n">
+      <c r="B168" s="7" t="n">
         <v>46241</v>
       </c>
-      <c r="C168" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D168" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E168" s="5" t="inlineStr">
+      <c r="C168" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D168" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E168" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F168" s="6" t="inlineStr">
         <is>
           <t>No entry</t>
         </is>
@@ -4051,7 +4649,10 @@
       <c r="D169" s="4" t="n">
         <v>0.7666666666666667</v>
       </c>
-      <c r="E169" s="2" t="inlineStr">
+      <c r="E169" s="5" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="F169" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4072,7 +4673,10 @@
       <c r="D170" s="4" t="n">
         <v>0.7319444444444444</v>
       </c>
-      <c r="E170" s="2" t="inlineStr">
+      <c r="E170" s="5" t="n">
+        <v>14.93</v>
+      </c>
+      <c r="F170" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4093,7 +4697,10 @@
       <c r="D171" s="4" t="n">
         <v>0.7652777777777777</v>
       </c>
-      <c r="E171" s="2" t="inlineStr">
+      <c r="E171" s="5" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="F171" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4114,7 +4721,10 @@
       <c r="D172" s="4" t="n">
         <v>0.7409722222222223</v>
       </c>
-      <c r="E172" s="2" t="inlineStr">
+      <c r="E172" s="5" t="n">
+        <v>15.07</v>
+      </c>
+      <c r="F172" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4135,7 +4745,10 @@
       <c r="D173" s="4" t="n">
         <v>0.7368055555555556</v>
       </c>
-      <c r="E173" s="2" t="inlineStr">
+      <c r="E173" s="5" t="n">
+        <v>14.75</v>
+      </c>
+      <c r="F173" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4156,32 +4769,40 @@
       <c r="D174" s="4" t="n">
         <v>0.7756944444444445</v>
       </c>
-      <c r="E174" s="2" t="inlineStr">
+      <c r="E174" s="5" t="n">
+        <v>14.17</v>
+      </c>
+      <c r="F174" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="5" t="inlineStr">
+      <c r="A175" s="6" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="B175" s="6" t="n">
+      <c r="B175" s="7" t="n">
         <v>46248</v>
       </c>
-      <c r="C175" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D175" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E175" s="5" t="inlineStr">
+      <c r="C175" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D175" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E175" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F175" s="6" t="inlineStr">
         <is>
           <t>No entry</t>
         </is>
@@ -4202,7 +4823,10 @@
       <c r="D176" s="4" t="n">
         <v>0.7701388888888889</v>
       </c>
-      <c r="E176" s="2" t="inlineStr">
+      <c r="E176" s="5" t="n">
+        <v>14.73</v>
+      </c>
+      <c r="F176" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4223,7 +4847,10 @@
       <c r="D177" s="4" t="n">
         <v>0.7673611111111112</v>
       </c>
-      <c r="E177" s="2" t="inlineStr">
+      <c r="E177" s="5" t="n">
+        <v>13.37</v>
+      </c>
+      <c r="F177" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4248,6 +4875,11 @@
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
           <t>single punch only</t>
         </is>
       </c>
@@ -4267,7 +4899,10 @@
       <c r="D179" s="4" t="n">
         <v>0.7694444444444445</v>
       </c>
-      <c r="E179" s="2" t="inlineStr">
+      <c r="E179" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="F179" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4288,7 +4923,10 @@
       <c r="D180" s="4" t="n">
         <v>0.7604166666666666</v>
       </c>
-      <c r="E180" s="2" t="inlineStr">
+      <c r="E180" s="5" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="F180" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4309,32 +4947,40 @@
       <c r="D181" s="4" t="n">
         <v>0.7673611111111112</v>
       </c>
-      <c r="E181" s="2" t="inlineStr">
+      <c r="E181" s="5" t="n">
+        <v>14.17</v>
+      </c>
+      <c r="F181" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="5" t="inlineStr">
+      <c r="A182" s="6" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="B182" s="6" t="n">
+      <c r="B182" s="7" t="n">
         <v>46255</v>
       </c>
-      <c r="C182" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D182" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E182" s="5" t="inlineStr">
+      <c r="C182" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D182" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E182" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F182" s="6" t="inlineStr">
         <is>
           <t>No entry</t>
         </is>
@@ -4355,7 +5001,10 @@
       <c r="D183" s="4" t="n">
         <v>0.7569444444444444</v>
       </c>
-      <c r="E183" s="2" t="inlineStr">
+      <c r="E183" s="5" t="n">
+        <v>12.92</v>
+      </c>
+      <c r="F183" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4376,7 +5025,10 @@
       <c r="D184" s="4" t="n">
         <v>0.7694444444444445</v>
       </c>
-      <c r="E184" s="2" t="inlineStr">
+      <c r="E184" s="5" t="n">
+        <v>11.58</v>
+      </c>
+      <c r="F184" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4397,7 +5049,10 @@
       <c r="D185" s="4" t="n">
         <v>0.7729166666666667</v>
       </c>
-      <c r="E185" s="2" t="inlineStr">
+      <c r="E185" s="5" t="n">
+        <v>14.17</v>
+      </c>
+      <c r="F185" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4418,7 +5073,10 @@
       <c r="D186" s="4" t="n">
         <v>0.7361111111111112</v>
       </c>
-      <c r="E186" s="2" t="inlineStr">
+      <c r="E186" s="5" t="n">
+        <v>14.68</v>
+      </c>
+      <c r="F186" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4439,7 +5097,10 @@
       <c r="D187" s="4" t="n">
         <v>0.7611111111111111</v>
       </c>
-      <c r="E187" s="2" t="inlineStr">
+      <c r="E187" s="5" t="n">
+        <v>13.73</v>
+      </c>
+      <c r="F187" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4460,32 +5121,40 @@
       <c r="D188" s="4" t="n">
         <v>0.7395833333333334</v>
       </c>
-      <c r="E188" s="2" t="inlineStr">
+      <c r="E188" s="5" t="n">
+        <v>15.02</v>
+      </c>
+      <c r="F188" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="5" t="inlineStr">
+      <c r="A189" s="6" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="B189" s="6" t="n">
+      <c r="B189" s="7" t="n">
         <v>46262</v>
       </c>
-      <c r="C189" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D189" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E189" s="5" t="inlineStr">
+      <c r="C189" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D189" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E189" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F189" s="6" t="inlineStr">
         <is>
           <t>No entry</t>
         </is>
@@ -4506,7 +5175,10 @@
       <c r="D190" s="4" t="n">
         <v>0.7569444444444444</v>
       </c>
-      <c r="E190" s="2" t="inlineStr">
+      <c r="E190" s="5" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="F190" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4527,7 +5199,10 @@
       <c r="D191" s="4" t="n">
         <v>0.7534722222222222</v>
       </c>
-      <c r="E191" s="2" t="inlineStr">
+      <c r="E191" s="5" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="F191" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4548,7 +5223,10 @@
       <c r="D192" s="4" t="n">
         <v>0.7680555555555556</v>
       </c>
-      <c r="E192" s="2" t="inlineStr">
+      <c r="E192" s="5" t="n">
+        <v>13.53</v>
+      </c>
+      <c r="F192" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4575,6 +5253,11 @@
       </c>
       <c r="E194" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F194" s="2" t="inlineStr">
+        <is>
           <t>No entry</t>
         </is>
       </c>
@@ -4594,7 +5277,10 @@
       <c r="D195" s="4" t="n">
         <v>0.775</v>
       </c>
-      <c r="E195" s="2" t="inlineStr">
+      <c r="E195" s="5" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="F195" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4615,7 +5301,10 @@
       <c r="D196" s="4" t="n">
         <v>0.7041666666666667</v>
       </c>
-      <c r="E196" s="2" t="inlineStr">
+      <c r="E196" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="F196" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4636,7 +5325,10 @@
       <c r="D197" s="4" t="n">
         <v>0.7597222222222222</v>
       </c>
-      <c r="E197" s="2" t="inlineStr">
+      <c r="E197" s="5" t="n">
+        <v>13.08</v>
+      </c>
+      <c r="F197" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4657,7 +5349,10 @@
       <c r="D198" s="4" t="n">
         <v>0.7715277777777778</v>
       </c>
-      <c r="E198" s="2" t="inlineStr">
+      <c r="E198" s="5" t="n">
+        <v>12.53</v>
+      </c>
+      <c r="F198" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4678,32 +5373,40 @@
       <c r="D199" s="4" t="n">
         <v>0.7458333333333333</v>
       </c>
-      <c r="E199" s="2" t="inlineStr">
+      <c r="E199" s="5" t="n">
+        <v>13.28</v>
+      </c>
+      <c r="F199" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="5" t="inlineStr">
+      <c r="A200" s="6" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="B200" s="6" t="n">
+      <c r="B200" s="7" t="n">
         <v>46241</v>
       </c>
-      <c r="C200" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D200" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E200" s="5" t="inlineStr">
+      <c r="C200" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D200" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E200" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F200" s="6" t="inlineStr">
         <is>
           <t>No entry</t>
         </is>
@@ -4724,7 +5427,10 @@
       <c r="D201" s="4" t="n">
         <v>0.7666666666666667</v>
       </c>
-      <c r="E201" s="2" t="inlineStr">
+      <c r="E201" s="5" t="n">
+        <v>13.12</v>
+      </c>
+      <c r="F201" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4745,7 +5451,10 @@
       <c r="D202" s="4" t="n">
         <v>0.7694444444444445</v>
       </c>
-      <c r="E202" s="2" t="inlineStr">
+      <c r="E202" s="5" t="n">
+        <v>12.83</v>
+      </c>
+      <c r="F202" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4766,7 +5475,10 @@
       <c r="D203" s="4" t="n">
         <v>0.7479166666666667</v>
       </c>
-      <c r="E203" s="2" t="inlineStr">
+      <c r="E203" s="5" t="n">
+        <v>11.62</v>
+      </c>
+      <c r="F203" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4787,7 +5499,10 @@
       <c r="D204" s="4" t="n">
         <v>0.7458333333333333</v>
       </c>
-      <c r="E204" s="2" t="inlineStr">
+      <c r="E204" s="5" t="n">
+        <v>11.85</v>
+      </c>
+      <c r="F204" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4808,7 +5523,10 @@
       <c r="D205" s="4" t="n">
         <v>0.70625</v>
       </c>
-      <c r="E205" s="2" t="inlineStr">
+      <c r="E205" s="5" t="n">
+        <v>14.33</v>
+      </c>
+      <c r="F205" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4829,32 +5547,40 @@
       <c r="D206" s="4" t="n">
         <v>0.7631944444444444</v>
       </c>
-      <c r="E206" s="2" t="inlineStr">
+      <c r="E206" s="5" t="n">
+        <v>12.03</v>
+      </c>
+      <c r="F206" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="5" t="inlineStr">
+      <c r="A207" s="6" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="B207" s="6" t="n">
+      <c r="B207" s="7" t="n">
         <v>46248</v>
       </c>
-      <c r="C207" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D207" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E207" s="5" t="inlineStr">
+      <c r="C207" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D207" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E207" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F207" s="6" t="inlineStr">
         <is>
           <t>No entry</t>
         </is>
@@ -4875,7 +5601,10 @@
       <c r="D208" s="4" t="n">
         <v>0.7638888888888888</v>
       </c>
-      <c r="E208" s="2" t="inlineStr">
+      <c r="E208" s="5" t="n">
+        <v>12.13</v>
+      </c>
+      <c r="F208" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4896,7 +5625,10 @@
       <c r="D209" s="4" t="n">
         <v>0.7180555555555556</v>
       </c>
-      <c r="E209" s="2" t="inlineStr">
+      <c r="E209" s="5" t="n">
+        <v>13.55</v>
+      </c>
+      <c r="F209" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4917,7 +5649,10 @@
       <c r="D210" s="4" t="n">
         <v>0.7465277777777778</v>
       </c>
-      <c r="E210" s="2" t="inlineStr">
+      <c r="E210" s="5" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="F210" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4938,7 +5673,10 @@
       <c r="D211" s="4" t="n">
         <v>0.7569444444444444</v>
       </c>
-      <c r="E211" s="2" t="inlineStr">
+      <c r="E211" s="5" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="F211" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4959,7 +5697,10 @@
       <c r="D212" s="4" t="n">
         <v>0.7506944444444444</v>
       </c>
-      <c r="E212" s="2" t="inlineStr">
+      <c r="E212" s="5" t="n">
+        <v>12.43</v>
+      </c>
+      <c r="F212" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4980,32 +5721,40 @@
       <c r="D213" s="4" t="n">
         <v>0.7451388888888889</v>
       </c>
-      <c r="E213" s="2" t="inlineStr">
+      <c r="E213" s="5" t="n">
+        <v>12.38</v>
+      </c>
+      <c r="F213" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="5" t="inlineStr">
+      <c r="A214" s="6" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="B214" s="6" t="n">
+      <c r="B214" s="7" t="n">
         <v>46255</v>
       </c>
-      <c r="C214" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D214" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E214" s="5" t="inlineStr">
+      <c r="C214" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D214" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E214" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F214" s="6" t="inlineStr">
         <is>
           <t>No entry</t>
         </is>
@@ -5026,7 +5775,10 @@
       <c r="D215" s="4" t="n">
         <v>0.7541666666666667</v>
       </c>
-      <c r="E215" s="2" t="inlineStr">
+      <c r="E215" s="5" t="n">
+        <v>13.12</v>
+      </c>
+      <c r="F215" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -5047,7 +5799,10 @@
       <c r="D216" s="4" t="n">
         <v>0.74375</v>
       </c>
-      <c r="E216" s="2" t="inlineStr">
+      <c r="E216" s="5" t="n">
+        <v>12.25</v>
+      </c>
+      <c r="F216" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -5068,7 +5823,10 @@
       <c r="D217" s="4" t="n">
         <v>0.7472222222222222</v>
       </c>
-      <c r="E217" s="2" t="inlineStr">
+      <c r="E217" s="5" t="n">
+        <v>12.22</v>
+      </c>
+      <c r="F217" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -5089,7 +5847,10 @@
       <c r="D218" s="4" t="n">
         <v>0.7479166666666667</v>
       </c>
-      <c r="E218" s="2" t="inlineStr">
+      <c r="E218" s="5" t="n">
+        <v>12.18</v>
+      </c>
+      <c r="F218" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -5110,7 +5871,10 @@
       <c r="D219" s="4" t="n">
         <v>0.7416666666666667</v>
       </c>
-      <c r="E219" s="2" t="inlineStr">
+      <c r="E219" s="5" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="F219" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -5131,32 +5895,40 @@
       <c r="D220" s="4" t="n">
         <v>0.7430555555555556</v>
       </c>
-      <c r="E220" s="2" t="inlineStr">
+      <c r="E220" s="5" t="n">
+        <v>13.15</v>
+      </c>
+      <c r="F220" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="5" t="inlineStr">
+      <c r="A221" s="6" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="B221" s="6" t="n">
+      <c r="B221" s="7" t="n">
         <v>46262</v>
       </c>
-      <c r="C221" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D221" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E221" s="5" t="inlineStr">
+      <c r="C221" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D221" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E221" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F221" s="6" t="inlineStr">
         <is>
           <t>No entry</t>
         </is>
@@ -5177,7 +5949,10 @@
       <c r="D222" s="4" t="n">
         <v>0.7513888888888889</v>
       </c>
-      <c r="E222" s="2" t="inlineStr">
+      <c r="E222" s="5" t="n">
+        <v>12.57</v>
+      </c>
+      <c r="F222" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -5198,7 +5973,10 @@
       <c r="D223" s="4" t="n">
         <v>0.7493055555555556</v>
       </c>
-      <c r="E223" s="2" t="inlineStr">
+      <c r="E223" s="5" t="n">
+        <v>13.68</v>
+      </c>
+      <c r="F223" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -5219,7 +5997,10 @@
       <c r="D224" s="4" t="n">
         <v>0.7555555555555555</v>
       </c>
-      <c r="E224" s="2" t="inlineStr">
+      <c r="E224" s="5" t="n">
+        <v>12.18</v>
+      </c>
+      <c r="F224" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -5244,6 +6025,11 @@
       </c>
       <c r="E226" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F226" s="2" t="inlineStr">
+        <is>
           <t>Night Security; single punch only; last day of month</t>
         </is>
       </c>
@@ -5267,6 +6053,11 @@
       </c>
       <c r="E227" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F227" s="2" t="inlineStr">
+        <is>
           <t>Night Security; single punch only</t>
         </is>
       </c>
@@ -5286,7 +6077,10 @@
       <c r="D228" s="4" t="n">
         <v>0.74375</v>
       </c>
-      <c r="E228" s="2" t="inlineStr">
+      <c r="E228" s="5" t="n">
+        <v>14.55</v>
+      </c>
+      <c r="F228" s="2" t="inlineStr">
         <is>
           <t>Night Security; extra punch: 17:50</t>
         </is>
@@ -5307,7 +6101,10 @@
       <c r="D229" s="4" t="n">
         <v>0.7701388888888889</v>
       </c>
-      <c r="E229" s="2" t="inlineStr">
+      <c r="E229" s="5" t="n">
+        <v>14.78</v>
+      </c>
+      <c r="F229" s="2" t="inlineStr">
         <is>
           <t>Night Security</t>
         </is>
@@ -5334,6 +6131,11 @@
       </c>
       <c r="E230" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F230" s="2" t="inlineStr">
+        <is>
           <t>No entry</t>
         </is>
       </c>
@@ -5357,28 +6159,36 @@
       </c>
       <c r="E231" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F231" s="2" t="inlineStr">
+        <is>
           <t>Night Security; single punch only</t>
         </is>
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="5" t="inlineStr">
+      <c r="A232" s="6" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="B232" s="6" t="n">
+      <c r="B232" s="7" t="n">
         <v>46241</v>
       </c>
-      <c r="C232" s="7" t="n">
+      <c r="C232" s="8" t="n">
         <v>0.7666666666666667</v>
       </c>
-      <c r="D232" s="7" t="n">
+      <c r="D232" s="8" t="n">
         <v>0.7708333333333334</v>
       </c>
-      <c r="E232" s="5" t="inlineStr">
-        <is>
-          <t>Night Security</t>
+      <c r="E232" s="9" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="F232" s="6" t="inlineStr">
+        <is>
+          <t>Night Security; PLEASE VERIFY: check-in/out only 6 min apart across the day boundary (~23.9h shift) - possible missed punch</t>
         </is>
       </c>
     </row>
@@ -5401,6 +6211,11 @@
       </c>
       <c r="E233" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F233" s="2" t="inlineStr">
+        <is>
           <t>Night Security; single punch only</t>
         </is>
       </c>
@@ -5420,7 +6235,10 @@
       <c r="D234" s="4" t="n">
         <v>0.7222222222222222</v>
       </c>
-      <c r="E234" s="2" t="inlineStr">
+      <c r="E234" s="5" t="n">
+        <v>19.78</v>
+      </c>
+      <c r="F234" s="2" t="inlineStr">
         <is>
           <t>Night Security</t>
         </is>
@@ -5441,7 +6259,10 @@
       <c r="D235" s="4" t="n">
         <v>0.7555555555555555</v>
       </c>
-      <c r="E235" s="2" t="inlineStr">
+      <c r="E235" s="5" t="n">
+        <v>11.37</v>
+      </c>
+      <c r="F235" s="2" t="inlineStr">
         <is>
           <t>Night Security</t>
         </is>
@@ -5466,6 +6287,11 @@
       </c>
       <c r="E236" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F236" s="2" t="inlineStr">
+        <is>
           <t>Night Security; single punch only</t>
         </is>
       </c>
@@ -5485,7 +6311,10 @@
       <c r="D237" s="4" t="n">
         <v>0.7659722222222223</v>
       </c>
-      <c r="E237" s="2" t="inlineStr">
+      <c r="E237" s="5" t="n">
+        <v>13.55</v>
+      </c>
+      <c r="F237" s="2" t="inlineStr">
         <is>
           <t>Night Security</t>
         </is>
@@ -5506,28 +6335,34 @@
       <c r="D238" s="4" t="n">
         <v>0.7569444444444444</v>
       </c>
-      <c r="E238" s="2" t="inlineStr">
+      <c r="E238" s="5" t="n">
+        <v>12.35</v>
+      </c>
+      <c r="F238" s="2" t="inlineStr">
         <is>
           <t>Night Security</t>
         </is>
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="5" t="inlineStr">
+      <c r="A239" s="6" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="B239" s="6" t="n">
+      <c r="B239" s="7" t="n">
         <v>46248</v>
       </c>
-      <c r="C239" s="7" t="n">
+      <c r="C239" s="8" t="n">
         <v>0.2354166666666667</v>
       </c>
-      <c r="D239" s="7" t="n">
+      <c r="D239" s="8" t="n">
         <v>0.7611111111111111</v>
       </c>
-      <c r="E239" s="5" t="inlineStr">
+      <c r="E239" s="9" t="n">
+        <v>11.38</v>
+      </c>
+      <c r="F239" s="6" t="inlineStr">
         <is>
           <t>Night Security; PLEASE VERIFY: extra punches 05:39 05:39 05:39 05:39 repeated - possible device anomaly</t>
         </is>
@@ -5548,7 +6383,10 @@
       <c r="D240" s="4" t="n">
         <v>0.7125</v>
       </c>
-      <c r="E240" s="2" t="inlineStr">
+      <c r="E240" s="5" t="n">
+        <v>12.65</v>
+      </c>
+      <c r="F240" s="2" t="inlineStr">
         <is>
           <t>Night Security; extra punch: 09:31</t>
         </is>
@@ -5573,6 +6411,11 @@
       </c>
       <c r="E241" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F241" s="2" t="inlineStr">
+        <is>
           <t>Night Security; single punch only</t>
         </is>
       </c>
@@ -5592,7 +6435,10 @@
       <c r="D242" s="4" t="n">
         <v>0.7402777777777778</v>
       </c>
-      <c r="E242" s="2" t="inlineStr">
+      <c r="E242" s="5" t="n">
+        <v>14.45</v>
+      </c>
+      <c r="F242" s="2" t="inlineStr">
         <is>
           <t>Night Security</t>
         </is>
@@ -5613,7 +6459,10 @@
       <c r="D243" s="4" t="n">
         <v>0.7923611111111111</v>
       </c>
-      <c r="E243" s="2" t="inlineStr">
+      <c r="E243" s="5" t="n">
+        <v>11.73</v>
+      </c>
+      <c r="F243" s="2" t="inlineStr">
         <is>
           <t>Night Security</t>
         </is>
@@ -5634,7 +6483,10 @@
       <c r="D244" s="4" t="n">
         <v>0.7215277777777778</v>
       </c>
-      <c r="E244" s="2" t="inlineStr">
+      <c r="E244" s="5" t="n">
+        <v>14.33</v>
+      </c>
+      <c r="F244" s="2" t="inlineStr">
         <is>
           <t>Night Security; extra punch: 17:19</t>
         </is>
@@ -5659,26 +6511,36 @@
       </c>
       <c r="E245" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F245" s="2" t="inlineStr">
+        <is>
           <t>Night Security; single punch only</t>
         </is>
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="5" t="inlineStr">
+      <c r="A246" s="6" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="B246" s="6" t="n">
+      <c r="B246" s="7" t="n">
         <v>46255</v>
       </c>
-      <c r="C246" s="7" t="n">
+      <c r="C246" s="8" t="n">
         <v>0.7590277777777777</v>
       </c>
-      <c r="D246" s="7" t="n">
+      <c r="D246" s="8" t="n">
         <v>0.7590277777777777</v>
       </c>
-      <c r="E246" s="5" t="inlineStr">
+      <c r="E246" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F246" s="6" t="inlineStr">
         <is>
           <t>Night Security; PLEASE VERIFY: in/out times read identical - likely OCR error</t>
         </is>
@@ -5699,7 +6561,10 @@
       <c r="D247" s="4" t="n">
         <v>0.7729166666666667</v>
       </c>
-      <c r="E247" s="2" t="inlineStr">
+      <c r="E247" s="5" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="F247" s="2" t="inlineStr">
         <is>
           <t>Night Security; extra punch: 05:45</t>
         </is>
@@ -5720,7 +6585,10 @@
       <c r="D248" s="4" t="n">
         <v>0.7430555555555556</v>
       </c>
-      <c r="E248" s="2" t="inlineStr">
+      <c r="E248" s="5" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="F248" s="2" t="inlineStr">
         <is>
           <t>Night Security</t>
         </is>
@@ -5741,7 +6609,10 @@
       <c r="D249" s="4" t="n">
         <v>0.8027777777777778</v>
       </c>
-      <c r="E249" s="2" t="inlineStr">
+      <c r="E249" s="5" t="n">
+        <v>16.92</v>
+      </c>
+      <c r="F249" s="2" t="inlineStr">
         <is>
           <t>Night Security</t>
         </is>
@@ -5762,7 +6633,10 @@
       <c r="D250" s="4" t="n">
         <v>0.7840277777777778</v>
       </c>
-      <c r="E250" s="2" t="inlineStr">
+      <c r="E250" s="5" t="n">
+        <v>10.17</v>
+      </c>
+      <c r="F250" s="2" t="inlineStr">
         <is>
           <t>Night Security</t>
         </is>
@@ -5783,7 +6657,10 @@
       <c r="D251" s="4" t="n">
         <v>0.8013888888888889</v>
       </c>
-      <c r="E251" s="2" t="inlineStr">
+      <c r="E251" s="5" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="F251" s="2" t="inlineStr">
         <is>
           <t>Night Security</t>
         </is>
@@ -5804,32 +6681,40 @@
       <c r="D252" s="4" t="n">
         <v>0.7493055555555556</v>
       </c>
-      <c r="E252" s="2" t="inlineStr">
+      <c r="E252" s="5" t="n">
+        <v>12.73</v>
+      </c>
+      <c r="F252" s="2" t="inlineStr">
         <is>
           <t>Night Security</t>
         </is>
       </c>
     </row>
     <row r="253">
-      <c r="A253" s="5" t="inlineStr">
+      <c r="A253" s="6" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="B253" s="6" t="n">
+      <c r="B253" s="7" t="n">
         <v>46262</v>
       </c>
-      <c r="C253" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D253" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E253" s="5" t="inlineStr">
+      <c r="C253" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D253" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E253" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F253" s="6" t="inlineStr">
         <is>
           <t>No entry</t>
         </is>
@@ -5850,7 +6735,10 @@
       <c r="D254" s="4" t="n">
         <v>0.8895833333333333</v>
       </c>
-      <c r="E254" s="2" t="inlineStr">
+      <c r="E254" s="5" t="n">
+        <v>10.68</v>
+      </c>
+      <c r="F254" s="2" t="inlineStr">
         <is>
           <t>Night Security; extra punch: 08:02</t>
         </is>
@@ -5871,7 +6759,10 @@
       <c r="D255" s="4" t="n">
         <v>0.7354166666666667</v>
       </c>
-      <c r="E255" s="2" t="inlineStr">
+      <c r="E255" s="5" t="n">
+        <v>14.05</v>
+      </c>
+      <c r="F255" s="2" t="inlineStr">
         <is>
           <t>Night Security</t>
         </is>
@@ -5898,6 +6789,11 @@
       </c>
       <c r="E256" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F256" s="2" t="inlineStr">
+        <is>
           <t>No entry</t>
         </is>
       </c>
@@ -5917,7 +6813,10 @@
       <c r="D258" s="4" t="n">
         <v>0.9923611111111111</v>
       </c>
-      <c r="E258" s="2" t="inlineStr">
+      <c r="E258" s="5" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="F258" s="2" t="inlineStr">
         <is>
           <t>extra punches: 20:11 16:59; last day of month</t>
         </is>
@@ -5938,7 +6837,10 @@
       <c r="D259" s="4" t="n">
         <v>0.8208333333333333</v>
       </c>
-      <c r="E259" s="2" t="inlineStr">
+      <c r="E259" s="5" t="n">
+        <v>10.13</v>
+      </c>
+      <c r="F259" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -5959,7 +6861,10 @@
       <c r="D260" s="4" t="n">
         <v>0.7423611111111111</v>
       </c>
-      <c r="E260" s="2" t="inlineStr">
+      <c r="E260" s="5" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="F260" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -5986,6 +6891,11 @@
       </c>
       <c r="E261" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F261" s="2" t="inlineStr">
+        <is>
           <t>No entry</t>
         </is>
       </c>
@@ -6005,7 +6915,10 @@
       <c r="D262" s="4" t="n">
         <v>0.7756944444444445</v>
       </c>
-      <c r="E262" s="2" t="inlineStr">
+      <c r="E262" s="5" t="n">
+        <v>10.02</v>
+      </c>
+      <c r="F262" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -6026,28 +6939,34 @@
       <c r="D263" s="4" t="n">
         <v>0.7229166666666667</v>
       </c>
-      <c r="E263" s="2" t="inlineStr">
+      <c r="E263" s="5" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="F263" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="264">
-      <c r="A264" s="5" t="inlineStr">
+      <c r="A264" s="6" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="B264" s="6" t="n">
+      <c r="B264" s="7" t="n">
         <v>46241</v>
       </c>
-      <c r="C264" s="7" t="n">
+      <c r="C264" s="8" t="n">
         <v>0.1486111111111111</v>
       </c>
-      <c r="D264" s="7" t="n">
+      <c r="D264" s="8" t="n">
         <v>0.7201388888888889</v>
       </c>
-      <c r="E264" s="5" t="inlineStr">
+      <c r="E264" s="9" t="n">
+        <v>10.28</v>
+      </c>
+      <c r="F264" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -6068,7 +6987,10 @@
       <c r="D265" s="4" t="n">
         <v>0.7305555555555555</v>
       </c>
-      <c r="E265" s="2" t="inlineStr">
+      <c r="E265" s="5" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="F265" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -6089,7 +7011,10 @@
       <c r="D266" s="4" t="n">
         <v>0.8013888888888889</v>
       </c>
-      <c r="E266" s="2" t="inlineStr">
+      <c r="E266" s="5" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="F266" s="2" t="inlineStr">
         <is>
           <t>extra punch: 03:39</t>
         </is>
@@ -6110,7 +7035,10 @@
       <c r="D267" s="4" t="n">
         <v>0.7868055555555555</v>
       </c>
-      <c r="E267" s="2" t="inlineStr">
+      <c r="E267" s="5" t="n">
+        <v>10.08</v>
+      </c>
+      <c r="F267" s="2" t="inlineStr">
         <is>
           <t>extra punch: 18:20</t>
         </is>
@@ -6131,7 +7059,10 @@
       <c r="D268" s="4" t="n">
         <v>0.7354166666666667</v>
       </c>
-      <c r="E268" s="2" t="inlineStr">
+      <c r="E268" s="5" t="n">
+        <v>11.72</v>
+      </c>
+      <c r="F268" s="2" t="inlineStr">
         <is>
           <t>extra punch: 06:13</t>
         </is>
@@ -6152,7 +7083,10 @@
       <c r="D269" s="4" t="n">
         <v>0.8291666666666667</v>
       </c>
-      <c r="E269" s="2" t="inlineStr">
+      <c r="E269" s="5" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="F269" s="2" t="inlineStr">
         <is>
           <t>extra punches: 18:57 05:15</t>
         </is>
@@ -6173,28 +7107,34 @@
       <c r="D270" s="4" t="n">
         <v>0.7291666666666666</v>
       </c>
-      <c r="E270" s="2" t="inlineStr">
+      <c r="E270" s="5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="F270" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="271">
-      <c r="A271" s="5" t="inlineStr">
+      <c r="A271" s="6" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="B271" s="6" t="n">
+      <c r="B271" s="7" t="n">
         <v>46248</v>
       </c>
-      <c r="C271" s="7" t="n">
+      <c r="C271" s="8" t="n">
         <v>0.2361111111111111</v>
       </c>
-      <c r="D271" s="7" t="n">
+      <c r="D271" s="8" t="n">
         <v>0.7972222222222223</v>
       </c>
-      <c r="E271" s="5" t="inlineStr">
+      <c r="E271" s="9" t="n">
+        <v>10.53</v>
+      </c>
+      <c r="F271" s="6" t="inlineStr">
         <is>
           <t>extra punch: 17:01</t>
         </is>
@@ -6215,7 +7155,10 @@
       <c r="D272" s="4" t="n">
         <v>0.7340277777777777</v>
       </c>
-      <c r="E272" s="2" t="inlineStr">
+      <c r="E272" s="5" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="F272" s="2" t="inlineStr">
         <is>
           <t>extra punches: 17:20 17:05</t>
         </is>
@@ -6236,7 +7179,10 @@
       <c r="D273" s="4" t="n">
         <v>0.7256944444444444</v>
       </c>
-      <c r="E273" s="2" t="inlineStr">
+      <c r="E273" s="5" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="F273" s="2" t="inlineStr">
         <is>
           <t>extra punch: 04:52</t>
         </is>
@@ -6257,7 +7203,10 @@
       <c r="D274" s="4" t="n">
         <v>0.7319444444444444</v>
       </c>
-      <c r="E274" s="2" t="inlineStr">
+      <c r="E274" s="5" t="n">
+        <v>10.58</v>
+      </c>
+      <c r="F274" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -6278,7 +7227,10 @@
       <c r="D275" s="4" t="n">
         <v>0.7173611111111111</v>
       </c>
-      <c r="E275" s="2" t="inlineStr">
+      <c r="E275" s="5" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="F275" s="2" t="inlineStr">
         <is>
           <t>extra punch: 03:41</t>
         </is>
@@ -6299,7 +7251,10 @@
       <c r="D276" s="4" t="n">
         <v>0.7305555555555555</v>
       </c>
-      <c r="E276" s="2" t="inlineStr">
+      <c r="E276" s="5" t="n">
+        <v>10.08</v>
+      </c>
+      <c r="F276" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -6320,28 +7275,34 @@
       <c r="D277" s="4" t="n">
         <v>0.7319444444444444</v>
       </c>
-      <c r="E277" s="2" t="inlineStr">
+      <c r="E277" s="5" t="n">
+        <v>10.07</v>
+      </c>
+      <c r="F277" s="2" t="inlineStr">
         <is>
           <t>extra punches: 17:24 05:12</t>
         </is>
       </c>
     </row>
     <row r="278">
-      <c r="A278" s="5" t="inlineStr">
+      <c r="A278" s="6" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="B278" s="6" t="n">
+      <c r="B278" s="7" t="n">
         <v>46255</v>
       </c>
-      <c r="C278" s="7" t="n">
+      <c r="C278" s="8" t="n">
         <v>0.1493055555555556</v>
       </c>
-      <c r="D278" s="7" t="n">
+      <c r="D278" s="8" t="n">
         <v>0.7236111111111111</v>
       </c>
-      <c r="E278" s="5" t="inlineStr">
+      <c r="E278" s="9" t="n">
+        <v>10.22</v>
+      </c>
+      <c r="F278" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -6362,7 +7323,10 @@
       <c r="D279" s="4" t="n">
         <v>0.7520833333333333</v>
       </c>
-      <c r="E279" s="2" t="inlineStr">
+      <c r="E279" s="5" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="F279" s="2" t="inlineStr">
         <is>
           <t>extra punch: 03:39</t>
         </is>
@@ -6383,7 +7347,10 @@
       <c r="D280" s="4" t="n">
         <v>0.7111111111111111</v>
       </c>
-      <c r="E280" s="2" t="inlineStr">
+      <c r="E280" s="5" t="n">
+        <v>10.55</v>
+      </c>
+      <c r="F280" s="2" t="inlineStr">
         <is>
           <t>extra punch: 03:38</t>
         </is>
@@ -6404,7 +7371,10 @@
       <c r="D281" s="4" t="n">
         <v>0.7111111111111111</v>
       </c>
-      <c r="E281" s="2" t="inlineStr">
+      <c r="E281" s="5" t="n">
+        <v>10.63</v>
+      </c>
+      <c r="F281" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -6425,7 +7395,10 @@
       <c r="D282" s="4" t="n">
         <v>0.7180555555555556</v>
       </c>
-      <c r="E282" s="2" t="inlineStr">
+      <c r="E282" s="5" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="F282" s="2" t="inlineStr">
         <is>
           <t>extra punch: 17:14</t>
         </is>
@@ -6446,7 +7419,10 @@
       <c r="D283" s="4" t="n">
         <v>0.7006944444444444</v>
       </c>
-      <c r="E283" s="2" t="inlineStr">
+      <c r="E283" s="5" t="n">
+        <v>10.65</v>
+      </c>
+      <c r="F283" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -6467,28 +7443,34 @@
       <c r="D284" s="4" t="n">
         <v>0.7104166666666667</v>
       </c>
-      <c r="E284" s="2" t="inlineStr">
+      <c r="E284" s="5" t="n">
+        <v>10.42</v>
+      </c>
+      <c r="F284" s="2" t="inlineStr">
         <is>
           <t>extra punch: 03:30</t>
         </is>
       </c>
     </row>
     <row r="285">
-      <c r="A285" s="5" t="inlineStr">
+      <c r="A285" s="6" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="B285" s="6" t="n">
+      <c r="B285" s="7" t="n">
         <v>46262</v>
       </c>
-      <c r="C285" s="7" t="n">
+      <c r="C285" s="8" t="n">
         <v>0.1493055555555556</v>
       </c>
-      <c r="D285" s="7" t="n">
+      <c r="D285" s="8" t="n">
         <v>0.7159722222222222</v>
       </c>
-      <c r="E285" s="5" t="inlineStr">
+      <c r="E285" s="9" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="F285" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -6509,7 +7491,10 @@
       <c r="D286" s="4" t="n">
         <v>0.7479166666666667</v>
       </c>
-      <c r="E286" s="2" t="inlineStr">
+      <c r="E286" s="5" t="n">
+        <v>9.529999999999999</v>
+      </c>
+      <c r="F286" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -6530,7 +7515,10 @@
       <c r="D287" s="4" t="n">
         <v>0.75625</v>
       </c>
-      <c r="E287" s="2" t="inlineStr">
+      <c r="E287" s="5" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="F287" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -6551,7 +7539,10 @@
       <c r="D288" s="4" t="n">
         <v>0.9326388888888889</v>
       </c>
-      <c r="E288" s="2" t="inlineStr">
+      <c r="E288" s="5" t="n">
+        <v>5.17</v>
+      </c>
+      <c r="F288" s="2" t="inlineStr">
         <is>
           <t>extra punch: 22:23</t>
         </is>
@@ -6578,6 +7569,11 @@
       </c>
       <c r="E290" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F290" s="2" t="inlineStr">
+        <is>
           <t>No entry</t>
         </is>
       </c>
@@ -6603,6 +7599,11 @@
       </c>
       <c r="E291" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F291" s="2" t="inlineStr">
+        <is>
           <t>No entry</t>
         </is>
       </c>
@@ -6628,6 +7629,11 @@
       </c>
       <c r="E292" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F292" s="2" t="inlineStr">
+        <is>
           <t>No entry</t>
         </is>
       </c>
@@ -6653,6 +7659,11 @@
       </c>
       <c r="E293" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F293" s="2" t="inlineStr">
+        <is>
           <t>PLEASE VERIFY: check-in/out times not captured (last image in album; sequence ends here)</t>
         </is>
       </c>
@@ -6672,7 +7683,10 @@
       <c r="D294" s="4" t="n">
         <v>0.5354166666666667</v>
       </c>
-      <c r="E294" s="2" t="inlineStr">
+      <c r="E294" s="5" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="F294" s="2" t="inlineStr">
         <is>
           <t>extra punch: 04:27</t>
         </is>
@@ -6693,28 +7707,34 @@
       <c r="D295" s="4" t="n">
         <v>0.4840277777777778</v>
       </c>
-      <c r="E295" s="2" t="inlineStr">
+      <c r="E295" s="5" t="n">
+        <v>16.75</v>
+      </c>
+      <c r="F295" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="296">
-      <c r="A296" s="5" t="inlineStr">
+      <c r="A296" s="6" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="B296" s="6" t="n">
+      <c r="B296" s="7" t="n">
         <v>46241</v>
       </c>
-      <c r="C296" s="7" t="n">
+      <c r="C296" s="8" t="n">
         <v>0.1791666666666667</v>
       </c>
-      <c r="D296" s="7" t="n">
+      <c r="D296" s="8" t="n">
         <v>0.5618055555555556</v>
       </c>
-      <c r="E296" s="5" t="inlineStr">
+      <c r="E296" s="9" t="n">
+        <v>14.82</v>
+      </c>
+      <c r="F296" s="6" t="inlineStr">
         <is>
           <t>extra punch: 04:18</t>
         </is>
@@ -6735,7 +7755,10 @@
       <c r="D297" s="4" t="n">
         <v>0.5006944444444444</v>
       </c>
-      <c r="E297" s="2" t="inlineStr">
+      <c r="E297" s="5" t="n">
+        <v>16.32</v>
+      </c>
+      <c r="F297" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -6756,7 +7779,10 @@
       <c r="D298" s="4" t="n">
         <v>0.5284722222222222</v>
       </c>
-      <c r="E298" s="2" t="inlineStr">
+      <c r="E298" s="5" t="n">
+        <v>15.47</v>
+      </c>
+      <c r="F298" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -6777,7 +7803,10 @@
       <c r="D299" s="4" t="n">
         <v>0.5208333333333334</v>
       </c>
-      <c r="E299" s="2" t="inlineStr">
+      <c r="E299" s="5" t="n">
+        <v>15.62</v>
+      </c>
+      <c r="F299" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -6798,7 +7827,10 @@
       <c r="D300" s="4" t="n">
         <v>0.4430555555555555</v>
       </c>
-      <c r="E300" s="2" t="inlineStr">
+      <c r="E300" s="5" t="n">
+        <v>17.48</v>
+      </c>
+      <c r="F300" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -6819,7 +7851,10 @@
       <c r="D301" s="4" t="n">
         <v>0.5118055555555555</v>
       </c>
-      <c r="E301" s="2" t="inlineStr">
+      <c r="E301" s="5" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="F301" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -6840,28 +7875,34 @@
       <c r="D302" s="4" t="n">
         <v>0.5076388888888889</v>
       </c>
-      <c r="E302" s="2" t="inlineStr">
+      <c r="E302" s="5" t="n">
+        <v>16.27</v>
+      </c>
+      <c r="F302" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="303">
-      <c r="A303" s="5" t="inlineStr">
+      <c r="A303" s="6" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="B303" s="6" t="n">
+      <c r="B303" s="7" t="n">
         <v>46248</v>
       </c>
-      <c r="C303" s="7" t="n">
+      <c r="C303" s="8" t="n">
         <v>0.1743055555555555</v>
       </c>
-      <c r="D303" s="7" t="n">
+      <c r="D303" s="8" t="n">
         <v>0.5298611111111111</v>
       </c>
-      <c r="E303" s="5" t="inlineStr">
+      <c r="E303" s="9" t="n">
+        <v>15.47</v>
+      </c>
+      <c r="F303" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -6882,7 +7923,10 @@
       <c r="D304" s="4" t="n">
         <v>0.5354166666666667</v>
       </c>
-      <c r="E304" s="2" t="inlineStr">
+      <c r="E304" s="5" t="n">
+        <v>15.55</v>
+      </c>
+      <c r="F304" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -6903,7 +7947,10 @@
       <c r="D305" s="4" t="n">
         <v>0.4166666666666667</v>
       </c>
-      <c r="E305" s="2" t="inlineStr">
+      <c r="E305" s="5" t="n">
+        <v>18.48</v>
+      </c>
+      <c r="F305" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -6924,7 +7971,10 @@
       <c r="D306" s="4" t="n">
         <v>0.5027777777777778</v>
       </c>
-      <c r="E306" s="2" t="inlineStr">
+      <c r="E306" s="5" t="n">
+        <v>16.62</v>
+      </c>
+      <c r="F306" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -6945,7 +7995,10 @@
       <c r="D307" s="4" t="n">
         <v>0.41875</v>
       </c>
-      <c r="E307" s="2" t="inlineStr">
+      <c r="E307" s="5" t="n">
+        <v>18.47</v>
+      </c>
+      <c r="F307" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -6966,7 +8019,10 @@
       <c r="D308" s="4" t="n">
         <v>0.5173611111111112</v>
       </c>
-      <c r="E308" s="2" t="inlineStr">
+      <c r="E308" s="5" t="n">
+        <v>16.15</v>
+      </c>
+      <c r="F308" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -6987,28 +8043,34 @@
       <c r="D309" s="4" t="n">
         <v>0.5048611111111111</v>
       </c>
-      <c r="E309" s="2" t="inlineStr">
+      <c r="E309" s="5" t="n">
+        <v>16.33</v>
+      </c>
+      <c r="F309" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="310">
-      <c r="A310" s="5" t="inlineStr">
+      <c r="A310" s="6" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="B310" s="6" t="n">
+      <c r="B310" s="7" t="n">
         <v>46255</v>
       </c>
-      <c r="C310" s="7" t="n">
+      <c r="C310" s="8" t="n">
         <v>0.1854166666666667</v>
       </c>
-      <c r="D310" s="7" t="n">
+      <c r="D310" s="8" t="n">
         <v>0.5319444444444444</v>
       </c>
-      <c r="E310" s="5" t="inlineStr">
+      <c r="E310" s="9" t="n">
+        <v>15.68</v>
+      </c>
+      <c r="F310" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -7029,7 +8091,10 @@
       <c r="D311" s="4" t="n">
         <v>0.5159722222222223</v>
       </c>
-      <c r="E311" s="2" t="inlineStr">
+      <c r="E311" s="5" t="n">
+        <v>16.07</v>
+      </c>
+      <c r="F311" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -7050,7 +8115,10 @@
       <c r="D312" s="4" t="n">
         <v>0.4256944444444444</v>
       </c>
-      <c r="E312" s="2" t="inlineStr">
+      <c r="E312" s="5" t="n">
+        <v>18.27</v>
+      </c>
+      <c r="F312" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -7071,7 +8139,10 @@
       <c r="D313" s="4" t="n">
         <v>0.4930555555555556</v>
       </c>
-      <c r="E313" s="2" t="inlineStr">
+      <c r="E313" s="5" t="n">
+        <v>16.63</v>
+      </c>
+      <c r="F313" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -7092,7 +8163,10 @@
       <c r="D314" s="4" t="n">
         <v>0.4881944444444444</v>
       </c>
-      <c r="E314" s="2" t="inlineStr">
+      <c r="E314" s="5" t="n">
+        <v>16.72</v>
+      </c>
+      <c r="F314" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -7113,7 +8187,10 @@
       <c r="D315" s="4" t="n">
         <v>0.5048611111111111</v>
       </c>
-      <c r="E315" s="2" t="inlineStr">
+      <c r="E315" s="5" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="F315" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -7134,28 +8211,34 @@
       <c r="D316" s="4" t="n">
         <v>0.4979166666666667</v>
       </c>
-      <c r="E316" s="2" t="inlineStr">
+      <c r="E316" s="5" t="n">
+        <v>16.37</v>
+      </c>
+      <c r="F316" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="317">
-      <c r="A317" s="5" t="inlineStr">
+      <c r="A317" s="6" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="B317" s="6" t="n">
+      <c r="B317" s="7" t="n">
         <v>46262</v>
       </c>
-      <c r="C317" s="7" t="n">
+      <c r="C317" s="8" t="n">
         <v>0.1881944444444444</v>
       </c>
-      <c r="D317" s="7" t="n">
+      <c r="D317" s="8" t="n">
         <v>0.4055555555555556</v>
       </c>
-      <c r="E317" s="5" t="inlineStr">
+      <c r="E317" s="9" t="n">
+        <v>18.78</v>
+      </c>
+      <c r="F317" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -7176,7 +8259,10 @@
       <c r="D318" s="4" t="n">
         <v>0.4527777777777778</v>
       </c>
-      <c r="E318" s="2" t="inlineStr">
+      <c r="E318" s="5" t="n">
+        <v>17.57</v>
+      </c>
+      <c r="F318" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -7197,7 +8283,10 @@
       <c r="D319" s="4" t="n">
         <v>0.5097222222222222</v>
       </c>
-      <c r="E319" s="2" t="inlineStr">
+      <c r="E319" s="5" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="F319" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -7218,7 +8307,10 @@
       <c r="D320" s="4" t="n">
         <v>0.4131944444444444</v>
       </c>
-      <c r="E320" s="2" t="inlineStr">
+      <c r="E320" s="5" t="n">
+        <v>18.57</v>
+      </c>
+      <c r="F320" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -7239,7 +8331,10 @@
       <c r="D322" s="4" t="n">
         <v>0.7430555555555556</v>
       </c>
-      <c r="E322" s="2" t="inlineStr">
+      <c r="E322" s="5" t="n">
+        <v>11.85</v>
+      </c>
+      <c r="F322" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -7260,7 +8355,10 @@
       <c r="D323" s="4" t="n">
         <v>0.7534722222222222</v>
       </c>
-      <c r="E323" s="2" t="inlineStr">
+      <c r="E323" s="5" t="n">
+        <v>12.17</v>
+      </c>
+      <c r="F323" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -7281,7 +8379,10 @@
       <c r="D324" s="4" t="n">
         <v>0.7444444444444445</v>
       </c>
-      <c r="E324" s="2" t="inlineStr">
+      <c r="E324" s="5" t="n">
+        <v>13.57</v>
+      </c>
+      <c r="F324" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -7306,6 +8407,11 @@
       </c>
       <c r="E325" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F325" s="2" t="inlineStr">
+        <is>
           <t>single punch only</t>
         </is>
       </c>
@@ -7329,6 +8435,11 @@
       </c>
       <c r="E326" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F326" s="2" t="inlineStr">
+        <is>
           <t>single punch only</t>
         </is>
       </c>
@@ -7348,32 +8459,40 @@
       <c r="D327" s="4" t="n">
         <v>0.7576388888888889</v>
       </c>
-      <c r="E327" s="2" t="inlineStr">
+      <c r="E327" s="5" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="F327" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="328">
-      <c r="A328" s="5" t="inlineStr">
+      <c r="A328" s="6" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="B328" s="6" t="n">
+      <c r="B328" s="7" t="n">
         <v>46241</v>
       </c>
-      <c r="C328" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D328" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E328" s="5" t="inlineStr">
+      <c r="C328" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D328" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E328" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F328" s="6" t="inlineStr">
         <is>
           <t>No entry</t>
         </is>
@@ -7394,7 +8513,10 @@
       <c r="D329" s="4" t="n">
         <v>0.7243055555555555</v>
       </c>
-      <c r="E329" s="2" t="inlineStr">
+      <c r="E329" s="5" t="n">
+        <v>12.38</v>
+      </c>
+      <c r="F329" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -7415,7 +8537,10 @@
       <c r="D330" s="4" t="n">
         <v>0.725</v>
       </c>
-      <c r="E330" s="2" t="inlineStr">
+      <c r="E330" s="5" t="n">
+        <v>12.37</v>
+      </c>
+      <c r="F330" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -7436,7 +8561,10 @@
       <c r="D331" s="4" t="n">
         <v>0.7597222222222222</v>
       </c>
-      <c r="E331" s="2" t="inlineStr">
+      <c r="E331" s="5" t="n">
+        <v>11.55</v>
+      </c>
+      <c r="F331" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -7457,7 +8585,10 @@
       <c r="D332" s="4" t="n">
         <v>0.7319444444444444</v>
       </c>
-      <c r="E332" s="2" t="inlineStr">
+      <c r="E332" s="5" t="n">
+        <v>11.75</v>
+      </c>
+      <c r="F332" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -7478,7 +8609,10 @@
       <c r="D333" s="4" t="n">
         <v>0.7402777777777778</v>
       </c>
-      <c r="E333" s="2" t="inlineStr">
+      <c r="E333" s="5" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="F333" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -7499,32 +8633,40 @@
       <c r="D334" s="4" t="n">
         <v>0.7243055555555555</v>
       </c>
-      <c r="E334" s="2" t="inlineStr">
+      <c r="E334" s="5" t="n">
+        <v>12.57</v>
+      </c>
+      <c r="F334" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="335">
-      <c r="A335" s="5" t="inlineStr">
+      <c r="A335" s="6" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="B335" s="6" t="n">
+      <c r="B335" s="7" t="n">
         <v>46248</v>
       </c>
-      <c r="C335" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D335" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E335" s="5" t="inlineStr">
+      <c r="C335" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D335" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E335" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F335" s="6" t="inlineStr">
         <is>
           <t>No entry</t>
         </is>
@@ -7549,6 +8691,11 @@
       </c>
       <c r="E336" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F336" s="2" t="inlineStr">
+        <is>
           <t>single punch only</t>
         </is>
       </c>
@@ -7568,7 +8715,10 @@
       <c r="D337" s="4" t="n">
         <v>0.7180555555555556</v>
       </c>
-      <c r="E337" s="2" t="inlineStr">
+      <c r="E337" s="5" t="n">
+        <v>12.28</v>
+      </c>
+      <c r="F337" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -7589,7 +8739,10 @@
       <c r="D338" s="4" t="n">
         <v>0.7402777777777778</v>
       </c>
-      <c r="E338" s="2" t="inlineStr">
+      <c r="E338" s="5" t="n">
+        <v>12.17</v>
+      </c>
+      <c r="F338" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -7614,6 +8767,11 @@
       </c>
       <c r="E339" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F339" s="2" t="inlineStr">
+        <is>
           <t>single punch only</t>
         </is>
       </c>
@@ -7633,7 +8791,10 @@
       <c r="D340" s="4" t="n">
         <v>0.7305555555555555</v>
       </c>
-      <c r="E340" s="2" t="inlineStr">
+      <c r="E340" s="5" t="n">
+        <v>11.78</v>
+      </c>
+      <c r="F340" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -7654,32 +8815,40 @@
       <c r="D341" s="4" t="n">
         <v>0.7291666666666666</v>
       </c>
-      <c r="E341" s="2" t="inlineStr">
+      <c r="E341" s="5" t="n">
+        <v>11.83</v>
+      </c>
+      <c r="F341" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="342">
-      <c r="A342" s="5" t="inlineStr">
+      <c r="A342" s="6" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="B342" s="6" t="n">
+      <c r="B342" s="7" t="n">
         <v>46255</v>
       </c>
-      <c r="C342" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D342" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E342" s="5" t="inlineStr">
+      <c r="C342" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D342" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E342" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F342" s="6" t="inlineStr">
         <is>
           <t>No entry</t>
         </is>
@@ -7700,7 +8869,10 @@
       <c r="D343" s="4" t="n">
         <v>0.7541666666666667</v>
       </c>
-      <c r="E343" s="2" t="inlineStr">
+      <c r="E343" s="5" t="n">
+        <v>11.63</v>
+      </c>
+      <c r="F343" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -7721,7 +8893,10 @@
       <c r="D344" s="4" t="n">
         <v>0.7291666666666666</v>
       </c>
-      <c r="E344" s="2" t="inlineStr">
+      <c r="E344" s="5" t="n">
+        <v>12.52</v>
+      </c>
+      <c r="F344" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -7746,6 +8921,11 @@
       </c>
       <c r="E345" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F345" s="2" t="inlineStr">
+        <is>
           <t>single punch only</t>
         </is>
       </c>
@@ -7765,7 +8945,10 @@
       <c r="D346" s="4" t="n">
         <v>0.725</v>
       </c>
-      <c r="E346" s="2" t="inlineStr">
+      <c r="E346" s="5" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="F346" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -7786,7 +8969,10 @@
       <c r="D347" s="4" t="n">
         <v>0.7381944444444445</v>
       </c>
-      <c r="E347" s="2" t="inlineStr">
+      <c r="E347" s="5" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="F347" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -7807,32 +8993,40 @@
       <c r="D348" s="4" t="n">
         <v>0.7166666666666667</v>
       </c>
-      <c r="E348" s="2" t="inlineStr">
+      <c r="E348" s="5" t="n">
+        <v>12.47</v>
+      </c>
+      <c r="F348" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="349">
-      <c r="A349" s="5" t="inlineStr">
+      <c r="A349" s="6" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="B349" s="6" t="n">
+      <c r="B349" s="7" t="n">
         <v>46262</v>
       </c>
-      <c r="C349" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D349" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E349" s="5" t="inlineStr">
+      <c r="C349" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D349" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E349" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F349" s="6" t="inlineStr">
         <is>
           <t>No entry</t>
         </is>
@@ -7853,7 +9047,10 @@
       <c r="D350" s="4" t="n">
         <v>0.7347222222222223</v>
       </c>
-      <c r="E350" s="2" t="inlineStr">
+      <c r="E350" s="5" t="n">
+        <v>11.82</v>
+      </c>
+      <c r="F350" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -7878,6 +9075,11 @@
       </c>
       <c r="E351" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F351" s="2" t="inlineStr">
+        <is>
           <t>single punch only</t>
         </is>
       </c>
@@ -7901,6 +9103,11 @@
       </c>
       <c r="E352" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F352" s="2" t="inlineStr">
+        <is>
           <t>single punch only</t>
         </is>
       </c>
@@ -7920,7 +9127,10 @@
       <c r="D354" s="4" t="n">
         <v>0.7576388888888889</v>
       </c>
-      <c r="E354" s="2" t="inlineStr">
+      <c r="E354" s="5" t="n">
+        <v>9.27</v>
+      </c>
+      <c r="F354" s="2" t="inlineStr">
         <is>
           <t>last day of month; final record</t>
         </is>
@@ -7941,7 +9151,10 @@
       <c r="D355" s="4" t="n">
         <v>0.7395833333333334</v>
       </c>
-      <c r="E355" s="2" t="inlineStr">
+      <c r="E355" s="5" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="F355" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -7962,7 +9175,10 @@
       <c r="D356" s="4" t="n">
         <v>0.7472222222222222</v>
       </c>
-      <c r="E356" s="2" t="inlineStr">
+      <c r="E356" s="5" t="n">
+        <v>9.57</v>
+      </c>
+      <c r="F356" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -7983,7 +9199,10 @@
       <c r="D357" s="4" t="n">
         <v>0.7708333333333334</v>
       </c>
-      <c r="E357" s="2" t="inlineStr">
+      <c r="E357" s="5" t="n">
+        <v>8.98</v>
+      </c>
+      <c r="F357" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -8004,7 +9223,10 @@
       <c r="D358" s="4" t="n">
         <v>0.6881944444444444</v>
       </c>
-      <c r="E358" s="2" t="inlineStr">
+      <c r="E358" s="5" t="n">
+        <v>10.95</v>
+      </c>
+      <c r="F358" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -8025,28 +9247,34 @@
       <c r="D359" s="4" t="n">
         <v>0.7659722222222223</v>
       </c>
-      <c r="E359" s="2" t="inlineStr">
+      <c r="E359" s="5" t="n">
+        <v>9.08</v>
+      </c>
+      <c r="F359" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="360">
-      <c r="A360" s="5" t="inlineStr">
+      <c r="A360" s="6" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="B360" s="6" t="n">
+      <c r="B360" s="7" t="n">
         <v>46241</v>
       </c>
-      <c r="C360" s="7" t="n">
+      <c r="C360" s="8" t="n">
         <v>0.1451388888888889</v>
       </c>
-      <c r="D360" s="7" t="n">
+      <c r="D360" s="8" t="n">
         <v>0.7298611111111111</v>
       </c>
-      <c r="E360" s="5" t="inlineStr">
+      <c r="E360" s="9" t="n">
+        <v>9.970000000000001</v>
+      </c>
+      <c r="F360" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -8067,7 +9295,10 @@
       <c r="D361" s="4" t="n">
         <v>0.8090277777777778</v>
       </c>
-      <c r="E361" s="2" t="inlineStr">
+      <c r="E361" s="5" t="n">
+        <v>7.92</v>
+      </c>
+      <c r="F361" s="2" t="inlineStr">
         <is>
           <t>extra punch: 03:24</t>
         </is>
@@ -8088,7 +9319,10 @@
       <c r="D362" s="4" t="n">
         <v>0.8381944444444445</v>
       </c>
-      <c r="E362" s="2" t="inlineStr">
+      <c r="E362" s="5" t="n">
+        <v>7.35</v>
+      </c>
+      <c r="F362" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -8109,7 +9343,10 @@
       <c r="D363" s="4" t="n">
         <v>0.7638888888888888</v>
       </c>
-      <c r="E363" s="2" t="inlineStr">
+      <c r="E363" s="5" t="n">
+        <v>8.92</v>
+      </c>
+      <c r="F363" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -8130,7 +9367,10 @@
       <c r="D364" s="4" t="n">
         <v>0.7444444444444445</v>
       </c>
-      <c r="E364" s="2" t="inlineStr">
+      <c r="E364" s="5" t="n">
+        <v>9.58</v>
+      </c>
+      <c r="F364" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -8151,7 +9391,10 @@
       <c r="D365" s="4" t="n">
         <v>0.7409722222222223</v>
       </c>
-      <c r="E365" s="2" t="inlineStr">
+      <c r="E365" s="5" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="F365" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -8172,28 +9415,34 @@
       <c r="D366" s="4" t="n">
         <v>0.75</v>
       </c>
-      <c r="E366" s="2" t="inlineStr">
+      <c r="E366" s="5" t="n">
+        <v>9.42</v>
+      </c>
+      <c r="F366" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="367">
-      <c r="A367" s="5" t="inlineStr">
+      <c r="A367" s="6" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="B367" s="6" t="n">
+      <c r="B367" s="7" t="n">
         <v>46248</v>
       </c>
-      <c r="C367" s="7" t="n">
+      <c r="C367" s="8" t="n">
         <v>0.15</v>
       </c>
-      <c r="D367" s="7" t="n">
+      <c r="D367" s="8" t="n">
         <v>0.7076388888888889</v>
       </c>
-      <c r="E367" s="5" t="inlineStr">
+      <c r="E367" s="9" t="n">
+        <v>10.62</v>
+      </c>
+      <c r="F367" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -8214,7 +9463,10 @@
       <c r="D368" s="4" t="n">
         <v>0.7277777777777777</v>
       </c>
-      <c r="E368" s="2" t="inlineStr">
+      <c r="E368" s="5" t="n">
+        <v>10.17</v>
+      </c>
+      <c r="F368" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -8235,7 +9487,10 @@
       <c r="D369" s="4" t="n">
         <v>0.7229166666666667</v>
       </c>
-      <c r="E369" s="2" t="inlineStr">
+      <c r="E369" s="5" t="n">
+        <v>13.15</v>
+      </c>
+      <c r="F369" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -8256,7 +9511,10 @@
       <c r="D370" s="4" t="n">
         <v>0.8888888888888888</v>
       </c>
-      <c r="E370" s="2" t="inlineStr">
+      <c r="E370" s="5" t="n">
+        <v>8.27</v>
+      </c>
+      <c r="F370" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -8277,7 +9535,10 @@
       <c r="D371" s="4" t="n">
         <v>0.7416666666666667</v>
       </c>
-      <c r="E371" s="2" t="inlineStr">
+      <c r="E371" s="5" t="n">
+        <v>12.35</v>
+      </c>
+      <c r="F371" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -8298,7 +9559,10 @@
       <c r="D372" s="4" t="n">
         <v>0.7451388888888889</v>
       </c>
-      <c r="E372" s="2" t="inlineStr">
+      <c r="E372" s="5" t="n">
+        <v>12.78</v>
+      </c>
+      <c r="F372" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -8319,28 +9583,34 @@
       <c r="D373" s="4" t="n">
         <v>0.7979166666666667</v>
       </c>
-      <c r="E373" s="2" t="inlineStr">
+      <c r="E373" s="5" t="n">
+        <v>11.15</v>
+      </c>
+      <c r="F373" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="374">
-      <c r="A374" s="5" t="inlineStr">
+      <c r="A374" s="6" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="B374" s="6" t="n">
+      <c r="B374" s="7" t="n">
         <v>46255</v>
       </c>
-      <c r="C374" s="7" t="n">
+      <c r="C374" s="8" t="n">
         <v>0.275</v>
       </c>
-      <c r="D374" s="7" t="n">
+      <c r="D374" s="8" t="n">
         <v>0.8354166666666667</v>
       </c>
-      <c r="E374" s="5" t="inlineStr">
+      <c r="E374" s="9" t="n">
+        <v>10.55</v>
+      </c>
+      <c r="F374" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -8361,7 +9631,10 @@
       <c r="D375" s="4" t="n">
         <v>0.7513888888888889</v>
       </c>
-      <c r="E375" s="2" t="inlineStr">
+      <c r="E375" s="5" t="n">
+        <v>12.23</v>
+      </c>
+      <c r="F375" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -8382,7 +9655,10 @@
       <c r="D376" s="4" t="n">
         <v>0.7263888888888889</v>
       </c>
-      <c r="E376" s="2" t="inlineStr">
+      <c r="E376" s="5" t="n">
+        <v>12.42</v>
+      </c>
+      <c r="F376" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -8403,7 +9679,10 @@
       <c r="D377" s="4" t="n">
         <v>0.7270833333333333</v>
       </c>
-      <c r="E377" s="2" t="inlineStr">
+      <c r="E377" s="5" t="n">
+        <v>12.87</v>
+      </c>
+      <c r="F377" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -8424,7 +9703,10 @@
       <c r="D378" s="4" t="n">
         <v>0.7298611111111111</v>
       </c>
-      <c r="E378" s="2" t="inlineStr">
+      <c r="E378" s="5" t="n">
+        <v>12.75</v>
+      </c>
+      <c r="F378" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -8445,7 +9727,10 @@
       <c r="D379" s="4" t="n">
         <v>0.8791666666666667</v>
       </c>
-      <c r="E379" s="2" t="inlineStr">
+      <c r="E379" s="5" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="F379" s="2" t="inlineStr">
         <is>
           <t>extra punch: 17:56</t>
         </is>
@@ -8466,28 +9751,34 @@
       <c r="D380" s="4" t="n">
         <v>0.8506944444444444</v>
       </c>
-      <c r="E380" s="2" t="inlineStr">
+      <c r="E380" s="5" t="n">
+        <v>9.720000000000001</v>
+      </c>
+      <c r="F380" s="2" t="inlineStr">
         <is>
           <t>extra punches: 17:07 17:02</t>
         </is>
       </c>
     </row>
     <row r="381">
-      <c r="A381" s="5" t="inlineStr">
+      <c r="A381" s="6" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="B381" s="6" t="n">
+      <c r="B381" s="7" t="n">
         <v>46262</v>
       </c>
-      <c r="C381" s="7" t="n">
+      <c r="C381" s="8" t="n">
         <v>0.2805555555555556</v>
       </c>
-      <c r="D381" s="7" t="n">
+      <c r="D381" s="8" t="n">
         <v>0.7701388888888889</v>
       </c>
-      <c r="E381" s="5" t="inlineStr">
+      <c r="E381" s="9" t="n">
+        <v>12.25</v>
+      </c>
+      <c r="F381" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -8508,7 +9799,10 @@
       <c r="D382" s="4" t="n">
         <v>0.7479166666666667</v>
       </c>
-      <c r="E382" s="2" t="inlineStr">
+      <c r="E382" s="5" t="n">
+        <v>12.15</v>
+      </c>
+      <c r="F382" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -8529,7 +9823,10 @@
       <c r="D383" s="4" t="n">
         <v>0.7354166666666667</v>
       </c>
-      <c r="E383" s="2" t="inlineStr">
+      <c r="E383" s="5" t="n">
+        <v>12.73</v>
+      </c>
+      <c r="F383" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -8550,7 +9847,10 @@
       <c r="D384" s="4" t="n">
         <v>0.7354166666666667</v>
       </c>
-      <c r="E384" s="2" t="inlineStr">
+      <c r="E384" s="5" t="n">
+        <v>12.42</v>
+      </c>
+      <c r="F384" s="2" t="inlineStr">
         <is>
           <t>corrected from a clearer re-scan photo later in the album</t>
         </is>
@@ -8571,7 +9871,10 @@
       <c r="D386" s="4" t="n">
         <v>0.7444444444444445</v>
       </c>
-      <c r="E386" s="2" t="inlineStr">
+      <c r="E386" s="5" t="n">
+        <v>12.43</v>
+      </c>
+      <c r="F386" s="2" t="inlineStr">
         <is>
           <t>last day of month; final record</t>
         </is>
@@ -8592,7 +9895,10 @@
       <c r="D387" s="4" t="n">
         <v>0.7493055555555556</v>
       </c>
-      <c r="E387" s="2" t="inlineStr">
+      <c r="E387" s="5" t="n">
+        <v>12.37</v>
+      </c>
+      <c r="F387" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -8613,7 +9919,10 @@
       <c r="D388" s="4" t="n">
         <v>0.7479166666666667</v>
       </c>
-      <c r="E388" s="2" t="inlineStr">
+      <c r="E388" s="5" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="F388" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -8634,7 +9943,10 @@
       <c r="D389" s="4" t="n">
         <v>0.75</v>
       </c>
-      <c r="E389" s="2" t="inlineStr">
+      <c r="E389" s="5" t="n">
+        <v>12.07</v>
+      </c>
+      <c r="F389" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -8655,7 +9967,10 @@
       <c r="D390" s="4" t="n">
         <v>0.7763888888888889</v>
       </c>
-      <c r="E390" s="2" t="inlineStr">
+      <c r="E390" s="5" t="n">
+        <v>11.52</v>
+      </c>
+      <c r="F390" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -8676,32 +9991,40 @@
       <c r="D391" s="4" t="n">
         <v>0.7423611111111111</v>
       </c>
-      <c r="E391" s="2" t="inlineStr">
+      <c r="E391" s="5" t="n">
+        <v>12.67</v>
+      </c>
+      <c r="F391" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="392">
-      <c r="A392" s="5" t="inlineStr">
+      <c r="A392" s="6" t="inlineStr">
         <is>
           <t>37</t>
         </is>
       </c>
-      <c r="B392" s="6" t="n">
+      <c r="B392" s="7" t="n">
         <v>46241</v>
       </c>
-      <c r="C392" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D392" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E392" s="5" t="inlineStr">
+      <c r="C392" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D392" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E392" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F392" s="6" t="inlineStr">
         <is>
           <t>No entry</t>
         </is>
@@ -8722,7 +10045,10 @@
       <c r="D393" s="4" t="n">
         <v>0.7326388888888888</v>
       </c>
-      <c r="E393" s="2" t="inlineStr">
+      <c r="E393" s="5" t="n">
+        <v>12.65</v>
+      </c>
+      <c r="F393" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -8743,7 +10069,10 @@
       <c r="D394" s="4" t="n">
         <v>0.75625</v>
       </c>
-      <c r="E394" s="2" t="inlineStr">
+      <c r="E394" s="5" t="n">
+        <v>11.57</v>
+      </c>
+      <c r="F394" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -8768,6 +10097,11 @@
       </c>
       <c r="E395" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F395" s="2" t="inlineStr">
+        <is>
           <t>single punch only</t>
         </is>
       </c>
@@ -8787,7 +10121,10 @@
       <c r="D396" s="4" t="n">
         <v>0.7402777777777778</v>
       </c>
-      <c r="E396" s="2" t="inlineStr">
+      <c r="E396" s="5" t="n">
+        <v>11.95</v>
+      </c>
+      <c r="F396" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -8808,7 +10145,10 @@
       <c r="D397" s="4" t="n">
         <v>0.7493055555555556</v>
       </c>
-      <c r="E397" s="2" t="inlineStr">
+      <c r="E397" s="5" t="n">
+        <v>11.63</v>
+      </c>
+      <c r="F397" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -8829,32 +10169,40 @@
       <c r="D398" s="4" t="n">
         <v>0.7270833333333333</v>
       </c>
-      <c r="E398" s="2" t="inlineStr">
+      <c r="E398" s="5" t="n">
+        <v>12.47</v>
+      </c>
+      <c r="F398" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="399">
-      <c r="A399" s="5" t="inlineStr">
+      <c r="A399" s="6" t="inlineStr">
         <is>
           <t>37</t>
         </is>
       </c>
-      <c r="B399" s="6" t="n">
+      <c r="B399" s="7" t="n">
         <v>46248</v>
       </c>
-      <c r="C399" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D399" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E399" s="5" t="inlineStr">
+      <c r="C399" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D399" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E399" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F399" s="6" t="inlineStr">
         <is>
           <t>No entry</t>
         </is>
@@ -8875,7 +10223,10 @@
       <c r="D400" s="4" t="n">
         <v>0.7388888888888889</v>
       </c>
-      <c r="E400" s="2" t="inlineStr">
+      <c r="E400" s="5" t="n">
+        <v>12.02</v>
+      </c>
+      <c r="F400" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -8896,7 +10247,10 @@
       <c r="D401" s="4" t="n">
         <v>0.7236111111111111</v>
       </c>
-      <c r="E401" s="2" t="inlineStr">
+      <c r="E401" s="5" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="F401" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -8917,7 +10271,10 @@
       <c r="D402" s="4" t="n">
         <v>0.7333333333333333</v>
       </c>
-      <c r="E402" s="2" t="inlineStr">
+      <c r="E402" s="5" t="n">
+        <v>12.98</v>
+      </c>
+      <c r="F402" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -8938,7 +10295,10 @@
       <c r="D403" s="4" t="n">
         <v>0.7451388888888889</v>
       </c>
-      <c r="E403" s="2" t="inlineStr">
+      <c r="E403" s="5" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="F403" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -8959,7 +10319,10 @@
       <c r="D404" s="4" t="n">
         <v>0.7298611111111111</v>
       </c>
-      <c r="E404" s="2" t="inlineStr">
+      <c r="E404" s="5" t="n">
+        <v>13.12</v>
+      </c>
+      <c r="F404" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -8980,32 +10343,40 @@
       <c r="D405" s="4" t="n">
         <v>0.7256944444444444</v>
       </c>
-      <c r="E405" s="2" t="inlineStr">
+      <c r="E405" s="5" t="n">
+        <v>13.18</v>
+      </c>
+      <c r="F405" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="406">
-      <c r="A406" s="5" t="inlineStr">
+      <c r="A406" s="6" t="inlineStr">
         <is>
           <t>37</t>
         </is>
       </c>
-      <c r="B406" s="6" t="n">
+      <c r="B406" s="7" t="n">
         <v>46255</v>
       </c>
-      <c r="C406" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D406" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E406" s="5" t="inlineStr">
+      <c r="C406" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D406" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E406" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F406" s="6" t="inlineStr">
         <is>
           <t>No entry</t>
         </is>
@@ -9026,7 +10397,10 @@
       <c r="D407" s="4" t="n">
         <v>0.7513888888888889</v>
       </c>
-      <c r="E407" s="2" t="inlineStr">
+      <c r="E407" s="5" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="F407" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -9053,6 +10427,11 @@
       </c>
       <c r="E408" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F408" s="2" t="inlineStr">
+        <is>
           <t>No entry</t>
         </is>
       </c>
@@ -9078,6 +10457,11 @@
       </c>
       <c r="E409" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F409" s="2" t="inlineStr">
+        <is>
           <t>No entry</t>
         </is>
       </c>
@@ -9103,6 +10487,11 @@
       </c>
       <c r="E410" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F410" s="2" t="inlineStr">
+        <is>
           <t>No entry</t>
         </is>
       </c>
@@ -9128,6 +10517,11 @@
       </c>
       <c r="E411" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F411" s="2" t="inlineStr">
+        <is>
           <t>No entry</t>
         </is>
       </c>
@@ -9147,32 +10541,40 @@
       <c r="D412" s="4" t="n">
         <v>0.6763888888888889</v>
       </c>
-      <c r="E412" s="2" t="inlineStr">
+      <c r="E412" s="5" t="n">
+        <v>13.62</v>
+      </c>
+      <c r="F412" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="413">
-      <c r="A413" s="5" t="inlineStr">
+      <c r="A413" s="6" t="inlineStr">
         <is>
           <t>37</t>
         </is>
       </c>
-      <c r="B413" s="6" t="n">
+      <c r="B413" s="7" t="n">
         <v>46262</v>
       </c>
-      <c r="C413" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D413" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E413" s="5" t="inlineStr">
+      <c r="C413" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D413" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E413" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F413" s="6" t="inlineStr">
         <is>
           <t>No entry</t>
         </is>
@@ -9193,7 +10595,10 @@
       <c r="D414" s="4" t="n">
         <v>0.7472222222222222</v>
       </c>
-      <c r="E414" s="2" t="inlineStr">
+      <c r="E414" s="5" t="n">
+        <v>13.18</v>
+      </c>
+      <c r="F414" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -9214,7 +10619,10 @@
       <c r="D415" s="4" t="n">
         <v>0.75</v>
       </c>
-      <c r="E415" s="2" t="inlineStr">
+      <c r="E415" s="5" t="n">
+        <v>12.93</v>
+      </c>
+      <c r="F415" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -9235,7 +10643,10 @@
       <c r="D416" s="4" t="n">
         <v>0.75</v>
       </c>
-      <c r="E416" s="2" t="inlineStr">
+      <c r="E416" s="5" t="n">
+        <v>12.98</v>
+      </c>
+      <c r="F416" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -9256,7 +10667,10 @@
       <c r="D418" s="4" t="n">
         <v>0.7458333333333333</v>
       </c>
-      <c r="E418" s="2" t="inlineStr">
+      <c r="E418" s="5" t="n">
+        <v>11.82</v>
+      </c>
+      <c r="F418" s="2" t="inlineStr">
         <is>
           <t>last day of month; final record</t>
         </is>
@@ -9277,7 +10691,10 @@
       <c r="D419" s="4" t="n">
         <v>0.7430555555555556</v>
       </c>
-      <c r="E419" s="2" t="inlineStr">
+      <c r="E419" s="5" t="n">
+        <v>13.27</v>
+      </c>
+      <c r="F419" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -9298,7 +10715,10 @@
       <c r="D420" s="4" t="n">
         <v>0.7159722222222222</v>
       </c>
-      <c r="E420" s="2" t="inlineStr">
+      <c r="E420" s="5" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="F420" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -9319,7 +10739,10 @@
       <c r="D421" s="4" t="n">
         <v>0.7166666666666667</v>
       </c>
-      <c r="E421" s="2" t="inlineStr">
+      <c r="E421" s="5" t="n">
+        <v>13.43</v>
+      </c>
+      <c r="F421" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -9340,7 +10763,10 @@
       <c r="D422" s="4" t="n">
         <v>0.7715277777777778</v>
       </c>
-      <c r="E422" s="2" t="inlineStr">
+      <c r="E422" s="5" t="n">
+        <v>13.22</v>
+      </c>
+      <c r="F422" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -9361,32 +10787,40 @@
       <c r="D423" s="4" t="n">
         <v>0.7590277777777777</v>
       </c>
-      <c r="E423" s="2" t="inlineStr">
+      <c r="E423" s="5" t="n">
+        <v>13.13</v>
+      </c>
+      <c r="F423" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="424">
-      <c r="A424" s="5" t="inlineStr">
+      <c r="A424" s="6" t="inlineStr">
         <is>
           <t>38</t>
         </is>
       </c>
-      <c r="B424" s="6" t="n">
+      <c r="B424" s="7" t="n">
         <v>46241</v>
       </c>
-      <c r="C424" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D424" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E424" s="5" t="inlineStr">
+      <c r="C424" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D424" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E424" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F424" s="6" t="inlineStr">
         <is>
           <t>No entry</t>
         </is>
@@ -9407,7 +10841,10 @@
       <c r="D425" s="4" t="n">
         <v>0.7604166666666666</v>
       </c>
-      <c r="E425" s="2" t="inlineStr">
+      <c r="E425" s="5" t="n">
+        <v>13.08</v>
+      </c>
+      <c r="F425" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -9428,7 +10865,10 @@
       <c r="D426" s="4" t="n">
         <v>0.75</v>
       </c>
-      <c r="E426" s="2" t="inlineStr">
+      <c r="E426" s="5" t="n">
+        <v>12.72</v>
+      </c>
+      <c r="F426" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -9449,7 +10889,10 @@
       <c r="D427" s="4" t="n">
         <v>0.75</v>
       </c>
-      <c r="E427" s="2" t="inlineStr">
+      <c r="E427" s="5" t="n">
+        <v>11.43</v>
+      </c>
+      <c r="F427" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -9474,6 +10917,11 @@
       </c>
       <c r="E428" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F428" s="2" t="inlineStr">
+        <is>
           <t>single punch only</t>
         </is>
       </c>
@@ -9497,6 +10945,11 @@
       </c>
       <c r="E429" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F429" s="2" t="inlineStr">
+        <is>
           <t>single punch only</t>
         </is>
       </c>
@@ -9520,30 +10973,40 @@
       </c>
       <c r="E430" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F430" s="2" t="inlineStr">
+        <is>
           <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="431">
-      <c r="A431" s="5" t="inlineStr">
+      <c r="A431" s="6" t="inlineStr">
         <is>
           <t>38</t>
         </is>
       </c>
-      <c r="B431" s="6" t="n">
+      <c r="B431" s="7" t="n">
         <v>46248</v>
       </c>
-      <c r="C431" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D431" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E431" s="5" t="inlineStr">
+      <c r="C431" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D431" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E431" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F431" s="6" t="inlineStr">
         <is>
           <t>No entry</t>
         </is>
@@ -9564,7 +11027,10 @@
       <c r="D432" s="4" t="n">
         <v>0.75</v>
       </c>
-      <c r="E432" s="2" t="inlineStr">
+      <c r="E432" s="5" t="n">
+        <v>11.65</v>
+      </c>
+      <c r="F432" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -9585,7 +11051,10 @@
       <c r="D433" s="4" t="n">
         <v>0.7722222222222223</v>
       </c>
-      <c r="E433" s="2" t="inlineStr">
+      <c r="E433" s="5" t="n">
+        <v>13.27</v>
+      </c>
+      <c r="F433" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -9606,7 +11075,10 @@
       <c r="D434" s="4" t="n">
         <v>0.7680555555555556</v>
       </c>
-      <c r="E434" s="2" t="inlineStr">
+      <c r="E434" s="5" t="n">
+        <v>15.12</v>
+      </c>
+      <c r="F434" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -9627,7 +11099,10 @@
       <c r="D435" s="4" t="n">
         <v>0.7583333333333333</v>
       </c>
-      <c r="E435" s="2" t="inlineStr">
+      <c r="E435" s="5" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="F435" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -9648,7 +11123,10 @@
       <c r="D436" s="4" t="n">
         <v>0.7173611111111111</v>
       </c>
-      <c r="E436" s="2" t="inlineStr">
+      <c r="E436" s="5" t="n">
+        <v>18.18</v>
+      </c>
+      <c r="F436" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -9673,30 +11151,40 @@
       </c>
       <c r="E437" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F437" s="2" t="inlineStr">
+        <is>
           <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="438">
-      <c r="A438" s="5" t="inlineStr">
+      <c r="A438" s="6" t="inlineStr">
         <is>
           <t>38</t>
         </is>
       </c>
-      <c r="B438" s="6" t="n">
+      <c r="B438" s="7" t="n">
         <v>46255</v>
       </c>
-      <c r="C438" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D438" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E438" s="5" t="inlineStr">
+      <c r="C438" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D438" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E438" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F438" s="6" t="inlineStr">
         <is>
           <t>No entry</t>
         </is>
@@ -9717,7 +11205,10 @@
       <c r="D439" s="4" t="n">
         <v>0.7243055555555555</v>
       </c>
-      <c r="E439" s="2" t="inlineStr">
+      <c r="E439" s="5" t="n">
+        <v>11.58</v>
+      </c>
+      <c r="F439" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -9738,7 +11229,10 @@
       <c r="D440" s="4" t="n">
         <v>0.7493055555555556</v>
       </c>
-      <c r="E440" s="2" t="inlineStr">
+      <c r="E440" s="5" t="n">
+        <v>12.02</v>
+      </c>
+      <c r="F440" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -9759,7 +11253,10 @@
       <c r="D441" s="4" t="n">
         <v>0.7388888888888889</v>
       </c>
-      <c r="E441" s="2" t="inlineStr">
+      <c r="E441" s="5" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="F441" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -9780,7 +11277,10 @@
       <c r="D442" s="4" t="n">
         <v>0.7548611111111111</v>
       </c>
-      <c r="E442" s="2" t="inlineStr">
+      <c r="E442" s="5" t="n">
+        <v>12.52</v>
+      </c>
+      <c r="F442" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -9801,7 +11301,10 @@
       <c r="D443" s="4" t="n">
         <v>0.7534722222222222</v>
       </c>
-      <c r="E443" s="2" t="inlineStr">
+      <c r="E443" s="5" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="F443" s="2" t="inlineStr">
         <is>
           <t>extra punch: 17:56</t>
         </is>
@@ -9822,32 +11325,40 @@
       <c r="D444" s="4" t="n">
         <v>0.75</v>
       </c>
-      <c r="E444" s="2" t="inlineStr">
+      <c r="E444" s="5" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="F444" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="445">
-      <c r="A445" s="5" t="inlineStr">
+      <c r="A445" s="6" t="inlineStr">
         <is>
           <t>38</t>
         </is>
       </c>
-      <c r="B445" s="6" t="n">
+      <c r="B445" s="7" t="n">
         <v>46262</v>
       </c>
-      <c r="C445" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D445" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E445" s="5" t="inlineStr">
+      <c r="C445" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D445" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E445" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F445" s="6" t="inlineStr">
         <is>
           <t>No entry</t>
         </is>
@@ -9868,7 +11379,10 @@
       <c r="D446" s="4" t="n">
         <v>0.7326388888888888</v>
       </c>
-      <c r="E446" s="2" t="inlineStr">
+      <c r="E446" s="5" t="n">
+        <v>13.53</v>
+      </c>
+      <c r="F446" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -9889,7 +11403,10 @@
       <c r="D447" s="4" t="n">
         <v>0.75625</v>
       </c>
-      <c r="E447" s="2" t="inlineStr">
+      <c r="E447" s="5" t="n">
+        <v>12.97</v>
+      </c>
+      <c r="F447" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -9910,7 +11427,10 @@
       <c r="D448" s="4" t="n">
         <v>0.7604166666666666</v>
       </c>
-      <c r="E448" s="2" t="inlineStr">
+      <c r="E448" s="5" t="n">
+        <v>11.82</v>
+      </c>
+      <c r="F448" s="2" t="inlineStr">
         <is>
           <t>corrected from a clearer re-scan photo later in the album</t>
         </is>
@@ -9931,7 +11451,10 @@
       <c r="D450" s="4" t="n">
         <v>0.7319444444444444</v>
       </c>
-      <c r="E450" s="2" t="inlineStr">
+      <c r="E450" s="5" t="n">
+        <v>12.65</v>
+      </c>
+      <c r="F450" s="2" t="inlineStr">
         <is>
           <t>last day of month; final record</t>
         </is>
@@ -9952,7 +11475,10 @@
       <c r="D451" s="4" t="n">
         <v>0.7430555555555556</v>
       </c>
-      <c r="E451" s="2" t="inlineStr">
+      <c r="E451" s="5" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="F451" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -9973,7 +11499,10 @@
       <c r="D452" s="4" t="n">
         <v>0.7472222222222222</v>
       </c>
-      <c r="E452" s="2" t="inlineStr">
+      <c r="E452" s="5" t="n">
+        <v>12.35</v>
+      </c>
+      <c r="F452" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -9994,7 +11523,10 @@
       <c r="D453" s="4" t="n">
         <v>0.7506944444444444</v>
       </c>
-      <c r="E453" s="2" t="inlineStr">
+      <c r="E453" s="5" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="F453" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -10015,7 +11547,10 @@
       <c r="D454" s="4" t="n">
         <v>0.7722222222222223</v>
       </c>
-      <c r="E454" s="2" t="inlineStr">
+      <c r="E454" s="5" t="n">
+        <v>16.85</v>
+      </c>
+      <c r="F454" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -10036,32 +11571,40 @@
       <c r="D455" s="4" t="n">
         <v>0.7625</v>
       </c>
-      <c r="E455" s="2" t="inlineStr">
+      <c r="E455" s="5" t="n">
+        <v>11.48</v>
+      </c>
+      <c r="F455" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="456">
-      <c r="A456" s="5" t="inlineStr">
+      <c r="A456" s="6" t="inlineStr">
         <is>
           <t>39</t>
         </is>
       </c>
-      <c r="B456" s="6" t="n">
+      <c r="B456" s="7" t="n">
         <v>46241</v>
       </c>
-      <c r="C456" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D456" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E456" s="5" t="inlineStr">
+      <c r="C456" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D456" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E456" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F456" s="6" t="inlineStr">
         <is>
           <t>No entry</t>
         </is>
@@ -10082,7 +11625,10 @@
       <c r="D457" s="4" t="n">
         <v>0.7618055555555555</v>
       </c>
-      <c r="E457" s="2" t="inlineStr">
+      <c r="E457" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="F457" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -10103,7 +11649,10 @@
       <c r="D458" s="4" t="n">
         <v>0.725</v>
       </c>
-      <c r="E458" s="2" t="inlineStr">
+      <c r="E458" s="5" t="n">
+        <v>12.35</v>
+      </c>
+      <c r="F458" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -10124,7 +11673,10 @@
       <c r="D459" s="4" t="n">
         <v>0.7611111111111111</v>
       </c>
-      <c r="E459" s="2" t="inlineStr">
+      <c r="E459" s="5" t="n">
+        <v>11.15</v>
+      </c>
+      <c r="F459" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -10145,7 +11697,10 @@
       <c r="D460" s="4" t="n">
         <v>0.7375</v>
       </c>
-      <c r="E460" s="2" t="inlineStr">
+      <c r="E460" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="F460" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -10166,7 +11721,10 @@
       <c r="D461" s="4" t="n">
         <v>0.7423611111111111</v>
       </c>
-      <c r="E461" s="2" t="inlineStr">
+      <c r="E461" s="5" t="n">
+        <v>11.67</v>
+      </c>
+      <c r="F461" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -10191,30 +11749,40 @@
       </c>
       <c r="E462" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F462" s="2" t="inlineStr">
+        <is>
           <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="463">
-      <c r="A463" s="5" t="inlineStr">
+      <c r="A463" s="6" t="inlineStr">
         <is>
           <t>39</t>
         </is>
       </c>
-      <c r="B463" s="6" t="n">
+      <c r="B463" s="7" t="n">
         <v>46248</v>
       </c>
-      <c r="C463" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D463" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E463" s="5" t="inlineStr">
+      <c r="C463" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D463" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E463" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F463" s="6" t="inlineStr">
         <is>
           <t>No entry</t>
         </is>
@@ -10235,7 +11803,10 @@
       <c r="D464" s="4" t="n">
         <v>0.7611111111111111</v>
       </c>
-      <c r="E464" s="2" t="inlineStr">
+      <c r="E464" s="5" t="n">
+        <v>11.38</v>
+      </c>
+      <c r="F464" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -10256,7 +11827,10 @@
       <c r="D465" s="4" t="n">
         <v>0.7381944444444445</v>
       </c>
-      <c r="E465" s="2" t="inlineStr">
+      <c r="E465" s="5" t="n">
+        <v>12.07</v>
+      </c>
+      <c r="F465" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -10277,7 +11851,10 @@
       <c r="D466" s="4" t="n">
         <v>0.7326388888888888</v>
       </c>
-      <c r="E466" s="2" t="inlineStr">
+      <c r="E466" s="5" t="n">
+        <v>14.62</v>
+      </c>
+      <c r="F466" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -10298,7 +11875,10 @@
       <c r="D467" s="4" t="n">
         <v>0.7416666666666667</v>
       </c>
-      <c r="E467" s="2" t="inlineStr">
+      <c r="E467" s="5" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="F467" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -10319,7 +11899,10 @@
       <c r="D468" s="4" t="n">
         <v>0.7416666666666667</v>
       </c>
-      <c r="E468" s="2" t="inlineStr">
+      <c r="E468" s="5" t="n">
+        <v>11.95</v>
+      </c>
+      <c r="F468" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -10340,32 +11923,40 @@
       <c r="D469" s="4" t="n">
         <v>0.7243055555555555</v>
       </c>
-      <c r="E469" s="2" t="inlineStr">
+      <c r="E469" s="5" t="n">
+        <v>12.55</v>
+      </c>
+      <c r="F469" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="470">
-      <c r="A470" s="5" t="inlineStr">
+      <c r="A470" s="6" t="inlineStr">
         <is>
           <t>39</t>
         </is>
       </c>
-      <c r="B470" s="6" t="n">
+      <c r="B470" s="7" t="n">
         <v>46255</v>
       </c>
-      <c r="C470" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D470" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E470" s="5" t="inlineStr">
+      <c r="C470" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D470" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E470" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F470" s="6" t="inlineStr">
         <is>
           <t>No entry</t>
         </is>
@@ -10390,6 +11981,11 @@
       </c>
       <c r="E471" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F471" s="2" t="inlineStr">
+        <is>
           <t>single punch only</t>
         </is>
       </c>
@@ -10409,7 +12005,10 @@
       <c r="D472" s="4" t="n">
         <v>0.7618055555555555</v>
       </c>
-      <c r="E472" s="2" t="inlineStr">
+      <c r="E472" s="5" t="n">
+        <v>11.67</v>
+      </c>
+      <c r="F472" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -10430,7 +12029,10 @@
       <c r="D473" s="4" t="n">
         <v>0.7506944444444444</v>
       </c>
-      <c r="E473" s="2" t="inlineStr">
+      <c r="E473" s="5" t="n">
+        <v>11.68</v>
+      </c>
+      <c r="F473" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -10451,7 +12053,10 @@
       <c r="D474" s="4" t="n">
         <v>0.7597222222222222</v>
       </c>
-      <c r="E474" s="2" t="inlineStr">
+      <c r="E474" s="5" t="n">
+        <v>11.47</v>
+      </c>
+      <c r="F474" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -10472,7 +12077,10 @@
       <c r="D475" s="4" t="n">
         <v>0.7555555555555555</v>
       </c>
-      <c r="E475" s="2" t="inlineStr">
+      <c r="E475" s="5" t="n">
+        <v>11.82</v>
+      </c>
+      <c r="F475" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -10493,30 +12101,38 @@
       <c r="D476" s="4" t="n">
         <v>0.7944444444444444</v>
       </c>
-      <c r="E476" s="2" t="inlineStr">
+      <c r="E476" s="5" t="n">
+        <v>10.92</v>
+      </c>
+      <c r="F476" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="477">
-      <c r="A477" s="5" t="inlineStr">
+      <c r="A477" s="6" t="inlineStr">
         <is>
           <t>39</t>
         </is>
       </c>
-      <c r="B477" s="6" t="n">
+      <c r="B477" s="7" t="n">
         <v>46262</v>
       </c>
-      <c r="C477" s="7" t="n">
+      <c r="C477" s="8" t="n">
         <v>0.25</v>
       </c>
-      <c r="D477" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E477" s="5" t="inlineStr">
+      <c r="D477" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E477" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F477" s="6" t="inlineStr">
         <is>
           <t>single punch only</t>
         </is>
@@ -10537,7 +12153,10 @@
       <c r="D478" s="4" t="n">
         <v>0.7458333333333333</v>
       </c>
-      <c r="E478" s="2" t="inlineStr">
+      <c r="E478" s="5" t="n">
+        <v>12.27</v>
+      </c>
+      <c r="F478" s="2" t="inlineStr">
         <is>
           <t>extra punch: 17:53</t>
         </is>
@@ -10558,7 +12177,10 @@
       <c r="D479" s="4" t="n">
         <v>0.7541666666666667</v>
       </c>
-      <c r="E479" s="2" t="inlineStr">
+      <c r="E479" s="5" t="n">
+        <v>12.12</v>
+      </c>
+      <c r="F479" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -10579,7 +12201,10 @@
       <c r="D480" s="4" t="n">
         <v>0.7513888888888889</v>
       </c>
-      <c r="E480" s="2" t="inlineStr">
+      <c r="E480" s="5" t="n">
+        <v>12.63</v>
+      </c>
+      <c r="F480" s="2" t="inlineStr">
         <is>
           <t>corrected from a clearer re-scan photo later in the album</t>
         </is>
@@ -10600,7 +12225,10 @@
       <c r="D482" s="4" t="n">
         <v>0.7506944444444444</v>
       </c>
-      <c r="E482" s="2" t="inlineStr">
+      <c r="E482" s="5" t="n">
+        <v>11.87</v>
+      </c>
+      <c r="F482" s="2" t="inlineStr">
         <is>
           <t>last day of month; final record</t>
         </is>
@@ -10621,7 +12249,10 @@
       <c r="D483" s="4" t="n">
         <v>0.7520833333333333</v>
       </c>
-      <c r="E483" s="2" t="inlineStr">
+      <c r="E483" s="5" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="F483" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -10642,7 +12273,10 @@
       <c r="D484" s="4" t="n">
         <v>0.7527777777777778</v>
       </c>
-      <c r="E484" s="2" t="inlineStr">
+      <c r="E484" s="5" t="n">
+        <v>11.78</v>
+      </c>
+      <c r="F484" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -10663,7 +12297,10 @@
       <c r="D485" s="4" t="n">
         <v>0.7520833333333333</v>
       </c>
-      <c r="E485" s="2" t="inlineStr">
+      <c r="E485" s="5" t="n">
+        <v>11.83</v>
+      </c>
+      <c r="F485" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -10684,7 +12321,10 @@
       <c r="D486" s="4" t="n">
         <v>0.7611111111111111</v>
       </c>
-      <c r="E486" s="2" t="inlineStr">
+      <c r="E486" s="5" t="n">
+        <v>11.42</v>
+      </c>
+      <c r="F486" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -10705,32 +12345,40 @@
       <c r="D487" s="4" t="n">
         <v>0.7513888888888889</v>
       </c>
-      <c r="E487" s="2" t="inlineStr">
+      <c r="E487" s="5" t="n">
+        <v>11.73</v>
+      </c>
+      <c r="F487" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="488">
-      <c r="A488" s="5" t="inlineStr">
+      <c r="A488" s="6" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="B488" s="6" t="n">
+      <c r="B488" s="7" t="n">
         <v>46241</v>
       </c>
-      <c r="C488" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D488" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E488" s="5" t="inlineStr">
+      <c r="C488" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D488" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E488" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F488" s="6" t="inlineStr">
         <is>
           <t>No entry</t>
         </is>
@@ -10751,7 +12399,10 @@
       <c r="D489" s="4" t="n">
         <v>0.7548611111111111</v>
       </c>
-      <c r="E489" s="2" t="inlineStr">
+      <c r="E489" s="5" t="n">
+        <v>11.72</v>
+      </c>
+      <c r="F489" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -10778,6 +12429,11 @@
       </c>
       <c r="E490" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F490" s="2" t="inlineStr">
+        <is>
           <t>No entry</t>
         </is>
       </c>
@@ -10803,6 +12459,11 @@
       </c>
       <c r="E491" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F491" s="2" t="inlineStr">
+        <is>
           <t>No entry</t>
         </is>
       </c>
@@ -10828,6 +12489,11 @@
       </c>
       <c r="E492" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F492" s="2" t="inlineStr">
+        <is>
           <t>No entry</t>
         </is>
       </c>
@@ -10853,6 +12519,11 @@
       </c>
       <c r="E493" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F493" s="2" t="inlineStr">
+        <is>
           <t>PLEASE VERIFY: check-in/out times not captured (gap between source photos)</t>
         </is>
       </c>
@@ -10872,32 +12543,40 @@
       <c r="D494" s="4" t="n">
         <v>0.7576388888888889</v>
       </c>
-      <c r="E494" s="2" t="inlineStr">
+      <c r="E494" s="5" t="n">
+        <v>11.68</v>
+      </c>
+      <c r="F494" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="495">
-      <c r="A495" s="5" t="inlineStr">
+      <c r="A495" s="6" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="B495" s="6" t="n">
+      <c r="B495" s="7" t="n">
         <v>46248</v>
       </c>
-      <c r="C495" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D495" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E495" s="5" t="inlineStr">
+      <c r="C495" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D495" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E495" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F495" s="6" t="inlineStr">
         <is>
           <t>No entry</t>
         </is>
@@ -10918,7 +12597,10 @@
       <c r="D496" s="4" t="n">
         <v>0.7513888888888889</v>
       </c>
-      <c r="E496" s="2" t="inlineStr">
+      <c r="E496" s="5" t="n">
+        <v>11.68</v>
+      </c>
+      <c r="F496" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -10939,7 +12621,10 @@
       <c r="D497" s="4" t="n">
         <v>0.7520833333333333</v>
       </c>
-      <c r="E497" s="2" t="inlineStr">
+      <c r="E497" s="5" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="F497" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -10960,7 +12645,10 @@
       <c r="D498" s="4" t="n">
         <v>0.7541666666666667</v>
       </c>
-      <c r="E498" s="2" t="inlineStr">
+      <c r="E498" s="5" t="n">
+        <v>11.65</v>
+      </c>
+      <c r="F498" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -10981,7 +12669,10 @@
       <c r="D499" s="4" t="n">
         <v>0.7527777777777778</v>
       </c>
-      <c r="E499" s="2" t="inlineStr">
+      <c r="E499" s="5" t="n">
+        <v>11.82</v>
+      </c>
+      <c r="F499" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -11002,7 +12693,10 @@
       <c r="D500" s="4" t="n">
         <v>0.7506944444444444</v>
       </c>
-      <c r="E500" s="2" t="inlineStr">
+      <c r="E500" s="5" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="F500" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -11023,32 +12717,40 @@
       <c r="D501" s="4" t="n">
         <v>0.7520833333333333</v>
       </c>
-      <c r="E501" s="2" t="inlineStr">
+      <c r="E501" s="5" t="n">
+        <v>11.72</v>
+      </c>
+      <c r="F501" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="502">
-      <c r="A502" s="5" t="inlineStr">
+      <c r="A502" s="6" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="B502" s="6" t="n">
+      <c r="B502" s="7" t="n">
         <v>46255</v>
       </c>
-      <c r="C502" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D502" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E502" s="5" t="inlineStr">
+      <c r="C502" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D502" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E502" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F502" s="6" t="inlineStr">
         <is>
           <t>No entry</t>
         </is>
@@ -11069,7 +12771,10 @@
       <c r="D503" s="4" t="n">
         <v>0.75</v>
       </c>
-      <c r="E503" s="2" t="inlineStr">
+      <c r="E503" s="5" t="n">
+        <v>11.77</v>
+      </c>
+      <c r="F503" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -11090,7 +12795,10 @@
       <c r="D504" s="4" t="n">
         <v>0.7527777777777778</v>
       </c>
-      <c r="E504" s="2" t="inlineStr">
+      <c r="E504" s="5" t="n">
+        <v>11.83</v>
+      </c>
+      <c r="F504" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -11111,7 +12819,10 @@
       <c r="D505" s="4" t="n">
         <v>0.7520833333333333</v>
       </c>
-      <c r="E505" s="2" t="inlineStr">
+      <c r="E505" s="5" t="n">
+        <v>11.58</v>
+      </c>
+      <c r="F505" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -11132,7 +12843,10 @@
       <c r="D506" s="4" t="n">
         <v>0.7506944444444444</v>
       </c>
-      <c r="E506" s="2" t="inlineStr">
+      <c r="E506" s="5" t="n">
+        <v>11.67</v>
+      </c>
+      <c r="F506" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -11153,7 +12867,10 @@
       <c r="D507" s="4" t="n">
         <v>0.7555555555555555</v>
       </c>
-      <c r="E507" s="2" t="inlineStr">
+      <c r="E507" s="5" t="n">
+        <v>11.78</v>
+      </c>
+      <c r="F507" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -11174,32 +12891,40 @@
       <c r="D508" s="4" t="n">
         <v>0.7513888888888889</v>
       </c>
-      <c r="E508" s="2" t="inlineStr">
+      <c r="E508" s="5" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="F508" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="509">
-      <c r="A509" s="5" t="inlineStr">
+      <c r="A509" s="6" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="B509" s="6" t="n">
+      <c r="B509" s="7" t="n">
         <v>46262</v>
       </c>
-      <c r="C509" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D509" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E509" s="5" t="inlineStr">
+      <c r="C509" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D509" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E509" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F509" s="6" t="inlineStr">
         <is>
           <t>No entry</t>
         </is>
@@ -11220,7 +12945,10 @@
       <c r="D510" s="4" t="n">
         <v>0.7548611111111111</v>
       </c>
-      <c r="E510" s="2" t="inlineStr">
+      <c r="E510" s="5" t="n">
+        <v>11.75</v>
+      </c>
+      <c r="F510" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -11241,7 +12969,10 @@
       <c r="D511" s="4" t="n">
         <v>0.7513888888888889</v>
       </c>
-      <c r="E511" s="2" t="inlineStr">
+      <c r="E511" s="5" t="n">
+        <v>11.78</v>
+      </c>
+      <c r="F511" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -11262,7 +12993,10 @@
       <c r="D512" s="4" t="n">
         <v>0.7520833333333333</v>
       </c>
-      <c r="E512" s="2" t="inlineStr">
+      <c r="E512" s="5" t="n">
+        <v>11.62</v>
+      </c>
+      <c r="F512" s="2" t="inlineStr">
         <is>
           <t>corrected from a clearer re-scan photo later in the album</t>
         </is>
@@ -11283,7 +13017,10 @@
       <c r="D514" s="4" t="n">
         <v>0.7854166666666667</v>
       </c>
-      <c r="E514" s="2" t="inlineStr">
+      <c r="E514" s="5" t="n">
+        <v>11.75</v>
+      </c>
+      <c r="F514" s="2" t="inlineStr">
         <is>
           <t>last day of month; final record</t>
         </is>
@@ -11304,7 +13041,10 @@
       <c r="D515" s="4" t="n">
         <v>0.7722222222222223</v>
       </c>
-      <c r="E515" s="2" t="inlineStr">
+      <c r="E515" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="F515" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -11325,7 +13065,10 @@
       <c r="D516" s="4" t="n">
         <v>0.7201388888888889</v>
       </c>
-      <c r="E516" s="2" t="inlineStr">
+      <c r="E516" s="5" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="F516" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -11346,7 +13089,10 @@
       <c r="D517" s="4" t="n">
         <v>0.7527777777777778</v>
       </c>
-      <c r="E517" s="2" t="inlineStr">
+      <c r="E517" s="5" t="n">
+        <v>12.48</v>
+      </c>
+      <c r="F517" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -11367,7 +13113,10 @@
       <c r="D518" s="4" t="n">
         <v>0.7152777777777778</v>
       </c>
-      <c r="E518" s="2" t="inlineStr">
+      <c r="E518" s="5" t="n">
+        <v>13.45</v>
+      </c>
+      <c r="F518" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -11392,30 +13141,40 @@
       </c>
       <c r="E519" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F519" s="2" t="inlineStr">
+        <is>
           <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="520">
-      <c r="A520" s="5" t="inlineStr">
+      <c r="A520" s="6" t="inlineStr">
         <is>
           <t>41</t>
         </is>
       </c>
-      <c r="B520" s="6" t="n">
+      <c r="B520" s="7" t="n">
         <v>46241</v>
       </c>
-      <c r="C520" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D520" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E520" s="5" t="inlineStr">
+      <c r="C520" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D520" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E520" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F520" s="6" t="inlineStr">
         <is>
           <t>No entry</t>
         </is>
@@ -11436,7 +13195,10 @@
       <c r="D521" s="4" t="n">
         <v>0.6965277777777777</v>
       </c>
-      <c r="E521" s="2" t="inlineStr">
+      <c r="E521" s="5" t="n">
+        <v>13.02</v>
+      </c>
+      <c r="F521" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -11457,7 +13219,10 @@
       <c r="D522" s="4" t="n">
         <v>0.7694444444444445</v>
       </c>
-      <c r="E522" s="2" t="inlineStr">
+      <c r="E522" s="5" t="n">
+        <v>11.42</v>
+      </c>
+      <c r="F522" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -11478,7 +13243,10 @@
       <c r="D523" s="4" t="n">
         <v>0.75625</v>
       </c>
-      <c r="E523" s="2" t="inlineStr">
+      <c r="E523" s="5" t="n">
+        <v>11.37</v>
+      </c>
+      <c r="F523" s="2" t="inlineStr">
         <is>
           <t>extra punch: 06:48</t>
         </is>
@@ -11499,7 +13267,10 @@
       <c r="D524" s="4" t="n">
         <v>0.7618055555555555</v>
       </c>
-      <c r="E524" s="2" t="inlineStr">
+      <c r="E524" s="5" t="n">
+        <v>12.32</v>
+      </c>
+      <c r="F524" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -11520,7 +13291,10 @@
       <c r="D525" s="4" t="n">
         <v>0.7222222222222222</v>
       </c>
-      <c r="E525" s="2" t="inlineStr">
+      <c r="E525" s="5" t="n">
+        <v>13.13</v>
+      </c>
+      <c r="F525" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -11541,32 +13315,40 @@
       <c r="D526" s="4" t="n">
         <v>0.7583333333333333</v>
       </c>
-      <c r="E526" s="2" t="inlineStr">
+      <c r="E526" s="5" t="n">
+        <v>13.98</v>
+      </c>
+      <c r="F526" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="527">
-      <c r="A527" s="5" t="inlineStr">
+      <c r="A527" s="6" t="inlineStr">
         <is>
           <t>41</t>
         </is>
       </c>
-      <c r="B527" s="6" t="n">
+      <c r="B527" s="7" t="n">
         <v>46248</v>
       </c>
-      <c r="C527" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D527" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E527" s="5" t="inlineStr">
+      <c r="C527" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D527" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E527" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F527" s="6" t="inlineStr">
         <is>
           <t>No entry</t>
         </is>
@@ -11587,7 +13369,10 @@
       <c r="D528" s="4" t="n">
         <v>0.7625</v>
       </c>
-      <c r="E528" s="2" t="inlineStr">
+      <c r="E528" s="5" t="n">
+        <v>12.13</v>
+      </c>
+      <c r="F528" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -11608,7 +13393,10 @@
       <c r="D529" s="4" t="n">
         <v>0.7173611111111111</v>
       </c>
-      <c r="E529" s="2" t="inlineStr">
+      <c r="E529" s="5" t="n">
+        <v>14.98</v>
+      </c>
+      <c r="F529" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -11629,7 +13417,10 @@
       <c r="D530" s="4" t="n">
         <v>0.7069444444444445</v>
       </c>
-      <c r="E530" s="2" t="inlineStr">
+      <c r="E530" s="5" t="n">
+        <v>14.48</v>
+      </c>
+      <c r="F530" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -11650,7 +13441,10 @@
       <c r="D531" s="4" t="n">
         <v>0.7208333333333333</v>
       </c>
-      <c r="E531" s="2" t="inlineStr">
+      <c r="E531" s="5" t="n">
+        <v>15.48</v>
+      </c>
+      <c r="F531" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -11671,7 +13465,10 @@
       <c r="D532" s="4" t="n">
         <v>0.7305555555555555</v>
       </c>
-      <c r="E532" s="2" t="inlineStr">
+      <c r="E532" s="5" t="n">
+        <v>13.53</v>
+      </c>
+      <c r="F532" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -11692,32 +13489,40 @@
       <c r="D533" s="4" t="n">
         <v>0.70625</v>
       </c>
-      <c r="E533" s="2" t="inlineStr">
+      <c r="E533" s="5" t="n">
+        <v>17.37</v>
+      </c>
+      <c r="F533" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="534">
-      <c r="A534" s="5" t="inlineStr">
+      <c r="A534" s="6" t="inlineStr">
         <is>
           <t>41</t>
         </is>
       </c>
-      <c r="B534" s="6" t="n">
+      <c r="B534" s="7" t="n">
         <v>46255</v>
       </c>
-      <c r="C534" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D534" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E534" s="5" t="inlineStr">
+      <c r="C534" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D534" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E534" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F534" s="6" t="inlineStr">
         <is>
           <t>No entry</t>
         </is>
@@ -11738,7 +13543,10 @@
       <c r="D535" s="4" t="n">
         <v>0.7083333333333334</v>
       </c>
-      <c r="E535" s="2" t="inlineStr">
+      <c r="E535" s="5" t="n">
+        <v>13.93</v>
+      </c>
+      <c r="F535" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -11759,7 +13567,10 @@
       <c r="D536" s="4" t="n">
         <v>0.7076388888888889</v>
       </c>
-      <c r="E536" s="2" t="inlineStr">
+      <c r="E536" s="5" t="n">
+        <v>12.88</v>
+      </c>
+      <c r="F536" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -11780,7 +13591,10 @@
       <c r="D537" s="4" t="n">
         <v>0.7055555555555556</v>
       </c>
-      <c r="E537" s="2" t="inlineStr">
+      <c r="E537" s="5" t="n">
+        <v>13.75</v>
+      </c>
+      <c r="F537" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -11801,7 +13615,10 @@
       <c r="D538" s="4" t="n">
         <v>0.7222222222222222</v>
       </c>
-      <c r="E538" s="2" t="inlineStr">
+      <c r="E538" s="5" t="n">
+        <v>13.52</v>
+      </c>
+      <c r="F538" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -11822,7 +13639,10 @@
       <c r="D539" s="4" t="n">
         <v>0.7152777777777778</v>
       </c>
-      <c r="E539" s="2" t="inlineStr">
+      <c r="E539" s="5" t="n">
+        <v>12.53</v>
+      </c>
+      <c r="F539" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -11843,32 +13663,40 @@
       <c r="D540" s="4" t="n">
         <v>0.7111111111111111</v>
       </c>
-      <c r="E540" s="2" t="inlineStr">
+      <c r="E540" s="5" t="n">
+        <v>18.65</v>
+      </c>
+      <c r="F540" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="541">
-      <c r="A541" s="5" t="inlineStr">
+      <c r="A541" s="6" t="inlineStr">
         <is>
           <t>41</t>
         </is>
       </c>
-      <c r="B541" s="6" t="n">
+      <c r="B541" s="7" t="n">
         <v>46262</v>
       </c>
-      <c r="C541" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D541" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E541" s="5" t="inlineStr">
+      <c r="C541" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D541" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E541" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F541" s="6" t="inlineStr">
         <is>
           <t>No entry</t>
         </is>
@@ -11889,7 +13717,10 @@
       <c r="D542" s="4" t="n">
         <v>0.7104166666666667</v>
       </c>
-      <c r="E542" s="2" t="inlineStr">
+      <c r="E542" s="5" t="n">
+        <v>12.98</v>
+      </c>
+      <c r="F542" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -11910,7 +13741,10 @@
       <c r="D543" s="4" t="n">
         <v>0.7215277777777778</v>
       </c>
-      <c r="E543" s="2" t="inlineStr">
+      <c r="E543" s="5" t="n">
+        <v>13.78</v>
+      </c>
+      <c r="F543" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -11935,6 +13769,11 @@
       </c>
       <c r="E544" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F544" s="2" t="inlineStr">
+        <is>
           <t>single punch only</t>
         </is>
       </c>
@@ -11954,7 +13793,10 @@
       <c r="D546" s="4" t="n">
         <v>0.7347222222222223</v>
       </c>
-      <c r="E546" s="2" t="inlineStr">
+      <c r="E546" s="5" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="F546" s="2" t="inlineStr">
         <is>
           <t>last day of month; final record</t>
         </is>
@@ -11979,6 +13821,11 @@
       </c>
       <c r="E547" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F547" s="2" t="inlineStr">
+        <is>
           <t>single punch only</t>
         </is>
       </c>
@@ -11998,7 +13845,10 @@
       <c r="D548" s="4" t="n">
         <v>0.7111111111111111</v>
       </c>
-      <c r="E548" s="2" t="inlineStr">
+      <c r="E548" s="5" t="n">
+        <v>14.83</v>
+      </c>
+      <c r="F548" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -12019,7 +13869,10 @@
       <c r="D549" s="4" t="n">
         <v>0.7263888888888889</v>
       </c>
-      <c r="E549" s="2" t="inlineStr">
+      <c r="E549" s="5" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="F549" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -12044,6 +13897,11 @@
       </c>
       <c r="E550" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F550" s="2" t="inlineStr">
+        <is>
           <t>single punch only</t>
         </is>
       </c>
@@ -12063,32 +13921,40 @@
       <c r="D551" s="4" t="n">
         <v>0.7277777777777777</v>
       </c>
-      <c r="E551" s="2" t="inlineStr">
+      <c r="E551" s="5" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="F551" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="552">
-      <c r="A552" s="5" t="inlineStr">
+      <c r="A552" s="6" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="B552" s="6" t="n">
+      <c r="B552" s="7" t="n">
         <v>46241</v>
       </c>
-      <c r="C552" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D552" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E552" s="5" t="inlineStr">
+      <c r="C552" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D552" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E552" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F552" s="6" t="inlineStr">
         <is>
           <t>No entry</t>
         </is>
@@ -12109,7 +13975,10 @@
       <c r="D553" s="4" t="n">
         <v>0.7284722222222222</v>
       </c>
-      <c r="E553" s="2" t="inlineStr">
+      <c r="E553" s="5" t="n">
+        <v>13.22</v>
+      </c>
+      <c r="F553" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -12130,7 +13999,10 @@
       <c r="D554" s="4" t="n">
         <v>0.7555555555555555</v>
       </c>
-      <c r="E554" s="2" t="inlineStr">
+      <c r="E554" s="5" t="n">
+        <v>12.55</v>
+      </c>
+      <c r="F554" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -12151,7 +14023,10 @@
       <c r="D555" s="4" t="n">
         <v>0.7479166666666667</v>
       </c>
-      <c r="E555" s="2" t="inlineStr">
+      <c r="E555" s="5" t="n">
+        <v>12.95</v>
+      </c>
+      <c r="F555" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -12172,7 +14047,10 @@
       <c r="D556" s="4" t="n">
         <v>0.7465277777777778</v>
       </c>
-      <c r="E556" s="2" t="inlineStr">
+      <c r="E556" s="5" t="n">
+        <v>13.28</v>
+      </c>
+      <c r="F556" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -12193,7 +14071,10 @@
       <c r="D557" s="4" t="n">
         <v>0.7222222222222222</v>
       </c>
-      <c r="E557" s="2" t="inlineStr">
+      <c r="E557" s="5" t="n">
+        <v>12.78</v>
+      </c>
+      <c r="F557" s="2" t="inlineStr">
         <is>
           <t>extra punches: 07:44 06:16</t>
         </is>
@@ -12214,32 +14095,40 @@
       <c r="D558" s="4" t="n">
         <v>0.7236111111111111</v>
       </c>
-      <c r="E558" s="2" t="inlineStr">
+      <c r="E558" s="5" t="n">
+        <v>14.77</v>
+      </c>
+      <c r="F558" s="2" t="inlineStr">
         <is>
           <t>extra punch: 17:21</t>
         </is>
       </c>
     </row>
     <row r="559">
-      <c r="A559" s="5" t="inlineStr">
+      <c r="A559" s="6" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="B559" s="6" t="n">
+      <c r="B559" s="7" t="n">
         <v>46248</v>
       </c>
-      <c r="C559" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D559" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E559" s="5" t="inlineStr">
+      <c r="C559" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D559" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E559" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F559" s="6" t="inlineStr">
         <is>
           <t>No entry</t>
         </is>
@@ -12260,7 +14149,10 @@
       <c r="D560" s="4" t="n">
         <v>0.7270833333333333</v>
       </c>
-      <c r="E560" s="2" t="inlineStr">
+      <c r="E560" s="5" t="n">
+        <v>12.37</v>
+      </c>
+      <c r="F560" s="2" t="inlineStr">
         <is>
           <t>extra punches: 17:27 07:28</t>
         </is>
@@ -12281,7 +14173,10 @@
       <c r="D561" s="4" t="n">
         <v>0.7104166666666667</v>
       </c>
-      <c r="E561" s="2" t="inlineStr">
+      <c r="E561" s="5" t="n">
+        <v>15.13</v>
+      </c>
+      <c r="F561" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -12302,7 +14197,10 @@
       <c r="D562" s="4" t="n">
         <v>0.7326388888888888</v>
       </c>
-      <c r="E562" s="2" t="inlineStr">
+      <c r="E562" s="5" t="n">
+        <v>13.22</v>
+      </c>
+      <c r="F562" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -12323,7 +14221,10 @@
       <c r="D563" s="4" t="n">
         <v>0.7645833333333333</v>
       </c>
-      <c r="E563" s="2" t="inlineStr">
+      <c r="E563" s="5" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="F563" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -12344,7 +14245,10 @@
       <c r="D564" s="4" t="n">
         <v>0.74375</v>
       </c>
-      <c r="E564" s="2" t="inlineStr">
+      <c r="E564" s="5" t="n">
+        <v>13.75</v>
+      </c>
+      <c r="F564" s="2" t="inlineStr">
         <is>
           <t>extra punch: 08:01</t>
         </is>
@@ -12369,30 +14273,40 @@
       </c>
       <c r="E565" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F565" s="2" t="inlineStr">
+        <is>
           <t>single punch only</t>
         </is>
       </c>
     </row>
     <row r="566">
-      <c r="A566" s="5" t="inlineStr">
+      <c r="A566" s="6" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="B566" s="6" t="n">
+      <c r="B566" s="7" t="n">
         <v>46255</v>
       </c>
-      <c r="C566" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D566" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E566" s="5" t="inlineStr">
+      <c r="C566" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D566" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E566" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F566" s="6" t="inlineStr">
         <is>
           <t>No entry</t>
         </is>
@@ -12417,6 +14331,11 @@
       </c>
       <c r="E567" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F567" s="2" t="inlineStr">
+        <is>
           <t>single punch only</t>
         </is>
       </c>
@@ -12436,7 +14355,10 @@
       <c r="D568" s="4" t="n">
         <v>0.7569444444444444</v>
       </c>
-      <c r="E568" s="2" t="inlineStr">
+      <c r="E568" s="5" t="n">
+        <v>11.95</v>
+      </c>
+      <c r="F568" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -12461,6 +14383,11 @@
       </c>
       <c r="E569" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F569" s="2" t="inlineStr">
+        <is>
           <t>single punch only</t>
         </is>
       </c>
@@ -12480,7 +14407,10 @@
       <c r="D570" s="4" t="n">
         <v>0.6895833333333333</v>
       </c>
-      <c r="E570" s="2" t="inlineStr">
+      <c r="E570" s="5" t="n">
+        <v>14.33</v>
+      </c>
+      <c r="F570" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -12505,6 +14435,11 @@
       </c>
       <c r="E571" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F571" s="2" t="inlineStr">
+        <is>
           <t>single punch only</t>
         </is>
       </c>
@@ -12524,32 +14459,40 @@
       <c r="D572" s="4" t="n">
         <v>0.8645833333333334</v>
       </c>
-      <c r="E572" s="2" t="inlineStr">
+      <c r="E572" s="5" t="n">
+        <v>10.05</v>
+      </c>
+      <c r="F572" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="573">
-      <c r="A573" s="5" t="inlineStr">
+      <c r="A573" s="6" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="B573" s="6" t="n">
+      <c r="B573" s="7" t="n">
         <v>46262</v>
       </c>
-      <c r="C573" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D573" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E573" s="5" t="inlineStr">
+      <c r="C573" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D573" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E573" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F573" s="6" t="inlineStr">
         <is>
           <t>No entry</t>
         </is>
@@ -12574,6 +14517,11 @@
       </c>
       <c r="E574" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F574" s="2" t="inlineStr">
+        <is>
           <t>single punch only</t>
         </is>
       </c>
@@ -12593,7 +14541,10 @@
       <c r="D575" s="4" t="n">
         <v>0.7472222222222222</v>
       </c>
-      <c r="E575" s="2" t="inlineStr">
+      <c r="E575" s="5" t="n">
+        <v>12.78</v>
+      </c>
+      <c r="F575" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -12614,7 +14565,10 @@
       <c r="D576" s="4" t="n">
         <v>0.7215277777777778</v>
       </c>
-      <c r="E576" s="2" t="inlineStr">
+      <c r="E576" s="5" t="n">
+        <v>16.02</v>
+      </c>
+      <c r="F576" s="2" t="inlineStr">
         <is>
           <t>corrected from a clearer re-scan photo later in the album</t>
         </is>
@@ -12635,7 +14589,10 @@
       <c r="D578" s="4" t="n">
         <v>0.7430555555555556</v>
       </c>
-      <c r="E578" s="2" t="inlineStr">
+      <c r="E578" s="5" t="n">
+        <v>12.33</v>
+      </c>
+      <c r="F578" s="2" t="inlineStr">
         <is>
           <t>extra punch: 17:55; last day of month; final record</t>
         </is>
@@ -12656,7 +14613,10 @@
       <c r="D579" s="4" t="n">
         <v>0.7381944444444445</v>
       </c>
-      <c r="E579" s="2" t="inlineStr">
+      <c r="E579" s="5" t="n">
+        <v>11.57</v>
+      </c>
+      <c r="F579" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -12677,7 +14637,10 @@
       <c r="D580" s="4" t="n">
         <v>0.7402777777777778</v>
       </c>
-      <c r="E580" s="2" t="inlineStr">
+      <c r="E580" s="5" t="n">
+        <v>12.17</v>
+      </c>
+      <c r="F580" s="2" t="inlineStr">
         <is>
           <t>extra punch: 17:46</t>
         </is>
@@ -12698,7 +14661,10 @@
       <c r="D581" s="4" t="n">
         <v>0.7604166666666666</v>
       </c>
-      <c r="E581" s="2" t="inlineStr">
+      <c r="E581" s="5" t="n">
+        <v>10.97</v>
+      </c>
+      <c r="F581" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -12719,7 +14685,10 @@
       <c r="D582" s="4" t="n">
         <v>0.7611111111111111</v>
       </c>
-      <c r="E582" s="2" t="inlineStr">
+      <c r="E582" s="5" t="n">
+        <v>11.33</v>
+      </c>
+      <c r="F582" s="2" t="inlineStr">
         <is>
           <t>extra punch: 18:16</t>
         </is>
@@ -12740,32 +14709,40 @@
       <c r="D583" s="4" t="n">
         <v>0.75625</v>
       </c>
-      <c r="E583" s="2" t="inlineStr">
+      <c r="E583" s="5" t="n">
+        <v>11.32</v>
+      </c>
+      <c r="F583" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="584">
-      <c r="A584" s="5" t="inlineStr">
+      <c r="A584" s="6" t="inlineStr">
         <is>
           <t>44</t>
         </is>
       </c>
-      <c r="B584" s="6" t="n">
+      <c r="B584" s="7" t="n">
         <v>46241</v>
       </c>
-      <c r="C584" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D584" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E584" s="5" t="inlineStr">
+      <c r="C584" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D584" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E584" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F584" s="6" t="inlineStr">
         <is>
           <t>No entry</t>
         </is>
@@ -12786,7 +14763,10 @@
       <c r="D585" s="4" t="n">
         <v>0.7291666666666666</v>
       </c>
-      <c r="E585" s="2" t="inlineStr">
+      <c r="E585" s="5" t="n">
+        <v>12.45</v>
+      </c>
+      <c r="F585" s="2" t="inlineStr">
         <is>
           <t>extra punch: 07:09</t>
         </is>
@@ -12807,7 +14787,10 @@
       <c r="D586" s="4" t="n">
         <v>0.6729166666666667</v>
       </c>
-      <c r="E586" s="2" t="inlineStr">
+      <c r="E586" s="5" t="n">
+        <v>13.53</v>
+      </c>
+      <c r="F586" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -12828,7 +14811,10 @@
       <c r="D587" s="4" t="n">
         <v>0.7479166666666667</v>
       </c>
-      <c r="E587" s="2" t="inlineStr">
+      <c r="E587" s="5" t="n">
+        <v>12.13</v>
+      </c>
+      <c r="F587" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -12849,7 +14835,10 @@
       <c r="D588" s="4" t="n">
         <v>0.7465277777777778</v>
       </c>
-      <c r="E588" s="2" t="inlineStr">
+      <c r="E588" s="5" t="n">
+        <v>12.18</v>
+      </c>
+      <c r="F588" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -12870,7 +14859,10 @@
       <c r="D589" s="4" t="n">
         <v>0.75</v>
       </c>
-      <c r="E589" s="2" t="inlineStr">
+      <c r="E589" s="5" t="n">
+        <v>12.28</v>
+      </c>
+      <c r="F589" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -12891,32 +14883,40 @@
       <c r="D590" s="4" t="n">
         <v>0.75</v>
       </c>
-      <c r="E590" s="2" t="inlineStr">
+      <c r="E590" s="5" t="n">
+        <v>12.15</v>
+      </c>
+      <c r="F590" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="591">
-      <c r="A591" s="5" t="inlineStr">
+      <c r="A591" s="6" t="inlineStr">
         <is>
           <t>44</t>
         </is>
       </c>
-      <c r="B591" s="6" t="n">
+      <c r="B591" s="7" t="n">
         <v>46248</v>
       </c>
-      <c r="C591" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D591" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E591" s="5" t="inlineStr">
+      <c r="C591" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D591" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E591" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F591" s="6" t="inlineStr">
         <is>
           <t>No entry</t>
         </is>
@@ -12937,7 +14937,10 @@
       <c r="D592" s="4" t="n">
         <v>0.7506944444444444</v>
       </c>
-      <c r="E592" s="2" t="inlineStr">
+      <c r="E592" s="5" t="n">
+        <v>11.58</v>
+      </c>
+      <c r="F592" s="2" t="inlineStr">
         <is>
           <t>extra punch: 06:05</t>
         </is>
@@ -12958,7 +14961,10 @@
       <c r="D593" s="4" t="n">
         <v>0.7458333333333333</v>
       </c>
-      <c r="E593" s="2" t="inlineStr">
+      <c r="E593" s="5" t="n">
+        <v>12.25</v>
+      </c>
+      <c r="F593" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -12979,7 +14985,10 @@
       <c r="D594" s="4" t="n">
         <v>0.7555555555555555</v>
       </c>
-      <c r="E594" s="2" t="inlineStr">
+      <c r="E594" s="5" t="n">
+        <v>11.97</v>
+      </c>
+      <c r="F594" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -13000,7 +15009,10 @@
       <c r="D595" s="4" t="n">
         <v>0.7611111111111111</v>
       </c>
-      <c r="E595" s="2" t="inlineStr">
+      <c r="E595" s="5" t="n">
+        <v>11.48</v>
+      </c>
+      <c r="F595" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -13021,7 +15033,10 @@
       <c r="D596" s="4" t="n">
         <v>0.7423611111111111</v>
       </c>
-      <c r="E596" s="2" t="inlineStr">
+      <c r="E596" s="5" t="n">
+        <v>12.25</v>
+      </c>
+      <c r="F596" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -13042,32 +15057,40 @@
       <c r="D597" s="4" t="n">
         <v>0.7451388888888889</v>
       </c>
-      <c r="E597" s="2" t="inlineStr">
+      <c r="E597" s="5" t="n">
+        <v>12.32</v>
+      </c>
+      <c r="F597" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="598">
-      <c r="A598" s="5" t="inlineStr">
+      <c r="A598" s="6" t="inlineStr">
         <is>
           <t>44</t>
         </is>
       </c>
-      <c r="B598" s="6" t="n">
+      <c r="B598" s="7" t="n">
         <v>46255</v>
       </c>
-      <c r="C598" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D598" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E598" s="5" t="inlineStr">
+      <c r="C598" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D598" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E598" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F598" s="6" t="inlineStr">
         <is>
           <t>No entry</t>
         </is>
@@ -13088,7 +15111,10 @@
       <c r="D599" s="4" t="n">
         <v>0.74375</v>
       </c>
-      <c r="E599" s="2" t="inlineStr">
+      <c r="E599" s="5" t="n">
+        <v>11.92</v>
+      </c>
+      <c r="F599" s="2" t="inlineStr">
         <is>
           <t>extra punches: 17:51 06:13</t>
         </is>
@@ -13109,7 +15135,10 @@
       <c r="D600" s="4" t="n">
         <v>0.75</v>
       </c>
-      <c r="E600" s="2" t="inlineStr">
+      <c r="E600" s="5" t="n">
+        <v>11.77</v>
+      </c>
+      <c r="F600" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -13130,7 +15159,10 @@
       <c r="D601" s="4" t="n">
         <v>0.7513888888888889</v>
       </c>
-      <c r="E601" s="2" t="inlineStr">
+      <c r="E601" s="5" t="n">
+        <v>11.53</v>
+      </c>
+      <c r="F601" s="2" t="inlineStr">
         <is>
           <t>extra punch: 18:02</t>
         </is>
@@ -13151,7 +15183,10 @@
       <c r="D602" s="4" t="n">
         <v>0.7541666666666667</v>
       </c>
-      <c r="E602" s="2" t="inlineStr">
+      <c r="E602" s="5" t="n">
+        <v>14.43</v>
+      </c>
+      <c r="F602" s="2" t="inlineStr">
         <is>
           <t>extra punch: 06:33</t>
         </is>
@@ -13172,7 +15207,10 @@
       <c r="D603" s="4" t="n">
         <v>0.7541666666666667</v>
       </c>
-      <c r="E603" s="2" t="inlineStr">
+      <c r="E603" s="5" t="n">
+        <v>12.03</v>
+      </c>
+      <c r="F603" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -13193,32 +15231,40 @@
       <c r="D604" s="4" t="n">
         <v>0.7569444444444444</v>
       </c>
-      <c r="E604" s="2" t="inlineStr">
+      <c r="E604" s="5" t="n">
+        <v>12.37</v>
+      </c>
+      <c r="F604" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="605">
-      <c r="A605" s="5" t="inlineStr">
+      <c r="A605" s="6" t="inlineStr">
         <is>
           <t>44</t>
         </is>
       </c>
-      <c r="B605" s="6" t="n">
+      <c r="B605" s="7" t="n">
         <v>46262</v>
       </c>
-      <c r="C605" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D605" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E605" s="5" t="inlineStr">
+      <c r="C605" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D605" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E605" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F605" s="6" t="inlineStr">
         <is>
           <t>No entry</t>
         </is>
@@ -13239,7 +15285,10 @@
       <c r="D606" s="4" t="n">
         <v>0.7444444444444445</v>
       </c>
-      <c r="E606" s="2" t="inlineStr">
+      <c r="E606" s="5" t="n">
+        <v>11.42</v>
+      </c>
+      <c r="F606" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -13260,7 +15309,10 @@
       <c r="D607" s="4" t="n">
         <v>0.7458333333333333</v>
       </c>
-      <c r="E607" s="2" t="inlineStr">
+      <c r="E607" s="5" t="n">
+        <v>12.23</v>
+      </c>
+      <c r="F607" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -13281,7 +15333,10 @@
       <c r="D608" s="4" t="n">
         <v>0.7527777777777778</v>
       </c>
-      <c r="E608" s="2" t="inlineStr">
+      <c r="E608" s="5" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="F608" s="2" t="inlineStr">
         <is>
           <t>corrected from a clearer re-scan photo later in the album</t>
         </is>
